--- a/reports/screener_2026-08-27.xlsx
+++ b/reports/screener_2026-08-27.xlsx
@@ -1186,10 +1186,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.868716032846779</v>
+        <v>5.86871600316745</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646824093077</v>
+        <v>10.88646818587562</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.21781573324146</v>
@@ -1198,7 +1198,7 @@
         <v>27.66761889587421</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.26108670948989</v>
+        <v>71.26108658508552</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -1268,7 +1268,7 @@
         <v>-4.94053016263244</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-26.59162359529691</v>
+        <v>-26.59161854099229</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
@@ -1512,10 +1512,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01485127426129</v>
+        <v>15.01485115023178</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85254911375469</v>
+        <v>27.85254888367994</v>
       </c>
       <c r="BZ3" t="n">
         <v>39.46006465010361</v>
@@ -1524,13 +1524,13 @@
         <v>23.87433491384053</v>
       </c>
       <c r="CB3" t="n">
-        <v>76.71128032987153</v>
+        <v>76.71128055869886</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.54748517967845</v>
+        <v>48.54748526964112</v>
       </c>
       <c r="CD3" t="n">
-        <v>27.26172491273605</v>
+        <v>27.26172529540181</v>
       </c>
       <c r="CE3" t="n">
         <v>8.973116408407053</v>
@@ -1830,10 +1830,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388473973969</v>
+        <v>16.25388479636543</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.15095619221712</v>
+        <v>30.15095629725787</v>
       </c>
       <c r="BZ4" t="n">
         <v>70.99454413334874</v>
@@ -1842,19 +1842,19 @@
         <v>51.39538022233962</v>
       </c>
       <c r="CB4" t="n">
-        <v>124.8365656449476</v>
+        <v>124.8365656247644</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.69771469791199</v>
+        <v>25.69771468978261</v>
       </c>
       <c r="CD4" t="n">
-        <v>61.55225165406679</v>
+        <v>61.55225153257966</v>
       </c>
       <c r="CE4" t="n">
         <v>43.02986521586298</v>
       </c>
       <c r="CF4" t="n">
-        <v>47.13678535262454</v>
+        <v>47.13678534852858</v>
       </c>
       <c r="CG4" t="n">
         <v>47.2126227191013</v>
@@ -1875,7 +1875,7 @@
         <v>73.15142160530792</v>
       </c>
       <c r="CM4" t="n">
-        <v>92.0814327386573</v>
+        <v>92.08143272196634</v>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         <v>4.059999942779541</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.548072845498024</v>
+        <v>3.54807282876565</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.581675128398835</v>
+        <v>6.58167509736028</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.56892505650208</v>
@@ -2168,25 +2168,25 @@
         <v>8.462578627869229</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.40274522527432</v>
+        <v>24.40274523688278</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.26517502718242</v>
+        <v>11.26517503412428</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.57787749431459</v>
+        <v>10.57787753601435</v>
       </c>
       <c r="CE5" t="n">
         <v>5.216748691568468</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.11216333763927</v>
+        <v>9.112163340573114</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.52022806109191</v>
+        <v>9.520228081941788</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.568205254982718</v>
+        <v>8.56820527374761</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -2198,10 +2198,10 @@
         <v>6.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>111.0395412743969</v>
+        <v>111.0395417365863</v>
       </c>
       <c r="CM5" t="n">
-        <v>124.4375237946663</v>
+        <v>124.4375238669285</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294910810901</v>
+        <v>18.38294915543341</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037059554221</v>
+        <v>34.10037068332898</v>
       </c>
       <c r="BZ6" t="n">
         <v>75.02112937085505</v>
@@ -2478,23 +2478,23 @@
         <v>56.1385860856476</v>
       </c>
       <c r="CB6" t="n">
-        <v>100.7448469377449</v>
+        <v>100.7448468641835</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.40370000702437</v>
+        <v>48.4036999955209</v>
       </c>
       <c r="CD6" t="n">
-        <v>59.46380262122727</v>
+        <v>59.46380252610901</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>43.97703727038266</v>
+        <v>43.97703730128458</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.25203530128329</v>
+        <v>41.25203533942494</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.12683177115496</v>
+        <v>37.12683180548245</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -2506,10 +2506,10 @@
         <v>4.1</v>
       </c>
       <c r="CL6" t="n">
-        <v>-23.03725025008134</v>
+        <v>-23.03725017892155</v>
       </c>
       <c r="CM6" t="n">
-        <v>-8.836990588221772</v>
+        <v>-8.836990524163069</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
         <v>4.380000114440918</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774201436924</v>
+        <v>3.052774220937844</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.662896143665495</v>
+        <v>5.6628961798397</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.64379118003097</v>
@@ -2804,7 +2804,7 @@
         <v>8.50525545154361</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.62501972477794</v>
+        <v>23.62501978425786</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -2816,7 +2816,7 @@
         <v>5.24246353170767</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.25728133204965</v>
+        <v>11.25728134571453</v>
       </c>
       <c r="CG7" t="n">
         <v>11.54640553044338</v>
@@ -2837,7 +2837,7 @@
         <v>137.2549019607844</v>
       </c>
       <c r="CM7" t="n">
-        <v>157.0155488109292</v>
+        <v>157.0155491229127</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -3122,10 +3122,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX8" t="n">
-        <v>121.1494721699117</v>
+        <v>121.1494725411449</v>
       </c>
       <c r="BY8" t="n">
-        <v>224.7322708751862</v>
+        <v>224.7322715638238</v>
       </c>
       <c r="BZ8" t="n">
         <v>136.6302942100011</v>
@@ -3146,13 +3146,13 @@
         <v>57.66739801003497</v>
       </c>
       <c r="CF8" t="n">
-        <v>116.3031158084362</v>
+        <v>116.3031159598463</v>
       </c>
       <c r="CG8" t="n">
-        <v>121.1494721699117</v>
+        <v>121.1494725411449</v>
       </c>
       <c r="CH8" t="n">
-        <v>109.0345249529205</v>
+        <v>109.0345252870304</v>
       </c>
       <c r="CI8" t="n">
         <v>7</v>
@@ -3164,10 +3164,10 @@
         <v>5.5</v>
       </c>
       <c r="CL8" t="n">
-        <v>163.6868899068033</v>
+        <v>163.686890714808</v>
       </c>
       <c r="CM8" t="n">
-        <v>181.2651030234609</v>
+        <v>181.2651033896281</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -3450,10 +3450,10 @@
         <v>15.75</v>
       </c>
       <c r="BX9" t="n">
-        <v>6.426879109893282</v>
+        <v>6.426879087734028</v>
       </c>
       <c r="BY9" t="n">
-        <v>11.92186074885204</v>
+        <v>11.92186070774662</v>
       </c>
       <c r="BZ9" t="n">
         <v>25.54314565483476</v>
@@ -3462,19 +3462,19 @@
         <v>18.71731215268055</v>
       </c>
       <c r="CB9" t="n">
-        <v>35.49020390929299</v>
+        <v>35.49020394518685</v>
       </c>
       <c r="CC9" t="n">
-        <v>12.30123101826934</v>
+        <v>12.30123102245168</v>
       </c>
       <c r="CD9" t="n">
-        <v>20.53560232491412</v>
+        <v>20.53560237134395</v>
       </c>
       <c r="CE9" t="n">
         <v>18.47523885586486</v>
       </c>
       <c r="CF9" t="n">
-        <v>20.42637066638695</v>
+        <v>20.42637067287276</v>
       </c>
       <c r="CG9" t="n">
         <v>18.71731215268055</v>
@@ -3495,7 +3495,7 @@
         <v>6.956069443888868</v>
       </c>
       <c r="CM9" t="n">
-        <v>29.69124232626637</v>
+        <v>29.69124236744607</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -3778,37 +3778,37 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX10" t="n">
-        <v>24.20136282954487</v>
+        <v>24.20136286936076</v>
       </c>
       <c r="BY10" t="n">
-        <v>37.09024834900521</v>
+        <v>37.09024797787244</v>
       </c>
       <c r="BZ10" t="n">
-        <v>39.76038163298968</v>
+        <v>39.76038116972554</v>
       </c>
       <c r="CA10" t="n">
         <v>21.15376420319533</v>
       </c>
       <c r="CB10" t="n">
-        <v>53.96364536039312</v>
+        <v>53.96364505251905</v>
       </c>
       <c r="CC10" t="n">
-        <v>51.52714067805403</v>
+        <v>51.52714062780147</v>
       </c>
       <c r="CD10" t="n">
-        <v>19.88022358695261</v>
+        <v>19.88022335437046</v>
       </c>
       <c r="CE10" t="n">
         <v>24.52549486359719</v>
       </c>
       <c r="CF10" t="n">
-        <v>34.01278268796651</v>
+        <v>34.01278251480528</v>
       </c>
       <c r="CG10" t="n">
-        <v>30.8078716063012</v>
+        <v>30.80787142073481</v>
       </c>
       <c r="CH10" t="n">
-        <v>27.72708444567108</v>
+        <v>27.72708427866133</v>
       </c>
       <c r="CI10" t="n">
         <v>8</v>
@@ -3820,10 +3820,10 @@
         <v>2.7</v>
       </c>
       <c r="CL10" t="n">
-        <v>-14.89538708606791</v>
+        <v>-14.8953875986822</v>
       </c>
       <c r="CM10" t="n">
-        <v>4.39773105091148</v>
+        <v>4.397730519416032</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -4114,10 +4114,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.05538999516349</v>
+        <v>46.05538998425735</v>
       </c>
       <c r="BY11" t="n">
-        <v>85.43274844102828</v>
+        <v>85.43274842079738</v>
       </c>
       <c r="BZ11" t="n">
         <v>69.47297200868543</v>
@@ -4138,7 +4138,7 @@
         <v>25.94666723750103</v>
       </c>
       <c r="CF11" t="n">
-        <v>78.49436730847503</v>
+        <v>78.49436730402689</v>
       </c>
       <c r="CG11" t="n">
         <v>69.47297200868543</v>
@@ -4159,7 +4159,7 @@
         <v>89.58664546899841</v>
       </c>
       <c r="CM11" t="n">
-        <v>138.0059684596116</v>
+        <v>138.0059684461242</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX12" t="n">
-        <v>127.6301643215276</v>
+        <v>127.6301659713547</v>
       </c>
       <c r="BY12" t="n">
-        <v>236.7539548164336</v>
+        <v>236.7539578768629</v>
       </c>
       <c r="BZ12" t="n">
         <v>137.215088724016</v>
@@ -4468,13 +4468,13 @@
         <v>56.54612056896573</v>
       </c>
       <c r="CF12" t="n">
-        <v>142.9573011925048</v>
+        <v>142.9573017812868</v>
       </c>
       <c r="CG12" t="n">
-        <v>126.4680094649372</v>
+        <v>126.4680102898507</v>
       </c>
       <c r="CH12" t="n">
-        <v>113.8212085184434</v>
+        <v>113.8212092608657</v>
       </c>
       <c r="CI12" t="n">
         <v>8</v>
@@ -4486,10 +4486,10 @@
         <v>5.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>147.5450405646253</v>
+        <v>147.5450421792887</v>
       </c>
       <c r="CM12" t="n">
-        <v>210.9119239141944</v>
+        <v>210.9119251947122</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -4754,10 +4754,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX13" t="n">
-        <v>13.15731121066379</v>
+        <v>13.15731119057001</v>
       </c>
       <c r="BY13" t="n">
-        <v>24.40681229578133</v>
+        <v>24.40681225850738</v>
       </c>
       <c r="BZ13" t="n">
         <v>19.90620030713044</v>
@@ -4766,7 +4766,7 @@
         <v>12.44114419785431</v>
       </c>
       <c r="CB13" t="n">
-        <v>33.68872442204027</v>
+        <v>33.6887243999592</v>
       </c>
       <c r="CC13" t="n">
         <v>22.8984489302328</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="CE13" t="inlineStr"/>
       <c r="CF13" t="n">
-        <v>20.09219318595209</v>
+        <v>20.09219317161016</v>
       </c>
       <c r="CG13" t="n">
         <v>21.40232461868162</v>
@@ -4797,7 +4797,7 @@
         <v>0.6378932657179259</v>
       </c>
       <c r="CM13" t="n">
-        <v>4.974889376530656</v>
+        <v>4.974889301598906</v>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
@@ -4815,7 +4815,11 @@
         </is>
       </c>
       <c r="CQ13" t="inlineStr"/>
-      <c r="CR13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="CS13" t="b">
         <v>0</v>
       </c>
@@ -4842,14 +4846,14 @@
         <v>1</v>
       </c>
       <c r="DB13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD13" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.1%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -5080,10 +5084,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX14" t="n">
-        <v>3.363729732811315</v>
+        <v>3.363729732909307</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.23971865436499</v>
+        <v>6.239718654546764</v>
       </c>
       <c r="BZ14" t="n">
         <v>20.7379196371351</v>
@@ -5092,7 +5096,7 @@
         <v>14.20601824710207</v>
       </c>
       <c r="CB14" t="n">
-        <v>33.37021289880997</v>
+        <v>33.37021289909818</v>
       </c>
       <c r="CC14" t="n">
         <v>10.95072400487419</v>
@@ -5406,10 +5410,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX15" t="n">
-        <v>10.74426547264768</v>
+        <v>10.74426541307544</v>
       </c>
       <c r="BY15" t="n">
-        <v>19.93061245176145</v>
+        <v>19.93061234125494</v>
       </c>
       <c r="BZ15" t="n">
         <v>37.5845483977432</v>
@@ -5418,25 +5422,25 @@
         <v>37.1651975122017</v>
       </c>
       <c r="CB15" t="n">
-        <v>41.90042983968529</v>
+        <v>41.90042981465468</v>
       </c>
       <c r="CC15" t="n">
-        <v>34.50408897775664</v>
+        <v>34.50408899034814</v>
       </c>
       <c r="CD15" t="n">
-        <v>18.61582866217975</v>
+        <v>18.61582873127402</v>
       </c>
       <c r="CE15" t="n">
         <v>31.97921770241074</v>
       </c>
       <c r="CF15" t="n">
-        <v>31.66856050624839</v>
+        <v>31.66856049855534</v>
       </c>
       <c r="CG15" t="n">
-        <v>34.50408897775664</v>
+        <v>34.50408899034814</v>
       </c>
       <c r="CH15" t="n">
-        <v>31.05368007998098</v>
+        <v>31.05368009131333</v>
       </c>
       <c r="CI15" t="n">
         <v>7</v>
@@ -5448,10 +5452,10 @@
         <v>3.9</v>
       </c>
       <c r="CL15" t="n">
-        <v>77.14591479530242</v>
+        <v>77.14591485994788</v>
       </c>
       <c r="CM15" t="n">
-        <v>80.65350408328136</v>
+        <v>80.65350403939631</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -5490,7 +5494,7 @@
         <v>-5.040678244190966</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-23.2212515115939</v>
+        <v>-23.22124503926587</v>
       </c>
       <c r="DA15" t="b">
         <v>1</v>
@@ -5736,10 +5740,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX16" t="n">
-        <v>5.044350364577175</v>
+        <v>5.044350330400213</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.357269926290659</v>
+        <v>9.357269862892394</v>
       </c>
       <c r="BZ16" t="n">
         <v>8.531826591579675</v>
@@ -6054,37 +6058,37 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX17" t="n">
-        <v>10.37863321319145</v>
+        <v>10.37863321725536</v>
       </c>
       <c r="BY17" t="n">
-        <v>18.0755304925735</v>
+        <v>18.07553048217811</v>
       </c>
       <c r="BZ17" t="n">
-        <v>23.22146474366123</v>
+        <v>23.22146472121366</v>
       </c>
       <c r="CA17" t="n">
         <v>17.75681071950086</v>
       </c>
       <c r="CB17" t="n">
-        <v>36.48041911177744</v>
+        <v>36.48041910786196</v>
       </c>
       <c r="CC17" t="n">
-        <v>24.12244063019823</v>
+        <v>24.12244062846323</v>
       </c>
       <c r="CD17" t="n">
-        <v>11.46100443647042</v>
+        <v>11.46100442756559</v>
       </c>
       <c r="CE17" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF17" t="n">
-        <v>18.9820378755063</v>
+        <v>18.9820378700895</v>
       </c>
       <c r="CG17" t="n">
-        <v>17.91617060603718</v>
+        <v>17.91617060083949</v>
       </c>
       <c r="CH17" t="n">
-        <v>16.12455354543346</v>
+        <v>16.12455354075554</v>
       </c>
       <c r="CI17" t="n">
         <v>8</v>
@@ -6096,10 +6100,10 @@
         <v>3.5</v>
       </c>
       <c r="CL17" t="n">
-        <v>55.64241389757998</v>
+        <v>55.64241385242625</v>
       </c>
       <c r="CM17" t="n">
-        <v>83.22430988954679</v>
+        <v>83.2243098372611</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -6382,10 +6386,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX18" t="n">
-        <v>3.454302382686342</v>
+        <v>3.454302383090375</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.407730919883164</v>
+        <v>6.407730920632644</v>
       </c>
       <c r="BZ18" t="n">
         <v>20.16620865234961</v>
@@ -6394,13 +6398,13 @@
         <v>19.00949927082382</v>
       </c>
       <c r="CB18" t="n">
-        <v>21.6058827163297</v>
+        <v>21.60588271629159</v>
       </c>
       <c r="CC18" t="n">
-        <v>15.92827012512917</v>
+        <v>15.9282701250515</v>
       </c>
       <c r="CD18" t="n">
-        <v>13.47116575685435</v>
+        <v>13.471165756342</v>
       </c>
       <c r="CE18" t="n">
         <v>30.336208848481</v>
@@ -6604,13 +6608,13 @@
         <v>1</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="AS19" t="b">
         <v>1</v>
       </c>
       <c r="AT19" t="n">
-        <v>3602869248</v>
+        <v>5725241856</v>
       </c>
       <c r="AU19" t="n">
         <v>6.7</v>
@@ -6700,10 +6704,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX19" t="n">
-        <v>9.774107146014483</v>
+        <v>9.774107130994336</v>
       </c>
       <c r="BY19" t="n">
-        <v>18.13096875585686</v>
+        <v>18.1309687279945</v>
       </c>
       <c r="BZ19" t="n">
         <v>22.32723873053024</v>
@@ -6712,25 +6716,25 @@
         <v>13.19107667093893</v>
       </c>
       <c r="CB19" t="n">
-        <v>32.07171951973582</v>
+        <v>32.07171956569217</v>
       </c>
       <c r="CC19" t="n">
-        <v>25.27239702552844</v>
+        <v>25.27239703637801</v>
       </c>
       <c r="CD19" t="n">
-        <v>11.82328977684374</v>
+        <v>11.82328982545854</v>
       </c>
       <c r="CE19" t="n">
         <v>9.733055502947964</v>
       </c>
       <c r="CF19" t="n">
-        <v>17.79048164104956</v>
+        <v>17.79048164886684</v>
       </c>
       <c r="CG19" t="n">
-        <v>15.6610227133979</v>
+        <v>15.66102269946671</v>
       </c>
       <c r="CH19" t="n">
-        <v>14.09492044205811</v>
+        <v>14.09492042952004</v>
       </c>
       <c r="CI19" t="n">
         <v>8</v>
@@ -6742,10 +6746,10 @@
         <v>3.3</v>
       </c>
       <c r="CL19" t="n">
-        <v>24.84429131693913</v>
+        <v>24.8442912058845</v>
       </c>
       <c r="CM19" t="n">
-        <v>57.57734013428295</v>
+        <v>57.57734020352368</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -7028,10 +7032,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX20" t="n">
-        <v>7.290978518749648</v>
+        <v>7.290978496927618</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.5247651522806</v>
+        <v>13.52476511180073</v>
       </c>
       <c r="BZ20" t="n">
         <v>35.92512375028262</v>
@@ -7040,19 +7044,19 @@
         <v>28.41024685094796</v>
       </c>
       <c r="CB20" t="n">
-        <v>44.74749254244985</v>
+        <v>44.74749257504084</v>
       </c>
       <c r="CC20" t="n">
-        <v>26.46268145282235</v>
+        <v>26.46268145824689</v>
       </c>
       <c r="CD20" t="n">
-        <v>29.04887753344142</v>
+        <v>29.04887757284678</v>
       </c>
       <c r="CE20" t="n">
         <v>24.98203479043206</v>
       </c>
       <c r="CF20" t="n">
-        <v>29.01446029609383</v>
+        <v>29.01446030137112</v>
       </c>
       <c r="CG20" t="n">
         <v>28.41024685094796</v>
@@ -7073,7 +7077,7 @@
         <v>-7.088583791648039</v>
       </c>
       <c r="CM20" t="n">
-        <v>5.430449903602952</v>
+        <v>5.430449922779168</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -7187,7 +7191,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -7336,10 +7340,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX21" t="n">
-        <v>35.62892565405816</v>
+        <v>35.6289255576336</v>
       </c>
       <c r="BY21" t="n">
-        <v>51.87571575230869</v>
+        <v>51.87571561191452</v>
       </c>
       <c r="BZ21" t="n">
         <v>48.56662855571916</v>
@@ -7356,13 +7360,13 @@
       </c>
       <c r="CE21" t="inlineStr"/>
       <c r="CF21" t="n">
-        <v>48.89385873647593</v>
+        <v>48.89385867727125</v>
       </c>
       <c r="CG21" t="n">
-        <v>50.22117215401393</v>
+        <v>50.22117208381684</v>
       </c>
       <c r="CH21" t="n">
-        <v>45.19905493861253</v>
+        <v>45.19905487543516</v>
       </c>
       <c r="CI21" t="n">
         <v>4</v>
@@ -7374,10 +7378,10 @@
         <v>1.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>16.19293872917478</v>
+        <v>16.19293856676509</v>
       </c>
       <c r="CM21" t="n">
-        <v>25.69114863388486</v>
+        <v>25.69114848168772</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -7395,7 +7399,11 @@
         </is>
       </c>
       <c r="CQ21" t="inlineStr"/>
-      <c r="CR21" t="inlineStr"/>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="CS21" t="b">
         <v>0</v>
       </c>
@@ -7422,14 +7430,14 @@
         <v>1</v>
       </c>
       <c r="DB21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD21" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -7660,10 +7668,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.10874053265072</v>
+        <v>3.108740526292904</v>
       </c>
       <c r="BY22" t="n">
-        <v>5.766713688067086</v>
+        <v>5.766713676273336</v>
       </c>
       <c r="BZ22" t="n">
         <v>31.95928917556512</v>
@@ -7672,7 +7680,7 @@
         <v>26.70105358379499</v>
       </c>
       <c r="CB22" t="n">
-        <v>40.93687026005173</v>
+        <v>40.93687025032393</v>
       </c>
       <c r="CC22" t="n">
         <v>10.85340539909456</v>
@@ -7978,10 +7986,10 @@
         <v>32.75</v>
       </c>
       <c r="BX23" t="n">
-        <v>3.249356687194955</v>
+        <v>3.24935669499341</v>
       </c>
       <c r="BY23" t="n">
-        <v>6.027556654746641</v>
+        <v>6.027556669212775</v>
       </c>
       <c r="BZ23" t="n">
         <v>32.74999999999999</v>
@@ -7990,7 +7998,7 @@
         <v>22.94333650394972</v>
       </c>
       <c r="CB23" t="n">
-        <v>40.50875423552675</v>
+        <v>40.50875424376662</v>
       </c>
       <c r="CC23" t="n">
         <v>10.59424454785779</v>
@@ -8056,7 +8064,7 @@
         <v>0.738239590458023</v>
       </c>
       <c r="CZ23" t="n">
-        <v>-31.318349352401</v>
+        <v>-31.31834368818209</v>
       </c>
       <c r="DA23" t="b">
         <v>1</v>
@@ -8280,35 +8288,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX24" t="n">
-        <v>8.627042048386361</v>
+        <v>8.627042062321403</v>
       </c>
       <c r="BY24" t="n">
-        <v>13.85196406791223</v>
+        <v>13.85196405170026</v>
       </c>
       <c r="BZ24" t="n">
-        <v>18.49124807290187</v>
+        <v>18.49124802139176</v>
       </c>
       <c r="CA24" t="n">
         <v>17.39822241629838</v>
       </c>
       <c r="CB24" t="n">
-        <v>22.98547050967757</v>
+        <v>22.98547049638615</v>
       </c>
       <c r="CC24" t="n">
-        <v>17.3368128665782</v>
+        <v>17.33681286270502</v>
       </c>
       <c r="CD24" t="n">
-        <v>9.229677303930041</v>
+        <v>9.229677280189192</v>
       </c>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="n">
-        <v>14.57676676394466</v>
+        <v>14.57676674952961</v>
       </c>
       <c r="CG24" t="n">
-        <v>15.59438846724522</v>
+        <v>15.59438845720264</v>
       </c>
       <c r="CH24" t="n">
-        <v>14.0349496205207</v>
+        <v>14.03494961148238</v>
       </c>
       <c r="CI24" t="n">
         <v>4</v>
@@ -8320,10 +8328,10 @@
         <v>2.1</v>
       </c>
       <c r="CL24" t="n">
-        <v>9.221394582678144</v>
+        <v>9.221394512341053</v>
       </c>
       <c r="CM24" t="n">
-        <v>13.43787028181735</v>
+        <v>13.43787016963798</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -8590,10 +8598,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX25" t="n">
-        <v>9.186485019046415</v>
+        <v>9.186484952657352</v>
       </c>
       <c r="BY25" t="n">
-        <v>17.0409297103311</v>
+        <v>17.04092958717939</v>
       </c>
       <c r="BZ25" t="n">
         <v>30.69514051126462</v>
@@ -8602,23 +8610,23 @@
         <v>29.25728964348931</v>
       </c>
       <c r="CB25" t="n">
-        <v>34.71948757568801</v>
+        <v>34.71948756133753</v>
       </c>
       <c r="CC25" t="n">
-        <v>25.51046012997303</v>
+        <v>25.51046014357987</v>
       </c>
       <c r="CD25" t="n">
-        <v>15.34133392427264</v>
+        <v>15.34133400682346</v>
       </c>
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="n">
-        <v>20.6082538426538</v>
+        <v>20.60825379867031</v>
       </c>
       <c r="CG25" t="n">
-        <v>21.27569492015207</v>
+        <v>21.27569486537963</v>
       </c>
       <c r="CH25" t="n">
-        <v>19.14812542813686</v>
+        <v>19.14812537884167</v>
       </c>
       <c r="CI25" t="n">
         <v>4</v>
@@ -8630,10 +8638,10 @@
         <v>3.3</v>
       </c>
       <c r="CL25" t="n">
-        <v>29.55430158379006</v>
+        <v>29.55430125026371</v>
       </c>
       <c r="CM25" t="n">
-        <v>39.43338440447295</v>
+        <v>39.43338410688506</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -8898,10 +8906,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX26" t="n">
-        <v>20.16127570477438</v>
+        <v>20.16127561026532</v>
       </c>
       <c r="BY26" t="n">
-        <v>37.39916643235646</v>
+        <v>37.39916625704217</v>
       </c>
       <c r="BZ26" t="n">
         <v>56.01071616333269</v>
@@ -8910,23 +8918,23 @@
         <v>42.36568036412405</v>
       </c>
       <c r="CB26" t="n">
-        <v>61.78700424729585</v>
+        <v>61.78700440252356</v>
       </c>
       <c r="CC26" t="n">
-        <v>45.16919928118866</v>
+        <v>45.16919931072515</v>
       </c>
       <c r="CD26" t="n">
-        <v>31.11427789412564</v>
+        <v>31.11427808083772</v>
       </c>
       <c r="CE26" t="inlineStr"/>
       <c r="CF26" t="n">
-        <v>39.68508939541304</v>
+        <v>39.68508933534133</v>
       </c>
       <c r="CG26" t="n">
-        <v>41.28418285677256</v>
+        <v>41.28418278388367</v>
       </c>
       <c r="CH26" t="n">
-        <v>37.1557645710953</v>
+        <v>37.1557645054953</v>
       </c>
       <c r="CI26" t="n">
         <v>4</v>
@@ -8938,10 +8946,10 @@
         <v>2.8</v>
       </c>
       <c r="CL26" t="n">
-        <v>-5.79166869967076</v>
+        <v>-5.791668865999378</v>
       </c>
       <c r="CM26" t="n">
-        <v>0.621426919974799</v>
+        <v>0.6214267676631469</v>
       </c>
       <c r="CN26" t="inlineStr">
         <is>
@@ -9224,10 +9232,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX27" t="n">
-        <v>6.975750787871223</v>
+        <v>6.975750796989641</v>
       </c>
       <c r="BY27" t="n">
-        <v>12.94001771150112</v>
+        <v>12.94001772841578</v>
       </c>
       <c r="BZ27" t="n">
         <v>5.584946345257502</v>
@@ -9248,7 +9256,7 @@
         <v>5.373183328823668</v>
       </c>
       <c r="CF27" t="n">
-        <v>7.287571955600599</v>
+        <v>7.287571958854734</v>
       </c>
       <c r="CG27" t="n">
         <v>5.859139839295418</v>
@@ -9269,7 +9277,7 @@
         <v>-10.31928991948218</v>
       </c>
       <c r="CM27" t="n">
-        <v>23.93829615245706</v>
+        <v>23.9382962077995</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -9552,37 +9560,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX28" t="n">
-        <v>16.91883605882122</v>
+        <v>16.91883609990701</v>
       </c>
       <c r="BY28" t="n">
-        <v>28.00431312808389</v>
+        <v>28.00431313303428</v>
       </c>
       <c r="BZ28" t="n">
-        <v>46.83168344484847</v>
+        <v>46.8316833394007</v>
       </c>
       <c r="CA28" t="n">
         <v>52.67243426197095</v>
       </c>
       <c r="CB28" t="n">
-        <v>55.69855922279349</v>
+        <v>55.69855923579338</v>
       </c>
       <c r="CC28" t="n">
-        <v>43.03544430153126</v>
+        <v>43.0354442939745</v>
       </c>
       <c r="CD28" t="n">
-        <v>23.30397207725829</v>
+        <v>23.30397203130465</v>
       </c>
       <c r="CE28" t="n">
         <v>30.43448362223624</v>
       </c>
       <c r="CF28" t="n">
-        <v>37.11246576469297</v>
+        <v>37.11246575220272</v>
       </c>
       <c r="CG28" t="n">
-        <v>36.73496396188375</v>
+        <v>36.73496395810537</v>
       </c>
       <c r="CH28" t="n">
-        <v>33.06146756569537</v>
+        <v>33.06146756229483</v>
       </c>
       <c r="CI28" t="n">
         <v>8</v>
@@ -9594,10 +9602,10 @@
         <v>3.3</v>
       </c>
       <c r="CL28" t="n">
-        <v>24.94886133649419</v>
+        <v>24.94886132364256</v>
       </c>
       <c r="CM28" t="n">
-        <v>40.25875679818684</v>
+        <v>40.25875675098256</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -9709,7 +9717,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -9880,37 +9888,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX29" t="n">
-        <v>5.939526969908054</v>
+        <v>5.939526962110235</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.534880603215935</v>
+        <v>8.534880609653715</v>
       </c>
       <c r="BZ29" t="n">
-        <v>10.8150154441064</v>
+        <v>10.81501546646275</v>
       </c>
       <c r="CA29" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB29" t="n">
-        <v>9.810403804227111</v>
+        <v>9.810403816800907</v>
       </c>
       <c r="CC29" t="n">
-        <v>14.90925677880722</v>
+        <v>14.90925678154334</v>
       </c>
       <c r="CD29" t="n">
-        <v>5.384140030600174</v>
+        <v>5.384140043226401</v>
       </c>
       <c r="CE29" t="n">
         <v>11.00534556207784</v>
       </c>
       <c r="CF29" t="n">
-        <v>9.757252263120744</v>
+        <v>9.757252269237304</v>
       </c>
       <c r="CG29" t="n">
-        <v>10.31270962416675</v>
+        <v>10.31270964163183</v>
       </c>
       <c r="CH29" t="n">
-        <v>9.281438661750078</v>
+        <v>9.281438677468648</v>
       </c>
       <c r="CI29" t="n">
         <v>8</v>
@@ -9922,10 +9930,10 @@
         <v>2.8</v>
       </c>
       <c r="CL29" t="n">
-        <v>-39.37662699304846</v>
+        <v>-39.37662689037982</v>
       </c>
       <c r="CM29" t="n">
-        <v>-36.26876554086321</v>
+        <v>-36.26876550091181</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -9943,7 +9951,11 @@
         </is>
       </c>
       <c r="CQ29" t="inlineStr"/>
-      <c r="CR29" t="inlineStr"/>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="CS29" t="b">
         <v>0</v>
       </c>
@@ -9970,14 +9982,14 @@
         <v>1</v>
       </c>
       <c r="DB29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD29" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.5%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -10208,37 +10220,37 @@
         <v>38.86000061035156</v>
       </c>
       <c r="BX30" t="n">
-        <v>30.97422547438646</v>
+        <v>30.97422560804202</v>
       </c>
       <c r="BY30" t="n">
-        <v>35.52640292494711</v>
+        <v>35.52640282107112</v>
       </c>
       <c r="BZ30" t="n">
-        <v>38.58971760703754</v>
+        <v>38.58971732768785</v>
       </c>
       <c r="CA30" t="n">
         <v>49.80959882281965</v>
       </c>
       <c r="CB30" t="n">
-        <v>60.09290038986127</v>
+        <v>60.09290023981547</v>
       </c>
       <c r="CC30" t="n">
-        <v>16.76379309441224</v>
+        <v>16.76379308121115</v>
       </c>
       <c r="CD30" t="n">
-        <v>17.31674469858584</v>
+        <v>17.31674446170541</v>
       </c>
       <c r="CE30" t="n">
         <v>28.40888631687585</v>
       </c>
       <c r="CF30" t="n">
-        <v>34.68528366611574</v>
+        <v>34.68528358490357</v>
       </c>
       <c r="CG30" t="n">
-        <v>33.25031419966679</v>
+        <v>33.25031421455657</v>
       </c>
       <c r="CH30" t="n">
-        <v>29.92528277970011</v>
+        <v>29.92528279310091</v>
       </c>
       <c r="CI30" t="n">
         <v>8</v>
@@ -10250,10 +10262,10 @@
         <v>3.6</v>
       </c>
       <c r="CL30" t="n">
-        <v>-22.99206816860269</v>
+        <v>-22.99206813411787</v>
       </c>
       <c r="CM30" t="n">
-        <v>-10.74296674901172</v>
+        <v>-10.74296695799828</v>
       </c>
       <c r="CN30" t="inlineStr">
         <is>
@@ -10440,7 +10452,7 @@
         <v>1</v>
       </c>
       <c r="AT31" t="n">
-        <v>184726978560</v>
+        <v>185049546752</v>
       </c>
       <c r="AU31" t="n">
         <v>7.27</v>
@@ -10518,35 +10530,35 @@
         <v>16.78000068664551</v>
       </c>
       <c r="BX31" t="n">
-        <v>9.985664108946926</v>
+        <v>9.985664045721835</v>
       </c>
       <c r="BY31" t="n">
-        <v>17.51097129326892</v>
+        <v>17.51097130396708</v>
       </c>
       <c r="BZ31" t="n">
-        <v>28.9109798047249</v>
+        <v>28.91098000544013</v>
       </c>
       <c r="CA31" t="n">
         <v>29.08689850705222</v>
       </c>
       <c r="CB31" t="n">
-        <v>32.08964773664928</v>
+        <v>32.0896477399672</v>
       </c>
       <c r="CC31" t="n">
-        <v>27.89695681486392</v>
+        <v>27.89695682918288</v>
       </c>
       <c r="CD31" t="n">
-        <v>14.24941551442479</v>
+        <v>14.2494155930414</v>
       </c>
       <c r="CE31" t="inlineStr"/>
       <c r="CF31" t="n">
-        <v>21.07614300545117</v>
+        <v>21.07614304607798</v>
       </c>
       <c r="CG31" t="n">
-        <v>22.70396405406642</v>
+        <v>22.70396406657498</v>
       </c>
       <c r="CH31" t="n">
-        <v>20.43356764865978</v>
+        <v>20.43356765991748</v>
       </c>
       <c r="CI31" t="n">
         <v>4</v>
@@ -10558,10 +10570,10 @@
         <v>2.9</v>
       </c>
       <c r="CL31" t="n">
-        <v>21.77334214844215</v>
+        <v>21.77334221553217</v>
       </c>
       <c r="CM31" t="n">
-        <v>25.60275412994935</v>
+        <v>25.60275437206383</v>
       </c>
       <c r="CN31" t="inlineStr">
         <is>
@@ -10600,7 +10612,7 @@
         <v>-7.744448996751174</v>
       </c>
       <c r="CZ31" t="n">
-        <v>-20.99429475986069</v>
+        <v>-20.99430923793453</v>
       </c>
       <c r="DA31" t="b">
         <v>1</v>
@@ -10844,37 +10856,37 @@
         <v>44.2400016784668</v>
       </c>
       <c r="BX32" t="n">
-        <v>32.08627708822074</v>
+        <v>32.08627715399735</v>
       </c>
       <c r="BY32" t="n">
-        <v>44.20766662732892</v>
+        <v>44.20766650010867</v>
       </c>
       <c r="BZ32" t="n">
-        <v>50.92127242261198</v>
+        <v>50.92127217168321</v>
       </c>
       <c r="CA32" t="n">
         <v>47.73853825853298</v>
       </c>
       <c r="CB32" t="n">
-        <v>70.56922577512088</v>
+        <v>70.56922563943867</v>
       </c>
       <c r="CC32" t="n">
-        <v>59.89362090459586</v>
+        <v>59.89362087737182</v>
       </c>
       <c r="CD32" t="n">
-        <v>25.15601731684175</v>
+        <v>25.15601716385589</v>
       </c>
       <c r="CE32" t="n">
         <v>76.57366731847841</v>
       </c>
       <c r="CF32" t="n">
-        <v>50.89328571396643</v>
+        <v>50.89328563543337</v>
       </c>
       <c r="CG32" t="n">
-        <v>49.32990534057248</v>
+        <v>49.32990521510809</v>
       </c>
       <c r="CH32" t="n">
-        <v>44.39691480651523</v>
+        <v>44.39691469359728</v>
       </c>
       <c r="CI32" t="n">
         <v>8</v>
@@ -10886,10 +10898,10 @@
         <v>3</v>
       </c>
       <c r="CL32" t="n">
-        <v>0.3546860806852292</v>
+        <v>0.3546858254457552</v>
       </c>
       <c r="CM32" t="n">
-        <v>15.03906822575469</v>
+        <v>15.03906804823874</v>
       </c>
       <c r="CN32" t="inlineStr">
         <is>
@@ -11154,10 +11166,10 @@
         <v>54.20000076293945</v>
       </c>
       <c r="BX33" t="n">
-        <v>10.59687583420033</v>
+        <v>10.59687590534817</v>
       </c>
       <c r="BY33" t="n">
-        <v>19.65720467244162</v>
+        <v>19.65720480442086</v>
       </c>
       <c r="BZ33" t="n">
         <v>62.12370329662177</v>
@@ -11166,7 +11178,7 @@
         <v>46.53820959650967</v>
       </c>
       <c r="CB33" t="n">
-        <v>83.16230736357235</v>
+        <v>83.16230744973755</v>
       </c>
       <c r="CC33" t="n">
         <v>11.76833333333333</v>
@@ -11176,7 +11188,7 @@
       </c>
       <c r="CE33" t="inlineStr"/>
       <c r="CF33" t="n">
-        <v>14.00747127999176</v>
+        <v>14.00747134770079</v>
       </c>
       <c r="CG33" t="n">
         <v>11.76833333333333</v>
@@ -11197,7 +11209,7 @@
         <v>-80.45848735994448</v>
       </c>
       <c r="CM33" t="n">
-        <v>-74.15595741177609</v>
+        <v>-74.15595728685167</v>
       </c>
       <c r="CN33" t="inlineStr">
         <is>
@@ -11462,10 +11474,10 @@
         <v>29.69000053405762</v>
       </c>
       <c r="BX34" t="n">
-        <v>15.52022457805166</v>
+        <v>15.52022458567649</v>
       </c>
       <c r="BY34" t="n">
-        <v>28.79001659228583</v>
+        <v>28.79001660642989</v>
       </c>
       <c r="BZ34" t="n">
         <v>54.71383964899351</v>
@@ -11474,23 +11486,23 @@
         <v>49.40805952371795</v>
       </c>
       <c r="CB34" t="n">
-        <v>60.9179064682199</v>
+        <v>60.91790646631788</v>
       </c>
       <c r="CC34" t="n">
-        <v>36.63500708690665</v>
+        <v>36.63500708552354</v>
       </c>
       <c r="CD34" t="n">
-        <v>30.3269633420922</v>
+        <v>30.32696333156444</v>
       </c>
       <c r="CE34" t="inlineStr"/>
       <c r="CF34" t="n">
-        <v>33.91477197655941</v>
+        <v>33.91477198165586</v>
       </c>
       <c r="CG34" t="n">
-        <v>32.71251183959625</v>
+        <v>32.71251184597671</v>
       </c>
       <c r="CH34" t="n">
-        <v>29.44126065563662</v>
+        <v>29.44126066137904</v>
       </c>
       <c r="CI34" t="n">
         <v>4</v>
@@ -11502,10 +11514,10 @@
         <v>3.5</v>
       </c>
       <c r="CL34" t="n">
-        <v>-0.8377900772876812</v>
+        <v>-0.8377900579464193</v>
       </c>
       <c r="CM34" t="n">
-        <v>14.22961053050684</v>
+        <v>14.22961054767235</v>
       </c>
       <c r="CN34" t="inlineStr">
         <is>
@@ -11790,10 +11802,10 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX35" t="n">
-        <v>13.08696650480585</v>
+        <v>13.08696646023153</v>
       </c>
       <c r="BY35" t="n">
-        <v>19.05462323099731</v>
+        <v>19.0546231660971</v>
       </c>
       <c r="BZ35" t="n">
         <v>16.71315021106592</v>
@@ -11812,7 +11824,7 @@
         <v>14.7644299189986</v>
       </c>
       <c r="CF35" t="n">
-        <v>16.15917317961202</v>
+        <v>16.15917316136627</v>
       </c>
       <c r="CG35" t="n">
         <v>15.73879006503226</v>
@@ -11833,7 +11845,7 @@
         <v>34.77555423456011</v>
       </c>
       <c r="CM35" t="n">
-        <v>53.75045506855527</v>
+        <v>53.7504548949515</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -12116,37 +12128,37 @@
         <v>18.63999938964844</v>
       </c>
       <c r="BX36" t="n">
-        <v>8.745140368994457</v>
+        <v>8.745140358007564</v>
       </c>
       <c r="BY36" t="n">
-        <v>9.206222538695553</v>
+        <v>9.206222539254405</v>
       </c>
       <c r="BZ36" t="n">
-        <v>9.666395044717083</v>
+        <v>9.666395057448174</v>
       </c>
       <c r="CA36" t="n">
         <v>16.93457208699175</v>
       </c>
       <c r="CB36" t="n">
-        <v>9.239151923695749</v>
+        <v>9.239151933083861</v>
       </c>
       <c r="CC36" t="n">
-        <v>17.54224666112583</v>
+        <v>17.54224666383774</v>
       </c>
       <c r="CD36" t="n">
-        <v>3.934238764415331</v>
+        <v>3.934238776984336</v>
       </c>
       <c r="CE36" t="n">
         <v>16.16233025852235</v>
       </c>
       <c r="CF36" t="n">
-        <v>11.42878720589476</v>
+        <v>11.42878720926627</v>
       </c>
       <c r="CG36" t="n">
-        <v>9.452773484206416</v>
+        <v>9.452773495266017</v>
       </c>
       <c r="CH36" t="n">
-        <v>8.507496135785775</v>
+        <v>8.507496145739415</v>
       </c>
       <c r="CI36" t="n">
         <v>8</v>
@@ -12158,10 +12170,10 @@
         <v>4.5</v>
       </c>
       <c r="CL36" t="n">
-        <v>-54.35892481568245</v>
+        <v>-54.3589247622831</v>
       </c>
       <c r="CM36" t="n">
-        <v>-38.68676190922174</v>
+        <v>-38.68676189113424</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -13000,10 +13012,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.868716032846779</v>
+        <v>5.86871600316745</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646824093077</v>
+        <v>10.88646818587562</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.21781573324146</v>
@@ -13012,7 +13024,7 @@
         <v>27.66761889587421</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.26108670948989</v>
+        <v>71.26108658508552</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -13082,7 +13094,7 @@
         <v>-4.94053016263244</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-26.59162359529691</v>
+        <v>-26.59161854099229</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
@@ -13326,10 +13338,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01485127426129</v>
+        <v>15.01485115023178</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85254911375469</v>
+        <v>27.85254888367994</v>
       </c>
       <c r="BZ3" t="n">
         <v>39.46006465010361</v>
@@ -13338,13 +13350,13 @@
         <v>23.87433491384053</v>
       </c>
       <c r="CB3" t="n">
-        <v>76.71128032987153</v>
+        <v>76.71128055869886</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.54748517967845</v>
+        <v>48.54748526964112</v>
       </c>
       <c r="CD3" t="n">
-        <v>27.26172491273605</v>
+        <v>27.26172529540181</v>
       </c>
       <c r="CE3" t="n">
         <v>8.973116408407053</v>
@@ -13644,10 +13656,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388473973969</v>
+        <v>16.25388479636543</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.15095619221712</v>
+        <v>30.15095629725787</v>
       </c>
       <c r="BZ4" t="n">
         <v>70.99454413334874</v>
@@ -13656,19 +13668,19 @@
         <v>51.39538022233962</v>
       </c>
       <c r="CB4" t="n">
-        <v>124.8365656449476</v>
+        <v>124.8365656247644</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.69771469791199</v>
+        <v>25.69771468978261</v>
       </c>
       <c r="CD4" t="n">
-        <v>61.55225165406679</v>
+        <v>61.55225153257966</v>
       </c>
       <c r="CE4" t="n">
         <v>43.02986521586298</v>
       </c>
       <c r="CF4" t="n">
-        <v>47.13678535262454</v>
+        <v>47.13678534852858</v>
       </c>
       <c r="CG4" t="n">
         <v>47.2126227191013</v>
@@ -13689,7 +13701,7 @@
         <v>73.15142160530792</v>
       </c>
       <c r="CM4" t="n">
-        <v>92.0814327386573</v>
+        <v>92.08143272196634</v>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
@@ -13970,10 +13982,10 @@
         <v>4.059999942779541</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.548072845498024</v>
+        <v>3.54807282876565</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.581675128398835</v>
+        <v>6.58167509736028</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.56892505650208</v>
@@ -13982,25 +13994,25 @@
         <v>8.462578627869229</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.40274522527432</v>
+        <v>24.40274523688278</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.26517502718242</v>
+        <v>11.26517503412428</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.57787749431459</v>
+        <v>10.57787753601435</v>
       </c>
       <c r="CE5" t="n">
         <v>5.216748691568468</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.11216333763927</v>
+        <v>9.112163340573114</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.52022806109191</v>
+        <v>9.520228081941788</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.568205254982718</v>
+        <v>8.56820527374761</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -14012,10 +14024,10 @@
         <v>6.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>111.0395412743969</v>
+        <v>111.0395417365863</v>
       </c>
       <c r="CM5" t="n">
-        <v>124.4375237946663</v>
+        <v>124.4375238669285</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -14280,10 +14292,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294910810901</v>
+        <v>18.38294915543341</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037059554221</v>
+        <v>34.10037068332898</v>
       </c>
       <c r="BZ6" t="n">
         <v>75.02112937085505</v>
@@ -14292,23 +14304,23 @@
         <v>56.1385860856476</v>
       </c>
       <c r="CB6" t="n">
-        <v>100.7448469377449</v>
+        <v>100.7448468641835</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.40370000702437</v>
+        <v>48.4036999955209</v>
       </c>
       <c r="CD6" t="n">
-        <v>59.46380262122727</v>
+        <v>59.46380252610901</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>43.97703727038266</v>
+        <v>43.97703730128458</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.25203530128329</v>
+        <v>41.25203533942494</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.12683177115496</v>
+        <v>37.12683180548245</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -14320,10 +14332,10 @@
         <v>4.1</v>
       </c>
       <c r="CL6" t="n">
-        <v>-23.03725025008134</v>
+        <v>-23.03725017892155</v>
       </c>
       <c r="CM6" t="n">
-        <v>-8.836990588221772</v>
+        <v>-8.836990524163069</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -14606,10 +14618,10 @@
         <v>4.380000114440918</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774201436924</v>
+        <v>3.052774220937844</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.662896143665495</v>
+        <v>5.6628961798397</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.64379118003097</v>
@@ -14618,7 +14630,7 @@
         <v>8.50525545154361</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.62501972477794</v>
+        <v>23.62501978425786</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -14630,7 +14642,7 @@
         <v>5.24246353170767</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.25728133204965</v>
+        <v>11.25728134571453</v>
       </c>
       <c r="CG7" t="n">
         <v>11.54640553044338</v>
@@ -14651,7 +14663,7 @@
         <v>137.2549019607844</v>
       </c>
       <c r="CM7" t="n">
-        <v>157.0155488109292</v>
+        <v>157.0155491229127</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -15146,10 +15158,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX9" t="n">
-        <v>121.1494721699117</v>
+        <v>121.1494725411449</v>
       </c>
       <c r="BY9" t="n">
-        <v>224.7322708751862</v>
+        <v>224.7322715638238</v>
       </c>
       <c r="BZ9" t="n">
         <v>136.6302942100011</v>
@@ -15170,13 +15182,13 @@
         <v>57.66739801003497</v>
       </c>
       <c r="CF9" t="n">
-        <v>116.3031158084362</v>
+        <v>116.3031159598463</v>
       </c>
       <c r="CG9" t="n">
-        <v>121.1494721699117</v>
+        <v>121.1494725411449</v>
       </c>
       <c r="CH9" t="n">
-        <v>109.0345249529205</v>
+        <v>109.0345252870304</v>
       </c>
       <c r="CI9" t="n">
         <v>7</v>
@@ -15188,10 +15200,10 @@
         <v>5.5</v>
       </c>
       <c r="CL9" t="n">
-        <v>163.6868899068033</v>
+        <v>163.686890714808</v>
       </c>
       <c r="CM9" t="n">
-        <v>181.2651030234609</v>
+        <v>181.2651033896281</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -15474,10 +15486,10 @@
         <v>15.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.426879109893282</v>
+        <v>6.426879087734028</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.92186074885204</v>
+        <v>11.92186070774662</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.54314565483476</v>
@@ -15486,19 +15498,19 @@
         <v>18.71731215268055</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.49020390929299</v>
+        <v>35.49020394518685</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.30123101826934</v>
+        <v>12.30123102245168</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.53560232491412</v>
+        <v>20.53560237134395</v>
       </c>
       <c r="CE10" t="n">
         <v>18.47523885586486</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.42637066638695</v>
+        <v>20.42637067287276</v>
       </c>
       <c r="CG10" t="n">
         <v>18.71731215268055</v>
@@ -15519,7 +15531,7 @@
         <v>6.956069443888868</v>
       </c>
       <c r="CM10" t="n">
-        <v>29.69124232626637</v>
+        <v>29.69124236744607</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -15802,37 +15814,37 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX11" t="n">
-        <v>24.20136282954487</v>
+        <v>24.20136286936076</v>
       </c>
       <c r="BY11" t="n">
-        <v>37.09024834900521</v>
+        <v>37.09024797787244</v>
       </c>
       <c r="BZ11" t="n">
-        <v>39.76038163298968</v>
+        <v>39.76038116972554</v>
       </c>
       <c r="CA11" t="n">
         <v>21.15376420319533</v>
       </c>
       <c r="CB11" t="n">
-        <v>53.96364536039312</v>
+        <v>53.96364505251905</v>
       </c>
       <c r="CC11" t="n">
-        <v>51.52714067805403</v>
+        <v>51.52714062780147</v>
       </c>
       <c r="CD11" t="n">
-        <v>19.88022358695261</v>
+        <v>19.88022335437046</v>
       </c>
       <c r="CE11" t="n">
         <v>24.52549486359719</v>
       </c>
       <c r="CF11" t="n">
-        <v>34.01278268796651</v>
+        <v>34.01278251480528</v>
       </c>
       <c r="CG11" t="n">
-        <v>30.8078716063012</v>
+        <v>30.80787142073481</v>
       </c>
       <c r="CH11" t="n">
-        <v>27.72708444567108</v>
+        <v>27.72708427866133</v>
       </c>
       <c r="CI11" t="n">
         <v>8</v>
@@ -15844,10 +15856,10 @@
         <v>2.7</v>
       </c>
       <c r="CL11" t="n">
-        <v>-14.89538708606791</v>
+        <v>-14.8953875986822</v>
       </c>
       <c r="CM11" t="n">
-        <v>4.39773105091148</v>
+        <v>4.397730519416032</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -16138,10 +16150,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX12" t="n">
-        <v>46.05538999516349</v>
+        <v>46.05538998425735</v>
       </c>
       <c r="BY12" t="n">
-        <v>85.43274844102828</v>
+        <v>85.43274842079738</v>
       </c>
       <c r="BZ12" t="n">
         <v>69.47297200868543</v>
@@ -16162,7 +16174,7 @@
         <v>25.94666723750103</v>
       </c>
       <c r="CF12" t="n">
-        <v>78.49436730847503</v>
+        <v>78.49436730402689</v>
       </c>
       <c r="CG12" t="n">
         <v>69.47297200868543</v>
@@ -16183,7 +16195,7 @@
         <v>89.58664546899841</v>
       </c>
       <c r="CM12" t="n">
-        <v>138.0059684596116</v>
+        <v>138.0059684461242</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -16468,10 +16480,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX13" t="n">
-        <v>127.6301643215276</v>
+        <v>127.6301659713547</v>
       </c>
       <c r="BY13" t="n">
-        <v>236.7539548164336</v>
+        <v>236.7539578768629</v>
       </c>
       <c r="BZ13" t="n">
         <v>137.215088724016</v>
@@ -16492,13 +16504,13 @@
         <v>56.54612056896573</v>
       </c>
       <c r="CF13" t="n">
-        <v>142.9573011925048</v>
+        <v>142.9573017812868</v>
       </c>
       <c r="CG13" t="n">
-        <v>126.4680094649372</v>
+        <v>126.4680102898507</v>
       </c>
       <c r="CH13" t="n">
-        <v>113.8212085184434</v>
+        <v>113.8212092608657</v>
       </c>
       <c r="CI13" t="n">
         <v>8</v>
@@ -16510,10 +16522,10 @@
         <v>5.5</v>
       </c>
       <c r="CL13" t="n">
-        <v>147.5450405646253</v>
+        <v>147.5450421792887</v>
       </c>
       <c r="CM13" t="n">
-        <v>210.9119239141944</v>
+        <v>210.9119251947122</v>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
@@ -16796,10 +16808,10 @@
         <v>7.050000190734863</v>
       </c>
       <c r="BX14" t="n">
-        <v>6.618982258856694</v>
+        <v>6.618982258250529</v>
       </c>
       <c r="BY14" t="n">
-        <v>12.27821209017917</v>
+        <v>12.27821208905473</v>
       </c>
       <c r="BZ14" t="n">
         <v>41.15088217058896</v>
@@ -16808,7 +16820,7 @@
         <v>27.74453639251564</v>
       </c>
       <c r="CB14" t="n">
-        <v>87.40782135903818</v>
+        <v>87.40782135529973</v>
       </c>
       <c r="CC14" t="n">
         <v>51.88018214566937</v>
@@ -17108,10 +17120,10 @@
         <v>13.81999969482422</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.2035398171108576</v>
+        <v>0.2035398171342778</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.2963539737134087</v>
+        <v>0.2963539737475085</v>
       </c>
       <c r="BZ15" t="n">
         <v>77.27311657321069</v>
@@ -17406,10 +17418,10 @@
         <v>14</v>
       </c>
       <c r="BX16" t="n">
-        <v>10.16255143730977</v>
+        <v>10.16255143946796</v>
       </c>
       <c r="BY16" t="n">
-        <v>18.85153291620964</v>
+        <v>18.85153292021306</v>
       </c>
       <c r="BZ16" t="n">
         <v>50.13513513513512</v>
@@ -17418,23 +17430,23 @@
         <v>49.31969619160719</v>
       </c>
       <c r="CB16" t="n">
-        <v>69.76010981511241</v>
+        <v>69.76010981927207</v>
       </c>
       <c r="CC16" t="n">
-        <v>33.93518588552259</v>
+        <v>33.93518588519073</v>
       </c>
       <c r="CD16" t="n">
-        <v>29.78692738423737</v>
+        <v>29.78692738171904</v>
       </c>
       <c r="CE16" t="inlineStr"/>
       <c r="CF16" t="n">
-        <v>34.30728464562245</v>
+        <v>34.30728464684631</v>
       </c>
       <c r="CG16" t="n">
-        <v>33.93518588552259</v>
+        <v>33.93518588519073</v>
       </c>
       <c r="CH16" t="n">
-        <v>30.54166729697033</v>
+        <v>30.54166729667165</v>
       </c>
       <c r="CI16" t="n">
         <v>3</v>
@@ -17446,10 +17458,10 @@
         <v>4.9</v>
       </c>
       <c r="CL16" t="n">
-        <v>118.1547664069309</v>
+        <v>118.1547664047975</v>
       </c>
       <c r="CM16" t="n">
-        <v>145.0520331830175</v>
+        <v>145.0520331917593</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -17559,7 +17571,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -17710,10 +17722,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX17" t="n">
-        <v>13.15731121066379</v>
+        <v>13.15731119057001</v>
       </c>
       <c r="BY17" t="n">
-        <v>24.40681229578133</v>
+        <v>24.40681225850738</v>
       </c>
       <c r="BZ17" t="n">
         <v>19.90620030713044</v>
@@ -17722,7 +17734,7 @@
         <v>12.44114419785431</v>
       </c>
       <c r="CB17" t="n">
-        <v>33.68872442204027</v>
+        <v>33.6887243999592</v>
       </c>
       <c r="CC17" t="n">
         <v>22.8984489302328</v>
@@ -17732,7 +17744,7 @@
       </c>
       <c r="CE17" t="inlineStr"/>
       <c r="CF17" t="n">
-        <v>20.09219318595209</v>
+        <v>20.09219317161016</v>
       </c>
       <c r="CG17" t="n">
         <v>21.40232461868162</v>
@@ -17753,7 +17765,7 @@
         <v>0.6378932657179259</v>
       </c>
       <c r="CM17" t="n">
-        <v>4.974889376530656</v>
+        <v>4.974889301598906</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -17771,7 +17783,11 @@
         </is>
       </c>
       <c r="CQ17" t="inlineStr"/>
-      <c r="CR17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="CS17" t="b">
         <v>0</v>
       </c>
@@ -17798,14 +17814,14 @@
         <v>1</v>
       </c>
       <c r="DB17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD17" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.1%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -18036,10 +18052,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX18" t="n">
-        <v>3.363729732811315</v>
+        <v>3.363729732909307</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.23971865436499</v>
+        <v>6.239718654546764</v>
       </c>
       <c r="BZ18" t="n">
         <v>20.7379196371351</v>
@@ -18048,7 +18064,7 @@
         <v>14.20601824710207</v>
       </c>
       <c r="CB18" t="n">
-        <v>33.37021289880997</v>
+        <v>33.37021289909818</v>
       </c>
       <c r="CC18" t="n">
         <v>10.95072400487419</v>
@@ -18362,10 +18378,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX19" t="n">
-        <v>10.74426547264768</v>
+        <v>10.74426541307544</v>
       </c>
       <c r="BY19" t="n">
-        <v>19.93061245176145</v>
+        <v>19.93061234125494</v>
       </c>
       <c r="BZ19" t="n">
         <v>37.5845483977432</v>
@@ -18374,25 +18390,25 @@
         <v>37.1651975122017</v>
       </c>
       <c r="CB19" t="n">
-        <v>41.90042983968529</v>
+        <v>41.90042981465468</v>
       </c>
       <c r="CC19" t="n">
-        <v>34.50408897775664</v>
+        <v>34.50408899034814</v>
       </c>
       <c r="CD19" t="n">
-        <v>18.61582866217975</v>
+        <v>18.61582873127402</v>
       </c>
       <c r="CE19" t="n">
         <v>31.97921770241074</v>
       </c>
       <c r="CF19" t="n">
-        <v>31.66856050624839</v>
+        <v>31.66856049855534</v>
       </c>
       <c r="CG19" t="n">
-        <v>34.50408897775664</v>
+        <v>34.50408899034814</v>
       </c>
       <c r="CH19" t="n">
-        <v>31.05368007998098</v>
+        <v>31.05368009131333</v>
       </c>
       <c r="CI19" t="n">
         <v>7</v>
@@ -18404,10 +18420,10 @@
         <v>3.9</v>
       </c>
       <c r="CL19" t="n">
-        <v>77.14591479530242</v>
+        <v>77.14591485994788</v>
       </c>
       <c r="CM19" t="n">
-        <v>80.65350408328136</v>
+        <v>80.65350403939631</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -18446,7 +18462,7 @@
         <v>-5.040678244190966</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-23.2212515115939</v>
+        <v>-23.22124503926587</v>
       </c>
       <c r="DA19" t="b">
         <v>1</v>
@@ -18692,10 +18708,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX20" t="n">
-        <v>5.044350364577175</v>
+        <v>5.044350330400213</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.357269926290659</v>
+        <v>9.357269862892394</v>
       </c>
       <c r="BZ20" t="n">
         <v>8.531826591579675</v>
@@ -19010,37 +19026,37 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX21" t="n">
-        <v>10.37863321319145</v>
+        <v>10.37863321725536</v>
       </c>
       <c r="BY21" t="n">
-        <v>18.0755304925735</v>
+        <v>18.07553048217811</v>
       </c>
       <c r="BZ21" t="n">
-        <v>23.22146474366123</v>
+        <v>23.22146472121366</v>
       </c>
       <c r="CA21" t="n">
         <v>17.75681071950086</v>
       </c>
       <c r="CB21" t="n">
-        <v>36.48041911177744</v>
+        <v>36.48041910786196</v>
       </c>
       <c r="CC21" t="n">
-        <v>24.12244063019823</v>
+        <v>24.12244062846323</v>
       </c>
       <c r="CD21" t="n">
-        <v>11.46100443647042</v>
+        <v>11.46100442756559</v>
       </c>
       <c r="CE21" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF21" t="n">
-        <v>18.9820378755063</v>
+        <v>18.9820378700895</v>
       </c>
       <c r="CG21" t="n">
-        <v>17.91617060603718</v>
+        <v>17.91617060083949</v>
       </c>
       <c r="CH21" t="n">
-        <v>16.12455354543346</v>
+        <v>16.12455354075554</v>
       </c>
       <c r="CI21" t="n">
         <v>8</v>
@@ -19052,10 +19068,10 @@
         <v>3.5</v>
       </c>
       <c r="CL21" t="n">
-        <v>55.64241389757998</v>
+        <v>55.64241385242625</v>
       </c>
       <c r="CM21" t="n">
-        <v>83.22430988954679</v>
+        <v>83.2243098372611</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -19338,10 +19354,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.454302382686342</v>
+        <v>3.454302383090375</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.407730919883164</v>
+        <v>6.407730920632644</v>
       </c>
       <c r="BZ22" t="n">
         <v>20.16620865234961</v>
@@ -19350,13 +19366,13 @@
         <v>19.00949927082382</v>
       </c>
       <c r="CB22" t="n">
-        <v>21.6058827163297</v>
+        <v>21.60588271629159</v>
       </c>
       <c r="CC22" t="n">
-        <v>15.92827012512917</v>
+        <v>15.9282701250515</v>
       </c>
       <c r="CD22" t="n">
-        <v>13.47116575685435</v>
+        <v>13.471165756342</v>
       </c>
       <c r="CE22" t="n">
         <v>30.336208848481</v>
@@ -19656,37 +19672,37 @@
         <v>35.20000076293945</v>
       </c>
       <c r="BX23" t="n">
-        <v>25.31139907183827</v>
+        <v>25.31139903711134</v>
       </c>
       <c r="BY23" t="n">
-        <v>29.80495159259062</v>
+        <v>29.80495164107754</v>
       </c>
       <c r="BZ23" t="n">
-        <v>32.18096622231304</v>
+        <v>32.18096631881718</v>
       </c>
       <c r="CA23" t="n">
         <v>35.90922954270143</v>
       </c>
       <c r="CB23" t="n">
-        <v>45.73499579164744</v>
+        <v>45.73499586302033</v>
       </c>
       <c r="CC23" t="n">
-        <v>48.24380383732599</v>
+        <v>48.24380385269888</v>
       </c>
       <c r="CD23" t="n">
-        <v>14.75792641440402</v>
+        <v>14.75792649248404</v>
       </c>
       <c r="CE23" t="n">
         <v>30.3203711305658</v>
       </c>
       <c r="CF23" t="n">
-        <v>32.78295545042333</v>
+        <v>32.78295548480956</v>
       </c>
       <c r="CG23" t="n">
-        <v>31.25066867643942</v>
+        <v>31.25066872469149</v>
       </c>
       <c r="CH23" t="n">
-        <v>28.12560180879548</v>
+        <v>28.12560185222234</v>
       </c>
       <c r="CI23" t="n">
         <v>8</v>
@@ -19698,10 +19714,10 @@
         <v>3.3</v>
       </c>
       <c r="CL23" t="n">
-        <v>-20.09772386593895</v>
+        <v>-20.09772374256719</v>
       </c>
       <c r="CM23" t="n">
-        <v>-6.866605852636587</v>
+        <v>-6.866605754948429</v>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
@@ -19888,13 +19904,13 @@
         <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="AS24" t="b">
         <v>1</v>
       </c>
       <c r="AT24" t="n">
-        <v>3602869248</v>
+        <v>5725241856</v>
       </c>
       <c r="AU24" t="n">
         <v>6.7</v>
@@ -19984,10 +20000,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX24" t="n">
-        <v>9.774107146014483</v>
+        <v>9.774107130994336</v>
       </c>
       <c r="BY24" t="n">
-        <v>18.13096875585686</v>
+        <v>18.1309687279945</v>
       </c>
       <c r="BZ24" t="n">
         <v>22.32723873053024</v>
@@ -19996,25 +20012,25 @@
         <v>13.19107667093893</v>
       </c>
       <c r="CB24" t="n">
-        <v>32.07171951973582</v>
+        <v>32.07171956569217</v>
       </c>
       <c r="CC24" t="n">
-        <v>25.27239702552844</v>
+        <v>25.27239703637801</v>
       </c>
       <c r="CD24" t="n">
-        <v>11.82328977684374</v>
+        <v>11.82328982545854</v>
       </c>
       <c r="CE24" t="n">
         <v>9.733055502947964</v>
       </c>
       <c r="CF24" t="n">
-        <v>17.79048164104956</v>
+        <v>17.79048164886684</v>
       </c>
       <c r="CG24" t="n">
-        <v>15.6610227133979</v>
+        <v>15.66102269946671</v>
       </c>
       <c r="CH24" t="n">
-        <v>14.09492044205811</v>
+        <v>14.09492042952004</v>
       </c>
       <c r="CI24" t="n">
         <v>8</v>
@@ -20026,10 +20042,10 @@
         <v>3.3</v>
       </c>
       <c r="CL24" t="n">
-        <v>24.84429131693913</v>
+        <v>24.8442912058845</v>
       </c>
       <c r="CM24" t="n">
-        <v>57.57734013428295</v>
+        <v>57.57734020352368</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -20141,7 +20157,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -20312,10 +20328,10 @@
         <v>14.13000011444092</v>
       </c>
       <c r="BX25" t="n">
-        <v>4.339755649309138</v>
+        <v>4.339755639171419</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.050246729468451</v>
+        <v>8.050246710662982</v>
       </c>
       <c r="BZ25" t="n">
         <v>23.63920473691189</v>
@@ -20324,25 +20340,25 @@
         <v>19.91603197659278</v>
       </c>
       <c r="CB25" t="n">
-        <v>28.93109438543271</v>
+        <v>28.9310943931589</v>
       </c>
       <c r="CC25" t="n">
-        <v>16.71775062331386</v>
+        <v>16.71775062546117</v>
       </c>
       <c r="CD25" t="n">
-        <v>18.12938007370421</v>
+        <v>18.1293800898248</v>
       </c>
       <c r="CE25" t="n">
         <v>13.90588124012942</v>
       </c>
       <c r="CF25" t="n">
-        <v>18.46994139507905</v>
+        <v>18.46994139610599</v>
       </c>
       <c r="CG25" t="n">
-        <v>18.12938007370421</v>
+        <v>18.1293800898248</v>
       </c>
       <c r="CH25" t="n">
-        <v>16.31644206633379</v>
+        <v>16.31644208084232</v>
       </c>
       <c r="CI25" t="n">
         <v>7</v>
@@ -20354,10 +20370,10 @@
         <v>6.7</v>
       </c>
       <c r="CL25" t="n">
-        <v>15.47375749599831</v>
+        <v>15.47375759867724</v>
       </c>
       <c r="CM25" t="n">
-        <v>30.71437541039148</v>
+        <v>30.71437541765931</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -20373,7 +20389,7 @@
       <c r="CQ25" t="inlineStr"/>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="CS25" t="b">
@@ -20409,7 +20425,7 @@
       </c>
       <c r="DD25" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$13.81 (candidato)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -20638,10 +20654,10 @@
         <v>8</v>
       </c>
       <c r="BX26" t="n">
-        <v>3.706794289133744</v>
+        <v>3.706794285075357</v>
       </c>
       <c r="BY26" t="n">
-        <v>6.876103406343096</v>
+        <v>6.876103398814785</v>
       </c>
       <c r="BZ26" t="n">
         <v>24.65116279069767</v>
@@ -20650,13 +20666,13 @@
         <v>22.8747855498907</v>
       </c>
       <c r="CB26" t="n">
-        <v>31.90962338395977</v>
+        <v>31.90962337914971</v>
       </c>
       <c r="CC26" t="n">
-        <v>9.605681426459231</v>
+        <v>9.605681426851284</v>
       </c>
       <c r="CD26" t="n">
-        <v>17.44157960843456</v>
+        <v>17.44157961371663</v>
       </c>
       <c r="CE26" t="inlineStr"/>
       <c r="CF26" t="inlineStr"/>
@@ -20950,10 +20966,10 @@
         <v>13.23999977111816</v>
       </c>
       <c r="BX27" t="n">
-        <v>8.302793986814326</v>
+        <v>8.302793977641096</v>
       </c>
       <c r="BY27" t="n">
-        <v>15.40168284554057</v>
+        <v>15.40168282852423</v>
       </c>
       <c r="BZ27" t="n">
         <v>13.23999977111816</v>
@@ -20974,7 +20990,7 @@
         <v>6.052411187494985</v>
       </c>
       <c r="CF27" t="n">
-        <v>10.88286237632113</v>
+        <v>10.88286237257976</v>
       </c>
       <c r="CG27" t="n">
         <v>10.76229112776816</v>
@@ -20995,7 +21011,7 @@
         <v>-26.84243064625581</v>
       </c>
       <c r="CM27" t="n">
-        <v>-17.80315283644427</v>
+        <v>-17.80315286470234</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -21274,10 +21290,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX28" t="n">
-        <v>7.290978518749648</v>
+        <v>7.290978496927618</v>
       </c>
       <c r="BY28" t="n">
-        <v>13.5247651522806</v>
+        <v>13.52476511180073</v>
       </c>
       <c r="BZ28" t="n">
         <v>35.92512375028262</v>
@@ -21286,19 +21302,19 @@
         <v>28.41024685094796</v>
       </c>
       <c r="CB28" t="n">
-        <v>44.74749254244985</v>
+        <v>44.74749257504084</v>
       </c>
       <c r="CC28" t="n">
-        <v>26.46268145282235</v>
+        <v>26.46268145824689</v>
       </c>
       <c r="CD28" t="n">
-        <v>29.04887753344142</v>
+        <v>29.04887757284678</v>
       </c>
       <c r="CE28" t="n">
         <v>24.98203479043206</v>
       </c>
       <c r="CF28" t="n">
-        <v>29.01446029609383</v>
+        <v>29.01446030137112</v>
       </c>
       <c r="CG28" t="n">
         <v>28.41024685094796</v>
@@ -21319,7 +21335,7 @@
         <v>-7.088583791648039</v>
       </c>
       <c r="CM28" t="n">
-        <v>5.430449903602952</v>
+        <v>5.430449922779168</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -21433,7 +21449,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -21582,10 +21598,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX29" t="n">
-        <v>35.62892565405816</v>
+        <v>35.6289255576336</v>
       </c>
       <c r="BY29" t="n">
-        <v>51.87571575230869</v>
+        <v>51.87571561191452</v>
       </c>
       <c r="BZ29" t="n">
         <v>48.56662855571916</v>
@@ -21602,13 +21618,13 @@
       </c>
       <c r="CE29" t="inlineStr"/>
       <c r="CF29" t="n">
-        <v>48.89385873647593</v>
+        <v>48.89385867727125</v>
       </c>
       <c r="CG29" t="n">
-        <v>50.22117215401393</v>
+        <v>50.22117208381684</v>
       </c>
       <c r="CH29" t="n">
-        <v>45.19905493861253</v>
+        <v>45.19905487543516</v>
       </c>
       <c r="CI29" t="n">
         <v>4</v>
@@ -21620,10 +21636,10 @@
         <v>1.7</v>
       </c>
       <c r="CL29" t="n">
-        <v>16.19293872917478</v>
+        <v>16.19293856676509</v>
       </c>
       <c r="CM29" t="n">
-        <v>25.69114863388486</v>
+        <v>25.69114848168772</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -21641,7 +21657,11 @@
         </is>
       </c>
       <c r="CQ29" t="inlineStr"/>
-      <c r="CR29" t="inlineStr"/>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="CS29" t="b">
         <v>0</v>
       </c>
@@ -21668,14 +21688,14 @@
         <v>1</v>
       </c>
       <c r="DB29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD29" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -21906,10 +21926,10 @@
         <v>24.72999954223633</v>
       </c>
       <c r="BX30" t="n">
-        <v>12.83053368880796</v>
+        <v>12.83053368128606</v>
       </c>
       <c r="BY30" t="n">
-        <v>23.80063999273876</v>
+        <v>23.80063997878564</v>
       </c>
       <c r="BZ30" t="n">
         <v>61.13292797287897</v>
@@ -21918,13 +21938,13 @@
         <v>51.18231610165188</v>
       </c>
       <c r="CB30" t="n">
-        <v>84.96070712654081</v>
+        <v>84.96070712612305</v>
       </c>
       <c r="CC30" t="n">
-        <v>33.64819480577633</v>
+        <v>33.648194807038</v>
       </c>
       <c r="CD30" t="n">
-        <v>44.66427060451993</v>
+        <v>44.66427061660671</v>
       </c>
       <c r="CE30" t="n">
         <v>5.441506065857172</v>
@@ -22220,10 +22240,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX31" t="n">
-        <v>3.10874053265072</v>
+        <v>3.108740526292904</v>
       </c>
       <c r="BY31" t="n">
-        <v>5.766713688067086</v>
+        <v>5.766713676273336</v>
       </c>
       <c r="BZ31" t="n">
         <v>31.95928917556512</v>
@@ -22232,7 +22252,7 @@
         <v>26.70105358379499</v>
       </c>
       <c r="CB31" t="n">
-        <v>40.93687026005173</v>
+        <v>40.93687025032393</v>
       </c>
       <c r="CC31" t="n">
         <v>10.85340539909456</v>
@@ -22538,10 +22558,10 @@
         <v>12.02999973297119</v>
       </c>
       <c r="BX32" t="n">
-        <v>2.081024032334844</v>
+        <v>2.08102403333652</v>
       </c>
       <c r="BY32" t="n">
-        <v>3.860299579981135</v>
+        <v>3.860299581839244</v>
       </c>
       <c r="BZ32" t="n">
         <v>28.46383865390505</v>
@@ -22550,7 +22570,7 @@
         <v>24.11364501630011</v>
       </c>
       <c r="CB32" t="n">
-        <v>37.42577365129566</v>
+        <v>37.42577365379986</v>
       </c>
       <c r="CC32" t="n">
         <v>9.158754146</v>
@@ -22852,10 +22872,10 @@
         <v>32.75</v>
       </c>
       <c r="BX33" t="n">
-        <v>3.249356687194955</v>
+        <v>3.24935669499341</v>
       </c>
       <c r="BY33" t="n">
-        <v>6.027556654746641</v>
+        <v>6.027556669212775</v>
       </c>
       <c r="BZ33" t="n">
         <v>32.74999999999999</v>
@@ -22864,7 +22884,7 @@
         <v>22.94333650394972</v>
       </c>
       <c r="CB33" t="n">
-        <v>40.50875423552675</v>
+        <v>40.50875424376662</v>
       </c>
       <c r="CC33" t="n">
         <v>10.59424454785779</v>
@@ -22930,7 +22950,7 @@
         <v>0.738239590458023</v>
       </c>
       <c r="CZ33" t="n">
-        <v>-31.318349352401</v>
+        <v>-31.31834368818209</v>
       </c>
       <c r="DA33" t="b">
         <v>1</v>
@@ -23174,10 +23194,10 @@
         <v>33.43000030517578</v>
       </c>
       <c r="BX34" t="n">
-        <v>7.930922129968906</v>
+        <v>7.930922153366162</v>
       </c>
       <c r="BY34" t="n">
-        <v>14.71186055109232</v>
+        <v>14.71186059449423</v>
       </c>
       <c r="BZ34" t="n">
         <v>65.23527305501902</v>
@@ -23186,7 +23206,7 @@
         <v>38.10857086024811</v>
       </c>
       <c r="CB34" t="n">
-        <v>90.20366927793835</v>
+        <v>90.20366932618012</v>
       </c>
       <c r="CC34" t="n">
         <v>22.51480113099953</v>
@@ -23470,35 +23490,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="BX35" t="n">
-        <v>16.54376617378674</v>
+        <v>16.54376620264756</v>
       </c>
       <c r="BY35" t="n">
-        <v>29.62891132267158</v>
+        <v>29.62891131829394</v>
       </c>
       <c r="BZ35" t="n">
-        <v>50.06208068345838</v>
+        <v>50.0620805887278</v>
       </c>
       <c r="CA35" t="n">
         <v>49.44990718954784</v>
       </c>
       <c r="CB35" t="n">
-        <v>61.76490017278544</v>
+        <v>61.76490018461578</v>
       </c>
       <c r="CC35" t="n">
-        <v>45.76209350782156</v>
+        <v>45.7620935015432</v>
       </c>
       <c r="CD35" t="n">
-        <v>24.56071167367637</v>
+        <v>24.56071163799285</v>
       </c>
       <c r="CE35" t="inlineStr"/>
       <c r="CF35" t="n">
-        <v>35.49921292193456</v>
+        <v>35.49921290280312</v>
       </c>
       <c r="CG35" t="n">
-        <v>37.69550241524657</v>
+        <v>37.69550240991857</v>
       </c>
       <c r="CH35" t="n">
-        <v>33.92595217372191</v>
+        <v>33.92595216892671</v>
       </c>
       <c r="CI35" t="n">
         <v>4</v>
@@ -23510,10 +23530,10 @@
         <v>3</v>
       </c>
       <c r="CL35" t="n">
-        <v>47.18417916116304</v>
+        <v>47.1841791403596</v>
       </c>
       <c r="CM35" t="n">
-        <v>54.00960562661434</v>
+        <v>54.0096055436146</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -23792,10 +23812,10 @@
         <v>33.65000152587891</v>
       </c>
       <c r="BX36" t="n">
-        <v>15.24688685387707</v>
+        <v>15.24688683049825</v>
       </c>
       <c r="BY36" t="n">
-        <v>28.28297511394196</v>
+        <v>28.28297507057425</v>
       </c>
       <c r="BZ36" t="n">
         <v>20.19304892291193</v>
@@ -23804,7 +23824,7 @@
         <v>37.28531071349501</v>
       </c>
       <c r="CB36" t="n">
-        <v>27.1934526042521</v>
+        <v>27.19345258942858</v>
       </c>
       <c r="CC36" t="n">
         <v>15.03391666666667</v>
@@ -23816,7 +23836,7 @@
         <v>79.29138454079849</v>
       </c>
       <c r="CF36" t="n">
-        <v>22.61760391840966</v>
+        <v>22.61760390675679</v>
       </c>
       <c r="CG36" t="n">
         <v>20.19304892291193</v>
@@ -23837,7 +23857,7 @@
         <v>-45.99184782608695</v>
       </c>
       <c r="CM36" t="n">
-        <v>-32.78572691589526</v>
+        <v>-32.78572695052488</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -24096,35 +24116,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX37" t="n">
-        <v>8.627042048386361</v>
+        <v>8.627042062321403</v>
       </c>
       <c r="BY37" t="n">
-        <v>13.85196406791223</v>
+        <v>13.85196405170026</v>
       </c>
       <c r="BZ37" t="n">
-        <v>18.49124807290187</v>
+        <v>18.49124802139176</v>
       </c>
       <c r="CA37" t="n">
         <v>17.39822241629838</v>
       </c>
       <c r="CB37" t="n">
-        <v>22.98547050967757</v>
+        <v>22.98547049638615</v>
       </c>
       <c r="CC37" t="n">
-        <v>17.3368128665782</v>
+        <v>17.33681286270502</v>
       </c>
       <c r="CD37" t="n">
-        <v>9.229677303930041</v>
+        <v>9.229677280189192</v>
       </c>
       <c r="CE37" t="inlineStr"/>
       <c r="CF37" t="n">
-        <v>14.57676676394466</v>
+        <v>14.57676674952961</v>
       </c>
       <c r="CG37" t="n">
-        <v>15.59438846724522</v>
+        <v>15.59438845720264</v>
       </c>
       <c r="CH37" t="n">
-        <v>14.0349496205207</v>
+        <v>14.03494961148238</v>
       </c>
       <c r="CI37" t="n">
         <v>4</v>
@@ -24136,10 +24156,10 @@
         <v>2.1</v>
       </c>
       <c r="CL37" t="n">
-        <v>9.221394582678144</v>
+        <v>9.221394512341053</v>
       </c>
       <c r="CM37" t="n">
-        <v>13.43787028181735</v>
+        <v>13.43787016963798</v>
       </c>
       <c r="CN37" t="inlineStr">
         <is>
@@ -24406,10 +24426,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX38" t="n">
-        <v>9.186485019046415</v>
+        <v>9.186484952657352</v>
       </c>
       <c r="BY38" t="n">
-        <v>17.0409297103311</v>
+        <v>17.04092958717939</v>
       </c>
       <c r="BZ38" t="n">
         <v>30.69514051126462</v>
@@ -24418,23 +24438,23 @@
         <v>29.25728964348931</v>
       </c>
       <c r="CB38" t="n">
-        <v>34.71948757568801</v>
+        <v>34.71948756133753</v>
       </c>
       <c r="CC38" t="n">
-        <v>25.51046012997303</v>
+        <v>25.51046014357987</v>
       </c>
       <c r="CD38" t="n">
-        <v>15.34133392427264</v>
+        <v>15.34133400682346</v>
       </c>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="n">
-        <v>20.6082538426538</v>
+        <v>20.60825379867031</v>
       </c>
       <c r="CG38" t="n">
-        <v>21.27569492015207</v>
+        <v>21.27569486537963</v>
       </c>
       <c r="CH38" t="n">
-        <v>19.14812542813686</v>
+        <v>19.14812537884167</v>
       </c>
       <c r="CI38" t="n">
         <v>4</v>
@@ -24446,10 +24466,10 @@
         <v>3.3</v>
       </c>
       <c r="CL38" t="n">
-        <v>29.55430158379006</v>
+        <v>29.55430125026371</v>
       </c>
       <c r="CM38" t="n">
-        <v>39.43338440447295</v>
+        <v>39.43338410688506</v>
       </c>
       <c r="CN38" t="inlineStr">
         <is>
@@ -24714,10 +24734,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX39" t="n">
-        <v>20.16127570477438</v>
+        <v>20.16127561026532</v>
       </c>
       <c r="BY39" t="n">
-        <v>37.39916643235646</v>
+        <v>37.39916625704217</v>
       </c>
       <c r="BZ39" t="n">
         <v>56.01071616333269</v>
@@ -24726,23 +24746,23 @@
         <v>42.36568036412405</v>
       </c>
       <c r="CB39" t="n">
-        <v>61.78700424729585</v>
+        <v>61.78700440252356</v>
       </c>
       <c r="CC39" t="n">
-        <v>45.16919928118866</v>
+        <v>45.16919931072515</v>
       </c>
       <c r="CD39" t="n">
-        <v>31.11427789412564</v>
+        <v>31.11427808083772</v>
       </c>
       <c r="CE39" t="inlineStr"/>
       <c r="CF39" t="n">
-        <v>39.68508939541304</v>
+        <v>39.68508933534133</v>
       </c>
       <c r="CG39" t="n">
-        <v>41.28418285677256</v>
+        <v>41.28418278388367</v>
       </c>
       <c r="CH39" t="n">
-        <v>37.1557645710953</v>
+        <v>37.1557645054953</v>
       </c>
       <c r="CI39" t="n">
         <v>4</v>
@@ -24754,10 +24774,10 @@
         <v>2.8</v>
       </c>
       <c r="CL39" t="n">
-        <v>-5.79166869967076</v>
+        <v>-5.791668865999378</v>
       </c>
       <c r="CM39" t="n">
-        <v>0.621426919974799</v>
+        <v>0.6214267676631469</v>
       </c>
       <c r="CN39" t="inlineStr">
         <is>
@@ -25040,10 +25060,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX40" t="n">
-        <v>6.975750787871223</v>
+        <v>6.975750796989641</v>
       </c>
       <c r="BY40" t="n">
-        <v>12.94001771150112</v>
+        <v>12.94001772841578</v>
       </c>
       <c r="BZ40" t="n">
         <v>5.584946345257502</v>
@@ -25064,7 +25084,7 @@
         <v>5.373183328823668</v>
       </c>
       <c r="CF40" t="n">
-        <v>7.287571955600599</v>
+        <v>7.287571958854734</v>
       </c>
       <c r="CG40" t="n">
         <v>5.859139839295418</v>
@@ -25085,7 +25105,7 @@
         <v>-10.31928991948218</v>
       </c>
       <c r="CM40" t="n">
-        <v>23.93829615245706</v>
+        <v>23.9382962077995</v>
       </c>
       <c r="CN40" t="inlineStr">
         <is>
@@ -25368,37 +25388,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX41" t="n">
-        <v>16.91883605882122</v>
+        <v>16.91883609990701</v>
       </c>
       <c r="BY41" t="n">
-        <v>28.00431312808389</v>
+        <v>28.00431313303428</v>
       </c>
       <c r="BZ41" t="n">
-        <v>46.83168344484847</v>
+        <v>46.8316833394007</v>
       </c>
       <c r="CA41" t="n">
         <v>52.67243426197095</v>
       </c>
       <c r="CB41" t="n">
-        <v>55.69855922279349</v>
+        <v>55.69855923579338</v>
       </c>
       <c r="CC41" t="n">
-        <v>43.03544430153126</v>
+        <v>43.0354442939745</v>
       </c>
       <c r="CD41" t="n">
-        <v>23.30397207725829</v>
+        <v>23.30397203130465</v>
       </c>
       <c r="CE41" t="n">
         <v>30.43448362223624</v>
       </c>
       <c r="CF41" t="n">
-        <v>37.11246576469297</v>
+        <v>37.11246575220272</v>
       </c>
       <c r="CG41" t="n">
-        <v>36.73496396188375</v>
+        <v>36.73496395810537</v>
       </c>
       <c r="CH41" t="n">
-        <v>33.06146756569537</v>
+        <v>33.06146756229483</v>
       </c>
       <c r="CI41" t="n">
         <v>8</v>
@@ -25410,10 +25430,10 @@
         <v>3.3</v>
       </c>
       <c r="CL41" t="n">
-        <v>24.94886133649419</v>
+        <v>24.94886132364256</v>
       </c>
       <c r="CM41" t="n">
-        <v>40.25875679818684</v>
+        <v>40.25875675098256</v>
       </c>
       <c r="CN41" t="inlineStr">
         <is>
@@ -25525,7 +25545,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -25696,37 +25716,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX42" t="n">
-        <v>5.939526969908054</v>
+        <v>5.939526962110235</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.534880603215935</v>
+        <v>8.534880609653715</v>
       </c>
       <c r="BZ42" t="n">
-        <v>10.8150154441064</v>
+        <v>10.81501546646275</v>
       </c>
       <c r="CA42" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB42" t="n">
-        <v>9.810403804227111</v>
+        <v>9.810403816800907</v>
       </c>
       <c r="CC42" t="n">
-        <v>14.90925677880722</v>
+        <v>14.90925678154334</v>
       </c>
       <c r="CD42" t="n">
-        <v>5.384140030600174</v>
+        <v>5.384140043226401</v>
       </c>
       <c r="CE42" t="n">
         <v>11.00534556207784</v>
       </c>
       <c r="CF42" t="n">
-        <v>9.757252263120744</v>
+        <v>9.757252269237304</v>
       </c>
       <c r="CG42" t="n">
-        <v>10.31270962416675</v>
+        <v>10.31270964163183</v>
       </c>
       <c r="CH42" t="n">
-        <v>9.281438661750078</v>
+        <v>9.281438677468648</v>
       </c>
       <c r="CI42" t="n">
         <v>8</v>
@@ -25738,10 +25758,10 @@
         <v>2.8</v>
       </c>
       <c r="CL42" t="n">
-        <v>-39.37662699304846</v>
+        <v>-39.37662689037982</v>
       </c>
       <c r="CM42" t="n">
-        <v>-36.26876554086321</v>
+        <v>-36.26876550091181</v>
       </c>
       <c r="CN42" t="inlineStr">
         <is>
@@ -25759,7 +25779,11 @@
         </is>
       </c>
       <c r="CQ42" t="inlineStr"/>
-      <c r="CR42" t="inlineStr"/>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="CS42" t="b">
         <v>0</v>
       </c>
@@ -25786,14 +25810,14 @@
         <v>1</v>
       </c>
       <c r="DB42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD42" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-3.5%))</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -26024,10 +26048,10 @@
         <v>9.25</v>
       </c>
       <c r="BX43" t="n">
-        <v>2.521670918557618</v>
+        <v>2.521670926061534</v>
       </c>
       <c r="BY43" t="n">
-        <v>4.677699553924382</v>
+        <v>4.677699567844145</v>
       </c>
       <c r="BZ43" t="n">
         <v>13.54281767955801</v>
@@ -26036,19 +26060,19 @@
         <v>15.28931421405346</v>
       </c>
       <c r="CB43" t="n">
-        <v>10.60496388735971</v>
+        <v>10.60496388844148</v>
       </c>
       <c r="CC43" t="n">
-        <v>7.31063985075799</v>
+        <v>7.31063985005142</v>
       </c>
       <c r="CD43" t="n">
-        <v>6.944431466637953</v>
+        <v>6.944431460021301</v>
       </c>
       <c r="CE43" t="n">
         <v>10.29452216806777</v>
       </c>
       <c r="CF43" t="n">
-        <v>9.809198402908468</v>
+        <v>9.80919840400537</v>
       </c>
       <c r="CG43" t="n">
         <v>10.29452216806777</v>
@@ -26069,7 +26093,7 @@
         <v>0.1629183920107247</v>
       </c>
       <c r="CM43" t="n">
-        <v>6.045388139551</v>
+        <v>6.045388151409403</v>
       </c>
       <c r="CN43" t="inlineStr">
         <is>
@@ -26104,7 +26128,7 @@
         <v>-0.5376364484882101</v>
       </c>
       <c r="CZ43" t="n">
-        <v>-35.23798556234104</v>
+        <v>-35.23799006988425</v>
       </c>
       <c r="DA43" t="b">
         <v>0</v>
@@ -26348,10 +26372,10 @@
         <v>11.76000022888184</v>
       </c>
       <c r="BX44" t="n">
-        <v>4.779815376429557</v>
+        <v>4.779815380923924</v>
       </c>
       <c r="BY44" t="n">
-        <v>8.866557523276827</v>
+        <v>8.866557531613877</v>
       </c>
       <c r="BZ44" t="n">
         <v>25.84079652283322</v>
@@ -26360,25 +26384,25 @@
         <v>29.08539831347033</v>
       </c>
       <c r="CB44" t="n">
-        <v>24.10032307864492</v>
+        <v>24.1003230826931</v>
       </c>
       <c r="CC44" t="n">
-        <v>14.25753217762013</v>
+        <v>14.25753217718242</v>
       </c>
       <c r="CD44" t="n">
-        <v>13.38320656277272</v>
+        <v>13.38320655875835</v>
       </c>
       <c r="CE44" t="n">
         <v>4.91926228677063</v>
       </c>
       <c r="CF44" t="n">
-        <v>19.25563569643635</v>
+        <v>19.25563569775855</v>
       </c>
       <c r="CG44" t="n">
-        <v>19.17892762813252</v>
+        <v>19.17892762993776</v>
       </c>
       <c r="CH44" t="n">
-        <v>17.26103486531927</v>
+        <v>17.26103486694398</v>
       </c>
       <c r="CI44" t="n">
         <v>6</v>
@@ -26390,10 +26414,10 @@
         <v>6.1</v>
       </c>
       <c r="CL44" t="n">
-        <v>46.77750450146449</v>
+        <v>46.77750451528006</v>
       </c>
       <c r="CM44" t="n">
-        <v>63.73839559242269</v>
+        <v>63.73839560366581</v>
       </c>
       <c r="CN44" t="inlineStr">
         <is>
@@ -26672,37 +26696,37 @@
         <v>38.86000061035156</v>
       </c>
       <c r="BX45" t="n">
-        <v>30.97422547438646</v>
+        <v>30.97422560804202</v>
       </c>
       <c r="BY45" t="n">
-        <v>35.52640292494711</v>
+        <v>35.52640282107112</v>
       </c>
       <c r="BZ45" t="n">
-        <v>38.58971760703754</v>
+        <v>38.58971732768785</v>
       </c>
       <c r="CA45" t="n">
         <v>49.80959882281965</v>
       </c>
       <c r="CB45" t="n">
-        <v>60.09290038986127</v>
+        <v>60.09290023981547</v>
       </c>
       <c r="CC45" t="n">
-        <v>16.76379309441224</v>
+        <v>16.76379308121115</v>
       </c>
       <c r="CD45" t="n">
-        <v>17.31674469858584</v>
+        <v>17.31674446170541</v>
       </c>
       <c r="CE45" t="n">
         <v>28.40888631687585</v>
       </c>
       <c r="CF45" t="n">
-        <v>34.68528366611574</v>
+        <v>34.68528358490357</v>
       </c>
       <c r="CG45" t="n">
-        <v>33.25031419966679</v>
+        <v>33.25031421455657</v>
       </c>
       <c r="CH45" t="n">
-        <v>29.92528277970011</v>
+        <v>29.92528279310091</v>
       </c>
       <c r="CI45" t="n">
         <v>8</v>
@@ -26714,10 +26738,10 @@
         <v>3.6</v>
       </c>
       <c r="CL45" t="n">
-        <v>-22.99206816860269</v>
+        <v>-22.99206813411787</v>
       </c>
       <c r="CM45" t="n">
-        <v>-10.74296674901172</v>
+        <v>-10.74296695799828</v>
       </c>
       <c r="CN45" t="inlineStr">
         <is>
@@ -27000,10 +27024,10 @@
         <v>34.09000015258789</v>
       </c>
       <c r="BX46" t="n">
-        <v>14.7640295843103</v>
+        <v>14.76402957549056</v>
       </c>
       <c r="BY46" t="n">
-        <v>27.38727487889561</v>
+        <v>27.38727486253499</v>
       </c>
       <c r="BZ46" t="n">
         <v>56.67409059244536</v>
@@ -27012,25 +27036,25 @@
         <v>43.80170806643823</v>
       </c>
       <c r="CB46" t="n">
-        <v>73.43420501666635</v>
+        <v>73.43420502770878</v>
       </c>
       <c r="CC46" t="n">
-        <v>38.4778865538025</v>
+        <v>38.47788655595097</v>
       </c>
       <c r="CD46" t="n">
-        <v>41.28355407751093</v>
+        <v>41.28355409419013</v>
       </c>
       <c r="CE46" t="n">
         <v>21.79677261947583</v>
       </c>
       <c r="CF46" t="n">
-        <v>43.26507025789068</v>
+        <v>43.26507025982061</v>
       </c>
       <c r="CG46" t="n">
-        <v>41.28355407751093</v>
+        <v>41.28355409419013</v>
       </c>
       <c r="CH46" t="n">
-        <v>37.15519866975983</v>
+        <v>37.15519868477111</v>
       </c>
       <c r="CI46" t="n">
         <v>7</v>
@@ -27042,10 +27066,10 @@
         <v>5</v>
       </c>
       <c r="CL46" t="n">
-        <v>8.991488716491691</v>
+        <v>8.991488760525957</v>
       </c>
       <c r="CM46" t="n">
-        <v>26.91425656859752</v>
+        <v>26.91425657425879</v>
       </c>
       <c r="CN46" t="inlineStr">
         <is>
@@ -27322,10 +27346,10 @@
         <v>6.400000095367432</v>
       </c>
       <c r="BX47" t="n">
-        <v>7.601720074269004</v>
+        <v>7.601720069726899</v>
       </c>
       <c r="BY47" t="n">
-        <v>11.06810442813567</v>
+        <v>11.06810442152237</v>
       </c>
       <c r="BZ47" t="n">
         <v>7.942720882078913</v>
@@ -27344,7 +27368,7 @@
         <v>5.254390410546408</v>
       </c>
       <c r="CF47" t="n">
-        <v>8.250643827429332</v>
+        <v>8.250643825570098</v>
       </c>
       <c r="CG47" t="n">
         <v>8.296106057582163</v>
@@ -27365,7 +27389,7 @@
         <v>16.66398969632026</v>
       </c>
       <c r="CM47" t="n">
-        <v>28.91630788258064</v>
+        <v>28.9163078535301</v>
       </c>
       <c r="CN47" t="inlineStr">
         <is>
@@ -27552,7 +27576,7 @@
         <v>1</v>
       </c>
       <c r="AT48" t="n">
-        <v>184726978560</v>
+        <v>185049546752</v>
       </c>
       <c r="AU48" t="n">
         <v>7.27</v>
@@ -27630,35 +27654,35 @@
         <v>16.78000068664551</v>
       </c>
       <c r="BX48" t="n">
-        <v>9.985664108946926</v>
+        <v>9.985664045721835</v>
       </c>
       <c r="BY48" t="n">
-        <v>17.51097129326892</v>
+        <v>17.51097130396708</v>
       </c>
       <c r="BZ48" t="n">
-        <v>28.9109798047249</v>
+        <v>28.91098000544013</v>
       </c>
       <c r="CA48" t="n">
         <v>29.08689850705222</v>
       </c>
       <c r="CB48" t="n">
-        <v>32.08964773664928</v>
+        <v>32.0896477399672</v>
       </c>
       <c r="CC48" t="n">
-        <v>27.89695681486392</v>
+        <v>27.89695682918288</v>
       </c>
       <c r="CD48" t="n">
-        <v>14.24941551442479</v>
+        <v>14.2494155930414</v>
       </c>
       <c r="CE48" t="inlineStr"/>
       <c r="CF48" t="n">
-        <v>21.07614300545117</v>
+        <v>21.07614304607798</v>
       </c>
       <c r="CG48" t="n">
-        <v>22.70396405406642</v>
+        <v>22.70396406657498</v>
       </c>
       <c r="CH48" t="n">
-        <v>20.43356764865978</v>
+        <v>20.43356765991748</v>
       </c>
       <c r="CI48" t="n">
         <v>4</v>
@@ -27670,10 +27694,10 @@
         <v>2.9</v>
       </c>
       <c r="CL48" t="n">
-        <v>21.77334214844215</v>
+        <v>21.77334221553217</v>
       </c>
       <c r="CM48" t="n">
-        <v>25.60275412994935</v>
+        <v>25.60275437206383</v>
       </c>
       <c r="CN48" t="inlineStr">
         <is>
@@ -27712,7 +27736,7 @@
         <v>-7.744448996751174</v>
       </c>
       <c r="CZ48" t="n">
-        <v>-20.99429475986069</v>
+        <v>-20.99430923793453</v>
       </c>
       <c r="DA48" t="b">
         <v>1</v>
@@ -27956,10 +27980,10 @@
         <v>12.96000003814697</v>
       </c>
       <c r="BX49" t="n">
-        <v>1.595679006273383</v>
+        <v>1.59567901658905</v>
       </c>
       <c r="BY49" t="n">
-        <v>2.959984556637125</v>
+        <v>2.959984575772688</v>
       </c>
       <c r="BZ49" t="n">
         <v>12.85329345100654</v>
@@ -27968,7 +27992,7 @@
         <v>9.387296094048613</v>
       </c>
       <c r="CB49" t="n">
-        <v>16.22301696557125</v>
+        <v>16.22301697638109</v>
       </c>
       <c r="CC49" t="n">
         <v>6.104046666666666</v>
@@ -28270,10 +28294,10 @@
         <v>32.65999984741211</v>
       </c>
       <c r="BX50" t="n">
-        <v>11.09799940986902</v>
+        <v>11.0979994128159</v>
       </c>
       <c r="BY50" t="n">
-        <v>20.58678890530702</v>
+        <v>20.58678891077349</v>
       </c>
       <c r="BZ50" t="n">
         <v>55.48012794592442</v>
@@ -28282,19 +28306,19 @@
         <v>52.41446107539311</v>
       </c>
       <c r="CB50" t="n">
-        <v>57.78863445266099</v>
+        <v>57.7886344520176</v>
       </c>
       <c r="CC50" t="n">
-        <v>28.23732416031558</v>
+        <v>28.23732416744662</v>
       </c>
       <c r="CD50" t="n">
-        <v>34.98921552956044</v>
+        <v>34.98921552583134</v>
       </c>
       <c r="CE50" t="n">
         <v>54.03219538348082</v>
       </c>
       <c r="CF50" t="n">
-        <v>43.36124963609176</v>
+        <v>43.36124963726677</v>
       </c>
       <c r="CG50" t="n">
         <v>52.41446107539311</v>
@@ -28315,7 +28339,7 @@
         <v>44.43666622243312</v>
       </c>
       <c r="CM50" t="n">
-        <v>32.76561493777101</v>
+        <v>32.76561494136872</v>
       </c>
       <c r="CN50" t="inlineStr">
         <is>
@@ -28594,37 +28618,37 @@
         <v>44.2400016784668</v>
       </c>
       <c r="BX51" t="n">
-        <v>32.08627708822074</v>
+        <v>32.08627715399735</v>
       </c>
       <c r="BY51" t="n">
-        <v>44.20766662732892</v>
+        <v>44.20766650010867</v>
       </c>
       <c r="BZ51" t="n">
-        <v>50.92127242261198</v>
+        <v>50.92127217168321</v>
       </c>
       <c r="CA51" t="n">
         <v>47.73853825853298</v>
       </c>
       <c r="CB51" t="n">
-        <v>70.56922577512088</v>
+        <v>70.56922563943867</v>
       </c>
       <c r="CC51" t="n">
-        <v>59.89362090459586</v>
+        <v>59.89362087737182</v>
       </c>
       <c r="CD51" t="n">
-        <v>25.15601731684175</v>
+        <v>25.15601716385589</v>
       </c>
       <c r="CE51" t="n">
         <v>76.57366731847841</v>
       </c>
       <c r="CF51" t="n">
-        <v>50.89328571396643</v>
+        <v>50.89328563543337</v>
       </c>
       <c r="CG51" t="n">
-        <v>49.32990534057248</v>
+        <v>49.32990521510809</v>
       </c>
       <c r="CH51" t="n">
-        <v>44.39691480651523</v>
+        <v>44.39691469359728</v>
       </c>
       <c r="CI51" t="n">
         <v>8</v>
@@ -28636,10 +28660,10 @@
         <v>3</v>
       </c>
       <c r="CL51" t="n">
-        <v>0.3546860806852292</v>
+        <v>0.3546858254457552</v>
       </c>
       <c r="CM51" t="n">
-        <v>15.03906822575469</v>
+        <v>15.03906804823874</v>
       </c>
       <c r="CN51" t="inlineStr">
         <is>
@@ -28832,7 +28856,7 @@
         <v>1</v>
       </c>
       <c r="AT52" t="n">
-        <v>3038503936</v>
+        <v>3043409408</v>
       </c>
       <c r="AU52" t="n">
         <v>6.1</v>
@@ -28922,37 +28946,37 @@
         <v>10.59000015258789</v>
       </c>
       <c r="BX52" t="n">
-        <v>8.101227370225404</v>
+        <v>8.101227394387069</v>
       </c>
       <c r="BY52" t="n">
-        <v>11.67224167694054</v>
+        <v>11.67224168392359</v>
       </c>
       <c r="BZ52" t="n">
-        <v>17.86658482191027</v>
+        <v>17.8665847793126</v>
       </c>
       <c r="CA52" t="n">
         <v>24.4848677465562</v>
       </c>
       <c r="CB52" t="n">
-        <v>25.3703046655923</v>
+        <v>25.37030468295685</v>
       </c>
       <c r="CC52" t="n">
-        <v>21.06883213633419</v>
+        <v>21.06883213188546</v>
       </c>
       <c r="CD52" t="n">
-        <v>8.897807355316299</v>
+        <v>8.89780733137499</v>
       </c>
       <c r="CE52" t="n">
         <v>10.22838513722926</v>
       </c>
       <c r="CF52" t="n">
-        <v>15.96128136376306</v>
+        <v>15.96128136095325</v>
       </c>
       <c r="CG52" t="n">
-        <v>14.76941324942541</v>
+        <v>14.7694132316181</v>
       </c>
       <c r="CH52" t="n">
-        <v>13.29247192448287</v>
+        <v>13.29247190845629</v>
       </c>
       <c r="CI52" t="n">
         <v>8</v>
@@ -28964,10 +28988,10 @@
         <v>3.1</v>
       </c>
       <c r="CL52" t="n">
-        <v>25.51909096275669</v>
+        <v>25.51909081141979</v>
       </c>
       <c r="CM52" t="n">
-        <v>50.72031287801806</v>
+        <v>50.72031285148544</v>
       </c>
       <c r="CN52" t="inlineStr">
         <is>
@@ -29232,10 +29256,10 @@
         <v>54.20000076293945</v>
       </c>
       <c r="BX53" t="n">
-        <v>10.59687583420033</v>
+        <v>10.59687590534817</v>
       </c>
       <c r="BY53" t="n">
-        <v>19.65720467244162</v>
+        <v>19.65720480442086</v>
       </c>
       <c r="BZ53" t="n">
         <v>62.12370329662177</v>
@@ -29244,7 +29268,7 @@
         <v>46.53820959650967</v>
       </c>
       <c r="CB53" t="n">
-        <v>83.16230736357235</v>
+        <v>83.16230744973755</v>
       </c>
       <c r="CC53" t="n">
         <v>11.76833333333333</v>
@@ -29254,7 +29278,7 @@
       </c>
       <c r="CE53" t="inlineStr"/>
       <c r="CF53" t="n">
-        <v>14.00747127999176</v>
+        <v>14.00747134770079</v>
       </c>
       <c r="CG53" t="n">
         <v>11.76833333333333</v>
@@ -29275,7 +29299,7 @@
         <v>-80.45848735994448</v>
       </c>
       <c r="CM53" t="n">
-        <v>-74.15595741177609</v>
+        <v>-74.15595728685167</v>
       </c>
       <c r="CN53" t="inlineStr">
         <is>
@@ -29540,10 +29564,10 @@
         <v>29.69000053405762</v>
       </c>
       <c r="BX54" t="n">
-        <v>15.52022457805166</v>
+        <v>15.52022458567649</v>
       </c>
       <c r="BY54" t="n">
-        <v>28.79001659228583</v>
+        <v>28.79001660642989</v>
       </c>
       <c r="BZ54" t="n">
         <v>54.71383964899351</v>
@@ -29552,23 +29576,23 @@
         <v>49.40805952371795</v>
       </c>
       <c r="CB54" t="n">
-        <v>60.9179064682199</v>
+        <v>60.91790646631788</v>
       </c>
       <c r="CC54" t="n">
-        <v>36.63500708690665</v>
+        <v>36.63500708552354</v>
       </c>
       <c r="CD54" t="n">
-        <v>30.3269633420922</v>
+        <v>30.32696333156444</v>
       </c>
       <c r="CE54" t="inlineStr"/>
       <c r="CF54" t="n">
-        <v>33.91477197655941</v>
+        <v>33.91477198165586</v>
       </c>
       <c r="CG54" t="n">
-        <v>32.71251183959625</v>
+        <v>32.71251184597671</v>
       </c>
       <c r="CH54" t="n">
-        <v>29.44126065563662</v>
+        <v>29.44126066137904</v>
       </c>
       <c r="CI54" t="n">
         <v>4</v>
@@ -29580,10 +29604,10 @@
         <v>3.5</v>
       </c>
       <c r="CL54" t="n">
-        <v>-0.8377900772876812</v>
+        <v>-0.8377900579464193</v>
       </c>
       <c r="CM54" t="n">
-        <v>14.22961053050684</v>
+        <v>14.22961054767235</v>
       </c>
       <c r="CN54" t="inlineStr">
         <is>
@@ -29780,7 +29804,7 @@
         <v>1</v>
       </c>
       <c r="AT55" t="n">
-        <v>35602051072</v>
+        <v>35655647232</v>
       </c>
       <c r="AU55" t="n">
         <v>10.8</v>
@@ -29870,10 +29894,10 @@
         <v>33.61999893188477</v>
       </c>
       <c r="BX55" t="n">
-        <v>11.88440176800716</v>
+        <v>11.88440178686683</v>
       </c>
       <c r="BY55" t="n">
-        <v>22.04556527965328</v>
+        <v>22.04556531463798</v>
       </c>
       <c r="BZ55" t="n">
         <v>41.2467579488401</v>
@@ -29882,25 +29906,25 @@
         <v>33.64692724932318</v>
       </c>
       <c r="CB55" t="n">
-        <v>43.30177836400607</v>
+        <v>43.30177833762696</v>
       </c>
       <c r="CC55" t="n">
-        <v>23.86565137359892</v>
+        <v>23.86565137002273</v>
       </c>
       <c r="CD55" t="n">
-        <v>25.85073199701815</v>
+        <v>25.85073196506986</v>
       </c>
       <c r="CE55" t="n">
         <v>27.17936043616258</v>
       </c>
       <c r="CF55" t="n">
-        <v>28.62764680207618</v>
+        <v>28.62764680106878</v>
       </c>
       <c r="CG55" t="n">
-        <v>26.51504621659036</v>
+        <v>26.51504620061622</v>
       </c>
       <c r="CH55" t="n">
-        <v>23.86354159493133</v>
+        <v>23.8635415805546</v>
       </c>
       <c r="CI55" t="n">
         <v>8</v>
@@ -29912,10 +29936,10 @@
         <v>3.6</v>
       </c>
       <c r="CL55" t="n">
-        <v>-29.01980263806774</v>
+        <v>-29.01980268083016</v>
       </c>
       <c r="CM55" t="n">
-        <v>-14.84935243431523</v>
+        <v>-14.84935243731167</v>
       </c>
       <c r="CN55" t="inlineStr">
         <is>
@@ -30192,10 +30216,10 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX56" t="n">
-        <v>13.08696650480585</v>
+        <v>13.08696646023153</v>
       </c>
       <c r="BY56" t="n">
-        <v>19.05462323099731</v>
+        <v>19.0546231660971</v>
       </c>
       <c r="BZ56" t="n">
         <v>16.71315021106592</v>
@@ -30214,7 +30238,7 @@
         <v>14.7644299189986</v>
       </c>
       <c r="CF56" t="n">
-        <v>16.15917317961202</v>
+        <v>16.15917316136627</v>
       </c>
       <c r="CG56" t="n">
         <v>15.73879006503226</v>
@@ -30235,7 +30259,7 @@
         <v>34.77555423456011</v>
       </c>
       <c r="CM56" t="n">
-        <v>53.75045506855527</v>
+        <v>53.7504548949515</v>
       </c>
       <c r="CN56" t="inlineStr">
         <is>
@@ -30516,10 +30540,10 @@
         <v>4.639999866485596</v>
       </c>
       <c r="BX57" t="n">
-        <v>1.073494104211733</v>
+        <v>1.073494103516816</v>
       </c>
       <c r="BY57" t="n">
-        <v>1.991331563312764</v>
+        <v>1.991331562023693</v>
       </c>
       <c r="BZ57" t="n">
         <v>9.429447581431615</v>
@@ -30528,13 +30552,13 @@
         <v>8.84348872808631</v>
       </c>
       <c r="CB57" t="n">
-        <v>10.45610111139015</v>
+        <v>10.45610111131063</v>
       </c>
       <c r="CC57" t="n">
-        <v>4.222542560345945</v>
+        <v>4.222542560421149</v>
       </c>
       <c r="CD57" t="n">
-        <v>7.024657961599446</v>
+        <v>7.024657962487384</v>
       </c>
       <c r="CE57" t="n">
         <v>6.880721573088802</v>
@@ -30586,7 +30610,7 @@
         <v>7.906968852776419</v>
       </c>
       <c r="CZ57" t="n">
-        <v>-35.92779681249883</v>
+        <v>-35.92780109506861</v>
       </c>
       <c r="DA57" t="b">
         <v>0</v>
@@ -30826,10 +30850,10 @@
         <v>24.32999992370605</v>
       </c>
       <c r="BX58" t="n">
-        <v>4.265826975745319</v>
+        <v>4.265826971582199</v>
       </c>
       <c r="BY58" t="n">
-        <v>7.913109040007566</v>
+        <v>7.91310903228498</v>
       </c>
       <c r="BZ58" t="n">
         <v>28.32798760888446</v>
@@ -30838,13 +30862,13 @@
         <v>28.21652766068684</v>
       </c>
       <c r="CB58" t="n">
-        <v>25.16978179004833</v>
+        <v>25.16978179246282</v>
       </c>
       <c r="CC58" t="n">
-        <v>2.969809686195788</v>
+        <v>2.969809686291547</v>
       </c>
       <c r="CD58" t="n">
-        <v>18.23371040244403</v>
+        <v>18.233710407181</v>
       </c>
       <c r="CE58" t="n">
         <v>18.22960446774209</v>
@@ -31044,7 +31068,7 @@
         <v>1</v>
       </c>
       <c r="AR59" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="AS59" t="b">
         <v>1</v>
@@ -31140,10 +31164,10 @@
         <v>49.58000183105469</v>
       </c>
       <c r="BX59" t="n">
-        <v>8.252002656023382</v>
+        <v>8.25200271076403</v>
       </c>
       <c r="BY59" t="n">
-        <v>15.30746492692337</v>
+        <v>15.30746502846728</v>
       </c>
       <c r="BZ59" t="n">
         <v>19.41297353018541</v>
@@ -31152,25 +31176,25 @@
         <v>12.06941420422284</v>
       </c>
       <c r="CB59" t="n">
-        <v>13.68856533723321</v>
+        <v>13.68856510575207</v>
       </c>
       <c r="CC59" t="n">
-        <v>20.60981128769878</v>
+        <v>20.60981125429353</v>
       </c>
       <c r="CD59" t="n">
-        <v>10.37232056350202</v>
+        <v>10.37232040376443</v>
       </c>
       <c r="CE59" t="n">
         <v>12.92608390047425</v>
       </c>
       <c r="CF59" t="n">
-        <v>14.07982955078291</v>
+        <v>14.07982951724048</v>
       </c>
       <c r="CG59" t="n">
-        <v>13.30732461885373</v>
+        <v>13.30732450311316</v>
       </c>
       <c r="CH59" t="n">
-        <v>11.97659215696836</v>
+        <v>11.97659205280184</v>
       </c>
       <c r="CI59" t="n">
         <v>8</v>
@@ -31182,10 +31206,10 @@
         <v>2.5</v>
       </c>
       <c r="CL59" t="n">
-        <v>-75.84390537584297</v>
+        <v>-75.84390558594082</v>
       </c>
       <c r="CM59" t="n">
-        <v>-71.60179703348875</v>
+        <v>-71.60179710114188</v>
       </c>
       <c r="CN59" t="inlineStr">
         <is>
@@ -31232,7 +31256,7 @@
         <v>0.6291888987432825</v>
       </c>
       <c r="CZ59" t="n">
-        <v>-8.667873268803072</v>
+        <v>-8.667879823856294</v>
       </c>
       <c r="DA59" t="b">
         <v>0</v>
@@ -31476,37 +31500,37 @@
         <v>23.78000068664551</v>
       </c>
       <c r="BX60" t="n">
-        <v>10.50498166141875</v>
+        <v>10.50498166312909</v>
       </c>
       <c r="BY60" t="n">
-        <v>14.29883865886529</v>
+        <v>14.29883865790862</v>
       </c>
       <c r="BZ60" t="n">
-        <v>17.83956633521545</v>
+        <v>17.83956633111738</v>
       </c>
       <c r="CA60" t="n">
         <v>21.12463825554054</v>
       </c>
       <c r="CB60" t="n">
-        <v>17.52809442314059</v>
+        <v>17.52809442092475</v>
       </c>
       <c r="CC60" t="n">
-        <v>23.23161878080916</v>
+        <v>23.23161878031145</v>
       </c>
       <c r="CD60" t="n">
-        <v>8.786388876565754</v>
+        <v>8.786388874011594</v>
       </c>
       <c r="CE60" t="n">
         <v>18.54956014100212</v>
       </c>
       <c r="CF60" t="n">
-        <v>16.4829608915697</v>
+        <v>16.48296089049319</v>
       </c>
       <c r="CG60" t="n">
-        <v>17.68383037917802</v>
+        <v>17.68383037602106</v>
       </c>
       <c r="CH60" t="n">
-        <v>15.91544734126022</v>
+        <v>15.91544733841896</v>
       </c>
       <c r="CI60" t="n">
         <v>8</v>
@@ -31518,10 +31542,10 @@
         <v>2.6</v>
       </c>
       <c r="CL60" t="n">
-        <v>-33.07213254119839</v>
+        <v>-33.0721325531465</v>
       </c>
       <c r="CM60" t="n">
-        <v>-30.6856164187317</v>
+        <v>-30.68561642325865</v>
       </c>
       <c r="CN60" t="inlineStr">
         <is>
@@ -31804,10 +31828,10 @@
         <v>4.519999980926514</v>
       </c>
       <c r="BX61" t="n">
-        <v>2.935043324979339</v>
+        <v>2.935043322074368</v>
       </c>
       <c r="BY61" t="n">
-        <v>5.444505367836673</v>
+        <v>5.444505362447952</v>
       </c>
       <c r="BZ61" t="n">
         <v>13.16263730709369</v>
@@ -31816,13 +31840,13 @@
         <v>14.66138724509534</v>
       </c>
       <c r="CB61" t="n">
-        <v>15.01900792221398</v>
+        <v>15.01900791745644</v>
       </c>
       <c r="CC61" t="n">
-        <v>9.454768182849323</v>
+        <v>9.454768183224612</v>
       </c>
       <c r="CD61" t="n">
-        <v>6.417766701014832</v>
+        <v>6.417766703642784</v>
       </c>
       <c r="CE61" t="n">
         <v>1.463859008533987</v>
@@ -32118,37 +32142,37 @@
         <v>30</v>
       </c>
       <c r="BX62" t="n">
-        <v>13.81421956836389</v>
+        <v>13.81421956339626</v>
       </c>
       <c r="BY62" t="n">
-        <v>14.42907655209517</v>
+        <v>14.42907655106563</v>
       </c>
       <c r="BZ62" t="n">
-        <v>15.22607859580997</v>
+        <v>15.22607860019891</v>
       </c>
       <c r="CA62" t="n">
         <v>30.50864986347318</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.22999673786265</v>
+        <v>14.22999674012103</v>
       </c>
       <c r="CC62" t="n">
-        <v>30.46475764548752</v>
+        <v>30.46475764652542</v>
       </c>
       <c r="CD62" t="n">
-        <v>6.126727537354133</v>
+        <v>6.126727541747511</v>
       </c>
       <c r="CE62" t="n">
         <v>37.56051795197769</v>
       </c>
       <c r="CF62" t="n">
-        <v>17.82850092863522</v>
+        <v>17.82850092950399</v>
       </c>
       <c r="CG62" t="n">
-        <v>14.42907655209517</v>
+        <v>14.42907655106563</v>
       </c>
       <c r="CH62" t="n">
-        <v>12.98616889688566</v>
+        <v>12.98616889595907</v>
       </c>
       <c r="CI62" t="n">
         <v>7</v>
@@ -32160,10 +32184,10 @@
         <v>6.1</v>
       </c>
       <c r="CL62" t="n">
-        <v>-56.71277034371448</v>
+        <v>-56.71277034680309</v>
       </c>
       <c r="CM62" t="n">
-        <v>-40.57166357121594</v>
+        <v>-40.57166356832003</v>
       </c>
       <c r="CN62" t="inlineStr">
         <is>
@@ -32442,35 +32466,35 @@
         <v>3.509999990463257</v>
       </c>
       <c r="BX63" t="n">
-        <v>2.69427716364097</v>
+        <v>2.694277176986419</v>
       </c>
       <c r="BY63" t="n">
-        <v>3.136287803815716</v>
+        <v>3.13628780818983</v>
       </c>
       <c r="BZ63" t="n">
-        <v>3.840069870095834</v>
+        <v>3.840069856430643</v>
       </c>
       <c r="CA63" t="n">
         <v>7.068546969028743</v>
       </c>
       <c r="CB63" t="n">
-        <v>5.776564267106581</v>
+        <v>5.776564273735336</v>
       </c>
       <c r="CC63" t="n">
-        <v>8.48010465707106</v>
+        <v>8.480104653831324</v>
       </c>
       <c r="CD63" t="n">
-        <v>1.745072098372617</v>
+        <v>1.745072087086637</v>
       </c>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="n">
-        <v>4.677274689875931</v>
+        <v>4.677274689326991</v>
       </c>
       <c r="CG63" t="n">
-        <v>3.840069870095834</v>
+        <v>3.840069856430643</v>
       </c>
       <c r="CH63" t="n">
-        <v>3.456062883086251</v>
+        <v>3.456062870787579</v>
       </c>
       <c r="CI63" t="n">
         <v>7</v>
@@ -32482,10 +32506,10 @@
         <v>4.9</v>
       </c>
       <c r="CL63" t="n">
-        <v>-1.536669730015783</v>
+        <v>-1.536670080405311</v>
       </c>
       <c r="CM63" t="n">
-        <v>33.25568953231293</v>
+        <v>33.25568951667361</v>
       </c>
       <c r="CN63" t="inlineStr">
         <is>
@@ -32764,37 +32788,37 @@
         <v>18.63999938964844</v>
       </c>
       <c r="BX64" t="n">
-        <v>8.745140368994457</v>
+        <v>8.745140358007564</v>
       </c>
       <c r="BY64" t="n">
-        <v>9.206222538695553</v>
+        <v>9.206222539254405</v>
       </c>
       <c r="BZ64" t="n">
-        <v>9.666395044717083</v>
+        <v>9.666395057448174</v>
       </c>
       <c r="CA64" t="n">
         <v>16.93457208699175</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.239151923695749</v>
+        <v>9.239151933083861</v>
       </c>
       <c r="CC64" t="n">
-        <v>17.54224666112583</v>
+        <v>17.54224666383774</v>
       </c>
       <c r="CD64" t="n">
-        <v>3.934238764415331</v>
+        <v>3.934238776984336</v>
       </c>
       <c r="CE64" t="n">
         <v>16.16233025852235</v>
       </c>
       <c r="CF64" t="n">
-        <v>11.42878720589476</v>
+        <v>11.42878720926627</v>
       </c>
       <c r="CG64" t="n">
-        <v>9.452773484206416</v>
+        <v>9.452773495266017</v>
       </c>
       <c r="CH64" t="n">
-        <v>8.507496135785775</v>
+        <v>8.507496145739415</v>
       </c>
       <c r="CI64" t="n">
         <v>8</v>
@@ -32806,10 +32830,10 @@
         <v>4.5</v>
       </c>
       <c r="CL64" t="n">
-        <v>-54.35892481568245</v>
+        <v>-54.3589247622831</v>
       </c>
       <c r="CM64" t="n">
-        <v>-38.68676190922174</v>
+        <v>-38.68676189113424</v>
       </c>
       <c r="CN64" t="inlineStr">
         <is>
@@ -33070,10 +33094,10 @@
         <v>12.85999965667725</v>
       </c>
       <c r="BX65" t="n">
-        <v>10.87454813590146</v>
+        <v>10.87454813936121</v>
       </c>
       <c r="BY65" t="n">
-        <v>15.83334208587253</v>
+        <v>15.83334209090992</v>
       </c>
       <c r="BZ65" t="n">
         <v>15.62429864829946</v>
@@ -33090,13 +33114,13 @@
       </c>
       <c r="CE65" t="inlineStr"/>
       <c r="CF65" t="n">
-        <v>12.4163805508517</v>
+        <v>12.41638055297598</v>
       </c>
       <c r="CG65" t="n">
-        <v>13.24942339210046</v>
+        <v>13.24942339383033</v>
       </c>
       <c r="CH65" t="n">
-        <v>11.92448105289041</v>
+        <v>11.9244810544473</v>
       </c>
       <c r="CI65" t="n">
         <v>4</v>
@@ -33108,10 +33132,10 @@
         <v>2.2</v>
       </c>
       <c r="CL65" t="n">
-        <v>-7.274639414948092</v>
+        <v>-7.274639402841665</v>
       </c>
       <c r="CM65" t="n">
-        <v>-3.449604336460543</v>
+        <v>-3.449604319942001</v>
       </c>
       <c r="CN65" t="inlineStr">
         <is>
@@ -33388,25 +33412,25 @@
         <v>2.170000076293945</v>
       </c>
       <c r="BX66" t="n">
-        <v>0.6228125152856525</v>
+        <v>0.6228125133092667</v>
       </c>
       <c r="BY66" t="n">
-        <v>0.8838074844942948</v>
+        <v>0.8838074820951158</v>
       </c>
       <c r="BZ66" t="n">
-        <v>3.35295880828858</v>
+        <v>3.35295880982668</v>
       </c>
       <c r="CA66" t="n">
         <v>6.892227907447849</v>
       </c>
       <c r="CB66" t="n">
-        <v>2.573963646665436</v>
+        <v>2.573963643861446</v>
       </c>
       <c r="CC66" t="n">
-        <v>2.231320701730961</v>
+        <v>2.231320701822876</v>
       </c>
       <c r="CD66" t="n">
-        <v>1.666128858502869</v>
+        <v>1.66612885939161</v>
       </c>
       <c r="CE66" t="n">
         <v>4.745898587185464</v>
@@ -33702,10 +33726,10 @@
         <v>36.06999969482422</v>
       </c>
       <c r="BX67" t="n">
-        <v>10.32734671595157</v>
+        <v>10.32734669248367</v>
       </c>
       <c r="BY67" t="n">
-        <v>19.15722815809016</v>
+        <v>19.15722811455722</v>
       </c>
       <c r="BZ67" t="n">
         <v>29.14192048514762</v>
@@ -33714,25 +33738,25 @@
         <v>21.64477052485838</v>
       </c>
       <c r="CB67" t="n">
-        <v>26.34387247886638</v>
+        <v>26.34387253525365</v>
       </c>
       <c r="CC67" t="n">
-        <v>22.88383980055268</v>
+        <v>22.88383980791708</v>
       </c>
       <c r="CD67" t="n">
-        <v>16.89301632983967</v>
+        <v>16.89301637787563</v>
       </c>
       <c r="CE67" t="n">
         <v>26.70821873920952</v>
       </c>
       <c r="CF67" t="n">
-        <v>21.63752665406449</v>
+        <v>21.63752665966285</v>
       </c>
       <c r="CG67" t="n">
-        <v>22.26430516270553</v>
+        <v>22.26430516638773</v>
       </c>
       <c r="CH67" t="n">
-        <v>20.03787464643498</v>
+        <v>20.03787464974896</v>
       </c>
       <c r="CI67" t="n">
         <v>8</v>
@@ -33744,10 +33768,10 @@
         <v>2.8</v>
       </c>
       <c r="CL67" t="n">
-        <v>-44.44725584705158</v>
+        <v>-44.44725583786394</v>
       </c>
       <c r="CM67" t="n">
-        <v>-40.01240133869666</v>
+        <v>-40.01240132317585</v>
       </c>
       <c r="CN67" t="inlineStr">
         <is>
@@ -34030,10 +34054,10 @@
         <v>8.960000038146973</v>
       </c>
       <c r="BX68" t="n">
-        <v>0.5329545618999434</v>
+        <v>0.5329545606120012</v>
       </c>
       <c r="BY68" t="n">
-        <v>0.9886307123243948</v>
+        <v>0.9886307099352621</v>
       </c>
       <c r="BZ68" t="n">
         <v>10.10382983025084</v>
@@ -34042,13 +34066,13 @@
         <v>9.267312794547912</v>
       </c>
       <c r="CB68" t="n">
-        <v>11.09857033859789</v>
+        <v>11.09857033980587</v>
       </c>
       <c r="CC68" t="n">
-        <v>0.7358541828398629</v>
+        <v>0.7358541828631348</v>
       </c>
       <c r="CD68" t="n">
-        <v>8.614201655997848</v>
+        <v>8.614201657721731</v>
       </c>
       <c r="CE68" t="inlineStr"/>
       <c r="CF68" t="inlineStr"/>
@@ -34346,10 +34370,10 @@
         <v>8.510000228881836</v>
       </c>
       <c r="BX69" t="n">
-        <v>1.637947945052621</v>
+        <v>1.637947944939745</v>
       </c>
       <c r="BY69" t="n">
-        <v>3.038393438072611</v>
+        <v>3.038393437863226</v>
       </c>
       <c r="BZ69" t="n">
         <v>24.61954214687431</v>
@@ -34358,13 +34382,13 @@
         <v>24.35075698940731</v>
       </c>
       <c r="CB69" t="n">
-        <v>26.29479861918688</v>
+        <v>26.29479861904839</v>
       </c>
       <c r="CC69" t="n">
-        <v>6.709480300441717</v>
+        <v>6.709480300448409</v>
       </c>
       <c r="CD69" t="n">
-        <v>18.34473464250477</v>
+        <v>18.3447346426346</v>
       </c>
       <c r="CE69" t="n">
         <v>14.67770218220867</v>
@@ -34660,10 +34684,10 @@
         <v>21.79999923706055</v>
       </c>
       <c r="BX70" t="n">
-        <v>6.028554316427626</v>
+        <v>6.028554337916608</v>
       </c>
       <c r="BY70" t="n">
-        <v>11.18296825697325</v>
+        <v>11.18296829683531</v>
       </c>
       <c r="BZ70" t="n">
         <v>32.56482411398559</v>
@@ -34672,25 +34696,25 @@
         <v>33.56557093257108</v>
       </c>
       <c r="CB70" t="n">
-        <v>29.04126497426466</v>
+        <v>29.04126497177954</v>
       </c>
       <c r="CC70" t="n">
-        <v>25.18528583534735</v>
+        <v>25.18528583189161</v>
       </c>
       <c r="CD70" t="n">
-        <v>18.83916136667244</v>
+        <v>18.83916134379097</v>
       </c>
       <c r="CE70" t="n">
         <v>13.17078629161308</v>
       </c>
       <c r="CF70" t="n">
-        <v>23.36426596734678</v>
+        <v>23.36426596892388</v>
       </c>
       <c r="CG70" t="n">
-        <v>25.18528583534735</v>
+        <v>25.18528583189161</v>
       </c>
       <c r="CH70" t="n">
-        <v>22.66675725181262</v>
+        <v>22.66675724870245</v>
       </c>
       <c r="CI70" t="n">
         <v>7</v>
@@ -34702,10 +34726,10 @@
         <v>5.6</v>
       </c>
       <c r="CL70" t="n">
-        <v>3.975954335257792</v>
+        <v>3.975954320990938</v>
       </c>
       <c r="CM70" t="n">
-        <v>7.175535711152414</v>
+        <v>7.17553571838685</v>
       </c>
       <c r="CN70" t="inlineStr">
         <is>
@@ -34984,25 +35008,25 @@
         <v>17.30999946594238</v>
       </c>
       <c r="BX71" t="n">
-        <v>4.028449959362463</v>
+        <v>4.028449923961087</v>
       </c>
       <c r="BY71" t="n">
-        <v>6.904966326115181</v>
+        <v>6.904966282653684</v>
       </c>
       <c r="BZ71" t="n">
-        <v>23.3918415125636</v>
+        <v>23.39184157089357</v>
       </c>
       <c r="CA71" t="n">
         <v>32.83973692061836</v>
       </c>
       <c r="CB71" t="n">
-        <v>16.52656710737862</v>
+        <v>16.52656709058938</v>
       </c>
       <c r="CC71" t="n">
-        <v>20.29662203391253</v>
+        <v>20.29662203773423</v>
       </c>
       <c r="CD71" t="n">
-        <v>11.57930532458114</v>
+        <v>11.57930534841335</v>
       </c>
       <c r="CE71" t="n">
         <v>22.32522379682559</v>
@@ -35054,7 +35078,7 @@
         <v>-1.364797304640797</v>
       </c>
       <c r="CZ71" t="n">
-        <v>-40.04428381701424</v>
+        <v>-40.04429185860444</v>
       </c>
       <c r="DA71" t="b">
         <v>0</v>
@@ -35298,35 +35322,35 @@
         <v>23.89999961853027</v>
       </c>
       <c r="BX72" t="n">
-        <v>22.96133598802207</v>
+        <v>22.96133592951301</v>
       </c>
       <c r="BY72" t="n">
-        <v>28.91661739630188</v>
+        <v>28.91661738030071</v>
       </c>
       <c r="BZ72" t="n">
-        <v>38.25461873928671</v>
+        <v>38.25461881559702</v>
       </c>
       <c r="CA72" t="n">
         <v>61.73697842188816</v>
       </c>
       <c r="CB72" t="n">
-        <v>68.23386856861949</v>
+        <v>68.23386850994055</v>
       </c>
       <c r="CC72" t="n">
-        <v>41.71087888165556</v>
+        <v>41.71087888997986</v>
       </c>
       <c r="CD72" t="n">
-        <v>18.29686827577983</v>
+        <v>18.29686833051155</v>
       </c>
       <c r="CE72" t="inlineStr"/>
       <c r="CF72" t="n">
-        <v>40.01588089593624</v>
+        <v>40.01588089681869</v>
       </c>
       <c r="CG72" t="n">
-        <v>38.25461873928671</v>
+        <v>38.25461881559702</v>
       </c>
       <c r="CH72" t="n">
-        <v>34.42915686535804</v>
+        <v>34.42915693403732</v>
       </c>
       <c r="CI72" t="n">
         <v>7</v>
@@ -35338,10 +35362,10 @@
         <v>3.7</v>
       </c>
       <c r="CL72" t="n">
-        <v>44.05505194512322</v>
+        <v>44.05505223248423</v>
       </c>
       <c r="CM72" t="n">
-        <v>67.43046667210371</v>
+        <v>67.43046667579597</v>
       </c>
       <c r="CN72" t="inlineStr">
         <is>
@@ -35624,10 +35648,10 @@
         <v>24.69000053405762</v>
       </c>
       <c r="BX73" t="n">
-        <v>4.528795225603813</v>
+        <v>4.528795226970716</v>
       </c>
       <c r="BY73" t="n">
-        <v>8.400915143495071</v>
+        <v>8.400915146030677</v>
       </c>
       <c r="BZ73" t="n">
         <v>29.76728908792206</v>
@@ -35636,19 +35660,19 @@
         <v>25.23396384622111</v>
       </c>
       <c r="CB73" t="n">
-        <v>34.47267202160594</v>
+        <v>34.47267201994089</v>
       </c>
       <c r="CC73" t="n">
-        <v>11.78156829089155</v>
+        <v>11.78156829073316</v>
       </c>
       <c r="CD73" t="n">
-        <v>24.04380283850851</v>
+        <v>24.04380283636739</v>
       </c>
       <c r="CE73" t="n">
         <v>24.69000053405762</v>
       </c>
       <c r="CF73" t="n">
-        <v>24.99821610320113</v>
+        <v>24.99821610254037</v>
       </c>
       <c r="CG73" t="n">
         <v>24.96198219013936</v>
@@ -35669,7 +35693,7 @@
         <v>-9.008572356505573</v>
       </c>
       <c r="CM73" t="n">
-        <v>1.248341686823218</v>
+        <v>1.248341684146981</v>
       </c>
       <c r="CN73" t="inlineStr">
         <is>
@@ -35948,10 +35972,10 @@
         <v>4.050000190734863</v>
       </c>
       <c r="BX74" t="n">
-        <v>0.9831252803867552</v>
+        <v>0.9831252852257534</v>
       </c>
       <c r="BY74" t="n">
-        <v>1.823697395117431</v>
+        <v>1.823697404093773</v>
       </c>
       <c r="BZ74" t="n">
         <v>6.002517061212185</v>
@@ -35960,7 +35984,7 @@
         <v>3.984656322398878</v>
       </c>
       <c r="CB74" t="n">
-        <v>8.334872123762587</v>
+        <v>8.334872131340436</v>
       </c>
       <c r="CC74" t="n">
         <v>3.760485277130923</v>
@@ -36018,7 +36042,7 @@
         <v>1.50376393620828</v>
       </c>
       <c r="CZ74" t="n">
-        <v>-44.63291810308804</v>
+        <v>-44.6329217901767</v>
       </c>
       <c r="DA74" t="b">
         <v>0</v>
@@ -36262,10 +36286,10 @@
         <v>12.53999996185303</v>
       </c>
       <c r="BX75" t="n">
-        <v>2.074260016618082</v>
+        <v>2.074260018315232</v>
       </c>
       <c r="BY75" t="n">
-        <v>3.847752330826541</v>
+        <v>3.847752333974756</v>
       </c>
       <c r="BZ75" t="n">
         <v>16.17867570540921</v>
@@ -36274,7 +36298,7 @@
         <v>12.83897725188507</v>
       </c>
       <c r="CB75" t="n">
-        <v>21.1431002590505</v>
+        <v>21.14310026136404</v>
       </c>
       <c r="CC75" t="n">
         <v>9.294207014285712</v>
@@ -36578,10 +36602,10 @@
         <v>55.5</v>
       </c>
       <c r="BX76" t="n">
-        <v>40.36268314759089</v>
+        <v>40.36268280731368</v>
       </c>
       <c r="BY76" t="n">
-        <v>58.76806666289232</v>
+        <v>58.76806616744873</v>
       </c>
       <c r="BZ76" t="n">
         <v>35.62962962962963</v>
@@ -36600,13 +36624,13 @@
         <v>48.31609747574325</v>
       </c>
       <c r="CF76" t="n">
-        <v>43.22743367524398</v>
+        <v>43.22743353595718</v>
       </c>
       <c r="CG76" t="n">
-        <v>41.42467013687187</v>
+        <v>41.42466996673326</v>
       </c>
       <c r="CH76" t="n">
-        <v>37.28220312318468</v>
+        <v>37.28220297005993</v>
       </c>
       <c r="CI76" t="n">
         <v>6</v>
@@ -36618,10 +36642,10 @@
         <v>6.4</v>
       </c>
       <c r="CL76" t="n">
-        <v>-32.82485923750508</v>
+        <v>-32.82485951340553</v>
       </c>
       <c r="CM76" t="n">
-        <v>-22.11273211667751</v>
+        <v>-22.11273236764473</v>
       </c>
       <c r="CN76" t="inlineStr">
         <is>
@@ -36904,10 +36928,10 @@
         <v>28.85000038146973</v>
       </c>
       <c r="BX77" t="n">
-        <v>13.47679396000606</v>
+        <v>13.476794007096</v>
       </c>
       <c r="BY77" t="n">
-        <v>24.99945279581124</v>
+        <v>24.99945288316308</v>
       </c>
       <c r="BZ77" t="n">
         <v>37.04094041225521</v>
@@ -36916,19 +36940,19 @@
         <v>25.82930863038749</v>
       </c>
       <c r="CB77" t="n">
-        <v>42.24730476188387</v>
+        <v>42.24730465191892</v>
       </c>
       <c r="CC77" t="n">
-        <v>42.15809545719594</v>
+        <v>42.15809543304904</v>
       </c>
       <c r="CD77" t="n">
-        <v>22.53170146490495</v>
+        <v>22.53170135562991</v>
       </c>
       <c r="CE77" t="n">
         <v>25.12299540697245</v>
       </c>
       <c r="CF77" t="n">
-        <v>29.17582411117715</v>
+        <v>29.17582409755902</v>
       </c>
       <c r="CG77" t="n">
         <v>25.47615201867997</v>
@@ -36949,7 +36973,7 @@
         <v>-20.52500341892921</v>
       </c>
       <c r="CM77" t="n">
-        <v>1.129371665161916</v>
+        <v>1.129371617958674</v>
       </c>
       <c r="CN77" t="inlineStr">
         <is>
@@ -36988,7 +37012,7 @@
         <v>-2.337816543811788</v>
       </c>
       <c r="CZ77" t="n">
-        <v>-24.19493061245316</v>
+        <v>-24.19493858539801</v>
       </c>
       <c r="DA77" t="b">
         <v>0</v>
@@ -37232,10 +37256,10 @@
         <v>15.11999988555908</v>
       </c>
       <c r="BX78" t="n">
-        <v>2.439882936514444</v>
+        <v>2.439882946110683</v>
       </c>
       <c r="BY78" t="n">
-        <v>4.525982847234292</v>
+        <v>4.525982865035316</v>
       </c>
       <c r="BZ78" t="n">
         <v>25.45616245027419</v>
@@ -37244,7 +37268,7 @@
         <v>19.49357338326157</v>
       </c>
       <c r="CB78" t="n">
-        <v>33.15862254060844</v>
+        <v>33.15862255767926</v>
       </c>
       <c r="CC78" t="n">
         <v>10.38593205872702</v>
@@ -37550,10 +37574,10 @@
         <v>14.64999961853027</v>
       </c>
       <c r="BX79" t="n">
-        <v>9.577574314743025</v>
+        <v>9.577574299101698</v>
       </c>
       <c r="BY79" t="n">
-        <v>17.76640035384831</v>
+        <v>17.76640032483365</v>
       </c>
       <c r="BZ79" t="n">
         <v>13.92485616538925</v>
@@ -37574,7 +37598,7 @@
         <v>12.21188626720157</v>
       </c>
       <c r="CF79" t="n">
-        <v>15.01496754096154</v>
+        <v>15.01496753537954</v>
       </c>
       <c r="CG79" t="n">
         <v>13.27530794084946</v>
@@ -37595,7 +37619,7 @@
         <v>-18.44520506572443</v>
       </c>
       <c r="CM79" t="n">
-        <v>2.491248682147584</v>
+        <v>2.491248644045196</v>
       </c>
       <c r="CN79" t="inlineStr">
         <is>
@@ -37874,25 +37898,25 @@
         <v>26.55999946594238</v>
       </c>
       <c r="BX80" t="n">
-        <v>12.09583915727284</v>
+        <v>12.09583918761416</v>
       </c>
       <c r="BY80" t="n">
-        <v>12.77825688660922</v>
+        <v>12.77825690067539</v>
       </c>
       <c r="BZ80" t="n">
-        <v>14.05452305393115</v>
+        <v>14.05452303414772</v>
       </c>
       <c r="CA80" t="n">
         <v>32.71469597157468</v>
       </c>
       <c r="CB80" t="n">
-        <v>13.10490990707559</v>
+        <v>13.10490990598231</v>
       </c>
       <c r="CC80" t="n">
-        <v>24.67124335385076</v>
+        <v>24.67124334978705</v>
       </c>
       <c r="CD80" t="n">
-        <v>5.748575086502372</v>
+        <v>5.74857506709121</v>
       </c>
       <c r="CE80" t="n">
         <v>64.69524327175267</v>
@@ -37944,7 +37968,7 @@
         <v>-2.572884986294177</v>
       </c>
       <c r="CZ80" t="n">
-        <v>-18.09285086071385</v>
+        <v>-18.09284111970466</v>
       </c>
       <c r="DA80" t="b">
         <v>0</v>
@@ -38188,10 +38212,10 @@
         <v>6.949999809265137</v>
       </c>
       <c r="BX81" t="n">
-        <v>1.251744409315434</v>
+        <v>1.251744409468299</v>
       </c>
       <c r="BY81" t="n">
-        <v>2.32198587928013</v>
+        <v>2.321985879563695</v>
       </c>
       <c r="BZ81" t="n">
         <v>10.39362273958951</v>
@@ -38200,13 +38224,13 @@
         <v>10.1957267373713</v>
       </c>
       <c r="CB81" t="n">
-        <v>10.06783796772863</v>
+        <v>10.06783796768597</v>
       </c>
       <c r="CC81" t="n">
-        <v>1.873467349285255</v>
+        <v>1.873467349279102</v>
       </c>
       <c r="CD81" t="n">
-        <v>7.180621350425031</v>
+        <v>7.180621350246386</v>
       </c>
       <c r="CE81" t="n">
         <v>11.09654186695129</v>
@@ -38502,10 +38526,10 @@
         <v>9.840000152587891</v>
       </c>
       <c r="BX82" t="n">
-        <v>6.031752834336914</v>
+        <v>6.031752916606836</v>
       </c>
       <c r="BY82" t="n">
-        <v>11.18890150769498</v>
+        <v>11.18890166030568</v>
       </c>
       <c r="BZ82" t="n">
         <v>7.877945741497857</v>
@@ -38526,7 +38550,7 @@
         <v>39.41309108925088</v>
       </c>
       <c r="CF82" t="n">
-        <v>10.02204606903851</v>
+        <v>10.02204610259289</v>
       </c>
       <c r="CG82" t="n">
         <v>7.877945741497857</v>
@@ -38547,7 +38571,7 @@
         <v>-27.94561933534744</v>
       </c>
       <c r="CM82" t="n">
-        <v>1.85006009784201</v>
+        <v>1.850060438841772</v>
       </c>
       <c r="CN82" t="inlineStr">
         <is>
@@ -39150,10 +39174,10 @@
         <v>5.159999847412109</v>
       </c>
       <c r="BX84" t="n">
-        <v>3.051428238164765</v>
+        <v>3.051428234957723</v>
       </c>
       <c r="BY84" t="n">
-        <v>4.442879514767899</v>
+        <v>4.442879510098445</v>
       </c>
       <c r="BZ84" t="n">
         <v>4.310361318320155</v>
@@ -39462,10 +39486,10 @@
         <v>18.45999908447266</v>
       </c>
       <c r="BX85" t="n">
-        <v>4.484582526614111</v>
+        <v>4.484582526113639</v>
       </c>
       <c r="BY85" t="n">
-        <v>8.318900586869175</v>
+        <v>8.318900585940799</v>
       </c>
       <c r="BZ85" t="n">
         <v>32.05701020567007</v>
@@ -39474,13 +39498,13 @@
         <v>34.58764733946176</v>
       </c>
       <c r="CB85" t="n">
-        <v>27.93570166416457</v>
+        <v>27.935701664017</v>
       </c>
       <c r="CC85" t="n">
-        <v>11.13048461173803</v>
+        <v>11.13048461177082</v>
       </c>
       <c r="CD85" t="n">
-        <v>18.85057246788134</v>
+        <v>18.85057246836579</v>
       </c>
       <c r="CE85" t="n">
         <v>43.59359053230504</v>
@@ -40064,10 +40088,10 @@
         <v>52.93999862670898</v>
       </c>
       <c r="BX87" t="n">
-        <v>11.11616389206109</v>
+        <v>11.1161639310337</v>
       </c>
       <c r="BY87" t="n">
-        <v>16.18513462684095</v>
+        <v>16.18513468358507</v>
       </c>
       <c r="BZ87" t="inlineStr"/>
       <c r="CA87" t="inlineStr"/>
@@ -40078,13 +40102,13 @@
       <c r="CD87" t="inlineStr"/>
       <c r="CE87" t="inlineStr"/>
       <c r="CF87" t="n">
-        <v>17.87633283963401</v>
+        <v>17.87633287153959</v>
       </c>
       <c r="CG87" t="n">
-        <v>16.18513462684095</v>
+        <v>16.18513468358507</v>
       </c>
       <c r="CH87" t="n">
-        <v>14.56662116415685</v>
+        <v>14.56662121522656</v>
       </c>
       <c r="CI87" t="n">
         <v>3</v>
@@ -40096,10 +40120,10 @@
         <v>2.4</v>
       </c>
       <c r="CL87" t="n">
-        <v>-72.48465896860112</v>
+        <v>-72.48465887213398</v>
       </c>
       <c r="CM87" t="n">
-        <v>-66.23284226793473</v>
+        <v>-66.2328422076673</v>
       </c>
       <c r="CN87" t="inlineStr">
         <is>
@@ -40386,10 +40410,10 @@
         <v>22.45000076293945</v>
       </c>
       <c r="BX88" t="n">
-        <v>11.31405127711271</v>
+        <v>11.31405123453609</v>
       </c>
       <c r="BY88" t="n">
-        <v>20.98756511904407</v>
+        <v>20.98756504006445</v>
       </c>
       <c r="BZ88" t="n">
         <v>14.70402916999247</v>
@@ -40410,13 +40434,13 @@
         <v>22.45000076293945</v>
       </c>
       <c r="CF88" t="n">
-        <v>19.21790737576281</v>
+        <v>19.21790736056828</v>
       </c>
       <c r="CG88" t="n">
-        <v>17.84579714451827</v>
+        <v>17.84579710502846</v>
       </c>
       <c r="CH88" t="n">
-        <v>16.06121743006645</v>
+        <v>16.06121739452561</v>
       </c>
       <c r="CI88" t="n">
         <v>8</v>
@@ -40428,10 +40452,10 @@
         <v>2.9</v>
       </c>
       <c r="CL88" t="n">
-        <v>-28.4578312505879</v>
+        <v>-28.45783140889896</v>
       </c>
       <c r="CM88" t="n">
-        <v>-14.39685201486585</v>
+        <v>-14.3968520825475</v>
       </c>
       <c r="CN88" t="inlineStr">
         <is>
@@ -40714,25 +40738,25 @@
         <v>1.690000057220459</v>
       </c>
       <c r="BX89" t="n">
-        <v>0.1506862964655604</v>
+        <v>0.1506862969119019</v>
       </c>
       <c r="BY89" t="n">
-        <v>0.1716552917534419</v>
+        <v>0.171655292241899</v>
       </c>
       <c r="BZ89" t="n">
-        <v>0.7699467078869987</v>
+        <v>0.76994670779731</v>
       </c>
       <c r="CA89" t="n">
         <v>3.206293162785219</v>
       </c>
       <c r="CB89" t="n">
-        <v>0.2622355695370812</v>
+        <v>0.2622355697644808</v>
       </c>
       <c r="CC89" t="n">
-        <v>0.5414652897239964</v>
+        <v>0.5414652897170932</v>
       </c>
       <c r="CD89" t="n">
-        <v>0.3433710222704051</v>
+        <v>0.3433710221934202</v>
       </c>
       <c r="CE89" t="inlineStr"/>
       <c r="CF89" t="inlineStr"/>
@@ -41024,10 +41048,10 @@
         <v>13.89999961853027</v>
       </c>
       <c r="BX90" t="n">
-        <v>6.000512446956895</v>
+        <v>6.000512423971051</v>
       </c>
       <c r="BY90" t="n">
-        <v>8.73674612276924</v>
+        <v>8.736746089301851</v>
       </c>
       <c r="BZ90" t="n">
         <v>3.721936046156407</v>
@@ -41240,13 +41264,13 @@
         <v>0</v>
       </c>
       <c r="AR91" t="n">
-        <v>5.54</v>
+        <v>5.5</v>
       </c>
       <c r="AS91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="n">
-        <v>2883450880</v>
+        <v>2905931264</v>
       </c>
       <c r="AU91" t="n">
         <v>6.69</v>
@@ -41336,10 +41360,10 @@
         <v>7.420000076293945</v>
       </c>
       <c r="BX91" t="n">
-        <v>3.087627410921433</v>
+        <v>3.087627415681174</v>
       </c>
       <c r="BY91" t="n">
-        <v>5.727548847259259</v>
+        <v>5.727548856088577</v>
       </c>
       <c r="BZ91" t="n">
         <v>14.69581479983479</v>
@@ -41348,23 +41372,23 @@
         <v>15.81853464622579</v>
       </c>
       <c r="CB91" t="n">
-        <v>13.96090354078211</v>
+        <v>13.96090354335939</v>
       </c>
       <c r="CC91" t="n">
-        <v>14.98505630921318</v>
+        <v>14.98505630827882</v>
       </c>
       <c r="CD91" t="n">
-        <v>7.676901762553888</v>
+        <v>7.676901757912952</v>
       </c>
       <c r="CE91" t="inlineStr"/>
       <c r="CF91" t="n">
-        <v>12.14412665097817</v>
+        <v>12.14412665195005</v>
       </c>
       <c r="CG91" t="n">
-        <v>14.32835917030845</v>
+        <v>14.32835917159709</v>
       </c>
       <c r="CH91" t="n">
-        <v>12.8955232532776</v>
+        <v>12.89552325443738</v>
       </c>
       <c r="CI91" t="n">
         <v>6</v>
@@ -41376,10 +41400,10 @@
         <v>5.1</v>
       </c>
       <c r="CL91" t="n">
-        <v>73.79411213858786</v>
+        <v>73.7941121542183</v>
       </c>
       <c r="CM91" t="n">
-        <v>63.66747339770613</v>
+        <v>63.66747341080434</v>
       </c>
       <c r="CN91" t="inlineStr">
         <is>
@@ -41660,10 +41684,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="BX92" t="n">
-        <v>33.76252252757943</v>
+        <v>33.76252270278441</v>
       </c>
       <c r="BY92" t="n">
-        <v>62.62947928865985</v>
+        <v>62.62947961366508</v>
       </c>
       <c r="BZ92" t="n">
         <v>4.845639321919829</v>
@@ -41956,35 +41980,35 @@
         <v>19.56999969482422</v>
       </c>
       <c r="BX93" t="n">
-        <v>11.66679778820169</v>
+        <v>11.66679783229677</v>
       </c>
       <c r="BY93" t="n">
-        <v>15.05415848162744</v>
+        <v>15.05415850942537</v>
       </c>
       <c r="BZ93" t="n">
-        <v>23.36416668695797</v>
+        <v>23.36416664179487</v>
       </c>
       <c r="CA93" t="n">
         <v>42.43044465422032</v>
       </c>
       <c r="CB93" t="n">
-        <v>28.36136799884158</v>
+        <v>28.36136802948199</v>
       </c>
       <c r="CC93" t="n">
-        <v>15.78799047584118</v>
+        <v>15.78799047285409</v>
       </c>
       <c r="CD93" t="n">
-        <v>11.30020723028571</v>
+        <v>11.30020719928157</v>
       </c>
       <c r="CE93" t="inlineStr"/>
       <c r="CF93" t="n">
-        <v>16.46827835815707</v>
+        <v>16.46827836409277</v>
       </c>
       <c r="CG93" t="n">
-        <v>15.42107447873431</v>
+        <v>15.42107449113973</v>
       </c>
       <c r="CH93" t="n">
-        <v>13.87896703086088</v>
+        <v>13.87896704202575</v>
       </c>
       <c r="CI93" t="n">
         <v>4</v>
@@ -41996,10 +42020,10 @@
         <v>2</v>
       </c>
       <c r="CL93" t="n">
-        <v>-29.08039219575704</v>
+        <v>-29.08039213870607</v>
       </c>
       <c r="CM93" t="n">
-        <v>-15.84936834458651</v>
+        <v>-15.84936831425591</v>
       </c>
       <c r="CN93" t="inlineStr">
         <is>
@@ -42284,10 +42308,10 @@
         <v>7.78000020980835</v>
       </c>
       <c r="BX94" t="n">
-        <v>5.007638599162151</v>
+        <v>5.007638630278256</v>
       </c>
       <c r="BY94" t="n">
-        <v>7.291121800380092</v>
+        <v>7.291121845685142</v>
       </c>
       <c r="BZ94" t="n">
         <v>5.901677766740105</v>
@@ -42306,13 +42330,13 @@
         <v>7.749646363977103</v>
       </c>
       <c r="CF94" t="n">
-        <v>6.63572261221213</v>
+        <v>6.63572262494899</v>
       </c>
       <c r="CG94" t="n">
-        <v>6.596399783560098</v>
+        <v>6.596399806212624</v>
       </c>
       <c r="CH94" t="n">
-        <v>5.936759805204089</v>
+        <v>5.936759825591362</v>
       </c>
       <c r="CI94" t="n">
         <v>6</v>
@@ -42324,10 +42348,10 @@
         <v>5.9</v>
       </c>
       <c r="CL94" t="n">
-        <v>-23.69203540997934</v>
+        <v>-23.69203514793213</v>
       </c>
       <c r="CM94" t="n">
-        <v>-14.7079378758064</v>
+        <v>-14.70793771209356</v>
       </c>
       <c r="CN94" t="inlineStr">
         <is>
@@ -42604,10 +42628,10 @@
         <v>78.69999694824219</v>
       </c>
       <c r="BX95" t="n">
-        <v>58.83949696770487</v>
+        <v>58.83949690255483</v>
       </c>
       <c r="BY95" t="n">
-        <v>85.67030758497829</v>
+        <v>85.67030749011985</v>
       </c>
       <c r="BZ95" t="n">
         <v>24.36677488126581</v>
@@ -42920,10 +42944,10 @@
         <v>35.65000152587891</v>
       </c>
       <c r="BX96" t="n">
-        <v>8.82343359107422</v>
+        <v>8.82343361691944</v>
       </c>
       <c r="BY96" t="n">
-        <v>16.36746931144268</v>
+        <v>16.36746935938556</v>
       </c>
       <c r="BZ96" t="n">
         <v>40.6508192958602</v>
@@ -42932,19 +42956,19 @@
         <v>40.9156147189668</v>
       </c>
       <c r="CB96" t="n">
-        <v>33.77771535652502</v>
+        <v>33.77771534196432</v>
       </c>
       <c r="CC96" t="n">
-        <v>50.02798605662933</v>
+        <v>50.02798604970015</v>
       </c>
       <c r="CD96" t="n">
-        <v>22.74549483737613</v>
+        <v>22.74549480865072</v>
       </c>
       <c r="CE96" t="n">
         <v>51.81998252253128</v>
       </c>
       <c r="CF96" t="n">
-        <v>36.61501172847591</v>
+        <v>36.61501172815129</v>
       </c>
       <c r="CG96" t="n">
         <v>40.6508192958602</v>
@@ -42965,7 +42989,7 @@
         <v>2.624784853700501</v>
       </c>
       <c r="CM96" t="n">
-        <v>2.706900873192075</v>
+        <v>2.706900872281492</v>
       </c>
       <c r="CN96" t="inlineStr">
         <is>
@@ -43152,7 +43176,7 @@
         <v>1</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AS97" t="b">
         <v>1</v>
@@ -43248,10 +43272,10 @@
         <v>19.59000015258789</v>
       </c>
       <c r="BX97" t="n">
-        <v>2.021554710947838</v>
+        <v>2.02155471065194</v>
       </c>
       <c r="BY97" t="n">
-        <v>3.749983988808239</v>
+        <v>3.749983988259349</v>
       </c>
       <c r="BZ97" t="n">
         <v>10.29621190090399</v>
@@ -43260,19 +43284,19 @@
         <v>8.591723366671241</v>
       </c>
       <c r="CB97" t="n">
-        <v>10.2181918440686</v>
+        <v>10.21819184466693</v>
       </c>
       <c r="CC97" t="n">
-        <v>7.543992734658171</v>
+        <v>7.543992734724452</v>
       </c>
       <c r="CD97" t="n">
-        <v>7.793097664024891</v>
+        <v>7.793097664504271</v>
       </c>
       <c r="CE97" t="n">
         <v>13.94714750731148</v>
       </c>
       <c r="CF97" t="n">
-        <v>8.877192715206659</v>
+        <v>8.877192715291674</v>
       </c>
       <c r="CG97" t="n">
         <v>8.591723366671241</v>
@@ -43293,7 +43317,7 @@
         <v>-60.5280705983934</v>
       </c>
       <c r="CM97" t="n">
-        <v>-54.68508092873109</v>
+        <v>-54.68508092829711</v>
       </c>
       <c r="CN97" t="inlineStr">
         <is>
@@ -43572,10 +43596,10 @@
         <v>6.96999979019165</v>
       </c>
       <c r="BX98" t="n">
-        <v>3.120765495385176</v>
+        <v>3.120765487311461</v>
       </c>
       <c r="BY98" t="n">
-        <v>5.7890199939395</v>
+        <v>5.789019978962759</v>
       </c>
       <c r="BZ98" t="inlineStr"/>
       <c r="CA98" t="inlineStr"/>
@@ -43586,13 +43610,13 @@
         <v>9.575517828204783</v>
       </c>
       <c r="CF98" t="n">
-        <v>6.161767772509819</v>
+        <v>6.161767764826334</v>
       </c>
       <c r="CG98" t="n">
-        <v>5.7890199939395</v>
+        <v>5.789019978962759</v>
       </c>
       <c r="CH98" t="n">
-        <v>5.21011799454555</v>
+        <v>5.210117981066483</v>
       </c>
       <c r="CI98" t="n">
         <v>3</v>
@@ -43604,10 +43628,10 @@
         <v>3.1</v>
       </c>
       <c r="CL98" t="n">
-        <v>-25.24938089844203</v>
+        <v>-25.24938109182894</v>
       </c>
       <c r="CM98" t="n">
-        <v>-11.59586860847822</v>
+        <v>-11.59586871871474</v>
       </c>
       <c r="CN98" t="inlineStr">
         <is>
@@ -43886,10 +43910,10 @@
         <v>15.90999984741211</v>
       </c>
       <c r="BX99" t="n">
-        <v>8.011259034438897</v>
+        <v>8.011259078355248</v>
       </c>
       <c r="BY99" t="n">
-        <v>14.86088550888416</v>
+        <v>14.86088559034899</v>
       </c>
       <c r="BZ99" t="n">
         <v>10.0768402475244</v>
@@ -43910,7 +43934,7 @@
         <v>9.68787499591881</v>
       </c>
       <c r="CF99" t="n">
-        <v>12.14489900933284</v>
+        <v>12.14489902500549</v>
       </c>
       <c r="CG99" t="n">
         <v>9.882357621721603</v>
@@ -43931,7 +43955,7 @@
         <v>-44.09728507322303</v>
       </c>
       <c r="CM99" t="n">
-        <v>-23.66499606655679</v>
+        <v>-23.66499596804863</v>
       </c>
       <c r="CN99" t="inlineStr">
         <is>
@@ -44210,37 +44234,37 @@
         <v>23.35000038146973</v>
       </c>
       <c r="BX100" t="n">
-        <v>5.11442746968105</v>
+        <v>5.114427473520455</v>
       </c>
       <c r="BY100" t="n">
-        <v>7.241067272759674</v>
+        <v>7.241067273608026</v>
       </c>
       <c r="BZ100" t="n">
-        <v>10.68010867829654</v>
+        <v>10.68010867153024</v>
       </c>
       <c r="CA100" t="n">
         <v>14.69322801178486</v>
       </c>
       <c r="CB100" t="n">
-        <v>7.189980057551855</v>
+        <v>7.189980053737015</v>
       </c>
       <c r="CC100" t="n">
-        <v>8.433621534685914</v>
+        <v>8.433621534205118</v>
       </c>
       <c r="CD100" t="n">
-        <v>5.305073947922764</v>
+        <v>5.30507394399674</v>
       </c>
       <c r="CE100" t="n">
         <v>10.70565447273137</v>
       </c>
       <c r="CF100" t="n">
-        <v>8.670395180676753</v>
+        <v>8.670395179389228</v>
       </c>
       <c r="CG100" t="n">
-        <v>7.837344403722794</v>
+        <v>7.837344403906572</v>
       </c>
       <c r="CH100" t="n">
-        <v>7.053609963350515</v>
+        <v>7.053609963515915</v>
       </c>
       <c r="CI100" t="n">
         <v>8</v>
@@ -44252,10 +44276,10 @@
         <v>2.9</v>
       </c>
       <c r="CL100" t="n">
-        <v>-69.7918207789488</v>
+        <v>-69.79182077824045</v>
       </c>
       <c r="CM100" t="n">
-        <v>-62.8676871990226</v>
+        <v>-62.86768720453664</v>
       </c>
       <c r="CN100" t="inlineStr">
         <is>
@@ -44538,10 +44562,10 @@
         <v>46.34000015258789</v>
       </c>
       <c r="BX101" t="n">
-        <v>10.13865030172593</v>
+        <v>10.13865031786108</v>
       </c>
       <c r="BY101" t="n">
-        <v>18.80719630970159</v>
+        <v>18.8071963396323</v>
       </c>
       <c r="BZ101" t="n">
         <v>85.99509832237949</v>
@@ -44550,13 +44574,13 @@
         <v>76.05105676896386</v>
       </c>
       <c r="CB101" t="n">
-        <v>103.2434128202686</v>
+        <v>103.2434128147695</v>
       </c>
       <c r="CC101" t="n">
-        <v>16.00028353605608</v>
+        <v>16.00028353524475</v>
       </c>
       <c r="CD101" t="n">
-        <v>69.73813928428642</v>
+        <v>69.73813926094338</v>
       </c>
       <c r="CE101" t="n">
         <v>22.26855095916991</v>
@@ -44856,25 +44880,25 @@
         <v>47.2400016784668</v>
       </c>
       <c r="BX102" t="n">
-        <v>18.15640577959575</v>
+        <v>18.15640585802479</v>
       </c>
       <c r="BY102" t="n">
-        <v>20.03634734176276</v>
+        <v>20.03634737804936</v>
       </c>
       <c r="BZ102" t="n">
-        <v>23.56749661055763</v>
+        <v>23.5674965514363</v>
       </c>
       <c r="CA102" t="n">
         <v>50.82999467797423</v>
       </c>
       <c r="CB102" t="n">
-        <v>19.57321332947267</v>
+        <v>19.57321331354185</v>
       </c>
       <c r="CC102" t="n">
-        <v>23.26810817483054</v>
+        <v>23.26810816825912</v>
       </c>
       <c r="CD102" t="n">
-        <v>10.17796768561637</v>
+        <v>10.17796763192072</v>
       </c>
       <c r="CE102" t="n">
         <v>117.5954097189415</v>
@@ -45170,10 +45194,10 @@
         <v>12.18000030517578</v>
       </c>
       <c r="BX103" t="n">
-        <v>2.16666622579208</v>
+        <v>2.166666237221406</v>
       </c>
       <c r="BY103" t="n">
-        <v>4.019165848844309</v>
+        <v>4.019165870045708</v>
       </c>
       <c r="BZ103" t="n">
         <v>12.21688145674331</v>
@@ -45182,25 +45206,25 @@
         <v>13.53155185697616</v>
       </c>
       <c r="CB103" t="n">
-        <v>8.761607913496317</v>
+        <v>8.761607908888049</v>
       </c>
       <c r="CC103" t="n">
-        <v>5.73527818523675</v>
+        <v>5.735278184264804</v>
       </c>
       <c r="CD103" t="n">
-        <v>6.527079750860331</v>
+        <v>6.527079740349924</v>
       </c>
       <c r="CE103" t="n">
         <v>12.18000030517578</v>
       </c>
       <c r="CF103" t="n">
-        <v>8.995937902476136</v>
+        <v>8.995937903206247</v>
       </c>
       <c r="CG103" t="n">
-        <v>8.761607913496317</v>
+        <v>8.761607908888049</v>
       </c>
       <c r="CH103" t="n">
-        <v>7.885447122146685</v>
+        <v>7.885447117999244</v>
       </c>
       <c r="CI103" t="n">
         <v>7</v>
@@ -45212,10 +45236,10 @@
         <v>6.2</v>
       </c>
       <c r="CL103" t="n">
-        <v>-35.2590564484975</v>
+        <v>-35.25905648254874</v>
       </c>
       <c r="CM103" t="n">
-        <v>-26.14172678917427</v>
+        <v>-26.14172678317993</v>
       </c>
       <c r="CN103" t="inlineStr">
         <is>
@@ -45494,37 +45518,37 @@
         <v>53.65000152587891</v>
       </c>
       <c r="BX104" t="n">
-        <v>16.38838753932967</v>
+        <v>16.38838751286237</v>
       </c>
       <c r="BY104" t="n">
-        <v>24.84231882381813</v>
+        <v>24.84231880869928</v>
       </c>
       <c r="BZ104" t="n">
-        <v>44.54715955689633</v>
+        <v>44.54715960172905</v>
       </c>
       <c r="CA104" t="n">
         <v>62.04793706021404</v>
       </c>
       <c r="CB104" t="n">
-        <v>35.53900669621403</v>
+        <v>35.53900670433367</v>
       </c>
       <c r="CC104" t="n">
-        <v>26.75432547470745</v>
+        <v>26.754325476984</v>
       </c>
       <c r="CD104" t="n">
-        <v>22.27011836451801</v>
+        <v>22.27011838748315</v>
       </c>
       <c r="CE104" t="n">
         <v>21.66551392102021</v>
       </c>
       <c r="CF104" t="n">
-        <v>31.75684592958974</v>
+        <v>31.75684593416572</v>
       </c>
       <c r="CG104" t="n">
-        <v>25.79832214926279</v>
+        <v>25.79832214284164</v>
       </c>
       <c r="CH104" t="n">
-        <v>23.21848993433651</v>
+        <v>23.21848992855747</v>
       </c>
       <c r="CI104" t="n">
         <v>8</v>
@@ -45536,10 +45560,10 @@
         <v>3.8</v>
       </c>
       <c r="CL104" t="n">
-        <v>-56.72229399073415</v>
+        <v>-56.7222940015059</v>
       </c>
       <c r="CM104" t="n">
-        <v>-40.80737180543913</v>
+        <v>-40.8073717969098</v>
       </c>
       <c r="CN104" t="inlineStr">
         <is>
@@ -45826,10 +45850,10 @@
         <v>3.009999990463257</v>
       </c>
       <c r="BX105" t="n">
-        <v>0.6299352399971967</v>
+        <v>0.6299352424866833</v>
       </c>
       <c r="BY105" t="n">
-        <v>1.1685298701948</v>
+        <v>1.168529874812797</v>
       </c>
       <c r="BZ105" t="n">
         <v>3.379872870647301</v>
@@ -45838,13 +45862,13 @@
         <v>3.910006936746576</v>
       </c>
       <c r="CB105" t="n">
-        <v>2.344554567883461</v>
+        <v>2.344554567501675</v>
       </c>
       <c r="CC105" t="n">
-        <v>2.634385252584747</v>
+        <v>2.63438525226058</v>
       </c>
       <c r="CD105" t="n">
-        <v>1.685378477025967</v>
+        <v>1.685378474929421</v>
       </c>
       <c r="CE105" t="n">
         <v>8.886211075297577</v>
@@ -46138,10 +46162,10 @@
         <v>58.11999893188477</v>
       </c>
       <c r="BX106" t="n">
-        <v>65.76464389020659</v>
+        <v>65.76464389965633</v>
       </c>
       <c r="BY106" t="n">
-        <v>95.7533215041408</v>
+        <v>95.75332151789962</v>
       </c>
       <c r="BZ106" t="n">
         <v>25.32249639261004</v>
@@ -47048,10 +47072,10 @@
         <v>96.33999633789062</v>
       </c>
       <c r="BX109" t="n">
-        <v>4.919793606869623</v>
+        <v>4.919793634320357</v>
       </c>
       <c r="BY109" t="n">
-        <v>9.126217140743151</v>
+        <v>9.12621719166426</v>
       </c>
       <c r="BZ109" t="n">
         <v>41.29747497499355</v>
@@ -47060,13 +47084,13 @@
         <v>40.9954214454957</v>
       </c>
       <c r="CB109" t="n">
-        <v>33.81684472975765</v>
+        <v>33.8168446921921</v>
       </c>
       <c r="CC109" t="n">
-        <v>17.69240963028401</v>
+        <v>17.69240962770702</v>
       </c>
       <c r="CD109" t="n">
-        <v>28.18193278163029</v>
+        <v>28.1819327502025</v>
       </c>
       <c r="CE109" t="n">
         <v>42.5335436716941</v>
@@ -47672,10 +47696,10 @@
         <v>17.45000076293945</v>
       </c>
       <c r="BX111" t="n">
-        <v>3.276083601121225</v>
+        <v>3.27608360827524</v>
       </c>
       <c r="BY111" t="n">
-        <v>6.077135080079872</v>
+        <v>6.07713509335057</v>
       </c>
       <c r="BZ111" t="n">
         <v>14.88812041912091</v>
@@ -47684,23 +47708,23 @@
         <v>15.87749399405222</v>
       </c>
       <c r="CB111" t="n">
-        <v>10.46760142473343</v>
+        <v>10.46760141986499</v>
       </c>
       <c r="CC111" t="n">
-        <v>13.01572396826181</v>
+        <v>13.01572396703299</v>
       </c>
       <c r="CD111" t="n">
-        <v>7.724960031209506</v>
+        <v>7.724960024095552</v>
       </c>
       <c r="CE111" t="inlineStr"/>
       <c r="CF111" t="n">
-        <v>11.34183915290963</v>
+        <v>11.34183915291954</v>
       </c>
       <c r="CG111" t="n">
-        <v>11.74166269649762</v>
+        <v>11.74166269344899</v>
       </c>
       <c r="CH111" t="n">
-        <v>10.56749642684786</v>
+        <v>10.56749642410409</v>
       </c>
       <c r="CI111" t="n">
         <v>6</v>
@@ -47712,10 +47736,10 @@
         <v>4.8</v>
       </c>
       <c r="CL111" t="n">
-        <v>-39.44128386921763</v>
+        <v>-39.44128388494124</v>
       </c>
       <c r="CM111" t="n">
-        <v>-35.00378993107223</v>
+        <v>-35.00378993101542</v>
       </c>
       <c r="CN111" t="inlineStr">
         <is>
@@ -47994,25 +48018,25 @@
         <v>14.64000034332275</v>
       </c>
       <c r="BX112" t="n">
-        <v>3.695490807025397</v>
+        <v>3.695490806073948</v>
       </c>
       <c r="BY112" t="n">
-        <v>4.692826219440469</v>
+        <v>4.692826218392233</v>
       </c>
       <c r="BZ112" t="n">
-        <v>14.0077073460843</v>
+        <v>14.00770734656185</v>
       </c>
       <c r="CA112" t="n">
         <v>36.58780695463401</v>
       </c>
       <c r="CB112" t="n">
-        <v>9.596024411776089</v>
+        <v>9.596024410907802</v>
       </c>
       <c r="CC112" t="n">
-        <v>48.40176703934667</v>
+        <v>48.40176703951053</v>
       </c>
       <c r="CD112" t="n">
-        <v>6.726870750020724</v>
+        <v>6.726870750358145</v>
       </c>
       <c r="CE112" t="n">
         <v>25.86701731463541</v>
@@ -48218,7 +48242,7 @@
         <v>0</v>
       </c>
       <c r="AT113" t="n">
-        <v>27074949120</v>
+        <v>27077031936</v>
       </c>
       <c r="AU113" t="n">
         <v>22.1</v>
@@ -48308,10 +48332,10 @@
         <v>14.52999973297119</v>
       </c>
       <c r="BX113" t="n">
-        <v>1.359804409330757</v>
+        <v>1.359804409298964</v>
       </c>
       <c r="BY113" t="n">
-        <v>2.522437179308555</v>
+        <v>2.522437179249578</v>
       </c>
       <c r="BZ113" t="n">
         <v>8.711425179270055</v>
@@ -48320,13 +48344,13 @@
         <v>10.72111427832558</v>
       </c>
       <c r="CB113" t="n">
-        <v>4.822366877922448</v>
+        <v>4.822366877940052</v>
       </c>
       <c r="CC113" t="n">
-        <v>7.692408686130846</v>
+        <v>7.692408686135011</v>
       </c>
       <c r="CD113" t="n">
-        <v>4.246115052365647</v>
+        <v>4.246115052389372</v>
       </c>
       <c r="CE113" t="n">
         <v>11.54934248649259</v>
@@ -48536,7 +48560,7 @@
         <v>1</v>
       </c>
       <c r="AT114" t="n">
-        <v>44763660288</v>
+        <v>44512468992</v>
       </c>
       <c r="AU114" t="n">
         <v>3282.69</v>
@@ -48626,10 +48650,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX114" t="n">
-        <v>11.98290321268409</v>
+        <v>11.98290323524745</v>
       </c>
       <c r="BY114" t="n">
-        <v>14.95257922626232</v>
+        <v>14.95257925441746</v>
       </c>
       <c r="BZ114" t="inlineStr"/>
       <c r="CA114" t="inlineStr"/>
@@ -48932,10 +48956,10 @@
         <v>11.18000030517578</v>
       </c>
       <c r="BX115" t="n">
-        <v>2.429612154081693</v>
+        <v>2.429612148331315</v>
       </c>
       <c r="BY115" t="n">
-        <v>4.50693054582154</v>
+        <v>4.506930535154589</v>
       </c>
       <c r="BZ115" t="n">
         <v>12.14221344619501</v>
@@ -48944,13 +48968,13 @@
         <v>12.65237085480843</v>
       </c>
       <c r="CB115" t="n">
-        <v>9.593565638315892</v>
+        <v>9.593565641224775</v>
       </c>
       <c r="CC115" t="n">
-        <v>0.7923053612695574</v>
+        <v>0.7923053613460772</v>
       </c>
       <c r="CD115" t="n">
-        <v>6.7258138229526</v>
+        <v>6.725813828928852</v>
       </c>
       <c r="CE115" t="n">
         <v>7.373367923247756</v>
@@ -49246,25 +49270,25 @@
         <v>8.739999771118164</v>
       </c>
       <c r="BX116" t="n">
-        <v>2.247634683951095</v>
+        <v>2.24763468413627</v>
       </c>
       <c r="BY116" t="n">
-        <v>2.439544378331372</v>
+        <v>2.439544378481581</v>
       </c>
       <c r="BZ116" t="n">
-        <v>3.256074274429679</v>
+        <v>3.256074274361908</v>
       </c>
       <c r="CA116" t="n">
         <v>10.09773875906247</v>
       </c>
       <c r="CB116" t="n">
-        <v>1.921804786630324</v>
+        <v>1.921804786654056</v>
       </c>
       <c r="CC116" t="n">
-        <v>5.911010295658421</v>
+        <v>5.911010295644364</v>
       </c>
       <c r="CD116" t="n">
-        <v>1.379500464553726</v>
+        <v>1.379500464490337</v>
       </c>
       <c r="CE116" t="n">
         <v>14.45896929706421</v>
@@ -49560,10 +49584,10 @@
         <v>4.809999942779541</v>
       </c>
       <c r="BX117" t="n">
-        <v>1.479509787386544</v>
+        <v>1.479509787783132</v>
       </c>
       <c r="BY117" t="n">
-        <v>1.541977978409531</v>
+        <v>1.541977978822864</v>
       </c>
       <c r="BZ117" t="inlineStr"/>
       <c r="CA117" t="inlineStr"/>
@@ -49864,10 +49888,10 @@
         <v>3.430000066757202</v>
       </c>
       <c r="BX118" t="n">
-        <v>1.689358882511283</v>
+        <v>1.689358880608014</v>
       </c>
       <c r="BY118" t="n">
-        <v>3.13376072705843</v>
+        <v>3.133760723527866</v>
       </c>
       <c r="BZ118" t="n">
         <v>1.178617761528343</v>
@@ -49876,7 +49900,7 @@
         <v>4.705827767414989</v>
       </c>
       <c r="CB118" t="n">
-        <v>1.636307705468511</v>
+        <v>1.63630770477749</v>
       </c>
       <c r="CC118" t="n">
         <v>0.7445919647652398</v>
@@ -50178,10 +50202,10 @@
         <v>6.559999942779541</v>
       </c>
       <c r="BX119" t="n">
-        <v>1.053693242548313</v>
+        <v>1.053693236410784</v>
       </c>
       <c r="BY119" t="n">
-        <v>1.954600964927121</v>
+        <v>1.954600953542004</v>
       </c>
       <c r="BZ119" t="inlineStr"/>
       <c r="CA119" t="inlineStr"/>
@@ -50482,25 +50506,25 @@
         <v>3.700000047683716</v>
       </c>
       <c r="BX120" t="n">
-        <v>1.26703092786411</v>
+        <v>1.267030927879381</v>
       </c>
       <c r="BY120" t="n">
-        <v>1.270803242898341</v>
+        <v>1.270803242908066</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.281162746210086</v>
+        <v>1.281162746204448</v>
       </c>
       <c r="CA120" t="n">
         <v>4.001025037561948</v>
       </c>
       <c r="CB120" t="n">
-        <v>0.8638648792587855</v>
+        <v>0.8638648792594766</v>
       </c>
       <c r="CC120" t="n">
-        <v>2.294198993174025</v>
+        <v>2.294198993172789</v>
       </c>
       <c r="CD120" t="n">
-        <v>0.481831795093966</v>
+        <v>0.4818317950879053</v>
       </c>
       <c r="CE120" t="n">
         <v>5.12793832390089</v>
@@ -50800,10 +50824,10 @@
         <v>5.510000228881836</v>
       </c>
       <c r="BX121" t="n">
-        <v>5.460836736854465</v>
+        <v>5.460836728833823</v>
       </c>
       <c r="BY121" t="n">
-        <v>7.950978288860102</v>
+        <v>7.950978277182046</v>
       </c>
       <c r="BZ121" t="inlineStr"/>
       <c r="CA121" t="inlineStr"/>
@@ -50812,13 +50836,13 @@
       <c r="CD121" t="inlineStr"/>
       <c r="CE121" t="inlineStr"/>
       <c r="CF121" t="n">
-        <v>6.705907512857284</v>
+        <v>6.705907503007935</v>
       </c>
       <c r="CG121" t="n">
-        <v>6.705907512857284</v>
+        <v>6.705907503007935</v>
       </c>
       <c r="CH121" t="n">
-        <v>6.035316761571555</v>
+        <v>6.035316752707141</v>
       </c>
       <c r="CI121" t="n">
         <v>2</v>
@@ -50830,10 +50854,10 @@
         <v>1.5</v>
       </c>
       <c r="CL121" t="n">
-        <v>9.533874970388577</v>
+        <v>9.533874809509935</v>
       </c>
       <c r="CM121" t="n">
-        <v>21.70430552265399</v>
+        <v>21.70430534389993</v>
       </c>
       <c r="CN121" t="inlineStr">
         <is>
@@ -51112,10 +51136,10 @@
         <v>5.079999923706055</v>
       </c>
       <c r="BX122" t="n">
-        <v>5.591984088049994</v>
+        <v>5.591984094963508</v>
       </c>
       <c r="BY122" t="n">
-        <v>9.969901269272748</v>
+        <v>9.969901281598791</v>
       </c>
       <c r="BZ122" t="inlineStr"/>
       <c r="CA122" t="inlineStr"/>
@@ -51124,13 +51148,13 @@
       <c r="CD122" t="inlineStr"/>
       <c r="CE122" t="inlineStr"/>
       <c r="CF122" t="n">
-        <v>7.780942678661371</v>
+        <v>7.780942688281149</v>
       </c>
       <c r="CG122" t="n">
-        <v>7.780942678661371</v>
+        <v>7.780942688281149</v>
       </c>
       <c r="CH122" t="n">
-        <v>7.002848410795234</v>
+        <v>7.002848419453034</v>
       </c>
       <c r="CI122" t="n">
         <v>2</v>
@@ -51142,10 +51166,10 @@
         <v>1.8</v>
       </c>
       <c r="CL122" t="n">
-        <v>37.85134873951708</v>
+        <v>37.85134890994619</v>
       </c>
       <c r="CM122" t="n">
-        <v>53.16816526613006</v>
+        <v>53.16816545549579</v>
       </c>
       <c r="CN122" t="inlineStr">
         <is>
@@ -51410,10 +51434,10 @@
         <v>21.88999938964844</v>
       </c>
       <c r="BX123" t="n">
-        <v>37.95658330950415</v>
+        <v>37.9565833683093</v>
       </c>
       <c r="BY123" t="n">
-        <v>70.40946203913019</v>
+        <v>70.40946214821373</v>
       </c>
       <c r="BZ123" t="n">
         <v>19.65057533284836</v>
@@ -51432,7 +51456,7 @@
       </c>
       <c r="CE123" t="inlineStr"/>
       <c r="CF123" t="n">
-        <v>25.716431081257</v>
+        <v>25.71643109105786</v>
       </c>
       <c r="CG123" t="n">
         <v>22.88916053088746</v>
@@ -51453,7 +51477,7 @@
         <v>-5.891982402062723</v>
       </c>
       <c r="CM123" t="n">
-        <v>17.48027317633478</v>
+        <v>17.48027322110799</v>
       </c>
       <c r="CN123" t="inlineStr">
         <is>
@@ -51732,25 +51756,25 @@
         <v>9.210000038146973</v>
       </c>
       <c r="BX124" t="n">
-        <v>3.561519053892174</v>
+        <v>3.561519069203598</v>
       </c>
       <c r="BY124" t="n">
-        <v>3.675673659848864</v>
+        <v>3.675673673216738</v>
       </c>
       <c r="BZ124" t="n">
-        <v>4.437535490670403</v>
+        <v>4.437535487731526</v>
       </c>
       <c r="CA124" t="n">
         <v>19.1542749461826</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.489372629777359</v>
+        <v>3.489372639007585</v>
       </c>
       <c r="CC124" t="n">
-        <v>7.742073752436401</v>
+        <v>7.74207375182394</v>
       </c>
       <c r="CD124" t="n">
-        <v>1.752959779927192</v>
+        <v>1.752959776922478</v>
       </c>
       <c r="CE124" t="n">
         <v>21.67646595176141</v>
@@ -52046,10 +52070,10 @@
         <v>11.46000003814697</v>
       </c>
       <c r="BX125" t="n">
-        <v>0.7792719068935744</v>
+        <v>0.7792719063686609</v>
       </c>
       <c r="BY125" t="n">
-        <v>1.44554938728758</v>
+        <v>1.445549386313866</v>
       </c>
       <c r="BZ125" t="n">
         <v>15.9836842637313</v>
@@ -52058,13 +52082,13 @@
         <v>16.66499025937759</v>
       </c>
       <c r="CB125" t="n">
-        <v>14.05168116881867</v>
+        <v>14.05168116890934</v>
       </c>
       <c r="CC125" t="n">
-        <v>1.723472327632195</v>
+        <v>1.723472327643349</v>
       </c>
       <c r="CD125" t="n">
-        <v>11.33321991135827</v>
+        <v>11.33321991190149</v>
       </c>
       <c r="CE125" t="inlineStr"/>
       <c r="CF125" t="inlineStr"/>
@@ -52652,25 +52676,25 @@
         <v>19</v>
       </c>
       <c r="BX127" t="n">
-        <v>0.5916775930303556</v>
+        <v>0.5916775930181861</v>
       </c>
       <c r="BY127" t="n">
-        <v>0.7959309541317295</v>
+        <v>0.7959309541164623</v>
       </c>
       <c r="BZ127" t="n">
-        <v>4.744394285117225</v>
+        <v>4.744394285123802</v>
       </c>
       <c r="CA127" t="n">
         <v>11.86264950263866</v>
       </c>
       <c r="CB127" t="n">
-        <v>1.821996306740074</v>
+        <v>1.821996306742308</v>
       </c>
       <c r="CC127" t="n">
-        <v>0.674271078103833</v>
+        <v>0.6742710781039213</v>
       </c>
       <c r="CD127" t="n">
-        <v>2.328996506371048</v>
+        <v>2.328996506375236</v>
       </c>
       <c r="CE127" t="n">
         <v>19</v>
@@ -52970,10 +52994,10 @@
         <v>5.150000095367432</v>
       </c>
       <c r="BX128" t="n">
-        <v>1.2697570405103</v>
+        <v>1.269757057783039</v>
       </c>
       <c r="BY128" t="n">
-        <v>2.125111555981329</v>
+        <v>2.125111584889613</v>
       </c>
       <c r="BZ128" t="inlineStr"/>
       <c r="CA128" t="inlineStr"/>
@@ -52984,13 +53008,13 @@
         <v>5.966766218226677</v>
       </c>
       <c r="CF128" t="n">
-        <v>1.697434298245815</v>
+        <v>1.697434321336326</v>
       </c>
       <c r="CG128" t="n">
-        <v>1.697434298245815</v>
+        <v>1.697434321336326</v>
       </c>
       <c r="CH128" t="n">
-        <v>1.527690868421233</v>
+        <v>1.527690889202693</v>
       </c>
       <c r="CI128" t="n">
         <v>2</v>
@@ -53002,10 +53026,10 @@
         <v>4.7</v>
       </c>
       <c r="CL128" t="n">
-        <v>-70.33610019162072</v>
+        <v>-70.3360997880972</v>
       </c>
       <c r="CM128" t="n">
-        <v>-67.04011132402302</v>
+        <v>-67.04011087566357</v>
       </c>
       <c r="CN128" t="inlineStr">
         <is>
@@ -53586,37 +53610,37 @@
         <v>17.20999908447266</v>
       </c>
       <c r="BX130" t="n">
-        <v>2.072771881815013</v>
+        <v>2.072771886510078</v>
       </c>
       <c r="BY130" t="n">
-        <v>3.668389125058654</v>
+        <v>3.668389129583747</v>
       </c>
       <c r="BZ130" t="n">
-        <v>9.537870356325502</v>
+        <v>9.537870346486448</v>
       </c>
       <c r="CA130" t="n">
         <v>11.82323496807012</v>
       </c>
       <c r="CB130" t="n">
-        <v>5.529878480923976</v>
+        <v>5.529878477778123</v>
       </c>
       <c r="CC130" t="n">
-        <v>5.536636594728404</v>
+        <v>5.536636594309717</v>
       </c>
       <c r="CD130" t="n">
-        <v>4.691832897972618</v>
+        <v>4.691832894183888</v>
       </c>
       <c r="CE130" t="n">
         <v>15.57105866321647</v>
       </c>
       <c r="CF130" t="n">
-        <v>6.79797373717988</v>
+        <v>6.797973735068674</v>
       </c>
       <c r="CG130" t="n">
-        <v>5.53325753782619</v>
+        <v>5.533257536043919</v>
       </c>
       <c r="CH130" t="n">
-        <v>4.979931784043571</v>
+        <v>4.979931782439528</v>
       </c>
       <c r="CI130" t="n">
         <v>6</v>
@@ -53628,10 +53652,10 @@
         <v>7.5</v>
       </c>
       <c r="CL130" t="n">
-        <v>-71.06373010480515</v>
+        <v>-71.06373011412556</v>
       </c>
       <c r="CM130" t="n">
-        <v>-60.49985997202521</v>
+        <v>-60.49985998429253</v>
       </c>
       <c r="CN130" t="inlineStr">
         <is>
@@ -53902,10 +53926,10 @@
         <v>4.21999979019165</v>
       </c>
       <c r="BX131" t="n">
-        <v>0.8881979196853528</v>
+        <v>0.8881979195949974</v>
       </c>
       <c r="BY131" t="n">
-        <v>0.9831240723517251</v>
+        <v>0.9831240722517127</v>
       </c>
       <c r="BZ131" t="inlineStr"/>
       <c r="CA131" t="inlineStr"/>
@@ -53914,13 +53938,13 @@
       <c r="CD131" t="inlineStr"/>
       <c r="CE131" t="inlineStr"/>
       <c r="CF131" t="n">
-        <v>0.9356609960185389</v>
+        <v>0.9356609959233551</v>
       </c>
       <c r="CG131" t="n">
-        <v>0.9356609960185389</v>
+        <v>0.9356609959233551</v>
       </c>
       <c r="CH131" t="n">
-        <v>0.842094896416685</v>
+        <v>0.8420948963310195</v>
       </c>
       <c r="CI131" t="n">
         <v>2</v>
@@ -53932,10 +53956,10 @@
         <v>1.1</v>
       </c>
       <c r="CL131" t="n">
-        <v>-80.04514364256778</v>
+        <v>-80.04514364459776</v>
       </c>
       <c r="CM131" t="n">
-        <v>-77.82793738063086</v>
+        <v>-77.8279373828864</v>
       </c>
       <c r="CN131" t="inlineStr">
         <is>
@@ -54216,10 +54240,10 @@
         <v>1.220000028610229</v>
       </c>
       <c r="BX132" t="n">
-        <v>0.3581979138116445</v>
+        <v>0.3581979135207498</v>
       </c>
       <c r="BY132" t="n">
-        <v>0.6644571301206005</v>
+        <v>0.6644571295809908</v>
       </c>
       <c r="BZ132" t="inlineStr"/>
       <c r="CA132" t="inlineStr"/>
@@ -54228,13 +54252,13 @@
       <c r="CD132" t="inlineStr"/>
       <c r="CE132" t="inlineStr"/>
       <c r="CF132" t="n">
-        <v>0.5113275219661224</v>
+        <v>0.5113275215508702</v>
       </c>
       <c r="CG132" t="n">
-        <v>0.5113275219661224</v>
+        <v>0.5113275215508702</v>
       </c>
       <c r="CH132" t="n">
-        <v>0.4601947697695102</v>
+        <v>0.4601947693957832</v>
       </c>
       <c r="CI132" t="n">
         <v>2</v>
@@ -54246,10 +54270,10 @@
         <v>1.9</v>
       </c>
       <c r="CL132" t="n">
-        <v>-62.27911811660005</v>
+        <v>-62.27911814723341</v>
       </c>
       <c r="CM132" t="n">
-        <v>-58.08790901844451</v>
+        <v>-58.08790905248157</v>
       </c>
       <c r="CN132" t="inlineStr">
         <is>
@@ -54836,10 +54860,10 @@
         <v>37.15000152587891</v>
       </c>
       <c r="BX134" t="n">
-        <v>8.367448515399895</v>
+        <v>8.367448543454859</v>
       </c>
       <c r="BY134" t="n">
-        <v>12.18300503842225</v>
+        <v>12.18300507927028</v>
       </c>
       <c r="BZ134" t="n">
         <v>7.98264495597398</v>
@@ -55146,10 +55170,10 @@
         <v>5.460000038146973</v>
       </c>
       <c r="BX135" t="n">
-        <v>1.040921917587345</v>
+        <v>1.040921915472592</v>
       </c>
       <c r="BY135" t="n">
-        <v>1.930910157124526</v>
+        <v>1.930910153201658</v>
       </c>
       <c r="BZ135" t="inlineStr"/>
       <c r="CA135" t="inlineStr"/>
@@ -55160,13 +55184,13 @@
         <v>2.921035340023647</v>
       </c>
       <c r="CF135" t="n">
-        <v>1.964289138245173</v>
+        <v>1.964289136232632</v>
       </c>
       <c r="CG135" t="n">
-        <v>1.930910157124526</v>
+        <v>1.930910153201658</v>
       </c>
       <c r="CH135" t="n">
-        <v>1.737819141412073</v>
+        <v>1.737819137881492</v>
       </c>
       <c r="CI135" t="n">
         <v>3</v>
@@ -55178,10 +55202,10 @@
         <v>2.8</v>
       </c>
       <c r="CL135" t="n">
-        <v>-68.1718108192201</v>
+        <v>-68.17181088388276</v>
       </c>
       <c r="CM135" t="n">
-        <v>-64.02400870839888</v>
+        <v>-64.0240087452586</v>
       </c>
       <c r="CN135" t="inlineStr">
         <is>
@@ -55460,25 +55484,25 @@
         <v>4.840000152587891</v>
       </c>
       <c r="BX136" t="n">
-        <v>1.502502732223173</v>
+        <v>1.502502726022025</v>
       </c>
       <c r="BY136" t="n">
-        <v>1.66182903631869</v>
+        <v>1.661829030967253</v>
       </c>
       <c r="BZ136" t="n">
-        <v>2.45426220164267</v>
+        <v>2.454262203868694</v>
       </c>
       <c r="CA136" t="n">
         <v>7.637283478890028</v>
       </c>
       <c r="CB136" t="n">
-        <v>1.720253738993954</v>
+        <v>1.720253736625191</v>
       </c>
       <c r="CC136" t="n">
-        <v>1.782246221503003</v>
+        <v>1.782246221684628</v>
       </c>
       <c r="CD136" t="n">
-        <v>1.062540517732988</v>
+        <v>1.062540519746624</v>
       </c>
       <c r="CE136" t="n">
         <v>0.3893443649538701</v>
@@ -55772,10 +55796,10 @@
         <v>1.990000009536743</v>
       </c>
       <c r="BX137" t="n">
-        <v>0.5586583805071971</v>
+        <v>0.5586583793212254</v>
       </c>
       <c r="BY137" t="n">
-        <v>0.813406602018479</v>
+        <v>0.8134066002917043</v>
       </c>
       <c r="BZ137" t="n">
         <v>0.3437302790098343</v>
@@ -55838,7 +55862,7 @@
         <v>-0.9950239314132636</v>
       </c>
       <c r="CZ137" t="n">
-        <v>-53.22526227613638</v>
+        <v>-53.22525700906506</v>
       </c>
       <c r="DA137" t="b">
         <v>0</v>
@@ -56080,10 +56104,10 @@
         <v>6.889999866485596</v>
       </c>
       <c r="BX138" t="n">
-        <v>1.890787836008848</v>
+        <v>1.890787839573564</v>
       </c>
       <c r="BY138" t="n">
-        <v>2.752987089228883</v>
+        <v>2.752987094419109</v>
       </c>
       <c r="BZ138" t="n">
         <v>1.748560239420454</v>
@@ -57258,25 +57282,25 @@
         <v>4.539999961853027</v>
       </c>
       <c r="BX142" t="n">
-        <v>0.7601321063839337</v>
+        <v>0.7601321081395994</v>
       </c>
       <c r="BY142" t="n">
-        <v>0.7617072498526766</v>
+        <v>0.7617072515022747</v>
       </c>
       <c r="BZ142" t="n">
-        <v>0.7870130671805293</v>
+        <v>0.787013067067179</v>
       </c>
       <c r="CA142" t="n">
         <v>5.834017088524545</v>
       </c>
       <c r="CB142" t="n">
-        <v>0.2605273415463846</v>
+        <v>0.2605273419474931</v>
       </c>
       <c r="CC142" t="n">
-        <v>0.4173726784988233</v>
+        <v>0.4173726784914545</v>
       </c>
       <c r="CD142" t="n">
-        <v>0.295489834398444</v>
+        <v>0.2954898342763901</v>
       </c>
       <c r="CE142" t="inlineStr"/>
       <c r="CF142" t="inlineStr"/>
@@ -57572,10 +57596,10 @@
         <v>18.30999946594238</v>
       </c>
       <c r="BX143" t="n">
-        <v>27.83633528641845</v>
+        <v>27.83633516612048</v>
       </c>
       <c r="BY143" t="n">
-        <v>37.23883076094202</v>
+        <v>37.23883060001006</v>
       </c>
       <c r="BZ143" t="n">
         <v>2.491274627922611</v>
@@ -57584,7 +57608,7 @@
         <v>6.909187799009217</v>
       </c>
       <c r="CB143" t="n">
-        <v>6.383321832562637</v>
+        <v>6.383321808581837</v>
       </c>
       <c r="CC143" t="n">
         <v>3.046690502845772</v>
@@ -57886,10 +57910,10 @@
         <v>3.75</v>
       </c>
       <c r="BX144" t="n">
-        <v>0.6783189620965461</v>
+        <v>0.6783189640326317</v>
       </c>
       <c r="BY144" t="n">
-        <v>1.258281674689093</v>
+        <v>1.258281678280532</v>
       </c>
       <c r="BZ144" t="inlineStr"/>
       <c r="CA144" t="inlineStr"/>
@@ -57900,13 +57924,13 @@
         <v>3.41418274193782</v>
       </c>
       <c r="CF144" t="n">
-        <v>0.9683003183928194</v>
+        <v>0.9683003211565817</v>
       </c>
       <c r="CG144" t="n">
-        <v>0.9683003183928194</v>
+        <v>0.9683003211565817</v>
       </c>
       <c r="CH144" t="n">
-        <v>0.8714702865535374</v>
+        <v>0.8714702890409236</v>
       </c>
       <c r="CI144" t="n">
         <v>2</v>
@@ -57918,10 +57942,10 @@
         <v>5</v>
       </c>
       <c r="CL144" t="n">
-        <v>-76.76079235857233</v>
+        <v>-76.76079229224204</v>
       </c>
       <c r="CM144" t="n">
-        <v>-74.17865817619148</v>
+        <v>-74.17865810249116</v>
       </c>
       <c r="CN144" t="inlineStr">
         <is>
@@ -58198,10 +58222,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX145" t="n">
-        <v>9.498631727168846</v>
+        <v>9.498631713004629</v>
       </c>
       <c r="BY145" t="n">
-        <v>13.83000779475784</v>
+        <v>13.83000777413474</v>
       </c>
       <c r="BZ145" t="n">
         <v>4.684999942779541</v>
@@ -59130,10 +59154,10 @@
         <v>10.71000003814697</v>
       </c>
       <c r="BX148" t="n">
-        <v>5.722370903606293</v>
+        <v>5.722370909251392</v>
       </c>
       <c r="BY148" t="n">
-        <v>10.47405815023048</v>
+        <v>10.4740581605631</v>
       </c>
       <c r="BZ148" t="inlineStr"/>
       <c r="CA148" t="inlineStr"/>
@@ -59144,13 +59168,13 @@
         <v>3.193949960809536</v>
       </c>
       <c r="CF148" t="n">
-        <v>6.463459671548769</v>
+        <v>6.463459676874677</v>
       </c>
       <c r="CG148" t="n">
-        <v>5.722370903606293</v>
+        <v>5.722370909251392</v>
       </c>
       <c r="CH148" t="n">
-        <v>5.150133813245663</v>
+        <v>5.150133818326253</v>
       </c>
       <c r="CI148" t="n">
         <v>3</v>
@@ -59162,10 +59186,10 @@
         <v>3.3</v>
       </c>
       <c r="CL148" t="n">
-        <v>-51.91284972080419</v>
+        <v>-51.91284967336638</v>
       </c>
       <c r="CM148" t="n">
-        <v>-39.65023670842987</v>
+        <v>-39.65023665870151</v>
       </c>
       <c r="CN148" t="inlineStr">
         <is>
@@ -59346,13 +59370,13 @@
         <v>1</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AS149" t="b">
         <v>1</v>
       </c>
       <c r="AT149" t="n">
-        <v>50465071104</v>
+        <v>50658746368</v>
       </c>
       <c r="AU149" t="n">
         <v>53.28</v>
@@ -59591,7 +59615,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S150" t="n">
@@ -59758,10 +59782,10 @@
         <v>15.35000038146973</v>
       </c>
       <c r="BX150" t="n">
-        <v>3.926986140572328</v>
+        <v>3.926986152100071</v>
       </c>
       <c r="BY150" t="n">
-        <v>5.717691820673309</v>
+        <v>5.717691837457703</v>
       </c>
       <c r="BZ150" t="inlineStr"/>
       <c r="CA150" t="inlineStr"/>
@@ -59772,7 +59796,7 @@
         <v>5.502528941537498</v>
       </c>
       <c r="CF150" t="n">
-        <v>5.049068967594379</v>
+        <v>5.049068977031758</v>
       </c>
       <c r="CG150" t="n">
         <v>5.502528941537498</v>
@@ -59793,7 +59817,7 @@
         <v>-67.7376161282572</v>
       </c>
       <c r="CM150" t="n">
-        <v>-67.10704337382602</v>
+        <v>-67.10704331234471</v>
       </c>
       <c r="CN150" t="inlineStr">
         <is>
@@ -59807,7 +59831,11 @@
       </c>
       <c r="CP150" t="inlineStr"/>
       <c r="CQ150" t="inlineStr"/>
-      <c r="CR150" t="inlineStr"/>
+      <c r="CR150" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="CS150" t="b">
         <v>0</v>
       </c>
@@ -59834,14 +59862,14 @@
         <v>0</v>
       </c>
       <c r="DB150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC150" t="b">
         <v>0</v>
       </c>
       <c r="DD150" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>

--- a/reports/screener_2026-08-27.xlsx
+++ b/reports/screener_2026-08-27.xlsx
@@ -1186,10 +1186,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.86871600316745</v>
+        <v>5.86871597626807</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646818587562</v>
+        <v>10.88646813597727</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.21781573324146</v>
@@ -1198,7 +1198,7 @@
         <v>27.66761889587421</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.26108658508552</v>
+        <v>71.26108647233362</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -1512,10 +1512,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01485115023178</v>
+        <v>15.01485126196847</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85254888367994</v>
+        <v>27.85254909095152</v>
       </c>
       <c r="BZ3" t="n">
         <v>39.46006465010361</v>
@@ -1524,13 +1524,13 @@
         <v>23.87433491384053</v>
       </c>
       <c r="CB3" t="n">
-        <v>76.71128055869886</v>
+        <v>76.71128035255107</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.54748526964112</v>
+        <v>48.54748518859483</v>
       </c>
       <c r="CD3" t="n">
-        <v>27.26172529540181</v>
+        <v>27.26172495066282</v>
       </c>
       <c r="CE3" t="n">
         <v>8.973116408407053</v>
@@ -1830,10 +1830,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388479636543</v>
+        <v>16.25388477265026</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.15095629725787</v>
+        <v>30.15095625326622</v>
       </c>
       <c r="BZ4" t="n">
         <v>70.99454413334874</v>
@@ -1842,19 +1842,19 @@
         <v>51.39538022233962</v>
       </c>
       <c r="CB4" t="n">
-        <v>124.8365656247644</v>
+        <v>124.8365656332173</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.69771468978261</v>
+        <v>25.69771469318724</v>
       </c>
       <c r="CD4" t="n">
-        <v>61.55225153257966</v>
+        <v>61.55225158345913</v>
       </c>
       <c r="CE4" t="n">
         <v>43.02986521586298</v>
       </c>
       <c r="CF4" t="n">
-        <v>47.13678534852858</v>
+        <v>47.13678535024399</v>
       </c>
       <c r="CG4" t="n">
         <v>47.2126227191013</v>
@@ -1875,7 +1875,7 @@
         <v>73.15142160530792</v>
       </c>
       <c r="CM4" t="n">
-        <v>92.08143272196634</v>
+        <v>92.08143272895661</v>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         <v>4.059999942779541</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.54807282876565</v>
+        <v>3.548072834096487</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.58167509736028</v>
+        <v>6.581675107248985</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.56892505650208</v>
@@ -2168,25 +2168,25 @@
         <v>8.462578627869229</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.40274523688278</v>
+        <v>24.40274523318439</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.26517503412428</v>
+        <v>11.26517503191264</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.57787753601435</v>
+        <v>10.57787752272904</v>
       </c>
       <c r="CE5" t="n">
         <v>5.216748691568468</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.112163340573114</v>
+        <v>9.112163339638409</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.520228081941788</v>
+        <v>9.520228075299137</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.56820527374761</v>
+        <v>8.568205267769224</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -2198,10 +2198,10 @@
         <v>6.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>111.0395417365863</v>
+        <v>111.0395415893354</v>
       </c>
       <c r="CM5" t="n">
-        <v>124.4375238669285</v>
+        <v>124.4375238439062</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294915543341</v>
+        <v>18.38294920812385</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037068332898</v>
+        <v>34.10037078106974</v>
       </c>
       <c r="BZ6" t="n">
         <v>75.02112937085505</v>
@@ -2478,23 +2478,23 @@
         <v>56.1385860856476</v>
       </c>
       <c r="CB6" t="n">
-        <v>100.7448468641835</v>
+        <v>100.7448467822811</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.4036999955209</v>
+        <v>48.40369998271307</v>
       </c>
       <c r="CD6" t="n">
-        <v>59.46380252610901</v>
+        <v>59.46380242020545</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>43.97703730128458</v>
+        <v>43.97703733569043</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.25203533942494</v>
+        <v>41.2520353818914</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.12683180548245</v>
+        <v>37.12683184370226</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -2506,10 +2506,10 @@
         <v>4.1</v>
       </c>
       <c r="CL6" t="n">
-        <v>-23.03725017892155</v>
+        <v>-23.03725009969308</v>
       </c>
       <c r="CM6" t="n">
-        <v>-8.836990524163069</v>
+        <v>-8.836990452840842</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
         <v>4.380000114440918</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774220937844</v>
+        <v>3.052774202256612</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.6628961798397</v>
+        <v>5.662896145186015</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.64379118003097</v>
@@ -2804,7 +2804,7 @@
         <v>8.50525545154361</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.62501978425786</v>
+        <v>23.62501972727807</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -2816,7 +2816,7 @@
         <v>5.24246353170767</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.25728134571453</v>
+        <v>11.25728133262403</v>
       </c>
       <c r="CG7" t="n">
         <v>11.54640553044338</v>
@@ -2837,7 +2837,7 @@
         <v>137.2549019607844</v>
       </c>
       <c r="CM7" t="n">
-        <v>157.0155491229127</v>
+        <v>157.0155488240429</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -3122,10 +3122,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX8" t="n">
-        <v>121.1494725411449</v>
+        <v>121.1494733628736</v>
       </c>
       <c r="BY8" t="n">
-        <v>224.7322715638238</v>
+        <v>224.7322730881305</v>
       </c>
       <c r="BZ8" t="n">
         <v>136.6302942100011</v>
@@ -3146,13 +3146,13 @@
         <v>57.66739801003497</v>
       </c>
       <c r="CF8" t="n">
-        <v>116.3031159598463</v>
+        <v>116.3031162949942</v>
       </c>
       <c r="CG8" t="n">
-        <v>121.1494725411449</v>
+        <v>121.1494733628736</v>
       </c>
       <c r="CH8" t="n">
-        <v>109.0345252870304</v>
+        <v>109.0345260265862</v>
       </c>
       <c r="CI8" t="n">
         <v>7</v>
@@ -3164,10 +3164,10 @@
         <v>5.5</v>
       </c>
       <c r="CL8" t="n">
-        <v>163.686890714808</v>
+        <v>163.6868925033347</v>
       </c>
       <c r="CM8" t="n">
-        <v>181.2651033896281</v>
+        <v>181.265104200143</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -3450,10 +3450,10 @@
         <v>15.75</v>
       </c>
       <c r="BX9" t="n">
-        <v>6.426879087734028</v>
+        <v>6.426879098208645</v>
       </c>
       <c r="BY9" t="n">
-        <v>11.92186070774662</v>
+        <v>11.92186072717704</v>
       </c>
       <c r="BZ9" t="n">
         <v>25.54314565483476</v>
@@ -3462,19 +3462,19 @@
         <v>18.71731215268055</v>
       </c>
       <c r="CB9" t="n">
-        <v>35.49020394518685</v>
+        <v>35.49020392821991</v>
       </c>
       <c r="CC9" t="n">
-        <v>12.30123102245168</v>
+        <v>12.3012310204747</v>
       </c>
       <c r="CD9" t="n">
-        <v>20.53560237134395</v>
+        <v>20.5356023493967</v>
       </c>
       <c r="CE9" t="n">
         <v>18.47523885586486</v>
       </c>
       <c r="CF9" t="n">
-        <v>20.42637067287276</v>
+        <v>20.42637066980694</v>
       </c>
       <c r="CG9" t="n">
         <v>18.71731215268055</v>
@@ -3495,7 +3495,7 @@
         <v>6.956069443888868</v>
       </c>
       <c r="CM9" t="n">
-        <v>29.69124236744607</v>
+        <v>29.69124234798055</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -3778,37 +3778,37 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX10" t="n">
-        <v>24.20136286936076</v>
+        <v>24.20136299867336</v>
       </c>
       <c r="BY10" t="n">
-        <v>37.09024797787244</v>
+        <v>37.09024677252115</v>
       </c>
       <c r="BZ10" t="n">
-        <v>39.76038116972554</v>
+        <v>39.76037966515335</v>
       </c>
       <c r="CA10" t="n">
         <v>21.15376420319533</v>
       </c>
       <c r="CB10" t="n">
-        <v>53.96364505251905</v>
+        <v>53.96364405261692</v>
       </c>
       <c r="CC10" t="n">
-        <v>51.52714062780147</v>
+        <v>51.52714046459301</v>
       </c>
       <c r="CD10" t="n">
-        <v>19.88022335437046</v>
+        <v>19.8802225989987</v>
       </c>
       <c r="CE10" t="n">
         <v>24.52549486359719</v>
       </c>
       <c r="CF10" t="n">
-        <v>34.01278251480528</v>
+        <v>34.01278195241862</v>
       </c>
       <c r="CG10" t="n">
-        <v>30.80787142073481</v>
+        <v>30.80787081805916</v>
       </c>
       <c r="CH10" t="n">
-        <v>27.72708427866133</v>
+        <v>27.72708373625325</v>
       </c>
       <c r="CI10" t="n">
         <v>8</v>
@@ -3820,10 +3820,10 @@
         <v>2.7</v>
       </c>
       <c r="CL10" t="n">
-        <v>-14.8953875986822</v>
+        <v>-14.89538926353197</v>
       </c>
       <c r="CM10" t="n">
-        <v>4.397730519416032</v>
+        <v>4.397728793244671</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -4114,10 +4114,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.05538998425735</v>
+        <v>46.05539002065863</v>
       </c>
       <c r="BY11" t="n">
-        <v>85.43274842079738</v>
+        <v>85.43274848832176</v>
       </c>
       <c r="BZ11" t="n">
         <v>69.47297200868543</v>
@@ -4138,7 +4138,7 @@
         <v>25.94666723750103</v>
       </c>
       <c r="CF11" t="n">
-        <v>78.49436730402689</v>
+        <v>78.49436731887342</v>
       </c>
       <c r="CG11" t="n">
         <v>69.47297200868543</v>
@@ -4159,7 +4159,7 @@
         <v>89.58664546899841</v>
       </c>
       <c r="CM11" t="n">
-        <v>138.0059684461242</v>
+        <v>138.0059684911409</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -4444,10 +4444,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX12" t="n">
-        <v>127.6301659713547</v>
+        <v>127.6301650953702</v>
       </c>
       <c r="BY12" t="n">
-        <v>236.7539578768629</v>
+        <v>236.7539562519117</v>
       </c>
       <c r="BZ12" t="n">
         <v>137.215088724016</v>
@@ -4468,13 +4468,13 @@
         <v>56.54612056896573</v>
       </c>
       <c r="CF12" t="n">
-        <v>142.9573017812868</v>
+        <v>142.9573014686699</v>
       </c>
       <c r="CG12" t="n">
-        <v>126.4680102898507</v>
+        <v>126.4680098518585</v>
       </c>
       <c r="CH12" t="n">
-        <v>113.8212092608657</v>
+        <v>113.8212088666726</v>
       </c>
       <c r="CI12" t="n">
         <v>8</v>
@@ -4486,10 +4486,10 @@
         <v>5.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>147.5450421792887</v>
+        <v>147.5450413219745</v>
       </c>
       <c r="CM12" t="n">
-        <v>210.9119251947122</v>
+        <v>210.9119245148145</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -4754,10 +4754,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX13" t="n">
-        <v>13.15731119057001</v>
+        <v>13.15731118693232</v>
       </c>
       <c r="BY13" t="n">
-        <v>24.40681225850738</v>
+        <v>24.40681225175945</v>
       </c>
       <c r="BZ13" t="n">
         <v>19.90620030713044</v>
@@ -4766,7 +4766,7 @@
         <v>12.44114419785431</v>
       </c>
       <c r="CB13" t="n">
-        <v>33.6887243999592</v>
+        <v>33.68872439596174</v>
       </c>
       <c r="CC13" t="n">
         <v>22.8984489302328</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="CE13" t="inlineStr"/>
       <c r="CF13" t="n">
-        <v>20.09219317161016</v>
+        <v>20.09219316901375</v>
       </c>
       <c r="CG13" t="n">
         <v>21.40232461868162</v>
@@ -4797,7 +4797,7 @@
         <v>0.6378932657179259</v>
       </c>
       <c r="CM13" t="n">
-        <v>4.974889301598906</v>
+        <v>4.974889288033602</v>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
@@ -5084,10 +5084,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX14" t="n">
-        <v>3.363729732909307</v>
+        <v>3.363729732974996</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.239718654546764</v>
+        <v>6.239718654668616</v>
       </c>
       <c r="BZ14" t="n">
         <v>20.7379196371351</v>
@@ -5096,7 +5096,7 @@
         <v>14.20601824710207</v>
       </c>
       <c r="CB14" t="n">
-        <v>33.37021289909818</v>
+        <v>33.37021289929139</v>
       </c>
       <c r="CC14" t="n">
         <v>10.95072400487419</v>
@@ -5410,10 +5410,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX15" t="n">
-        <v>10.74426541307544</v>
+        <v>10.74426546359599</v>
       </c>
       <c r="BY15" t="n">
-        <v>19.93061234125494</v>
+        <v>19.93061243497056</v>
       </c>
       <c r="BZ15" t="n">
         <v>37.5845483977432</v>
@@ -5422,25 +5422,25 @@
         <v>37.1651975122017</v>
       </c>
       <c r="CB15" t="n">
-        <v>41.90042981465468</v>
+        <v>41.90042983588201</v>
       </c>
       <c r="CC15" t="n">
-        <v>34.50408899034814</v>
+        <v>34.50408897966985</v>
       </c>
       <c r="CD15" t="n">
-        <v>18.61582873127402</v>
+        <v>18.61582867267827</v>
       </c>
       <c r="CE15" t="n">
         <v>31.97921770241074</v>
       </c>
       <c r="CF15" t="n">
-        <v>31.66856049855534</v>
+        <v>31.66856050507948</v>
       </c>
       <c r="CG15" t="n">
-        <v>34.50408899034814</v>
+        <v>34.50408897966985</v>
       </c>
       <c r="CH15" t="n">
-        <v>31.05368009131333</v>
+        <v>31.05368008170287</v>
       </c>
       <c r="CI15" t="n">
         <v>7</v>
@@ -5452,10 +5452,10 @@
         <v>3.9</v>
       </c>
       <c r="CL15" t="n">
-        <v>77.14591485994788</v>
+        <v>77.14591480512493</v>
       </c>
       <c r="CM15" t="n">
-        <v>80.65350403939631</v>
+        <v>80.65350407661329</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -5740,10 +5740,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX16" t="n">
-        <v>5.044350330400213</v>
+        <v>5.044350326490063</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.357269862892394</v>
+        <v>9.357269855639066</v>
       </c>
       <c r="BZ16" t="n">
         <v>8.531826591579675</v>
@@ -6058,37 +6058,37 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX17" t="n">
-        <v>10.37863321725536</v>
+        <v>10.3786331450779</v>
       </c>
       <c r="BY17" t="n">
-        <v>18.07553048217811</v>
+        <v>18.07553066680664</v>
       </c>
       <c r="BZ17" t="n">
-        <v>23.22146472121366</v>
+        <v>23.22146511989621</v>
       </c>
       <c r="CA17" t="n">
         <v>17.75681071950086</v>
       </c>
       <c r="CB17" t="n">
-        <v>36.48041910786196</v>
+        <v>36.48041917740331</v>
       </c>
       <c r="CC17" t="n">
-        <v>24.12244062846323</v>
+        <v>24.12244065927788</v>
       </c>
       <c r="CD17" t="n">
-        <v>11.46100442756559</v>
+        <v>11.46100458572084</v>
       </c>
       <c r="CE17" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF17" t="n">
-        <v>18.9820378700895</v>
+        <v>18.98203796629511</v>
       </c>
       <c r="CG17" t="n">
-        <v>17.91617060083949</v>
+        <v>17.91617069315375</v>
       </c>
       <c r="CH17" t="n">
-        <v>16.12455354075554</v>
+        <v>16.12455362383837</v>
       </c>
       <c r="CI17" t="n">
         <v>8</v>
@@ -6100,10 +6100,10 @@
         <v>3.5</v>
       </c>
       <c r="CL17" t="n">
-        <v>55.64241385242625</v>
+        <v>55.64241465438411</v>
       </c>
       <c r="CM17" t="n">
-        <v>83.2243098372611</v>
+        <v>83.22431076588668</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX18" t="n">
-        <v>3.454302383090375</v>
+        <v>3.454302376873577</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.407730920632644</v>
+        <v>6.407730909100485</v>
       </c>
       <c r="BZ18" t="n">
         <v>20.16620865234961</v>
@@ -6398,13 +6398,13 @@
         <v>19.00949927082382</v>
       </c>
       <c r="CB18" t="n">
-        <v>21.60588271629159</v>
+        <v>21.60588271687798</v>
       </c>
       <c r="CC18" t="n">
-        <v>15.9282701250515</v>
+        <v>15.92827012624657</v>
       </c>
       <c r="CD18" t="n">
-        <v>13.471165756342</v>
+        <v>13.4711657642254</v>
       </c>
       <c r="CE18" t="n">
         <v>30.336208848481</v>
@@ -6460,7 +6460,7 @@
         <v>-18.94659940111765</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-32.89649636084019</v>
+        <v>-32.89648837260555</v>
       </c>
       <c r="DA18" t="b">
         <v>1</v>
@@ -6608,13 +6608,13 @@
         <v>1</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AS19" t="b">
         <v>1</v>
       </c>
       <c r="AT19" t="n">
-        <v>5725241856</v>
+        <v>3602869248</v>
       </c>
       <c r="AU19" t="n">
         <v>6.7</v>
@@ -6704,10 +6704,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX19" t="n">
-        <v>9.774107130994336</v>
+        <v>9.774107128522251</v>
       </c>
       <c r="BY19" t="n">
-        <v>18.1309687279945</v>
+        <v>18.13096872340877</v>
       </c>
       <c r="BZ19" t="n">
         <v>22.32723873053024</v>
@@ -6716,25 +6716,25 @@
         <v>13.19107667093893</v>
       </c>
       <c r="CB19" t="n">
-        <v>32.07171956569217</v>
+        <v>32.07171957325589</v>
       </c>
       <c r="CC19" t="n">
-        <v>25.27239703637801</v>
+        <v>25.27239703816369</v>
       </c>
       <c r="CD19" t="n">
-        <v>11.82328982545854</v>
+        <v>11.8232898334598</v>
       </c>
       <c r="CE19" t="n">
         <v>9.733055502947964</v>
       </c>
       <c r="CF19" t="n">
-        <v>17.79048164886684</v>
+        <v>17.79048165015344</v>
       </c>
       <c r="CG19" t="n">
-        <v>15.66102269946671</v>
+        <v>15.66102269717385</v>
       </c>
       <c r="CH19" t="n">
-        <v>14.09492042952004</v>
+        <v>14.09492042745647</v>
       </c>
       <c r="CI19" t="n">
         <v>8</v>
@@ -6746,10 +6746,10 @@
         <v>3.3</v>
       </c>
       <c r="CL19" t="n">
-        <v>24.8442912058845</v>
+        <v>24.8442911876066</v>
       </c>
       <c r="CM19" t="n">
-        <v>57.57734020352368</v>
+        <v>57.57734021491962</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -7032,10 +7032,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX20" t="n">
-        <v>7.290978496927618</v>
+        <v>7.290978528882397</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.52476511180073</v>
+        <v>13.52476517107684</v>
       </c>
       <c r="BZ20" t="n">
         <v>35.92512375028262</v>
@@ -7044,19 +7044,19 @@
         <v>28.41024685094796</v>
       </c>
       <c r="CB20" t="n">
-        <v>44.74749257504084</v>
+        <v>44.7474925273167</v>
       </c>
       <c r="CC20" t="n">
-        <v>26.46268145824689</v>
+        <v>26.46268145030354</v>
       </c>
       <c r="CD20" t="n">
-        <v>29.04887757284678</v>
+        <v>29.04887751514411</v>
       </c>
       <c r="CE20" t="n">
         <v>24.98203479043206</v>
       </c>
       <c r="CF20" t="n">
-        <v>29.01446030137112</v>
+        <v>29.0144602936434</v>
       </c>
       <c r="CG20" t="n">
         <v>28.41024685094796</v>
@@ -7077,7 +7077,7 @@
         <v>-7.088583791648039</v>
       </c>
       <c r="CM20" t="n">
-        <v>5.430449922779168</v>
+        <v>5.430449894698786</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -7340,10 +7340,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX21" t="n">
-        <v>35.6289255576336</v>
+        <v>35.62892560284679</v>
       </c>
       <c r="BY21" t="n">
-        <v>51.87571561191452</v>
+        <v>51.87571567774493</v>
       </c>
       <c r="BZ21" t="n">
         <v>48.56662855571916</v>
@@ -7360,13 +7360,13 @@
       </c>
       <c r="CE21" t="inlineStr"/>
       <c r="CF21" t="n">
-        <v>48.89385867727125</v>
+        <v>48.89385870503214</v>
       </c>
       <c r="CG21" t="n">
-        <v>50.22117208381684</v>
+        <v>50.22117211673205</v>
       </c>
       <c r="CH21" t="n">
-        <v>45.19905487543516</v>
+        <v>45.19905490505884</v>
       </c>
       <c r="CI21" t="n">
         <v>4</v>
@@ -7378,10 +7378,10 @@
         <v>1.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>16.19293856676509</v>
+        <v>16.19293864291851</v>
       </c>
       <c r="CM21" t="n">
-        <v>25.69114848168772</v>
+        <v>25.6911485530525</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -7668,10 +7668,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.108740526292904</v>
+        <v>3.108740528356239</v>
       </c>
       <c r="BY22" t="n">
-        <v>5.766713676273336</v>
+        <v>5.766713680100823</v>
       </c>
       <c r="BZ22" t="n">
         <v>31.95928917556512</v>
@@ -7680,7 +7680,7 @@
         <v>26.70105358379499</v>
       </c>
       <c r="CB22" t="n">
-        <v>40.93687025032393</v>
+        <v>40.93687025348094</v>
       </c>
       <c r="CC22" t="n">
         <v>10.85340539909456</v>
@@ -7986,10 +7986,10 @@
         <v>32.75</v>
       </c>
       <c r="BX23" t="n">
-        <v>3.24935669499341</v>
+        <v>3.249356697982276</v>
       </c>
       <c r="BY23" t="n">
-        <v>6.027556669212775</v>
+        <v>6.027556674757121</v>
       </c>
       <c r="BZ23" t="n">
         <v>32.74999999999999</v>
@@ -7998,7 +7998,7 @@
         <v>22.94333650394972</v>
       </c>
       <c r="CB23" t="n">
-        <v>40.50875424376662</v>
+        <v>40.50875424692467</v>
       </c>
       <c r="CC23" t="n">
         <v>10.59424454785779</v>
@@ -8288,35 +8288,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX24" t="n">
-        <v>8.627042062321403</v>
+        <v>8.627042091816078</v>
       </c>
       <c r="BY24" t="n">
-        <v>13.85196405170026</v>
+        <v>13.85196401738628</v>
       </c>
       <c r="BZ24" t="n">
-        <v>18.49124802139176</v>
+        <v>18.49124791236634</v>
       </c>
       <c r="CA24" t="n">
         <v>17.39822241629838</v>
       </c>
       <c r="CB24" t="n">
-        <v>22.98547049638615</v>
+        <v>22.98547046825374</v>
       </c>
       <c r="CC24" t="n">
-        <v>17.33681286270502</v>
+        <v>17.33681285450712</v>
       </c>
       <c r="CD24" t="n">
-        <v>9.229677280189192</v>
+        <v>9.229677229939698</v>
       </c>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="n">
-        <v>14.57676674952961</v>
+        <v>14.57676671901895</v>
       </c>
       <c r="CG24" t="n">
-        <v>15.59438845720264</v>
+        <v>15.5943884359467</v>
       </c>
       <c r="CH24" t="n">
-        <v>14.03494961148238</v>
+        <v>14.03494959235203</v>
       </c>
       <c r="CI24" t="n">
         <v>4</v>
@@ -8328,10 +8328,10 @@
         <v>2.1</v>
       </c>
       <c r="CL24" t="n">
-        <v>9.221394512341053</v>
+        <v>9.221394363466739</v>
       </c>
       <c r="CM24" t="n">
-        <v>13.43787016963798</v>
+        <v>13.43786993220093</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -8598,10 +8598,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX25" t="n">
-        <v>9.186484952657352</v>
+        <v>9.186484939067871</v>
       </c>
       <c r="BY25" t="n">
-        <v>17.04092958717939</v>
+        <v>17.0409295619709</v>
       </c>
       <c r="BZ25" t="n">
         <v>30.69514051126462</v>
@@ -8610,23 +8610,23 @@
         <v>29.25728964348931</v>
       </c>
       <c r="CB25" t="n">
-        <v>34.71948756133753</v>
+        <v>34.71948755840006</v>
       </c>
       <c r="CC25" t="n">
-        <v>25.51046014357987</v>
+        <v>25.51046014636512</v>
       </c>
       <c r="CD25" t="n">
-        <v>15.34133400682346</v>
+        <v>15.34133402372116</v>
       </c>
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="n">
-        <v>20.60825379867031</v>
+        <v>20.60825378966713</v>
       </c>
       <c r="CG25" t="n">
-        <v>21.27569486537963</v>
+        <v>21.27569485416801</v>
       </c>
       <c r="CH25" t="n">
-        <v>19.14812537884167</v>
+        <v>19.14812536875121</v>
       </c>
       <c r="CI25" t="n">
         <v>4</v>
@@ -8638,10 +8638,10 @@
         <v>3.3</v>
       </c>
       <c r="CL25" t="n">
-        <v>29.55430125026371</v>
+        <v>29.55430118199269</v>
       </c>
       <c r="CM25" t="n">
-        <v>39.43338410688506</v>
+        <v>39.43338404597046</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>-7.171627471148123</v>
       </c>
       <c r="CZ25" t="n">
-        <v>-18.74747840191868</v>
+        <v>-18.7474872046273</v>
       </c>
       <c r="DA25" t="b">
         <v>1</v>
@@ -8906,10 +8906,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX26" t="n">
-        <v>20.16127561026532</v>
+        <v>20.16127578131654</v>
       </c>
       <c r="BY26" t="n">
-        <v>37.39916625704217</v>
+        <v>37.39916657434217</v>
       </c>
       <c r="BZ26" t="n">
         <v>56.01071616333269</v>
@@ -8918,23 +8918,23 @@
         <v>42.36568036412405</v>
       </c>
       <c r="CB26" t="n">
-        <v>61.78700440252356</v>
+        <v>61.78700412157808</v>
       </c>
       <c r="CC26" t="n">
-        <v>45.16919931072515</v>
+        <v>45.16919925726728</v>
       </c>
       <c r="CD26" t="n">
-        <v>31.11427808083772</v>
+        <v>31.11427774290894</v>
       </c>
       <c r="CE26" t="inlineStr"/>
       <c r="CF26" t="n">
-        <v>39.68508933534133</v>
+        <v>39.68508944406467</v>
       </c>
       <c r="CG26" t="n">
-        <v>41.28418278388367</v>
+        <v>41.28418291580473</v>
       </c>
       <c r="CH26" t="n">
-        <v>37.1557645054953</v>
+        <v>37.15576462422425</v>
       </c>
       <c r="CI26" t="n">
         <v>4</v>
@@ -8946,10 +8946,10 @@
         <v>2.8</v>
       </c>
       <c r="CL26" t="n">
-        <v>-5.791668865999378</v>
+        <v>-5.79166856496246</v>
       </c>
       <c r="CM26" t="n">
-        <v>0.6214267676631469</v>
+        <v>0.6214270433308577</v>
       </c>
       <c r="CN26" t="inlineStr">
         <is>
@@ -9232,10 +9232,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX27" t="n">
-        <v>6.975750796989641</v>
+        <v>6.975750761435104</v>
       </c>
       <c r="BY27" t="n">
-        <v>12.94001772841578</v>
+        <v>12.94001766246212</v>
       </c>
       <c r="BZ27" t="n">
         <v>5.584946345257502</v>
@@ -9256,7 +9256,7 @@
         <v>5.373183328823668</v>
       </c>
       <c r="CF27" t="n">
-        <v>7.287571958854734</v>
+        <v>7.287571946166208</v>
       </c>
       <c r="CG27" t="n">
         <v>5.859139839295418</v>
@@ -9277,7 +9277,7 @@
         <v>-10.31928991948218</v>
       </c>
       <c r="CM27" t="n">
-        <v>23.9382962077995</v>
+        <v>23.93829599200825</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -9560,37 +9560,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX28" t="n">
-        <v>16.91883609990701</v>
+        <v>16.91883610520417</v>
       </c>
       <c r="BY28" t="n">
-        <v>28.00431313303428</v>
+        <v>28.00431313367254</v>
       </c>
       <c r="BZ28" t="n">
-        <v>46.8316833394007</v>
+        <v>46.83168332580541</v>
       </c>
       <c r="CA28" t="n">
         <v>52.67243426197095</v>
       </c>
       <c r="CB28" t="n">
-        <v>55.69855923579338</v>
+        <v>55.69855923746945</v>
       </c>
       <c r="CC28" t="n">
-        <v>43.0354442939745</v>
+        <v>43.03544429300022</v>
       </c>
       <c r="CD28" t="n">
-        <v>23.30397203130465</v>
+        <v>23.30397202537988</v>
       </c>
       <c r="CE28" t="n">
         <v>30.43448362223624</v>
       </c>
       <c r="CF28" t="n">
-        <v>37.11246575220272</v>
+        <v>37.11246575059236</v>
       </c>
       <c r="CG28" t="n">
-        <v>36.73496395810537</v>
+        <v>36.73496395761823</v>
       </c>
       <c r="CH28" t="n">
-        <v>33.06146756229483</v>
+        <v>33.06146756185641</v>
       </c>
       <c r="CI28" t="n">
         <v>8</v>
@@ -9602,10 +9602,10 @@
         <v>3.3</v>
       </c>
       <c r="CL28" t="n">
-        <v>24.94886132364256</v>
+        <v>24.94886132198564</v>
       </c>
       <c r="CM28" t="n">
-        <v>40.25875675098256</v>
+        <v>40.25875674489654</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -9888,37 +9888,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX29" t="n">
-        <v>5.939526962110235</v>
+        <v>5.939526969706941</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.534880609653715</v>
+        <v>8.534880603381971</v>
       </c>
       <c r="BZ29" t="n">
-        <v>10.81501546646275</v>
+        <v>10.81501544468299</v>
       </c>
       <c r="CA29" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB29" t="n">
-        <v>9.810403816800907</v>
+        <v>9.810403804551399</v>
       </c>
       <c r="CC29" t="n">
-        <v>14.90925678154334</v>
+        <v>14.90925677887778</v>
       </c>
       <c r="CD29" t="n">
-        <v>5.384140043226401</v>
+        <v>5.384140030925815</v>
       </c>
       <c r="CE29" t="n">
         <v>11.00534556207784</v>
       </c>
       <c r="CF29" t="n">
-        <v>9.757252269237304</v>
+        <v>9.757252263278495</v>
       </c>
       <c r="CG29" t="n">
-        <v>10.31270964163183</v>
+        <v>10.31270962461719</v>
       </c>
       <c r="CH29" t="n">
-        <v>9.281438677468648</v>
+        <v>9.281438662155473</v>
       </c>
       <c r="CI29" t="n">
         <v>8</v>
@@ -9930,10 +9930,10 @@
         <v>2.8</v>
       </c>
       <c r="CL29" t="n">
-        <v>-39.37662689037982</v>
+        <v>-39.37662699040055</v>
       </c>
       <c r="CM29" t="n">
-        <v>-36.26876550091181</v>
+        <v>-36.26876553983283</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -10220,37 +10220,37 @@
         <v>38.86000061035156</v>
       </c>
       <c r="BX30" t="n">
-        <v>30.97422560804202</v>
+        <v>30.97422553975776</v>
       </c>
       <c r="BY30" t="n">
-        <v>35.52640282107112</v>
+        <v>35.52640287414108</v>
       </c>
       <c r="BZ30" t="n">
-        <v>38.58971732768785</v>
+        <v>38.58971747040682</v>
       </c>
       <c r="CA30" t="n">
         <v>49.80959882281965</v>
       </c>
       <c r="CB30" t="n">
-        <v>60.09290023981547</v>
+        <v>60.09290031647345</v>
       </c>
       <c r="CC30" t="n">
-        <v>16.76379308121115</v>
+        <v>16.76379308795554</v>
       </c>
       <c r="CD30" t="n">
-        <v>17.31674446170541</v>
+        <v>17.31674458272697</v>
       </c>
       <c r="CE30" t="n">
         <v>28.40888631687585</v>
       </c>
       <c r="CF30" t="n">
-        <v>34.68528358490357</v>
+        <v>34.68528362639464</v>
       </c>
       <c r="CG30" t="n">
-        <v>33.25031421455657</v>
+        <v>33.25031420694942</v>
       </c>
       <c r="CH30" t="n">
-        <v>29.92528279310091</v>
+        <v>29.92528278625448</v>
       </c>
       <c r="CI30" t="n">
         <v>8</v>
@@ -10262,10 +10262,10 @@
         <v>3.6</v>
       </c>
       <c r="CL30" t="n">
-        <v>-22.99206813411787</v>
+        <v>-22.99206815173607</v>
       </c>
       <c r="CM30" t="n">
-        <v>-10.74296695799828</v>
+        <v>-10.74296685122762</v>
       </c>
       <c r="CN30" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>1</v>
       </c>
       <c r="AT31" t="n">
-        <v>185049546752</v>
+        <v>184726978560</v>
       </c>
       <c r="AU31" t="n">
         <v>7.27</v>
@@ -10530,35 +10530,35 @@
         <v>16.78000068664551</v>
       </c>
       <c r="BX31" t="n">
-        <v>9.985664045721835</v>
+        <v>9.985664042179227</v>
       </c>
       <c r="BY31" t="n">
-        <v>17.51097130396708</v>
+        <v>17.51097130456651</v>
       </c>
       <c r="BZ31" t="n">
-        <v>28.91098000544013</v>
+        <v>28.91098001668654</v>
       </c>
       <c r="CA31" t="n">
         <v>29.08689850705222</v>
       </c>
       <c r="CB31" t="n">
-        <v>32.0896477399672</v>
+        <v>32.0896477401531</v>
       </c>
       <c r="CC31" t="n">
-        <v>27.89695682918288</v>
+        <v>27.8969568299852</v>
       </c>
       <c r="CD31" t="n">
-        <v>14.2494155930414</v>
+        <v>14.24941559744642</v>
       </c>
       <c r="CE31" t="inlineStr"/>
       <c r="CF31" t="n">
-        <v>21.07614304607798</v>
+        <v>21.07614304835437</v>
       </c>
       <c r="CG31" t="n">
-        <v>22.70396406657498</v>
+        <v>22.70396406727586</v>
       </c>
       <c r="CH31" t="n">
-        <v>20.43356765991748</v>
+        <v>20.43356766054827</v>
       </c>
       <c r="CI31" t="n">
         <v>4</v>
@@ -10570,10 +10570,10 @@
         <v>2.9</v>
       </c>
       <c r="CL31" t="n">
-        <v>21.77334221553217</v>
+        <v>21.77334221929135</v>
       </c>
       <c r="CM31" t="n">
-        <v>25.60275437206383</v>
+        <v>25.60275438562989</v>
       </c>
       <c r="CN31" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>-7.744448996751174</v>
       </c>
       <c r="CZ31" t="n">
-        <v>-20.99430923793453</v>
+        <v>-20.99430199889827</v>
       </c>
       <c r="DA31" t="b">
         <v>1</v>
@@ -10856,37 +10856,37 @@
         <v>44.2400016784668</v>
       </c>
       <c r="BX32" t="n">
-        <v>32.08627715399735</v>
+        <v>32.08627719702323</v>
       </c>
       <c r="BY32" t="n">
-        <v>44.20766650010867</v>
+        <v>44.20766641689121</v>
       </c>
       <c r="BZ32" t="n">
-        <v>50.92127217168321</v>
+        <v>50.92127200754537</v>
       </c>
       <c r="CA32" t="n">
         <v>47.73853825853298</v>
       </c>
       <c r="CB32" t="n">
-        <v>70.56922563943867</v>
+        <v>70.56922555068604</v>
       </c>
       <c r="CC32" t="n">
-        <v>59.89362087737182</v>
+        <v>59.893620859564</v>
       </c>
       <c r="CD32" t="n">
-        <v>25.15601716385589</v>
+        <v>25.15601706378459</v>
       </c>
       <c r="CE32" t="n">
         <v>76.57366731847841</v>
       </c>
       <c r="CF32" t="n">
-        <v>50.89328563543337</v>
+        <v>50.89328558406323</v>
       </c>
       <c r="CG32" t="n">
-        <v>49.32990521510809</v>
+        <v>49.32990513303918</v>
       </c>
       <c r="CH32" t="n">
-        <v>44.39691469359728</v>
+        <v>44.39691461973526</v>
       </c>
       <c r="CI32" t="n">
         <v>8</v>
@@ -10898,10 +10898,10 @@
         <v>3</v>
       </c>
       <c r="CL32" t="n">
-        <v>0.3546858254457552</v>
+        <v>0.3546856584882185</v>
       </c>
       <c r="CM32" t="n">
-        <v>15.03906804823874</v>
+        <v>15.03906793212177</v>
       </c>
       <c r="CN32" t="inlineStr">
         <is>
@@ -11166,10 +11166,10 @@
         <v>54.20000076293945</v>
       </c>
       <c r="BX33" t="n">
-        <v>10.59687590534817</v>
+        <v>10.5968759006117</v>
       </c>
       <c r="BY33" t="n">
-        <v>19.65720480442086</v>
+        <v>19.6572047956347</v>
       </c>
       <c r="BZ33" t="n">
         <v>62.12370329662177</v>
@@ -11178,7 +11178,7 @@
         <v>46.53820959650967</v>
       </c>
       <c r="CB33" t="n">
-        <v>83.16230744973755</v>
+        <v>83.16230744400134</v>
       </c>
       <c r="CC33" t="n">
         <v>11.76833333333333</v>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="CE33" t="inlineStr"/>
       <c r="CF33" t="n">
-        <v>14.00747134770079</v>
+        <v>14.00747134319324</v>
       </c>
       <c r="CG33" t="n">
         <v>11.76833333333333</v>
@@ -11209,7 +11209,7 @@
         <v>-80.45848735994448</v>
       </c>
       <c r="CM33" t="n">
-        <v>-74.15595728685167</v>
+        <v>-74.15595729516818</v>
       </c>
       <c r="CN33" t="inlineStr">
         <is>
@@ -11474,10 +11474,10 @@
         <v>29.69000053405762</v>
       </c>
       <c r="BX34" t="n">
-        <v>15.52022458567649</v>
+        <v>15.52022462881667</v>
       </c>
       <c r="BY34" t="n">
-        <v>28.79001660642989</v>
+        <v>28.79001668645492</v>
       </c>
       <c r="BZ34" t="n">
         <v>54.71383964899351</v>
@@ -11486,23 +11486,23 @@
         <v>49.40805952371795</v>
       </c>
       <c r="CB34" t="n">
-        <v>60.91790646631788</v>
+        <v>60.9179064555565</v>
       </c>
       <c r="CC34" t="n">
-        <v>36.63500708552354</v>
+        <v>36.63500707769816</v>
       </c>
       <c r="CD34" t="n">
-        <v>30.32696333156444</v>
+        <v>30.32696327199993</v>
       </c>
       <c r="CE34" t="inlineStr"/>
       <c r="CF34" t="n">
-        <v>33.91477198165586</v>
+        <v>33.91477201049081</v>
       </c>
       <c r="CG34" t="n">
-        <v>32.71251184597671</v>
+        <v>32.71251188207653</v>
       </c>
       <c r="CH34" t="n">
-        <v>29.44126066137904</v>
+        <v>29.44126069386888</v>
       </c>
       <c r="CI34" t="n">
         <v>4</v>
@@ -11514,10 +11514,10 @@
         <v>3.5</v>
       </c>
       <c r="CL34" t="n">
-        <v>-0.8377900579464193</v>
+        <v>-0.8377899485161877</v>
       </c>
       <c r="CM34" t="n">
-        <v>14.22961054767235</v>
+        <v>14.22961064479244</v>
       </c>
       <c r="CN34" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>-0.8018702595090188</v>
       </c>
       <c r="CZ34" t="n">
-        <v>-18.56623828442452</v>
+        <v>-18.56622956112421</v>
       </c>
       <c r="DA34" t="b">
         <v>1</v>
@@ -11802,10 +11802,10 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX35" t="n">
-        <v>13.08696646023153</v>
+        <v>13.08696643078177</v>
       </c>
       <c r="BY35" t="n">
-        <v>19.0546231660971</v>
+        <v>19.05462312321825</v>
       </c>
       <c r="BZ35" t="n">
         <v>16.71315021106592</v>
@@ -11824,7 +11824,7 @@
         <v>14.7644299189986</v>
       </c>
       <c r="CF35" t="n">
-        <v>16.15917316136627</v>
+        <v>16.1591731493115</v>
       </c>
       <c r="CG35" t="n">
         <v>15.73879006503226</v>
@@ -11845,7 +11845,7 @@
         <v>34.77555423456011</v>
       </c>
       <c r="CM35" t="n">
-        <v>53.7504548949515</v>
+        <v>53.7504547802534</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -12128,37 +12128,37 @@
         <v>18.63999938964844</v>
       </c>
       <c r="BX36" t="n">
-        <v>8.745140358007564</v>
+        <v>8.745140376463256</v>
       </c>
       <c r="BY36" t="n">
-        <v>9.206222539254405</v>
+        <v>9.206222538315652</v>
       </c>
       <c r="BZ36" t="n">
-        <v>9.666395057448174</v>
+        <v>9.666395036062593</v>
       </c>
       <c r="CA36" t="n">
         <v>16.93457208699175</v>
       </c>
       <c r="CB36" t="n">
-        <v>9.239151933083861</v>
+        <v>9.239151917313791</v>
       </c>
       <c r="CC36" t="n">
-        <v>17.54224666383774</v>
+        <v>17.5422466592823</v>
       </c>
       <c r="CD36" t="n">
-        <v>3.934238776984336</v>
+        <v>3.934238755871024</v>
       </c>
       <c r="CE36" t="n">
         <v>16.16233025852235</v>
       </c>
       <c r="CF36" t="n">
-        <v>11.42878720926627</v>
+        <v>11.42878720360284</v>
       </c>
       <c r="CG36" t="n">
-        <v>9.452773495266017</v>
+        <v>9.452773476688192</v>
       </c>
       <c r="CH36" t="n">
-        <v>8.507496145739415</v>
+        <v>8.507496129019373</v>
       </c>
       <c r="CI36" t="n">
         <v>8</v>
@@ -12170,10 +12170,10 @@
         <v>4.5</v>
       </c>
       <c r="CL36" t="n">
-        <v>-54.3589247622831</v>
+        <v>-54.35892485198291</v>
       </c>
       <c r="CM36" t="n">
-        <v>-38.68676189113424</v>
+        <v>-38.68676192151745</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.86871600316745</v>
+        <v>5.86871597626807</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646818587562</v>
+        <v>10.88646813597727</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.21781573324146</v>
@@ -13024,7 +13024,7 @@
         <v>27.66761889587421</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.26108658508552</v>
+        <v>71.26108647233362</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -13338,10 +13338,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01485115023178</v>
+        <v>15.01485126196847</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85254888367994</v>
+        <v>27.85254909095152</v>
       </c>
       <c r="BZ3" t="n">
         <v>39.46006465010361</v>
@@ -13350,13 +13350,13 @@
         <v>23.87433491384053</v>
       </c>
       <c r="CB3" t="n">
-        <v>76.71128055869886</v>
+        <v>76.71128035255107</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.54748526964112</v>
+        <v>48.54748518859483</v>
       </c>
       <c r="CD3" t="n">
-        <v>27.26172529540181</v>
+        <v>27.26172495066282</v>
       </c>
       <c r="CE3" t="n">
         <v>8.973116408407053</v>
@@ -13656,10 +13656,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388479636543</v>
+        <v>16.25388477265026</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.15095629725787</v>
+        <v>30.15095625326622</v>
       </c>
       <c r="BZ4" t="n">
         <v>70.99454413334874</v>
@@ -13668,19 +13668,19 @@
         <v>51.39538022233962</v>
       </c>
       <c r="CB4" t="n">
-        <v>124.8365656247644</v>
+        <v>124.8365656332173</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.69771468978261</v>
+        <v>25.69771469318724</v>
       </c>
       <c r="CD4" t="n">
-        <v>61.55225153257966</v>
+        <v>61.55225158345913</v>
       </c>
       <c r="CE4" t="n">
         <v>43.02986521586298</v>
       </c>
       <c r="CF4" t="n">
-        <v>47.13678534852858</v>
+        <v>47.13678535024399</v>
       </c>
       <c r="CG4" t="n">
         <v>47.2126227191013</v>
@@ -13701,7 +13701,7 @@
         <v>73.15142160530792</v>
       </c>
       <c r="CM4" t="n">
-        <v>92.08143272196634</v>
+        <v>92.08143272895661</v>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
@@ -13982,10 +13982,10 @@
         <v>4.059999942779541</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.54807282876565</v>
+        <v>3.548072834096487</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.58167509736028</v>
+        <v>6.581675107248985</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.56892505650208</v>
@@ -13994,25 +13994,25 @@
         <v>8.462578627869229</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.40274523688278</v>
+        <v>24.40274523318439</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.26517503412428</v>
+        <v>11.26517503191264</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.57787753601435</v>
+        <v>10.57787752272904</v>
       </c>
       <c r="CE5" t="n">
         <v>5.216748691568468</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.112163340573114</v>
+        <v>9.112163339638409</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.520228081941788</v>
+        <v>9.520228075299137</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.56820527374761</v>
+        <v>8.568205267769224</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -14024,10 +14024,10 @@
         <v>6.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>111.0395417365863</v>
+        <v>111.0395415893354</v>
       </c>
       <c r="CM5" t="n">
-        <v>124.4375238669285</v>
+        <v>124.4375238439062</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -14292,10 +14292,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294915543341</v>
+        <v>18.38294920812385</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037068332898</v>
+        <v>34.10037078106974</v>
       </c>
       <c r="BZ6" t="n">
         <v>75.02112937085505</v>
@@ -14304,23 +14304,23 @@
         <v>56.1385860856476</v>
       </c>
       <c r="CB6" t="n">
-        <v>100.7448468641835</v>
+        <v>100.7448467822811</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.4036999955209</v>
+        <v>48.40369998271307</v>
       </c>
       <c r="CD6" t="n">
-        <v>59.46380252610901</v>
+        <v>59.46380242020545</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>43.97703730128458</v>
+        <v>43.97703733569043</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.25203533942494</v>
+        <v>41.2520353818914</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.12683180548245</v>
+        <v>37.12683184370226</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -14332,10 +14332,10 @@
         <v>4.1</v>
       </c>
       <c r="CL6" t="n">
-        <v>-23.03725017892155</v>
+        <v>-23.03725009969308</v>
       </c>
       <c r="CM6" t="n">
-        <v>-8.836990524163069</v>
+        <v>-8.836990452840842</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -14618,10 +14618,10 @@
         <v>4.380000114440918</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774220937844</v>
+        <v>3.052774202256612</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.6628961798397</v>
+        <v>5.662896145186015</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.64379118003097</v>
@@ -14630,7 +14630,7 @@
         <v>8.50525545154361</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.62501978425786</v>
+        <v>23.62501972727807</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -14642,7 +14642,7 @@
         <v>5.24246353170767</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.25728134571453</v>
+        <v>11.25728133262403</v>
       </c>
       <c r="CG7" t="n">
         <v>11.54640553044338</v>
@@ -14663,7 +14663,7 @@
         <v>137.2549019607844</v>
       </c>
       <c r="CM7" t="n">
-        <v>157.0155491229127</v>
+        <v>157.0155488240429</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -15158,10 +15158,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX9" t="n">
-        <v>121.1494725411449</v>
+        <v>121.1494733628736</v>
       </c>
       <c r="BY9" t="n">
-        <v>224.7322715638238</v>
+        <v>224.7322730881305</v>
       </c>
       <c r="BZ9" t="n">
         <v>136.6302942100011</v>
@@ -15182,13 +15182,13 @@
         <v>57.66739801003497</v>
       </c>
       <c r="CF9" t="n">
-        <v>116.3031159598463</v>
+        <v>116.3031162949942</v>
       </c>
       <c r="CG9" t="n">
-        <v>121.1494725411449</v>
+        <v>121.1494733628736</v>
       </c>
       <c r="CH9" t="n">
-        <v>109.0345252870304</v>
+        <v>109.0345260265862</v>
       </c>
       <c r="CI9" t="n">
         <v>7</v>
@@ -15200,10 +15200,10 @@
         <v>5.5</v>
       </c>
       <c r="CL9" t="n">
-        <v>163.686890714808</v>
+        <v>163.6868925033347</v>
       </c>
       <c r="CM9" t="n">
-        <v>181.2651033896281</v>
+        <v>181.265104200143</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -15486,10 +15486,10 @@
         <v>15.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.426879087734028</v>
+        <v>6.426879098208645</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.92186070774662</v>
+        <v>11.92186072717704</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.54314565483476</v>
@@ -15498,19 +15498,19 @@
         <v>18.71731215268055</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.49020394518685</v>
+        <v>35.49020392821991</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.30123102245168</v>
+        <v>12.3012310204747</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.53560237134395</v>
+        <v>20.5356023493967</v>
       </c>
       <c r="CE10" t="n">
         <v>18.47523885586486</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.42637067287276</v>
+        <v>20.42637066980694</v>
       </c>
       <c r="CG10" t="n">
         <v>18.71731215268055</v>
@@ -15531,7 +15531,7 @@
         <v>6.956069443888868</v>
       </c>
       <c r="CM10" t="n">
-        <v>29.69124236744607</v>
+        <v>29.69124234798055</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -15814,37 +15814,37 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX11" t="n">
-        <v>24.20136286936076</v>
+        <v>24.20136299867336</v>
       </c>
       <c r="BY11" t="n">
-        <v>37.09024797787244</v>
+        <v>37.09024677252115</v>
       </c>
       <c r="BZ11" t="n">
-        <v>39.76038116972554</v>
+        <v>39.76037966515335</v>
       </c>
       <c r="CA11" t="n">
         <v>21.15376420319533</v>
       </c>
       <c r="CB11" t="n">
-        <v>53.96364505251905</v>
+        <v>53.96364405261692</v>
       </c>
       <c r="CC11" t="n">
-        <v>51.52714062780147</v>
+        <v>51.52714046459301</v>
       </c>
       <c r="CD11" t="n">
-        <v>19.88022335437046</v>
+        <v>19.8802225989987</v>
       </c>
       <c r="CE11" t="n">
         <v>24.52549486359719</v>
       </c>
       <c r="CF11" t="n">
-        <v>34.01278251480528</v>
+        <v>34.01278195241862</v>
       </c>
       <c r="CG11" t="n">
-        <v>30.80787142073481</v>
+        <v>30.80787081805916</v>
       </c>
       <c r="CH11" t="n">
-        <v>27.72708427866133</v>
+        <v>27.72708373625325</v>
       </c>
       <c r="CI11" t="n">
         <v>8</v>
@@ -15856,10 +15856,10 @@
         <v>2.7</v>
       </c>
       <c r="CL11" t="n">
-        <v>-14.8953875986822</v>
+        <v>-14.89538926353197</v>
       </c>
       <c r="CM11" t="n">
-        <v>4.397730519416032</v>
+        <v>4.397728793244671</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -16150,10 +16150,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX12" t="n">
-        <v>46.05538998425735</v>
+        <v>46.05539002065863</v>
       </c>
       <c r="BY12" t="n">
-        <v>85.43274842079738</v>
+        <v>85.43274848832176</v>
       </c>
       <c r="BZ12" t="n">
         <v>69.47297200868543</v>
@@ -16174,7 +16174,7 @@
         <v>25.94666723750103</v>
       </c>
       <c r="CF12" t="n">
-        <v>78.49436730402689</v>
+        <v>78.49436731887342</v>
       </c>
       <c r="CG12" t="n">
         <v>69.47297200868543</v>
@@ -16195,7 +16195,7 @@
         <v>89.58664546899841</v>
       </c>
       <c r="CM12" t="n">
-        <v>138.0059684461242</v>
+        <v>138.0059684911409</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -16480,10 +16480,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX13" t="n">
-        <v>127.6301659713547</v>
+        <v>127.6301650953702</v>
       </c>
       <c r="BY13" t="n">
-        <v>236.7539578768629</v>
+        <v>236.7539562519117</v>
       </c>
       <c r="BZ13" t="n">
         <v>137.215088724016</v>
@@ -16504,13 +16504,13 @@
         <v>56.54612056896573</v>
       </c>
       <c r="CF13" t="n">
-        <v>142.9573017812868</v>
+        <v>142.9573014686699</v>
       </c>
       <c r="CG13" t="n">
-        <v>126.4680102898507</v>
+        <v>126.4680098518585</v>
       </c>
       <c r="CH13" t="n">
-        <v>113.8212092608657</v>
+        <v>113.8212088666726</v>
       </c>
       <c r="CI13" t="n">
         <v>8</v>
@@ -16522,10 +16522,10 @@
         <v>5.5</v>
       </c>
       <c r="CL13" t="n">
-        <v>147.5450421792887</v>
+        <v>147.5450413219745</v>
       </c>
       <c r="CM13" t="n">
-        <v>210.9119251947122</v>
+        <v>210.9119245148145</v>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
@@ -16808,10 +16808,10 @@
         <v>7.050000190734863</v>
       </c>
       <c r="BX14" t="n">
-        <v>6.618982258250529</v>
+        <v>6.61898229297842</v>
       </c>
       <c r="BY14" t="n">
-        <v>12.27821208905473</v>
+        <v>12.27821215347497</v>
       </c>
       <c r="BZ14" t="n">
         <v>41.15088217058896</v>
@@ -16820,7 +16820,7 @@
         <v>27.74453639251564</v>
       </c>
       <c r="CB14" t="n">
-        <v>87.40782135529973</v>
+        <v>87.40782156948055</v>
       </c>
       <c r="CC14" t="n">
         <v>51.88018214566937</v>
@@ -17418,10 +17418,10 @@
         <v>14</v>
       </c>
       <c r="BX16" t="n">
-        <v>10.16255143946796</v>
+        <v>10.16255141045656</v>
       </c>
       <c r="BY16" t="n">
-        <v>18.85153292021306</v>
+        <v>18.85153286639692</v>
       </c>
       <c r="BZ16" t="n">
         <v>50.13513513513512</v>
@@ -17430,23 +17430,23 @@
         <v>49.31969619160719</v>
       </c>
       <c r="CB16" t="n">
-        <v>69.76010981927207</v>
+        <v>69.76010976335598</v>
       </c>
       <c r="CC16" t="n">
-        <v>33.93518588519073</v>
+        <v>33.93518588965181</v>
       </c>
       <c r="CD16" t="n">
-        <v>29.78692738171904</v>
+        <v>29.78692741557185</v>
       </c>
       <c r="CE16" t="inlineStr"/>
       <c r="CF16" t="n">
-        <v>34.30728464684631</v>
+        <v>34.30728463039462</v>
       </c>
       <c r="CG16" t="n">
-        <v>33.93518588519073</v>
+        <v>33.93518588965181</v>
       </c>
       <c r="CH16" t="n">
-        <v>30.54166729667165</v>
+        <v>30.54166730068663</v>
       </c>
       <c r="CI16" t="n">
         <v>3</v>
@@ -17458,10 +17458,10 @@
         <v>4.9</v>
       </c>
       <c r="CL16" t="n">
-        <v>118.1547664047975</v>
+        <v>118.1547664334759</v>
       </c>
       <c r="CM16" t="n">
-        <v>145.0520331917593</v>
+        <v>145.0520330742473</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -17722,10 +17722,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX17" t="n">
-        <v>13.15731119057001</v>
+        <v>13.15731118693232</v>
       </c>
       <c r="BY17" t="n">
-        <v>24.40681225850738</v>
+        <v>24.40681225175945</v>
       </c>
       <c r="BZ17" t="n">
         <v>19.90620030713044</v>
@@ -17734,7 +17734,7 @@
         <v>12.44114419785431</v>
       </c>
       <c r="CB17" t="n">
-        <v>33.6887243999592</v>
+        <v>33.68872439596174</v>
       </c>
       <c r="CC17" t="n">
         <v>22.8984489302328</v>
@@ -17744,7 +17744,7 @@
       </c>
       <c r="CE17" t="inlineStr"/>
       <c r="CF17" t="n">
-        <v>20.09219317161016</v>
+        <v>20.09219316901375</v>
       </c>
       <c r="CG17" t="n">
         <v>21.40232461868162</v>
@@ -17765,7 +17765,7 @@
         <v>0.6378932657179259</v>
       </c>
       <c r="CM17" t="n">
-        <v>4.974889301598906</v>
+        <v>4.974889288033602</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -18052,10 +18052,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX18" t="n">
-        <v>3.363729732909307</v>
+        <v>3.363729732974996</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.239718654546764</v>
+        <v>6.239718654668616</v>
       </c>
       <c r="BZ18" t="n">
         <v>20.7379196371351</v>
@@ -18064,7 +18064,7 @@
         <v>14.20601824710207</v>
       </c>
       <c r="CB18" t="n">
-        <v>33.37021289909818</v>
+        <v>33.37021289929139</v>
       </c>
       <c r="CC18" t="n">
         <v>10.95072400487419</v>
@@ -18378,10 +18378,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX19" t="n">
-        <v>10.74426541307544</v>
+        <v>10.74426546359599</v>
       </c>
       <c r="BY19" t="n">
-        <v>19.93061234125494</v>
+        <v>19.93061243497056</v>
       </c>
       <c r="BZ19" t="n">
         <v>37.5845483977432</v>
@@ -18390,25 +18390,25 @@
         <v>37.1651975122017</v>
       </c>
       <c r="CB19" t="n">
-        <v>41.90042981465468</v>
+        <v>41.90042983588201</v>
       </c>
       <c r="CC19" t="n">
-        <v>34.50408899034814</v>
+        <v>34.50408897966985</v>
       </c>
       <c r="CD19" t="n">
-        <v>18.61582873127402</v>
+        <v>18.61582867267827</v>
       </c>
       <c r="CE19" t="n">
         <v>31.97921770241074</v>
       </c>
       <c r="CF19" t="n">
-        <v>31.66856049855534</v>
+        <v>31.66856050507948</v>
       </c>
       <c r="CG19" t="n">
-        <v>34.50408899034814</v>
+        <v>34.50408897966985</v>
       </c>
       <c r="CH19" t="n">
-        <v>31.05368009131333</v>
+        <v>31.05368008170287</v>
       </c>
       <c r="CI19" t="n">
         <v>7</v>
@@ -18420,10 +18420,10 @@
         <v>3.9</v>
       </c>
       <c r="CL19" t="n">
-        <v>77.14591485994788</v>
+        <v>77.14591480512493</v>
       </c>
       <c r="CM19" t="n">
-        <v>80.65350403939631</v>
+        <v>80.65350407661329</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -18708,10 +18708,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX20" t="n">
-        <v>5.044350330400213</v>
+        <v>5.044350326490063</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.357269862892394</v>
+        <v>9.357269855639066</v>
       </c>
       <c r="BZ20" t="n">
         <v>8.531826591579675</v>
@@ -19026,37 +19026,37 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX21" t="n">
-        <v>10.37863321725536</v>
+        <v>10.3786331450779</v>
       </c>
       <c r="BY21" t="n">
-        <v>18.07553048217811</v>
+        <v>18.07553066680664</v>
       </c>
       <c r="BZ21" t="n">
-        <v>23.22146472121366</v>
+        <v>23.22146511989621</v>
       </c>
       <c r="CA21" t="n">
         <v>17.75681071950086</v>
       </c>
       <c r="CB21" t="n">
-        <v>36.48041910786196</v>
+        <v>36.48041917740331</v>
       </c>
       <c r="CC21" t="n">
-        <v>24.12244062846323</v>
+        <v>24.12244065927788</v>
       </c>
       <c r="CD21" t="n">
-        <v>11.46100442756559</v>
+        <v>11.46100458572084</v>
       </c>
       <c r="CE21" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF21" t="n">
-        <v>18.9820378700895</v>
+        <v>18.98203796629511</v>
       </c>
       <c r="CG21" t="n">
-        <v>17.91617060083949</v>
+        <v>17.91617069315375</v>
       </c>
       <c r="CH21" t="n">
-        <v>16.12455354075554</v>
+        <v>16.12455362383837</v>
       </c>
       <c r="CI21" t="n">
         <v>8</v>
@@ -19068,10 +19068,10 @@
         <v>3.5</v>
       </c>
       <c r="CL21" t="n">
-        <v>55.64241385242625</v>
+        <v>55.64241465438411</v>
       </c>
       <c r="CM21" t="n">
-        <v>83.2243098372611</v>
+        <v>83.22431076588668</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -19354,10 +19354,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.454302383090375</v>
+        <v>3.454302376873577</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.407730920632644</v>
+        <v>6.407730909100485</v>
       </c>
       <c r="BZ22" t="n">
         <v>20.16620865234961</v>
@@ -19366,13 +19366,13 @@
         <v>19.00949927082382</v>
       </c>
       <c r="CB22" t="n">
-        <v>21.60588271629159</v>
+        <v>21.60588271687798</v>
       </c>
       <c r="CC22" t="n">
-        <v>15.9282701250515</v>
+        <v>15.92827012624657</v>
       </c>
       <c r="CD22" t="n">
-        <v>13.471165756342</v>
+        <v>13.4711657642254</v>
       </c>
       <c r="CE22" t="n">
         <v>30.336208848481</v>
@@ -19428,7 +19428,7 @@
         <v>-18.94659940111765</v>
       </c>
       <c r="CZ22" t="n">
-        <v>-32.89649636084019</v>
+        <v>-32.89648837260555</v>
       </c>
       <c r="DA22" t="b">
         <v>1</v>
@@ -19672,37 +19672,37 @@
         <v>35.20000076293945</v>
       </c>
       <c r="BX23" t="n">
-        <v>25.31139903711134</v>
+        <v>25.31139913744763</v>
       </c>
       <c r="BY23" t="n">
-        <v>29.80495164107754</v>
+        <v>29.80495150098457</v>
       </c>
       <c r="BZ23" t="n">
-        <v>32.18096631881718</v>
+        <v>32.18096603998838</v>
       </c>
       <c r="CA23" t="n">
         <v>35.90922954270143</v>
       </c>
       <c r="CB23" t="n">
-        <v>45.73499586302033</v>
+        <v>45.73499565680308</v>
       </c>
       <c r="CC23" t="n">
-        <v>48.24380385269888</v>
+        <v>48.24380380828207</v>
       </c>
       <c r="CD23" t="n">
-        <v>14.75792649248404</v>
+        <v>14.75792626688792</v>
       </c>
       <c r="CE23" t="n">
         <v>30.3203711305658</v>
       </c>
       <c r="CF23" t="n">
-        <v>32.78295548480956</v>
+        <v>32.78295538545761</v>
       </c>
       <c r="CG23" t="n">
-        <v>31.25066872469149</v>
+        <v>31.25066858527709</v>
       </c>
       <c r="CH23" t="n">
-        <v>28.12560185222234</v>
+        <v>28.12560172674938</v>
       </c>
       <c r="CI23" t="n">
         <v>8</v>
@@ -19714,10 +19714,10 @@
         <v>3.3</v>
       </c>
       <c r="CL23" t="n">
-        <v>-20.09772374256719</v>
+        <v>-20.09772409902445</v>
       </c>
       <c r="CM23" t="n">
-        <v>-6.866605754948429</v>
+        <v>-6.866606037198276</v>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
@@ -19904,13 +19904,13 @@
         <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AS24" t="b">
         <v>1</v>
       </c>
       <c r="AT24" t="n">
-        <v>5725241856</v>
+        <v>3602869248</v>
       </c>
       <c r="AU24" t="n">
         <v>6.7</v>
@@ -20000,10 +20000,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX24" t="n">
-        <v>9.774107130994336</v>
+        <v>9.774107128522251</v>
       </c>
       <c r="BY24" t="n">
-        <v>18.1309687279945</v>
+        <v>18.13096872340877</v>
       </c>
       <c r="BZ24" t="n">
         <v>22.32723873053024</v>
@@ -20012,25 +20012,25 @@
         <v>13.19107667093893</v>
       </c>
       <c r="CB24" t="n">
-        <v>32.07171956569217</v>
+        <v>32.07171957325589</v>
       </c>
       <c r="CC24" t="n">
-        <v>25.27239703637801</v>
+        <v>25.27239703816369</v>
       </c>
       <c r="CD24" t="n">
-        <v>11.82328982545854</v>
+        <v>11.8232898334598</v>
       </c>
       <c r="CE24" t="n">
         <v>9.733055502947964</v>
       </c>
       <c r="CF24" t="n">
-        <v>17.79048164886684</v>
+        <v>17.79048165015344</v>
       </c>
       <c r="CG24" t="n">
-        <v>15.66102269946671</v>
+        <v>15.66102269717385</v>
       </c>
       <c r="CH24" t="n">
-        <v>14.09492042952004</v>
+        <v>14.09492042745647</v>
       </c>
       <c r="CI24" t="n">
         <v>8</v>
@@ -20042,10 +20042,10 @@
         <v>3.3</v>
       </c>
       <c r="CL24" t="n">
-        <v>24.8442912058845</v>
+        <v>24.8442911876066</v>
       </c>
       <c r="CM24" t="n">
-        <v>57.57734020352368</v>
+        <v>57.57734021491962</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -20328,10 +20328,10 @@
         <v>14.13000011444092</v>
       </c>
       <c r="BX25" t="n">
-        <v>4.339755639171419</v>
+        <v>4.339755634840489</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.050246710662982</v>
+        <v>8.050246702629106</v>
       </c>
       <c r="BZ25" t="n">
         <v>23.63920473691189</v>
@@ -20340,25 +20340,25 @@
         <v>19.91603197659278</v>
       </c>
       <c r="CB25" t="n">
-        <v>28.9310943931589</v>
+        <v>28.9310943964596</v>
       </c>
       <c r="CC25" t="n">
-        <v>16.71775062546117</v>
+        <v>16.71775062637852</v>
       </c>
       <c r="CD25" t="n">
-        <v>18.1293800898248</v>
+        <v>18.12938009671167</v>
       </c>
       <c r="CE25" t="n">
         <v>13.90588124012942</v>
       </c>
       <c r="CF25" t="n">
-        <v>18.46994139610599</v>
+        <v>18.46994139654472</v>
       </c>
       <c r="CG25" t="n">
-        <v>18.1293800898248</v>
+        <v>18.12938009671167</v>
       </c>
       <c r="CH25" t="n">
-        <v>16.31644208084232</v>
+        <v>16.31644208704051</v>
       </c>
       <c r="CI25" t="n">
         <v>7</v>
@@ -20370,10 +20370,10 @@
         <v>6.7</v>
       </c>
       <c r="CL25" t="n">
-        <v>15.47375759867724</v>
+        <v>15.47375764254266</v>
       </c>
       <c r="CM25" t="n">
-        <v>30.71437541765931</v>
+        <v>30.71437542076423</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -20654,10 +20654,10 @@
         <v>8</v>
       </c>
       <c r="BX26" t="n">
-        <v>3.706794285075357</v>
+        <v>3.706794289133744</v>
       </c>
       <c r="BY26" t="n">
-        <v>6.876103398814785</v>
+        <v>6.876103406343096</v>
       </c>
       <c r="BZ26" t="n">
         <v>24.65116279069767</v>
@@ -20666,13 +20666,13 @@
         <v>22.8747855498907</v>
       </c>
       <c r="CB26" t="n">
-        <v>31.90962337914971</v>
+        <v>31.90962338395977</v>
       </c>
       <c r="CC26" t="n">
-        <v>9.605681426851284</v>
+        <v>9.605681426459231</v>
       </c>
       <c r="CD26" t="n">
-        <v>17.44157961371663</v>
+        <v>17.44157960843456</v>
       </c>
       <c r="CE26" t="inlineStr"/>
       <c r="CF26" t="inlineStr"/>
@@ -20966,10 +20966,10 @@
         <v>13.23999977111816</v>
       </c>
       <c r="BX27" t="n">
-        <v>8.302793977641096</v>
+        <v>8.302793976110308</v>
       </c>
       <c r="BY27" t="n">
-        <v>15.40168282852423</v>
+        <v>15.40168282568462</v>
       </c>
       <c r="BZ27" t="n">
         <v>13.23999977111816</v>
@@ -20990,7 +20990,7 @@
         <v>6.052411187494985</v>
       </c>
       <c r="CF27" t="n">
-        <v>10.88286237257976</v>
+        <v>10.88286237195542</v>
       </c>
       <c r="CG27" t="n">
         <v>10.76229112776816</v>
@@ -21011,7 +21011,7 @@
         <v>-26.84243064625581</v>
       </c>
       <c r="CM27" t="n">
-        <v>-17.80315286470234</v>
+        <v>-17.80315286941791</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -21290,10 +21290,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX28" t="n">
-        <v>7.290978496927618</v>
+        <v>7.290978528882397</v>
       </c>
       <c r="BY28" t="n">
-        <v>13.52476511180073</v>
+        <v>13.52476517107684</v>
       </c>
       <c r="BZ28" t="n">
         <v>35.92512375028262</v>
@@ -21302,19 +21302,19 @@
         <v>28.41024685094796</v>
       </c>
       <c r="CB28" t="n">
-        <v>44.74749257504084</v>
+        <v>44.7474925273167</v>
       </c>
       <c r="CC28" t="n">
-        <v>26.46268145824689</v>
+        <v>26.46268145030354</v>
       </c>
       <c r="CD28" t="n">
-        <v>29.04887757284678</v>
+        <v>29.04887751514411</v>
       </c>
       <c r="CE28" t="n">
         <v>24.98203479043206</v>
       </c>
       <c r="CF28" t="n">
-        <v>29.01446030137112</v>
+        <v>29.0144602936434</v>
       </c>
       <c r="CG28" t="n">
         <v>28.41024685094796</v>
@@ -21335,7 +21335,7 @@
         <v>-7.088583791648039</v>
       </c>
       <c r="CM28" t="n">
-        <v>5.430449922779168</v>
+        <v>5.430449894698786</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -21598,10 +21598,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX29" t="n">
-        <v>35.6289255576336</v>
+        <v>35.62892560284679</v>
       </c>
       <c r="BY29" t="n">
-        <v>51.87571561191452</v>
+        <v>51.87571567774493</v>
       </c>
       <c r="BZ29" t="n">
         <v>48.56662855571916</v>
@@ -21618,13 +21618,13 @@
       </c>
       <c r="CE29" t="inlineStr"/>
       <c r="CF29" t="n">
-        <v>48.89385867727125</v>
+        <v>48.89385870503214</v>
       </c>
       <c r="CG29" t="n">
-        <v>50.22117208381684</v>
+        <v>50.22117211673205</v>
       </c>
       <c r="CH29" t="n">
-        <v>45.19905487543516</v>
+        <v>45.19905490505884</v>
       </c>
       <c r="CI29" t="n">
         <v>4</v>
@@ -21636,10 +21636,10 @@
         <v>1.7</v>
       </c>
       <c r="CL29" t="n">
-        <v>16.19293856676509</v>
+        <v>16.19293864291851</v>
       </c>
       <c r="CM29" t="n">
-        <v>25.69114848168772</v>
+        <v>25.6911485530525</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -21926,10 +21926,10 @@
         <v>24.72999954223633</v>
       </c>
       <c r="BX30" t="n">
-        <v>12.83053368128606</v>
+        <v>12.83053367577991</v>
       </c>
       <c r="BY30" t="n">
-        <v>23.80063997878564</v>
+        <v>23.80063996857173</v>
       </c>
       <c r="BZ30" t="n">
         <v>61.13292797287897</v>
@@ -21938,13 +21938,13 @@
         <v>51.18231610165188</v>
       </c>
       <c r="CB30" t="n">
-        <v>84.96070712612305</v>
+        <v>84.96070712581724</v>
       </c>
       <c r="CC30" t="n">
-        <v>33.648194807038</v>
+        <v>33.64819480796157</v>
       </c>
       <c r="CD30" t="n">
-        <v>44.66427061660671</v>
+        <v>44.66427062545444</v>
       </c>
       <c r="CE30" t="n">
         <v>5.441506065857172</v>
@@ -22240,10 +22240,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX31" t="n">
-        <v>3.108740526292904</v>
+        <v>3.108740528356239</v>
       </c>
       <c r="BY31" t="n">
-        <v>5.766713676273336</v>
+        <v>5.766713680100823</v>
       </c>
       <c r="BZ31" t="n">
         <v>31.95928917556512</v>
@@ -22252,7 +22252,7 @@
         <v>26.70105358379499</v>
       </c>
       <c r="CB31" t="n">
-        <v>40.93687025032393</v>
+        <v>40.93687025348094</v>
       </c>
       <c r="CC31" t="n">
         <v>10.85340539909456</v>
@@ -22558,10 +22558,10 @@
         <v>12.02999973297119</v>
       </c>
       <c r="BX32" t="n">
-        <v>2.08102403333652</v>
+        <v>2.081024034886541</v>
       </c>
       <c r="BY32" t="n">
-        <v>3.860299581839244</v>
+        <v>3.860299584714533</v>
       </c>
       <c r="BZ32" t="n">
         <v>28.46383865390505</v>
@@ -22570,7 +22570,7 @@
         <v>24.11364501630011</v>
       </c>
       <c r="CB32" t="n">
-        <v>37.42577365379986</v>
+        <v>37.42577365767491</v>
       </c>
       <c r="CC32" t="n">
         <v>9.158754146</v>
@@ -22872,10 +22872,10 @@
         <v>32.75</v>
       </c>
       <c r="BX33" t="n">
-        <v>3.24935669499341</v>
+        <v>3.249356697982276</v>
       </c>
       <c r="BY33" t="n">
-        <v>6.027556669212775</v>
+        <v>6.027556674757121</v>
       </c>
       <c r="BZ33" t="n">
         <v>32.74999999999999</v>
@@ -22884,7 +22884,7 @@
         <v>22.94333650394972</v>
       </c>
       <c r="CB33" t="n">
-        <v>40.50875424376662</v>
+        <v>40.50875424692467</v>
       </c>
       <c r="CC33" t="n">
         <v>10.59424454785779</v>
@@ -23155,7 +23155,7 @@
         <v>-11.5</v>
       </c>
       <c r="BK34" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="BL34" t="n">
         <v>7.18</v>
@@ -23194,10 +23194,10 @@
         <v>33.43000030517578</v>
       </c>
       <c r="BX34" t="n">
-        <v>7.930922153366162</v>
+        <v>7.930922164176469</v>
       </c>
       <c r="BY34" t="n">
-        <v>14.71186059449423</v>
+        <v>14.71186061454735</v>
       </c>
       <c r="BZ34" t="n">
         <v>65.23527305501902</v>
@@ -23206,7 +23206,7 @@
         <v>38.10857086024811</v>
       </c>
       <c r="CB34" t="n">
-        <v>90.20366932618012</v>
+        <v>90.20366934846943</v>
       </c>
       <c r="CC34" t="n">
         <v>22.51480113099953</v>
@@ -23490,35 +23490,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="BX35" t="n">
-        <v>16.54376620264756</v>
+        <v>16.54376614351627</v>
       </c>
       <c r="BY35" t="n">
-        <v>29.62891131829394</v>
+        <v>29.62891132726303</v>
       </c>
       <c r="BZ35" t="n">
-        <v>50.0620805887278</v>
+        <v>50.06208078281589</v>
       </c>
       <c r="CA35" t="n">
         <v>49.44990718954784</v>
       </c>
       <c r="CB35" t="n">
-        <v>61.76490018461578</v>
+        <v>61.76490016037727</v>
       </c>
       <c r="CC35" t="n">
-        <v>45.7620935015432</v>
+        <v>45.76209351440657</v>
       </c>
       <c r="CD35" t="n">
-        <v>24.56071163799285</v>
+        <v>24.56071171110277</v>
       </c>
       <c r="CE35" t="inlineStr"/>
       <c r="CF35" t="n">
-        <v>35.49921290280312</v>
+        <v>35.49921294200044</v>
       </c>
       <c r="CG35" t="n">
-        <v>37.69550240991857</v>
+        <v>37.6955024208348</v>
       </c>
       <c r="CH35" t="n">
-        <v>33.92595216892671</v>
+        <v>33.92595217875132</v>
       </c>
       <c r="CI35" t="n">
         <v>4</v>
@@ -23530,10 +23530,10 @@
         <v>3</v>
       </c>
       <c r="CL35" t="n">
-        <v>47.1841791403596</v>
+        <v>47.18417918298263</v>
       </c>
       <c r="CM35" t="n">
-        <v>54.0096055436146</v>
+        <v>54.00960571366804</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -23812,10 +23812,10 @@
         <v>33.65000152587891</v>
       </c>
       <c r="BX36" t="n">
-        <v>15.24688683049825</v>
+        <v>15.24688686621493</v>
       </c>
       <c r="BY36" t="n">
-        <v>28.28297507057425</v>
+        <v>28.28297513682869</v>
       </c>
       <c r="BZ36" t="n">
         <v>20.19304892291193</v>
@@ -23824,7 +23824,7 @@
         <v>37.28531071349501</v>
       </c>
       <c r="CB36" t="n">
-        <v>27.19345258942858</v>
+        <v>27.19345261207502</v>
       </c>
       <c r="CC36" t="n">
         <v>15.03391666666667</v>
@@ -23836,7 +23836,7 @@
         <v>79.29138454079849</v>
       </c>
       <c r="CF36" t="n">
-        <v>22.61760390675679</v>
+        <v>22.6176039245593</v>
       </c>
       <c r="CG36" t="n">
         <v>20.19304892291193</v>
@@ -23857,7 +23857,7 @@
         <v>-45.99184782608695</v>
       </c>
       <c r="CM36" t="n">
-        <v>-32.78572695052488</v>
+        <v>-32.78572689761995</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -24116,35 +24116,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX37" t="n">
-        <v>8.627042062321403</v>
+        <v>8.627042091816078</v>
       </c>
       <c r="BY37" t="n">
-        <v>13.85196405170026</v>
+        <v>13.85196401738628</v>
       </c>
       <c r="BZ37" t="n">
-        <v>18.49124802139176</v>
+        <v>18.49124791236634</v>
       </c>
       <c r="CA37" t="n">
         <v>17.39822241629838</v>
       </c>
       <c r="CB37" t="n">
-        <v>22.98547049638615</v>
+        <v>22.98547046825374</v>
       </c>
       <c r="CC37" t="n">
-        <v>17.33681286270502</v>
+        <v>17.33681285450712</v>
       </c>
       <c r="CD37" t="n">
-        <v>9.229677280189192</v>
+        <v>9.229677229939698</v>
       </c>
       <c r="CE37" t="inlineStr"/>
       <c r="CF37" t="n">
-        <v>14.57676674952961</v>
+        <v>14.57676671901895</v>
       </c>
       <c r="CG37" t="n">
-        <v>15.59438845720264</v>
+        <v>15.5943884359467</v>
       </c>
       <c r="CH37" t="n">
-        <v>14.03494961148238</v>
+        <v>14.03494959235203</v>
       </c>
       <c r="CI37" t="n">
         <v>4</v>
@@ -24156,10 +24156,10 @@
         <v>2.1</v>
       </c>
       <c r="CL37" t="n">
-        <v>9.221394512341053</v>
+        <v>9.221394363466739</v>
       </c>
       <c r="CM37" t="n">
-        <v>13.43787016963798</v>
+        <v>13.43786993220093</v>
       </c>
       <c r="CN37" t="inlineStr">
         <is>
@@ -24426,10 +24426,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX38" t="n">
-        <v>9.186484952657352</v>
+        <v>9.186484939067871</v>
       </c>
       <c r="BY38" t="n">
-        <v>17.04092958717939</v>
+        <v>17.0409295619709</v>
       </c>
       <c r="BZ38" t="n">
         <v>30.69514051126462</v>
@@ -24438,23 +24438,23 @@
         <v>29.25728964348931</v>
       </c>
       <c r="CB38" t="n">
-        <v>34.71948756133753</v>
+        <v>34.71948755840006</v>
       </c>
       <c r="CC38" t="n">
-        <v>25.51046014357987</v>
+        <v>25.51046014636512</v>
       </c>
       <c r="CD38" t="n">
-        <v>15.34133400682346</v>
+        <v>15.34133402372116</v>
       </c>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="n">
-        <v>20.60825379867031</v>
+        <v>20.60825378966713</v>
       </c>
       <c r="CG38" t="n">
-        <v>21.27569486537963</v>
+        <v>21.27569485416801</v>
       </c>
       <c r="CH38" t="n">
-        <v>19.14812537884167</v>
+        <v>19.14812536875121</v>
       </c>
       <c r="CI38" t="n">
         <v>4</v>
@@ -24466,10 +24466,10 @@
         <v>3.3</v>
       </c>
       <c r="CL38" t="n">
-        <v>29.55430125026371</v>
+        <v>29.55430118199269</v>
       </c>
       <c r="CM38" t="n">
-        <v>39.43338410688506</v>
+        <v>39.43338404597046</v>
       </c>
       <c r="CN38" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>-7.171627471148123</v>
       </c>
       <c r="CZ38" t="n">
-        <v>-18.74747840191868</v>
+        <v>-18.7474872046273</v>
       </c>
       <c r="DA38" t="b">
         <v>1</v>
@@ -24734,10 +24734,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX39" t="n">
-        <v>20.16127561026532</v>
+        <v>20.16127578131654</v>
       </c>
       <c r="BY39" t="n">
-        <v>37.39916625704217</v>
+        <v>37.39916657434217</v>
       </c>
       <c r="BZ39" t="n">
         <v>56.01071616333269</v>
@@ -24746,23 +24746,23 @@
         <v>42.36568036412405</v>
       </c>
       <c r="CB39" t="n">
-        <v>61.78700440252356</v>
+        <v>61.78700412157808</v>
       </c>
       <c r="CC39" t="n">
-        <v>45.16919931072515</v>
+        <v>45.16919925726728</v>
       </c>
       <c r="CD39" t="n">
-        <v>31.11427808083772</v>
+        <v>31.11427774290894</v>
       </c>
       <c r="CE39" t="inlineStr"/>
       <c r="CF39" t="n">
-        <v>39.68508933534133</v>
+        <v>39.68508944406467</v>
       </c>
       <c r="CG39" t="n">
-        <v>41.28418278388367</v>
+        <v>41.28418291580473</v>
       </c>
       <c r="CH39" t="n">
-        <v>37.1557645054953</v>
+        <v>37.15576462422425</v>
       </c>
       <c r="CI39" t="n">
         <v>4</v>
@@ -24774,10 +24774,10 @@
         <v>2.8</v>
       </c>
       <c r="CL39" t="n">
-        <v>-5.791668865999378</v>
+        <v>-5.79166856496246</v>
       </c>
       <c r="CM39" t="n">
-        <v>0.6214267676631469</v>
+        <v>0.6214270433308577</v>
       </c>
       <c r="CN39" t="inlineStr">
         <is>
@@ -25060,10 +25060,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX40" t="n">
-        <v>6.975750796989641</v>
+        <v>6.975750761435104</v>
       </c>
       <c r="BY40" t="n">
-        <v>12.94001772841578</v>
+        <v>12.94001766246212</v>
       </c>
       <c r="BZ40" t="n">
         <v>5.584946345257502</v>
@@ -25084,7 +25084,7 @@
         <v>5.373183328823668</v>
       </c>
       <c r="CF40" t="n">
-        <v>7.287571958854734</v>
+        <v>7.287571946166208</v>
       </c>
       <c r="CG40" t="n">
         <v>5.859139839295418</v>
@@ -25105,7 +25105,7 @@
         <v>-10.31928991948218</v>
       </c>
       <c r="CM40" t="n">
-        <v>23.9382962077995</v>
+        <v>23.93829599200825</v>
       </c>
       <c r="CN40" t="inlineStr">
         <is>
@@ -25388,37 +25388,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX41" t="n">
-        <v>16.91883609990701</v>
+        <v>16.91883610520417</v>
       </c>
       <c r="BY41" t="n">
-        <v>28.00431313303428</v>
+        <v>28.00431313367254</v>
       </c>
       <c r="BZ41" t="n">
-        <v>46.8316833394007</v>
+        <v>46.83168332580541</v>
       </c>
       <c r="CA41" t="n">
         <v>52.67243426197095</v>
       </c>
       <c r="CB41" t="n">
-        <v>55.69855923579338</v>
+        <v>55.69855923746945</v>
       </c>
       <c r="CC41" t="n">
-        <v>43.0354442939745</v>
+        <v>43.03544429300022</v>
       </c>
       <c r="CD41" t="n">
-        <v>23.30397203130465</v>
+        <v>23.30397202537988</v>
       </c>
       <c r="CE41" t="n">
         <v>30.43448362223624</v>
       </c>
       <c r="CF41" t="n">
-        <v>37.11246575220272</v>
+        <v>37.11246575059236</v>
       </c>
       <c r="CG41" t="n">
-        <v>36.73496395810537</v>
+        <v>36.73496395761823</v>
       </c>
       <c r="CH41" t="n">
-        <v>33.06146756229483</v>
+        <v>33.06146756185641</v>
       </c>
       <c r="CI41" t="n">
         <v>8</v>
@@ -25430,10 +25430,10 @@
         <v>3.3</v>
       </c>
       <c r="CL41" t="n">
-        <v>24.94886132364256</v>
+        <v>24.94886132198564</v>
       </c>
       <c r="CM41" t="n">
-        <v>40.25875675098256</v>
+        <v>40.25875674489654</v>
       </c>
       <c r="CN41" t="inlineStr">
         <is>
@@ -25716,37 +25716,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX42" t="n">
-        <v>5.939526962110235</v>
+        <v>5.939526969706941</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.534880609653715</v>
+        <v>8.534880603381971</v>
       </c>
       <c r="BZ42" t="n">
-        <v>10.81501546646275</v>
+        <v>10.81501544468299</v>
       </c>
       <c r="CA42" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB42" t="n">
-        <v>9.810403816800907</v>
+        <v>9.810403804551399</v>
       </c>
       <c r="CC42" t="n">
-        <v>14.90925678154334</v>
+        <v>14.90925677887778</v>
       </c>
       <c r="CD42" t="n">
-        <v>5.384140043226401</v>
+        <v>5.384140030925815</v>
       </c>
       <c r="CE42" t="n">
         <v>11.00534556207784</v>
       </c>
       <c r="CF42" t="n">
-        <v>9.757252269237304</v>
+        <v>9.757252263278495</v>
       </c>
       <c r="CG42" t="n">
-        <v>10.31270964163183</v>
+        <v>10.31270962461719</v>
       </c>
       <c r="CH42" t="n">
-        <v>9.281438677468648</v>
+        <v>9.281438662155473</v>
       </c>
       <c r="CI42" t="n">
         <v>8</v>
@@ -25758,10 +25758,10 @@
         <v>2.8</v>
       </c>
       <c r="CL42" t="n">
-        <v>-39.37662689037982</v>
+        <v>-39.37662699040055</v>
       </c>
       <c r="CM42" t="n">
-        <v>-36.26876550091181</v>
+        <v>-36.26876553983283</v>
       </c>
       <c r="CN42" t="inlineStr">
         <is>
@@ -26048,10 +26048,10 @@
         <v>9.25</v>
       </c>
       <c r="BX43" t="n">
-        <v>2.521670926061534</v>
+        <v>2.521670929592308</v>
       </c>
       <c r="BY43" t="n">
-        <v>4.677699567844145</v>
+        <v>4.677699574393731</v>
       </c>
       <c r="BZ43" t="n">
         <v>13.54281767955801</v>
@@ -26060,19 +26060,19 @@
         <v>15.28931421405346</v>
       </c>
       <c r="CB43" t="n">
-        <v>10.60496388844148</v>
+        <v>10.60496388895048</v>
       </c>
       <c r="CC43" t="n">
-        <v>7.31063985005142</v>
+        <v>7.31063984971896</v>
       </c>
       <c r="CD43" t="n">
-        <v>6.944431460021301</v>
+        <v>6.944431456908005</v>
       </c>
       <c r="CE43" t="n">
         <v>10.29452216806777</v>
       </c>
       <c r="CF43" t="n">
-        <v>9.80919840400537</v>
+        <v>9.80919840452149</v>
       </c>
       <c r="CG43" t="n">
         <v>10.29452216806777</v>
@@ -26093,7 +26093,7 @@
         <v>0.1629183920107247</v>
       </c>
       <c r="CM43" t="n">
-        <v>6.045388151409403</v>
+        <v>6.045388156989095</v>
       </c>
       <c r="CN43" t="inlineStr">
         <is>
@@ -26372,10 +26372,10 @@
         <v>11.76000022888184</v>
       </c>
       <c r="BX44" t="n">
-        <v>4.779815380923924</v>
+        <v>4.779815368453594</v>
       </c>
       <c r="BY44" t="n">
-        <v>8.866557531613877</v>
+        <v>8.866557508481415</v>
       </c>
       <c r="BZ44" t="n">
         <v>25.84079652283322</v>
@@ -26384,25 +26384,25 @@
         <v>29.08539831347033</v>
       </c>
       <c r="CB44" t="n">
-        <v>24.1003230826931</v>
+        <v>24.10032307146077</v>
       </c>
       <c r="CC44" t="n">
-        <v>14.25753217718242</v>
+        <v>14.25753217839691</v>
       </c>
       <c r="CD44" t="n">
-        <v>13.38320655875835</v>
+        <v>13.38320656989685</v>
       </c>
       <c r="CE44" t="n">
         <v>4.91926228677063</v>
       </c>
       <c r="CF44" t="n">
-        <v>19.25563569775855</v>
+        <v>19.25563569408991</v>
       </c>
       <c r="CG44" t="n">
-        <v>19.17892762993776</v>
+        <v>19.17892762492884</v>
       </c>
       <c r="CH44" t="n">
-        <v>17.26103486694398</v>
+        <v>17.26103486243596</v>
       </c>
       <c r="CI44" t="n">
         <v>6</v>
@@ -26414,10 +26414,10 @@
         <v>6.1</v>
       </c>
       <c r="CL44" t="n">
-        <v>46.77750451528006</v>
+        <v>46.7775044769465</v>
       </c>
       <c r="CM44" t="n">
-        <v>63.73839560366581</v>
+        <v>63.73839557246996</v>
       </c>
       <c r="CN44" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>4.347823879462331</v>
       </c>
       <c r="CZ44" t="n">
-        <v>-28.48247563627588</v>
+        <v>-28.48248018644097</v>
       </c>
       <c r="DA44" t="b">
         <v>0</v>
@@ -26696,37 +26696,37 @@
         <v>38.86000061035156</v>
       </c>
       <c r="BX45" t="n">
-        <v>30.97422560804202</v>
+        <v>30.97422553975776</v>
       </c>
       <c r="BY45" t="n">
-        <v>35.52640282107112</v>
+        <v>35.52640287414108</v>
       </c>
       <c r="BZ45" t="n">
-        <v>38.58971732768785</v>
+        <v>38.58971747040682</v>
       </c>
       <c r="CA45" t="n">
         <v>49.80959882281965</v>
       </c>
       <c r="CB45" t="n">
-        <v>60.09290023981547</v>
+        <v>60.09290031647345</v>
       </c>
       <c r="CC45" t="n">
-        <v>16.76379308121115</v>
+        <v>16.76379308795554</v>
       </c>
       <c r="CD45" t="n">
-        <v>17.31674446170541</v>
+        <v>17.31674458272697</v>
       </c>
       <c r="CE45" t="n">
         <v>28.40888631687585</v>
       </c>
       <c r="CF45" t="n">
-        <v>34.68528358490357</v>
+        <v>34.68528362639464</v>
       </c>
       <c r="CG45" t="n">
-        <v>33.25031421455657</v>
+        <v>33.25031420694942</v>
       </c>
       <c r="CH45" t="n">
-        <v>29.92528279310091</v>
+        <v>29.92528278625448</v>
       </c>
       <c r="CI45" t="n">
         <v>8</v>
@@ -26738,10 +26738,10 @@
         <v>3.6</v>
       </c>
       <c r="CL45" t="n">
-        <v>-22.99206813411787</v>
+        <v>-22.99206815173607</v>
       </c>
       <c r="CM45" t="n">
-        <v>-10.74296695799828</v>
+        <v>-10.74296685122762</v>
       </c>
       <c r="CN45" t="inlineStr">
         <is>
@@ -27024,10 +27024,10 @@
         <v>34.09000015258789</v>
       </c>
       <c r="BX46" t="n">
-        <v>14.76402957549056</v>
+        <v>14.76402959169838</v>
       </c>
       <c r="BY46" t="n">
-        <v>27.38727486253499</v>
+        <v>27.38727489260049</v>
       </c>
       <c r="BZ46" t="n">
         <v>56.67409059244536</v>
@@ -27036,25 +27036,25 @@
         <v>43.80170806643823</v>
       </c>
       <c r="CB46" t="n">
-        <v>73.43420502770878</v>
+        <v>73.43420500741638</v>
       </c>
       <c r="CC46" t="n">
-        <v>38.47788655595097</v>
+        <v>38.47788655200277</v>
       </c>
       <c r="CD46" t="n">
-        <v>41.28355409419013</v>
+        <v>41.28355406353919</v>
       </c>
       <c r="CE46" t="n">
         <v>21.79677261947583</v>
       </c>
       <c r="CF46" t="n">
-        <v>43.26507025982061</v>
+        <v>43.26507025627404</v>
       </c>
       <c r="CG46" t="n">
-        <v>41.28355409419013</v>
+        <v>41.28355406353919</v>
       </c>
       <c r="CH46" t="n">
-        <v>37.15519868477111</v>
+        <v>37.15519865718527</v>
       </c>
       <c r="CI46" t="n">
         <v>7</v>
@@ -27066,10 +27066,10 @@
         <v>5</v>
       </c>
       <c r="CL46" t="n">
-        <v>8.991488760525957</v>
+        <v>8.991488679605331</v>
       </c>
       <c r="CM46" t="n">
-        <v>26.91425657425879</v>
+        <v>26.91425656385524</v>
       </c>
       <c r="CN46" t="inlineStr">
         <is>
@@ -27346,10 +27346,10 @@
         <v>6.400000095367432</v>
       </c>
       <c r="BX47" t="n">
-        <v>7.601720069726899</v>
+        <v>7.601720118418401</v>
       </c>
       <c r="BY47" t="n">
-        <v>11.06810442152237</v>
+        <v>11.06810449241719</v>
       </c>
       <c r="BZ47" t="n">
         <v>7.942720882078913</v>
@@ -27368,7 +27368,7 @@
         <v>5.254390410546408</v>
       </c>
       <c r="CF47" t="n">
-        <v>8.250643825570098</v>
+        <v>8.250643845501154</v>
       </c>
       <c r="CG47" t="n">
         <v>8.296106057582163</v>
@@ -27389,7 +27389,7 @@
         <v>16.66398969632026</v>
       </c>
       <c r="CM47" t="n">
-        <v>28.9163078535301</v>
+        <v>28.91630816495283</v>
       </c>
       <c r="CN47" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>1</v>
       </c>
       <c r="AT48" t="n">
-        <v>185049546752</v>
+        <v>184726978560</v>
       </c>
       <c r="AU48" t="n">
         <v>7.27</v>
@@ -27654,35 +27654,35 @@
         <v>16.78000068664551</v>
       </c>
       <c r="BX48" t="n">
-        <v>9.985664045721835</v>
+        <v>9.985664042179227</v>
       </c>
       <c r="BY48" t="n">
-        <v>17.51097130396708</v>
+        <v>17.51097130456651</v>
       </c>
       <c r="BZ48" t="n">
-        <v>28.91098000544013</v>
+        <v>28.91098001668654</v>
       </c>
       <c r="CA48" t="n">
         <v>29.08689850705222</v>
       </c>
       <c r="CB48" t="n">
-        <v>32.0896477399672</v>
+        <v>32.0896477401531</v>
       </c>
       <c r="CC48" t="n">
-        <v>27.89695682918288</v>
+        <v>27.8969568299852</v>
       </c>
       <c r="CD48" t="n">
-        <v>14.2494155930414</v>
+        <v>14.24941559744642</v>
       </c>
       <c r="CE48" t="inlineStr"/>
       <c r="CF48" t="n">
-        <v>21.07614304607798</v>
+        <v>21.07614304835437</v>
       </c>
       <c r="CG48" t="n">
-        <v>22.70396406657498</v>
+        <v>22.70396406727586</v>
       </c>
       <c r="CH48" t="n">
-        <v>20.43356765991748</v>
+        <v>20.43356766054827</v>
       </c>
       <c r="CI48" t="n">
         <v>4</v>
@@ -27694,10 +27694,10 @@
         <v>2.9</v>
       </c>
       <c r="CL48" t="n">
-        <v>21.77334221553217</v>
+        <v>21.77334221929135</v>
       </c>
       <c r="CM48" t="n">
-        <v>25.60275437206383</v>
+        <v>25.60275438562989</v>
       </c>
       <c r="CN48" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>-7.744448996751174</v>
       </c>
       <c r="CZ48" t="n">
-        <v>-20.99430923793453</v>
+        <v>-20.99430199889827</v>
       </c>
       <c r="DA48" t="b">
         <v>1</v>
@@ -27980,10 +27980,10 @@
         <v>12.96000003814697</v>
       </c>
       <c r="BX49" t="n">
-        <v>1.59567901658905</v>
+        <v>1.595679008623957</v>
       </c>
       <c r="BY49" t="n">
-        <v>2.959984575772688</v>
+        <v>2.95998456099744</v>
       </c>
       <c r="BZ49" t="n">
         <v>12.85329345100654</v>
@@ -27992,7 +27992,7 @@
         <v>9.387296094048613</v>
       </c>
       <c r="CB49" t="n">
-        <v>16.22301697638109</v>
+        <v>16.22301696803443</v>
       </c>
       <c r="CC49" t="n">
         <v>6.104046666666666</v>
@@ -28050,7 +28050,7 @@
         <v>-13.54235999978114</v>
       </c>
       <c r="CZ49" t="n">
-        <v>-28.70447669205222</v>
+        <v>-28.7044691786816</v>
       </c>
       <c r="DA49" t="b">
         <v>0</v>
@@ -28294,10 +28294,10 @@
         <v>32.65999984741211</v>
       </c>
       <c r="BX50" t="n">
-        <v>11.0979994128159</v>
+        <v>11.09799943479086</v>
       </c>
       <c r="BY50" t="n">
-        <v>20.58678891077349</v>
+        <v>20.58678895153704</v>
       </c>
       <c r="BZ50" t="n">
         <v>55.48012794592442</v>
@@ -28306,19 +28306,19 @@
         <v>52.41446107539311</v>
       </c>
       <c r="CB50" t="n">
-        <v>57.7886344520176</v>
+        <v>57.78863444721983</v>
       </c>
       <c r="CC50" t="n">
-        <v>28.23732416744662</v>
+        <v>28.23732422062287</v>
       </c>
       <c r="CD50" t="n">
-        <v>34.98921552583134</v>
+        <v>34.98921549802334</v>
       </c>
       <c r="CE50" t="n">
         <v>54.03219538348082</v>
       </c>
       <c r="CF50" t="n">
-        <v>43.36124963726677</v>
+        <v>43.36124964602878</v>
       </c>
       <c r="CG50" t="n">
         <v>52.41446107539311</v>
@@ -28339,7 +28339,7 @@
         <v>44.43666622243312</v>
       </c>
       <c r="CM50" t="n">
-        <v>32.76561494136872</v>
+        <v>32.76561496819668</v>
       </c>
       <c r="CN50" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>-0.2500150878204321</v>
       </c>
       <c r="CZ50" t="n">
-        <v>-10.82896174015665</v>
+        <v>-10.82895234146481</v>
       </c>
       <c r="DA50" t="b">
         <v>0</v>
@@ -28618,37 +28618,37 @@
         <v>44.2400016784668</v>
       </c>
       <c r="BX51" t="n">
-        <v>32.08627715399735</v>
+        <v>32.08627719702323</v>
       </c>
       <c r="BY51" t="n">
-        <v>44.20766650010867</v>
+        <v>44.20766641689121</v>
       </c>
       <c r="BZ51" t="n">
-        <v>50.92127217168321</v>
+        <v>50.92127200754537</v>
       </c>
       <c r="CA51" t="n">
         <v>47.73853825853298</v>
       </c>
       <c r="CB51" t="n">
-        <v>70.56922563943867</v>
+        <v>70.56922555068604</v>
       </c>
       <c r="CC51" t="n">
-        <v>59.89362087737182</v>
+        <v>59.893620859564</v>
       </c>
       <c r="CD51" t="n">
-        <v>25.15601716385589</v>
+        <v>25.15601706378459</v>
       </c>
       <c r="CE51" t="n">
         <v>76.57366731847841</v>
       </c>
       <c r="CF51" t="n">
-        <v>50.89328563543337</v>
+        <v>50.89328558406323</v>
       </c>
       <c r="CG51" t="n">
-        <v>49.32990521510809</v>
+        <v>49.32990513303918</v>
       </c>
       <c r="CH51" t="n">
-        <v>44.39691469359728</v>
+        <v>44.39691461973526</v>
       </c>
       <c r="CI51" t="n">
         <v>8</v>
@@ -28660,10 +28660,10 @@
         <v>3</v>
       </c>
       <c r="CL51" t="n">
-        <v>0.3546858254457552</v>
+        <v>0.3546856584882185</v>
       </c>
       <c r="CM51" t="n">
-        <v>15.03906804823874</v>
+        <v>15.03906793212177</v>
       </c>
       <c r="CN51" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>1</v>
       </c>
       <c r="AT52" t="n">
-        <v>3043409408</v>
+        <v>3038503936</v>
       </c>
       <c r="AU52" t="n">
         <v>6.1</v>
@@ -28946,37 +28946,37 @@
         <v>10.59000015258789</v>
       </c>
       <c r="BX52" t="n">
-        <v>8.101227394387069</v>
+        <v>8.101227402681777</v>
       </c>
       <c r="BY52" t="n">
-        <v>11.67224168392359</v>
+        <v>11.67224168632088</v>
       </c>
       <c r="BZ52" t="n">
-        <v>17.8665847793126</v>
+        <v>17.86658476468881</v>
       </c>
       <c r="CA52" t="n">
         <v>24.4848677465562</v>
       </c>
       <c r="CB52" t="n">
-        <v>25.37030468295685</v>
+        <v>25.37030468891811</v>
       </c>
       <c r="CC52" t="n">
-        <v>21.06883213188546</v>
+        <v>21.06883213035821</v>
       </c>
       <c r="CD52" t="n">
-        <v>8.89780733137499</v>
+        <v>8.897807323155927</v>
       </c>
       <c r="CE52" t="n">
         <v>10.22838513722926</v>
       </c>
       <c r="CF52" t="n">
-        <v>15.96128136095325</v>
+        <v>15.96128135998865</v>
       </c>
       <c r="CG52" t="n">
-        <v>14.7694132316181</v>
+        <v>14.76941322550484</v>
       </c>
       <c r="CH52" t="n">
-        <v>13.29247190845629</v>
+        <v>13.29247190295436</v>
       </c>
       <c r="CI52" t="n">
         <v>8</v>
@@ -28988,10 +28988,10 @@
         <v>3.1</v>
       </c>
       <c r="CL52" t="n">
-        <v>25.51909081141979</v>
+        <v>25.51909075946577</v>
       </c>
       <c r="CM52" t="n">
-        <v>50.72031285148544</v>
+        <v>50.72031284237677</v>
       </c>
       <c r="CN52" t="inlineStr">
         <is>
@@ -29256,10 +29256,10 @@
         <v>54.20000076293945</v>
       </c>
       <c r="BX53" t="n">
-        <v>10.59687590534817</v>
+        <v>10.5968759006117</v>
       </c>
       <c r="BY53" t="n">
-        <v>19.65720480442086</v>
+        <v>19.6572047956347</v>
       </c>
       <c r="BZ53" t="n">
         <v>62.12370329662177</v>
@@ -29268,7 +29268,7 @@
         <v>46.53820959650967</v>
       </c>
       <c r="CB53" t="n">
-        <v>83.16230744973755</v>
+        <v>83.16230744400134</v>
       </c>
       <c r="CC53" t="n">
         <v>11.76833333333333</v>
@@ -29278,7 +29278,7 @@
       </c>
       <c r="CE53" t="inlineStr"/>
       <c r="CF53" t="n">
-        <v>14.00747134770079</v>
+        <v>14.00747134319324</v>
       </c>
       <c r="CG53" t="n">
         <v>11.76833333333333</v>
@@ -29299,7 +29299,7 @@
         <v>-80.45848735994448</v>
       </c>
       <c r="CM53" t="n">
-        <v>-74.15595728685167</v>
+        <v>-74.15595729516818</v>
       </c>
       <c r="CN53" t="inlineStr">
         <is>
@@ -29564,10 +29564,10 @@
         <v>29.69000053405762</v>
       </c>
       <c r="BX54" t="n">
-        <v>15.52022458567649</v>
+        <v>15.52022462881667</v>
       </c>
       <c r="BY54" t="n">
-        <v>28.79001660642989</v>
+        <v>28.79001668645492</v>
       </c>
       <c r="BZ54" t="n">
         <v>54.71383964899351</v>
@@ -29576,23 +29576,23 @@
         <v>49.40805952371795</v>
       </c>
       <c r="CB54" t="n">
-        <v>60.91790646631788</v>
+        <v>60.9179064555565</v>
       </c>
       <c r="CC54" t="n">
-        <v>36.63500708552354</v>
+        <v>36.63500707769816</v>
       </c>
       <c r="CD54" t="n">
-        <v>30.32696333156444</v>
+        <v>30.32696327199993</v>
       </c>
       <c r="CE54" t="inlineStr"/>
       <c r="CF54" t="n">
-        <v>33.91477198165586</v>
+        <v>33.91477201049081</v>
       </c>
       <c r="CG54" t="n">
-        <v>32.71251184597671</v>
+        <v>32.71251188207653</v>
       </c>
       <c r="CH54" t="n">
-        <v>29.44126066137904</v>
+        <v>29.44126069386888</v>
       </c>
       <c r="CI54" t="n">
         <v>4</v>
@@ -29604,10 +29604,10 @@
         <v>3.5</v>
       </c>
       <c r="CL54" t="n">
-        <v>-0.8377900579464193</v>
+        <v>-0.8377899485161877</v>
       </c>
       <c r="CM54" t="n">
-        <v>14.22961054767235</v>
+        <v>14.22961064479244</v>
       </c>
       <c r="CN54" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>-0.8018702595090188</v>
       </c>
       <c r="CZ54" t="n">
-        <v>-18.56623828442452</v>
+        <v>-18.56622956112421</v>
       </c>
       <c r="DA54" t="b">
         <v>1</v>
@@ -29804,7 +29804,7 @@
         <v>1</v>
       </c>
       <c r="AT55" t="n">
-        <v>35655647232</v>
+        <v>35602051072</v>
       </c>
       <c r="AU55" t="n">
         <v>10.8</v>
@@ -29894,10 +29894,10 @@
         <v>33.61999893188477</v>
       </c>
       <c r="BX55" t="n">
-        <v>11.88440178686683</v>
+        <v>11.88440174707618</v>
       </c>
       <c r="BY55" t="n">
-        <v>22.04556531463798</v>
+        <v>22.04556524082631</v>
       </c>
       <c r="BZ55" t="n">
         <v>41.2467579488401</v>
@@ -29906,25 +29906,25 @@
         <v>33.64692724932318</v>
       </c>
       <c r="CB55" t="n">
-        <v>43.30177833762696</v>
+        <v>43.3017783932823</v>
       </c>
       <c r="CC55" t="n">
-        <v>23.86565137002273</v>
+        <v>23.86565137756786</v>
       </c>
       <c r="CD55" t="n">
-        <v>25.85073196506986</v>
+        <v>25.85073203247523</v>
       </c>
       <c r="CE55" t="n">
         <v>27.17936043616258</v>
       </c>
       <c r="CF55" t="n">
-        <v>28.62764680106878</v>
+        <v>28.62764680319422</v>
       </c>
       <c r="CG55" t="n">
-        <v>26.51504620061622</v>
+        <v>26.5150462343189</v>
       </c>
       <c r="CH55" t="n">
-        <v>23.8635415805546</v>
+        <v>23.86354161088701</v>
       </c>
       <c r="CI55" t="n">
         <v>8</v>
@@ -29936,10 +29936,10 @@
         <v>3.6</v>
       </c>
       <c r="CL55" t="n">
-        <v>-29.01980268083016</v>
+        <v>-29.01980259060882</v>
       </c>
       <c r="CM55" t="n">
-        <v>-14.84935243731167</v>
+        <v>-14.84935243098971</v>
       </c>
       <c r="CN55" t="inlineStr">
         <is>
@@ -30216,10 +30216,10 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX56" t="n">
-        <v>13.08696646023153</v>
+        <v>13.08696643078177</v>
       </c>
       <c r="BY56" t="n">
-        <v>19.0546231660971</v>
+        <v>19.05462312321825</v>
       </c>
       <c r="BZ56" t="n">
         <v>16.71315021106592</v>
@@ -30238,7 +30238,7 @@
         <v>14.7644299189986</v>
       </c>
       <c r="CF56" t="n">
-        <v>16.15917316136627</v>
+        <v>16.1591731493115</v>
       </c>
       <c r="CG56" t="n">
         <v>15.73879006503226</v>
@@ -30259,7 +30259,7 @@
         <v>34.77555423456011</v>
       </c>
       <c r="CM56" t="n">
-        <v>53.7504548949515</v>
+        <v>53.7504547802534</v>
       </c>
       <c r="CN56" t="inlineStr">
         <is>
@@ -30540,10 +30540,10 @@
         <v>4.639999866485596</v>
       </c>
       <c r="BX57" t="n">
-        <v>1.073494103516816</v>
+        <v>1.073494105837267</v>
       </c>
       <c r="BY57" t="n">
-        <v>1.991331562023693</v>
+        <v>1.99133156632813</v>
       </c>
       <c r="BZ57" t="n">
         <v>9.429447581431615</v>
@@ -30552,13 +30552,13 @@
         <v>8.84348872808631</v>
       </c>
       <c r="CB57" t="n">
-        <v>10.45610111131063</v>
+        <v>10.45610111157618</v>
       </c>
       <c r="CC57" t="n">
-        <v>4.222542560421149</v>
+        <v>4.222542560170031</v>
       </c>
       <c r="CD57" t="n">
-        <v>7.024657962487384</v>
+        <v>7.024657959522403</v>
       </c>
       <c r="CE57" t="n">
         <v>6.880721573088802</v>
@@ -30610,7 +30610,7 @@
         <v>7.906968852776419</v>
       </c>
       <c r="CZ57" t="n">
-        <v>-35.92780109506861</v>
+        <v>-35.92779681249883</v>
       </c>
       <c r="DA57" t="b">
         <v>0</v>
@@ -30850,10 +30850,10 @@
         <v>24.32999992370605</v>
       </c>
       <c r="BX58" t="n">
-        <v>4.265826971582199</v>
+        <v>4.265826977744358</v>
       </c>
       <c r="BY58" t="n">
-        <v>7.91310903228498</v>
+        <v>7.913109043715785</v>
       </c>
       <c r="BZ58" t="n">
         <v>28.32798760888446</v>
@@ -30862,13 +30862,13 @@
         <v>28.21652766068684</v>
       </c>
       <c r="CB58" t="n">
-        <v>25.16978179246282</v>
+        <v>25.16978178888895</v>
       </c>
       <c r="CC58" t="n">
-        <v>2.969809686291547</v>
+        <v>2.969809686149806</v>
       </c>
       <c r="CD58" t="n">
-        <v>18.233710407181</v>
+        <v>18.23371040016945</v>
       </c>
       <c r="CE58" t="n">
         <v>18.22960446774209</v>
@@ -31068,7 +31068,7 @@
         <v>1</v>
       </c>
       <c r="AR59" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="AS59" t="b">
         <v>1</v>
@@ -31164,10 +31164,10 @@
         <v>49.58000183105469</v>
       </c>
       <c r="BX59" t="n">
-        <v>8.25200271076403</v>
+        <v>8.25200269479908</v>
       </c>
       <c r="BY59" t="n">
-        <v>15.30746502846728</v>
+        <v>15.30746499885229</v>
       </c>
       <c r="BZ59" t="n">
         <v>19.41297353018541</v>
@@ -31176,25 +31176,25 @@
         <v>12.06941420422284</v>
       </c>
       <c r="CB59" t="n">
-        <v>13.68856510575207</v>
+        <v>13.68856517326287</v>
       </c>
       <c r="CC59" t="n">
-        <v>20.60981125429353</v>
+        <v>20.60981126403607</v>
       </c>
       <c r="CD59" t="n">
-        <v>10.37232040376443</v>
+        <v>10.37232045035143</v>
       </c>
       <c r="CE59" t="n">
         <v>12.92608390047425</v>
       </c>
       <c r="CF59" t="n">
-        <v>14.07982951724048</v>
+        <v>14.07982952702303</v>
       </c>
       <c r="CG59" t="n">
-        <v>13.30732450311316</v>
+        <v>13.30732453686856</v>
       </c>
       <c r="CH59" t="n">
-        <v>11.97659205280184</v>
+        <v>11.9765920831817</v>
       </c>
       <c r="CI59" t="n">
         <v>8</v>
@@ -31206,10 +31206,10 @@
         <v>2.5</v>
       </c>
       <c r="CL59" t="n">
-        <v>-75.84390558594082</v>
+        <v>-75.84390552466638</v>
       </c>
       <c r="CM59" t="n">
-        <v>-71.60179710114188</v>
+        <v>-71.60179708141105</v>
       </c>
       <c r="CN59" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>0.6291888987432825</v>
       </c>
       <c r="CZ59" t="n">
-        <v>-8.667879823856294</v>
+        <v>-8.667873268803072</v>
       </c>
       <c r="DA59" t="b">
         <v>0</v>
@@ -31500,37 +31500,37 @@
         <v>23.78000068664551</v>
       </c>
       <c r="BX60" t="n">
-        <v>10.50498166312909</v>
+        <v>10.50498160392796</v>
       </c>
       <c r="BY60" t="n">
-        <v>14.29883865790862</v>
+        <v>14.29883869102245</v>
       </c>
       <c r="BZ60" t="n">
-        <v>17.83956633111738</v>
+        <v>17.83956647296637</v>
       </c>
       <c r="CA60" t="n">
         <v>21.12463825554054</v>
       </c>
       <c r="CB60" t="n">
-        <v>17.52809442092475</v>
+        <v>17.52809449762296</v>
       </c>
       <c r="CC60" t="n">
-        <v>23.23161878031145</v>
+        <v>23.23161879753909</v>
       </c>
       <c r="CD60" t="n">
-        <v>8.786388874011594</v>
+        <v>8.786388962420199</v>
       </c>
       <c r="CE60" t="n">
         <v>18.54956014100212</v>
       </c>
       <c r="CF60" t="n">
-        <v>16.48296089049319</v>
+        <v>16.48296092775521</v>
       </c>
       <c r="CG60" t="n">
-        <v>17.68383037602106</v>
+        <v>17.68383048529466</v>
       </c>
       <c r="CH60" t="n">
-        <v>15.91544733841896</v>
+        <v>15.9154474367652</v>
       </c>
       <c r="CI60" t="n">
         <v>8</v>
@@ -31542,10 +31542,10 @@
         <v>2.6</v>
       </c>
       <c r="CL60" t="n">
-        <v>-33.0721325531465</v>
+        <v>-33.07213213957948</v>
       </c>
       <c r="CM60" t="n">
-        <v>-30.68561642325865</v>
+        <v>-30.6856162665639</v>
       </c>
       <c r="CN60" t="inlineStr">
         <is>
@@ -31828,10 +31828,10 @@
         <v>4.519999980926514</v>
       </c>
       <c r="BX61" t="n">
-        <v>2.935043322074368</v>
+        <v>2.935043325145307</v>
       </c>
       <c r="BY61" t="n">
-        <v>5.444505362447952</v>
+        <v>5.444505368144545</v>
       </c>
       <c r="BZ61" t="n">
         <v>13.16263730709369</v>
@@ -31840,13 +31840,13 @@
         <v>14.66138724509534</v>
       </c>
       <c r="CB61" t="n">
-        <v>15.01900791745644</v>
+        <v>15.01900792248579</v>
       </c>
       <c r="CC61" t="n">
-        <v>9.454768183224612</v>
+        <v>9.454768182827884</v>
       </c>
       <c r="CD61" t="n">
-        <v>6.417766703642784</v>
+        <v>6.417766700864689</v>
       </c>
       <c r="CE61" t="n">
         <v>1.463859008533987</v>
@@ -32142,37 +32142,37 @@
         <v>30</v>
       </c>
       <c r="BX62" t="n">
-        <v>13.81421956339626</v>
+        <v>13.81421954786151</v>
       </c>
       <c r="BY62" t="n">
-        <v>14.42907655106563</v>
+        <v>14.42907654784607</v>
       </c>
       <c r="BZ62" t="n">
-        <v>15.22607860019891</v>
+        <v>15.22607861392396</v>
       </c>
       <c r="CA62" t="n">
         <v>30.50864986347318</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.22999674012103</v>
+        <v>14.22999674718342</v>
       </c>
       <c r="CC62" t="n">
-        <v>30.46475764652542</v>
+        <v>30.46475764977117</v>
       </c>
       <c r="CD62" t="n">
-        <v>6.126727541747511</v>
+        <v>6.126727555486439</v>
       </c>
       <c r="CE62" t="n">
         <v>37.56051795197769</v>
       </c>
       <c r="CF62" t="n">
-        <v>17.82850092950399</v>
+        <v>17.82850093222082</v>
       </c>
       <c r="CG62" t="n">
-        <v>14.42907655106563</v>
+        <v>14.42907654784607</v>
       </c>
       <c r="CH62" t="n">
-        <v>12.98616889595907</v>
+        <v>12.98616889306147</v>
       </c>
       <c r="CI62" t="n">
         <v>7</v>
@@ -32184,10 +32184,10 @@
         <v>6.1</v>
       </c>
       <c r="CL62" t="n">
-        <v>-56.71277034680309</v>
+        <v>-56.71277035646178</v>
       </c>
       <c r="CM62" t="n">
-        <v>-40.57166356832003</v>
+        <v>-40.57166355926392</v>
       </c>
       <c r="CN62" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>-5.213268999738752</v>
       </c>
       <c r="CZ62" t="n">
-        <v>-27.23199551707314</v>
+        <v>-27.23200907385727</v>
       </c>
       <c r="DA62" t="b">
         <v>0</v>
@@ -32466,35 +32466,35 @@
         <v>3.509999990463257</v>
       </c>
       <c r="BX63" t="n">
-        <v>2.694277176986419</v>
+        <v>2.694277163240034</v>
       </c>
       <c r="BY63" t="n">
-        <v>3.13628780818983</v>
+        <v>3.136287803684305</v>
       </c>
       <c r="BZ63" t="n">
-        <v>3.840069856430643</v>
+        <v>3.840069870506376</v>
       </c>
       <c r="CA63" t="n">
         <v>7.068546969028743</v>
       </c>
       <c r="CB63" t="n">
-        <v>5.776564273735336</v>
+        <v>5.776564266907434</v>
       </c>
       <c r="CC63" t="n">
-        <v>8.480104653831324</v>
+        <v>8.480104657168392</v>
       </c>
       <c r="CD63" t="n">
-        <v>1.745072087086637</v>
+        <v>1.74507209871168</v>
       </c>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="n">
-        <v>4.677274689326991</v>
+        <v>4.677274689892423</v>
       </c>
       <c r="CG63" t="n">
-        <v>3.840069856430643</v>
+        <v>3.840069870506376</v>
       </c>
       <c r="CH63" t="n">
-        <v>3.456062870787579</v>
+        <v>3.456062883455739</v>
       </c>
       <c r="CI63" t="n">
         <v>7</v>
@@ -32506,10 +32506,10 @@
         <v>4.9</v>
       </c>
       <c r="CL63" t="n">
-        <v>-1.536670080405311</v>
+        <v>-1.536669719489059</v>
       </c>
       <c r="CM63" t="n">
-        <v>33.25568951667361</v>
+        <v>33.2556895327828</v>
       </c>
       <c r="CN63" t="inlineStr">
         <is>
@@ -32788,37 +32788,37 @@
         <v>18.63999938964844</v>
       </c>
       <c r="BX64" t="n">
-        <v>8.745140358007564</v>
+        <v>8.745140376463256</v>
       </c>
       <c r="BY64" t="n">
-        <v>9.206222539254405</v>
+        <v>9.206222538315652</v>
       </c>
       <c r="BZ64" t="n">
-        <v>9.666395057448174</v>
+        <v>9.666395036062593</v>
       </c>
       <c r="CA64" t="n">
         <v>16.93457208699175</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.239151933083861</v>
+        <v>9.239151917313791</v>
       </c>
       <c r="CC64" t="n">
-        <v>17.54224666383774</v>
+        <v>17.5422466592823</v>
       </c>
       <c r="CD64" t="n">
-        <v>3.934238776984336</v>
+        <v>3.934238755871024</v>
       </c>
       <c r="CE64" t="n">
         <v>16.16233025852235</v>
       </c>
       <c r="CF64" t="n">
-        <v>11.42878720926627</v>
+        <v>11.42878720360284</v>
       </c>
       <c r="CG64" t="n">
-        <v>9.452773495266017</v>
+        <v>9.452773476688192</v>
       </c>
       <c r="CH64" t="n">
-        <v>8.507496145739415</v>
+        <v>8.507496129019373</v>
       </c>
       <c r="CI64" t="n">
         <v>8</v>
@@ -32830,10 +32830,10 @@
         <v>4.5</v>
       </c>
       <c r="CL64" t="n">
-        <v>-54.3589247622831</v>
+        <v>-54.35892485198291</v>
       </c>
       <c r="CM64" t="n">
-        <v>-38.68676189113424</v>
+        <v>-38.68676192151745</v>
       </c>
       <c r="CN64" t="inlineStr">
         <is>
@@ -33094,10 +33094,10 @@
         <v>12.85999965667725</v>
       </c>
       <c r="BX65" t="n">
-        <v>10.87454813936121</v>
+        <v>10.87454815147874</v>
       </c>
       <c r="BY65" t="n">
-        <v>15.83334209090992</v>
+        <v>15.83334210855304</v>
       </c>
       <c r="BZ65" t="n">
         <v>15.62429864829946</v>
@@ -33114,13 +33114,13 @@
       </c>
       <c r="CE65" t="inlineStr"/>
       <c r="CF65" t="n">
-        <v>12.41638055297598</v>
+        <v>12.41638056041614</v>
       </c>
       <c r="CG65" t="n">
-        <v>13.24942339383033</v>
+        <v>13.2494233998891</v>
       </c>
       <c r="CH65" t="n">
-        <v>11.9244810544473</v>
+        <v>11.92448105990019</v>
       </c>
       <c r="CI65" t="n">
         <v>4</v>
@@ -33132,10 +33132,10 @@
         <v>2.2</v>
       </c>
       <c r="CL65" t="n">
-        <v>-7.274639402841665</v>
+        <v>-7.27463936043975</v>
       </c>
       <c r="CM65" t="n">
-        <v>-3.449604319942001</v>
+        <v>-3.449604262086925</v>
       </c>
       <c r="CN65" t="inlineStr">
         <is>
@@ -33412,25 +33412,25 @@
         <v>2.170000076293945</v>
       </c>
       <c r="BX66" t="n">
-        <v>0.6228125133092667</v>
+        <v>0.6228125150460905</v>
       </c>
       <c r="BY66" t="n">
-        <v>0.8838074820951158</v>
+        <v>0.8838074842034851</v>
       </c>
       <c r="BZ66" t="n">
-        <v>3.35295880982668</v>
+        <v>3.352958808475015</v>
       </c>
       <c r="CA66" t="n">
         <v>6.892227907447849</v>
       </c>
       <c r="CB66" t="n">
-        <v>2.573963643861446</v>
+        <v>2.573963646325559</v>
       </c>
       <c r="CC66" t="n">
-        <v>2.231320701822876</v>
+        <v>2.231320701742102</v>
       </c>
       <c r="CD66" t="n">
-        <v>1.66612885939161</v>
+        <v>1.666128858610595</v>
       </c>
       <c r="CE66" t="n">
         <v>4.745898587185464</v>
@@ -33726,10 +33726,10 @@
         <v>36.06999969482422</v>
       </c>
       <c r="BX67" t="n">
-        <v>10.32734669248367</v>
+        <v>10.3273466514841</v>
       </c>
       <c r="BY67" t="n">
-        <v>19.15722811455722</v>
+        <v>19.15722803850301</v>
       </c>
       <c r="BZ67" t="n">
         <v>29.14192048514762</v>
@@ -33738,25 +33738,25 @@
         <v>21.64477052485838</v>
       </c>
       <c r="CB67" t="n">
-        <v>26.34387253525365</v>
+        <v>26.34387263376502</v>
       </c>
       <c r="CC67" t="n">
-        <v>22.88383980791708</v>
+        <v>22.88383982078307</v>
       </c>
       <c r="CD67" t="n">
-        <v>16.89301637787563</v>
+        <v>16.89301646179683</v>
       </c>
       <c r="CE67" t="n">
         <v>26.70821873920952</v>
       </c>
       <c r="CF67" t="n">
-        <v>21.63752665966285</v>
+        <v>21.63752666944345</v>
       </c>
       <c r="CG67" t="n">
-        <v>22.26430516638773</v>
+        <v>22.26430517282072</v>
       </c>
       <c r="CH67" t="n">
-        <v>20.03787464974896</v>
+        <v>20.03787465553865</v>
       </c>
       <c r="CI67" t="n">
         <v>8</v>
@@ -33768,10 +33768,10 @@
         <v>2.8</v>
       </c>
       <c r="CL67" t="n">
-        <v>-44.44725583786394</v>
+        <v>-44.44725582181267</v>
       </c>
       <c r="CM67" t="n">
-        <v>-40.01240132317585</v>
+        <v>-40.01240129606025</v>
       </c>
       <c r="CN67" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>4.42964313474894</v>
       </c>
       <c r="CZ67" t="n">
-        <v>-19.75884710571682</v>
+        <v>-19.75885395890232</v>
       </c>
       <c r="DA67" t="b">
         <v>0</v>
@@ -34054,10 +34054,10 @@
         <v>8.960000038146973</v>
       </c>
       <c r="BX68" t="n">
-        <v>0.5329545606120012</v>
+        <v>0.5329545608790383</v>
       </c>
       <c r="BY68" t="n">
-        <v>0.9886307099352621</v>
+        <v>0.9886307104306159</v>
       </c>
       <c r="BZ68" t="n">
         <v>10.10382983025084</v>
@@ -34066,13 +34066,13 @@
         <v>9.267312794547912</v>
       </c>
       <c r="CB68" t="n">
-        <v>11.09857033980587</v>
+        <v>11.09857033955541</v>
       </c>
       <c r="CC68" t="n">
-        <v>0.7358541828631348</v>
+        <v>0.7358541828583098</v>
       </c>
       <c r="CD68" t="n">
-        <v>8.614201657721731</v>
+        <v>8.614201657364308</v>
       </c>
       <c r="CE68" t="inlineStr"/>
       <c r="CF68" t="inlineStr"/>
@@ -34370,10 +34370,10 @@
         <v>8.510000228881836</v>
       </c>
       <c r="BX69" t="n">
-        <v>1.637947944939745</v>
+        <v>1.637947947346442</v>
       </c>
       <c r="BY69" t="n">
-        <v>3.038393437863226</v>
+        <v>3.038393442327651</v>
       </c>
       <c r="BZ69" t="n">
         <v>24.61954214687431</v>
@@ -34382,13 +34382,13 @@
         <v>24.35075698940731</v>
       </c>
       <c r="CB69" t="n">
-        <v>26.29479861904839</v>
+        <v>26.29479862200133</v>
       </c>
       <c r="CC69" t="n">
-        <v>6.709480300448409</v>
+        <v>6.709480300305735</v>
       </c>
       <c r="CD69" t="n">
-        <v>18.3447346426346</v>
+        <v>18.34473463986651</v>
       </c>
       <c r="CE69" t="n">
         <v>14.67770218220867</v>
@@ -34684,10 +34684,10 @@
         <v>21.79999923706055</v>
       </c>
       <c r="BX70" t="n">
-        <v>6.028554337916608</v>
+        <v>6.028554339175082</v>
       </c>
       <c r="BY70" t="n">
-        <v>11.18296829683531</v>
+        <v>11.18296829916978</v>
       </c>
       <c r="BZ70" t="n">
         <v>32.56482411398559</v>
@@ -34696,25 +34696,25 @@
         <v>33.56557093257108</v>
       </c>
       <c r="CB70" t="n">
-        <v>29.04126497177954</v>
+        <v>29.04126497163401</v>
       </c>
       <c r="CC70" t="n">
-        <v>25.18528583189161</v>
+        <v>25.18528583168923</v>
       </c>
       <c r="CD70" t="n">
-        <v>18.83916134379097</v>
+        <v>18.83916134245095</v>
       </c>
       <c r="CE70" t="n">
         <v>13.17078629161308</v>
       </c>
       <c r="CF70" t="n">
-        <v>23.36426596892388</v>
+        <v>23.36426596901625</v>
       </c>
       <c r="CG70" t="n">
-        <v>25.18528583189161</v>
+        <v>25.18528583168923</v>
       </c>
       <c r="CH70" t="n">
-        <v>22.66675724870245</v>
+        <v>22.66675724852031</v>
       </c>
       <c r="CI70" t="n">
         <v>7</v>
@@ -34726,10 +34726,10 @@
         <v>5.6</v>
       </c>
       <c r="CL70" t="n">
-        <v>3.975954320990938</v>
+        <v>3.975954320155428</v>
       </c>
       <c r="CM70" t="n">
-        <v>7.17553571838685</v>
+        <v>7.175535718810533</v>
       </c>
       <c r="CN70" t="inlineStr">
         <is>
@@ -35008,25 +35008,25 @@
         <v>17.30999946594238</v>
       </c>
       <c r="BX71" t="n">
-        <v>4.028449923961087</v>
+        <v>4.028450003398035</v>
       </c>
       <c r="BY71" t="n">
-        <v>6.904966282653684</v>
+        <v>6.904966380176691</v>
       </c>
       <c r="BZ71" t="n">
-        <v>23.39184157089357</v>
+        <v>23.39184144000728</v>
       </c>
       <c r="CA71" t="n">
         <v>32.83973692061836</v>
       </c>
       <c r="CB71" t="n">
-        <v>16.52656709058938</v>
+        <v>16.52656712826266</v>
       </c>
       <c r="CC71" t="n">
-        <v>20.29662203773423</v>
+        <v>20.29662202915872</v>
       </c>
       <c r="CD71" t="n">
-        <v>11.57930534841335</v>
+        <v>11.5793052949364</v>
       </c>
       <c r="CE71" t="n">
         <v>22.32522379682559</v>
@@ -35078,7 +35078,7 @@
         <v>-1.364797304640797</v>
       </c>
       <c r="CZ71" t="n">
-        <v>-40.04429185860444</v>
+        <v>-40.0442878378096</v>
       </c>
       <c r="DA71" t="b">
         <v>0</v>
@@ -35322,35 +35322,35 @@
         <v>23.89999961853027</v>
       </c>
       <c r="BX72" t="n">
-        <v>22.96133592951301</v>
+        <v>22.96133605045733</v>
       </c>
       <c r="BY72" t="n">
-        <v>28.91661738030071</v>
+        <v>28.91661741337681</v>
       </c>
       <c r="BZ72" t="n">
-        <v>38.25461881559702</v>
+        <v>38.25461865785567</v>
       </c>
       <c r="CA72" t="n">
         <v>61.73697842188816</v>
       </c>
       <c r="CB72" t="n">
-        <v>68.23386850994055</v>
+        <v>68.23386863123601</v>
       </c>
       <c r="CC72" t="n">
-        <v>41.71087888997986</v>
+        <v>41.71087887277269</v>
       </c>
       <c r="CD72" t="n">
-        <v>18.29686833051155</v>
+        <v>18.2968682173754</v>
       </c>
       <c r="CE72" t="inlineStr"/>
       <c r="CF72" t="n">
-        <v>40.01588089681869</v>
+        <v>40.01588089499457</v>
       </c>
       <c r="CG72" t="n">
-        <v>38.25461881559702</v>
+        <v>38.25461865785567</v>
       </c>
       <c r="CH72" t="n">
-        <v>34.42915693403732</v>
+        <v>34.4291567920701</v>
       </c>
       <c r="CI72" t="n">
         <v>7</v>
@@ -35362,10 +35362,10 @@
         <v>3.7</v>
       </c>
       <c r="CL72" t="n">
-        <v>44.05505223248423</v>
+        <v>44.05505163847914</v>
       </c>
       <c r="CM72" t="n">
-        <v>67.43046667579597</v>
+        <v>67.43046666816367</v>
       </c>
       <c r="CN72" t="inlineStr">
         <is>
@@ -35648,10 +35648,10 @@
         <v>24.69000053405762</v>
       </c>
       <c r="BX73" t="n">
-        <v>4.528795226970716</v>
+        <v>4.528795224611128</v>
       </c>
       <c r="BY73" t="n">
-        <v>8.400915146030677</v>
+        <v>8.400915141653641</v>
       </c>
       <c r="BZ73" t="n">
         <v>29.76728908792206</v>
@@ -35660,19 +35660,19 @@
         <v>25.23396384622111</v>
       </c>
       <c r="CB73" t="n">
-        <v>34.47267201994089</v>
+        <v>34.47267202281515</v>
       </c>
       <c r="CC73" t="n">
-        <v>11.78156829073316</v>
+        <v>11.78156829100659</v>
       </c>
       <c r="CD73" t="n">
-        <v>24.04380283636739</v>
+        <v>24.04380284006345</v>
       </c>
       <c r="CE73" t="n">
         <v>24.69000053405762</v>
       </c>
       <c r="CF73" t="n">
-        <v>24.99821610254037</v>
+        <v>24.99821610368099</v>
       </c>
       <c r="CG73" t="n">
         <v>24.96198219013936</v>
@@ -35693,7 +35693,7 @@
         <v>-9.008572356505573</v>
       </c>
       <c r="CM73" t="n">
-        <v>1.248341684146981</v>
+        <v>1.248341688766752</v>
       </c>
       <c r="CN73" t="inlineStr">
         <is>
@@ -35972,10 +35972,10 @@
         <v>4.050000190734863</v>
       </c>
       <c r="BX74" t="n">
-        <v>0.9831252852257534</v>
+        <v>0.9831252892081325</v>
       </c>
       <c r="BY74" t="n">
-        <v>1.823697404093773</v>
+        <v>1.823697411481086</v>
       </c>
       <c r="BZ74" t="n">
         <v>6.002517061212185</v>
@@ -35984,7 +35984,7 @@
         <v>3.984656322398878</v>
       </c>
       <c r="CB74" t="n">
-        <v>8.334872131340436</v>
+        <v>8.334872137576824</v>
       </c>
       <c r="CC74" t="n">
         <v>3.760485277130923</v>
@@ -36286,10 +36286,10 @@
         <v>12.53999996185303</v>
       </c>
       <c r="BX75" t="n">
-        <v>2.074260018315232</v>
+        <v>2.074260018089848</v>
       </c>
       <c r="BY75" t="n">
-        <v>3.847752333974756</v>
+        <v>3.847752333556667</v>
       </c>
       <c r="BZ75" t="n">
         <v>16.17867570540921</v>
@@ -36298,7 +36298,7 @@
         <v>12.83897725188507</v>
       </c>
       <c r="CB75" t="n">
-        <v>21.14310026136404</v>
+        <v>21.1431002610568</v>
       </c>
       <c r="CC75" t="n">
         <v>9.294207014285712</v>
@@ -36602,10 +36602,10 @@
         <v>55.5</v>
       </c>
       <c r="BX76" t="n">
-        <v>40.36268280731368</v>
+        <v>40.36268332132143</v>
       </c>
       <c r="BY76" t="n">
-        <v>58.76806616744873</v>
+        <v>58.76806691584401</v>
       </c>
       <c r="BZ76" t="n">
         <v>35.62962962962963</v>
@@ -36624,13 +36624,13 @@
         <v>48.31609747574325</v>
       </c>
       <c r="CF76" t="n">
-        <v>43.22743353595718</v>
+        <v>43.22743374635768</v>
       </c>
       <c r="CG76" t="n">
-        <v>41.42466996673326</v>
+        <v>41.42467022373714</v>
       </c>
       <c r="CH76" t="n">
-        <v>37.28220297005993</v>
+        <v>37.28220320136342</v>
       </c>
       <c r="CI76" t="n">
         <v>6</v>
@@ -36642,10 +36642,10 @@
         <v>6.4</v>
       </c>
       <c r="CL76" t="n">
-        <v>-32.82485951340553</v>
+        <v>-32.82485909664248</v>
       </c>
       <c r="CM76" t="n">
-        <v>-22.11273236764473</v>
+        <v>-22.11273198854472</v>
       </c>
       <c r="CN76" t="inlineStr">
         <is>
@@ -36928,10 +36928,10 @@
         <v>28.85000038146973</v>
       </c>
       <c r="BX77" t="n">
-        <v>13.476794007096</v>
+        <v>13.47679403422093</v>
       </c>
       <c r="BY77" t="n">
-        <v>24.99945288316308</v>
+        <v>24.99945293347982</v>
       </c>
       <c r="BZ77" t="n">
         <v>37.04094041225521</v>
@@ -36940,19 +36940,19 @@
         <v>25.82930863038749</v>
       </c>
       <c r="CB77" t="n">
-        <v>42.24730465191892</v>
+        <v>42.2473045885765</v>
       </c>
       <c r="CC77" t="n">
-        <v>42.15809543304904</v>
+        <v>42.15809541913985</v>
       </c>
       <c r="CD77" t="n">
-        <v>22.53170135562991</v>
+        <v>22.53170129268489</v>
       </c>
       <c r="CE77" t="n">
         <v>25.12299540697245</v>
       </c>
       <c r="CF77" t="n">
-        <v>29.17582409755902</v>
+        <v>29.17582408971465</v>
       </c>
       <c r="CG77" t="n">
         <v>25.47615201867997</v>
@@ -36973,7 +36973,7 @@
         <v>-20.52500341892921</v>
       </c>
       <c r="CM77" t="n">
-        <v>1.129371617958674</v>
+        <v>1.129371590768491</v>
       </c>
       <c r="CN77" t="inlineStr">
         <is>
@@ -37256,10 +37256,10 @@
         <v>15.11999988555908</v>
       </c>
       <c r="BX78" t="n">
-        <v>2.439882946110683</v>
+        <v>2.439882943285004</v>
       </c>
       <c r="BY78" t="n">
-        <v>4.525982865035316</v>
+        <v>4.525982859793682</v>
       </c>
       <c r="BZ78" t="n">
         <v>25.45616245027419</v>
@@ -37268,7 +37268,7 @@
         <v>19.49357338326157</v>
       </c>
       <c r="CB78" t="n">
-        <v>33.15862255767926</v>
+        <v>33.15862255265264</v>
       </c>
       <c r="CC78" t="n">
         <v>10.38593205872702</v>
@@ -37574,10 +37574,10 @@
         <v>14.64999961853027</v>
       </c>
       <c r="BX79" t="n">
-        <v>9.577574299101698</v>
+        <v>9.577574210787636</v>
       </c>
       <c r="BY79" t="n">
-        <v>17.76640032483365</v>
+        <v>17.76640016101107</v>
       </c>
       <c r="BZ79" t="n">
         <v>13.92485616538925</v>
@@ -37598,7 +37598,7 @@
         <v>12.21188626720157</v>
       </c>
       <c r="CF79" t="n">
-        <v>15.01496753537954</v>
+        <v>15.01496750386246</v>
       </c>
       <c r="CG79" t="n">
         <v>13.27530794084946</v>
@@ -37619,7 +37619,7 @@
         <v>-18.44520506572443</v>
       </c>
       <c r="CM79" t="n">
-        <v>2.491248644045196</v>
+        <v>2.491248428911552</v>
       </c>
       <c r="CN79" t="inlineStr">
         <is>
@@ -37898,25 +37898,25 @@
         <v>26.55999946594238</v>
       </c>
       <c r="BX80" t="n">
-        <v>12.09583918761416</v>
+        <v>12.09583915021851</v>
       </c>
       <c r="BY80" t="n">
-        <v>12.77825690067539</v>
+        <v>12.77825688333884</v>
       </c>
       <c r="BZ80" t="n">
-        <v>14.05452303414772</v>
+        <v>14.05452305853078</v>
       </c>
       <c r="CA80" t="n">
         <v>32.71469597157468</v>
       </c>
       <c r="CB80" t="n">
-        <v>13.10490990598231</v>
+        <v>13.10490990732978</v>
       </c>
       <c r="CC80" t="n">
-        <v>24.67124334978705</v>
+        <v>24.67124335479556</v>
       </c>
       <c r="CD80" t="n">
-        <v>5.74857506709121</v>
+        <v>5.748575091015452</v>
       </c>
       <c r="CE80" t="n">
         <v>64.69524327175267</v>
@@ -37968,7 +37968,7 @@
         <v>-2.572884986294177</v>
       </c>
       <c r="CZ80" t="n">
-        <v>-18.09284111970466</v>
+        <v>-18.09285086071385</v>
       </c>
       <c r="DA80" t="b">
         <v>0</v>
@@ -38212,10 +38212,10 @@
         <v>6.949999809265137</v>
       </c>
       <c r="BX81" t="n">
-        <v>1.251744409468299</v>
+        <v>1.251744408776458</v>
       </c>
       <c r="BY81" t="n">
-        <v>2.321985879563695</v>
+        <v>2.321985878280329</v>
       </c>
       <c r="BZ81" t="n">
         <v>10.39362273958951</v>
@@ -38224,13 +38224,13 @@
         <v>10.1957267373713</v>
       </c>
       <c r="CB81" t="n">
-        <v>10.06783796768597</v>
+        <v>10.06783796787904</v>
       </c>
       <c r="CC81" t="n">
-        <v>1.873467349279102</v>
+        <v>1.87346734930695</v>
       </c>
       <c r="CD81" t="n">
-        <v>7.180621350246386</v>
+        <v>7.1806213510549</v>
       </c>
       <c r="CE81" t="n">
         <v>11.09654186695129</v>
@@ -38526,10 +38526,10 @@
         <v>9.840000152587891</v>
       </c>
       <c r="BX82" t="n">
-        <v>6.031752916606836</v>
+        <v>6.031752879907764</v>
       </c>
       <c r="BY82" t="n">
-        <v>11.18890166030568</v>
+        <v>11.1889015922289</v>
       </c>
       <c r="BZ82" t="n">
         <v>7.877945741497857</v>
@@ -38550,7 +38550,7 @@
         <v>39.41309108925088</v>
       </c>
       <c r="CF82" t="n">
-        <v>10.02204610259289</v>
+        <v>10.02204608762491</v>
       </c>
       <c r="CG82" t="n">
         <v>7.877945741497857</v>
@@ -38571,7 +38571,7 @@
         <v>-27.94561933534744</v>
       </c>
       <c r="CM82" t="n">
-        <v>1.850060438841772</v>
+        <v>1.850060286728183</v>
       </c>
       <c r="CN82" t="inlineStr">
         <is>
@@ -39174,10 +39174,10 @@
         <v>5.159999847412109</v>
       </c>
       <c r="BX84" t="n">
-        <v>3.051428234957723</v>
+        <v>3.051428247492851</v>
       </c>
       <c r="BY84" t="n">
-        <v>4.442879510098445</v>
+        <v>4.442879528349591</v>
       </c>
       <c r="BZ84" t="n">
         <v>4.310361318320155</v>
@@ -39486,10 +39486,10 @@
         <v>18.45999908447266</v>
       </c>
       <c r="BX85" t="n">
-        <v>4.484582526113639</v>
+        <v>4.484582523634422</v>
       </c>
       <c r="BY85" t="n">
-        <v>8.318900585940799</v>
+        <v>8.318900581341852</v>
       </c>
       <c r="BZ85" t="n">
         <v>32.05701020567007</v>
@@ -39498,13 +39498,13 @@
         <v>34.58764733946176</v>
       </c>
       <c r="CB85" t="n">
-        <v>27.935701664017</v>
+        <v>27.93570166328597</v>
       </c>
       <c r="CC85" t="n">
-        <v>11.13048461177082</v>
+        <v>11.13048461193323</v>
       </c>
       <c r="CD85" t="n">
-        <v>18.85057246836579</v>
+        <v>18.85057247076568</v>
       </c>
       <c r="CE85" t="n">
         <v>43.59359053230504</v>
@@ -40088,10 +40088,10 @@
         <v>52.93999862670898</v>
       </c>
       <c r="BX87" t="n">
-        <v>11.1161639310337</v>
+        <v>11.11616387744636</v>
       </c>
       <c r="BY87" t="n">
-        <v>16.18513468358507</v>
+        <v>16.1851346055619</v>
       </c>
       <c r="BZ87" t="inlineStr"/>
       <c r="CA87" t="inlineStr"/>
@@ -40102,13 +40102,13 @@
       <c r="CD87" t="inlineStr"/>
       <c r="CE87" t="inlineStr"/>
       <c r="CF87" t="n">
-        <v>17.87633287153959</v>
+        <v>17.87633282766942</v>
       </c>
       <c r="CG87" t="n">
-        <v>16.18513468358507</v>
+        <v>16.1851346055619</v>
       </c>
       <c r="CH87" t="n">
-        <v>14.56662121522656</v>
+        <v>14.56662114500571</v>
       </c>
       <c r="CI87" t="n">
         <v>3</v>
@@ -40120,10 +40120,10 @@
         <v>2.4</v>
       </c>
       <c r="CL87" t="n">
-        <v>-72.48465887213398</v>
+        <v>-72.48465900477632</v>
       </c>
       <c r="CM87" t="n">
-        <v>-66.2328422076673</v>
+        <v>-66.232842290535</v>
       </c>
       <c r="CN87" t="inlineStr">
         <is>
@@ -40410,10 +40410,10 @@
         <v>22.45000076293945</v>
       </c>
       <c r="BX88" t="n">
-        <v>11.31405123453609</v>
+        <v>11.31405120651349</v>
       </c>
       <c r="BY88" t="n">
-        <v>20.98756504006445</v>
+        <v>20.98756498808252</v>
       </c>
       <c r="BZ88" t="n">
         <v>14.70402916999247</v>
@@ -40434,13 +40434,13 @@
         <v>22.45000076293945</v>
       </c>
       <c r="CF88" t="n">
-        <v>19.21790736056828</v>
+        <v>19.21790735056771</v>
       </c>
       <c r="CG88" t="n">
-        <v>17.84579710502846</v>
+        <v>17.8457970790375</v>
       </c>
       <c r="CH88" t="n">
-        <v>16.06121739452561</v>
+        <v>16.06121737113375</v>
       </c>
       <c r="CI88" t="n">
         <v>8</v>
@@ -40452,10 +40452,10 @@
         <v>2.9</v>
       </c>
       <c r="CL88" t="n">
-        <v>-28.45783140889896</v>
+        <v>-28.45783151309436</v>
       </c>
       <c r="CM88" t="n">
-        <v>-14.3968520825475</v>
+        <v>-14.39685212709344</v>
       </c>
       <c r="CN88" t="inlineStr">
         <is>
@@ -40738,25 +40738,25 @@
         <v>1.690000057220459</v>
       </c>
       <c r="BX89" t="n">
-        <v>0.1506862969119019</v>
+        <v>0.1506862967442968</v>
       </c>
       <c r="BY89" t="n">
-        <v>0.171655292241899</v>
+        <v>0.1716552920584791</v>
       </c>
       <c r="BZ89" t="n">
-        <v>0.76994670779731</v>
+        <v>0.7699467078309888</v>
       </c>
       <c r="CA89" t="n">
         <v>3.206293162785219</v>
       </c>
       <c r="CB89" t="n">
-        <v>0.2622355697644808</v>
+        <v>0.2622355696790903</v>
       </c>
       <c r="CC89" t="n">
-        <v>0.5414652897170932</v>
+        <v>0.5414652897196853</v>
       </c>
       <c r="CD89" t="n">
-        <v>0.3433710221934202</v>
+        <v>0.3433710222223288</v>
       </c>
       <c r="CE89" t="inlineStr"/>
       <c r="CF89" t="inlineStr"/>
@@ -41009,7 +41009,7 @@
         <v>-19.6</v>
       </c>
       <c r="BK90" t="n">
-        <v>9.289999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="BL90" t="n">
         <v>5.03</v>
@@ -41048,10 +41048,10 @@
         <v>13.89999961853027</v>
       </c>
       <c r="BX90" t="n">
-        <v>6.000512423971051</v>
+        <v>6.000512447493907</v>
       </c>
       <c r="BY90" t="n">
-        <v>8.736746089301851</v>
+        <v>8.73674612355113</v>
       </c>
       <c r="BZ90" t="n">
         <v>3.721936046156407</v>
@@ -41264,13 +41264,13 @@
         <v>0</v>
       </c>
       <c r="AR91" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="AS91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="n">
-        <v>2905931264</v>
+        <v>2883450880</v>
       </c>
       <c r="AU91" t="n">
         <v>6.69</v>
@@ -41360,10 +41360,10 @@
         <v>7.420000076293945</v>
       </c>
       <c r="BX91" t="n">
-        <v>3.087627415681174</v>
+        <v>3.087627421786553</v>
       </c>
       <c r="BY91" t="n">
-        <v>5.727548856088577</v>
+        <v>5.727548867414054</v>
       </c>
       <c r="BZ91" t="n">
         <v>14.69581479983479</v>
@@ -41372,23 +41372,23 @@
         <v>15.81853464622579</v>
       </c>
       <c r="CB91" t="n">
-        <v>13.96090354335939</v>
+        <v>13.96090354666531</v>
       </c>
       <c r="CC91" t="n">
-        <v>14.98505630827882</v>
+        <v>14.9850563070803</v>
       </c>
       <c r="CD91" t="n">
-        <v>7.676901757912952</v>
+        <v>7.676901751959962</v>
       </c>
       <c r="CE91" t="inlineStr"/>
       <c r="CF91" t="n">
-        <v>12.14412665195005</v>
+        <v>12.1441266531967</v>
       </c>
       <c r="CG91" t="n">
-        <v>14.32835917159709</v>
+        <v>14.32835917325005</v>
       </c>
       <c r="CH91" t="n">
-        <v>12.89552325443738</v>
+        <v>12.89552325592505</v>
       </c>
       <c r="CI91" t="n">
         <v>6</v>
@@ -41400,10 +41400,10 @@
         <v>5.1</v>
       </c>
       <c r="CL91" t="n">
-        <v>73.7941121542183</v>
+        <v>73.79411217426765</v>
       </c>
       <c r="CM91" t="n">
-        <v>63.66747341080434</v>
+        <v>63.6674734276055</v>
       </c>
       <c r="CN91" t="inlineStr">
         <is>
@@ -41684,10 +41684,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="BX92" t="n">
-        <v>33.76252270278441</v>
+        <v>33.762522922606</v>
       </c>
       <c r="BY92" t="n">
-        <v>62.62947961366508</v>
+        <v>62.62948002143411</v>
       </c>
       <c r="BZ92" t="n">
         <v>4.845639321919829</v>
@@ -41980,35 +41980,35 @@
         <v>19.56999969482422</v>
       </c>
       <c r="BX93" t="n">
-        <v>11.66679783229677</v>
+        <v>11.66679786666319</v>
       </c>
       <c r="BY93" t="n">
-        <v>15.05415850942537</v>
+        <v>15.05415853109027</v>
       </c>
       <c r="BZ93" t="n">
-        <v>23.36416664179487</v>
+        <v>23.36416660659606</v>
       </c>
       <c r="CA93" t="n">
         <v>42.43044465422032</v>
       </c>
       <c r="CB93" t="n">
-        <v>28.36136802948199</v>
+        <v>28.36136805336224</v>
       </c>
       <c r="CC93" t="n">
-        <v>15.78799047285409</v>
+        <v>15.78799047052604</v>
       </c>
       <c r="CD93" t="n">
-        <v>11.30020719928157</v>
+        <v>11.30020717511785</v>
       </c>
       <c r="CE93" t="inlineStr"/>
       <c r="CF93" t="n">
-        <v>16.46827836409277</v>
+        <v>16.46827836871889</v>
       </c>
       <c r="CG93" t="n">
-        <v>15.42107449113973</v>
+        <v>15.42107450080815</v>
       </c>
       <c r="CH93" t="n">
-        <v>13.87896704202575</v>
+        <v>13.87896705072734</v>
       </c>
       <c r="CI93" t="n">
         <v>4</v>
@@ -42020,10 +42020,10 @@
         <v>2</v>
       </c>
       <c r="CL93" t="n">
-        <v>-29.08039213870607</v>
+        <v>-29.08039209424218</v>
       </c>
       <c r="CM93" t="n">
-        <v>-15.84936831425591</v>
+        <v>-15.84936829061707</v>
       </c>
       <c r="CN93" t="inlineStr">
         <is>
@@ -42308,10 +42308,10 @@
         <v>7.78000020980835</v>
       </c>
       <c r="BX94" t="n">
-        <v>5.007638630278256</v>
+        <v>5.007638606165846</v>
       </c>
       <c r="BY94" t="n">
-        <v>7.291121845685142</v>
+        <v>7.291121810577472</v>
       </c>
       <c r="BZ94" t="n">
         <v>5.901677766740105</v>
@@ -42330,13 +42330,13 @@
         <v>7.749646363977103</v>
       </c>
       <c r="CF94" t="n">
-        <v>6.63572262494899</v>
+        <v>6.635722615078976</v>
       </c>
       <c r="CG94" t="n">
-        <v>6.596399806212624</v>
+        <v>6.596399788658789</v>
       </c>
       <c r="CH94" t="n">
-        <v>5.936759825591362</v>
+        <v>5.93675980979291</v>
       </c>
       <c r="CI94" t="n">
         <v>6</v>
@@ -42348,10 +42348,10 @@
         <v>5.9</v>
       </c>
       <c r="CL94" t="n">
-        <v>-23.69203514793213</v>
+        <v>-23.69203535099705</v>
       </c>
       <c r="CM94" t="n">
-        <v>-14.70793771209356</v>
+        <v>-14.70793783895749</v>
       </c>
       <c r="CN94" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>-6.882715380023308</v>
       </c>
       <c r="CZ94" t="n">
-        <v>-19.82188790870523</v>
+        <v>-19.82189594768468</v>
       </c>
       <c r="DA94" t="b">
         <v>0</v>
@@ -42628,10 +42628,10 @@
         <v>78.69999694824219</v>
       </c>
       <c r="BX95" t="n">
-        <v>58.83949690255483</v>
+        <v>58.83949697462913</v>
       </c>
       <c r="BY95" t="n">
-        <v>85.67030749011985</v>
+        <v>85.67030759506001</v>
       </c>
       <c r="BZ95" t="n">
         <v>24.36677488126581</v>
@@ -42944,10 +42944,10 @@
         <v>35.65000152587891</v>
       </c>
       <c r="BX96" t="n">
-        <v>8.82343361691944</v>
+        <v>8.823433601533251</v>
       </c>
       <c r="BY96" t="n">
-        <v>16.36746935938556</v>
+        <v>16.36746933084418</v>
       </c>
       <c r="BZ96" t="n">
         <v>40.6508192958602</v>
@@ -42956,19 +42956,19 @@
         <v>40.9156147189668</v>
       </c>
       <c r="CB96" t="n">
-        <v>33.77771534196432</v>
+        <v>33.7777153506326</v>
       </c>
       <c r="CC96" t="n">
-        <v>50.02798604970015</v>
+        <v>50.02798605382524</v>
       </c>
       <c r="CD96" t="n">
-        <v>22.74549480865072</v>
+        <v>22.74549482575155</v>
       </c>
       <c r="CE96" t="n">
         <v>51.81998252253128</v>
       </c>
       <c r="CF96" t="n">
-        <v>36.61501172815129</v>
+        <v>36.61501172834455</v>
       </c>
       <c r="CG96" t="n">
         <v>40.6508192958602</v>
@@ -42989,7 +42989,7 @@
         <v>2.624784853700501</v>
       </c>
       <c r="CM96" t="n">
-        <v>2.706900872281492</v>
+        <v>2.706900872823592</v>
       </c>
       <c r="CN96" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>1</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AS97" t="b">
         <v>1</v>
@@ -43272,10 +43272,10 @@
         <v>19.59000015258789</v>
       </c>
       <c r="BX97" t="n">
-        <v>2.02155471065194</v>
+        <v>2.021554715127182</v>
       </c>
       <c r="BY97" t="n">
-        <v>3.749983988259349</v>
+        <v>3.749983996560923</v>
       </c>
       <c r="BZ97" t="n">
         <v>10.29621190090399</v>
@@ -43284,19 +43284,19 @@
         <v>8.591723366671241</v>
       </c>
       <c r="CB97" t="n">
-        <v>10.21819184466693</v>
+        <v>10.2181918356177</v>
       </c>
       <c r="CC97" t="n">
-        <v>7.543992734724452</v>
+        <v>7.543992733721995</v>
       </c>
       <c r="CD97" t="n">
-        <v>7.793097664504271</v>
+        <v>7.79309765725402</v>
       </c>
       <c r="CE97" t="n">
         <v>13.94714750731148</v>
       </c>
       <c r="CF97" t="n">
-        <v>8.877192715291674</v>
+        <v>8.877192714005906</v>
       </c>
       <c r="CG97" t="n">
         <v>8.591723366671241</v>
@@ -43317,7 +43317,7 @@
         <v>-60.5280705983934</v>
       </c>
       <c r="CM97" t="n">
-        <v>-54.68508092829711</v>
+        <v>-54.68508093486051</v>
       </c>
       <c r="CN97" t="inlineStr">
         <is>
@@ -43596,10 +43596,10 @@
         <v>6.96999979019165</v>
       </c>
       <c r="BX98" t="n">
-        <v>3.120765487311461</v>
+        <v>3.120765485120736</v>
       </c>
       <c r="BY98" t="n">
-        <v>5.789019978962759</v>
+        <v>5.789019974898966</v>
       </c>
       <c r="BZ98" t="inlineStr"/>
       <c r="CA98" t="inlineStr"/>
@@ -43610,13 +43610,13 @@
         <v>9.575517828204783</v>
       </c>
       <c r="CF98" t="n">
-        <v>6.161767764826334</v>
+        <v>6.161767762741495</v>
       </c>
       <c r="CG98" t="n">
-        <v>5.789019978962759</v>
+        <v>5.789019974898966</v>
       </c>
       <c r="CH98" t="n">
-        <v>5.210117981066483</v>
+        <v>5.21011797740907</v>
       </c>
       <c r="CI98" t="n">
         <v>3</v>
@@ -43628,10 +43628,10 @@
         <v>3.1</v>
       </c>
       <c r="CL98" t="n">
-        <v>-25.24938109182894</v>
+        <v>-25.2493811443026</v>
       </c>
       <c r="CM98" t="n">
-        <v>-11.59586871871474</v>
+        <v>-11.59586874862635</v>
       </c>
       <c r="CN98" t="inlineStr">
         <is>
@@ -43910,10 +43910,10 @@
         <v>15.90999984741211</v>
       </c>
       <c r="BX99" t="n">
-        <v>8.011259078355248</v>
+        <v>8.011259035912254</v>
       </c>
       <c r="BY99" t="n">
-        <v>14.86088559034899</v>
+        <v>14.86088551161723</v>
       </c>
       <c r="BZ99" t="n">
         <v>10.0768402475244</v>
@@ -43934,7 +43934,7 @@
         <v>9.68787499591881</v>
       </c>
       <c r="CF99" t="n">
-        <v>12.14489902500549</v>
+        <v>12.14489900985865</v>
       </c>
       <c r="CG99" t="n">
         <v>9.882357621721603</v>
@@ -43955,7 +43955,7 @@
         <v>-44.09728507322303</v>
       </c>
       <c r="CM99" t="n">
-        <v>-23.66499596804863</v>
+        <v>-23.66499606325192</v>
       </c>
       <c r="CN99" t="inlineStr">
         <is>
@@ -44234,37 +44234,37 @@
         <v>23.35000038146973</v>
       </c>
       <c r="BX100" t="n">
-        <v>5.114427473520455</v>
+        <v>5.114427495612932</v>
       </c>
       <c r="BY100" t="n">
-        <v>7.241067273608026</v>
+        <v>7.241067278489564</v>
       </c>
       <c r="BZ100" t="n">
-        <v>10.68010867153024</v>
+        <v>10.68010863259599</v>
       </c>
       <c r="CA100" t="n">
         <v>14.69322801178486</v>
       </c>
       <c r="CB100" t="n">
-        <v>7.189980053737015</v>
+        <v>7.189980031785877</v>
       </c>
       <c r="CC100" t="n">
-        <v>8.433621534205118</v>
+        <v>8.433621531438551</v>
       </c>
       <c r="CD100" t="n">
-        <v>5.30507394399674</v>
+        <v>5.305073921405858</v>
       </c>
       <c r="CE100" t="n">
         <v>10.70565447273137</v>
       </c>
       <c r="CF100" t="n">
-        <v>8.670395179389228</v>
+        <v>8.670395171980623</v>
       </c>
       <c r="CG100" t="n">
-        <v>7.837344403906572</v>
+        <v>7.837344404964057</v>
       </c>
       <c r="CH100" t="n">
-        <v>7.053609963515915</v>
+        <v>7.053609964467651</v>
       </c>
       <c r="CI100" t="n">
         <v>8</v>
@@ -44276,10 +44276,10 @@
         <v>2.9</v>
       </c>
       <c r="CL100" t="n">
-        <v>-69.79182077824045</v>
+        <v>-69.79182077416448</v>
       </c>
       <c r="CM100" t="n">
-        <v>-62.86768720453664</v>
+        <v>-62.86768723626513</v>
       </c>
       <c r="CN100" t="inlineStr">
         <is>
@@ -44562,10 +44562,10 @@
         <v>46.34000015258789</v>
       </c>
       <c r="BX101" t="n">
-        <v>10.13865031786108</v>
+        <v>10.13865032225718</v>
       </c>
       <c r="BY101" t="n">
-        <v>18.8071963396323</v>
+        <v>18.80719634778707</v>
       </c>
       <c r="BZ101" t="n">
         <v>85.99509832237949</v>
@@ -44574,13 +44574,13 @@
         <v>76.05105676896386</v>
       </c>
       <c r="CB101" t="n">
-        <v>103.2434128147695</v>
+        <v>103.2434128132712</v>
       </c>
       <c r="CC101" t="n">
-        <v>16.00028353524475</v>
+        <v>16.00028353502371</v>
       </c>
       <c r="CD101" t="n">
-        <v>69.73813926094338</v>
+        <v>69.73813925458346</v>
       </c>
       <c r="CE101" t="n">
         <v>22.26855095916991</v>
@@ -44880,25 +44880,25 @@
         <v>47.2400016784668</v>
       </c>
       <c r="BX102" t="n">
-        <v>18.15640585802479</v>
+        <v>18.15640579602986</v>
       </c>
       <c r="BY102" t="n">
-        <v>20.03634737804936</v>
+        <v>20.03634734936629</v>
       </c>
       <c r="BZ102" t="n">
-        <v>23.5674965514363</v>
+        <v>23.56749659816927</v>
       </c>
       <c r="CA102" t="n">
         <v>50.82999467797423</v>
       </c>
       <c r="CB102" t="n">
-        <v>19.57321331354185</v>
+        <v>19.57321332613451</v>
       </c>
       <c r="CC102" t="n">
-        <v>23.26810816825912</v>
+        <v>23.26810817345356</v>
       </c>
       <c r="CD102" t="n">
-        <v>10.17796763192072</v>
+        <v>10.17796767436493</v>
       </c>
       <c r="CE102" t="n">
         <v>117.5954097189415</v>
@@ -45194,10 +45194,10 @@
         <v>12.18000030517578</v>
       </c>
       <c r="BX103" t="n">
-        <v>2.166666237221406</v>
+        <v>2.166666230804696</v>
       </c>
       <c r="BY103" t="n">
-        <v>4.019165870045708</v>
+        <v>4.019165858142711</v>
       </c>
       <c r="BZ103" t="n">
         <v>12.21688145674331</v>
@@ -45206,25 +45206,25 @@
         <v>13.53155185697616</v>
       </c>
       <c r="CB103" t="n">
-        <v>8.761607908888049</v>
+        <v>8.761607911475245</v>
       </c>
       <c r="CC103" t="n">
-        <v>5.735278184264804</v>
+        <v>5.735278184810479</v>
       </c>
       <c r="CD103" t="n">
-        <v>6.527079740349924</v>
+        <v>6.52707974625073</v>
       </c>
       <c r="CE103" t="n">
         <v>12.18000030517578</v>
       </c>
       <c r="CF103" t="n">
-        <v>8.995937903206247</v>
+        <v>8.995937902796346</v>
       </c>
       <c r="CG103" t="n">
-        <v>8.761607908888049</v>
+        <v>8.761607911475245</v>
       </c>
       <c r="CH103" t="n">
-        <v>7.885447117999244</v>
+        <v>7.885447120327721</v>
       </c>
       <c r="CI103" t="n">
         <v>7</v>
@@ -45236,10 +45236,10 @@
         <v>6.2</v>
       </c>
       <c r="CL103" t="n">
-        <v>-35.25905648254874</v>
+        <v>-35.25905646343151</v>
       </c>
       <c r="CM103" t="n">
-        <v>-26.14172678317993</v>
+        <v>-26.14172678654529</v>
       </c>
       <c r="CN103" t="inlineStr">
         <is>
@@ -45518,37 +45518,37 @@
         <v>53.65000152587891</v>
       </c>
       <c r="BX104" t="n">
-        <v>16.38838751286237</v>
+        <v>16.38838749789565</v>
       </c>
       <c r="BY104" t="n">
-        <v>24.84231880869928</v>
+        <v>24.84231880014987</v>
       </c>
       <c r="BZ104" t="n">
-        <v>44.54715960172905</v>
+        <v>44.54715962708104</v>
       </c>
       <c r="CA104" t="n">
         <v>62.04793706021404</v>
       </c>
       <c r="CB104" t="n">
-        <v>35.53900670433367</v>
+        <v>35.53900670892518</v>
       </c>
       <c r="CC104" t="n">
-        <v>26.754325476984</v>
+        <v>26.75432547827134</v>
       </c>
       <c r="CD104" t="n">
-        <v>22.27011838748315</v>
+        <v>22.27011840046948</v>
       </c>
       <c r="CE104" t="n">
         <v>21.66551392102021</v>
       </c>
       <c r="CF104" t="n">
-        <v>31.75684593416572</v>
+        <v>31.75684593675335</v>
       </c>
       <c r="CG104" t="n">
-        <v>25.79832214284164</v>
+        <v>25.7983221392106</v>
       </c>
       <c r="CH104" t="n">
-        <v>23.21848992855747</v>
+        <v>23.21848992528955</v>
       </c>
       <c r="CI104" t="n">
         <v>8</v>
@@ -45560,10 +45560,10 @@
         <v>3.8</v>
       </c>
       <c r="CL104" t="n">
-        <v>-56.7222940015059</v>
+        <v>-56.7222940075971</v>
       </c>
       <c r="CM104" t="n">
-        <v>-40.8073717969098</v>
+        <v>-40.80737179208663</v>
       </c>
       <c r="CN104" t="inlineStr">
         <is>
@@ -45850,10 +45850,10 @@
         <v>3.009999990463257</v>
       </c>
       <c r="BX105" t="n">
-        <v>0.6299352424866833</v>
+        <v>0.6299352413568136</v>
       </c>
       <c r="BY105" t="n">
-        <v>1.168529874812797</v>
+        <v>1.168529872716889</v>
       </c>
       <c r="BZ105" t="n">
         <v>3.379872870647301</v>
@@ -45862,13 +45862,13 @@
         <v>3.910006936746576</v>
       </c>
       <c r="CB105" t="n">
-        <v>2.344554567501675</v>
+        <v>2.344554567674951</v>
       </c>
       <c r="CC105" t="n">
-        <v>2.63438525226058</v>
+        <v>2.634385252407706</v>
       </c>
       <c r="CD105" t="n">
-        <v>1.685378474929421</v>
+        <v>1.685378475880952</v>
       </c>
       <c r="CE105" t="n">
         <v>8.886211075297577</v>
@@ -46162,10 +46162,10 @@
         <v>58.11999893188477</v>
       </c>
       <c r="BX106" t="n">
-        <v>65.76464389965633</v>
+        <v>65.76464406875786</v>
       </c>
       <c r="BY106" t="n">
-        <v>95.75332151789962</v>
+        <v>95.75332176411146</v>
       </c>
       <c r="BZ106" t="n">
         <v>25.32249639261004</v>
@@ -47072,10 +47072,10 @@
         <v>96.33999633789062</v>
       </c>
       <c r="BX109" t="n">
-        <v>4.919793634320357</v>
+        <v>4.919793602141335</v>
       </c>
       <c r="BY109" t="n">
-        <v>9.12621719166426</v>
+        <v>9.126217131972178</v>
       </c>
       <c r="BZ109" t="n">
         <v>41.29747497499355</v>
@@ -47084,13 +47084,13 @@
         <v>40.9954214454957</v>
       </c>
       <c r="CB109" t="n">
-        <v>33.8168446921921</v>
+        <v>33.81684473622818</v>
       </c>
       <c r="CC109" t="n">
-        <v>17.69240962770702</v>
+        <v>17.69240963072789</v>
       </c>
       <c r="CD109" t="n">
-        <v>28.1819327502025</v>
+        <v>28.18193278704362</v>
       </c>
       <c r="CE109" t="n">
         <v>42.5335436716941</v>
@@ -47696,10 +47696,10 @@
         <v>17.45000076293945</v>
       </c>
       <c r="BX111" t="n">
-        <v>3.27608360827524</v>
+        <v>3.276083596303264</v>
       </c>
       <c r="BY111" t="n">
-        <v>6.07713509335057</v>
+        <v>6.077135071142554</v>
       </c>
       <c r="BZ111" t="n">
         <v>14.88812041912091</v>
@@ -47708,23 +47708,23 @@
         <v>15.87749399405222</v>
       </c>
       <c r="CB111" t="n">
-        <v>10.46760141986499</v>
+        <v>10.46760142801215</v>
       </c>
       <c r="CC111" t="n">
-        <v>13.01572396703299</v>
+        <v>13.01572396908937</v>
       </c>
       <c r="CD111" t="n">
-        <v>7.724960024095552</v>
+        <v>7.724960036000486</v>
       </c>
       <c r="CE111" t="inlineStr"/>
       <c r="CF111" t="n">
-        <v>11.34183915291954</v>
+        <v>11.34183915290295</v>
       </c>
       <c r="CG111" t="n">
-        <v>11.74166269344899</v>
+        <v>11.74166269855076</v>
       </c>
       <c r="CH111" t="n">
-        <v>10.56749642410409</v>
+        <v>10.56749642869568</v>
       </c>
       <c r="CI111" t="n">
         <v>6</v>
@@ -47736,10 +47736,10 @@
         <v>4.8</v>
       </c>
       <c r="CL111" t="n">
-        <v>-39.44128388494124</v>
+        <v>-39.4412838586284</v>
       </c>
       <c r="CM111" t="n">
-        <v>-35.00378993101542</v>
+        <v>-35.00378993111048</v>
       </c>
       <c r="CN111" t="inlineStr">
         <is>
@@ -48018,25 +48018,25 @@
         <v>14.64000034332275</v>
       </c>
       <c r="BX112" t="n">
-        <v>3.695490806073948</v>
+        <v>3.695490812263638</v>
       </c>
       <c r="BY112" t="n">
-        <v>4.692826218392233</v>
+        <v>4.692826225211578</v>
       </c>
       <c r="BZ112" t="n">
-        <v>14.00770734656185</v>
+        <v>14.00770734345512</v>
       </c>
       <c r="CA112" t="n">
         <v>36.58780695463401</v>
       </c>
       <c r="CB112" t="n">
-        <v>9.596024410907802</v>
+        <v>9.596024416556471</v>
       </c>
       <c r="CC112" t="n">
-        <v>48.40176703951053</v>
+        <v>48.40176703844456</v>
       </c>
       <c r="CD112" t="n">
-        <v>6.726870750358145</v>
+        <v>6.726870748163035</v>
       </c>
       <c r="CE112" t="n">
         <v>25.86701731463541</v>
@@ -48242,7 +48242,7 @@
         <v>0</v>
       </c>
       <c r="AT113" t="n">
-        <v>27077031936</v>
+        <v>27074949120</v>
       </c>
       <c r="AU113" t="n">
         <v>22.1</v>
@@ -48332,10 +48332,10 @@
         <v>14.52999973297119</v>
       </c>
       <c r="BX113" t="n">
-        <v>1.359804409298964</v>
+        <v>1.359804409229833</v>
       </c>
       <c r="BY113" t="n">
-        <v>2.522437179249578</v>
+        <v>2.52243717912134</v>
       </c>
       <c r="BZ113" t="n">
         <v>8.711425179270055</v>
@@ -48344,13 +48344,13 @@
         <v>10.72111427832558</v>
       </c>
       <c r="CB113" t="n">
-        <v>4.822366877940052</v>
+        <v>4.822366877978332</v>
       </c>
       <c r="CC113" t="n">
-        <v>7.692408686135011</v>
+        <v>7.692408686144068</v>
       </c>
       <c r="CD113" t="n">
-        <v>4.246115052389372</v>
+        <v>4.246115052440961</v>
       </c>
       <c r="CE113" t="n">
         <v>11.54934248649259</v>
@@ -48560,7 +48560,7 @@
         <v>1</v>
       </c>
       <c r="AT114" t="n">
-        <v>44512468992</v>
+        <v>44763660288</v>
       </c>
       <c r="AU114" t="n">
         <v>3282.69</v>
@@ -48650,10 +48650,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX114" t="n">
-        <v>11.98290323524745</v>
+        <v>11.98290321665384</v>
       </c>
       <c r="BY114" t="n">
-        <v>14.95257925441746</v>
+        <v>14.95257923121588</v>
       </c>
       <c r="BZ114" t="inlineStr"/>
       <c r="CA114" t="inlineStr"/>
@@ -48956,10 +48956,10 @@
         <v>11.18000030517578</v>
       </c>
       <c r="BX115" t="n">
-        <v>2.429612148331315</v>
+        <v>2.42961214764127</v>
       </c>
       <c r="BY115" t="n">
-        <v>4.506930535154589</v>
+        <v>4.506930533874555</v>
       </c>
       <c r="BZ115" t="n">
         <v>12.14221344619501</v>
@@ -48968,13 +48968,13 @@
         <v>12.65237085480843</v>
       </c>
       <c r="CB115" t="n">
-        <v>9.593565641224775</v>
+        <v>9.593565641573841</v>
       </c>
       <c r="CC115" t="n">
-        <v>0.7923053613460772</v>
+        <v>0.7923053613552596</v>
       </c>
       <c r="CD115" t="n">
-        <v>6.725813828928852</v>
+        <v>6.725813829646003</v>
       </c>
       <c r="CE115" t="n">
         <v>7.373367923247756</v>
@@ -49270,25 +49270,25 @@
         <v>8.739999771118164</v>
       </c>
       <c r="BX116" t="n">
-        <v>2.24763468413627</v>
+        <v>2.247634683543725</v>
       </c>
       <c r="BY116" t="n">
-        <v>2.439544378481581</v>
+        <v>2.439544378000921</v>
       </c>
       <c r="BZ116" t="n">
-        <v>3.256074274361908</v>
+        <v>3.256074274578769</v>
       </c>
       <c r="CA116" t="n">
         <v>10.09773875906247</v>
       </c>
       <c r="CB116" t="n">
-        <v>1.921804786654056</v>
+        <v>1.921804786578119</v>
       </c>
       <c r="CC116" t="n">
-        <v>5.911010295644364</v>
+        <v>5.911010295689342</v>
       </c>
       <c r="CD116" t="n">
-        <v>1.379500464490337</v>
+        <v>1.379500464693177</v>
       </c>
       <c r="CE116" t="n">
         <v>14.45896929706421</v>
@@ -49584,10 +49584,10 @@
         <v>4.809999942779541</v>
       </c>
       <c r="BX117" t="n">
-        <v>1.479509787783132</v>
+        <v>1.479509790828952</v>
       </c>
       <c r="BY117" t="n">
-        <v>1.541977978822864</v>
+        <v>1.541977981997286</v>
       </c>
       <c r="BZ117" t="inlineStr"/>
       <c r="CA117" t="inlineStr"/>
@@ -49888,10 +49888,10 @@
         <v>3.430000066757202</v>
       </c>
       <c r="BX118" t="n">
-        <v>1.689358880608014</v>
+        <v>1.689358881793472</v>
       </c>
       <c r="BY118" t="n">
-        <v>3.133760723527866</v>
+        <v>3.133760725726891</v>
       </c>
       <c r="BZ118" t="n">
         <v>1.178617761528343</v>
@@ -49900,7 +49900,7 @@
         <v>4.705827767414989</v>
       </c>
       <c r="CB118" t="n">
-        <v>1.63630770477749</v>
+        <v>1.636307705207895</v>
       </c>
       <c r="CC118" t="n">
         <v>0.7445919647652398</v>
@@ -50202,10 +50202,10 @@
         <v>6.559999942779541</v>
       </c>
       <c r="BX119" t="n">
-        <v>1.053693236410784</v>
+        <v>1.05369323979503</v>
       </c>
       <c r="BY119" t="n">
-        <v>1.954600953542004</v>
+        <v>1.954600959819782</v>
       </c>
       <c r="BZ119" t="inlineStr"/>
       <c r="CA119" t="inlineStr"/>
@@ -50506,25 +50506,25 @@
         <v>3.700000047683716</v>
       </c>
       <c r="BX120" t="n">
-        <v>1.267030927879381</v>
+        <v>1.267030928564613</v>
       </c>
       <c r="BY120" t="n">
-        <v>1.270803242908066</v>
+        <v>1.27080324334442</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.281162746204448</v>
+        <v>1.281162745951486</v>
       </c>
       <c r="CA120" t="n">
         <v>4.001025037561948</v>
       </c>
       <c r="CB120" t="n">
-        <v>0.8638648792594766</v>
+        <v>0.8638648792904871</v>
       </c>
       <c r="CC120" t="n">
-        <v>2.294198993172789</v>
+        <v>2.294198993117304</v>
       </c>
       <c r="CD120" t="n">
-        <v>0.4818317950879053</v>
+        <v>0.4818317948159505</v>
       </c>
       <c r="CE120" t="n">
         <v>5.12793832390089</v>
@@ -50824,10 +50824,10 @@
         <v>5.510000228881836</v>
       </c>
       <c r="BX121" t="n">
-        <v>5.460836728833823</v>
+        <v>5.460836727058601</v>
       </c>
       <c r="BY121" t="n">
-        <v>7.950978277182046</v>
+        <v>7.950978274597325</v>
       </c>
       <c r="BZ121" t="inlineStr"/>
       <c r="CA121" t="inlineStr"/>
@@ -50836,13 +50836,13 @@
       <c r="CD121" t="inlineStr"/>
       <c r="CE121" t="inlineStr"/>
       <c r="CF121" t="n">
-        <v>6.705907503007935</v>
+        <v>6.705907500827963</v>
       </c>
       <c r="CG121" t="n">
-        <v>6.705907503007935</v>
+        <v>6.705907500827963</v>
       </c>
       <c r="CH121" t="n">
-        <v>6.035316752707141</v>
+        <v>6.035316750745166</v>
       </c>
       <c r="CI121" t="n">
         <v>2</v>
@@ -50854,10 +50854,10 @@
         <v>1.5</v>
       </c>
       <c r="CL121" t="n">
-        <v>9.533874809509935</v>
+        <v>9.533874773902419</v>
       </c>
       <c r="CM121" t="n">
-        <v>21.70430534389993</v>
+        <v>21.70430530433602</v>
       </c>
       <c r="CN121" t="inlineStr">
         <is>
@@ -51136,10 +51136,10 @@
         <v>5.079999923706055</v>
       </c>
       <c r="BX122" t="n">
-        <v>5.591984094963508</v>
+        <v>5.591984088049994</v>
       </c>
       <c r="BY122" t="n">
-        <v>9.969901281598791</v>
+        <v>9.969901269272748</v>
       </c>
       <c r="BZ122" t="inlineStr"/>
       <c r="CA122" t="inlineStr"/>
@@ -51148,13 +51148,13 @@
       <c r="CD122" t="inlineStr"/>
       <c r="CE122" t="inlineStr"/>
       <c r="CF122" t="n">
-        <v>7.780942688281149</v>
+        <v>7.780942678661371</v>
       </c>
       <c r="CG122" t="n">
-        <v>7.780942688281149</v>
+        <v>7.780942678661371</v>
       </c>
       <c r="CH122" t="n">
-        <v>7.002848419453034</v>
+        <v>7.002848410795234</v>
       </c>
       <c r="CI122" t="n">
         <v>2</v>
@@ -51166,10 +51166,10 @@
         <v>1.8</v>
       </c>
       <c r="CL122" t="n">
-        <v>37.85134890994619</v>
+        <v>37.85134873951708</v>
       </c>
       <c r="CM122" t="n">
-        <v>53.16816545549579</v>
+        <v>53.16816526613006</v>
       </c>
       <c r="CN122" t="inlineStr">
         <is>
@@ -51434,10 +51434,10 @@
         <v>21.88999938964844</v>
       </c>
       <c r="BX123" t="n">
-        <v>37.9565833683093</v>
+        <v>37.9565835813944</v>
       </c>
       <c r="BY123" t="n">
-        <v>70.40946214821373</v>
+        <v>70.40946254348661</v>
       </c>
       <c r="BZ123" t="n">
         <v>19.65057533284836</v>
@@ -51456,7 +51456,7 @@
       </c>
       <c r="CE123" t="inlineStr"/>
       <c r="CF123" t="n">
-        <v>25.71643109105786</v>
+        <v>25.71643112657204</v>
       </c>
       <c r="CG123" t="n">
         <v>22.88916053088746</v>
@@ -51477,7 +51477,7 @@
         <v>-5.891982402062723</v>
       </c>
       <c r="CM123" t="n">
-        <v>17.48027322110799</v>
+        <v>17.48027338334732</v>
       </c>
       <c r="CN123" t="inlineStr">
         <is>
@@ -51756,25 +51756,25 @@
         <v>9.210000038146973</v>
       </c>
       <c r="BX124" t="n">
-        <v>3.561519069203598</v>
+        <v>3.561519078885751</v>
       </c>
       <c r="BY124" t="n">
-        <v>3.675673673216738</v>
+        <v>3.675673681669892</v>
       </c>
       <c r="BZ124" t="n">
-        <v>4.437535487731526</v>
+        <v>4.437535485873132</v>
       </c>
       <c r="CA124" t="n">
         <v>19.1542749461826</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.489372639007585</v>
+        <v>3.489372644844303</v>
       </c>
       <c r="CC124" t="n">
-        <v>7.74207375182394</v>
+        <v>7.742073751436652</v>
       </c>
       <c r="CD124" t="n">
-        <v>1.752959776922478</v>
+        <v>1.752959775022452</v>
       </c>
       <c r="CE124" t="n">
         <v>21.67646595176141</v>
@@ -52070,10 +52070,10 @@
         <v>11.46000003814697</v>
       </c>
       <c r="BX125" t="n">
-        <v>0.7792719063686609</v>
+        <v>0.7792719064819676</v>
       </c>
       <c r="BY125" t="n">
-        <v>1.445549386313866</v>
+        <v>1.44554938652405</v>
       </c>
       <c r="BZ125" t="n">
         <v>15.9836842637313</v>
@@ -52082,13 +52082,13 @@
         <v>16.66499025937759</v>
       </c>
       <c r="CB125" t="n">
-        <v>14.05168116890934</v>
+        <v>14.05168116888977</v>
       </c>
       <c r="CC125" t="n">
-        <v>1.723472327643349</v>
+        <v>1.723472327640941</v>
       </c>
       <c r="CD125" t="n">
-        <v>11.33321991190149</v>
+        <v>11.33321991178424</v>
       </c>
       <c r="CE125" t="inlineStr"/>
       <c r="CF125" t="inlineStr"/>
@@ -52676,25 +52676,25 @@
         <v>19</v>
       </c>
       <c r="BX127" t="n">
-        <v>0.5916775930181861</v>
+        <v>0.5916775937830067</v>
       </c>
       <c r="BY127" t="n">
-        <v>0.7959309541164623</v>
+        <v>0.7959309550759684</v>
       </c>
       <c r="BZ127" t="n">
-        <v>4.744394285123802</v>
+        <v>4.744394284710489</v>
       </c>
       <c r="CA127" t="n">
         <v>11.86264950263866</v>
       </c>
       <c r="CB127" t="n">
-        <v>1.821996306742308</v>
+        <v>1.821996306601906</v>
       </c>
       <c r="CC127" t="n">
-        <v>0.6742710781039213</v>
+        <v>0.6742710780983842</v>
       </c>
       <c r="CD127" t="n">
-        <v>2.328996506375236</v>
+        <v>2.328996506112076</v>
       </c>
       <c r="CE127" t="n">
         <v>19</v>
@@ -52994,10 +52994,10 @@
         <v>5.150000095367432</v>
       </c>
       <c r="BX128" t="n">
-        <v>1.269757057783039</v>
+        <v>1.26975705318016</v>
       </c>
       <c r="BY128" t="n">
-        <v>2.125111584889613</v>
+        <v>2.125111577186067</v>
       </c>
       <c r="BZ128" t="inlineStr"/>
       <c r="CA128" t="inlineStr"/>
@@ -53008,13 +53008,13 @@
         <v>5.966766218226677</v>
       </c>
       <c r="CF128" t="n">
-        <v>1.697434321336326</v>
+        <v>1.697434315183113</v>
       </c>
       <c r="CG128" t="n">
-        <v>1.697434321336326</v>
+        <v>1.697434315183113</v>
       </c>
       <c r="CH128" t="n">
-        <v>1.527690889202693</v>
+        <v>1.527690883664802</v>
       </c>
       <c r="CI128" t="n">
         <v>2</v>
@@ -53026,10 +53026,10 @@
         <v>4.7</v>
       </c>
       <c r="CL128" t="n">
-        <v>-70.3360997880972</v>
+        <v>-70.33609989562908</v>
       </c>
       <c r="CM128" t="n">
-        <v>-67.04011087566357</v>
+        <v>-67.04011099514342</v>
       </c>
       <c r="CN128" t="inlineStr">
         <is>
@@ -53304,10 +53304,10 @@
         <v>18.20000076293945</v>
       </c>
       <c r="BX129" t="n">
-        <v>1.401802103201183</v>
+        <v>1.401802102910439</v>
       </c>
       <c r="BY129" t="n">
-        <v>2.041023862260923</v>
+        <v>2.041023861837599</v>
       </c>
       <c r="BZ129" t="inlineStr"/>
       <c r="CA129" t="inlineStr"/>
@@ -53610,37 +53610,37 @@
         <v>17.20999908447266</v>
       </c>
       <c r="BX130" t="n">
-        <v>2.072771886510078</v>
+        <v>2.072771884170888</v>
       </c>
       <c r="BY130" t="n">
-        <v>3.668389129583747</v>
+        <v>3.668389127329242</v>
       </c>
       <c r="BZ130" t="n">
-        <v>9.537870346486448</v>
+        <v>9.537870351388493</v>
       </c>
       <c r="CA130" t="n">
         <v>11.82323496807012</v>
       </c>
       <c r="CB130" t="n">
-        <v>5.529878477778123</v>
+        <v>5.52987847934546</v>
       </c>
       <c r="CC130" t="n">
-        <v>5.536636594309717</v>
+        <v>5.536636594518317</v>
       </c>
       <c r="CD130" t="n">
-        <v>4.691832894183888</v>
+        <v>4.691832896071522</v>
       </c>
       <c r="CE130" t="n">
         <v>15.57105866321647</v>
       </c>
       <c r="CF130" t="n">
-        <v>6.797973735068674</v>
+        <v>6.797973736120526</v>
       </c>
       <c r="CG130" t="n">
-        <v>5.533257536043919</v>
+        <v>5.533257536931888</v>
       </c>
       <c r="CH130" t="n">
-        <v>4.979931782439528</v>
+        <v>4.979931783238699</v>
       </c>
       <c r="CI130" t="n">
         <v>6</v>
@@ -53652,10 +53652,10 @@
         <v>7.5</v>
       </c>
       <c r="CL130" t="n">
-        <v>-71.06373011412556</v>
+        <v>-71.06373010948191</v>
       </c>
       <c r="CM130" t="n">
-        <v>-60.49985998429253</v>
+        <v>-60.49985997818066</v>
       </c>
       <c r="CN130" t="inlineStr">
         <is>
@@ -53926,10 +53926,10 @@
         <v>4.21999979019165</v>
       </c>
       <c r="BX131" t="n">
-        <v>0.8881979195949974</v>
+        <v>0.888197918491655</v>
       </c>
       <c r="BY131" t="n">
-        <v>0.9831240722517127</v>
+        <v>0.9831240710304507</v>
       </c>
       <c r="BZ131" t="inlineStr"/>
       <c r="CA131" t="inlineStr"/>
@@ -53938,13 +53938,13 @@
       <c r="CD131" t="inlineStr"/>
       <c r="CE131" t="inlineStr"/>
       <c r="CF131" t="n">
-        <v>0.9356609959233551</v>
+        <v>0.9356609947610528</v>
       </c>
       <c r="CG131" t="n">
-        <v>0.9356609959233551</v>
+        <v>0.9356609947610528</v>
       </c>
       <c r="CH131" t="n">
-        <v>0.8420948963310195</v>
+        <v>0.8420948952849475</v>
       </c>
       <c r="CI131" t="n">
         <v>2</v>
@@ -53956,10 +53956,10 @@
         <v>1.1</v>
       </c>
       <c r="CL131" t="n">
-        <v>-80.04514364459776</v>
+        <v>-80.04514366938619</v>
       </c>
       <c r="CM131" t="n">
-        <v>-77.8279373828864</v>
+        <v>-77.82793741042912</v>
       </c>
       <c r="CN131" t="inlineStr">
         <is>
@@ -54240,10 +54240,10 @@
         <v>1.220000028610229</v>
       </c>
       <c r="BX132" t="n">
-        <v>0.3581979135207498</v>
+        <v>0.3581979140298155</v>
       </c>
       <c r="BY132" t="n">
-        <v>0.6644571295809908</v>
+        <v>0.6644571305253077</v>
       </c>
       <c r="BZ132" t="inlineStr"/>
       <c r="CA132" t="inlineStr"/>
@@ -54252,13 +54252,13 @@
       <c r="CD132" t="inlineStr"/>
       <c r="CE132" t="inlineStr"/>
       <c r="CF132" t="n">
-        <v>0.5113275215508702</v>
+        <v>0.5113275222775616</v>
       </c>
       <c r="CG132" t="n">
-        <v>0.5113275215508702</v>
+        <v>0.5113275222775616</v>
       </c>
       <c r="CH132" t="n">
-        <v>0.4601947693957832</v>
+        <v>0.4601947700498055</v>
       </c>
       <c r="CI132" t="n">
         <v>2</v>
@@ -54270,10 +54270,10 @@
         <v>1.9</v>
       </c>
       <c r="CL132" t="n">
-        <v>-62.27911814723341</v>
+        <v>-62.27911809362503</v>
       </c>
       <c r="CM132" t="n">
-        <v>-58.08790905248157</v>
+        <v>-58.0879089929167</v>
       </c>
       <c r="CN132" t="inlineStr">
         <is>
@@ -54860,10 +54860,10 @@
         <v>37.15000152587891</v>
       </c>
       <c r="BX134" t="n">
-        <v>8.367448543454859</v>
+        <v>8.367448517366313</v>
       </c>
       <c r="BY134" t="n">
-        <v>12.18300507927028</v>
+        <v>12.18300504128536</v>
       </c>
       <c r="BZ134" t="n">
         <v>7.98264495597398</v>
@@ -55170,10 +55170,10 @@
         <v>5.460000038146973</v>
       </c>
       <c r="BX135" t="n">
-        <v>1.040921915472592</v>
+        <v>1.040921914694933</v>
       </c>
       <c r="BY135" t="n">
-        <v>1.930910153201658</v>
+        <v>1.9309101517591</v>
       </c>
       <c r="BZ135" t="inlineStr"/>
       <c r="CA135" t="inlineStr"/>
@@ -55184,13 +55184,13 @@
         <v>2.921035340023647</v>
       </c>
       <c r="CF135" t="n">
-        <v>1.964289136232632</v>
+        <v>1.96428913549256</v>
       </c>
       <c r="CG135" t="n">
-        <v>1.930910153201658</v>
+        <v>1.9309101517591</v>
       </c>
       <c r="CH135" t="n">
-        <v>1.737819137881492</v>
+        <v>1.73781913658319</v>
       </c>
       <c r="CI135" t="n">
         <v>3</v>
@@ -55202,10 +55202,10 @@
         <v>2.8</v>
       </c>
       <c r="CL135" t="n">
-        <v>-68.17181088388276</v>
+        <v>-68.17181090766118</v>
       </c>
       <c r="CM135" t="n">
-        <v>-64.0240087452586</v>
+        <v>-64.02400875881303</v>
       </c>
       <c r="CN135" t="inlineStr">
         <is>
@@ -55484,25 +55484,25 @@
         <v>4.840000152587891</v>
       </c>
       <c r="BX136" t="n">
-        <v>1.502502726022025</v>
+        <v>1.502502734477237</v>
       </c>
       <c r="BY136" t="n">
-        <v>1.661829030967253</v>
+        <v>1.661829038263891</v>
       </c>
       <c r="BZ136" t="n">
-        <v>2.454262203868694</v>
+        <v>2.454262200833528</v>
       </c>
       <c r="CA136" t="n">
         <v>7.637283478890028</v>
       </c>
       <c r="CB136" t="n">
-        <v>1.720253736625191</v>
+        <v>1.72025373985498</v>
       </c>
       <c r="CC136" t="n">
-        <v>1.782246221684628</v>
+        <v>1.782246221436985</v>
       </c>
       <c r="CD136" t="n">
-        <v>1.062540519746624</v>
+        <v>1.062540517001048</v>
       </c>
       <c r="CE136" t="n">
         <v>0.3893443649538701</v>
@@ -55796,10 +55796,10 @@
         <v>1.990000009536743</v>
       </c>
       <c r="BX137" t="n">
-        <v>0.5586583793212254</v>
+        <v>0.5586583799970081</v>
       </c>
       <c r="BY137" t="n">
-        <v>0.8134066002917043</v>
+        <v>0.8134066012756438</v>
       </c>
       <c r="BZ137" t="n">
         <v>0.3437302790098343</v>
@@ -56104,10 +56104,10 @@
         <v>6.889999866485596</v>
       </c>
       <c r="BX138" t="n">
-        <v>1.890787839573564</v>
+        <v>1.890787840104773</v>
       </c>
       <c r="BY138" t="n">
-        <v>2.752987094419109</v>
+        <v>2.752987095192549</v>
       </c>
       <c r="BZ138" t="n">
         <v>1.748560239420454</v>
@@ -57596,10 +57596,10 @@
         <v>18.30999946594238</v>
       </c>
       <c r="BX143" t="n">
-        <v>27.83633516612048</v>
+        <v>27.83633521535095</v>
       </c>
       <c r="BY143" t="n">
-        <v>37.23883060001006</v>
+        <v>37.2388306658695</v>
       </c>
       <c r="BZ143" t="n">
         <v>2.491274627922611</v>
@@ -57608,7 +57608,7 @@
         <v>6.909187799009217</v>
       </c>
       <c r="CB143" t="n">
-        <v>6.383321808581837</v>
+        <v>6.383321818395685</v>
       </c>
       <c r="CC143" t="n">
         <v>3.046690502845772</v>
@@ -57910,10 +57910,10 @@
         <v>3.75</v>
       </c>
       <c r="BX144" t="n">
-        <v>0.6783189640326317</v>
+        <v>0.6783189622362282</v>
       </c>
       <c r="BY144" t="n">
-        <v>1.258281678280532</v>
+        <v>1.258281674948203</v>
       </c>
       <c r="BZ144" t="inlineStr"/>
       <c r="CA144" t="inlineStr"/>
@@ -57924,13 +57924,13 @@
         <v>3.41418274193782</v>
       </c>
       <c r="CF144" t="n">
-        <v>0.9683003211565817</v>
+        <v>0.9683003185922158</v>
       </c>
       <c r="CG144" t="n">
-        <v>0.9683003211565817</v>
+        <v>0.9683003185922158</v>
       </c>
       <c r="CH144" t="n">
-        <v>0.8714702890409236</v>
+        <v>0.8714702867329942</v>
       </c>
       <c r="CI144" t="n">
         <v>2</v>
@@ -57942,10 +57942,10 @@
         <v>5</v>
       </c>
       <c r="CL144" t="n">
-        <v>-76.76079229224204</v>
+        <v>-76.76079235378683</v>
       </c>
       <c r="CM144" t="n">
-        <v>-74.17865810249116</v>
+        <v>-74.17865817087424</v>
       </c>
       <c r="CN144" t="inlineStr">
         <is>
@@ -58222,10 +58222,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX145" t="n">
-        <v>9.498631713004629</v>
+        <v>9.498631705856553</v>
       </c>
       <c r="BY145" t="n">
-        <v>13.83000777413474</v>
+        <v>13.83000776372714</v>
       </c>
       <c r="BZ145" t="n">
         <v>4.684999942779541</v>
@@ -59154,10 +59154,10 @@
         <v>10.71000003814697</v>
       </c>
       <c r="BX148" t="n">
-        <v>5.722370909251392</v>
+        <v>5.722370902474492</v>
       </c>
       <c r="BY148" t="n">
-        <v>10.4740581605631</v>
+        <v>10.47405814815887</v>
       </c>
       <c r="BZ148" t="inlineStr"/>
       <c r="CA148" t="inlineStr"/>
@@ -59168,13 +59168,13 @@
         <v>3.193949960809536</v>
       </c>
       <c r="CF148" t="n">
-        <v>6.463459676874677</v>
+        <v>6.463459670480965</v>
       </c>
       <c r="CG148" t="n">
-        <v>5.722370909251392</v>
+        <v>5.722370902474492</v>
       </c>
       <c r="CH148" t="n">
-        <v>5.150133818326253</v>
+        <v>5.150133812227043</v>
       </c>
       <c r="CI148" t="n">
         <v>3</v>
@@ -59186,10 +59186,10 @@
         <v>3.3</v>
       </c>
       <c r="CL148" t="n">
-        <v>-51.91284967336638</v>
+        <v>-51.91284973031512</v>
       </c>
       <c r="CM148" t="n">
-        <v>-39.65023665870151</v>
+        <v>-39.65023671840002</v>
       </c>
       <c r="CN148" t="inlineStr">
         <is>
@@ -59370,13 +59370,13 @@
         <v>1</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AS149" t="b">
         <v>1</v>
       </c>
       <c r="AT149" t="n">
-        <v>50658746368</v>
+        <v>50465071104</v>
       </c>
       <c r="AU149" t="n">
         <v>53.28</v>
@@ -59782,10 +59782,10 @@
         <v>15.35000038146973</v>
       </c>
       <c r="BX150" t="n">
-        <v>3.926986152100071</v>
+        <v>3.926986143114278</v>
       </c>
       <c r="BY150" t="n">
-        <v>5.717691837457703</v>
+        <v>5.717691824374389</v>
       </c>
       <c r="BZ150" t="inlineStr"/>
       <c r="CA150" t="inlineStr"/>
@@ -59796,7 +59796,7 @@
         <v>5.502528941537498</v>
       </c>
       <c r="CF150" t="n">
-        <v>5.049068977031758</v>
+        <v>5.049068969675388</v>
       </c>
       <c r="CG150" t="n">
         <v>5.502528941537498</v>
@@ -59817,7 +59817,7 @@
         <v>-67.7376161282572</v>
       </c>
       <c r="CM150" t="n">
-        <v>-67.10704331234471</v>
+        <v>-67.10704336026895</v>
       </c>
       <c r="CN150" t="inlineStr">
         <is>

--- a/reports/screener_2026-08-27.xlsx
+++ b/reports/screener_2026-08-27.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -1186,10 +1186,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.86871597626807</v>
+        <v>5.86871607436566</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646813597727</v>
+        <v>10.8864683179483</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.21781573324146</v>
@@ -1198,7 +1198,7 @@
         <v>27.66761889587421</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.26108647233362</v>
+        <v>71.26108688352113</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -1238,16 +1238,8 @@
           <t>próxima</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>A JHSF3 apresenta uma notável assimetria de valor ao conjugar alta qualidade operacional com múltiplos de preço deprimidos, evidenciada por um ROE de 28,4% e um ROIC de 13,1% que se posicionam confortavelmente acima das médias setoriais de 15,2% e 9,1%, respectivamente, enquanto o papel é negociado a um P/L de apenas 3,34 vezes e com desconto sobre o valor patrimonial, dado o P/VP de 0,95. Essa forte rentabilidade convive com uma estrutura de endividamento bastante controlada, visto que a relação Dívida Líquida/EBITDA de 1,22 vezes está substancialmente abaixo da média do setor de 16,75 vezes, garantindo folga financeira mesmo com uma relação Dívida/Patrimônio de 0,86 e liquidez corrente de 1,73. O retorno em proventos é robusto, com um dividend yield de 6,48% que se mostra sustentável diante das margens elevadas, especialmente a margem líquida de 52,59%, e da sólida geração de caixa da companhia. No quesito expansão, a empresa supera drasticamente seus pares com um CAGR de receita de cinco anos de 90,2%, frente a uma média setorial quase estagnada de 0,2%, o que corrobora o excelente desempenho no checklist de critérios, onde a empresa atende a 7 de 8 requisitos, falhando apenas na questão das transações de insiders. Sob a ótica de valuation, as estimativas de preço-teto revelam uma dispersão extrema entre os métodos, variando desde a visão mais conservadora de Bazin a R$ 5,87, passando pelo modelo de Gordon a R$ 10,89, até projeções altamente otimistas como a de Graham a R$ 27,67, o fluxo de caixa descontado a R$ 41,22 e o modelo de Lynch a R$ 71,26, sugerindo que o preço atual de R$ 10,39 embute margens de segurança distintas a depender da metodologia adotada. Em um balanço final, os prós residem no crescimento exponencial das receitas, na rentabilidade muito acima dos pares e no endividamento sob controle, ao passo que os contras concentram-se na tendência de baixa do papel no mercado, na venda de ações por insiders e na pontuação de segurança moderada de 45 pontos.</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
       <c r="CS2" t="b">
         <v>0</v>
       </c>
@@ -1274,14 +1266,14 @@
         <v>1</v>
       </c>
       <c r="DB2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
@@ -1512,10 +1504,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01485126196847</v>
+        <v>15.01485122142624</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85254909095152</v>
+        <v>27.85254901574567</v>
       </c>
       <c r="BZ3" t="n">
         <v>39.46006465010361</v>
@@ -1524,13 +1516,13 @@
         <v>23.87433491384053</v>
       </c>
       <c r="CB3" t="n">
-        <v>76.71128035255107</v>
+        <v>76.71128042734917</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.54748518859483</v>
+        <v>48.54748521800145</v>
       </c>
       <c r="CD3" t="n">
-        <v>27.26172495066282</v>
+        <v>27.26172507574696</v>
       </c>
       <c r="CE3" t="n">
         <v>8.973116408407053</v>
@@ -1830,10 +1822,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388477265026</v>
+        <v>16.25388479636543</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.15095625326622</v>
+        <v>30.15095629725787</v>
       </c>
       <c r="BZ4" t="n">
         <v>70.99454413334874</v>
@@ -1842,19 +1834,19 @@
         <v>51.39538022233962</v>
       </c>
       <c r="CB4" t="n">
-        <v>124.8365656332173</v>
+        <v>124.8365656247644</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.69771469318724</v>
+        <v>25.69771468978261</v>
       </c>
       <c r="CD4" t="n">
-        <v>61.55225158345913</v>
+        <v>61.55225153257966</v>
       </c>
       <c r="CE4" t="n">
         <v>43.02986521586298</v>
       </c>
       <c r="CF4" t="n">
-        <v>47.13678535024399</v>
+        <v>47.13678534852858</v>
       </c>
       <c r="CG4" t="n">
         <v>47.2126227191013</v>
@@ -1875,7 +1867,7 @@
         <v>73.15142160530792</v>
       </c>
       <c r="CM4" t="n">
-        <v>92.08143272895661</v>
+        <v>92.08143272196634</v>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
@@ -2156,10 +2148,10 @@
         <v>4.059999942779541</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.548072834096487</v>
+        <v>3.548072808520895</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.581675107248985</v>
+        <v>6.581675059806259</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.56892505650208</v>
@@ -2168,25 +2160,25 @@
         <v>8.462578627869229</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.40274523318439</v>
+        <v>24.40274525092802</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.26517503191264</v>
+        <v>11.26517504252334</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.57787752272904</v>
+        <v>10.57787758646752</v>
       </c>
       <c r="CE5" t="n">
         <v>5.216748691568468</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.112163339638409</v>
+        <v>9.112163344122814</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.520228075299137</v>
+        <v>9.520228107168373</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.568205267769224</v>
+        <v>8.568205296451536</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -2198,10 +2190,10 @@
         <v>6.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>111.0395415893354</v>
+        <v>111.0395422957963</v>
       </c>
       <c r="CM5" t="n">
-        <v>124.4375238439062</v>
+        <v>124.4375239543595</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -2240,7 +2232,7 @@
         <v>-7.709252891958918</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-37.84196722993377</v>
+        <v>-37.84197197468594</v>
       </c>
       <c r="DA5" t="b">
         <v>1</v>
@@ -2466,10 +2458,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294920812385</v>
+        <v>18.38294920595807</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037078106974</v>
+        <v>34.10037077705221</v>
       </c>
       <c r="BZ6" t="n">
         <v>75.02112937085505</v>
@@ -2478,23 +2470,23 @@
         <v>56.1385860856476</v>
       </c>
       <c r="CB6" t="n">
-        <v>100.7448467822811</v>
+        <v>100.7448467856476</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.40369998271307</v>
+        <v>48.40369998323953</v>
       </c>
       <c r="CD6" t="n">
-        <v>59.46380242020545</v>
+        <v>59.4638024245585</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>43.97703733569043</v>
+        <v>43.97703733427621</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.2520353818914</v>
+        <v>41.25203538014587</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.12683184370226</v>
+        <v>37.12683184213128</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -2506,10 +2498,10 @@
         <v>4.1</v>
       </c>
       <c r="CL6" t="n">
-        <v>-23.03725009969308</v>
+        <v>-23.03725010294967</v>
       </c>
       <c r="CM6" t="n">
-        <v>-8.836990452840842</v>
+        <v>-8.836990455772465</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -2792,10 +2784,10 @@
         <v>4.380000114440918</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774202256612</v>
+        <v>3.052774215928209</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.662896145186015</v>
+        <v>5.662896170546828</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.64379118003097</v>
@@ -2804,7 +2796,7 @@
         <v>8.50525545154361</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.62501972727807</v>
+        <v>23.62501976897793</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -2816,7 +2808,7 @@
         <v>5.24246353170767</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.25728133262403</v>
+        <v>11.25728134220413</v>
       </c>
       <c r="CG7" t="n">
         <v>11.54640553044338</v>
@@ -2837,7 +2829,7 @@
         <v>137.2549019607844</v>
       </c>
       <c r="CM7" t="n">
-        <v>157.0155488240429</v>
+        <v>157.0155490427665</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -3122,10 +3114,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX8" t="n">
-        <v>121.1494733628736</v>
+        <v>121.1494722327765</v>
       </c>
       <c r="BY8" t="n">
-        <v>224.7322730881305</v>
+        <v>224.7322709918004</v>
       </c>
       <c r="BZ8" t="n">
         <v>136.6302942100011</v>
@@ -3146,13 +3138,13 @@
         <v>57.66739801003497</v>
       </c>
       <c r="CF8" t="n">
-        <v>116.3031162949942</v>
+        <v>116.3031158340761</v>
       </c>
       <c r="CG8" t="n">
-        <v>121.1494733628736</v>
+        <v>121.1494722327765</v>
       </c>
       <c r="CH8" t="n">
-        <v>109.0345260265862</v>
+        <v>109.0345250094988</v>
       </c>
       <c r="CI8" t="n">
         <v>7</v>
@@ -3164,10 +3156,10 @@
         <v>5.5</v>
       </c>
       <c r="CL8" t="n">
-        <v>163.6868925033347</v>
+        <v>163.6868900436311</v>
       </c>
       <c r="CM8" t="n">
-        <v>181.265104200143</v>
+        <v>181.2651030854678</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -3450,10 +3442,10 @@
         <v>15.75</v>
       </c>
       <c r="BX9" t="n">
-        <v>6.426879098208645</v>
+        <v>6.426879081406029</v>
       </c>
       <c r="BY9" t="n">
-        <v>11.92186072717704</v>
+        <v>11.92186069600818</v>
       </c>
       <c r="BZ9" t="n">
         <v>25.54314565483476</v>
@@ -3462,19 +3454,19 @@
         <v>18.71731215268055</v>
       </c>
       <c r="CB9" t="n">
-        <v>35.49020392821991</v>
+        <v>35.49020395543702</v>
       </c>
       <c r="CC9" t="n">
-        <v>12.3012310204747</v>
+        <v>12.30123102364604</v>
       </c>
       <c r="CD9" t="n">
-        <v>20.5356023493967</v>
+        <v>20.53560238460287</v>
       </c>
       <c r="CE9" t="n">
         <v>18.47523885586486</v>
       </c>
       <c r="CF9" t="n">
-        <v>20.42637066980694</v>
+        <v>20.4263706747249</v>
       </c>
       <c r="CG9" t="n">
         <v>18.71731215268055</v>
@@ -3495,7 +3487,7 @@
         <v>6.956069443888868</v>
       </c>
       <c r="CM9" t="n">
-        <v>29.69124234798055</v>
+        <v>29.69124237920568</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -3778,37 +3770,37 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX10" t="n">
-        <v>24.20136299867336</v>
+        <v>24.20136283206105</v>
       </c>
       <c r="BY10" t="n">
-        <v>37.09024677252115</v>
+        <v>37.09024832555132</v>
       </c>
       <c r="BZ10" t="n">
-        <v>39.76037966515335</v>
+        <v>39.76038160371352</v>
       </c>
       <c r="CA10" t="n">
         <v>21.15376420319533</v>
       </c>
       <c r="CB10" t="n">
-        <v>53.96364405261692</v>
+        <v>53.96364534093689</v>
       </c>
       <c r="CC10" t="n">
-        <v>51.52714046459301</v>
+        <v>51.5271406748783</v>
       </c>
       <c r="CD10" t="n">
-        <v>19.8802225989987</v>
+        <v>19.88022357225448</v>
       </c>
       <c r="CE10" t="n">
         <v>24.52549486359719</v>
       </c>
       <c r="CF10" t="n">
-        <v>34.01278195241862</v>
+        <v>34.01278267702351</v>
       </c>
       <c r="CG10" t="n">
-        <v>30.80787081805916</v>
+        <v>30.80787159457425</v>
       </c>
       <c r="CH10" t="n">
-        <v>27.72708373625325</v>
+        <v>27.72708443511683</v>
       </c>
       <c r="CI10" t="n">
         <v>8</v>
@@ -3820,10 +3812,10 @@
         <v>2.7</v>
       </c>
       <c r="CL10" t="n">
-        <v>-14.89538926353197</v>
+        <v>-14.89538711846279</v>
       </c>
       <c r="CM10" t="n">
-        <v>4.397728793244671</v>
+        <v>4.397731017323392</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -4114,10 +4106,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.05539002065863</v>
+        <v>46.05538996044413</v>
       </c>
       <c r="BY11" t="n">
-        <v>85.43274848832176</v>
+        <v>85.43274837662385</v>
       </c>
       <c r="BZ11" t="n">
         <v>69.47297200868543</v>
@@ -4138,7 +4130,7 @@
         <v>25.94666723750103</v>
       </c>
       <c r="CF11" t="n">
-        <v>78.49436731887342</v>
+        <v>78.4943672943145</v>
       </c>
       <c r="CG11" t="n">
         <v>69.47297200868543</v>
@@ -4159,7 +4151,7 @@
         <v>89.58664546899841</v>
       </c>
       <c r="CM11" t="n">
-        <v>138.0059684911409</v>
+        <v>138.0059684166748</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -4444,10 +4436,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX12" t="n">
-        <v>127.6301650953702</v>
+        <v>127.6301656980486</v>
       </c>
       <c r="BY12" t="n">
-        <v>236.7539562519117</v>
+        <v>236.7539573698802</v>
       </c>
       <c r="BZ12" t="n">
         <v>137.215088724016</v>
@@ -4468,13 +4460,13 @@
         <v>56.54612056896573</v>
       </c>
       <c r="CF12" t="n">
-        <v>142.9573014686699</v>
+        <v>142.9573016837507</v>
       </c>
       <c r="CG12" t="n">
-        <v>126.4680098518585</v>
+        <v>126.4680101531977</v>
       </c>
       <c r="CH12" t="n">
-        <v>113.8212088666726</v>
+        <v>113.8212091378779</v>
       </c>
       <c r="CI12" t="n">
         <v>8</v>
@@ -4486,10 +4478,10 @@
         <v>5.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>147.5450413219745</v>
+        <v>147.5450419118077</v>
       </c>
       <c r="CM12" t="n">
-        <v>210.9119245148145</v>
+        <v>210.9119249825849</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -4528,7 +4520,7 @@
         <v>-4.327813207567233</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-13.44221145597109</v>
+        <v>-13.4422178413344</v>
       </c>
       <c r="DA12" t="b">
         <v>1</v>
@@ -4603,7 +4595,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -4754,10 +4746,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX13" t="n">
-        <v>13.15731118693232</v>
+        <v>13.15731128507561</v>
       </c>
       <c r="BY13" t="n">
-        <v>24.40681225175945</v>
+        <v>24.40681243381526</v>
       </c>
       <c r="BZ13" t="n">
         <v>19.90620030713044</v>
@@ -4766,7 +4758,7 @@
         <v>12.44114419785431</v>
       </c>
       <c r="CB13" t="n">
-        <v>33.68872439596174</v>
+        <v>33.68872450381151</v>
       </c>
       <c r="CC13" t="n">
         <v>22.8984489302328</v>
@@ -4776,7 +4768,7 @@
       </c>
       <c r="CE13" t="inlineStr"/>
       <c r="CF13" t="n">
-        <v>20.09219316901375</v>
+        <v>20.09219323906353</v>
       </c>
       <c r="CG13" t="n">
         <v>21.40232461868162</v>
@@ -4797,7 +4789,7 @@
         <v>0.6378932657179259</v>
       </c>
       <c r="CM13" t="n">
-        <v>4.974889288033602</v>
+        <v>4.974889654019887</v>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
@@ -4815,11 +4807,7 @@
         </is>
       </c>
       <c r="CQ13" t="inlineStr"/>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="b">
         <v>0</v>
       </c>
@@ -4846,14 +4834,14 @@
         <v>1</v>
       </c>
       <c r="DB13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.1%))</t>
         </is>
       </c>
     </row>
@@ -5084,10 +5072,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX14" t="n">
-        <v>3.363729732974996</v>
+        <v>3.363729731674687</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.239718654668616</v>
+        <v>6.239718652256543</v>
       </c>
       <c r="BZ14" t="n">
         <v>20.7379196371351</v>
@@ -5096,7 +5084,7 @@
         <v>14.20601824710207</v>
       </c>
       <c r="CB14" t="n">
-        <v>33.37021289929139</v>
+        <v>33.37021289546695</v>
       </c>
       <c r="CC14" t="n">
         <v>10.95072400487419</v>
@@ -5410,10 +5398,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX15" t="n">
-        <v>10.74426546359599</v>
+        <v>10.74426550839139</v>
       </c>
       <c r="BY15" t="n">
-        <v>19.93061243497056</v>
+        <v>19.93061251806602</v>
       </c>
       <c r="BZ15" t="n">
         <v>37.5845483977432</v>
@@ -5422,25 +5410,25 @@
         <v>37.1651975122017</v>
       </c>
       <c r="CB15" t="n">
-        <v>41.90042983588201</v>
+        <v>41.90042985470379</v>
       </c>
       <c r="CC15" t="n">
-        <v>34.50408897966985</v>
+        <v>34.50408897020166</v>
       </c>
       <c r="CD15" t="n">
-        <v>18.61582867267827</v>
+        <v>18.61582862072277</v>
       </c>
       <c r="CE15" t="n">
         <v>31.97921770241074</v>
       </c>
       <c r="CF15" t="n">
-        <v>31.66856050507948</v>
+        <v>31.66856051086427</v>
       </c>
       <c r="CG15" t="n">
-        <v>34.50408897966985</v>
+        <v>34.50408897020166</v>
       </c>
       <c r="CH15" t="n">
-        <v>31.05368008170287</v>
+        <v>31.05368007318149</v>
       </c>
       <c r="CI15" t="n">
         <v>7</v>
@@ -5452,10 +5440,10 @@
         <v>3.9</v>
       </c>
       <c r="CL15" t="n">
-        <v>77.14591480512493</v>
+        <v>77.14591475651471</v>
       </c>
       <c r="CM15" t="n">
-        <v>80.65350407661329</v>
+        <v>80.65350410961265</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -5740,10 +5728,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX16" t="n">
-        <v>5.044350326490063</v>
+        <v>5.044350317209677</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.357269855639066</v>
+        <v>9.357269838423951</v>
       </c>
       <c r="BZ16" t="n">
         <v>8.531826591579675</v>
@@ -6058,37 +6046,37 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX17" t="n">
-        <v>10.3786331450779</v>
+        <v>10.37863317753584</v>
       </c>
       <c r="BY17" t="n">
-        <v>18.07553066680664</v>
+        <v>18.07553058377986</v>
       </c>
       <c r="BZ17" t="n">
-        <v>23.22146511989621</v>
+        <v>23.22146494061011</v>
       </c>
       <c r="CA17" t="n">
         <v>17.75681071950086</v>
       </c>
       <c r="CB17" t="n">
-        <v>36.48041917740331</v>
+        <v>36.48041914613081</v>
       </c>
       <c r="CC17" t="n">
-        <v>24.12244065927788</v>
+        <v>24.12244064542064</v>
       </c>
       <c r="CD17" t="n">
-        <v>11.46100458572084</v>
+        <v>11.461004514599</v>
       </c>
       <c r="CE17" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF17" t="n">
-        <v>18.98203796629511</v>
+        <v>18.9820379230318</v>
       </c>
       <c r="CG17" t="n">
-        <v>17.91617069315375</v>
+        <v>17.91617065164036</v>
       </c>
       <c r="CH17" t="n">
-        <v>16.12455362383837</v>
+        <v>16.12455358647632</v>
       </c>
       <c r="CI17" t="n">
         <v>8</v>
@@ -6100,10 +6088,10 @@
         <v>3.5</v>
       </c>
       <c r="CL17" t="n">
-        <v>55.64241465438411</v>
+        <v>55.64241429374657</v>
       </c>
       <c r="CM17" t="n">
-        <v>83.22431076588668</v>
+        <v>83.22431034828712</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -6386,10 +6374,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX18" t="n">
-        <v>3.454302376873577</v>
+        <v>3.454302387244496</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.407730909100485</v>
+        <v>6.407730928338538</v>
       </c>
       <c r="BZ18" t="n">
         <v>20.16620865234961</v>
@@ -6398,13 +6386,13 @@
         <v>19.00949927082382</v>
       </c>
       <c r="CB18" t="n">
-        <v>21.60588271687798</v>
+        <v>21.60588271589976</v>
       </c>
       <c r="CC18" t="n">
-        <v>15.92827012624657</v>
+        <v>15.92827012425295</v>
       </c>
       <c r="CD18" t="n">
-        <v>13.4711657642254</v>
+        <v>13.47116575107425</v>
       </c>
       <c r="CE18" t="n">
         <v>30.336208848481</v>
@@ -6460,7 +6448,7 @@
         <v>-18.94659940111765</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-32.89648837260555</v>
+        <v>-32.89649636084019</v>
       </c>
       <c r="DA18" t="b">
         <v>1</v>
@@ -6704,10 +6692,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX19" t="n">
-        <v>9.774107128522251</v>
+        <v>9.774107112442596</v>
       </c>
       <c r="BY19" t="n">
-        <v>18.13096872340877</v>
+        <v>18.13096869358102</v>
       </c>
       <c r="BZ19" t="n">
         <v>22.32723873053024</v>
@@ -6716,25 +6704,25 @@
         <v>13.19107667093893</v>
       </c>
       <c r="CB19" t="n">
-        <v>32.07171957325589</v>
+        <v>32.07171962245396</v>
       </c>
       <c r="CC19" t="n">
-        <v>25.27239703816369</v>
+        <v>25.27239704977857</v>
       </c>
       <c r="CD19" t="n">
-        <v>11.8232898334598</v>
+        <v>11.82328988550385</v>
       </c>
       <c r="CE19" t="n">
         <v>9.733055502947964</v>
       </c>
       <c r="CF19" t="n">
-        <v>17.79048165015344</v>
+        <v>17.79048165852214</v>
       </c>
       <c r="CG19" t="n">
-        <v>15.66102269717385</v>
+        <v>15.66102268225998</v>
       </c>
       <c r="CH19" t="n">
-        <v>14.09492042745647</v>
+        <v>14.09492041403398</v>
       </c>
       <c r="CI19" t="n">
         <v>8</v>
@@ -6746,10 +6734,10 @@
         <v>3.3</v>
       </c>
       <c r="CL19" t="n">
-        <v>24.8442911876066</v>
+        <v>24.84429106871831</v>
       </c>
       <c r="CM19" t="n">
-        <v>57.57734021491962</v>
+        <v>57.57734028904451</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -7032,10 +7020,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX20" t="n">
-        <v>7.290978528882397</v>
+        <v>7.290978517778295</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.52476517107684</v>
+        <v>13.52476515047874</v>
       </c>
       <c r="BZ20" t="n">
         <v>35.92512375028262</v>
@@ -7044,19 +7032,19 @@
         <v>28.41024685094796</v>
       </c>
       <c r="CB20" t="n">
-        <v>44.7474925273167</v>
+        <v>44.74749254390056</v>
       </c>
       <c r="CC20" t="n">
-        <v>26.46268145030354</v>
+        <v>26.46268145306381</v>
       </c>
       <c r="CD20" t="n">
-        <v>29.04887751514411</v>
+        <v>29.04887753519546</v>
       </c>
       <c r="CE20" t="n">
         <v>24.98203479043206</v>
       </c>
       <c r="CF20" t="n">
-        <v>29.0144602936434</v>
+        <v>29.01446029632875</v>
       </c>
       <c r="CG20" t="n">
         <v>28.41024685094796</v>
@@ -7077,7 +7065,7 @@
         <v>-7.088583791648039</v>
       </c>
       <c r="CM20" t="n">
-        <v>5.430449894698786</v>
+        <v>5.430449904456558</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -7191,7 +7179,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -7340,10 +7328,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX21" t="n">
-        <v>35.62892560284679</v>
+        <v>35.62892564590315</v>
       </c>
       <c r="BY21" t="n">
-        <v>51.87571567774493</v>
+        <v>51.875715740435</v>
       </c>
       <c r="BZ21" t="n">
         <v>48.56662855571916</v>
@@ -7360,13 +7348,13 @@
       </c>
       <c r="CE21" t="inlineStr"/>
       <c r="CF21" t="n">
-        <v>48.89385870503214</v>
+        <v>48.89385873146875</v>
       </c>
       <c r="CG21" t="n">
-        <v>50.22117211673205</v>
+        <v>50.22117214807708</v>
       </c>
       <c r="CH21" t="n">
-        <v>45.19905490505884</v>
+        <v>45.19905493326937</v>
       </c>
       <c r="CI21" t="n">
         <v>4</v>
@@ -7378,10 +7366,10 @@
         <v>1.7</v>
       </c>
       <c r="CL21" t="n">
-        <v>16.19293864291851</v>
+        <v>16.19293871543917</v>
       </c>
       <c r="CM21" t="n">
-        <v>25.6911485530525</v>
+        <v>25.69114862101294</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -7399,11 +7387,7 @@
         </is>
       </c>
       <c r="CQ21" t="inlineStr"/>
-      <c r="CR21" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR21" t="inlineStr"/>
       <c r="CS21" t="b">
         <v>0</v>
       </c>
@@ -7430,14 +7414,14 @@
         <v>1</v>
       </c>
       <c r="DB21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD21" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -7668,10 +7652,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.108740528356239</v>
+        <v>3.108740529578116</v>
       </c>
       <c r="BY22" t="n">
-        <v>5.766713680100823</v>
+        <v>5.766713682367405</v>
       </c>
       <c r="BZ22" t="n">
         <v>31.95928917556512</v>
@@ -7680,7 +7664,7 @@
         <v>26.70105358379499</v>
       </c>
       <c r="CB22" t="n">
-        <v>40.93687025348094</v>
+        <v>40.93687025535048</v>
       </c>
       <c r="CC22" t="n">
         <v>10.85340539909456</v>
@@ -7986,10 +7970,10 @@
         <v>32.75</v>
       </c>
       <c r="BX23" t="n">
-        <v>3.249356697982276</v>
+        <v>3.249356708540788</v>
       </c>
       <c r="BY23" t="n">
-        <v>6.027556674757121</v>
+        <v>6.027556694343162</v>
       </c>
       <c r="BZ23" t="n">
         <v>32.74999999999999</v>
@@ -7998,7 +7982,7 @@
         <v>22.94333650394972</v>
       </c>
       <c r="CB23" t="n">
-        <v>40.50875424692467</v>
+        <v>40.50875425808083</v>
       </c>
       <c r="CC23" t="n">
         <v>10.59424454785779</v>
@@ -8038,7 +8022,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ23" t="inlineStr"/>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>A TOTVS (TOTS3) apresenta uma sólida eficiência operacional no setor de tecnologia da informação, com um ROE de 26,1% e um ROIC de 23,4% que se posicionam significativamente acima dos pares setoriais (9,1% e 13,4%, respectivamente), sugerindo uma forte capacidade de geração de valor sobre o capital empregado. Essa elevada qualidade operacional convive com múltiplos de valuation que exigem atenção, pois o P/VP de 3,46 indica um prêmio em relação ao valor patrimonial, embora o P/L de 13,25 e o PEG de 0,88 sinalizem que o preço atual está atrativo quando confrontado com o forte ritmo de crescimento dos lucros. No âmbito financeiro, a excelente rentabilidade, traduzida em uma margem líquida de 21,63%, ajuda a suportar um endividamento cuja relação Dívida Líquida/EBITDA de 2,09 está acima da média do setor (1,39), mas que permanece sob controle e bem respaldada por uma liquidez corrente confortável de 1,84. Essa alavancagem mais alta e o foco na expansão explicam o modesto dividend yield de 2,16%, demonstrando que a companhia prioriza a retenção de caixa para sustentar seu crescimento em detrimento de proventos agressivos. O perfil de expansão da empresa é altamente robusto, evidenciado por um impressionante CAGR de receita de cinco anos de 269,5%, patamar que supera com folga a média setorial de 74,1%. No checklist de critérios fundamentalistas, a TOTS3 atende a 6 dos 8 requisitos avaliados, falhando apenas na relação de endividamento comparada ao setor e no registro de venda de ações por parte de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma enorme dispersão entre as metodologias, variando desde patamares muito baixos nos modelos de fluxo de caixa de dividendos, como Bazin (R$ 3,25) e Gordon (R$ 6,03), até avaliações mais generosas baseadas em crescimento e fluxo de caixa livre, como Graham (R$ 22,94), o próprio preço atual via DCF (R$ 32,75) e o modelo de Lynch (R$ 40,51), o qual aponta o maior potencial de valorização. Como prós, destacam-se o crescimento exponencial da receita, a rentabilidade muito acima da média e a forte tendência de alta no sinal gráfico de rompimento; como contras, pesam o endividamento superior ao dos pares, a distribuição tímida de dividendos e a pressão vendedora de insiders.</t>
+        </is>
+      </c>
       <c r="CR23" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -8064,7 +8052,7 @@
         <v>0.738239590458023</v>
       </c>
       <c r="CZ23" t="n">
-        <v>-31.31834368818209</v>
+        <v>-31.318349352401</v>
       </c>
       <c r="DA23" t="b">
         <v>1</v>
@@ -8135,7 +8123,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -8288,35 +8276,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX24" t="n">
-        <v>8.627042091816078</v>
+        <v>8.627042087914047</v>
       </c>
       <c r="BY24" t="n">
-        <v>13.85196401738628</v>
+        <v>13.85196402192589</v>
       </c>
       <c r="BZ24" t="n">
-        <v>18.49124791236634</v>
+        <v>18.49124792678998</v>
       </c>
       <c r="CA24" t="n">
         <v>17.39822241629838</v>
       </c>
       <c r="CB24" t="n">
-        <v>22.98547046825374</v>
+        <v>22.98547047197555</v>
       </c>
       <c r="CC24" t="n">
-        <v>17.33681285450712</v>
+        <v>17.33681285559167</v>
       </c>
       <c r="CD24" t="n">
-        <v>9.229677229939698</v>
+        <v>9.229677236587511</v>
       </c>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="n">
-        <v>14.57676671901895</v>
+        <v>14.5767667230554</v>
       </c>
       <c r="CG24" t="n">
-        <v>15.5943884359467</v>
+        <v>15.59438843875878</v>
       </c>
       <c r="CH24" t="n">
-        <v>14.03494959235203</v>
+        <v>14.0349495948829</v>
       </c>
       <c r="CI24" t="n">
         <v>4</v>
@@ -8328,10 +8316,10 @@
         <v>2.1</v>
       </c>
       <c r="CL24" t="n">
-        <v>9.221394363466739</v>
+        <v>9.221394383162252</v>
       </c>
       <c r="CM24" t="n">
-        <v>13.43786993220093</v>
+        <v>13.43786996361298</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -8349,11 +8337,7 @@
         </is>
       </c>
       <c r="CQ24" t="inlineStr"/>
-      <c r="CR24" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR24" t="inlineStr"/>
       <c r="CS24" t="b">
         <v>0</v>
       </c>
@@ -8380,14 +8364,14 @@
         <v>1</v>
       </c>
       <c r="DB24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD24" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
         </is>
       </c>
     </row>
@@ -8598,10 +8582,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX25" t="n">
-        <v>9.186484939067871</v>
+        <v>9.186484962458096</v>
       </c>
       <c r="BY25" t="n">
-        <v>17.0409295619709</v>
+        <v>17.04092960535977</v>
       </c>
       <c r="BZ25" t="n">
         <v>30.69514051126462</v>
@@ -8610,23 +8594,23 @@
         <v>29.25728964348931</v>
       </c>
       <c r="CB25" t="n">
-        <v>34.71948755840006</v>
+        <v>34.71948756345603</v>
       </c>
       <c r="CC25" t="n">
-        <v>25.51046014636512</v>
+        <v>25.51046014157115</v>
       </c>
       <c r="CD25" t="n">
-        <v>15.34133402372116</v>
+        <v>15.34133399463682</v>
       </c>
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="n">
-        <v>20.60825378966713</v>
+        <v>20.60825380516341</v>
       </c>
       <c r="CG25" t="n">
-        <v>21.27569485416801</v>
+        <v>21.27569487346546</v>
       </c>
       <c r="CH25" t="n">
-        <v>19.14812536875121</v>
+        <v>19.14812538611892</v>
       </c>
       <c r="CI25" t="n">
         <v>4</v>
@@ -8638,10 +8622,10 @@
         <v>3.3</v>
       </c>
       <c r="CL25" t="n">
-        <v>29.55430118199269</v>
+        <v>29.55430129950083</v>
       </c>
       <c r="CM25" t="n">
-        <v>39.43338404597046</v>
+        <v>39.43338415081674</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -8680,7 +8664,7 @@
         <v>-7.171627471148123</v>
       </c>
       <c r="CZ25" t="n">
-        <v>-18.7474872046273</v>
+        <v>-18.74746959920818</v>
       </c>
       <c r="DA25" t="b">
         <v>1</v>
@@ -8906,10 +8890,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX26" t="n">
-        <v>20.16127578131654</v>
+        <v>20.16127564389373</v>
       </c>
       <c r="BY26" t="n">
-        <v>37.39916657434217</v>
+        <v>37.39916631942287</v>
       </c>
       <c r="BZ26" t="n">
         <v>56.01071616333269</v>
@@ -8918,23 +8902,23 @@
         <v>42.36568036412405</v>
       </c>
       <c r="CB26" t="n">
-        <v>61.78700412157808</v>
+        <v>61.78700434729011</v>
       </c>
       <c r="CC26" t="n">
-        <v>45.16919925726728</v>
+        <v>45.16919930021541</v>
       </c>
       <c r="CD26" t="n">
-        <v>31.11427774290894</v>
+        <v>31.11427801440143</v>
       </c>
       <c r="CE26" t="inlineStr"/>
       <c r="CF26" t="n">
-        <v>39.68508944406467</v>
+        <v>39.68508935671618</v>
       </c>
       <c r="CG26" t="n">
-        <v>41.28418291580473</v>
+        <v>41.28418280981914</v>
       </c>
       <c r="CH26" t="n">
-        <v>37.15576462422425</v>
+        <v>37.15576452883723</v>
       </c>
       <c r="CI26" t="n">
         <v>4</v>
@@ -8946,10 +8930,10 @@
         <v>2.8</v>
       </c>
       <c r="CL26" t="n">
-        <v>-5.79166856496246</v>
+        <v>-5.791668806815975</v>
       </c>
       <c r="CM26" t="n">
-        <v>0.6214270433308577</v>
+        <v>0.6214268218589947</v>
       </c>
       <c r="CN26" t="inlineStr">
         <is>
@@ -8988,7 +8972,7 @@
         <v>-6.937240130506206</v>
       </c>
       <c r="CZ26" t="n">
-        <v>-19.01272601806555</v>
+        <v>-19.01273878297394</v>
       </c>
       <c r="DA26" t="b">
         <v>1</v>
@@ -9232,10 +9216,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX27" t="n">
-        <v>6.975750761435104</v>
+        <v>6.975750746615178</v>
       </c>
       <c r="BY27" t="n">
-        <v>12.94001766246212</v>
+        <v>12.94001763497115</v>
       </c>
       <c r="BZ27" t="n">
         <v>5.584946345257502</v>
@@ -9256,7 +9240,7 @@
         <v>5.373183328823668</v>
       </c>
       <c r="CF27" t="n">
-        <v>7.287571946166208</v>
+        <v>7.287571940877347</v>
       </c>
       <c r="CG27" t="n">
         <v>5.859139839295418</v>
@@ -9277,7 +9261,7 @@
         <v>-10.31928991948218</v>
       </c>
       <c r="CM27" t="n">
-        <v>23.93829599200825</v>
+        <v>23.93829590206163</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -9560,37 +9544,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX28" t="n">
-        <v>16.91883610520417</v>
+        <v>16.91883602994602</v>
       </c>
       <c r="BY28" t="n">
-        <v>28.00431313367254</v>
+        <v>28.00431312460474</v>
       </c>
       <c r="BZ28" t="n">
-        <v>46.83168332580541</v>
+        <v>46.83168351895741</v>
       </c>
       <c r="CA28" t="n">
         <v>52.67243426197095</v>
       </c>
       <c r="CB28" t="n">
-        <v>55.69855923746945</v>
+        <v>55.69855921365713</v>
       </c>
       <c r="CC28" t="n">
-        <v>43.03544429300022</v>
+        <v>43.03544430684217</v>
       </c>
       <c r="CD28" t="n">
-        <v>23.30397202537988</v>
+        <v>23.30397210955462</v>
       </c>
       <c r="CE28" t="n">
         <v>30.43448362223624</v>
       </c>
       <c r="CF28" t="n">
-        <v>37.11246575059236</v>
+        <v>37.11246577347116</v>
       </c>
       <c r="CG28" t="n">
-        <v>36.73496395761823</v>
+        <v>36.7349639645392</v>
       </c>
       <c r="CH28" t="n">
-        <v>33.06146756185641</v>
+        <v>33.06146756808528</v>
       </c>
       <c r="CI28" t="n">
         <v>8</v>
@@ -9602,10 +9586,10 @@
         <v>3.3</v>
       </c>
       <c r="CL28" t="n">
-        <v>24.94886132198564</v>
+        <v>24.94886134552636</v>
       </c>
       <c r="CM28" t="n">
-        <v>40.25875674489654</v>
+        <v>40.25875683136215</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -9717,7 +9701,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -9888,37 +9872,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX29" t="n">
-        <v>5.939526969706941</v>
+        <v>5.939526959977536</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.534880603381971</v>
+        <v>8.534880611414447</v>
       </c>
       <c r="BZ29" t="n">
-        <v>10.81501544468299</v>
+        <v>10.81501547257721</v>
       </c>
       <c r="CA29" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB29" t="n">
-        <v>9.810403804551399</v>
+        <v>9.810403820239834</v>
       </c>
       <c r="CC29" t="n">
-        <v>14.90925677887778</v>
+        <v>14.90925678229168</v>
       </c>
       <c r="CD29" t="n">
-        <v>5.384140030925815</v>
+        <v>5.38414004667967</v>
       </c>
       <c r="CE29" t="n">
         <v>11.00534556207784</v>
       </c>
       <c r="CF29" t="n">
-        <v>9.757252263278495</v>
+        <v>9.757252270910181</v>
       </c>
       <c r="CG29" t="n">
-        <v>10.31270962461719</v>
+        <v>10.31270964640852</v>
       </c>
       <c r="CH29" t="n">
-        <v>9.281438662155473</v>
+        <v>9.28143868176767</v>
       </c>
       <c r="CI29" t="n">
         <v>8</v>
@@ -9930,10 +9914,10 @@
         <v>2.8</v>
       </c>
       <c r="CL29" t="n">
-        <v>-39.37662699040055</v>
+        <v>-39.37662686229999</v>
       </c>
       <c r="CM29" t="n">
-        <v>-36.26876553983283</v>
+        <v>-36.26876548998512</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -9951,11 +9935,7 @@
         </is>
       </c>
       <c r="CQ29" t="inlineStr"/>
-      <c r="CR29" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR29" t="inlineStr"/>
       <c r="CS29" t="b">
         <v>0</v>
       </c>
@@ -9982,14 +9962,14 @@
         <v>1</v>
       </c>
       <c r="DB29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD29" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.5%))</t>
         </is>
       </c>
     </row>
@@ -10220,37 +10200,37 @@
         <v>38.86000061035156</v>
       </c>
       <c r="BX30" t="n">
-        <v>30.97422553975776</v>
+        <v>30.9742256602967</v>
       </c>
       <c r="BY30" t="n">
-        <v>35.52640287414108</v>
+        <v>35.52640278045922</v>
       </c>
       <c r="BZ30" t="n">
-        <v>38.58971747040682</v>
+        <v>38.58971721847183</v>
       </c>
       <c r="CA30" t="n">
         <v>49.80959882281965</v>
       </c>
       <c r="CB30" t="n">
-        <v>60.09290031647345</v>
+        <v>60.09290018115279</v>
       </c>
       <c r="CC30" t="n">
-        <v>16.76379308795554</v>
+        <v>16.76379307604998</v>
       </c>
       <c r="CD30" t="n">
-        <v>17.31674458272697</v>
+        <v>17.31674436909339</v>
       </c>
       <c r="CE30" t="n">
         <v>28.40888631687585</v>
       </c>
       <c r="CF30" t="n">
-        <v>34.68528362639464</v>
+        <v>34.68528355315243</v>
       </c>
       <c r="CG30" t="n">
-        <v>33.25031420694942</v>
+        <v>33.25031422037796</v>
       </c>
       <c r="CH30" t="n">
-        <v>29.92528278625448</v>
+        <v>29.92528279834016</v>
       </c>
       <c r="CI30" t="n">
         <v>8</v>
@@ -10262,10 +10242,10 @@
         <v>3.6</v>
       </c>
       <c r="CL30" t="n">
-        <v>-22.99206815173607</v>
+        <v>-22.99206812063549</v>
       </c>
       <c r="CM30" t="n">
-        <v>-10.74296685122762</v>
+        <v>-10.74296703970474</v>
       </c>
       <c r="CN30" t="inlineStr">
         <is>
@@ -10530,35 +10510,35 @@
         <v>16.78000068664551</v>
       </c>
       <c r="BX31" t="n">
-        <v>9.985664042179227</v>
+        <v>9.985664085228356</v>
       </c>
       <c r="BY31" t="n">
-        <v>17.51097130456651</v>
+        <v>17.51097129728228</v>
       </c>
       <c r="BZ31" t="n">
-        <v>28.91098001668654</v>
+        <v>28.91097988002219</v>
       </c>
       <c r="CA31" t="n">
         <v>29.08689850705222</v>
       </c>
       <c r="CB31" t="n">
-        <v>32.0896477401531</v>
+        <v>32.08964773789398</v>
       </c>
       <c r="CC31" t="n">
-        <v>27.8969568299852</v>
+        <v>27.8969568202356</v>
       </c>
       <c r="CD31" t="n">
-        <v>14.24941559744642</v>
+        <v>14.24941554391741</v>
       </c>
       <c r="CE31" t="inlineStr"/>
       <c r="CF31" t="n">
-        <v>21.07614304835437</v>
+        <v>21.07614302069211</v>
       </c>
       <c r="CG31" t="n">
-        <v>22.70396406727586</v>
+        <v>22.70396405875894</v>
       </c>
       <c r="CH31" t="n">
-        <v>20.43356766054827</v>
+        <v>20.43356765288305</v>
       </c>
       <c r="CI31" t="n">
         <v>4</v>
@@ -10570,10 +10550,10 @@
         <v>2.9</v>
       </c>
       <c r="CL31" t="n">
-        <v>21.77334221929135</v>
+        <v>21.77334217361064</v>
       </c>
       <c r="CM31" t="n">
-        <v>25.60275438562989</v>
+        <v>25.60275422077734</v>
       </c>
       <c r="CN31" t="inlineStr">
         <is>
@@ -10856,37 +10836,37 @@
         <v>44.2400016784668</v>
       </c>
       <c r="BX32" t="n">
-        <v>32.08627719702323</v>
+        <v>32.08627727406022</v>
       </c>
       <c r="BY32" t="n">
-        <v>44.20766641689121</v>
+        <v>44.20766626789196</v>
       </c>
       <c r="BZ32" t="n">
-        <v>50.92127200754537</v>
+        <v>50.92127171365978</v>
       </c>
       <c r="CA32" t="n">
         <v>47.73853825853298</v>
       </c>
       <c r="CB32" t="n">
-        <v>70.56922555068604</v>
+        <v>70.56922539177623</v>
       </c>
       <c r="CC32" t="n">
-        <v>59.893620859564</v>
+        <v>59.89362082767945</v>
       </c>
       <c r="CD32" t="n">
-        <v>25.15601706378459</v>
+        <v>25.15601688460888</v>
       </c>
       <c r="CE32" t="n">
         <v>76.57366731847841</v>
       </c>
       <c r="CF32" t="n">
-        <v>50.89328558406323</v>
+        <v>50.89328549208599</v>
       </c>
       <c r="CG32" t="n">
-        <v>49.32990513303918</v>
+        <v>49.32990498609638</v>
       </c>
       <c r="CH32" t="n">
-        <v>44.39691461973526</v>
+        <v>44.39691448748675</v>
       </c>
       <c r="CI32" t="n">
         <v>8</v>
@@ -10898,10 +10878,10 @@
         <v>3</v>
       </c>
       <c r="CL32" t="n">
-        <v>0.3546856584882185</v>
+        <v>0.3546853595539634</v>
       </c>
       <c r="CM32" t="n">
-        <v>15.03906793212177</v>
+        <v>15.03906772421661</v>
       </c>
       <c r="CN32" t="inlineStr">
         <is>
@@ -11166,10 +11146,10 @@
         <v>54.20000076293945</v>
       </c>
       <c r="BX33" t="n">
-        <v>10.5968759006117</v>
+        <v>10.59687588662215</v>
       </c>
       <c r="BY33" t="n">
-        <v>19.6572047956347</v>
+        <v>19.6572047696841</v>
       </c>
       <c r="BZ33" t="n">
         <v>62.12370329662177</v>
@@ -11178,7 +11158,7 @@
         <v>46.53820959650967</v>
       </c>
       <c r="CB33" t="n">
-        <v>83.16230744400134</v>
+        <v>83.16230742705898</v>
       </c>
       <c r="CC33" t="n">
         <v>11.76833333333333</v>
@@ -11188,7 +11168,7 @@
       </c>
       <c r="CE33" t="inlineStr"/>
       <c r="CF33" t="n">
-        <v>14.00747134319324</v>
+        <v>14.00747132987986</v>
       </c>
       <c r="CG33" t="n">
         <v>11.76833333333333</v>
@@ -11209,7 +11189,7 @@
         <v>-80.45848735994448</v>
       </c>
       <c r="CM33" t="n">
-        <v>-74.15595729516818</v>
+        <v>-74.15595731973161</v>
       </c>
       <c r="CN33" t="inlineStr">
         <is>
@@ -11474,10 +11454,10 @@
         <v>29.69000053405762</v>
       </c>
       <c r="BX34" t="n">
-        <v>15.52022462881667</v>
+        <v>15.52022456857821</v>
       </c>
       <c r="BY34" t="n">
-        <v>28.79001668645492</v>
+        <v>28.79001657471258</v>
       </c>
       <c r="BZ34" t="n">
         <v>54.71383964899351</v>
@@ -11486,23 +11466,23 @@
         <v>49.40805952371795</v>
       </c>
       <c r="CB34" t="n">
-        <v>60.9179064555565</v>
+        <v>60.91790647058306</v>
       </c>
       <c r="CC34" t="n">
-        <v>36.63500707769816</v>
+        <v>36.63500708862508</v>
       </c>
       <c r="CD34" t="n">
-        <v>30.32696327199993</v>
+        <v>30.32696335517236</v>
       </c>
       <c r="CE34" t="inlineStr"/>
       <c r="CF34" t="n">
-        <v>33.91477201049081</v>
+        <v>33.91477197022735</v>
       </c>
       <c r="CG34" t="n">
-        <v>32.71251188207653</v>
+        <v>32.71251183166883</v>
       </c>
       <c r="CH34" t="n">
-        <v>29.44126069386888</v>
+        <v>29.44126064850195</v>
       </c>
       <c r="CI34" t="n">
         <v>4</v>
@@ -11514,10 +11494,10 @@
         <v>3.5</v>
       </c>
       <c r="CL34" t="n">
-        <v>-0.8377899485161877</v>
+        <v>-0.8377901013182587</v>
       </c>
       <c r="CM34" t="n">
-        <v>14.22961064479244</v>
+        <v>14.22961050917957</v>
       </c>
       <c r="CN34" t="inlineStr">
         <is>
@@ -11560,7 +11540,7 @@
         <v>-0.8018702595090188</v>
       </c>
       <c r="CZ34" t="n">
-        <v>-18.56622956112421</v>
+        <v>-18.56623828442452</v>
       </c>
       <c r="DA34" t="b">
         <v>1</v>
@@ -11802,10 +11782,10 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX35" t="n">
-        <v>13.08696643078177</v>
+        <v>13.08696647328057</v>
       </c>
       <c r="BY35" t="n">
-        <v>19.05462312321825</v>
+        <v>19.05462318509651</v>
       </c>
       <c r="BZ35" t="n">
         <v>16.71315021106592</v>
@@ -11824,7 +11804,7 @@
         <v>14.7644299189986</v>
       </c>
       <c r="CF35" t="n">
-        <v>16.1591731493115</v>
+        <v>16.15917316670767</v>
       </c>
       <c r="CG35" t="n">
         <v>15.73879006503226</v>
@@ -11845,7 +11825,7 @@
         <v>34.77555423456011</v>
       </c>
       <c r="CM35" t="n">
-        <v>53.7504547802534</v>
+        <v>53.75045494577364</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -12128,37 +12108,37 @@
         <v>18.63999938964844</v>
       </c>
       <c r="BX36" t="n">
-        <v>8.745140376463256</v>
+        <v>8.74514040727321</v>
       </c>
       <c r="BY36" t="n">
-        <v>9.206222538315652</v>
+        <v>9.206222536748497</v>
       </c>
       <c r="BZ36" t="n">
-        <v>9.666395036062593</v>
+        <v>9.666395000361485</v>
       </c>
       <c r="CA36" t="n">
         <v>16.93457208699175</v>
       </c>
       <c r="CB36" t="n">
-        <v>9.239151917313791</v>
+        <v>9.239151890987216</v>
       </c>
       <c r="CC36" t="n">
-        <v>17.5422466592823</v>
+        <v>17.54224665167746</v>
       </c>
       <c r="CD36" t="n">
-        <v>3.934238755871024</v>
+        <v>3.934238720624436</v>
       </c>
       <c r="CE36" t="n">
         <v>16.16233025852235</v>
       </c>
       <c r="CF36" t="n">
-        <v>11.42878720360284</v>
+        <v>11.4287871941483</v>
       </c>
       <c r="CG36" t="n">
-        <v>9.452773476688192</v>
+        <v>9.45277344567435</v>
       </c>
       <c r="CH36" t="n">
-        <v>8.507496129019373</v>
+        <v>8.507496101106915</v>
       </c>
       <c r="CI36" t="n">
         <v>8</v>
@@ -12170,10 +12150,10 @@
         <v>4.5</v>
       </c>
       <c r="CL36" t="n">
-        <v>-54.35892485198291</v>
+        <v>-54.35892500172785</v>
       </c>
       <c r="CM36" t="n">
-        <v>-38.68676192151745</v>
+        <v>-38.68676197223924</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -12841,7 +12821,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -13012,10 +12992,10 @@
         <v>10.39000034332275</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.86871597626807</v>
+        <v>5.86871607436566</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.88646813597727</v>
+        <v>10.8864683179483</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.21781573324146</v>
@@ -13024,7 +13004,7 @@
         <v>27.66761889587421</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.26108647233362</v>
+        <v>71.26108688352113</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -13064,16 +13044,8 @@
           <t>próxima</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>A JHSF3 apresenta uma notável assimetria de valor ao conjugar alta qualidade operacional com múltiplos de preço deprimidos, evidenciada por um ROE de 28,4% e um ROIC de 13,1% que se posicionam confortavelmente acima das médias setoriais de 15,2% e 9,1%, respectivamente, enquanto o papel é negociado a um P/L de apenas 3,34 vezes e com desconto sobre o valor patrimonial, dado o P/VP de 0,95. Essa forte rentabilidade convive com uma estrutura de endividamento bastante controlada, visto que a relação Dívida Líquida/EBITDA de 1,22 vezes está substancialmente abaixo da média do setor de 16,75 vezes, garantindo folga financeira mesmo com uma relação Dívida/Patrimônio de 0,86 e liquidez corrente de 1,73. O retorno em proventos é robusto, com um dividend yield de 6,48% que se mostra sustentável diante das margens elevadas, especialmente a margem líquida de 52,59%, e da sólida geração de caixa da companhia. No quesito expansão, a empresa supera drasticamente seus pares com um CAGR de receita de cinco anos de 90,2%, frente a uma média setorial quase estagnada de 0,2%, o que corrobora o excelente desempenho no checklist de critérios, onde a empresa atende a 7 de 8 requisitos, falhando apenas na questão das transações de insiders. Sob a ótica de valuation, as estimativas de preço-teto revelam uma dispersão extrema entre os métodos, variando desde a visão mais conservadora de Bazin a R$ 5,87, passando pelo modelo de Gordon a R$ 10,89, até projeções altamente otimistas como a de Graham a R$ 27,67, o fluxo de caixa descontado a R$ 41,22 e o modelo de Lynch a R$ 71,26, sugerindo que o preço atual de R$ 10,39 embute margens de segurança distintas a depender da metodologia adotada. Em um balanço final, os prós residem no crescimento exponencial das receitas, na rentabilidade muito acima dos pares e no endividamento sob controle, ao passo que os contras concentram-se na tendência de baixa do papel no mercado, na venda de ações por insiders e na pontuação de segurança moderada de 45 pontos.</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
       <c r="CS2" t="b">
         <v>0</v>
       </c>
@@ -13100,14 +13072,14 @@
         <v>1</v>
       </c>
       <c r="DB2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-4.9%))</t>
         </is>
       </c>
     </row>
@@ -13338,10 +13310,10 @@
         <v>13.60999965667725</v>
       </c>
       <c r="BX3" t="n">
-        <v>15.01485126196847</v>
+        <v>15.01485122142624</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.85254909095152</v>
+        <v>27.85254901574567</v>
       </c>
       <c r="BZ3" t="n">
         <v>39.46006465010361</v>
@@ -13350,13 +13322,13 @@
         <v>23.87433491384053</v>
       </c>
       <c r="CB3" t="n">
-        <v>76.71128035255107</v>
+        <v>76.71128042734917</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.54748518859483</v>
+        <v>48.54748521800145</v>
       </c>
       <c r="CD3" t="n">
-        <v>27.26172495066282</v>
+        <v>27.26172507574696</v>
       </c>
       <c r="CE3" t="n">
         <v>8.973116408407053</v>
@@ -13656,10 +13628,10 @@
         <v>24.54000091552734</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.25388477265026</v>
+        <v>16.25388479636543</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.15095625326622</v>
+        <v>30.15095629725787</v>
       </c>
       <c r="BZ4" t="n">
         <v>70.99454413334874</v>
@@ -13668,19 +13640,19 @@
         <v>51.39538022233962</v>
       </c>
       <c r="CB4" t="n">
-        <v>124.8365656332173</v>
+        <v>124.8365656247644</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.69771469318724</v>
+        <v>25.69771468978261</v>
       </c>
       <c r="CD4" t="n">
-        <v>61.55225158345913</v>
+        <v>61.55225153257966</v>
       </c>
       <c r="CE4" t="n">
         <v>43.02986521586298</v>
       </c>
       <c r="CF4" t="n">
-        <v>47.13678535024399</v>
+        <v>47.13678534852858</v>
       </c>
       <c r="CG4" t="n">
         <v>47.2126227191013</v>
@@ -13701,7 +13673,7 @@
         <v>73.15142160530792</v>
       </c>
       <c r="CM4" t="n">
-        <v>92.08143272895661</v>
+        <v>92.08143272196634</v>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
@@ -13982,10 +13954,10 @@
         <v>4.059999942779541</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.548072834096487</v>
+        <v>3.548072808520895</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.581675107248985</v>
+        <v>6.581675059806259</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.56892505650208</v>
@@ -13994,25 +13966,25 @@
         <v>8.462578627869229</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.40274523318439</v>
+        <v>24.40274525092802</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.26517503191264</v>
+        <v>11.26517504252334</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.57787752272904</v>
+        <v>10.57787758646752</v>
       </c>
       <c r="CE5" t="n">
         <v>5.216748691568468</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.112163339638409</v>
+        <v>9.112163344122814</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.520228075299137</v>
+        <v>9.520228107168373</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.568205267769224</v>
+        <v>8.568205296451536</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -14024,10 +13996,10 @@
         <v>6.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>111.0395415893354</v>
+        <v>111.0395422957963</v>
       </c>
       <c r="CM5" t="n">
-        <v>124.4375238439062</v>
+        <v>124.4375239543595</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -14066,7 +14038,7 @@
         <v>-7.709252891958918</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-37.84196722993377</v>
+        <v>-37.84197197468594</v>
       </c>
       <c r="DA5" t="b">
         <v>1</v>
@@ -14292,10 +14264,10 @@
         <v>48.2400016784668</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.38294920812385</v>
+        <v>18.38294920595807</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.10037078106974</v>
+        <v>34.10037077705221</v>
       </c>
       <c r="BZ6" t="n">
         <v>75.02112937085505</v>
@@ -14304,23 +14276,23 @@
         <v>56.1385860856476</v>
       </c>
       <c r="CB6" t="n">
-        <v>100.7448467822811</v>
+        <v>100.7448467856476</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.40369998271307</v>
+        <v>48.40369998323953</v>
       </c>
       <c r="CD6" t="n">
-        <v>59.46380242020545</v>
+        <v>59.4638024245585</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>43.97703733569043</v>
+        <v>43.97703733427621</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.2520353818914</v>
+        <v>41.25203538014587</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.12683184370226</v>
+        <v>37.12683184213128</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -14332,10 +14304,10 @@
         <v>4.1</v>
       </c>
       <c r="CL6" t="n">
-        <v>-23.03725009969308</v>
+        <v>-23.03725010294967</v>
       </c>
       <c r="CM6" t="n">
-        <v>-8.836990452840842</v>
+        <v>-8.836990455772465</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -14618,10 +14590,10 @@
         <v>4.380000114440918</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.052774202256612</v>
+        <v>3.052774215928209</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.662896145186015</v>
+        <v>5.662896170546828</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.64379118003097</v>
@@ -14630,7 +14602,7 @@
         <v>8.50525545154361</v>
       </c>
       <c r="CB7" t="n">
-        <v>23.62501972727807</v>
+        <v>23.62501976897793</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -14642,7 +14614,7 @@
         <v>5.24246353170767</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.25728133262403</v>
+        <v>11.25728134220413</v>
       </c>
       <c r="CG7" t="n">
         <v>11.54640553044338</v>
@@ -14663,7 +14635,7 @@
         <v>137.2549019607844</v>
       </c>
       <c r="CM7" t="n">
-        <v>157.0155488240429</v>
+        <v>157.0155490427665</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -15158,10 +15130,10 @@
         <v>41.34999847412109</v>
       </c>
       <c r="BX9" t="n">
-        <v>121.1494733628736</v>
+        <v>121.1494722327765</v>
       </c>
       <c r="BY9" t="n">
-        <v>224.7322730881305</v>
+        <v>224.7322709918004</v>
       </c>
       <c r="BZ9" t="n">
         <v>136.6302942100011</v>
@@ -15182,13 +15154,13 @@
         <v>57.66739801003497</v>
       </c>
       <c r="CF9" t="n">
-        <v>116.3031162949942</v>
+        <v>116.3031158340761</v>
       </c>
       <c r="CG9" t="n">
-        <v>121.1494733628736</v>
+        <v>121.1494722327765</v>
       </c>
       <c r="CH9" t="n">
-        <v>109.0345260265862</v>
+        <v>109.0345250094988</v>
       </c>
       <c r="CI9" t="n">
         <v>7</v>
@@ -15200,10 +15172,10 @@
         <v>5.5</v>
       </c>
       <c r="CL9" t="n">
-        <v>163.6868925033347</v>
+        <v>163.6868900436311</v>
       </c>
       <c r="CM9" t="n">
-        <v>181.265104200143</v>
+        <v>181.2651030854678</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -15486,10 +15458,10 @@
         <v>15.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.426879098208645</v>
+        <v>6.426879081406029</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.92186072717704</v>
+        <v>11.92186069600818</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.54314565483476</v>
@@ -15498,19 +15470,19 @@
         <v>18.71731215268055</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.49020392821991</v>
+        <v>35.49020395543702</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.3012310204747</v>
+        <v>12.30123102364604</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.5356023493967</v>
+        <v>20.53560238460287</v>
       </c>
       <c r="CE10" t="n">
         <v>18.47523885586486</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.42637066980694</v>
+        <v>20.4263706747249</v>
       </c>
       <c r="CG10" t="n">
         <v>18.71731215268055</v>
@@ -15531,7 +15503,7 @@
         <v>6.956069443888868</v>
       </c>
       <c r="CM10" t="n">
-        <v>29.69124234798055</v>
+        <v>29.69124237920568</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -15814,37 +15786,37 @@
         <v>32.58000183105469</v>
       </c>
       <c r="BX11" t="n">
-        <v>24.20136299867336</v>
+        <v>24.20136283206105</v>
       </c>
       <c r="BY11" t="n">
-        <v>37.09024677252115</v>
+        <v>37.09024832555132</v>
       </c>
       <c r="BZ11" t="n">
-        <v>39.76037966515335</v>
+        <v>39.76038160371352</v>
       </c>
       <c r="CA11" t="n">
         <v>21.15376420319533</v>
       </c>
       <c r="CB11" t="n">
-        <v>53.96364405261692</v>
+        <v>53.96364534093689</v>
       </c>
       <c r="CC11" t="n">
-        <v>51.52714046459301</v>
+        <v>51.5271406748783</v>
       </c>
       <c r="CD11" t="n">
-        <v>19.8802225989987</v>
+        <v>19.88022357225448</v>
       </c>
       <c r="CE11" t="n">
         <v>24.52549486359719</v>
       </c>
       <c r="CF11" t="n">
-        <v>34.01278195241862</v>
+        <v>34.01278267702351</v>
       </c>
       <c r="CG11" t="n">
-        <v>30.80787081805916</v>
+        <v>30.80787159457425</v>
       </c>
       <c r="CH11" t="n">
-        <v>27.72708373625325</v>
+        <v>27.72708443511683</v>
       </c>
       <c r="CI11" t="n">
         <v>8</v>
@@ -15856,10 +15828,10 @@
         <v>2.7</v>
       </c>
       <c r="CL11" t="n">
-        <v>-14.89538926353197</v>
+        <v>-14.89538711846279</v>
       </c>
       <c r="CM11" t="n">
-        <v>4.397728793244671</v>
+        <v>4.397731017323392</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -16150,10 +16122,10 @@
         <v>32.97999954223633</v>
       </c>
       <c r="BX12" t="n">
-        <v>46.05539002065863</v>
+        <v>46.05538996044413</v>
       </c>
       <c r="BY12" t="n">
-        <v>85.43274848832176</v>
+        <v>85.43274837662385</v>
       </c>
       <c r="BZ12" t="n">
         <v>69.47297200868543</v>
@@ -16174,7 +16146,7 @@
         <v>25.94666723750103</v>
       </c>
       <c r="CF12" t="n">
-        <v>78.49436731887342</v>
+        <v>78.4943672943145</v>
       </c>
       <c r="CG12" t="n">
         <v>69.47297200868543</v>
@@ -16195,7 +16167,7 @@
         <v>89.58664546899841</v>
       </c>
       <c r="CM12" t="n">
-        <v>138.0059684911409</v>
+        <v>138.0059684166748</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -16480,10 +16452,10 @@
         <v>45.97999954223633</v>
       </c>
       <c r="BX13" t="n">
-        <v>127.6301650953702</v>
+        <v>127.6301656980486</v>
       </c>
       <c r="BY13" t="n">
-        <v>236.7539562519117</v>
+        <v>236.7539573698802</v>
       </c>
       <c r="BZ13" t="n">
         <v>137.215088724016</v>
@@ -16504,13 +16476,13 @@
         <v>56.54612056896573</v>
       </c>
       <c r="CF13" t="n">
-        <v>142.9573014686699</v>
+        <v>142.9573016837507</v>
       </c>
       <c r="CG13" t="n">
-        <v>126.4680098518585</v>
+        <v>126.4680101531977</v>
       </c>
       <c r="CH13" t="n">
-        <v>113.8212088666726</v>
+        <v>113.8212091378779</v>
       </c>
       <c r="CI13" t="n">
         <v>8</v>
@@ -16522,10 +16494,10 @@
         <v>5.5</v>
       </c>
       <c r="CL13" t="n">
-        <v>147.5450413219745</v>
+        <v>147.5450419118077</v>
       </c>
       <c r="CM13" t="n">
-        <v>210.9119245148145</v>
+        <v>210.9119249825849</v>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
@@ -16564,7 +16536,7 @@
         <v>-4.327813207567233</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-13.44221145597109</v>
+        <v>-13.4422178413344</v>
       </c>
       <c r="DA13" t="b">
         <v>1</v>
@@ -16808,10 +16780,10 @@
         <v>7.050000190734863</v>
       </c>
       <c r="BX14" t="n">
-        <v>6.61898229297842</v>
+        <v>6.61898225861528</v>
       </c>
       <c r="BY14" t="n">
-        <v>12.27821215347497</v>
+        <v>12.27821208973134</v>
       </c>
       <c r="BZ14" t="n">
         <v>41.15088217058896</v>
@@ -16820,7 +16792,7 @@
         <v>27.74453639251564</v>
       </c>
       <c r="CB14" t="n">
-        <v>87.40782156948055</v>
+        <v>87.40782135754928</v>
       </c>
       <c r="CC14" t="n">
         <v>51.88018214566937</v>
@@ -17120,10 +17092,10 @@
         <v>13.81999969482422</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.2035398171342778</v>
+        <v>0.2035398171108576</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.2963539737475085</v>
+        <v>0.2963539737134087</v>
       </c>
       <c r="BZ15" t="n">
         <v>77.27311657321069</v>
@@ -17418,10 +17390,10 @@
         <v>14</v>
       </c>
       <c r="BX16" t="n">
-        <v>10.16255141045656</v>
+        <v>10.1625513880544</v>
       </c>
       <c r="BY16" t="n">
-        <v>18.85153286639692</v>
+        <v>18.85153282484091</v>
       </c>
       <c r="BZ16" t="n">
         <v>50.13513513513512</v>
@@ -17430,23 +17402,23 @@
         <v>49.31969619160719</v>
       </c>
       <c r="CB16" t="n">
-        <v>69.76010976335598</v>
+        <v>69.76010972017841</v>
       </c>
       <c r="CC16" t="n">
-        <v>33.93518588965181</v>
+        <v>33.93518589309658</v>
       </c>
       <c r="CD16" t="n">
-        <v>29.78692741557185</v>
+        <v>29.78692744171249</v>
       </c>
       <c r="CE16" t="inlineStr"/>
       <c r="CF16" t="n">
-        <v>34.30728463039462</v>
+        <v>34.30728461769087</v>
       </c>
       <c r="CG16" t="n">
-        <v>33.93518588965181</v>
+        <v>33.93518589309658</v>
       </c>
       <c r="CH16" t="n">
-        <v>30.54166730068663</v>
+        <v>30.54166730378692</v>
       </c>
       <c r="CI16" t="n">
         <v>3</v>
@@ -17458,10 +17430,10 @@
         <v>4.9</v>
       </c>
       <c r="CL16" t="n">
-        <v>118.1547664334759</v>
+        <v>118.1547664556209</v>
       </c>
       <c r="CM16" t="n">
-        <v>145.0520330742473</v>
+        <v>145.0520329835062</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -17571,7 +17543,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -17722,10 +17694,10 @@
         <v>19.13999938964844</v>
       </c>
       <c r="BX17" t="n">
-        <v>13.15731118693232</v>
+        <v>13.15731128507561</v>
       </c>
       <c r="BY17" t="n">
-        <v>24.40681225175945</v>
+        <v>24.40681243381526</v>
       </c>
       <c r="BZ17" t="n">
         <v>19.90620030713044</v>
@@ -17734,7 +17706,7 @@
         <v>12.44114419785431</v>
       </c>
       <c r="CB17" t="n">
-        <v>33.68872439596174</v>
+        <v>33.68872450381151</v>
       </c>
       <c r="CC17" t="n">
         <v>22.8984489302328</v>
@@ -17744,7 +17716,7 @@
       </c>
       <c r="CE17" t="inlineStr"/>
       <c r="CF17" t="n">
-        <v>20.09219316901375</v>
+        <v>20.09219323906353</v>
       </c>
       <c r="CG17" t="n">
         <v>21.40232461868162</v>
@@ -17765,7 +17737,7 @@
         <v>0.6378932657179259</v>
       </c>
       <c r="CM17" t="n">
-        <v>4.974889288033602</v>
+        <v>4.974889654019887</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -17783,11 +17755,7 @@
         </is>
       </c>
       <c r="CQ17" t="inlineStr"/>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR17" t="inlineStr"/>
       <c r="CS17" t="b">
         <v>0</v>
       </c>
@@ -17814,14 +17782,14 @@
         <v>1</v>
       </c>
       <c r="DB17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD17" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.1%))</t>
         </is>
       </c>
     </row>
@@ -18052,10 +18020,10 @@
         <v>7.449999809265137</v>
       </c>
       <c r="BX18" t="n">
-        <v>3.363729732974996</v>
+        <v>3.363729731674687</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.239718654668616</v>
+        <v>6.239718652256543</v>
       </c>
       <c r="BZ18" t="n">
         <v>20.7379196371351</v>
@@ -18064,7 +18032,7 @@
         <v>14.20601824710207</v>
       </c>
       <c r="CB18" t="n">
-        <v>33.37021289929139</v>
+        <v>33.37021289546695</v>
       </c>
       <c r="CC18" t="n">
         <v>10.95072400487419</v>
@@ -18378,10 +18346,10 @@
         <v>17.53000068664551</v>
       </c>
       <c r="BX19" t="n">
-        <v>10.74426546359599</v>
+        <v>10.74426550839139</v>
       </c>
       <c r="BY19" t="n">
-        <v>19.93061243497056</v>
+        <v>19.93061251806602</v>
       </c>
       <c r="BZ19" t="n">
         <v>37.5845483977432</v>
@@ -18390,25 +18358,25 @@
         <v>37.1651975122017</v>
       </c>
       <c r="CB19" t="n">
-        <v>41.90042983588201</v>
+        <v>41.90042985470379</v>
       </c>
       <c r="CC19" t="n">
-        <v>34.50408897966985</v>
+        <v>34.50408897020166</v>
       </c>
       <c r="CD19" t="n">
-        <v>18.61582867267827</v>
+        <v>18.61582862072277</v>
       </c>
       <c r="CE19" t="n">
         <v>31.97921770241074</v>
       </c>
       <c r="CF19" t="n">
-        <v>31.66856050507948</v>
+        <v>31.66856051086427</v>
       </c>
       <c r="CG19" t="n">
-        <v>34.50408897966985</v>
+        <v>34.50408897020166</v>
       </c>
       <c r="CH19" t="n">
-        <v>31.05368008170287</v>
+        <v>31.05368007318149</v>
       </c>
       <c r="CI19" t="n">
         <v>7</v>
@@ -18420,10 +18388,10 @@
         <v>3.9</v>
       </c>
       <c r="CL19" t="n">
-        <v>77.14591480512493</v>
+        <v>77.14591475651471</v>
       </c>
       <c r="CM19" t="n">
-        <v>80.65350407661329</v>
+        <v>80.65350410961265</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -18708,10 +18676,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="BX20" t="n">
-        <v>5.044350326490063</v>
+        <v>5.044350317209677</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.357269855639066</v>
+        <v>9.357269838423951</v>
       </c>
       <c r="BZ20" t="n">
         <v>8.531826591579675</v>
@@ -19026,37 +18994,37 @@
         <v>10.35999965667725</v>
       </c>
       <c r="BX21" t="n">
-        <v>10.3786331450779</v>
+        <v>10.37863317753584</v>
       </c>
       <c r="BY21" t="n">
-        <v>18.07553066680664</v>
+        <v>18.07553058377986</v>
       </c>
       <c r="BZ21" t="n">
-        <v>23.22146511989621</v>
+        <v>23.22146494061011</v>
       </c>
       <c r="CA21" t="n">
         <v>17.75681071950086</v>
       </c>
       <c r="CB21" t="n">
-        <v>36.48041917740331</v>
+        <v>36.48041914613081</v>
       </c>
       <c r="CC21" t="n">
-        <v>24.12244065927788</v>
+        <v>24.12244064542064</v>
       </c>
       <c r="CD21" t="n">
-        <v>11.46100458572084</v>
+        <v>11.461004514599</v>
       </c>
       <c r="CE21" t="n">
         <v>10.35999965667725</v>
       </c>
       <c r="CF21" t="n">
-        <v>18.98203796629511</v>
+        <v>18.9820379230318</v>
       </c>
       <c r="CG21" t="n">
-        <v>17.91617069315375</v>
+        <v>17.91617065164036</v>
       </c>
       <c r="CH21" t="n">
-        <v>16.12455362383837</v>
+        <v>16.12455358647632</v>
       </c>
       <c r="CI21" t="n">
         <v>8</v>
@@ -19068,10 +19036,10 @@
         <v>3.5</v>
       </c>
       <c r="CL21" t="n">
-        <v>55.64241465438411</v>
+        <v>55.64241429374657</v>
       </c>
       <c r="CM21" t="n">
-        <v>83.22431076588668</v>
+        <v>83.22431034828712</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -19354,10 +19322,10 @@
         <v>11.07999992370605</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.454302376873577</v>
+        <v>3.454302387244496</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.407730909100485</v>
+        <v>6.407730928338538</v>
       </c>
       <c r="BZ22" t="n">
         <v>20.16620865234961</v>
@@ -19366,13 +19334,13 @@
         <v>19.00949927082382</v>
       </c>
       <c r="CB22" t="n">
-        <v>21.60588271687798</v>
+        <v>21.60588271589976</v>
       </c>
       <c r="CC22" t="n">
-        <v>15.92827012624657</v>
+        <v>15.92827012425295</v>
       </c>
       <c r="CD22" t="n">
-        <v>13.4711657642254</v>
+        <v>13.47116575107425</v>
       </c>
       <c r="CE22" t="n">
         <v>30.336208848481</v>
@@ -19428,7 +19396,7 @@
         <v>-18.94659940111765</v>
       </c>
       <c r="CZ22" t="n">
-        <v>-32.89648837260555</v>
+        <v>-32.89649636084019</v>
       </c>
       <c r="DA22" t="b">
         <v>1</v>
@@ -19672,37 +19640,37 @@
         <v>35.20000076293945</v>
       </c>
       <c r="BX23" t="n">
-        <v>25.31139913744763</v>
+        <v>25.31139914935138</v>
       </c>
       <c r="BY23" t="n">
-        <v>29.80495150098457</v>
+        <v>29.80495148436414</v>
       </c>
       <c r="BZ23" t="n">
-        <v>32.18096603998838</v>
+        <v>32.18096600690855</v>
       </c>
       <c r="CA23" t="n">
         <v>35.90922954270143</v>
       </c>
       <c r="CB23" t="n">
-        <v>45.73499565680308</v>
+        <v>45.73499563233776</v>
       </c>
       <c r="CC23" t="n">
-        <v>48.24380380828207</v>
+        <v>48.24380380301253</v>
       </c>
       <c r="CD23" t="n">
-        <v>14.75792626688792</v>
+        <v>14.75792624012352</v>
       </c>
       <c r="CE23" t="n">
         <v>30.3203711305658</v>
       </c>
       <c r="CF23" t="n">
-        <v>32.78295538545761</v>
+        <v>32.78295537367064</v>
       </c>
       <c r="CG23" t="n">
-        <v>31.25066858527709</v>
+        <v>31.25066856873717</v>
       </c>
       <c r="CH23" t="n">
-        <v>28.12560172674938</v>
+        <v>28.12560171186346</v>
       </c>
       <c r="CI23" t="n">
         <v>8</v>
@@ -19714,10 +19682,10 @@
         <v>3.3</v>
       </c>
       <c r="CL23" t="n">
-        <v>-20.09772409902445</v>
+        <v>-20.097724141314</v>
       </c>
       <c r="CM23" t="n">
-        <v>-6.866606037198276</v>
+        <v>-6.866606070684</v>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
@@ -20000,10 +19968,10 @@
         <v>11.28999996185303</v>
       </c>
       <c r="BX24" t="n">
-        <v>9.774107128522251</v>
+        <v>9.774107112442596</v>
       </c>
       <c r="BY24" t="n">
-        <v>18.13096872340877</v>
+        <v>18.13096869358102</v>
       </c>
       <c r="BZ24" t="n">
         <v>22.32723873053024</v>
@@ -20012,25 +19980,25 @@
         <v>13.19107667093893</v>
       </c>
       <c r="CB24" t="n">
-        <v>32.07171957325589</v>
+        <v>32.07171962245396</v>
       </c>
       <c r="CC24" t="n">
-        <v>25.27239703816369</v>
+        <v>25.27239704977857</v>
       </c>
       <c r="CD24" t="n">
-        <v>11.8232898334598</v>
+        <v>11.82328988550385</v>
       </c>
       <c r="CE24" t="n">
         <v>9.733055502947964</v>
       </c>
       <c r="CF24" t="n">
-        <v>17.79048165015344</v>
+        <v>17.79048165852214</v>
       </c>
       <c r="CG24" t="n">
-        <v>15.66102269717385</v>
+        <v>15.66102268225998</v>
       </c>
       <c r="CH24" t="n">
-        <v>14.09492042745647</v>
+        <v>14.09492041403398</v>
       </c>
       <c r="CI24" t="n">
         <v>8</v>
@@ -20042,10 +20010,10 @@
         <v>3.3</v>
       </c>
       <c r="CL24" t="n">
-        <v>24.8442911876066</v>
+        <v>24.84429106871831</v>
       </c>
       <c r="CM24" t="n">
-        <v>57.57734021491962</v>
+        <v>57.57734028904451</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -20328,10 +20296,10 @@
         <v>14.13000011444092</v>
       </c>
       <c r="BX25" t="n">
-        <v>4.339755634840489</v>
+        <v>4.339755647106034</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.050246702629106</v>
+        <v>8.050246725381694</v>
       </c>
       <c r="BZ25" t="n">
         <v>23.63920473691189</v>
@@ -20340,25 +20308,25 @@
         <v>19.91603197659278</v>
       </c>
       <c r="CB25" t="n">
-        <v>28.9310943964596</v>
+        <v>28.93109438711175</v>
       </c>
       <c r="CC25" t="n">
-        <v>16.71775062637852</v>
+        <v>16.71775062378051</v>
       </c>
       <c r="CD25" t="n">
-        <v>18.12938009671167</v>
+        <v>18.1293800772075</v>
       </c>
       <c r="CE25" t="n">
         <v>13.90588124012942</v>
       </c>
       <c r="CF25" t="n">
-        <v>18.46994139654472</v>
+        <v>18.46994139530222</v>
       </c>
       <c r="CG25" t="n">
-        <v>18.12938009671167</v>
+        <v>18.1293800772075</v>
       </c>
       <c r="CH25" t="n">
-        <v>16.31644208704051</v>
+        <v>16.31644206948675</v>
       </c>
       <c r="CI25" t="n">
         <v>7</v>
@@ -20370,10 +20338,10 @@
         <v>6.7</v>
       </c>
       <c r="CL25" t="n">
-        <v>15.47375764254266</v>
+        <v>15.47375751831224</v>
       </c>
       <c r="CM25" t="n">
-        <v>30.71437542076423</v>
+        <v>30.71437541197091</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -20966,10 +20934,10 @@
         <v>13.23999977111816</v>
       </c>
       <c r="BX27" t="n">
-        <v>8.302793976110308</v>
+        <v>8.30279399535676</v>
       </c>
       <c r="BY27" t="n">
-        <v>15.40168282568462</v>
+        <v>15.40168286138679</v>
       </c>
       <c r="BZ27" t="n">
         <v>13.23999977111816</v>
@@ -20990,7 +20958,7 @@
         <v>6.052411187494985</v>
       </c>
       <c r="CF27" t="n">
-        <v>10.88286237195542</v>
+        <v>10.88286237980522</v>
       </c>
       <c r="CG27" t="n">
         <v>10.76229112776816</v>
@@ -21011,7 +20979,7 @@
         <v>-26.84243064625581</v>
       </c>
       <c r="CM27" t="n">
-        <v>-17.80315286941791</v>
+        <v>-17.80315281012938</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -21290,10 +21258,10 @@
         <v>27.52000045776367</v>
       </c>
       <c r="BX28" t="n">
-        <v>7.290978528882397</v>
+        <v>7.290978517778295</v>
       </c>
       <c r="BY28" t="n">
-        <v>13.52476517107684</v>
+        <v>13.52476515047874</v>
       </c>
       <c r="BZ28" t="n">
         <v>35.92512375028262</v>
@@ -21302,19 +21270,19 @@
         <v>28.41024685094796</v>
       </c>
       <c r="CB28" t="n">
-        <v>44.7474925273167</v>
+        <v>44.74749254390056</v>
       </c>
       <c r="CC28" t="n">
-        <v>26.46268145030354</v>
+        <v>26.46268145306381</v>
       </c>
       <c r="CD28" t="n">
-        <v>29.04887751514411</v>
+        <v>29.04887753519546</v>
       </c>
       <c r="CE28" t="n">
         <v>24.98203479043206</v>
       </c>
       <c r="CF28" t="n">
-        <v>29.0144602936434</v>
+        <v>29.01446029632875</v>
       </c>
       <c r="CG28" t="n">
         <v>28.41024685094796</v>
@@ -21335,7 +21303,7 @@
         <v>-7.088583791648039</v>
       </c>
       <c r="CM28" t="n">
-        <v>5.430449894698786</v>
+        <v>5.430449904456558</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -21449,7 +21417,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -21598,10 +21566,10 @@
         <v>38.90000152587891</v>
       </c>
       <c r="BX29" t="n">
-        <v>35.62892560284679</v>
+        <v>35.62892564590315</v>
       </c>
       <c r="BY29" t="n">
-        <v>51.87571567774493</v>
+        <v>51.875715740435</v>
       </c>
       <c r="BZ29" t="n">
         <v>48.56662855571916</v>
@@ -21618,13 +21586,13 @@
       </c>
       <c r="CE29" t="inlineStr"/>
       <c r="CF29" t="n">
-        <v>48.89385870503214</v>
+        <v>48.89385873146875</v>
       </c>
       <c r="CG29" t="n">
-        <v>50.22117211673205</v>
+        <v>50.22117214807708</v>
       </c>
       <c r="CH29" t="n">
-        <v>45.19905490505884</v>
+        <v>45.19905493326937</v>
       </c>
       <c r="CI29" t="n">
         <v>4</v>
@@ -21636,10 +21604,10 @@
         <v>1.7</v>
       </c>
       <c r="CL29" t="n">
-        <v>16.19293864291851</v>
+        <v>16.19293871543917</v>
       </c>
       <c r="CM29" t="n">
-        <v>25.6911485530525</v>
+        <v>25.69114862101294</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -21657,11 +21625,7 @@
         </is>
       </c>
       <c r="CQ29" t="inlineStr"/>
-      <c r="CR29" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR29" t="inlineStr"/>
       <c r="CS29" t="b">
         <v>0</v>
       </c>
@@ -21688,14 +21652,14 @@
         <v>1</v>
       </c>
       <c r="DB29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD29" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -21926,10 +21890,10 @@
         <v>24.72999954223633</v>
       </c>
       <c r="BX30" t="n">
-        <v>12.83053367577991</v>
+        <v>12.83053368638596</v>
       </c>
       <c r="BY30" t="n">
-        <v>23.80063996857173</v>
+        <v>23.80063998824595</v>
       </c>
       <c r="BZ30" t="n">
         <v>61.13292797287897</v>
@@ -21938,13 +21902,13 @@
         <v>51.18231610165188</v>
       </c>
       <c r="CB30" t="n">
-        <v>84.96070712581724</v>
+        <v>84.96070712640629</v>
       </c>
       <c r="CC30" t="n">
-        <v>33.64819480796157</v>
+        <v>33.64819480618258</v>
       </c>
       <c r="CD30" t="n">
-        <v>44.66427062545444</v>
+        <v>44.66427060841179</v>
       </c>
       <c r="CE30" t="n">
         <v>5.441506065857172</v>
@@ -22240,10 +22204,10 @@
         <v>22.06999969482422</v>
       </c>
       <c r="BX31" t="n">
-        <v>3.108740528356239</v>
+        <v>3.108740529578116</v>
       </c>
       <c r="BY31" t="n">
-        <v>5.766713680100823</v>
+        <v>5.766713682367405</v>
       </c>
       <c r="BZ31" t="n">
         <v>31.95928917556512</v>
@@ -22252,7 +22216,7 @@
         <v>26.70105358379499</v>
       </c>
       <c r="CB31" t="n">
-        <v>40.93687025348094</v>
+        <v>40.93687025535048</v>
       </c>
       <c r="CC31" t="n">
         <v>10.85340539909456</v>
@@ -22387,7 +22351,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -22558,10 +22522,10 @@
         <v>12.02999973297119</v>
       </c>
       <c r="BX32" t="n">
-        <v>2.081024034886541</v>
+        <v>2.081024032334844</v>
       </c>
       <c r="BY32" t="n">
-        <v>3.860299584714533</v>
+        <v>3.860299579981135</v>
       </c>
       <c r="BZ32" t="n">
         <v>28.46383865390505</v>
@@ -22570,7 +22534,7 @@
         <v>24.11364501630011</v>
       </c>
       <c r="CB32" t="n">
-        <v>37.42577365767491</v>
+        <v>37.42577365129566</v>
       </c>
       <c r="CC32" t="n">
         <v>9.158754146</v>
@@ -22607,7 +22571,11 @@
       </c>
       <c r="CP32" t="inlineStr"/>
       <c r="CQ32" t="inlineStr"/>
-      <c r="CR32" t="inlineStr"/>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="CS32" t="b">
         <v>0</v>
       </c>
@@ -22634,14 +22602,14 @@
         <v>0</v>
       </c>
       <c r="DB32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC32" t="b">
         <v>0</v>
       </c>
       <c r="DD32" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -22872,10 +22840,10 @@
         <v>32.75</v>
       </c>
       <c r="BX33" t="n">
-        <v>3.249356697982276</v>
+        <v>3.249356708540788</v>
       </c>
       <c r="BY33" t="n">
-        <v>6.027556674757121</v>
+        <v>6.027556694343162</v>
       </c>
       <c r="BZ33" t="n">
         <v>32.74999999999999</v>
@@ -22884,7 +22852,7 @@
         <v>22.94333650394972</v>
       </c>
       <c r="CB33" t="n">
-        <v>40.50875424692467</v>
+        <v>40.50875425808083</v>
       </c>
       <c r="CC33" t="n">
         <v>10.59424454785779</v>
@@ -22924,7 +22892,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ33" t="inlineStr"/>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>A TOTVS (TOTS3) apresenta uma sólida eficiência operacional no setor de tecnologia da informação, com um ROE de 26,1% e um ROIC de 23,4% que se posicionam significativamente acima dos pares setoriais (9,1% e 13,4%, respectivamente), sugerindo uma forte capacidade de geração de valor sobre o capital empregado. Essa elevada qualidade operacional convive com múltiplos de valuation que exigem atenção, pois o P/VP de 3,46 indica um prêmio em relação ao valor patrimonial, embora o P/L de 13,25 e o PEG de 0,88 sinalizem que o preço atual está atrativo quando confrontado com o forte ritmo de crescimento dos lucros. No âmbito financeiro, a excelente rentabilidade, traduzida em uma margem líquida de 21,63%, ajuda a suportar um endividamento cuja relação Dívida Líquida/EBITDA de 2,09 está acima da média do setor (1,39), mas que permanece sob controle e bem respaldada por uma liquidez corrente confortável de 1,84. Essa alavancagem mais alta e o foco na expansão explicam o modesto dividend yield de 2,16%, demonstrando que a companhia prioriza a retenção de caixa para sustentar seu crescimento em detrimento de proventos agressivos. O perfil de expansão da empresa é altamente robusto, evidenciado por um impressionante CAGR de receita de cinco anos de 269,5%, patamar que supera com folga a média setorial de 74,1%. No checklist de critérios fundamentalistas, a TOTS3 atende a 6 dos 8 requisitos avaliados, falhando apenas na relação de endividamento comparada ao setor e no registro de venda de ações por parte de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma enorme dispersão entre as metodologias, variando desde patamares muito baixos nos modelos de fluxo de caixa de dividendos, como Bazin (R$ 3,25) e Gordon (R$ 6,03), até avaliações mais generosas baseadas em crescimento e fluxo de caixa livre, como Graham (R$ 22,94), o próprio preço atual via DCF (R$ 32,75) e o modelo de Lynch (R$ 40,51), o qual aponta o maior potencial de valorização. Como prós, destacam-se o crescimento exponencial da receita, a rentabilidade muito acima da média e a forte tendência de alta no sinal gráfico de rompimento; como contras, pesam o endividamento superior ao dos pares, a distribuição tímida de dividendos e a pressão vendedora de insiders.</t>
+        </is>
+      </c>
       <c r="CR33" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -22950,7 +22922,7 @@
         <v>0.738239590458023</v>
       </c>
       <c r="CZ33" t="n">
-        <v>-31.31834368818209</v>
+        <v>-31.318349352401</v>
       </c>
       <c r="DA33" t="b">
         <v>1</v>
@@ -23194,10 +23166,10 @@
         <v>33.43000030517578</v>
       </c>
       <c r="BX34" t="n">
-        <v>7.930922164176469</v>
+        <v>7.930922182941486</v>
       </c>
       <c r="BY34" t="n">
-        <v>14.71186061454735</v>
+        <v>14.71186064935646</v>
       </c>
       <c r="BZ34" t="n">
         <v>65.23527305501902</v>
@@ -23206,7 +23178,7 @@
         <v>38.10857086024811</v>
       </c>
       <c r="CB34" t="n">
-        <v>90.20366934846943</v>
+        <v>90.20366938716016</v>
       </c>
       <c r="CC34" t="n">
         <v>22.51480113099953</v>
@@ -23490,35 +23462,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="BX35" t="n">
-        <v>16.54376614351627</v>
+        <v>16.54376617010686</v>
       </c>
       <c r="BY35" t="n">
-        <v>29.62891132726303</v>
+        <v>29.62891132322974</v>
       </c>
       <c r="BZ35" t="n">
-        <v>50.06208078281589</v>
+        <v>50.06208069553695</v>
       </c>
       <c r="CA35" t="n">
         <v>49.44990718954784</v>
       </c>
       <c r="CB35" t="n">
-        <v>61.76490016037727</v>
+        <v>61.76490017127702</v>
       </c>
       <c r="CC35" t="n">
-        <v>45.76209351440657</v>
+        <v>45.76209350862207</v>
       </c>
       <c r="CD35" t="n">
-        <v>24.56071171110277</v>
+        <v>24.56071167822617</v>
       </c>
       <c r="CE35" t="inlineStr"/>
       <c r="CF35" t="n">
-        <v>35.49921294200044</v>
+        <v>35.4992129243739</v>
       </c>
       <c r="CG35" t="n">
-        <v>37.6955024208348</v>
+        <v>37.6955024159259</v>
       </c>
       <c r="CH35" t="n">
-        <v>33.92595217875132</v>
+        <v>33.92595217433331</v>
       </c>
       <c r="CI35" t="n">
         <v>4</v>
@@ -23530,10 +23502,10 @@
         <v>3</v>
       </c>
       <c r="CL35" t="n">
-        <v>47.18417918298263</v>
+        <v>47.18417916381554</v>
       </c>
       <c r="CM35" t="n">
-        <v>54.00960571366804</v>
+        <v>54.00960563719715</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -23812,10 +23784,10 @@
         <v>33.65000152587891</v>
       </c>
       <c r="BX36" t="n">
-        <v>15.24688686621493</v>
+        <v>15.24688687743688</v>
       </c>
       <c r="BY36" t="n">
-        <v>28.28297513682869</v>
+        <v>28.28297515764541</v>
       </c>
       <c r="BZ36" t="n">
         <v>20.19304892291193</v>
@@ -23824,7 +23796,7 @@
         <v>37.28531071349501</v>
       </c>
       <c r="CB36" t="n">
-        <v>27.19345261207502</v>
+        <v>27.19345261919038</v>
       </c>
       <c r="CC36" t="n">
         <v>15.03391666666667</v>
@@ -23836,7 +23808,7 @@
         <v>79.29138454079849</v>
       </c>
       <c r="CF36" t="n">
-        <v>22.6176039245593</v>
+        <v>22.61760393015274</v>
       </c>
       <c r="CG36" t="n">
         <v>20.19304892291193</v>
@@ -23857,7 +23829,7 @@
         <v>-45.99184782608695</v>
       </c>
       <c r="CM36" t="n">
-        <v>-32.78572689761995</v>
+        <v>-32.78572688099754</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -23963,7 +23935,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -24116,35 +24088,35 @@
         <v>12.85000038146973</v>
       </c>
       <c r="BX37" t="n">
-        <v>8.627042091816078</v>
+        <v>8.627042087914047</v>
       </c>
       <c r="BY37" t="n">
-        <v>13.85196401738628</v>
+        <v>13.85196402192589</v>
       </c>
       <c r="BZ37" t="n">
-        <v>18.49124791236634</v>
+        <v>18.49124792678998</v>
       </c>
       <c r="CA37" t="n">
         <v>17.39822241629838</v>
       </c>
       <c r="CB37" t="n">
-        <v>22.98547046825374</v>
+        <v>22.98547047197555</v>
       </c>
       <c r="CC37" t="n">
-        <v>17.33681285450712</v>
+        <v>17.33681285559167</v>
       </c>
       <c r="CD37" t="n">
-        <v>9.229677229939698</v>
+        <v>9.229677236587511</v>
       </c>
       <c r="CE37" t="inlineStr"/>
       <c r="CF37" t="n">
-        <v>14.57676671901895</v>
+        <v>14.5767667230554</v>
       </c>
       <c r="CG37" t="n">
-        <v>15.5943884359467</v>
+        <v>15.59438843875878</v>
       </c>
       <c r="CH37" t="n">
-        <v>14.03494959235203</v>
+        <v>14.0349495948829</v>
       </c>
       <c r="CI37" t="n">
         <v>4</v>
@@ -24156,10 +24128,10 @@
         <v>2.1</v>
       </c>
       <c r="CL37" t="n">
-        <v>9.221394363466739</v>
+        <v>9.221394383162252</v>
       </c>
       <c r="CM37" t="n">
-        <v>13.43786993220093</v>
+        <v>13.43786996361298</v>
       </c>
       <c r="CN37" t="inlineStr">
         <is>
@@ -24177,11 +24149,7 @@
         </is>
       </c>
       <c r="CQ37" t="inlineStr"/>
-      <c r="CR37" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR37" t="inlineStr"/>
       <c r="CS37" t="b">
         <v>0</v>
       </c>
@@ -24208,14 +24176,14 @@
         <v>1</v>
       </c>
       <c r="DB37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD37" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.4%))</t>
         </is>
       </c>
     </row>
@@ -24426,10 +24394,10 @@
         <v>14.77999973297119</v>
       </c>
       <c r="BX38" t="n">
-        <v>9.186484939067871</v>
+        <v>9.186484962458096</v>
       </c>
       <c r="BY38" t="n">
-        <v>17.0409295619709</v>
+        <v>17.04092960535977</v>
       </c>
       <c r="BZ38" t="n">
         <v>30.69514051126462</v>
@@ -24438,23 +24406,23 @@
         <v>29.25728964348931</v>
       </c>
       <c r="CB38" t="n">
-        <v>34.71948755840006</v>
+        <v>34.71948756345603</v>
       </c>
       <c r="CC38" t="n">
-        <v>25.51046014636512</v>
+        <v>25.51046014157115</v>
       </c>
       <c r="CD38" t="n">
-        <v>15.34133402372116</v>
+        <v>15.34133399463682</v>
       </c>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="n">
-        <v>20.60825378966713</v>
+        <v>20.60825380516341</v>
       </c>
       <c r="CG38" t="n">
-        <v>21.27569485416801</v>
+        <v>21.27569487346546</v>
       </c>
       <c r="CH38" t="n">
-        <v>19.14812536875121</v>
+        <v>19.14812538611892</v>
       </c>
       <c r="CI38" t="n">
         <v>4</v>
@@ -24466,10 +24434,10 @@
         <v>3.3</v>
       </c>
       <c r="CL38" t="n">
-        <v>29.55430118199269</v>
+        <v>29.55430129950083</v>
       </c>
       <c r="CM38" t="n">
-        <v>39.43338404597046</v>
+        <v>39.43338415081674</v>
       </c>
       <c r="CN38" t="inlineStr">
         <is>
@@ -24508,7 +24476,7 @@
         <v>-7.171627471148123</v>
       </c>
       <c r="CZ38" t="n">
-        <v>-18.7474872046273</v>
+        <v>-18.74746959920818</v>
       </c>
       <c r="DA38" t="b">
         <v>1</v>
@@ -24734,10 +24702,10 @@
         <v>39.43999862670898</v>
       </c>
       <c r="BX39" t="n">
-        <v>20.16127578131654</v>
+        <v>20.16127564389373</v>
       </c>
       <c r="BY39" t="n">
-        <v>37.39916657434217</v>
+        <v>37.39916631942287</v>
       </c>
       <c r="BZ39" t="n">
         <v>56.01071616333269</v>
@@ -24746,23 +24714,23 @@
         <v>42.36568036412405</v>
       </c>
       <c r="CB39" t="n">
-        <v>61.78700412157808</v>
+        <v>61.78700434729011</v>
       </c>
       <c r="CC39" t="n">
-        <v>45.16919925726728</v>
+        <v>45.16919930021541</v>
       </c>
       <c r="CD39" t="n">
-        <v>31.11427774290894</v>
+        <v>31.11427801440143</v>
       </c>
       <c r="CE39" t="inlineStr"/>
       <c r="CF39" t="n">
-        <v>39.68508944406467</v>
+        <v>39.68508935671618</v>
       </c>
       <c r="CG39" t="n">
-        <v>41.28418291580473</v>
+        <v>41.28418280981914</v>
       </c>
       <c r="CH39" t="n">
-        <v>37.15576462422425</v>
+        <v>37.15576452883723</v>
       </c>
       <c r="CI39" t="n">
         <v>4</v>
@@ -24774,10 +24742,10 @@
         <v>2.8</v>
       </c>
       <c r="CL39" t="n">
-        <v>-5.79166856496246</v>
+        <v>-5.791668806815975</v>
       </c>
       <c r="CM39" t="n">
-        <v>0.6214270433308577</v>
+        <v>0.6214268218589947</v>
       </c>
       <c r="CN39" t="inlineStr">
         <is>
@@ -24816,7 +24784,7 @@
         <v>-6.937240130506206</v>
       </c>
       <c r="CZ39" t="n">
-        <v>-19.01272601806555</v>
+        <v>-19.01273878297394</v>
       </c>
       <c r="DA39" t="b">
         <v>1</v>
@@ -25060,10 +25028,10 @@
         <v>5.880000114440918</v>
       </c>
       <c r="BX40" t="n">
-        <v>6.975750761435104</v>
+        <v>6.975750746615178</v>
       </c>
       <c r="BY40" t="n">
-        <v>12.94001766246212</v>
+        <v>12.94001763497115</v>
       </c>
       <c r="BZ40" t="n">
         <v>5.584946345257502</v>
@@ -25084,7 +25052,7 @@
         <v>5.373183328823668</v>
       </c>
       <c r="CF40" t="n">
-        <v>7.287571946166208</v>
+        <v>7.287571940877347</v>
       </c>
       <c r="CG40" t="n">
         <v>5.859139839295418</v>
@@ -25105,7 +25073,7 @@
         <v>-10.31928991948218</v>
       </c>
       <c r="CM40" t="n">
-        <v>23.93829599200825</v>
+        <v>23.93829590206163</v>
       </c>
       <c r="CN40" t="inlineStr">
         <is>
@@ -25388,37 +25356,37 @@
         <v>26.45999908447266</v>
       </c>
       <c r="BX41" t="n">
-        <v>16.91883610520417</v>
+        <v>16.91883602994602</v>
       </c>
       <c r="BY41" t="n">
-        <v>28.00431313367254</v>
+        <v>28.00431312460474</v>
       </c>
       <c r="BZ41" t="n">
-        <v>46.83168332580541</v>
+        <v>46.83168351895741</v>
       </c>
       <c r="CA41" t="n">
         <v>52.67243426197095</v>
       </c>
       <c r="CB41" t="n">
-        <v>55.69855923746945</v>
+        <v>55.69855921365713</v>
       </c>
       <c r="CC41" t="n">
-        <v>43.03544429300022</v>
+        <v>43.03544430684217</v>
       </c>
       <c r="CD41" t="n">
-        <v>23.30397202537988</v>
+        <v>23.30397210955462</v>
       </c>
       <c r="CE41" t="n">
         <v>30.43448362223624</v>
       </c>
       <c r="CF41" t="n">
-        <v>37.11246575059236</v>
+        <v>37.11246577347116</v>
       </c>
       <c r="CG41" t="n">
-        <v>36.73496395761823</v>
+        <v>36.7349639645392</v>
       </c>
       <c r="CH41" t="n">
-        <v>33.06146756185641</v>
+        <v>33.06146756808528</v>
       </c>
       <c r="CI41" t="n">
         <v>8</v>
@@ -25430,10 +25398,10 @@
         <v>3.3</v>
       </c>
       <c r="CL41" t="n">
-        <v>24.94886132198564</v>
+        <v>24.94886134552636</v>
       </c>
       <c r="CM41" t="n">
-        <v>40.25875674489654</v>
+        <v>40.25875683136215</v>
       </c>
       <c r="CN41" t="inlineStr">
         <is>
@@ -25545,7 +25513,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S42" t="n">
@@ -25716,37 +25684,37 @@
         <v>15.3100004196167</v>
       </c>
       <c r="BX42" t="n">
-        <v>5.939526969706941</v>
+        <v>5.939526959977536</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.534880603381971</v>
+        <v>8.534880611414447</v>
       </c>
       <c r="BZ42" t="n">
-        <v>10.81501544468299</v>
+        <v>10.81501547257721</v>
       </c>
       <c r="CA42" t="n">
         <v>11.65944891202323</v>
       </c>
       <c r="CB42" t="n">
-        <v>9.810403804551399</v>
+        <v>9.810403820239834</v>
       </c>
       <c r="CC42" t="n">
-        <v>14.90925677887778</v>
+        <v>14.90925678229168</v>
       </c>
       <c r="CD42" t="n">
-        <v>5.384140030925815</v>
+        <v>5.38414004667967</v>
       </c>
       <c r="CE42" t="n">
         <v>11.00534556207784</v>
       </c>
       <c r="CF42" t="n">
-        <v>9.757252263278495</v>
+        <v>9.757252270910181</v>
       </c>
       <c r="CG42" t="n">
-        <v>10.31270962461719</v>
+        <v>10.31270964640852</v>
       </c>
       <c r="CH42" t="n">
-        <v>9.281438662155473</v>
+        <v>9.28143868176767</v>
       </c>
       <c r="CI42" t="n">
         <v>8</v>
@@ -25758,10 +25726,10 @@
         <v>2.8</v>
       </c>
       <c r="CL42" t="n">
-        <v>-39.37662699040055</v>
+        <v>-39.37662686229999</v>
       </c>
       <c r="CM42" t="n">
-        <v>-36.26876553983283</v>
+        <v>-36.26876548998512</v>
       </c>
       <c r="CN42" t="inlineStr">
         <is>
@@ -25779,11 +25747,7 @@
         </is>
       </c>
       <c r="CQ42" t="inlineStr"/>
-      <c r="CR42" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR42" t="inlineStr"/>
       <c r="CS42" t="b">
         <v>0</v>
       </c>
@@ -25810,14 +25774,14 @@
         <v>1</v>
       </c>
       <c r="DB42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD42" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-3.5%))</t>
         </is>
       </c>
     </row>
@@ -26048,10 +26012,10 @@
         <v>9.25</v>
       </c>
       <c r="BX43" t="n">
-        <v>2.521670929592308</v>
+        <v>2.521670914006125</v>
       </c>
       <c r="BY43" t="n">
-        <v>4.677699574393731</v>
+        <v>4.677699545481363</v>
       </c>
       <c r="BZ43" t="n">
         <v>13.54281767955801</v>
@@ -26060,19 +26024,19 @@
         <v>15.28931421405346</v>
       </c>
       <c r="CB43" t="n">
-        <v>10.60496388895048</v>
+        <v>10.60496388670356</v>
       </c>
       <c r="CC43" t="n">
-        <v>7.31063984971896</v>
+        <v>7.310639851186559</v>
       </c>
       <c r="CD43" t="n">
-        <v>6.944431456908005</v>
+        <v>6.944431470651279</v>
       </c>
       <c r="CE43" t="n">
         <v>10.29452216806777</v>
       </c>
       <c r="CF43" t="n">
-        <v>9.80919840452149</v>
+        <v>9.809198402243142</v>
       </c>
       <c r="CG43" t="n">
         <v>10.29452216806777</v>
@@ -26093,7 +26057,7 @@
         <v>0.1629183920107247</v>
       </c>
       <c r="CM43" t="n">
-        <v>6.045388156989095</v>
+        <v>6.045388132358287</v>
       </c>
       <c r="CN43" t="inlineStr">
         <is>
@@ -26372,10 +26336,10 @@
         <v>11.76000022888184</v>
       </c>
       <c r="BX44" t="n">
-        <v>4.779815368453594</v>
+        <v>4.77981536586783</v>
       </c>
       <c r="BY44" t="n">
-        <v>8.866557508481415</v>
+        <v>8.866557503684826</v>
       </c>
       <c r="BZ44" t="n">
         <v>25.84079652283322</v>
@@ -26384,25 +26348,25 @@
         <v>29.08539831347033</v>
       </c>
       <c r="CB44" t="n">
-        <v>24.10032307146077</v>
+        <v>24.10032306913171</v>
       </c>
       <c r="CC44" t="n">
-        <v>14.25753217839691</v>
+        <v>14.25753217864874</v>
       </c>
       <c r="CD44" t="n">
-        <v>13.38320656989685</v>
+        <v>13.38320657220645</v>
       </c>
       <c r="CE44" t="n">
         <v>4.91926228677063</v>
       </c>
       <c r="CF44" t="n">
-        <v>19.25563569408991</v>
+        <v>19.25563569332921</v>
       </c>
       <c r="CG44" t="n">
-        <v>19.17892762492884</v>
+        <v>19.17892762389022</v>
       </c>
       <c r="CH44" t="n">
-        <v>17.26103486243596</v>
+        <v>17.2610348615012</v>
       </c>
       <c r="CI44" t="n">
         <v>6</v>
@@ -26414,10 +26378,10 @@
         <v>6.1</v>
       </c>
       <c r="CL44" t="n">
-        <v>46.7775044769465</v>
+        <v>46.77750446899791</v>
       </c>
       <c r="CM44" t="n">
-        <v>63.73839557246996</v>
+        <v>63.7383955660014</v>
       </c>
       <c r="CN44" t="inlineStr">
         <is>
@@ -26452,7 +26416,7 @@
         <v>4.347823879462331</v>
       </c>
       <c r="CZ44" t="n">
-        <v>-28.48248018644097</v>
+        <v>-28.48247563627588</v>
       </c>
       <c r="DA44" t="b">
         <v>0</v>
@@ -26696,37 +26660,37 @@
         <v>38.86000061035156</v>
       </c>
       <c r="BX45" t="n">
-        <v>30.97422553975776</v>
+        <v>30.9742256602967</v>
       </c>
       <c r="BY45" t="n">
-        <v>35.52640287414108</v>
+        <v>35.52640278045922</v>
       </c>
       <c r="BZ45" t="n">
-        <v>38.58971747040682</v>
+        <v>38.58971721847183</v>
       </c>
       <c r="CA45" t="n">
         <v>49.80959882281965</v>
       </c>
       <c r="CB45" t="n">
-        <v>60.09290031647345</v>
+        <v>60.09290018115279</v>
       </c>
       <c r="CC45" t="n">
-        <v>16.76379308795554</v>
+        <v>16.76379307604998</v>
       </c>
       <c r="CD45" t="n">
-        <v>17.31674458272697</v>
+        <v>17.31674436909339</v>
       </c>
       <c r="CE45" t="n">
         <v>28.40888631687585</v>
       </c>
       <c r="CF45" t="n">
-        <v>34.68528362639464</v>
+        <v>34.68528355315243</v>
       </c>
       <c r="CG45" t="n">
-        <v>33.25031420694942</v>
+        <v>33.25031422037796</v>
       </c>
       <c r="CH45" t="n">
-        <v>29.92528278625448</v>
+        <v>29.92528279834016</v>
       </c>
       <c r="CI45" t="n">
         <v>8</v>
@@ -26738,10 +26702,10 @@
         <v>3.6</v>
       </c>
       <c r="CL45" t="n">
-        <v>-22.99206815173607</v>
+        <v>-22.99206812063549</v>
       </c>
       <c r="CM45" t="n">
-        <v>-10.74296685122762</v>
+        <v>-10.74296703970474</v>
       </c>
       <c r="CN45" t="inlineStr">
         <is>
@@ -27024,10 +26988,10 @@
         <v>34.09000015258789</v>
       </c>
       <c r="BX46" t="n">
-        <v>14.76402959169838</v>
+        <v>14.76402958625189</v>
       </c>
       <c r="BY46" t="n">
-        <v>27.38727489260049</v>
+        <v>27.38727488249725</v>
       </c>
       <c r="BZ46" t="n">
         <v>56.67409059244536</v>
@@ -27036,25 +27000,25 @@
         <v>43.80170806643823</v>
       </c>
       <c r="CB46" t="n">
-        <v>73.43420500741638</v>
+        <v>73.43420501423546</v>
       </c>
       <c r="CC46" t="n">
-        <v>38.47788655200277</v>
+        <v>38.47788655332953</v>
       </c>
       <c r="CD46" t="n">
-        <v>41.28355406353919</v>
+        <v>41.28355407383916</v>
       </c>
       <c r="CE46" t="n">
         <v>21.79677261947583</v>
       </c>
       <c r="CF46" t="n">
-        <v>43.26507025627404</v>
+        <v>43.26507025746583</v>
       </c>
       <c r="CG46" t="n">
-        <v>41.28355406353919</v>
+        <v>41.28355407383916</v>
       </c>
       <c r="CH46" t="n">
-        <v>37.15519865718527</v>
+        <v>37.15519866645525</v>
       </c>
       <c r="CI46" t="n">
         <v>7</v>
@@ -27066,10 +27030,10 @@
         <v>5</v>
       </c>
       <c r="CL46" t="n">
-        <v>8.991488679605331</v>
+        <v>8.991488706798002</v>
       </c>
       <c r="CM46" t="n">
-        <v>26.91425656385524</v>
+        <v>26.91425656735125</v>
       </c>
       <c r="CN46" t="inlineStr">
         <is>
@@ -27346,10 +27310,10 @@
         <v>6.400000095367432</v>
       </c>
       <c r="BX47" t="n">
-        <v>7.601720118418401</v>
+        <v>7.601720127829612</v>
       </c>
       <c r="BY47" t="n">
-        <v>11.06810449241719</v>
+        <v>11.06810450611992</v>
       </c>
       <c r="BZ47" t="n">
         <v>7.942720882078913</v>
@@ -27368,7 +27332,7 @@
         <v>5.254390410546408</v>
       </c>
       <c r="CF47" t="n">
-        <v>8.250643845501154</v>
+        <v>8.250643849353475</v>
       </c>
       <c r="CG47" t="n">
         <v>8.296106057582163</v>
@@ -27389,7 +27353,7 @@
         <v>16.66398969632026</v>
       </c>
       <c r="CM47" t="n">
-        <v>28.91630816495283</v>
+        <v>28.91630822514535</v>
       </c>
       <c r="CN47" t="inlineStr">
         <is>
@@ -27654,35 +27618,35 @@
         <v>16.78000068664551</v>
       </c>
       <c r="BX48" t="n">
-        <v>9.985664042179227</v>
+        <v>9.985664085228356</v>
       </c>
       <c r="BY48" t="n">
-        <v>17.51097130456651</v>
+        <v>17.51097129728228</v>
       </c>
       <c r="BZ48" t="n">
-        <v>28.91098001668654</v>
+        <v>28.91097988002219</v>
       </c>
       <c r="CA48" t="n">
         <v>29.08689850705222</v>
       </c>
       <c r="CB48" t="n">
-        <v>32.0896477401531</v>
+        <v>32.08964773789398</v>
       </c>
       <c r="CC48" t="n">
-        <v>27.8969568299852</v>
+        <v>27.8969568202356</v>
       </c>
       <c r="CD48" t="n">
-        <v>14.24941559744642</v>
+        <v>14.24941554391741</v>
       </c>
       <c r="CE48" t="inlineStr"/>
       <c r="CF48" t="n">
-        <v>21.07614304835437</v>
+        <v>21.07614302069211</v>
       </c>
       <c r="CG48" t="n">
-        <v>22.70396406727586</v>
+        <v>22.70396405875894</v>
       </c>
       <c r="CH48" t="n">
-        <v>20.43356766054827</v>
+        <v>20.43356765288305</v>
       </c>
       <c r="CI48" t="n">
         <v>4</v>
@@ -27694,10 +27658,10 @@
         <v>2.9</v>
       </c>
       <c r="CL48" t="n">
-        <v>21.77334221929135</v>
+        <v>21.77334217361064</v>
       </c>
       <c r="CM48" t="n">
-        <v>25.60275438562989</v>
+        <v>25.60275422077734</v>
       </c>
       <c r="CN48" t="inlineStr">
         <is>
@@ -27980,10 +27944,10 @@
         <v>12.96000003814697</v>
       </c>
       <c r="BX49" t="n">
-        <v>1.595679008623957</v>
+        <v>1.595679012201583</v>
       </c>
       <c r="BY49" t="n">
-        <v>2.95998456099744</v>
+        <v>2.959984567633937</v>
       </c>
       <c r="BZ49" t="n">
         <v>12.85329345100654</v>
@@ -27992,7 +27956,7 @@
         <v>9.387296094048613</v>
       </c>
       <c r="CB49" t="n">
-        <v>16.22301696803443</v>
+        <v>16.22301697178344</v>
       </c>
       <c r="CC49" t="n">
         <v>6.104046666666666</v>
@@ -28294,10 +28258,10 @@
         <v>32.65999984741211</v>
       </c>
       <c r="BX50" t="n">
-        <v>11.09799943479086</v>
+        <v>11.09799945323042</v>
       </c>
       <c r="BY50" t="n">
-        <v>20.58678895153704</v>
+        <v>20.58678898574243</v>
       </c>
       <c r="BZ50" t="n">
         <v>55.48012794592442</v>
@@ -28306,19 +28270,19 @@
         <v>52.41446107539311</v>
       </c>
       <c r="CB50" t="n">
-        <v>57.78863444721983</v>
+        <v>57.78863444319396</v>
       </c>
       <c r="CC50" t="n">
-        <v>28.23732422062287</v>
+        <v>28.23732426524397</v>
       </c>
       <c r="CD50" t="n">
-        <v>34.98921549802334</v>
+        <v>34.98921547468918</v>
       </c>
       <c r="CE50" t="n">
         <v>54.03219538348082</v>
       </c>
       <c r="CF50" t="n">
-        <v>43.36124964602878</v>
+        <v>43.36124965338113</v>
       </c>
       <c r="CG50" t="n">
         <v>52.41446107539311</v>
@@ -28339,7 +28303,7 @@
         <v>44.43666622243312</v>
       </c>
       <c r="CM50" t="n">
-        <v>32.76561496819668</v>
+        <v>32.76561499070845</v>
       </c>
       <c r="CN50" t="inlineStr">
         <is>
@@ -28374,7 +28338,7 @@
         <v>-0.2500150878204321</v>
       </c>
       <c r="CZ50" t="n">
-        <v>-10.82895234146481</v>
+        <v>-10.82896174015665</v>
       </c>
       <c r="DA50" t="b">
         <v>0</v>
@@ -28618,37 +28582,37 @@
         <v>44.2400016784668</v>
       </c>
       <c r="BX51" t="n">
-        <v>32.08627719702323</v>
+        <v>32.08627727406022</v>
       </c>
       <c r="BY51" t="n">
-        <v>44.20766641689121</v>
+        <v>44.20766626789196</v>
       </c>
       <c r="BZ51" t="n">
-        <v>50.92127200754537</v>
+        <v>50.92127171365978</v>
       </c>
       <c r="CA51" t="n">
         <v>47.73853825853298</v>
       </c>
       <c r="CB51" t="n">
-        <v>70.56922555068604</v>
+        <v>70.56922539177623</v>
       </c>
       <c r="CC51" t="n">
-        <v>59.893620859564</v>
+        <v>59.89362082767945</v>
       </c>
       <c r="CD51" t="n">
-        <v>25.15601706378459</v>
+        <v>25.15601688460888</v>
       </c>
       <c r="CE51" t="n">
         <v>76.57366731847841</v>
       </c>
       <c r="CF51" t="n">
-        <v>50.89328558406323</v>
+        <v>50.89328549208599</v>
       </c>
       <c r="CG51" t="n">
-        <v>49.32990513303918</v>
+        <v>49.32990498609638</v>
       </c>
       <c r="CH51" t="n">
-        <v>44.39691461973526</v>
+        <v>44.39691448748675</v>
       </c>
       <c r="CI51" t="n">
         <v>8</v>
@@ -28660,10 +28624,10 @@
         <v>3</v>
       </c>
       <c r="CL51" t="n">
-        <v>0.3546856584882185</v>
+        <v>0.3546853595539634</v>
       </c>
       <c r="CM51" t="n">
-        <v>15.03906793212177</v>
+        <v>15.03906772421661</v>
       </c>
       <c r="CN51" t="inlineStr">
         <is>
@@ -28946,37 +28910,37 @@
         <v>10.59000015258789</v>
       </c>
       <c r="BX52" t="n">
-        <v>8.101227402681777</v>
+        <v>8.101227365721037</v>
       </c>
       <c r="BY52" t="n">
-        <v>11.67224168632088</v>
+        <v>11.67224167563872</v>
       </c>
       <c r="BZ52" t="n">
-        <v>17.86658476468881</v>
+        <v>17.86658482985159</v>
       </c>
       <c r="CA52" t="n">
         <v>24.4848677465562</v>
       </c>
       <c r="CB52" t="n">
-        <v>25.37030468891811</v>
+        <v>25.37030466235509</v>
       </c>
       <c r="CC52" t="n">
-        <v>21.06883213035821</v>
+        <v>21.06883213716355</v>
       </c>
       <c r="CD52" t="n">
-        <v>8.897807323155927</v>
+        <v>8.897807359779586</v>
       </c>
       <c r="CE52" t="n">
         <v>10.22838513722926</v>
       </c>
       <c r="CF52" t="n">
-        <v>15.96128135998865</v>
+        <v>15.96128136428688</v>
       </c>
       <c r="CG52" t="n">
-        <v>14.76941322550484</v>
+        <v>14.76941325274515</v>
       </c>
       <c r="CH52" t="n">
-        <v>13.29247190295436</v>
+        <v>13.29247192747064</v>
       </c>
       <c r="CI52" t="n">
         <v>8</v>
@@ -28988,10 +28952,10 @@
         <v>3.1</v>
       </c>
       <c r="CL52" t="n">
-        <v>25.51909075946577</v>
+        <v>25.51909099096983</v>
       </c>
       <c r="CM52" t="n">
-        <v>50.72031284237677</v>
+        <v>50.72031288296444</v>
       </c>
       <c r="CN52" t="inlineStr">
         <is>
@@ -29256,10 +29220,10 @@
         <v>54.20000076293945</v>
       </c>
       <c r="BX53" t="n">
-        <v>10.5968759006117</v>
+        <v>10.59687588662215</v>
       </c>
       <c r="BY53" t="n">
-        <v>19.6572047956347</v>
+        <v>19.6572047696841</v>
       </c>
       <c r="BZ53" t="n">
         <v>62.12370329662177</v>
@@ -29268,7 +29232,7 @@
         <v>46.53820959650967</v>
       </c>
       <c r="CB53" t="n">
-        <v>83.16230744400134</v>
+        <v>83.16230742705898</v>
       </c>
       <c r="CC53" t="n">
         <v>11.76833333333333</v>
@@ -29278,7 +29242,7 @@
       </c>
       <c r="CE53" t="inlineStr"/>
       <c r="CF53" t="n">
-        <v>14.00747134319324</v>
+        <v>14.00747132987986</v>
       </c>
       <c r="CG53" t="n">
         <v>11.76833333333333</v>
@@ -29299,7 +29263,7 @@
         <v>-80.45848735994448</v>
       </c>
       <c r="CM53" t="n">
-        <v>-74.15595729516818</v>
+        <v>-74.15595731973161</v>
       </c>
       <c r="CN53" t="inlineStr">
         <is>
@@ -29564,10 +29528,10 @@
         <v>29.69000053405762</v>
       </c>
       <c r="BX54" t="n">
-        <v>15.52022462881667</v>
+        <v>15.52022456857821</v>
       </c>
       <c r="BY54" t="n">
-        <v>28.79001668645492</v>
+        <v>28.79001657471258</v>
       </c>
       <c r="BZ54" t="n">
         <v>54.71383964899351</v>
@@ -29576,23 +29540,23 @@
         <v>49.40805952371795</v>
       </c>
       <c r="CB54" t="n">
-        <v>60.9179064555565</v>
+        <v>60.91790647058306</v>
       </c>
       <c r="CC54" t="n">
-        <v>36.63500707769816</v>
+        <v>36.63500708862508</v>
       </c>
       <c r="CD54" t="n">
-        <v>30.32696327199993</v>
+        <v>30.32696335517236</v>
       </c>
       <c r="CE54" t="inlineStr"/>
       <c r="CF54" t="n">
-        <v>33.91477201049081</v>
+        <v>33.91477197022735</v>
       </c>
       <c r="CG54" t="n">
-        <v>32.71251188207653</v>
+        <v>32.71251183166883</v>
       </c>
       <c r="CH54" t="n">
-        <v>29.44126069386888</v>
+        <v>29.44126064850195</v>
       </c>
       <c r="CI54" t="n">
         <v>4</v>
@@ -29604,10 +29568,10 @@
         <v>3.5</v>
       </c>
       <c r="CL54" t="n">
-        <v>-0.8377899485161877</v>
+        <v>-0.8377901013182587</v>
       </c>
       <c r="CM54" t="n">
-        <v>14.22961064479244</v>
+        <v>14.22961050917957</v>
       </c>
       <c r="CN54" t="inlineStr">
         <is>
@@ -29650,7 +29614,7 @@
         <v>-0.8018702595090188</v>
       </c>
       <c r="CZ54" t="n">
-        <v>-18.56622956112421</v>
+        <v>-18.56623828442452</v>
       </c>
       <c r="DA54" t="b">
         <v>1</v>
@@ -29894,10 +29858,10 @@
         <v>33.61999893188477</v>
       </c>
       <c r="BX55" t="n">
-        <v>11.88440174707618</v>
+        <v>11.88440178704831</v>
       </c>
       <c r="BY55" t="n">
-        <v>22.04556524082631</v>
+        <v>22.04556531497461</v>
       </c>
       <c r="BZ55" t="n">
         <v>41.2467579488401</v>
@@ -29906,25 +29870,25 @@
         <v>33.64692724932318</v>
       </c>
       <c r="CB55" t="n">
-        <v>43.3017783932823</v>
+        <v>43.30177833737314</v>
       </c>
       <c r="CC55" t="n">
-        <v>23.86565137756786</v>
+        <v>23.86565136998831</v>
       </c>
       <c r="CD55" t="n">
-        <v>25.85073203247523</v>
+        <v>25.85073196476245</v>
       </c>
       <c r="CE55" t="n">
         <v>27.17936043616258</v>
       </c>
       <c r="CF55" t="n">
-        <v>28.62764680319422</v>
+        <v>28.62764680105909</v>
       </c>
       <c r="CG55" t="n">
-        <v>26.5150462343189</v>
+        <v>26.51504620046251</v>
       </c>
       <c r="CH55" t="n">
-        <v>23.86354161088701</v>
+        <v>23.86354158041626</v>
       </c>
       <c r="CI55" t="n">
         <v>8</v>
@@ -29936,10 +29900,10 @@
         <v>3.6</v>
       </c>
       <c r="CL55" t="n">
-        <v>-29.01980259060882</v>
+        <v>-29.01980268124164</v>
       </c>
       <c r="CM55" t="n">
-        <v>-14.84935243098971</v>
+        <v>-14.8493524373405</v>
       </c>
       <c r="CN55" t="inlineStr">
         <is>
@@ -30216,10 +30180,10 @@
         <v>10.51000022888184</v>
       </c>
       <c r="BX56" t="n">
-        <v>13.08696643078177</v>
+        <v>13.08696647328057</v>
       </c>
       <c r="BY56" t="n">
-        <v>19.05462312321825</v>
+        <v>19.05462318509651</v>
       </c>
       <c r="BZ56" t="n">
         <v>16.71315021106592</v>
@@ -30238,7 +30202,7 @@
         <v>14.7644299189986</v>
       </c>
       <c r="CF56" t="n">
-        <v>16.1591731493115</v>
+        <v>16.15917316670767</v>
       </c>
       <c r="CG56" t="n">
         <v>15.73879006503226</v>
@@ -30259,7 +30223,7 @@
         <v>34.77555423456011</v>
       </c>
       <c r="CM56" t="n">
-        <v>53.7504547802534</v>
+        <v>53.75045494577364</v>
       </c>
       <c r="CN56" t="inlineStr">
         <is>
@@ -30540,10 +30504,10 @@
         <v>4.639999866485596</v>
       </c>
       <c r="BX57" t="n">
-        <v>1.073494105837267</v>
+        <v>1.07349410829596</v>
       </c>
       <c r="BY57" t="n">
-        <v>1.99133156632813</v>
+        <v>1.991331570889005</v>
       </c>
       <c r="BZ57" t="n">
         <v>9.429447581431615</v>
@@ -30552,13 +30516,13 @@
         <v>8.84348872808631</v>
       </c>
       <c r="CB57" t="n">
-        <v>10.45610111157618</v>
+        <v>10.45610111185755</v>
       </c>
       <c r="CC57" t="n">
-        <v>4.222542560170031</v>
+        <v>4.222542559903953</v>
       </c>
       <c r="CD57" t="n">
-        <v>7.024657959522403</v>
+        <v>7.024657956380784</v>
       </c>
       <c r="CE57" t="n">
         <v>6.880721573088802</v>
@@ -30610,7 +30574,7 @@
         <v>7.906968852776419</v>
       </c>
       <c r="CZ57" t="n">
-        <v>-35.92779681249883</v>
+        <v>-35.92780109506861</v>
       </c>
       <c r="DA57" t="b">
         <v>0</v>
@@ -30850,10 +30814,10 @@
         <v>24.32999992370605</v>
       </c>
       <c r="BX58" t="n">
-        <v>4.265826977744358</v>
+        <v>4.265826973211738</v>
       </c>
       <c r="BY58" t="n">
-        <v>7.913109043715785</v>
+        <v>7.913109035307773</v>
       </c>
       <c r="BZ58" t="n">
         <v>28.32798760888446</v>
@@ -30862,13 +30826,13 @@
         <v>28.21652766068684</v>
       </c>
       <c r="CB58" t="n">
-        <v>25.16978178888895</v>
+        <v>25.16978179151773</v>
       </c>
       <c r="CC58" t="n">
-        <v>2.969809686149806</v>
+        <v>2.969809686254065</v>
       </c>
       <c r="CD58" t="n">
-        <v>18.23371040016945</v>
+        <v>18.23371040532684</v>
       </c>
       <c r="CE58" t="n">
         <v>18.22960446774209</v>
@@ -31164,10 +31128,10 @@
         <v>49.58000183105469</v>
       </c>
       <c r="BX59" t="n">
-        <v>8.25200269479908</v>
+        <v>8.252002698275955</v>
       </c>
       <c r="BY59" t="n">
-        <v>15.30746499885229</v>
+        <v>15.3074650053019</v>
       </c>
       <c r="BZ59" t="n">
         <v>19.41297353018541</v>
@@ -31176,25 +31140,25 @@
         <v>12.06941420422284</v>
       </c>
       <c r="CB59" t="n">
-        <v>13.68856517326287</v>
+        <v>13.68856515856025</v>
       </c>
       <c r="CC59" t="n">
-        <v>20.60981126403607</v>
+        <v>20.60981126191432</v>
       </c>
       <c r="CD59" t="n">
-        <v>10.37232045035143</v>
+        <v>10.37232044020563</v>
       </c>
       <c r="CE59" t="n">
         <v>12.92608390047425</v>
       </c>
       <c r="CF59" t="n">
-        <v>14.07982952702303</v>
+        <v>14.07982952489257</v>
       </c>
       <c r="CG59" t="n">
-        <v>13.30732453686856</v>
+        <v>13.30732452951725</v>
       </c>
       <c r="CH59" t="n">
-        <v>11.9765920831817</v>
+        <v>11.97659207656552</v>
       </c>
       <c r="CI59" t="n">
         <v>8</v>
@@ -31206,10 +31170,10 @@
         <v>2.5</v>
       </c>
       <c r="CL59" t="n">
-        <v>-75.84390552466638</v>
+        <v>-75.84390553801084</v>
       </c>
       <c r="CM59" t="n">
-        <v>-71.60179708141105</v>
+        <v>-71.60179708570806</v>
       </c>
       <c r="CN59" t="inlineStr">
         <is>
@@ -31226,7 +31190,11 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ59" t="inlineStr"/>
+      <c r="CQ59" t="inlineStr">
+        <is>
+          <t>A WEG (WEGE3) consolida sua posição de destaque no setor de bens industriais ao apresentar uma eficiência operacional excepcional, evidenciada por um ROE de 33,2% e um ROIC de 24,3%, ambos situados confortavelmente acima das médias setoriais de 14,5% e 12,6%, respectivamente. Essa alta rentabilidade convive com múltiplos de preço bastante esticados, como o P/L de 33,84 e o P/VP de 11,22, o que sugere que o mercado cobra um prêmio elevado pela qualidade da empresa, gerando uma clara assimetria entre a excelência dos indicadores de retorno e o valuation pressionado. No âmbito financeiro, a excelente rentabilidade é sustentada por uma estrutura de capital extremamente robusta, onde a relação dívida líquida sobre EBITDA de -0,35 fica muito abaixo do par setorial de 2,39, indicando uma posição de caixa líquido que confere máxima segurança contra oscilações macroeconômicas. Essa solidez financeira e a margem líquida de 15,58% garantem a sustentabilidade do dividendo distribuído, embora o rendimento de 3,98% seja considerado moderado, refletindo uma postura que prioriza o reinvestimento ou a manutenção de caixa em detrimento de proventos agressivos. Por outro lado, o crescimento recente acende um sinal de alerta, visto que a taxa composta anual de receita nos últimos cinco anos recuou 2,1%, desempenho significativamente abaixo da média de expansão do setor, que foi de 21,6%. No checklist de critérios fundamentalistas, a companhia atende a 6 dos 8 requisitos avaliados, falhando justamente no crescimento frente aos pares e na ocorrência de vendas por parte de pessoas internas à empresa, o que não anula sua robustez geral. Sob a ótica de avaliação de preço, os diferentes métodos teóricos revelam uma dispersão notável, variando desde o conservador modelo de Bazin a R$ 8,25 até o fluxo de caixa descontado a R$ 19,41, resultando em uma média de R$ 14,08 e uma mediana de R$ 13,31. Frente ao preço atual de R$ 49,58, o preço-teto ajustado com margem de segurança fica estabelecido em R$ 11,98, o que aponta para um expressivo potencial de desvalorização de 75,8% em relação ao valor justo calculado. Em um balanço final, os pontos positivos residem na rentabilidade espetacular, na saúde financeira impecável com caixa líquido e no forte alinhamento aos critérios de qualidade, enquanto os pontos negativos concentram-se no valuation severamente esticado perante os modelos matemáticos e no crescimento de receita abaixo da média de seus pares de mercado.</t>
+        </is>
+      </c>
       <c r="CR59" t="inlineStr">
         <is>
           <t>Rompimento</t>
@@ -31256,7 +31224,7 @@
         <v>0.6291888987432825</v>
       </c>
       <c r="CZ59" t="n">
-        <v>-8.667873268803072</v>
+        <v>-8.667879823856294</v>
       </c>
       <c r="DA59" t="b">
         <v>0</v>
@@ -31500,37 +31468,37 @@
         <v>23.78000068664551</v>
       </c>
       <c r="BX60" t="n">
-        <v>10.50498160392796</v>
+        <v>10.50498165458117</v>
       </c>
       <c r="BY60" t="n">
-        <v>14.29883869102245</v>
+        <v>14.29883866268985</v>
       </c>
       <c r="BZ60" t="n">
-        <v>17.83956647296637</v>
+        <v>17.83956635159864</v>
       </c>
       <c r="CA60" t="n">
         <v>21.12463825554054</v>
       </c>
       <c r="CB60" t="n">
-        <v>17.52809449762296</v>
+        <v>17.52809443199903</v>
       </c>
       <c r="CC60" t="n">
-        <v>23.23161879753909</v>
+        <v>23.23161878279891</v>
       </c>
       <c r="CD60" t="n">
-        <v>8.786388962420199</v>
+        <v>8.786388886776715</v>
       </c>
       <c r="CE60" t="n">
         <v>18.54956014100212</v>
       </c>
       <c r="CF60" t="n">
-        <v>16.48296092775521</v>
+        <v>16.48296089587337</v>
       </c>
       <c r="CG60" t="n">
-        <v>17.68383048529466</v>
+        <v>17.68383039179884</v>
       </c>
       <c r="CH60" t="n">
-        <v>15.9154474367652</v>
+        <v>15.91544735261895</v>
       </c>
       <c r="CI60" t="n">
         <v>8</v>
@@ -31542,10 +31510,10 @@
         <v>2.6</v>
       </c>
       <c r="CL60" t="n">
-        <v>-33.07213213957948</v>
+        <v>-33.07213249343247</v>
       </c>
       <c r="CM60" t="n">
-        <v>-30.6856162665639</v>
+        <v>-30.68561640063385</v>
       </c>
       <c r="CN60" t="inlineStr">
         <is>
@@ -31828,10 +31796,10 @@
         <v>4.519999980926514</v>
       </c>
       <c r="BX61" t="n">
-        <v>2.935043325145307</v>
+        <v>2.935043317450478</v>
       </c>
       <c r="BY61" t="n">
-        <v>5.444505368144545</v>
+        <v>5.444505353870636</v>
       </c>
       <c r="BZ61" t="n">
         <v>13.16263730709369</v>
@@ -31840,13 +31808,13 @@
         <v>14.66138724509534</v>
       </c>
       <c r="CB61" t="n">
-        <v>15.01900792248579</v>
+        <v>15.01900790988379</v>
       </c>
       <c r="CC61" t="n">
-        <v>9.454768182827884</v>
+        <v>9.454768183821967</v>
       </c>
       <c r="CD61" t="n">
-        <v>6.417766700864689</v>
+        <v>6.417766707825741</v>
       </c>
       <c r="CE61" t="n">
         <v>1.463859008533987</v>
@@ -32142,37 +32110,37 @@
         <v>30</v>
       </c>
       <c r="BX62" t="n">
-        <v>13.81421954786151</v>
+        <v>13.8142195505888</v>
       </c>
       <c r="BY62" t="n">
-        <v>14.42907654784607</v>
+        <v>14.4290765484113</v>
       </c>
       <c r="BZ62" t="n">
-        <v>15.22607861392396</v>
+        <v>15.22607861151439</v>
       </c>
       <c r="CA62" t="n">
         <v>30.50864986347318</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.22999674718342</v>
+        <v>14.22999674594355</v>
       </c>
       <c r="CC62" t="n">
-        <v>30.46475764977117</v>
+        <v>30.46475764920133</v>
       </c>
       <c r="CD62" t="n">
-        <v>6.126727555486439</v>
+        <v>6.126727553074426</v>
       </c>
       <c r="CE62" t="n">
         <v>37.56051795197769</v>
       </c>
       <c r="CF62" t="n">
-        <v>17.82850093222082</v>
+        <v>17.82850093174385</v>
       </c>
       <c r="CG62" t="n">
-        <v>14.42907654784607</v>
+        <v>14.4290765484113</v>
       </c>
       <c r="CH62" t="n">
-        <v>12.98616889306147</v>
+        <v>12.98616889357017</v>
       </c>
       <c r="CI62" t="n">
         <v>7</v>
@@ -32184,10 +32152,10 @@
         <v>6.1</v>
       </c>
       <c r="CL62" t="n">
-        <v>-56.71277035646178</v>
+        <v>-56.71277035476609</v>
       </c>
       <c r="CM62" t="n">
-        <v>-40.57166355926392</v>
+        <v>-40.57166356085382</v>
       </c>
       <c r="CN62" t="inlineStr">
         <is>
@@ -32466,35 +32434,35 @@
         <v>3.509999990463257</v>
       </c>
       <c r="BX63" t="n">
-        <v>2.694277163240034</v>
+        <v>2.694277181541374</v>
       </c>
       <c r="BY63" t="n">
-        <v>3.136287803684305</v>
+        <v>3.136287809682764</v>
       </c>
       <c r="BZ63" t="n">
-        <v>3.840069870506376</v>
+        <v>3.840069851766555</v>
       </c>
       <c r="CA63" t="n">
         <v>7.068546969028743</v>
       </c>
       <c r="CB63" t="n">
-        <v>5.776564266907434</v>
+        <v>5.776564275997806</v>
       </c>
       <c r="CC63" t="n">
-        <v>8.480104657168392</v>
+        <v>8.480104652725563</v>
       </c>
       <c r="CD63" t="n">
-        <v>1.74507209871168</v>
+        <v>1.745072083234603</v>
       </c>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="n">
-        <v>4.677274689892423</v>
+        <v>4.67727468913963</v>
       </c>
       <c r="CG63" t="n">
-        <v>3.840069870506376</v>
+        <v>3.840069851766555</v>
       </c>
       <c r="CH63" t="n">
-        <v>3.456062883455739</v>
+        <v>3.4560628665899</v>
       </c>
       <c r="CI63" t="n">
         <v>7</v>
@@ -32506,10 +32474,10 @@
         <v>4.9</v>
       </c>
       <c r="CL63" t="n">
-        <v>-1.536669719489059</v>
+        <v>-1.536670199997314</v>
       </c>
       <c r="CM63" t="n">
-        <v>33.2556895327828</v>
+        <v>33.2556895113357</v>
       </c>
       <c r="CN63" t="inlineStr">
         <is>
@@ -32788,37 +32756,37 @@
         <v>18.63999938964844</v>
       </c>
       <c r="BX64" t="n">
-        <v>8.745140376463256</v>
+        <v>8.74514040727321</v>
       </c>
       <c r="BY64" t="n">
-        <v>9.206222538315652</v>
+        <v>9.206222536748497</v>
       </c>
       <c r="BZ64" t="n">
-        <v>9.666395036062593</v>
+        <v>9.666395000361485</v>
       </c>
       <c r="CA64" t="n">
         <v>16.93457208699175</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.239151917313791</v>
+        <v>9.239151890987216</v>
       </c>
       <c r="CC64" t="n">
-        <v>17.5422466592823</v>
+        <v>17.54224665167746</v>
       </c>
       <c r="CD64" t="n">
-        <v>3.934238755871024</v>
+        <v>3.934238720624436</v>
       </c>
       <c r="CE64" t="n">
         <v>16.16233025852235</v>
       </c>
       <c r="CF64" t="n">
-        <v>11.42878720360284</v>
+        <v>11.4287871941483</v>
       </c>
       <c r="CG64" t="n">
-        <v>9.452773476688192</v>
+        <v>9.45277344567435</v>
       </c>
       <c r="CH64" t="n">
-        <v>8.507496129019373</v>
+        <v>8.507496101106915</v>
       </c>
       <c r="CI64" t="n">
         <v>8</v>
@@ -32830,10 +32798,10 @@
         <v>4.5</v>
       </c>
       <c r="CL64" t="n">
-        <v>-54.35892485198291</v>
+        <v>-54.35892500172785</v>
       </c>
       <c r="CM64" t="n">
-        <v>-38.68676192151745</v>
+        <v>-38.68676197223924</v>
       </c>
       <c r="CN64" t="inlineStr">
         <is>
@@ -33094,10 +33062,10 @@
         <v>12.85999965667725</v>
       </c>
       <c r="BX65" t="n">
-        <v>10.87454815147874</v>
+        <v>10.87454823001372</v>
       </c>
       <c r="BY65" t="n">
-        <v>15.83334210855304</v>
+        <v>15.83334222289998</v>
       </c>
       <c r="BZ65" t="n">
         <v>15.62429864829946</v>
@@ -33114,13 +33082,13 @@
       </c>
       <c r="CE65" t="inlineStr"/>
       <c r="CF65" t="n">
-        <v>12.41638056041614</v>
+        <v>12.41638060863662</v>
       </c>
       <c r="CG65" t="n">
-        <v>13.2494233998891</v>
+        <v>13.24942343915659</v>
       </c>
       <c r="CH65" t="n">
-        <v>11.92448105990019</v>
+        <v>11.92448109524093</v>
       </c>
       <c r="CI65" t="n">
         <v>4</v>
@@ -33132,10 +33100,10 @@
         <v>2.2</v>
       </c>
       <c r="CL65" t="n">
-        <v>-7.27463936043975</v>
+        <v>-7.274639085628376</v>
       </c>
       <c r="CM65" t="n">
-        <v>-3.449604262086925</v>
+        <v>-3.449603887122077</v>
       </c>
       <c r="CN65" t="inlineStr">
         <is>
@@ -33726,10 +33694,10 @@
         <v>36.06999969482422</v>
       </c>
       <c r="BX67" t="n">
-        <v>10.3273466514841</v>
+        <v>10.32734671249398</v>
       </c>
       <c r="BY67" t="n">
-        <v>19.15722803850301</v>
+        <v>19.15722815167633</v>
       </c>
       <c r="BZ67" t="n">
         <v>29.14192048514762</v>
@@ -33738,25 +33706,25 @@
         <v>21.64477052485838</v>
       </c>
       <c r="CB67" t="n">
-        <v>26.34387263376502</v>
+        <v>26.34387248717407</v>
       </c>
       <c r="CC67" t="n">
-        <v>22.88383982078307</v>
+        <v>22.88383980163769</v>
       </c>
       <c r="CD67" t="n">
-        <v>16.89301646179683</v>
+        <v>16.89301633691694</v>
       </c>
       <c r="CE67" t="n">
         <v>26.70821873920952</v>
       </c>
       <c r="CF67" t="n">
-        <v>21.63752666944345</v>
+        <v>21.63752665488931</v>
       </c>
       <c r="CG67" t="n">
-        <v>22.26430517282072</v>
+        <v>22.26430516324804</v>
       </c>
       <c r="CH67" t="n">
-        <v>20.03787465553865</v>
+        <v>20.03787464692323</v>
       </c>
       <c r="CI67" t="n">
         <v>8</v>
@@ -33768,10 +33736,10 @@
         <v>2.8</v>
       </c>
       <c r="CL67" t="n">
-        <v>-44.44725582181267</v>
+        <v>-44.44725584569794</v>
       </c>
       <c r="CM67" t="n">
-        <v>-40.01240129606025</v>
+        <v>-40.01240133640993</v>
       </c>
       <c r="CN67" t="inlineStr">
         <is>
@@ -34054,10 +34022,10 @@
         <v>8.960000038146973</v>
       </c>
       <c r="BX68" t="n">
-        <v>0.5329545608790383</v>
+        <v>0.5329545607665733</v>
       </c>
       <c r="BY68" t="n">
-        <v>0.9886307104306159</v>
+        <v>0.9886307102219934</v>
       </c>
       <c r="BZ68" t="n">
         <v>10.10382983025084</v>
@@ -34066,13 +34034,13 @@
         <v>9.267312794547912</v>
       </c>
       <c r="CB68" t="n">
-        <v>11.09857033955541</v>
+        <v>11.09857033966089</v>
       </c>
       <c r="CC68" t="n">
-        <v>0.7358541828583098</v>
+        <v>0.7358541828603419</v>
       </c>
       <c r="CD68" t="n">
-        <v>8.614201657364308</v>
+        <v>8.614201657514842</v>
       </c>
       <c r="CE68" t="inlineStr"/>
       <c r="CF68" t="inlineStr"/>
@@ -34370,10 +34338,10 @@
         <v>8.510000228881836</v>
       </c>
       <c r="BX69" t="n">
-        <v>1.637947947346442</v>
+        <v>1.637947944462456</v>
       </c>
       <c r="BY69" t="n">
-        <v>3.038393442327651</v>
+        <v>3.038393436977855</v>
       </c>
       <c r="BZ69" t="n">
         <v>24.61954214687431</v>
@@ -34382,13 +34350,13 @@
         <v>24.35075698940731</v>
       </c>
       <c r="CB69" t="n">
-        <v>26.29479862200133</v>
+        <v>26.29479861846277</v>
       </c>
       <c r="CC69" t="n">
-        <v>6.709480300305735</v>
+        <v>6.709480300476703</v>
       </c>
       <c r="CD69" t="n">
-        <v>18.34473463986651</v>
+        <v>18.34473464318356</v>
       </c>
       <c r="CE69" t="n">
         <v>14.67770218220867</v>
@@ -34684,10 +34652,10 @@
         <v>21.79999923706055</v>
       </c>
       <c r="BX70" t="n">
-        <v>6.028554339175082</v>
+        <v>6.028554349483475</v>
       </c>
       <c r="BY70" t="n">
-        <v>11.18296829916978</v>
+        <v>11.18296831829185</v>
       </c>
       <c r="BZ70" t="n">
         <v>32.56482411398559</v>
@@ -34696,25 +34664,25 @@
         <v>33.56557093257108</v>
       </c>
       <c r="CB70" t="n">
-        <v>29.04126497163401</v>
+        <v>29.04126497044188</v>
       </c>
       <c r="CC70" t="n">
-        <v>25.18528583168923</v>
+        <v>25.18528583003149</v>
       </c>
       <c r="CD70" t="n">
-        <v>18.83916134245095</v>
+        <v>18.83916133147457</v>
       </c>
       <c r="CE70" t="n">
         <v>13.17078629161308</v>
       </c>
       <c r="CF70" t="n">
-        <v>23.36426596901625</v>
+        <v>23.36426596977279</v>
       </c>
       <c r="CG70" t="n">
-        <v>25.18528583168923</v>
+        <v>25.18528583003149</v>
       </c>
       <c r="CH70" t="n">
-        <v>22.66675724852031</v>
+        <v>22.66675724702834</v>
       </c>
       <c r="CI70" t="n">
         <v>7</v>
@@ -34726,10 +34694,10 @@
         <v>5.6</v>
       </c>
       <c r="CL70" t="n">
-        <v>3.975954320155428</v>
+        <v>3.975954313311525</v>
       </c>
       <c r="CM70" t="n">
-        <v>7.175535718810533</v>
+        <v>7.175535722280912</v>
       </c>
       <c r="CN70" t="inlineStr">
         <is>
@@ -35008,25 +34976,25 @@
         <v>17.30999946594238</v>
       </c>
       <c r="BX71" t="n">
-        <v>4.028450003398035</v>
+        <v>4.028449968012602</v>
       </c>
       <c r="BY71" t="n">
-        <v>6.904966380176691</v>
+        <v>6.904966336734769</v>
       </c>
       <c r="BZ71" t="n">
-        <v>23.39184144000728</v>
+        <v>23.39184149831099</v>
       </c>
       <c r="CA71" t="n">
         <v>32.83973692061836</v>
       </c>
       <c r="CB71" t="n">
-        <v>16.52656712826266</v>
+        <v>16.52656711148098</v>
       </c>
       <c r="CC71" t="n">
-        <v>20.29662202915872</v>
+        <v>20.29662203297871</v>
       </c>
       <c r="CD71" t="n">
-        <v>11.5793052949364</v>
+        <v>11.57930531875787</v>
       </c>
       <c r="CE71" t="n">
         <v>22.32522379682559</v>
@@ -35151,7 +35119,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -35322,35 +35290,35 @@
         <v>23.89999961853027</v>
       </c>
       <c r="BX72" t="n">
-        <v>22.96133605045733</v>
+        <v>22.96133599289675</v>
       </c>
       <c r="BY72" t="n">
-        <v>28.91661741337681</v>
+        <v>28.91661739763503</v>
       </c>
       <c r="BZ72" t="n">
-        <v>38.25461865785567</v>
+        <v>38.25461873292892</v>
       </c>
       <c r="CA72" t="n">
         <v>61.73697842188816</v>
       </c>
       <c r="CB72" t="n">
-        <v>68.23386863123601</v>
+        <v>68.2338685735083</v>
       </c>
       <c r="CC72" t="n">
-        <v>41.71087887277269</v>
+        <v>41.71087888096203</v>
       </c>
       <c r="CD72" t="n">
-        <v>18.2968682173754</v>
+        <v>18.29686827121986</v>
       </c>
       <c r="CE72" t="inlineStr"/>
       <c r="CF72" t="n">
-        <v>40.01588089499457</v>
+        <v>40.01588089586272</v>
       </c>
       <c r="CG72" t="n">
-        <v>38.25461865785567</v>
+        <v>38.25461873292892</v>
       </c>
       <c r="CH72" t="n">
-        <v>34.4291567920701</v>
+        <v>34.42915685963603</v>
       </c>
       <c r="CI72" t="n">
         <v>7</v>
@@ -35362,10 +35330,10 @@
         <v>3.7</v>
       </c>
       <c r="CL72" t="n">
-        <v>44.05505163847914</v>
+        <v>44.05505192118178</v>
       </c>
       <c r="CM72" t="n">
-        <v>67.43046666816367</v>
+        <v>67.43046667179608</v>
       </c>
       <c r="CN72" t="inlineStr">
         <is>
@@ -35379,11 +35347,7 @@
       </c>
       <c r="CP72" t="inlineStr"/>
       <c r="CQ72" t="inlineStr"/>
-      <c r="CR72" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR72" t="inlineStr"/>
       <c r="CS72" t="b">
         <v>0</v>
       </c>
@@ -35410,14 +35374,14 @@
         <v>0</v>
       </c>
       <c r="DB72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC72" t="b">
         <v>0</v>
       </c>
       <c r="DD72" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-6.9%))</t>
         </is>
       </c>
     </row>
@@ -35648,10 +35612,10 @@
         <v>24.69000053405762</v>
       </c>
       <c r="BX73" t="n">
-        <v>4.528795224611128</v>
+        <v>4.528795219833952</v>
       </c>
       <c r="BY73" t="n">
-        <v>8.400915141653641</v>
+        <v>8.40091513279198</v>
       </c>
       <c r="BZ73" t="n">
         <v>29.76728908792206</v>
@@ -35660,19 +35624,19 @@
         <v>25.23396384622111</v>
       </c>
       <c r="CB73" t="n">
-        <v>34.47267202281515</v>
+        <v>34.47267202863429</v>
       </c>
       <c r="CC73" t="n">
-        <v>11.78156829100659</v>
+        <v>11.78156829156017</v>
       </c>
       <c r="CD73" t="n">
-        <v>24.04380284006345</v>
+        <v>24.04380284754641</v>
       </c>
       <c r="CE73" t="n">
         <v>24.69000053405762</v>
       </c>
       <c r="CF73" t="n">
-        <v>24.99821610368099</v>
+        <v>24.99821610599028</v>
       </c>
       <c r="CG73" t="n">
         <v>24.96198219013936</v>
@@ -35693,7 +35657,7 @@
         <v>-9.008572356505573</v>
       </c>
       <c r="CM73" t="n">
-        <v>1.248341688766752</v>
+        <v>1.24834169811987</v>
       </c>
       <c r="CN73" t="inlineStr">
         <is>
@@ -35972,10 +35936,10 @@
         <v>4.050000190734863</v>
       </c>
       <c r="BX74" t="n">
-        <v>0.9831252892081325</v>
+        <v>0.9831252888117605</v>
       </c>
       <c r="BY74" t="n">
-        <v>1.823697411481086</v>
+        <v>1.823697410745816</v>
       </c>
       <c r="BZ74" t="n">
         <v>6.002517061212185</v>
@@ -35984,7 +35948,7 @@
         <v>3.984656322398878</v>
       </c>
       <c r="CB74" t="n">
-        <v>8.334872137576824</v>
+        <v>8.334872136956108</v>
       </c>
       <c r="CC74" t="n">
         <v>3.760485277130923</v>
@@ -36042,7 +36006,7 @@
         <v>1.50376393620828</v>
       </c>
       <c r="CZ74" t="n">
-        <v>-44.6329217901767</v>
+        <v>-44.63291810308804</v>
       </c>
       <c r="DA74" t="b">
         <v>0</v>
@@ -36286,10 +36250,10 @@
         <v>12.53999996185303</v>
       </c>
       <c r="BX75" t="n">
-        <v>2.074260018089848</v>
+        <v>2.074260018791665</v>
       </c>
       <c r="BY75" t="n">
-        <v>3.847752333556667</v>
+        <v>3.847752334858538</v>
       </c>
       <c r="BZ75" t="n">
         <v>16.17867570540921</v>
@@ -36298,7 +36262,7 @@
         <v>12.83897725188507</v>
       </c>
       <c r="CB75" t="n">
-        <v>21.1431002610568</v>
+        <v>21.14310026201351</v>
       </c>
       <c r="CC75" t="n">
         <v>9.294207014285712</v>
@@ -36433,7 +36397,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -36602,10 +36566,10 @@
         <v>55.5</v>
       </c>
       <c r="BX76" t="n">
-        <v>40.36268332132143</v>
+        <v>40.36268306319869</v>
       </c>
       <c r="BY76" t="n">
-        <v>58.76806691584401</v>
+        <v>58.7680665400173</v>
       </c>
       <c r="BZ76" t="n">
         <v>35.62962962962963</v>
@@ -36624,13 +36588,13 @@
         <v>48.31609747574325</v>
       </c>
       <c r="CF76" t="n">
-        <v>43.22743374635768</v>
+        <v>43.22743364069944</v>
       </c>
       <c r="CG76" t="n">
-        <v>41.42467022373714</v>
+        <v>41.42467009467578</v>
       </c>
       <c r="CH76" t="n">
-        <v>37.28220320136342</v>
+        <v>37.2822030852082</v>
       </c>
       <c r="CI76" t="n">
         <v>6</v>
@@ -36642,10 +36606,10 @@
         <v>6.4</v>
       </c>
       <c r="CL76" t="n">
-        <v>-32.82485909664248</v>
+        <v>-32.82485930593116</v>
       </c>
       <c r="CM76" t="n">
-        <v>-22.11273198854472</v>
+        <v>-22.11273217891993</v>
       </c>
       <c r="CN76" t="inlineStr">
         <is>
@@ -36659,11 +36623,7 @@
       </c>
       <c r="CP76" t="inlineStr"/>
       <c r="CQ76" t="inlineStr"/>
-      <c r="CR76" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CR76" t="inlineStr"/>
       <c r="CS76" t="b">
         <v>0</v>
       </c>
@@ -36690,14 +36650,14 @@
         <v>0</v>
       </c>
       <c r="DB76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC76" t="b">
         <v>0</v>
       </c>
       <c r="DD76" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-13.2%))</t>
         </is>
       </c>
     </row>
@@ -36928,10 +36888,10 @@
         <v>28.85000038146973</v>
       </c>
       <c r="BX77" t="n">
-        <v>13.47679403422093</v>
+        <v>13.47679401923087</v>
       </c>
       <c r="BY77" t="n">
-        <v>24.99945293347982</v>
+        <v>24.99945290567326</v>
       </c>
       <c r="BZ77" t="n">
         <v>37.04094041225521</v>
@@ -36940,19 +36900,19 @@
         <v>25.82930863038749</v>
       </c>
       <c r="CB77" t="n">
-        <v>42.2473045885765</v>
+        <v>42.24730462358146</v>
       </c>
       <c r="CC77" t="n">
-        <v>42.15809541913985</v>
+        <v>42.1580954268265</v>
       </c>
       <c r="CD77" t="n">
-        <v>22.53170129268489</v>
+        <v>22.53170132747023</v>
       </c>
       <c r="CE77" t="n">
         <v>25.12299540697245</v>
       </c>
       <c r="CF77" t="n">
-        <v>29.17582408971465</v>
+        <v>29.17582409404969</v>
       </c>
       <c r="CG77" t="n">
         <v>25.47615201867997</v>
@@ -36973,7 +36933,7 @@
         <v>-20.52500341892921</v>
       </c>
       <c r="CM77" t="n">
-        <v>1.129371590768491</v>
+        <v>1.129371605794627</v>
       </c>
       <c r="CN77" t="inlineStr">
         <is>
@@ -37012,7 +36972,7 @@
         <v>-2.337816543811788</v>
       </c>
       <c r="CZ77" t="n">
-        <v>-24.19493858539801</v>
+        <v>-24.19493061245316</v>
       </c>
       <c r="DA77" t="b">
         <v>0</v>
@@ -37256,10 +37216,10 @@
         <v>15.11999988555908</v>
       </c>
       <c r="BX78" t="n">
-        <v>2.439882943285004</v>
+        <v>2.439882942805009</v>
       </c>
       <c r="BY78" t="n">
-        <v>4.525982859793682</v>
+        <v>4.525982858903291</v>
       </c>
       <c r="BZ78" t="n">
         <v>25.45616245027419</v>
@@ -37268,7 +37228,7 @@
         <v>19.49357338326157</v>
       </c>
       <c r="CB78" t="n">
-        <v>33.15862255265264</v>
+        <v>33.15862255179877</v>
       </c>
       <c r="CC78" t="n">
         <v>10.38593205872702</v>
@@ -37574,10 +37534,10 @@
         <v>14.64999961853027</v>
       </c>
       <c r="BX79" t="n">
-        <v>9.577574210787636</v>
+        <v>9.577574390531973</v>
       </c>
       <c r="BY79" t="n">
-        <v>17.76640016101107</v>
+        <v>17.76640049443681</v>
       </c>
       <c r="BZ79" t="n">
         <v>13.92485616538925</v>
@@ -37598,7 +37558,7 @@
         <v>12.21188626720157</v>
       </c>
       <c r="CF79" t="n">
-        <v>15.01496750386246</v>
+        <v>15.01496756800872</v>
       </c>
       <c r="CG79" t="n">
         <v>13.27530794084946</v>
@@ -37619,7 +37579,7 @@
         <v>-18.44520506572443</v>
       </c>
       <c r="CM79" t="n">
-        <v>2.491248428911552</v>
+        <v>2.491248866769991</v>
       </c>
       <c r="CN79" t="inlineStr">
         <is>
@@ -37898,25 +37858,25 @@
         <v>26.55999946594238</v>
       </c>
       <c r="BX80" t="n">
-        <v>12.09583915021851</v>
+        <v>12.09583908826273</v>
       </c>
       <c r="BY80" t="n">
-        <v>12.77825688333884</v>
+        <v>12.77825685461627</v>
       </c>
       <c r="BZ80" t="n">
-        <v>14.05452305853078</v>
+        <v>14.05452309892776</v>
       </c>
       <c r="CA80" t="n">
         <v>32.71469597157468</v>
       </c>
       <c r="CB80" t="n">
-        <v>13.10490990732978</v>
+        <v>13.10490990956222</v>
       </c>
       <c r="CC80" t="n">
-        <v>24.67124335479556</v>
+        <v>24.67124336309348</v>
       </c>
       <c r="CD80" t="n">
-        <v>5.748575091015452</v>
+        <v>5.748575130652279</v>
       </c>
       <c r="CE80" t="n">
         <v>64.69524327175267</v>
@@ -38212,10 +38172,10 @@
         <v>6.949999809265137</v>
       </c>
       <c r="BX81" t="n">
-        <v>1.251744408776458</v>
+        <v>1.251744406074428</v>
       </c>
       <c r="BY81" t="n">
-        <v>2.321985878280329</v>
+        <v>2.321985873268065</v>
       </c>
       <c r="BZ81" t="n">
         <v>10.39362273958951</v>
@@ -38224,13 +38184,13 @@
         <v>10.1957267373713</v>
       </c>
       <c r="CB81" t="n">
-        <v>10.06783796787904</v>
+        <v>10.06783796863308</v>
       </c>
       <c r="CC81" t="n">
-        <v>1.87346734930695</v>
+        <v>1.873467349415714</v>
       </c>
       <c r="CD81" t="n">
-        <v>7.1806213510549</v>
+        <v>7.180621354212599</v>
       </c>
       <c r="CE81" t="n">
         <v>11.09654186695129</v>
@@ -38526,10 +38486,10 @@
         <v>9.840000152587891</v>
       </c>
       <c r="BX82" t="n">
-        <v>6.031752879907764</v>
+        <v>6.03175286958424</v>
       </c>
       <c r="BY82" t="n">
-        <v>11.1889015922289</v>
+        <v>11.18890157307876</v>
       </c>
       <c r="BZ82" t="n">
         <v>7.877945741497857</v>
@@ -38550,7 +38510,7 @@
         <v>39.41309108925088</v>
       </c>
       <c r="CF82" t="n">
-        <v>10.02204608762491</v>
+        <v>10.02204608341439</v>
       </c>
       <c r="CG82" t="n">
         <v>7.877945741497857</v>
@@ -38571,7 +38531,7 @@
         <v>-27.94561933534744</v>
       </c>
       <c r="CM82" t="n">
-        <v>1.850060286728183</v>
+        <v>1.850060243938279</v>
       </c>
       <c r="CN82" t="inlineStr">
         <is>
@@ -38854,35 +38814,35 @@
         <v>2.740000009536743</v>
       </c>
       <c r="BX83" t="n">
-        <v>1.259649643459965</v>
+        <v>1.259649640246443</v>
       </c>
       <c r="BY83" t="n">
-        <v>1.724742888473408</v>
+        <v>1.72474288541942</v>
       </c>
       <c r="BZ83" t="n">
-        <v>3.737472172875016</v>
+        <v>3.737472175791858</v>
       </c>
       <c r="CA83" t="n">
         <v>7.156543735561407</v>
       </c>
       <c r="CB83" t="n">
-        <v>3.768435163752396</v>
+        <v>3.768435160339057</v>
       </c>
       <c r="CC83" t="n">
-        <v>1.340681369350597</v>
+        <v>1.340681369447655</v>
       </c>
       <c r="CD83" t="n">
-        <v>1.843597822021595</v>
+        <v>1.843597823820138</v>
       </c>
       <c r="CE83" t="inlineStr"/>
       <c r="CF83" t="n">
-        <v>2.279096509988829</v>
+        <v>2.279096509177429</v>
       </c>
       <c r="CG83" t="n">
-        <v>1.784170355247502</v>
+        <v>1.784170354619779</v>
       </c>
       <c r="CH83" t="n">
-        <v>1.605753319722752</v>
+        <v>1.605753319157802</v>
       </c>
       <c r="CI83" t="n">
         <v>6</v>
@@ -38894,10 +38854,10 @@
         <v>5.7</v>
       </c>
       <c r="CL83" t="n">
-        <v>-41.3958644476706</v>
+        <v>-41.39586446828921</v>
       </c>
       <c r="CM83" t="n">
-        <v>-16.82129554539089</v>
+        <v>-16.82129557500404</v>
       </c>
       <c r="CN83" t="inlineStr">
         <is>
@@ -39174,10 +39134,10 @@
         <v>5.159999847412109</v>
       </c>
       <c r="BX84" t="n">
-        <v>3.051428247492851</v>
+        <v>3.051428223020478</v>
       </c>
       <c r="BY84" t="n">
-        <v>4.442879528349591</v>
+        <v>4.442879492717816</v>
       </c>
       <c r="BZ84" t="n">
         <v>4.310361318320155</v>
@@ -39486,10 +39446,10 @@
         <v>18.45999908447266</v>
       </c>
       <c r="BX85" t="n">
-        <v>4.484582523634422</v>
+        <v>4.484582539844998</v>
       </c>
       <c r="BY85" t="n">
-        <v>8.318900581341852</v>
+        <v>8.318900611412468</v>
       </c>
       <c r="BZ85" t="n">
         <v>32.05701020567007</v>
@@ -39498,13 +39458,13 @@
         <v>34.58764733946176</v>
       </c>
       <c r="CB85" t="n">
-        <v>27.93570166328597</v>
+        <v>27.93570166806586</v>
       </c>
       <c r="CC85" t="n">
-        <v>11.13048461193323</v>
+        <v>11.13048461087125</v>
       </c>
       <c r="CD85" t="n">
-        <v>18.85057247076568</v>
+        <v>18.85057245507384</v>
       </c>
       <c r="CE85" t="n">
         <v>43.59359053230504</v>
@@ -40088,10 +40048,10 @@
         <v>52.93999862670898</v>
       </c>
       <c r="BX87" t="n">
-        <v>11.11616387744636</v>
+        <v>11.11616390667582</v>
       </c>
       <c r="BY87" t="n">
-        <v>16.1851346055619</v>
+        <v>16.18513464811999</v>
       </c>
       <c r="BZ87" t="inlineStr"/>
       <c r="CA87" t="inlineStr"/>
@@ -40102,13 +40062,13 @@
       <c r="CD87" t="inlineStr"/>
       <c r="CE87" t="inlineStr"/>
       <c r="CF87" t="n">
-        <v>17.87633282766942</v>
+        <v>17.8763328515986</v>
       </c>
       <c r="CG87" t="n">
-        <v>16.1851346055619</v>
+        <v>16.18513464811999</v>
       </c>
       <c r="CH87" t="n">
-        <v>14.56662114500571</v>
+        <v>14.566621183308</v>
       </c>
       <c r="CI87" t="n">
         <v>3</v>
@@ -40120,10 +40080,10 @@
         <v>2.4</v>
       </c>
       <c r="CL87" t="n">
-        <v>-72.48465900477632</v>
+        <v>-72.48465893242594</v>
       </c>
       <c r="CM87" t="n">
-        <v>-66.232842290535</v>
+        <v>-66.23284224533444</v>
       </c>
       <c r="CN87" t="inlineStr">
         <is>
@@ -40166,7 +40126,7 @@
         <v>-2.665932669996351</v>
       </c>
       <c r="CZ87" t="n">
-        <v>-18.20649245743299</v>
+        <v>-18.20648739516069</v>
       </c>
       <c r="DA87" t="b">
         <v>0</v>
@@ -40410,10 +40370,10 @@
         <v>22.45000076293945</v>
       </c>
       <c r="BX88" t="n">
-        <v>11.31405120651349</v>
+        <v>11.31405121866598</v>
       </c>
       <c r="BY88" t="n">
-        <v>20.98756498808252</v>
+        <v>20.9875650106254</v>
       </c>
       <c r="BZ88" t="n">
         <v>14.70402916999247</v>
@@ -40434,13 +40394,13 @@
         <v>22.45000076293945</v>
       </c>
       <c r="CF88" t="n">
-        <v>19.21790735056771</v>
+        <v>19.21790735490463</v>
       </c>
       <c r="CG88" t="n">
-        <v>17.8457970790375</v>
+        <v>17.84579709030893</v>
       </c>
       <c r="CH88" t="n">
-        <v>16.06121737113375</v>
+        <v>16.06121738127804</v>
       </c>
       <c r="CI88" t="n">
         <v>8</v>
@@ -40452,10 +40412,10 @@
         <v>2.9</v>
       </c>
       <c r="CL88" t="n">
-        <v>-28.45783151309436</v>
+        <v>-28.45783146790819</v>
       </c>
       <c r="CM88" t="n">
-        <v>-14.39685212709344</v>
+        <v>-14.3968521077753</v>
       </c>
       <c r="CN88" t="inlineStr">
         <is>
@@ -40738,25 +40698,25 @@
         <v>1.690000057220459</v>
       </c>
       <c r="BX89" t="n">
-        <v>0.1506862967442968</v>
+        <v>0.1506862969119019</v>
       </c>
       <c r="BY89" t="n">
-        <v>0.1716552920584791</v>
+        <v>0.171655292241899</v>
       </c>
       <c r="BZ89" t="n">
-        <v>0.7699467078309888</v>
+        <v>0.76994670779731</v>
       </c>
       <c r="CA89" t="n">
         <v>3.206293162785219</v>
       </c>
       <c r="CB89" t="n">
-        <v>0.2622355696790903</v>
+        <v>0.2622355697644808</v>
       </c>
       <c r="CC89" t="n">
-        <v>0.5414652897196853</v>
+        <v>0.5414652897170932</v>
       </c>
       <c r="CD89" t="n">
-        <v>0.3433710222223288</v>
+        <v>0.3433710221934202</v>
       </c>
       <c r="CE89" t="inlineStr"/>
       <c r="CF89" t="inlineStr"/>
@@ -41048,10 +41008,10 @@
         <v>13.89999961853027</v>
       </c>
       <c r="BX90" t="n">
-        <v>6.000512447493907</v>
+        <v>6.000512475325112</v>
       </c>
       <c r="BY90" t="n">
-        <v>8.73674612355113</v>
+        <v>8.736746164073365</v>
       </c>
       <c r="BZ90" t="n">
         <v>3.721936046156407</v>
@@ -41360,10 +41320,10 @@
         <v>7.420000076293945</v>
       </c>
       <c r="BX91" t="n">
-        <v>3.087627421786553</v>
+        <v>3.087627417221872</v>
       </c>
       <c r="BY91" t="n">
-        <v>5.727548867414054</v>
+        <v>5.727548858946572</v>
       </c>
       <c r="BZ91" t="n">
         <v>14.69581479983479</v>
@@ -41372,23 +41332,23 @@
         <v>15.81853464622579</v>
       </c>
       <c r="CB91" t="n">
-        <v>13.96090354666531</v>
+        <v>13.96090354419364</v>
       </c>
       <c r="CC91" t="n">
-        <v>14.9850563070803</v>
+        <v>14.98505630797638</v>
       </c>
       <c r="CD91" t="n">
-        <v>7.676901751959962</v>
+        <v>7.67690175641071</v>
       </c>
       <c r="CE91" t="inlineStr"/>
       <c r="CF91" t="n">
-        <v>12.1441266531967</v>
+        <v>12.14412665226465</v>
       </c>
       <c r="CG91" t="n">
-        <v>14.32835917325005</v>
+        <v>14.32835917201422</v>
       </c>
       <c r="CH91" t="n">
-        <v>12.89552325592505</v>
+        <v>12.89552325481279</v>
       </c>
       <c r="CI91" t="n">
         <v>6</v>
@@ -41400,10 +41360,10 @@
         <v>5.1</v>
       </c>
       <c r="CL91" t="n">
-        <v>73.79411217426765</v>
+        <v>73.79411215927776</v>
       </c>
       <c r="CM91" t="n">
-        <v>63.6674734276055</v>
+        <v>63.66747341504413</v>
       </c>
       <c r="CN91" t="inlineStr">
         <is>
@@ -41684,10 +41644,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="BX92" t="n">
-        <v>33.762522922606</v>
+        <v>33.76252288353963</v>
       </c>
       <c r="BY92" t="n">
-        <v>62.62948002143411</v>
+        <v>62.62947994896602</v>
       </c>
       <c r="BZ92" t="n">
         <v>4.845639321919829</v>
@@ -41980,35 +41940,35 @@
         <v>19.56999969482422</v>
       </c>
       <c r="BX93" t="n">
-        <v>11.66679786666319</v>
+        <v>11.66679793416182</v>
       </c>
       <c r="BY93" t="n">
-        <v>15.05415853109027</v>
+        <v>15.05415857364201</v>
       </c>
       <c r="BZ93" t="n">
-        <v>23.36416660659606</v>
+        <v>23.36416653746256</v>
       </c>
       <c r="CA93" t="n">
         <v>42.43044465422032</v>
       </c>
       <c r="CB93" t="n">
-        <v>28.36136805336224</v>
+        <v>28.36136810026511</v>
       </c>
       <c r="CC93" t="n">
-        <v>15.78799047052604</v>
+        <v>15.78799046595354</v>
       </c>
       <c r="CD93" t="n">
-        <v>11.30020717511785</v>
+        <v>11.30020712765822</v>
       </c>
       <c r="CE93" t="inlineStr"/>
       <c r="CF93" t="n">
-        <v>16.46827836871889</v>
+        <v>16.46827837780498</v>
       </c>
       <c r="CG93" t="n">
-        <v>15.42107450080815</v>
+        <v>15.42107451979777</v>
       </c>
       <c r="CH93" t="n">
-        <v>13.87896705072734</v>
+        <v>13.878967067818</v>
       </c>
       <c r="CI93" t="n">
         <v>4</v>
@@ -42020,10 +41980,10 @@
         <v>2</v>
       </c>
       <c r="CL93" t="n">
-        <v>-29.08039209424218</v>
+        <v>-29.08039200691127</v>
       </c>
       <c r="CM93" t="n">
-        <v>-15.84936829061707</v>
+        <v>-15.8493682441884</v>
       </c>
       <c r="CN93" t="inlineStr">
         <is>
@@ -42040,7 +42000,11 @@
           <t>próxima</t>
         </is>
       </c>
-      <c r="CQ93" t="inlineStr"/>
+      <c r="CQ93" t="inlineStr">
+        <is>
+          <t>O Banco do Brasil (BBAS3) apresenta um cenário de valuation intrigante, onde múltiplos de preço historicamente baixos, como o P/L de 7,72 e o P/VP de 0,62, convivem com indicadores de rentabilidade que decepcionam frente aos seus pares. O ROE de 8,0% e o ROIC de 0,0% situam-se abaixo das médias do setor de produtos financeiros, que são de 15,9% e 0,2%, respectivamente, sugerindo que o desconto no preço das ações reflete diretamente essa menor eficiência na geração de retorno sobre o capital. Essa fragilidade operacional é reforçada pela contração na receita, com um CAGR de cinco anos negativo em 13,8%, enquanto o setor expandiu 4,2% no mesmo período, evidenciando uma perda de ritmo de crescimento que justifica o fraco desempenho no checklist de critérios da empresa, que atendeu a apenas dois de seis requisitos avaliados. No âmbito dos proventos, o dividend yield de 2,82% mostra-se modesto e coerente com a atual fase de transição da companhia, sendo sustentado por uma robusta margem líquida de 21,83%, ainda que o retorno geral ao acionista seja penalizado pela ausência de forte crescimento nos lucros. Sob a ótica do valuation por preço-teto, observa-se uma dispersão acentuada entre os métodos de cálculo, variando desde os conservadores R$ 11,67 pelo método de Bazin e R$ 15,05 por Gordon, até os otimistas R$ 28,36 de Lynch e R$ 42,43 de Graham. Essa divergência resulta em uma média de preço-teto de R$ 16,47 e uma mediana de R$ 15,42, patamares que, quando ajustados pela margem de segurança para R$ 13,88, revelam um upside negativo de 29,1% em relação ao preço atual de R$ 19,57. Em um balanço final, o papel traz como pontos positivos o seu elevado valor de mercado de mais de R$ 111 bilhões, a ausência de venda de ações por insiders e uma margem líquida saudável, contrapondo-se aos pontos negativos de uma tendência gráfica em baixa, rentabilidade abaixo da média setorial e um preço atual que se posiciona acima do teto médio recomendado pelas metodologias de fluxo de caixa e dividendos descontados.</t>
+        </is>
+      </c>
       <c r="CR93" t="inlineStr"/>
       <c r="CS93" t="b">
         <v>0</v>
@@ -42308,10 +42272,10 @@
         <v>7.78000020980835</v>
       </c>
       <c r="BX94" t="n">
-        <v>5.007638606165846</v>
+        <v>5.007638650100161</v>
       </c>
       <c r="BY94" t="n">
-        <v>7.291121810577472</v>
+        <v>7.291121874545836</v>
       </c>
       <c r="BZ94" t="n">
         <v>5.901677766740105</v>
@@ -42330,13 +42294,13 @@
         <v>7.749646363977103</v>
       </c>
       <c r="CF94" t="n">
-        <v>6.635722615078976</v>
+        <v>6.635722633062755</v>
       </c>
       <c r="CG94" t="n">
-        <v>6.596399788658789</v>
+        <v>6.59639982064297</v>
       </c>
       <c r="CH94" t="n">
-        <v>5.93675980979291</v>
+        <v>5.936759838578674</v>
       </c>
       <c r="CI94" t="n">
         <v>6</v>
@@ -42348,10 +42312,10 @@
         <v>5.9</v>
       </c>
       <c r="CL94" t="n">
-        <v>-23.69203535099705</v>
+        <v>-23.69203498100011</v>
       </c>
       <c r="CM94" t="n">
-        <v>-14.70793783895749</v>
+        <v>-14.70793760780351</v>
       </c>
       <c r="CN94" t="inlineStr">
         <is>
@@ -42628,10 +42592,10 @@
         <v>78.69999694824219</v>
       </c>
       <c r="BX95" t="n">
-        <v>58.83949697462913</v>
+        <v>58.83949667492262</v>
       </c>
       <c r="BY95" t="n">
-        <v>85.67030759506001</v>
+        <v>85.67030715868735</v>
       </c>
       <c r="BZ95" t="n">
         <v>24.36677488126581</v>
@@ -42944,10 +42908,10 @@
         <v>35.65000152587891</v>
       </c>
       <c r="BX96" t="n">
-        <v>8.823433601533251</v>
+        <v>8.823433622462915</v>
       </c>
       <c r="BY96" t="n">
-        <v>16.36746933084418</v>
+        <v>16.36746936966871</v>
       </c>
       <c r="BZ96" t="n">
         <v>40.6508192958602</v>
@@ -42956,19 +42920,19 @@
         <v>40.9156147189668</v>
       </c>
       <c r="CB96" t="n">
-        <v>33.7777153506326</v>
+        <v>33.77771533884123</v>
       </c>
       <c r="CC96" t="n">
-        <v>50.02798605382524</v>
+        <v>50.02798604821392</v>
       </c>
       <c r="CD96" t="n">
-        <v>22.74549482575155</v>
+        <v>22.74549480248948</v>
       </c>
       <c r="CE96" t="n">
         <v>51.81998252253128</v>
       </c>
       <c r="CF96" t="n">
-        <v>36.61501172834455</v>
+        <v>36.61501172808165</v>
       </c>
       <c r="CG96" t="n">
         <v>40.6508192958602</v>
@@ -42989,7 +42953,7 @@
         <v>2.624784853700501</v>
       </c>
       <c r="CM96" t="n">
-        <v>2.706900872823592</v>
+        <v>2.70690087208616</v>
       </c>
       <c r="CN96" t="inlineStr">
         <is>
@@ -43272,10 +43236,10 @@
         <v>19.59000015258789</v>
       </c>
       <c r="BX97" t="n">
-        <v>2.021554715127182</v>
+        <v>2.021554707302347</v>
       </c>
       <c r="BY97" t="n">
-        <v>3.749983996560923</v>
+        <v>3.749983982045854</v>
       </c>
       <c r="BZ97" t="n">
         <v>10.29621190090399</v>
@@ -43284,19 +43248,19 @@
         <v>8.591723366671241</v>
       </c>
       <c r="CB97" t="n">
-        <v>10.2181918356177</v>
+        <v>10.21819185144002</v>
       </c>
       <c r="CC97" t="n">
-        <v>7.543992733721995</v>
+        <v>7.543992735474763</v>
       </c>
       <c r="CD97" t="n">
-        <v>7.79309765725402</v>
+        <v>7.793097669930878</v>
       </c>
       <c r="CE97" t="n">
         <v>13.94714750731148</v>
       </c>
       <c r="CF97" t="n">
-        <v>8.877192714005906</v>
+        <v>8.877192716254033</v>
       </c>
       <c r="CG97" t="n">
         <v>8.591723366671241</v>
@@ -43317,7 +43281,7 @@
         <v>-60.5280705983934</v>
       </c>
       <c r="CM97" t="n">
-        <v>-54.68508093486051</v>
+        <v>-54.68508092338462</v>
       </c>
       <c r="CN97" t="inlineStr">
         <is>
@@ -43596,10 +43560,10 @@
         <v>6.96999979019165</v>
       </c>
       <c r="BX98" t="n">
-        <v>3.120765485120736</v>
+        <v>3.120765486232352</v>
       </c>
       <c r="BY98" t="n">
-        <v>5.789019974898966</v>
+        <v>5.789019976961011</v>
       </c>
       <c r="BZ98" t="inlineStr"/>
       <c r="CA98" t="inlineStr"/>
@@ -43610,13 +43574,13 @@
         <v>9.575517828204783</v>
       </c>
       <c r="CF98" t="n">
-        <v>6.161767762741495</v>
+        <v>6.161767763799382</v>
       </c>
       <c r="CG98" t="n">
-        <v>5.789019974898966</v>
+        <v>5.789019976961011</v>
       </c>
       <c r="CH98" t="n">
-        <v>5.21011797740907</v>
+        <v>5.21011797926491</v>
       </c>
       <c r="CI98" t="n">
         <v>3</v>
@@ -43628,10 +43592,10 @@
         <v>3.1</v>
       </c>
       <c r="CL98" t="n">
-        <v>-25.2493811443026</v>
+        <v>-25.24938111767647</v>
       </c>
       <c r="CM98" t="n">
-        <v>-11.59586874862635</v>
+        <v>-11.59586873344862</v>
       </c>
       <c r="CN98" t="inlineStr">
         <is>
@@ -43910,10 +43874,10 @@
         <v>15.90999984741211</v>
       </c>
       <c r="BX99" t="n">
-        <v>8.011259035912254</v>
+        <v>8.011259041652471</v>
       </c>
       <c r="BY99" t="n">
-        <v>14.86088551161723</v>
+        <v>14.86088552226533</v>
       </c>
       <c r="BZ99" t="n">
         <v>10.0768402475244</v>
@@ -43934,7 +43898,7 @@
         <v>9.68787499591881</v>
       </c>
       <c r="CF99" t="n">
-        <v>12.14489900985865</v>
+        <v>12.14489901190719</v>
       </c>
       <c r="CG99" t="n">
         <v>9.882357621721603</v>
@@ -43955,7 +43919,7 @@
         <v>-44.09728507322303</v>
       </c>
       <c r="CM99" t="n">
-        <v>-23.66499606325192</v>
+        <v>-23.66499605037612</v>
       </c>
       <c r="CN99" t="inlineStr">
         <is>
@@ -44234,37 +44198,37 @@
         <v>23.35000038146973</v>
       </c>
       <c r="BX100" t="n">
-        <v>5.114427495612932</v>
+        <v>5.114427472168967</v>
       </c>
       <c r="BY100" t="n">
-        <v>7.241067278489564</v>
+        <v>7.241067273309402</v>
       </c>
       <c r="BZ100" t="n">
-        <v>10.68010863259599</v>
+        <v>10.68010867391201</v>
       </c>
       <c r="CA100" t="n">
         <v>14.69322801178486</v>
       </c>
       <c r="CB100" t="n">
-        <v>7.189980031785877</v>
+        <v>7.189980055079855</v>
       </c>
       <c r="CC100" t="n">
-        <v>8.433621531438551</v>
+        <v>8.43362153437436</v>
       </c>
       <c r="CD100" t="n">
-        <v>5.305073921405858</v>
+        <v>5.305073945378718</v>
       </c>
       <c r="CE100" t="n">
         <v>10.70565447273137</v>
       </c>
       <c r="CF100" t="n">
-        <v>8.670395171980623</v>
+        <v>8.670395179842442</v>
       </c>
       <c r="CG100" t="n">
-        <v>7.837344404964057</v>
+        <v>7.837344403841881</v>
       </c>
       <c r="CH100" t="n">
-        <v>7.053609964467651</v>
+        <v>7.053609963457693</v>
       </c>
       <c r="CI100" t="n">
         <v>8</v>
@@ -44276,10 +44240,10 @@
         <v>2.9</v>
       </c>
       <c r="CL100" t="n">
-        <v>-69.79182077416448</v>
+        <v>-69.79182077848979</v>
       </c>
       <c r="CM100" t="n">
-        <v>-62.86768723626513</v>
+        <v>-62.86768720259568</v>
       </c>
       <c r="CN100" t="inlineStr">
         <is>
@@ -44562,10 +44526,10 @@
         <v>46.34000015258789</v>
       </c>
       <c r="BX101" t="n">
-        <v>10.13865032225718</v>
+        <v>10.13865034093924</v>
       </c>
       <c r="BY101" t="n">
-        <v>18.80719634778707</v>
+        <v>18.8071963824423</v>
       </c>
       <c r="BZ101" t="n">
         <v>85.99509832237949</v>
@@ -44574,13 +44538,13 @@
         <v>76.05105676896386</v>
       </c>
       <c r="CB101" t="n">
-        <v>103.2434128132712</v>
+        <v>103.2434128069041</v>
       </c>
       <c r="CC101" t="n">
-        <v>16.00028353502371</v>
+        <v>16.00028353408432</v>
       </c>
       <c r="CD101" t="n">
-        <v>69.73813925458346</v>
+        <v>69.73813922755572</v>
       </c>
       <c r="CE101" t="n">
         <v>22.26855095916991</v>
@@ -44880,25 +44844,25 @@
         <v>47.2400016784668</v>
       </c>
       <c r="BX102" t="n">
-        <v>18.15640579602986</v>
+        <v>18.15640580735634</v>
       </c>
       <c r="BY102" t="n">
-        <v>20.03634734936629</v>
+        <v>20.03634735460669</v>
       </c>
       <c r="BZ102" t="n">
-        <v>23.56749659816927</v>
+        <v>23.56749658963116</v>
       </c>
       <c r="CA102" t="n">
         <v>50.82999467797423</v>
       </c>
       <c r="CB102" t="n">
-        <v>19.57321332613451</v>
+        <v>19.57321332383383</v>
       </c>
       <c r="CC102" t="n">
-        <v>23.26810817345356</v>
+        <v>23.26810817250453</v>
       </c>
       <c r="CD102" t="n">
-        <v>10.17796767436493</v>
+        <v>10.17796766661036</v>
       </c>
       <c r="CE102" t="n">
         <v>117.5954097189415</v>
@@ -45194,10 +45158,10 @@
         <v>12.18000030517578</v>
       </c>
       <c r="BX103" t="n">
-        <v>2.166666230804696</v>
+        <v>2.166666225623491</v>
       </c>
       <c r="BY103" t="n">
-        <v>4.019165858142711</v>
+        <v>4.019165848531575</v>
       </c>
       <c r="BZ103" t="n">
         <v>12.21688145674331</v>
@@ -45206,25 +45170,25 @@
         <v>13.53155185697616</v>
       </c>
       <c r="CB103" t="n">
-        <v>8.761607911475245</v>
+        <v>8.761607913564292</v>
       </c>
       <c r="CC103" t="n">
-        <v>5.735278184810479</v>
+        <v>5.735278185251087</v>
       </c>
       <c r="CD103" t="n">
-        <v>6.52707974625073</v>
+        <v>6.527079751015366</v>
       </c>
       <c r="CE103" t="n">
         <v>12.18000030517578</v>
       </c>
       <c r="CF103" t="n">
-        <v>8.995937902796346</v>
+        <v>8.995937902465368</v>
       </c>
       <c r="CG103" t="n">
-        <v>8.761607911475245</v>
+        <v>8.761607913564292</v>
       </c>
       <c r="CH103" t="n">
-        <v>7.885447120327721</v>
+        <v>7.885447122207863</v>
       </c>
       <c r="CI103" t="n">
         <v>7</v>
@@ -45236,10 +45200,10 @@
         <v>6.2</v>
       </c>
       <c r="CL103" t="n">
-        <v>-35.25905646343151</v>
+        <v>-35.25905644799521</v>
       </c>
       <c r="CM103" t="n">
-        <v>-26.14172678654529</v>
+        <v>-26.14172678926268</v>
       </c>
       <c r="CN103" t="inlineStr">
         <is>
@@ -45274,7 +45238,7 @@
         <v>-2.090026398533917</v>
       </c>
       <c r="CZ103" t="n">
-        <v>-25.25442765560502</v>
+        <v>-25.25441878355007</v>
       </c>
       <c r="DA103" t="b">
         <v>0</v>
@@ -45518,37 +45482,37 @@
         <v>53.65000152587891</v>
       </c>
       <c r="BX104" t="n">
-        <v>16.38838749789565</v>
+        <v>16.38838752682028</v>
       </c>
       <c r="BY104" t="n">
-        <v>24.84231880014987</v>
+        <v>24.84231881667243</v>
       </c>
       <c r="BZ104" t="n">
-        <v>44.54715962708104</v>
+        <v>44.54715957808587</v>
       </c>
       <c r="CA104" t="n">
         <v>62.04793706021404</v>
       </c>
       <c r="CB104" t="n">
-        <v>35.53900670892518</v>
+        <v>35.53900670005167</v>
       </c>
       <c r="CC104" t="n">
-        <v>26.75432547827134</v>
+        <v>26.75432547578343</v>
       </c>
       <c r="CD104" t="n">
-        <v>22.27011840046948</v>
+        <v>22.27011837537216</v>
       </c>
       <c r="CE104" t="n">
         <v>21.66551392102021</v>
       </c>
       <c r="CF104" t="n">
-        <v>31.75684593675335</v>
+        <v>31.75684593175251</v>
       </c>
       <c r="CG104" t="n">
-        <v>25.7983221392106</v>
+        <v>25.79832214622793</v>
       </c>
       <c r="CH104" t="n">
-        <v>23.21848992528955</v>
+        <v>23.21848993160514</v>
       </c>
       <c r="CI104" t="n">
         <v>8</v>
@@ -45560,10 +45524,10 @@
         <v>3.8</v>
       </c>
       <c r="CL104" t="n">
-        <v>-56.7222940075971</v>
+        <v>-56.72229399582525</v>
       </c>
       <c r="CM104" t="n">
-        <v>-40.80737179208663</v>
+        <v>-40.80737180140787</v>
       </c>
       <c r="CN104" t="inlineStr">
         <is>
@@ -45850,10 +45814,10 @@
         <v>3.009999990463257</v>
       </c>
       <c r="BX105" t="n">
-        <v>0.6299352413568136</v>
+        <v>0.6299352402226432</v>
       </c>
       <c r="BY105" t="n">
-        <v>1.168529872716889</v>
+        <v>1.168529870613003</v>
       </c>
       <c r="BZ105" t="n">
         <v>3.379872870647301</v>
@@ -45862,13 +45826,13 @@
         <v>3.910006936746576</v>
       </c>
       <c r="CB105" t="n">
-        <v>2.344554567674951</v>
+        <v>2.344554567848887</v>
       </c>
       <c r="CC105" t="n">
-        <v>2.634385252407706</v>
+        <v>2.634385252555391</v>
       </c>
       <c r="CD105" t="n">
-        <v>1.685378475880952</v>
+        <v>1.685378476836105</v>
       </c>
       <c r="CE105" t="n">
         <v>8.886211075297577</v>
@@ -46162,10 +46126,10 @@
         <v>58.11999893188477</v>
       </c>
       <c r="BX106" t="n">
-        <v>65.76464406875786</v>
+        <v>65.76464378384792</v>
       </c>
       <c r="BY106" t="n">
-        <v>95.75332176411146</v>
+        <v>95.75332134928257</v>
       </c>
       <c r="BZ106" t="n">
         <v>25.32249639261004</v>
@@ -46770,10 +46734,10 @@
         <v>6.420000076293945</v>
       </c>
       <c r="BX108" t="n">
-        <v>0.06151323577687621</v>
+        <v>0.06151323549210524</v>
       </c>
       <c r="BY108" t="n">
-        <v>0.1141070523661054</v>
+        <v>0.1141070518378552</v>
       </c>
       <c r="BZ108" t="inlineStr"/>
       <c r="CA108" t="inlineStr"/>
@@ -47072,10 +47036,10 @@
         <v>96.33999633789062</v>
       </c>
       <c r="BX109" t="n">
-        <v>4.919793602141335</v>
+        <v>4.919793595706008</v>
       </c>
       <c r="BY109" t="n">
-        <v>9.126217131972178</v>
+        <v>9.126217120034646</v>
       </c>
       <c r="BZ109" t="n">
         <v>41.29747497499355</v>
@@ -47084,13 +47048,13 @@
         <v>40.9954214454957</v>
       </c>
       <c r="CB109" t="n">
-        <v>33.81684473622818</v>
+        <v>33.81684474503476</v>
       </c>
       <c r="CC109" t="n">
-        <v>17.69240963072789</v>
+        <v>17.69240963133202</v>
       </c>
       <c r="CD109" t="n">
-        <v>28.18193278704362</v>
+        <v>28.18193279441129</v>
       </c>
       <c r="CE109" t="n">
         <v>42.5335436716941</v>
@@ -47696,10 +47660,10 @@
         <v>17.45000076293945</v>
       </c>
       <c r="BX111" t="n">
-        <v>3.276083596303264</v>
+        <v>3.276083603141132</v>
       </c>
       <c r="BY111" t="n">
-        <v>6.077135071142554</v>
+        <v>6.077135083826801</v>
       </c>
       <c r="BZ111" t="n">
         <v>14.88812041912091</v>
@@ -47708,23 +47672,23 @@
         <v>15.87749399405222</v>
       </c>
       <c r="CB111" t="n">
-        <v>10.46760142801215</v>
+        <v>10.46760142335885</v>
       </c>
       <c r="CC111" t="n">
-        <v>13.01572396908937</v>
+        <v>13.01572396791486</v>
       </c>
       <c r="CD111" t="n">
-        <v>7.724960036000486</v>
+        <v>7.72496002920091</v>
       </c>
       <c r="CE111" t="inlineStr"/>
       <c r="CF111" t="n">
-        <v>11.34183915290295</v>
+        <v>11.34183915291243</v>
       </c>
       <c r="CG111" t="n">
-        <v>11.74166269855076</v>
+        <v>11.74166269563685</v>
       </c>
       <c r="CH111" t="n">
-        <v>10.56749642869568</v>
+        <v>10.56749642607317</v>
       </c>
       <c r="CI111" t="n">
         <v>6</v>
@@ -47736,10 +47700,10 @@
         <v>4.8</v>
       </c>
       <c r="CL111" t="n">
-        <v>-39.4412838586284</v>
+        <v>-39.44128387365713</v>
       </c>
       <c r="CM111" t="n">
-        <v>-35.00378993111048</v>
+        <v>-35.00378993105618</v>
       </c>
       <c r="CN111" t="inlineStr">
         <is>
@@ -48018,25 +47982,25 @@
         <v>14.64000034332275</v>
       </c>
       <c r="BX112" t="n">
-        <v>3.695490812263638</v>
+        <v>3.695490816116455</v>
       </c>
       <c r="BY112" t="n">
-        <v>4.692826225211578</v>
+        <v>4.692826229456329</v>
       </c>
       <c r="BZ112" t="n">
-        <v>14.00770734345512</v>
+        <v>14.00770734152131</v>
       </c>
       <c r="CA112" t="n">
         <v>36.58780695463401</v>
       </c>
       <c r="CB112" t="n">
-        <v>9.596024416556471</v>
+        <v>9.596024420072526</v>
       </c>
       <c r="CC112" t="n">
-        <v>48.40176703844456</v>
+        <v>48.40176703778103</v>
       </c>
       <c r="CD112" t="n">
-        <v>6.726870748163035</v>
+        <v>6.726870746796671</v>
       </c>
       <c r="CE112" t="n">
         <v>25.86701731463541</v>
@@ -48332,10 +48296,10 @@
         <v>14.52999973297119</v>
       </c>
       <c r="BX113" t="n">
-        <v>1.359804409229833</v>
+        <v>1.359804409369369</v>
       </c>
       <c r="BY113" t="n">
-        <v>2.52243717912134</v>
+        <v>2.52243717938018</v>
       </c>
       <c r="BZ113" t="n">
         <v>8.711425179270055</v>
@@ -48344,13 +48308,13 @@
         <v>10.72111427832558</v>
       </c>
       <c r="CB113" t="n">
-        <v>4.822366877978332</v>
+        <v>4.822366877901067</v>
       </c>
       <c r="CC113" t="n">
-        <v>7.692408686144068</v>
+        <v>7.692408686125787</v>
       </c>
       <c r="CD113" t="n">
-        <v>4.246115052440961</v>
+        <v>4.246115052336832</v>
       </c>
       <c r="CE113" t="n">
         <v>11.54934248649259</v>
@@ -48650,10 +48614,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX114" t="n">
-        <v>11.98290321665384</v>
+        <v>11.98290321559801</v>
       </c>
       <c r="BY114" t="n">
-        <v>14.95257923121588</v>
+        <v>14.95257922989838</v>
       </c>
       <c r="BZ114" t="inlineStr"/>
       <c r="CA114" t="inlineStr"/>
@@ -48956,10 +48920,10 @@
         <v>11.18000030517578</v>
       </c>
       <c r="BX115" t="n">
-        <v>2.42961214764127</v>
+        <v>2.429612151781542</v>
       </c>
       <c r="BY115" t="n">
-        <v>4.506930533874555</v>
+        <v>4.50693054155476</v>
       </c>
       <c r="BZ115" t="n">
         <v>12.14221344619501</v>
@@ -48968,13 +48932,13 @@
         <v>12.65237085480843</v>
       </c>
       <c r="CB115" t="n">
-        <v>9.593565641573841</v>
+        <v>9.593565639479445</v>
       </c>
       <c r="CC115" t="n">
-        <v>0.7923053613552596</v>
+        <v>0.7923053613001653</v>
       </c>
       <c r="CD115" t="n">
-        <v>6.725813829646003</v>
+        <v>6.725813825343101</v>
       </c>
       <c r="CE115" t="n">
         <v>7.373367923247756</v>
@@ -49270,25 +49234,25 @@
         <v>8.739999771118164</v>
       </c>
       <c r="BX116" t="n">
-        <v>2.247634683543725</v>
+        <v>2.247634685617395</v>
       </c>
       <c r="BY116" t="n">
-        <v>2.439544378000921</v>
+        <v>2.439544379683038</v>
       </c>
       <c r="BZ116" t="n">
-        <v>3.256074274578769</v>
+        <v>3.256074273819842</v>
       </c>
       <c r="CA116" t="n">
         <v>10.09773875906247</v>
       </c>
       <c r="CB116" t="n">
-        <v>1.921804786578119</v>
+        <v>1.921804786843867</v>
       </c>
       <c r="CC116" t="n">
-        <v>5.911010295689342</v>
+        <v>5.911010295531937</v>
       </c>
       <c r="CD116" t="n">
-        <v>1.379500464693177</v>
+        <v>1.379500463983318</v>
       </c>
       <c r="CE116" t="n">
         <v>14.45896929706421</v>
@@ -49584,10 +49548,10 @@
         <v>4.809999942779541</v>
       </c>
       <c r="BX117" t="n">
-        <v>1.479509790828952</v>
+        <v>1.479509789927031</v>
       </c>
       <c r="BY117" t="n">
-        <v>1.541977981997286</v>
+        <v>1.541977981057283</v>
       </c>
       <c r="BZ117" t="inlineStr"/>
       <c r="CA117" t="inlineStr"/>
@@ -49888,10 +49852,10 @@
         <v>3.430000066757202</v>
       </c>
       <c r="BX118" t="n">
-        <v>1.689358881793472</v>
+        <v>1.689358880179818</v>
       </c>
       <c r="BY118" t="n">
-        <v>3.133760725726891</v>
+        <v>3.133760722733562</v>
       </c>
       <c r="BZ118" t="n">
         <v>1.178617761528343</v>
@@ -49900,7 +49864,7 @@
         <v>4.705827767414989</v>
       </c>
       <c r="CB118" t="n">
-        <v>1.636307705207895</v>
+        <v>1.636307704622025</v>
       </c>
       <c r="CC118" t="n">
         <v>0.7445919647652398</v>
@@ -50202,10 +50166,10 @@
         <v>6.559999942779541</v>
       </c>
       <c r="BX119" t="n">
-        <v>1.05369323979503</v>
+        <v>1.053693237305225</v>
       </c>
       <c r="BY119" t="n">
-        <v>1.954600959819782</v>
+        <v>1.954600955201193</v>
       </c>
       <c r="BZ119" t="inlineStr"/>
       <c r="CA119" t="inlineStr"/>
@@ -50506,25 +50470,25 @@
         <v>3.700000047683716</v>
       </c>
       <c r="BX120" t="n">
-        <v>1.267030928564613</v>
+        <v>1.267030927241613</v>
       </c>
       <c r="BY120" t="n">
-        <v>1.27080324334442</v>
+        <v>1.270803242501936</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.281162745951486</v>
+        <v>1.281162746439889</v>
       </c>
       <c r="CA120" t="n">
         <v>4.001025037561948</v>
       </c>
       <c r="CB120" t="n">
-        <v>0.8638648792904871</v>
+        <v>0.8638648792306141</v>
       </c>
       <c r="CC120" t="n">
-        <v>2.294198993117304</v>
+        <v>2.29419899322443</v>
       </c>
       <c r="CD120" t="n">
-        <v>0.4818317948159505</v>
+        <v>0.4818317953410225</v>
       </c>
       <c r="CE120" t="n">
         <v>5.12793832390089</v>
@@ -50824,10 +50788,10 @@
         <v>5.510000228881836</v>
       </c>
       <c r="BX121" t="n">
-        <v>5.460836727058601</v>
+        <v>5.46083672858659</v>
       </c>
       <c r="BY121" t="n">
-        <v>7.950978274597325</v>
+        <v>7.950978276822076</v>
       </c>
       <c r="BZ121" t="inlineStr"/>
       <c r="CA121" t="inlineStr"/>
@@ -50836,13 +50800,13 @@
       <c r="CD121" t="inlineStr"/>
       <c r="CE121" t="inlineStr"/>
       <c r="CF121" t="n">
-        <v>6.705907500827963</v>
+        <v>6.705907502704333</v>
       </c>
       <c r="CG121" t="n">
-        <v>6.705907500827963</v>
+        <v>6.705907502704333</v>
       </c>
       <c r="CH121" t="n">
-        <v>6.035316750745166</v>
+        <v>6.0353167524339</v>
       </c>
       <c r="CI121" t="n">
         <v>2</v>
@@ -50854,10 +50818,10 @@
         <v>1.5</v>
       </c>
       <c r="CL121" t="n">
-        <v>9.533874773902419</v>
+        <v>9.533874804550923</v>
       </c>
       <c r="CM121" t="n">
-        <v>21.70430530433602</v>
+        <v>21.70430533838992</v>
       </c>
       <c r="CN121" t="inlineStr">
         <is>
@@ -51136,10 +51100,10 @@
         <v>5.079999923706055</v>
       </c>
       <c r="BX122" t="n">
-        <v>5.591984088049994</v>
+        <v>5.591984080499895</v>
       </c>
       <c r="BY122" t="n">
-        <v>9.969901269272748</v>
+        <v>9.969901255811738</v>
       </c>
       <c r="BZ122" t="inlineStr"/>
       <c r="CA122" t="inlineStr"/>
@@ -51148,13 +51112,13 @@
       <c r="CD122" t="inlineStr"/>
       <c r="CE122" t="inlineStr"/>
       <c r="CF122" t="n">
-        <v>7.780942678661371</v>
+        <v>7.780942668155816</v>
       </c>
       <c r="CG122" t="n">
-        <v>7.780942678661371</v>
+        <v>7.780942668155816</v>
       </c>
       <c r="CH122" t="n">
-        <v>7.002848410795234</v>
+        <v>7.002848401340235</v>
       </c>
       <c r="CI122" t="n">
         <v>2</v>
@@ -51166,10 +51130,10 @@
         <v>1.8</v>
       </c>
       <c r="CL122" t="n">
-        <v>37.85134873951708</v>
+        <v>37.85134855339503</v>
       </c>
       <c r="CM122" t="n">
-        <v>53.16816526613006</v>
+        <v>53.1681650593278</v>
       </c>
       <c r="CN122" t="inlineStr">
         <is>
@@ -51434,10 +51398,10 @@
         <v>21.88999938964844</v>
       </c>
       <c r="BX123" t="n">
-        <v>37.9565835813944</v>
+        <v>37.95658332503334</v>
       </c>
       <c r="BY123" t="n">
-        <v>70.40946254348661</v>
+        <v>70.40946206793686</v>
       </c>
       <c r="BZ123" t="n">
         <v>19.65057533284836</v>
@@ -51456,7 +51420,7 @@
       </c>
       <c r="CE123" t="inlineStr"/>
       <c r="CF123" t="n">
-        <v>25.71643112657204</v>
+        <v>25.7164310838452</v>
       </c>
       <c r="CG123" t="n">
         <v>22.88916053088746</v>
@@ -51477,7 +51441,7 @@
         <v>-5.891982402062723</v>
       </c>
       <c r="CM123" t="n">
-        <v>17.48027338334732</v>
+        <v>17.48027318815844</v>
       </c>
       <c r="CN123" t="inlineStr">
         <is>
@@ -51756,25 +51720,25 @@
         <v>9.210000038146973</v>
       </c>
       <c r="BX124" t="n">
-        <v>3.561519078885751</v>
+        <v>3.561519069010727</v>
       </c>
       <c r="BY124" t="n">
-        <v>3.675673681669892</v>
+        <v>3.67567367304835</v>
       </c>
       <c r="BZ124" t="n">
-        <v>4.437535485873132</v>
+        <v>4.437535487768545</v>
       </c>
       <c r="CA124" t="n">
         <v>19.1542749461826</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.489372644844303</v>
+        <v>3.489372638891317</v>
       </c>
       <c r="CC124" t="n">
-        <v>7.742073751436652</v>
+        <v>7.742073751831656</v>
       </c>
       <c r="CD124" t="n">
-        <v>1.752959775022452</v>
+        <v>1.752959776960327</v>
       </c>
       <c r="CE124" t="n">
         <v>21.67646595176141</v>
@@ -52070,10 +52034,10 @@
         <v>11.46000003814697</v>
       </c>
       <c r="BX125" t="n">
-        <v>0.7792719064819676</v>
+        <v>0.7792719070869522</v>
       </c>
       <c r="BY125" t="n">
-        <v>1.44554938652405</v>
+        <v>1.445549387646296</v>
       </c>
       <c r="BZ125" t="n">
         <v>15.9836842637313</v>
@@ -52082,13 +52046,13 @@
         <v>16.66499025937759</v>
       </c>
       <c r="CB125" t="n">
-        <v>14.05168116888977</v>
+        <v>14.05168116878528</v>
       </c>
       <c r="CC125" t="n">
-        <v>1.723472327640941</v>
+        <v>1.723472327628086</v>
       </c>
       <c r="CD125" t="n">
-        <v>11.33321991178424</v>
+        <v>11.33321991115815</v>
       </c>
       <c r="CE125" t="inlineStr"/>
       <c r="CF125" t="inlineStr"/>
@@ -52676,25 +52640,25 @@
         <v>19</v>
       </c>
       <c r="BX127" t="n">
-        <v>0.5916775937830067</v>
+        <v>0.591677593050139</v>
       </c>
       <c r="BY127" t="n">
-        <v>0.7959309550759684</v>
+        <v>0.7959309541565487</v>
       </c>
       <c r="BZ127" t="n">
-        <v>4.744394284710489</v>
+        <v>4.744394285106534</v>
       </c>
       <c r="CA127" t="n">
         <v>11.86264950263866</v>
       </c>
       <c r="CB127" t="n">
-        <v>1.821996306601906</v>
+        <v>1.821996306736442</v>
       </c>
       <c r="CC127" t="n">
-        <v>0.6742710780983842</v>
+        <v>0.6742710781036898</v>
       </c>
       <c r="CD127" t="n">
-        <v>2.328996506112076</v>
+        <v>2.328996506364242</v>
       </c>
       <c r="CE127" t="n">
         <v>19</v>
@@ -52994,10 +52958,10 @@
         <v>5.150000095367432</v>
       </c>
       <c r="BX128" t="n">
-        <v>1.26975705318016</v>
+        <v>1.269757046134565</v>
       </c>
       <c r="BY128" t="n">
-        <v>2.125111577186067</v>
+        <v>2.125111565394304</v>
       </c>
       <c r="BZ128" t="inlineStr"/>
       <c r="CA128" t="inlineStr"/>
@@ -53008,13 +52972,13 @@
         <v>5.966766218226677</v>
       </c>
       <c r="CF128" t="n">
-        <v>1.697434315183113</v>
+        <v>1.697434305764435</v>
       </c>
       <c r="CG128" t="n">
-        <v>1.697434315183113</v>
+        <v>1.697434305764435</v>
       </c>
       <c r="CH128" t="n">
-        <v>1.527690883664802</v>
+        <v>1.527690875187991</v>
       </c>
       <c r="CI128" t="n">
         <v>2</v>
@@ -53026,10 +52990,10 @@
         <v>4.7</v>
       </c>
       <c r="CL128" t="n">
-        <v>-70.33609989562908</v>
+        <v>-70.33610006022735</v>
       </c>
       <c r="CM128" t="n">
-        <v>-67.04011099514342</v>
+        <v>-67.04011117803039</v>
       </c>
       <c r="CN128" t="inlineStr">
         <is>
@@ -53610,37 +53574,37 @@
         <v>17.20999908447266</v>
       </c>
       <c r="BX130" t="n">
-        <v>2.072771884170888</v>
+        <v>2.072771887219414</v>
       </c>
       <c r="BY130" t="n">
-        <v>3.668389127329242</v>
+        <v>3.668389130267402</v>
       </c>
       <c r="BZ130" t="n">
-        <v>9.537870351388493</v>
+        <v>9.537870344999954</v>
       </c>
       <c r="CA130" t="n">
         <v>11.82323496807012</v>
       </c>
       <c r="CB130" t="n">
-        <v>5.52987847934546</v>
+        <v>5.529878477302843</v>
       </c>
       <c r="CC130" t="n">
-        <v>5.536636594518317</v>
+        <v>5.536636594246461</v>
       </c>
       <c r="CD130" t="n">
-        <v>4.691832896071522</v>
+        <v>4.691832893611482</v>
       </c>
       <c r="CE130" t="n">
         <v>15.57105866321647</v>
       </c>
       <c r="CF130" t="n">
-        <v>6.797973736120526</v>
+        <v>6.797973734749711</v>
       </c>
       <c r="CG130" t="n">
-        <v>5.533257536931888</v>
+        <v>5.533257535774652</v>
       </c>
       <c r="CH130" t="n">
-        <v>4.979931783238699</v>
+        <v>4.979931782197187</v>
       </c>
       <c r="CI130" t="n">
         <v>6</v>
@@ -53652,10 +53616,10 @@
         <v>7.5</v>
       </c>
       <c r="CL130" t="n">
-        <v>-71.06373010948191</v>
+        <v>-71.0637301155337</v>
       </c>
       <c r="CM130" t="n">
-        <v>-60.49985997818066</v>
+        <v>-60.49985998614589</v>
       </c>
       <c r="CN130" t="inlineStr">
         <is>
@@ -53926,10 +53890,10 @@
         <v>4.21999979019165</v>
       </c>
       <c r="BX131" t="n">
-        <v>0.888197918491655</v>
+        <v>0.8881979185522042</v>
       </c>
       <c r="BY131" t="n">
-        <v>0.9831240710304507</v>
+        <v>0.9831240710974711</v>
       </c>
       <c r="BZ131" t="inlineStr"/>
       <c r="CA131" t="inlineStr"/>
@@ -53938,13 +53902,13 @@
       <c r="CD131" t="inlineStr"/>
       <c r="CE131" t="inlineStr"/>
       <c r="CF131" t="n">
-        <v>0.9356609947610528</v>
+        <v>0.9356609948248377</v>
       </c>
       <c r="CG131" t="n">
-        <v>0.9356609947610528</v>
+        <v>0.9356609948248377</v>
       </c>
       <c r="CH131" t="n">
-        <v>0.8420948952849475</v>
+        <v>0.8420948953423539</v>
       </c>
       <c r="CI131" t="n">
         <v>2</v>
@@ -53956,10 +53920,10 @@
         <v>1.1</v>
       </c>
       <c r="CL131" t="n">
-        <v>-80.04514366938619</v>
+        <v>-80.04514366802586</v>
       </c>
       <c r="CM131" t="n">
-        <v>-77.82793741042912</v>
+        <v>-77.82793740891762</v>
       </c>
       <c r="CN131" t="inlineStr">
         <is>
@@ -54240,10 +54204,10 @@
         <v>1.220000028610229</v>
       </c>
       <c r="BX132" t="n">
-        <v>0.3581979140298155</v>
+        <v>0.358197914138901</v>
       </c>
       <c r="BY132" t="n">
-        <v>0.6644571305253077</v>
+        <v>0.6644571307276613</v>
       </c>
       <c r="BZ132" t="inlineStr"/>
       <c r="CA132" t="inlineStr"/>
@@ -54252,13 +54216,13 @@
       <c r="CD132" t="inlineStr"/>
       <c r="CE132" t="inlineStr"/>
       <c r="CF132" t="n">
-        <v>0.5113275222775616</v>
+        <v>0.5113275224332812</v>
       </c>
       <c r="CG132" t="n">
-        <v>0.5113275222775616</v>
+        <v>0.5113275224332812</v>
       </c>
       <c r="CH132" t="n">
-        <v>0.4601947700498055</v>
+        <v>0.4601947701899531</v>
       </c>
       <c r="CI132" t="n">
         <v>2</v>
@@ -54270,10 +54234,10 @@
         <v>1.9</v>
       </c>
       <c r="CL132" t="n">
-        <v>-62.27911809362503</v>
+        <v>-62.27911808213753</v>
       </c>
       <c r="CM132" t="n">
-        <v>-58.0879089929167</v>
+        <v>-58.08790898015281</v>
       </c>
       <c r="CN132" t="inlineStr">
         <is>
@@ -54860,10 +54824,10 @@
         <v>37.15000152587891</v>
       </c>
       <c r="BX134" t="n">
-        <v>8.367448517366313</v>
+        <v>8.367448540844919</v>
       </c>
       <c r="BY134" t="n">
-        <v>12.18300504128536</v>
+        <v>12.1830050754702</v>
       </c>
       <c r="BZ134" t="n">
         <v>7.98264495597398</v>
@@ -55170,10 +55134,10 @@
         <v>5.460000038146973</v>
       </c>
       <c r="BX135" t="n">
-        <v>1.040921914694933</v>
+        <v>1.040921915472592</v>
       </c>
       <c r="BY135" t="n">
-        <v>1.9309101517591</v>
+        <v>1.930910153201658</v>
       </c>
       <c r="BZ135" t="inlineStr"/>
       <c r="CA135" t="inlineStr"/>
@@ -55184,13 +55148,13 @@
         <v>2.921035340023647</v>
       </c>
       <c r="CF135" t="n">
-        <v>1.96428913549256</v>
+        <v>1.964289136232632</v>
       </c>
       <c r="CG135" t="n">
-        <v>1.9309101517591</v>
+        <v>1.930910153201658</v>
       </c>
       <c r="CH135" t="n">
-        <v>1.73781913658319</v>
+        <v>1.737819137881492</v>
       </c>
       <c r="CI135" t="n">
         <v>3</v>
@@ -55202,10 +55166,10 @@
         <v>2.8</v>
       </c>
       <c r="CL135" t="n">
-        <v>-68.17181090766118</v>
+        <v>-68.17181088388276</v>
       </c>
       <c r="CM135" t="n">
-        <v>-64.02400875881303</v>
+        <v>-64.0240087452586</v>
       </c>
       <c r="CN135" t="inlineStr">
         <is>
@@ -55484,25 +55448,25 @@
         <v>4.840000152587891</v>
       </c>
       <c r="BX136" t="n">
-        <v>1.502502734477237</v>
+        <v>1.502502739038417</v>
       </c>
       <c r="BY136" t="n">
-        <v>1.661829038263891</v>
+        <v>1.661829042200076</v>
       </c>
       <c r="BZ136" t="n">
-        <v>2.454262200833528</v>
+        <v>2.454262199196203</v>
       </c>
       <c r="CA136" t="n">
         <v>7.637283478890028</v>
       </c>
       <c r="CB136" t="n">
-        <v>1.72025373985498</v>
+        <v>1.720253741597295</v>
       </c>
       <c r="CC136" t="n">
-        <v>1.782246221436985</v>
+        <v>1.782246221303394</v>
       </c>
       <c r="CD136" t="n">
-        <v>1.062540517001048</v>
+        <v>1.062540515519942</v>
       </c>
       <c r="CE136" t="n">
         <v>0.3893443649538701</v>
@@ -55796,10 +55760,10 @@
         <v>1.990000009536743</v>
       </c>
       <c r="BX137" t="n">
-        <v>0.5586583799970081</v>
+        <v>0.5586583797530597</v>
       </c>
       <c r="BY137" t="n">
-        <v>0.8134066012756438</v>
+        <v>0.813406600920455</v>
       </c>
       <c r="BZ137" t="n">
         <v>0.3437302790098343</v>
@@ -56104,10 +56068,10 @@
         <v>6.889999866485596</v>
       </c>
       <c r="BX138" t="n">
-        <v>1.890787840104773</v>
+        <v>1.890787837853785</v>
       </c>
       <c r="BY138" t="n">
-        <v>2.752987095192549</v>
+        <v>2.752987091915112</v>
       </c>
       <c r="BZ138" t="n">
         <v>1.748560239420454</v>
@@ -57282,25 +57246,25 @@
         <v>4.539999961853027</v>
       </c>
       <c r="BX142" t="n">
-        <v>0.7601321081395994</v>
+        <v>0.7601321063839337</v>
       </c>
       <c r="BY142" t="n">
-        <v>0.7617072515022747</v>
+        <v>0.7617072498526766</v>
       </c>
       <c r="BZ142" t="n">
-        <v>0.787013067067179</v>
+        <v>0.7870130671805293</v>
       </c>
       <c r="CA142" t="n">
         <v>5.834017088524545</v>
       </c>
       <c r="CB142" t="n">
-        <v>0.2605273419474931</v>
+        <v>0.2605273415463846</v>
       </c>
       <c r="CC142" t="n">
-        <v>0.4173726784914545</v>
+        <v>0.4173726784988233</v>
       </c>
       <c r="CD142" t="n">
-        <v>0.2954898342763901</v>
+        <v>0.295489834398444</v>
       </c>
       <c r="CE142" t="inlineStr"/>
       <c r="CF142" t="inlineStr"/>
@@ -57596,10 +57560,10 @@
         <v>18.30999946594238</v>
       </c>
       <c r="BX143" t="n">
-        <v>27.83633521535095</v>
+        <v>27.83633524180653</v>
       </c>
       <c r="BY143" t="n">
-        <v>37.2388306658695</v>
+        <v>37.23883070126119</v>
       </c>
       <c r="BZ143" t="n">
         <v>2.491274627922611</v>
@@ -57608,7 +57572,7 @@
         <v>6.909187799009217</v>
       </c>
       <c r="CB143" t="n">
-        <v>6.383321818395685</v>
+        <v>6.383321823669474</v>
       </c>
       <c r="CC143" t="n">
         <v>3.046690502845772</v>
@@ -57910,10 +57874,10 @@
         <v>3.75</v>
       </c>
       <c r="BX144" t="n">
-        <v>0.6783189622362282</v>
+        <v>0.6783189640326317</v>
       </c>
       <c r="BY144" t="n">
-        <v>1.258281674948203</v>
+        <v>1.258281678280532</v>
       </c>
       <c r="BZ144" t="inlineStr"/>
       <c r="CA144" t="inlineStr"/>
@@ -57924,13 +57888,13 @@
         <v>3.41418274193782</v>
       </c>
       <c r="CF144" t="n">
-        <v>0.9683003185922158</v>
+        <v>0.9683003211565817</v>
       </c>
       <c r="CG144" t="n">
-        <v>0.9683003185922158</v>
+        <v>0.9683003211565817</v>
       </c>
       <c r="CH144" t="n">
-        <v>0.8714702867329942</v>
+        <v>0.8714702890409236</v>
       </c>
       <c r="CI144" t="n">
         <v>2</v>
@@ -57942,10 +57906,10 @@
         <v>5</v>
       </c>
       <c r="CL144" t="n">
-        <v>-76.76079235378683</v>
+        <v>-76.76079229224204</v>
       </c>
       <c r="CM144" t="n">
-        <v>-74.17865817087424</v>
+        <v>-74.17865810249116</v>
       </c>
       <c r="CN144" t="inlineStr">
         <is>
@@ -58222,10 +58186,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX145" t="n">
-        <v>9.498631705856553</v>
+        <v>9.498631626663959</v>
       </c>
       <c r="BY145" t="n">
-        <v>13.83000776372714</v>
+        <v>13.83000764842273</v>
       </c>
       <c r="BZ145" t="n">
         <v>4.684999942779541</v>
@@ -59154,10 +59118,10 @@
         <v>10.71000003814697</v>
       </c>
       <c r="BX148" t="n">
-        <v>5.722370902474492</v>
+        <v>5.722370889358022</v>
       </c>
       <c r="BY148" t="n">
-        <v>10.47405814815887</v>
+        <v>10.47405812415087</v>
       </c>
       <c r="BZ148" t="inlineStr"/>
       <c r="CA148" t="inlineStr"/>
@@ -59168,13 +59132,13 @@
         <v>3.193949960809536</v>
       </c>
       <c r="CF148" t="n">
-        <v>6.463459670480965</v>
+        <v>6.463459658106141</v>
       </c>
       <c r="CG148" t="n">
-        <v>5.722370902474492</v>
+        <v>5.722370889358022</v>
       </c>
       <c r="CH148" t="n">
-        <v>5.150133812227043</v>
+        <v>5.150133800422219</v>
       </c>
       <c r="CI148" t="n">
         <v>3</v>
@@ -59186,10 +59150,10 @@
         <v>3.3</v>
       </c>
       <c r="CL148" t="n">
-        <v>-51.91284973031512</v>
+        <v>-51.91284984053757</v>
       </c>
       <c r="CM148" t="n">
-        <v>-39.65023671840002</v>
+        <v>-39.6502368339446</v>
       </c>
       <c r="CN148" t="inlineStr">
         <is>
@@ -59297,7 +59261,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
       <c r="S149" t="n">
@@ -59517,7 +59481,11 @@
       </c>
       <c r="CP149" t="inlineStr"/>
       <c r="CQ149" t="inlineStr"/>
-      <c r="CR149" t="inlineStr"/>
+      <c r="CR149" t="inlineStr">
+        <is>
+          <t>Pivô de alta</t>
+        </is>
+      </c>
       <c r="CS149" t="b">
         <v>0</v>
       </c>
@@ -59544,14 +59512,14 @@
         <v>0</v>
       </c>
       <c r="DB149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC149" t="b">
         <v>0</v>
       </c>
       <c r="DD149" t="inlineStr">
         <is>
-          <t>sem sinal (Lateral)</t>
+          <t>Pivô de alta</t>
         </is>
       </c>
     </row>
@@ -59782,10 +59750,10 @@
         <v>15.35000038146973</v>
       </c>
       <c r="BX150" t="n">
-        <v>3.926986143114278</v>
+        <v>3.926986148296946</v>
       </c>
       <c r="BY150" t="n">
-        <v>5.717691824374389</v>
+        <v>5.717691831920352</v>
       </c>
       <c r="BZ150" t="inlineStr"/>
       <c r="CA150" t="inlineStr"/>
@@ -59796,7 +59764,7 @@
         <v>5.502528941537498</v>
       </c>
       <c r="CF150" t="n">
-        <v>5.049068969675388</v>
+        <v>5.049068973918266</v>
       </c>
       <c r="CG150" t="n">
         <v>5.502528941537498</v>
@@ -59817,7 +59785,7 @@
         <v>-67.7376161282572</v>
       </c>
       <c r="CM150" t="n">
-        <v>-67.10704336026895</v>
+        <v>-67.10704333262805</v>
       </c>
       <c r="CN150" t="inlineStr">
         <is>

--- a/reports/screener_2026-08-27.xlsx
+++ b/reports/screener_2026-08-27.xlsx
@@ -1186,10 +1186,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.87427218800108</v>
+        <v>5.874272108025008</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.896774908742</v>
+        <v>10.89677476038639</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.25748351662458</v>
@@ -1198,7 +1198,7 @@
         <v>27.69424604953494</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.32928290717642</v>
+        <v>71.32928257194737</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -1260,7 +1260,7 @@
         <v>-4.147472323669144</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-26.52097580569606</v>
+        <v>-26.52096568735769</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
@@ -1504,10 +1504,10 @@
         <v>13.36999988555908</v>
       </c>
       <c r="BX3" t="n">
-        <v>14.75007820110445</v>
+        <v>14.75007813219094</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.36139506304876</v>
+        <v>27.3613949352142</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.76422286294482</v>
@@ -1516,13 +1516,13 @@
         <v>23.45333307258707</v>
       </c>
       <c r="CB3" t="n">
-        <v>75.35854784329271</v>
+        <v>75.35854797043419</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.54748521036084</v>
+        <v>48.54748526124334</v>
       </c>
       <c r="CD3" t="n">
-        <v>26.78098970630979</v>
+        <v>26.78098991892728</v>
       </c>
       <c r="CE3" t="n">
         <v>8.814883789850169</v>
@@ -1822,10 +1822,10 @@
         <v>24.60000038146973</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.30060358702401</v>
+        <v>16.30060358833519</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.23761965392954</v>
+        <v>30.23761965636179</v>
       </c>
       <c r="BZ4" t="n">
         <v>71.16812337433926</v>
@@ -1834,19 +1834,19 @@
         <v>51.52104017548554</v>
       </c>
       <c r="CB4" t="n">
-        <v>125.1392993823085</v>
+        <v>125.1392993818412</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.69671526310594</v>
+        <v>25.69671526291816</v>
       </c>
       <c r="CD4" t="n">
-        <v>61.68777253041441</v>
+        <v>61.68777252760135</v>
       </c>
       <c r="CE4" t="n">
         <v>43.13507176990557</v>
       </c>
       <c r="CF4" t="n">
-        <v>47.24105712786337</v>
+        <v>47.24105712776861</v>
       </c>
       <c r="CG4" t="n">
         <v>47.32805597269555</v>
@@ -1867,7 +1867,7 @@
         <v>73.1514216053079</v>
       </c>
       <c r="CM4" t="n">
-        <v>92.03681461504496</v>
+        <v>92.03681461465976</v>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         <v>4.110000133514404</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.73321908983248</v>
+        <v>3.733219077861432</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.925121411639251</v>
+        <v>6.925121389432955</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.72371536660417</v>
@@ -2160,25 +2160,25 @@
         <v>8.566797975520885</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.60513833552532</v>
+        <v>24.6051383438305</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.20720451984052</v>
+        <v>11.2072045247466</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.35562989645032</v>
+        <v>10.35562992628408</v>
       </c>
       <c r="CE5" t="n">
         <v>5.28099461109321</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.176577296858058</v>
+        <v>9.176577298946984</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.461213935985601</v>
+        <v>9.461213950902485</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.515092542387041</v>
+        <v>8.515092555812236</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -2190,10 +2190,10 @@
         <v>6.6</v>
       </c>
       <c r="CL5" t="n">
-        <v>107.1798604810726</v>
+        <v>107.1798608077197</v>
       </c>
       <c r="CM5" t="n">
-        <v>123.2743795317421</v>
+        <v>123.2743795825676</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
         <v>48.54000091552734</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.49767256282114</v>
+        <v>18.49767258046552</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.31318260403322</v>
+        <v>34.31318263676354</v>
       </c>
       <c r="BZ6" t="n">
         <v>75.48767748013348</v>
@@ -2470,23 +2470,23 @@
         <v>56.48770574587493</v>
       </c>
       <c r="CB6" t="n">
-        <v>101.3707432448298</v>
+        <v>101.3707432174032</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.40360291175992</v>
+        <v>48.40360290749748</v>
       </c>
       <c r="CD6" t="n">
-        <v>59.83279359511664</v>
+        <v>59.83279355965287</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>44.17553388968694</v>
+        <v>44.175533901215</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.35839275789657</v>
+        <v>41.35839277213051</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.22255348210691</v>
+        <v>37.22255349491746</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -2498,10 +2498,10 @@
         <v>4.1</v>
       </c>
       <c r="CL6" t="n">
-        <v>-23.31571326732325</v>
+        <v>-23.31571324093151</v>
       </c>
       <c r="CM6" t="n">
-        <v>-8.991485256532549</v>
+        <v>-8.991485232782924</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         <v>4.409999847412109</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.217002919301321</v>
+        <v>3.217002916849567</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.967540415303951</v>
+        <v>5.967540410755946</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.73039171638572</v>
@@ -2796,7 +2796,7 @@
         <v>8.563510105820175</v>
       </c>
       <c r="CB7" t="n">
-        <v>24.223973547146</v>
+        <v>24.22397353966788</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -2808,7 +2808,7 @@
         <v>5.278370495623927</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.42348769089854</v>
+        <v>11.42348768918052</v>
       </c>
       <c r="CG7" t="n">
         <v>11.57513776217851</v>
@@ -2829,7 +2829,7 @@
         <v>136.2273094425153</v>
       </c>
       <c r="CM7" t="n">
-        <v>159.0360110239484</v>
+        <v>159.036010984991</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>-2.556002609200203</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-42.88871827907796</v>
+        <v>-42.88872193099961</v>
       </c>
       <c r="DA7" t="b">
         <v>1</v>
@@ -3114,10 +3114,10 @@
         <v>41.45000076293945</v>
       </c>
       <c r="BX8" t="n">
-        <v>121.4412679716231</v>
+        <v>121.4412680126986</v>
       </c>
       <c r="BY8" t="n">
-        <v>225.2735520873608</v>
+        <v>225.273552163556</v>
       </c>
       <c r="BZ8" t="n">
         <v>136.9607257129545</v>
@@ -3138,13 +3138,13 @@
         <v>57.8068628710751</v>
       </c>
       <c r="CF8" t="n">
-        <v>116.5644819207811</v>
+        <v>116.5644819375341</v>
       </c>
       <c r="CG8" t="n">
-        <v>121.4412679716231</v>
+        <v>121.4412680126986</v>
       </c>
       <c r="CH8" t="n">
-        <v>109.2971411744608</v>
+        <v>109.2971412114288</v>
       </c>
       <c r="CI8" t="n">
         <v>7</v>
@@ -3156,10 +3156,10 @@
         <v>5.5</v>
       </c>
       <c r="CL8" t="n">
-        <v>163.684292310517</v>
+        <v>163.6842923997039</v>
       </c>
       <c r="CM8" t="n">
-        <v>181.2170802780822</v>
+        <v>181.2170803184995</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
         <v>15.67000007629395</v>
       </c>
       <c r="BX9" t="n">
-        <v>6.392639624814289</v>
+        <v>6.392639630005946</v>
       </c>
       <c r="BY9" t="n">
-        <v>11.85834650403051</v>
+        <v>11.85834651366103</v>
       </c>
       <c r="BZ9" t="n">
         <v>25.41340281651098</v>
@@ -3454,19 +3454,19 @@
         <v>18.62224018162043</v>
       </c>
       <c r="CB9" t="n">
-        <v>35.3125200641127</v>
+        <v>35.31252005570318</v>
       </c>
       <c r="CC9" t="n">
-        <v>12.3015336058021</v>
+        <v>12.30153360481723</v>
       </c>
       <c r="CD9" t="n">
-        <v>20.43463668128798</v>
+        <v>20.43463667041001</v>
       </c>
       <c r="CE9" t="n">
         <v>18.38139646228262</v>
       </c>
       <c r="CF9" t="n">
-        <v>20.33201090223534</v>
+        <v>20.33201090071507</v>
       </c>
       <c r="CG9" t="n">
         <v>18.62224018162043</v>
@@ -3487,7 +3487,7 @@
         <v>6.956069443888868</v>
       </c>
       <c r="CM9" t="n">
-        <v>29.75118572586495</v>
+        <v>29.75118571616317</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -3770,37 +3770,37 @@
         <v>31.98999977111816</v>
       </c>
       <c r="BX10" t="n">
-        <v>23.76330226953226</v>
+        <v>23.76330220777687</v>
       </c>
       <c r="BY10" t="n">
-        <v>36.41661188629458</v>
+        <v>36.41661246186523</v>
       </c>
       <c r="BZ10" t="n">
-        <v>39.03790506670131</v>
+        <v>39.03790578515253</v>
       </c>
       <c r="CA10" t="n">
         <v>20.7706836705417</v>
       </c>
       <c r="CB10" t="n">
-        <v>52.98477640344</v>
+        <v>52.98477688095995</v>
       </c>
       <c r="CC10" t="n">
-        <v>51.52687081186153</v>
+        <v>51.52687089124198</v>
       </c>
       <c r="CD10" t="n">
-        <v>19.51897963063692</v>
+        <v>19.51897999137731</v>
       </c>
       <c r="CE10" t="n">
         <v>24.08135454201217</v>
       </c>
       <c r="CF10" t="n">
-        <v>33.51256053512756</v>
+        <v>33.51256080386597</v>
       </c>
       <c r="CG10" t="n">
-        <v>30.24898321415338</v>
+        <v>30.2489835019387</v>
       </c>
       <c r="CH10" t="n">
-        <v>27.22408489273804</v>
+        <v>27.22408515174483</v>
       </c>
       <c r="CI10" t="n">
         <v>8</v>
@@ -3812,10 +3812,10 @@
         <v>2.7</v>
       </c>
       <c r="CL10" t="n">
-        <v>-14.89813977017587</v>
+        <v>-14.89813896052664</v>
       </c>
       <c r="CM10" t="n">
-        <v>4.759489762122548</v>
+        <v>4.759490602192606</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         <v>32.34999847412109</v>
       </c>
       <c r="BX11" t="n">
-        <v>45.1758884852444</v>
+        <v>45.17588854290364</v>
       </c>
       <c r="BY11" t="n">
-        <v>83.80127314012836</v>
+        <v>83.80127324708624</v>
       </c>
       <c r="BZ11" t="n">
         <v>68.14586324039816</v>
@@ -4122,7 +4122,7 @@
         <v>25.45102053342143</v>
       </c>
       <c r="CF11" t="n">
-        <v>77.26388350077593</v>
+        <v>77.26388352429265</v>
       </c>
       <c r="CG11" t="n">
         <v>68.14586324039816</v>
@@ -4143,7 +4143,7 @@
         <v>89.58664546899837</v>
       </c>
       <c r="CM11" t="n">
-        <v>138.8373636635082</v>
+        <v>138.8373637362028</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -4428,10 +4428,10 @@
         <v>45.93000030517578</v>
       </c>
       <c r="BX12" t="n">
-        <v>127.4901592234444</v>
+        <v>127.490158728825</v>
       </c>
       <c r="BY12" t="n">
-        <v>236.4942453594893</v>
+        <v>236.4942444419704</v>
       </c>
       <c r="BZ12" t="n">
         <v>137.0658792890943</v>
@@ -4452,13 +4452,13 @@
         <v>56.48463159734047</v>
       </c>
       <c r="CF12" t="n">
-        <v>142.809052208906</v>
+        <v>142.8090520323887</v>
       </c>
       <c r="CG12" t="n">
-        <v>126.3298773248559</v>
+        <v>126.3298770775462</v>
       </c>
       <c r="CH12" t="n">
-        <v>113.6968895923703</v>
+        <v>113.6968893697916</v>
       </c>
       <c r="CI12" t="n">
         <v>8</v>
@@ -4470,10 +4470,10 @@
         <v>5.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>147.5438468036717</v>
+        <v>147.5438463190675</v>
       </c>
       <c r="CM12" t="n">
-        <v>210.9276099717618</v>
+        <v>210.9276095874438</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>-4.431848361876922</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-13.53632911913226</v>
+        <v>-13.53634187597278</v>
       </c>
       <c r="DA12" t="b">
         <v>1</v>
@@ -4738,10 +4738,10 @@
         <v>19.20999908447266</v>
       </c>
       <c r="BX13" t="n">
-        <v>13.20480146414876</v>
+        <v>13.20480144991564</v>
       </c>
       <c r="BY13" t="n">
-        <v>24.49490671599595</v>
+        <v>24.49490668959352</v>
       </c>
       <c r="BZ13" t="n">
         <v>19.97900218754024</v>
@@ -4750,7 +4750,7 @@
         <v>12.48664452830808</v>
       </c>
       <c r="CB13" t="n">
-        <v>33.81124087749864</v>
+        <v>33.81124086185785</v>
       </c>
       <c r="CC13" t="n">
         <v>22.8984489302328</v>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="CE13" t="inlineStr"/>
       <c r="CF13" t="n">
-        <v>20.14428982447944</v>
+        <v>20.14428981432055</v>
       </c>
       <c r="CG13" t="n">
         <v>21.43872555888652</v>
@@ -4781,7 +4781,7 @@
         <v>0.4417174522084899</v>
       </c>
       <c r="CM13" t="n">
-        <v>4.863564729484882</v>
+        <v>4.863564676601562</v>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
@@ -5072,10 +5072,10 @@
         <v>7.119999885559082</v>
       </c>
       <c r="BX14" t="n">
-        <v>3.21473233594391</v>
+        <v>3.214732338826915</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.963328483175953</v>
+        <v>5.963328488523926</v>
       </c>
       <c r="BZ14" t="n">
         <v>19.81932741253316</v>
@@ -5084,7 +5084,7 @@
         <v>13.57675850780915</v>
       </c>
       <c r="CB14" t="n">
-        <v>31.89206953500021</v>
+        <v>31.89206954347963</v>
       </c>
       <c r="CC14" t="n">
         <v>10.95072400487419</v>
@@ -5390,10 +5390,10 @@
         <v>17.47999954223633</v>
       </c>
       <c r="BX15" t="n">
-        <v>10.71384735269345</v>
+        <v>10.71384731370265</v>
       </c>
       <c r="BY15" t="n">
-        <v>19.87418683924636</v>
+        <v>19.87418676691842</v>
       </c>
       <c r="BZ15" t="n">
         <v>37.47734529686591</v>
@@ -5402,25 +5402,25 @@
         <v>37.0591905335928</v>
       </c>
       <c r="CB15" t="n">
-        <v>41.78101224739631</v>
+        <v>41.78101223101346</v>
       </c>
       <c r="CC15" t="n">
-        <v>34.50404065992525</v>
+        <v>34.50404066819012</v>
       </c>
       <c r="CD15" t="n">
-        <v>18.56246600890206</v>
+        <v>18.56246605412515</v>
       </c>
       <c r="CE15" t="n">
         <v>31.88800278970118</v>
       </c>
       <c r="CF15" t="n">
-        <v>31.59232062508998</v>
+        <v>31.59232062005814</v>
       </c>
       <c r="CG15" t="n">
-        <v>34.50404065992525</v>
+        <v>34.50404066819012</v>
       </c>
       <c r="CH15" t="n">
-        <v>31.05363659393273</v>
+        <v>31.05363660137111</v>
       </c>
       <c r="CI15" t="n">
         <v>7</v>
@@ -5432,10 +5432,10 @@
         <v>3.9</v>
       </c>
       <c r="CL15" t="n">
-        <v>77.65238791281934</v>
+        <v>77.65238795537302</v>
       </c>
       <c r="CM15" t="n">
-        <v>80.73410441890761</v>
+        <v>80.73410439012136</v>
       </c>
       <c r="CN15" t="inlineStr">
         <is>
@@ -5720,10 +5720,10 @@
         <v>3.480000019073486</v>
       </c>
       <c r="BX16" t="n">
-        <v>5.030148809289601</v>
+        <v>5.03014876148871</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.330926041232209</v>
+        <v>9.330925952561557</v>
       </c>
       <c r="BZ16" t="n">
         <v>8.507380120428724</v>
@@ -5794,7 +5794,7 @@
         <v>-2.096134038389974</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-28.72157845771649</v>
+        <v>-28.72158548753347</v>
       </c>
       <c r="DA16" t="b">
         <v>1</v>
@@ -6038,37 +6038,37 @@
         <v>10.25</v>
       </c>
       <c r="BX17" t="n">
-        <v>10.27005386738239</v>
+        <v>10.27005390284119</v>
       </c>
       <c r="BY17" t="n">
-        <v>17.87947162401748</v>
+        <v>17.87947153337628</v>
       </c>
       <c r="BZ17" t="n">
-        <v>22.96597064665681</v>
+        <v>22.96597045093602</v>
       </c>
       <c r="CA17" t="n">
         <v>17.56827373614594</v>
       </c>
       <c r="CB17" t="n">
-        <v>36.09152089278309</v>
+        <v>36.09152085861933</v>
       </c>
       <c r="CC17" t="n">
-        <v>24.12174237813253</v>
+        <v>24.12174236283168</v>
       </c>
       <c r="CD17" t="n">
-        <v>11.33576890530264</v>
+        <v>11.33576882760532</v>
       </c>
       <c r="CE17" t="n">
         <v>10.25</v>
       </c>
       <c r="CF17" t="n">
-        <v>18.81035025630261</v>
+        <v>18.81035020904447</v>
       </c>
       <c r="CG17" t="n">
-        <v>17.72387268008171</v>
+        <v>17.72387263476111</v>
       </c>
       <c r="CH17" t="n">
-        <v>15.95148541207354</v>
+        <v>15.951485371285</v>
       </c>
       <c r="CI17" t="n">
         <v>8</v>
@@ -6080,10 +6080,10 @@
         <v>3.5</v>
       </c>
       <c r="CL17" t="n">
-        <v>55.62424792266869</v>
+        <v>55.62424752473167</v>
       </c>
       <c r="CM17" t="n">
-        <v>83.51561225661086</v>
+        <v>83.5156117955558</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -6366,10 +6366,10 @@
         <v>10.80000019073486</v>
       </c>
       <c r="BX18" t="n">
-        <v>3.367718440283852</v>
+        <v>3.367718439463935</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.247117706726545</v>
+        <v>6.2471177052056</v>
       </c>
       <c r="BZ18" t="n">
         <v>19.65659375374133</v>
@@ -6378,13 +6378,13 @@
         <v>18.52911526753888</v>
       </c>
       <c r="CB18" t="n">
-        <v>21.05981933951412</v>
+        <v>21.05981933959146</v>
       </c>
       <c r="CC18" t="n">
-        <v>15.92813033546488</v>
+        <v>15.92813033562657</v>
       </c>
       <c r="CD18" t="n">
-        <v>13.12984067363762</v>
+        <v>13.12984067467734</v>
       </c>
       <c r="CE18" t="n">
         <v>29.56959057813611</v>
@@ -6440,7 +6440,7 @@
         <v>-20.99487834338889</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-34.59225116497123</v>
+        <v>-34.59224337860515</v>
       </c>
       <c r="DA18" t="b">
         <v>1</v>
@@ -6588,13 +6588,13 @@
         <v>1</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AS19" t="b">
         <v>1</v>
       </c>
       <c r="AT19" t="n">
-        <v>5725241856</v>
+        <v>3602869248</v>
       </c>
       <c r="AU19" t="n">
         <v>6.7</v>
@@ -6684,10 +6684,10 @@
         <v>11.01000022888184</v>
       </c>
       <c r="BX19" t="n">
-        <v>9.531702557211867</v>
+        <v>9.531702563879664</v>
       </c>
       <c r="BY19" t="n">
-        <v>17.68130824362801</v>
+        <v>17.68130825599678</v>
       </c>
       <c r="BZ19" t="n">
         <v>21.77350791532602</v>
@@ -6696,25 +6696,25 @@
         <v>12.86392893329986</v>
       </c>
       <c r="CB19" t="n">
-        <v>31.27631901617183</v>
+        <v>31.27631899577072</v>
       </c>
       <c r="CC19" t="n">
-        <v>25.272397052258</v>
+        <v>25.27239704731914</v>
       </c>
       <c r="CD19" t="n">
-        <v>11.53006420794424</v>
+        <v>11.53006418636298</v>
       </c>
       <c r="CE19" t="n">
         <v>9.491669059101429</v>
       </c>
       <c r="CF19" t="n">
-        <v>17.42761212311766</v>
+        <v>17.42761211963207</v>
       </c>
       <c r="CG19" t="n">
-        <v>15.27261858846394</v>
+        <v>15.27261859464832</v>
       </c>
       <c r="CH19" t="n">
-        <v>13.74535672961754</v>
+        <v>13.74535673518349</v>
       </c>
       <c r="CI19" t="n">
         <v>8</v>
@@ -6726,10 +6726,10 @@
         <v>3.3</v>
       </c>
       <c r="CL19" t="n">
-        <v>24.84429104333914</v>
+        <v>24.84429109389268</v>
       </c>
       <c r="CM19" t="n">
-        <v>58.28893515733913</v>
+        <v>58.28893512568077</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -7012,10 +7012,10 @@
         <v>27.42000007629395</v>
       </c>
       <c r="BX20" t="n">
-        <v>7.26488727784715</v>
+        <v>7.26488728278337</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.47636590040646</v>
+        <v>13.47636590956315</v>
       </c>
       <c r="BZ20" t="n">
         <v>35.79458138038372</v>
@@ -7024,19 +7024,19 @@
         <v>28.30701155023988</v>
       </c>
       <c r="CB20" t="n">
-        <v>44.58429128193586</v>
+        <v>44.58429127456367</v>
       </c>
       <c r="CC20" t="n">
-        <v>26.46258109875249</v>
+        <v>26.46258109752097</v>
       </c>
       <c r="CD20" t="n">
-        <v>28.94259526759421</v>
+        <v>28.94259525868057</v>
       </c>
       <c r="CE20" t="n">
         <v>24.89125670295465</v>
       </c>
       <c r="CF20" t="n">
-        <v>28.92266902603818</v>
+        <v>28.9226690248438</v>
       </c>
       <c r="CG20" t="n">
         <v>28.30701155023988</v>
@@ -7057,7 +7057,7 @@
         <v>-7.088583791648051</v>
       </c>
       <c r="CM20" t="n">
-        <v>5.480193091040042</v>
+        <v>5.480193086684171</v>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
@@ -7320,10 +7320,10 @@
         <v>39.40999984741211</v>
       </c>
       <c r="BX21" t="n">
-        <v>36.08952119338425</v>
+        <v>36.0895211397676</v>
       </c>
       <c r="BY21" t="n">
-        <v>52.54634285756747</v>
+        <v>52.54634277950162</v>
       </c>
       <c r="BZ21" t="n">
         <v>49.20336115403192</v>
@@ -7340,13 +7340,13 @@
       </c>
       <c r="CE21" t="inlineStr"/>
       <c r="CF21" t="n">
-        <v>49.33584754720034</v>
+        <v>49.33584751427971</v>
       </c>
       <c r="CG21" t="n">
-        <v>50.8748520057997</v>
+        <v>50.87485196676677</v>
       </c>
       <c r="CH21" t="n">
-        <v>45.78736680521973</v>
+        <v>45.7873667700901</v>
       </c>
       <c r="CI21" t="n">
         <v>4</v>
@@ -7358,10 +7358,10 @@
         <v>1.6</v>
       </c>
       <c r="CL21" t="n">
-        <v>16.18210348261748</v>
+        <v>16.18210339347861</v>
       </c>
       <c r="CM21" t="n">
-        <v>25.18611453493831</v>
+        <v>25.18611445140462</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -7652,10 +7652,10 @@
         <v>22.70000076293945</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.19748135082587</v>
+        <v>3.197481352371524</v>
       </c>
       <c r="BY22" t="n">
-        <v>5.931327905781989</v>
+        <v>5.931327908649177</v>
       </c>
       <c r="BZ22" t="n">
         <v>32.87158580425658</v>
@@ -7664,7 +7664,7 @@
         <v>27.4632507976689</v>
       </c>
       <c r="CB22" t="n">
-        <v>42.10543719733923</v>
+        <v>42.10543719970417</v>
       </c>
       <c r="CC22" t="n">
         <v>10.85340539909456</v>
@@ -7704,16 +7704,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ22" t="inlineStr">
-        <is>
-          <t>A Vivara (VIVA3) apresenta-se como uma opção robusta no setor de consumo discricionário, destacando-se por uma eficiência operacional superior à de seus pares, evidenciada por um ROE de 18,4% e um ROIC de 17,3% que se posicionam confortavelmente acima das médias setoriais de 12,5% e 13,1%, respectivamente. Essa alta rentabilidade convive com múltiplos de valuation bastante atrativos, uma vez que o P/L de 9,15 e o P/VP de 1,68 sugerem que a qualidade da empresa não está precificada com ágio excessivo, configurando uma relação favorável entre qualidade e preço. No âmbito financeiro, a excelente rentabilidade é acompanhada por um endividamento muito saudável, com a relação dívida líquida por EBITDA em 1,1, patamar significativamente abaixo da média do setor de 2,67, o que, somado a uma liquidez corrente de 4,19, confere extrema segurança ao balanço. Por outro lado, o dividend yield de 3,07% mostra-se modesto, o que é coerente com a estratégia de retenção de lucros para expansão, embora a sustentabilidade desses proventos seja garantida pela baixa alavancagem e forte geração de caixa. O grande ponto de atenção reside no crescimento histórico, visto que o CAGR de receita de cinco anos de apenas 0,4% ficou muito abaixo da média setorial de 31,0%, indicando uma expansão recente mais lenta que a de seus concorrentes. No checklist de critérios fundamentalistas, a companhia demonstra solidez ao atender a 6 dos 8 requisitos avaliados, falhando apenas no crescimento frente ao setor e na ocorrência de venda de ações por insiders. Sob a ótica de valuation, as estimativas de preço-teto revelam uma enorme dispersão entre os métodos de fluxo de caixa descontado (R$ 32,87), Graham (R$ 27,46) e Lynch (R$ 42,11), que apontam para um potencial de valorização perante o preço atual de R$ 22,7, em contraste com os modelos focados em dividendos como Bazin (R$ 3,2) e Gordon (R$ 5,93), que penalizam o papel pelo seu baixo yield. Em balanço, os prós da VIVA3 concentram-se em sua alta rentabilidade, sólida estrutura de capital e múltiplos de preço convidativos, enquanto os contras ficam por conta do fraco crescimento histórico de receita comparado ao setor e do baixo retorno em dividendos no curto prazo.</t>
-        </is>
-      </c>
-      <c r="CR22" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CQ22" t="inlineStr"/>
+      <c r="CR22" t="inlineStr"/>
       <c r="CS22" t="b">
         <v>0</v>
       </c>
@@ -7740,14 +7732,14 @@
         <v>1</v>
       </c>
       <c r="DB22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD22" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.7, +1.8% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -7978,10 +7970,10 @@
         <v>32.59999847412109</v>
       </c>
       <c r="BX23" t="n">
-        <v>3.234610403649413</v>
+        <v>3.234610402485425</v>
       </c>
       <c r="BY23" t="n">
-        <v>6.000202298769662</v>
+        <v>6.000202296610462</v>
       </c>
       <c r="BZ23" t="n">
         <v>32.59999847412109</v>
@@ -7990,7 +7982,7 @@
         <v>22.83825145099259</v>
       </c>
       <c r="CB23" t="n">
-        <v>40.32336020852137</v>
+        <v>40.32336020729149</v>
       </c>
       <c r="CC23" t="n">
         <v>10.59424454785779</v>
@@ -8060,7 +8052,7 @@
         <v>-0.458019926347808</v>
       </c>
       <c r="CZ23" t="n">
-        <v>-31.63291935983593</v>
+        <v>-31.63292499811159</v>
       </c>
       <c r="DA23" t="b">
         <v>1</v>
@@ -8284,35 +8276,35 @@
         <v>12.89999961853027</v>
       </c>
       <c r="BX24" t="n">
-        <v>8.660681316715355</v>
+        <v>8.66068132458957</v>
       </c>
       <c r="BY24" t="n">
-        <v>13.90577872637139</v>
+        <v>13.90577871721078</v>
       </c>
       <c r="BZ24" t="n">
-        <v>18.56293297149125</v>
+        <v>18.56293294238543</v>
       </c>
       <c r="CA24" t="n">
         <v>17.46591874479647</v>
       </c>
       <c r="CB24" t="n">
-        <v>23.07483854973443</v>
+        <v>23.07483854222391</v>
       </c>
       <c r="CC24" t="n">
-        <v>17.33679306371927</v>
+        <v>17.33679306153915</v>
       </c>
       <c r="CD24" t="n">
-        <v>9.265468041206981</v>
+        <v>9.26546802779184</v>
       </c>
       <c r="CE24" t="inlineStr"/>
       <c r="CF24" t="n">
-        <v>14.61654651957432</v>
+        <v>14.61654651143123</v>
       </c>
       <c r="CG24" t="n">
-        <v>15.62128589504533</v>
+        <v>15.62128588937497</v>
       </c>
       <c r="CH24" t="n">
-        <v>14.0591573055408</v>
+        <v>14.05915730043747</v>
       </c>
       <c r="CI24" t="n">
         <v>4</v>
@@ -8324,10 +8316,10 @@
         <v>2.1</v>
       </c>
       <c r="CL24" t="n">
-        <v>8.985718769676909</v>
+        <v>8.985718730116222</v>
       </c>
       <c r="CM24" t="n">
-        <v>13.30656551786482</v>
+        <v>13.30656545474014</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -8598,10 +8590,10 @@
         <v>14.92000007629395</v>
       </c>
       <c r="BX25" t="n">
-        <v>9.273887965142224</v>
+        <v>9.273888006358739</v>
       </c>
       <c r="BY25" t="n">
-        <v>17.20306217533882</v>
+        <v>17.20306225179546</v>
       </c>
       <c r="BZ25" t="n">
         <v>30.98589357537536</v>
@@ -8610,23 +8602,23 @@
         <v>29.53442297696593</v>
       </c>
       <c r="CB25" t="n">
-        <v>35.04844382265731</v>
+        <v>35.04844383156657</v>
       </c>
       <c r="CC25" t="n">
-        <v>25.51038176775274</v>
+        <v>25.51038175938443</v>
       </c>
       <c r="CD25" t="n">
-        <v>15.48617146806028</v>
+        <v>15.48617141681001</v>
       </c>
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="n">
-        <v>20.74330637090229</v>
+        <v>20.74330639822849</v>
       </c>
       <c r="CG25" t="n">
-        <v>21.35672197154578</v>
+        <v>21.35672200558994</v>
       </c>
       <c r="CH25" t="n">
-        <v>19.2210497743912</v>
+        <v>19.22104980503095</v>
       </c>
       <c r="CI25" t="n">
         <v>4</v>
@@ -8638,10 +8630,10 @@
         <v>3.3</v>
       </c>
       <c r="CL25" t="n">
-        <v>28.8274106977459</v>
+        <v>28.82741090310614</v>
       </c>
       <c r="CM25" t="n">
-        <v>39.03020284739047</v>
+        <v>39.03020303054201</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -8650,12 +8642,12 @@
       </c>
       <c r="CO25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>última</t>
+          <t>próxima</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr"/>
@@ -8680,7 +8672,7 @@
         <v>-5.269840785435265</v>
       </c>
       <c r="CZ25" t="n">
-        <v>-17.97784039185961</v>
+        <v>-17.97783150576924</v>
       </c>
       <c r="DA25" t="b">
         <v>1</v>
@@ -8906,10 +8898,10 @@
         <v>39.45000076293945</v>
       </c>
       <c r="BX26" t="n">
-        <v>20.16682100364162</v>
+        <v>20.16682114779781</v>
       </c>
       <c r="BY26" t="n">
-        <v>37.40945296175521</v>
+        <v>37.40945322916494</v>
       </c>
       <c r="BZ26" t="n">
         <v>56.0249206976364</v>
@@ -8918,23 +8910,23 @@
         <v>42.37642446456151</v>
       </c>
       <c r="CB26" t="n">
-        <v>61.80196359830609</v>
+        <v>61.80196336153472</v>
       </c>
       <c r="CC26" t="n">
-        <v>45.16906420399834</v>
+        <v>45.16906415895728</v>
       </c>
       <c r="CD26" t="n">
-        <v>31.12131450130616</v>
+        <v>31.12131421651119</v>
       </c>
       <c r="CE26" t="inlineStr"/>
       <c r="CF26" t="n">
-        <v>39.69256471675789</v>
+        <v>39.69256480838911</v>
       </c>
       <c r="CG26" t="n">
-        <v>41.28925858287677</v>
+        <v>41.28925869406111</v>
       </c>
       <c r="CH26" t="n">
-        <v>37.1603327245891</v>
+        <v>37.160332824655</v>
       </c>
       <c r="CI26" t="n">
         <v>4</v>
@@ -8946,10 +8938,10 @@
         <v>2.8</v>
       </c>
       <c r="CL26" t="n">
-        <v>-5.803974636424702</v>
+        <v>-5.803974382772226</v>
       </c>
       <c r="CM26" t="n">
-        <v>0.6148642563432061</v>
+        <v>0.6148644886149857</v>
       </c>
       <c r="CN26" t="inlineStr">
         <is>
@@ -9061,7 +9053,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -9232,10 +9224,10 @@
         <v>5.989999771118164</v>
       </c>
       <c r="BX27" t="n">
-        <v>7.105835133233375</v>
+        <v>7.105835100490797</v>
       </c>
       <c r="BY27" t="n">
-        <v>13.18132417214791</v>
+        <v>13.18132411141043</v>
       </c>
       <c r="BZ27" t="n">
         <v>5.689426305900764</v>
@@ -9256,7 +9248,7 @@
         <v>5.473701748879975</v>
       </c>
       <c r="CF27" t="n">
-        <v>7.409413556726272</v>
+        <v>7.409413545041264</v>
       </c>
       <c r="CG27" t="n">
         <v>5.911379819617049</v>
@@ -9277,7 +9269,7 @@
         <v>-11.18126809774143</v>
       </c>
       <c r="CM27" t="n">
-        <v>23.69639131627452</v>
+        <v>23.69639112119926</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -9294,16 +9286,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ27" t="inlineStr">
-        <is>
-          <t>A CSN Mineração (CMIN3) apresenta uma notável eficiência operacional, com seu ROE de 31,8% e ROIC de 20,3% situando-se muito acima dos pares do setor de materiais (5,6% e 9,2%, respectivamente), o que evidencia uma alta qualidade no emprego do capital. Essa forte rentabilidade, contudo, convive com múltiplos de preço que dividem opiniões: enquanto o P/L de 13,95 e o P/VP de 4,43 sugerem um prêmio em relação ao valor patrimonial, o indicador PEG de 0,15 sinaliza que o preço atual está bastante atrativo quando confrontado com o robusto crescimento da empresa. O espetacular avanço histórico é confirmado pelo CAGR de receita de 5 anos de 90,7%, que supera com folga a média setorial de 17,4%, validando o excelente desempenho operacional refletido no checklist de critérios, no qual a companhia atendeu a 7 de 8 requisitos possíveis. No âmbito financeiro, a excelente rentabilidade convive com um endividamento sob controle, visto que a relação Dívida Líquida/EBITDA de 0,2 está bem abaixo da média do setor de 1,76, embora a relação Dívida/Patrimônio de 1,24 e a liquidez corrente de 1,17 exijam monitoramento. Esse balanço saudável confere sustentabilidade ao expressivo dividend yield de 18,19%, uma vez que a geração de caixa e o baixo endividamento relativo dão suporte à distribuição de proventos sem comprometer a estrutura de capital. Sob a ótica do valuation, a análise dos preços-teto revela uma dispersão acentuada entre as metodologias, variando desde os conservadores R$ 3,61 pelo modelo de Graham até os otimistas R$ 13,18 pelo modelo de Gordon, resultando em uma média de R$ 7,41 e mediana de R$ 5,91. Frente ao preço atual de R$ 5,99, o preço-teto ajustado com margem de segurança fica em R$ 5,32, o que aponta para um upside negativo de 11,2% em relação a essa métrica mais rigorosa, apesar de o papel demonstrar tendência gráfica de alta e sinal de rompimento. Em suma, os principais pontos positivos da companhia residem em seu crescimento acelerado, rentabilidade muito acima dos pares e proventos altamente generosos, ao passo que os pontos negativos concentram-se na margem líquida de 13,41% (abaixo do patamar de 15% do checklist), na liquidez corrente apertada e na ausência de margem de segurança no preço atual perante o valuation ajustado.</t>
-        </is>
-      </c>
-      <c r="CR27" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="inlineStr"/>
       <c r="CS27" t="b">
         <v>0</v>
       </c>
@@ -9330,14 +9314,14 @@
         <v>1</v>
       </c>
       <c r="DB27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD27" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.7, +0.3% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9381,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -9568,37 +9552,37 @@
         <v>26.75</v>
       </c>
       <c r="BX28" t="n">
-        <v>17.10458218354911</v>
+        <v>17.10458209521638</v>
       </c>
       <c r="BY28" t="n">
-        <v>28.31127777305716</v>
+        <v>28.31127776241475</v>
       </c>
       <c r="BZ28" t="n">
-        <v>47.34414620291996</v>
+        <v>47.34414642962103</v>
       </c>
       <c r="CA28" t="n">
         <v>53.24972279891534</v>
       </c>
       <c r="CB28" t="n">
-        <v>56.30911403290522</v>
+        <v>56.30911400495602</v>
       </c>
       <c r="CC28" t="n">
-        <v>43.03538679041579</v>
+        <v>43.03538680648636</v>
       </c>
       <c r="CD28" t="n">
-        <v>23.55902945142269</v>
+        <v>23.55902955022109</v>
       </c>
       <c r="CE28" t="n">
         <v>30.7680447869919</v>
       </c>
       <c r="CF28" t="n">
-        <v>37.46016300252215</v>
+        <v>37.46016302935286</v>
       </c>
       <c r="CG28" t="n">
-        <v>36.90171578870385</v>
+        <v>36.90171579673913</v>
       </c>
       <c r="CH28" t="n">
-        <v>33.21154420983346</v>
+        <v>33.21154421706522</v>
       </c>
       <c r="CI28" t="n">
         <v>8</v>
@@ -9610,10 +9594,10 @@
         <v>3.3</v>
       </c>
       <c r="CL28" t="n">
-        <v>24.15530545732136</v>
+        <v>24.15530548435596</v>
       </c>
       <c r="CM28" t="n">
-        <v>40.0379925327931</v>
+        <v>40.0379926330948</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -9630,16 +9614,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ28" t="inlineStr">
-        <is>
-          <t>A ISA CTEEP (ISAE4) apresenta-se como uma alternativa robusta no setor de serviços públicos, combinando uma rentabilidade sólida com múltiplos de valuation que sugerem um ponto de entrada descontado. O retorno sobre o patrimônio líquido (ROE) de 12,7% situa-se acima da média setorial de 12,1%, enquanto o retorno sobre o capital investido (ROIC) de 9,6% fica ligeiramente abaixo dos pares, configurando uma operação eficiente que convive com um preço atraente, evidenciado pelo P/L de 6,68 e pelo P/VP de 0,85. Essa rentabilidade saudável é acompanhada por um endividamento sob controle, onde a relação Dívida Líquida/EBITDA de 3,41 vezes está ligeiramente acima da média do setor de 3,4 vezes, mas é amplamente mitigada por uma robusta liquidez corrente de 5,28, garantindo folga financeira no curto prazo. O dividend yield de 6,48% mostra-se coerente com a geração de caixa e a estrutura de capital da companhia, oferecendo um retorno atrativo e sustentável frente ao perfil de endividamento moderado. No quesito expansão, a empresa destaca-se com um impressionante crescimento composto anual (CAGR) de receita nos últimos cinco anos de 220,0%, patamar vastamente superior à média setorial de 37,6%, o que corrobora o cumprimento de 5 dos 8 critérios do checklist fundamentalista, penalizado apenas pelas métricas de alavancagem e pelo ROE/ROIC abaixo da taxa Selic. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 17,10 pelo modelo de Bazin até os otimistas R$ 56,31 pelo critério de Lynch, estabelecendo uma média de R$ 37,46 e uma mediana de R$ 36,90. Tomando como referência o preço-teto ajustado com margem de segurança de R$ 33,21, o papel, cotado atualmente a R$ 26,75, oferece um upside potencial de 24,2%, mesmo diante de uma tendência gráfica lateralizada com sinal de rompimento. Em suma, os principais prós do ativo residem no seu crescimento exponencial de receita, margem líquida elevada de 26,39% e valuation descontado, enquanto os contras concentram-se em uma alavancagem ligeiramente superior à do setor e em retornos sobre o capital que ainda não superam o custo de oportunidade da taxa básica de juros.</t>
-        </is>
-      </c>
-      <c r="CR28" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CQ28" t="inlineStr"/>
+      <c r="CR28" t="inlineStr"/>
       <c r="CS28" t="b">
         <v>0</v>
       </c>
@@ -9666,14 +9642,14 @@
         <v>1</v>
       </c>
       <c r="DB28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD28" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.8, +0.1% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -9904,37 +9880,37 @@
         <v>15.23999977111816</v>
       </c>
       <c r="BX29" t="n">
-        <v>5.91237611142607</v>
+        <v>5.912376111442303</v>
       </c>
       <c r="BY29" t="n">
-        <v>8.495852362904266</v>
+        <v>8.495852362890863</v>
       </c>
       <c r="BZ29" t="n">
-        <v>10.76554978675262</v>
+        <v>10.76554978670608</v>
       </c>
       <c r="CA29" t="n">
         <v>11.60613937821477</v>
       </c>
       <c r="CB29" t="n">
-        <v>9.765538913190749</v>
+        <v>9.765538913164574</v>
       </c>
       <c r="CC29" t="n">
-        <v>14.90925468167973</v>
+        <v>14.90925468167401</v>
       </c>
       <c r="CD29" t="n">
-        <v>5.35951293928006</v>
+        <v>5.359512939253776</v>
       </c>
       <c r="CE29" t="n">
         <v>10.95502673090989</v>
       </c>
       <c r="CF29" t="n">
-        <v>9.721156363044768</v>
+        <v>9.721156363032032</v>
       </c>
       <c r="CG29" t="n">
-        <v>10.26554434997168</v>
+        <v>10.26554434993533</v>
       </c>
       <c r="CH29" t="n">
-        <v>9.238989914974516</v>
+        <v>9.238989914941794</v>
       </c>
       <c r="CI29" t="n">
         <v>8</v>
@@ -9946,10 +9922,10 @@
         <v>2.8</v>
       </c>
       <c r="CL29" t="n">
-        <v>-39.37670568418488</v>
+        <v>-39.3767056843996</v>
       </c>
       <c r="CM29" t="n">
-        <v>-36.21288379893772</v>
+        <v>-36.2128837990213</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -10232,37 +10208,37 @@
         <v>38.93999862670898</v>
       </c>
       <c r="BX30" t="n">
-        <v>31.03837521548671</v>
+        <v>31.03837540531581</v>
       </c>
       <c r="BY30" t="n">
-        <v>35.59923868699851</v>
+        <v>35.59923853946942</v>
       </c>
       <c r="BZ30" t="n">
-        <v>38.66835340589296</v>
+        <v>38.66835300915131</v>
       </c>
       <c r="CA30" t="n">
         <v>49.91213791285566</v>
       </c>
       <c r="CB30" t="n">
-        <v>60.21617607377523</v>
+        <v>60.21617586066733</v>
       </c>
       <c r="CC30" t="n">
-        <v>16.76375509231805</v>
+        <v>16.76375507360725</v>
       </c>
       <c r="CD30" t="n">
-        <v>17.35171000040723</v>
+        <v>17.35170966396933</v>
       </c>
       <c r="CE30" t="n">
         <v>28.46736944905749</v>
       </c>
       <c r="CF30" t="n">
-        <v>34.75213947959898</v>
+        <v>34.7521393642617</v>
       </c>
       <c r="CG30" t="n">
-        <v>33.31880695124261</v>
+        <v>33.31880697239261</v>
       </c>
       <c r="CH30" t="n">
-        <v>29.98692625611835</v>
+        <v>29.98692627515335</v>
       </c>
       <c r="CI30" t="n">
         <v>8</v>
@@ -10274,10 +10250,10 @@
         <v>3.6</v>
       </c>
       <c r="CL30" t="n">
-        <v>-22.99196889146707</v>
+        <v>-22.99196884258416</v>
       </c>
       <c r="CM30" t="n">
-        <v>-10.75464636569747</v>
+        <v>-10.75464666188978</v>
       </c>
       <c r="CN30" t="inlineStr">
         <is>
@@ -10464,7 +10440,7 @@
         <v>1</v>
       </c>
       <c r="AT31" t="n">
-        <v>185049546752</v>
+        <v>184726978560</v>
       </c>
       <c r="AU31" t="n">
         <v>7.27</v>
@@ -10542,35 +10518,35 @@
         <v>16.98999977111816</v>
       </c>
       <c r="BX31" t="n">
-        <v>10.11113308174126</v>
+        <v>10.11113315030665</v>
       </c>
       <c r="BY31" t="n">
-        <v>17.73003376642088</v>
+        <v>17.73003375481931</v>
       </c>
       <c r="BZ31" t="n">
-        <v>29.27120913360595</v>
+        <v>29.27120891595919</v>
       </c>
       <c r="CA31" t="n">
         <v>29.45091649314749</v>
       </c>
       <c r="CB31" t="n">
-        <v>32.49121842356977</v>
+        <v>32.4912184199716</v>
       </c>
       <c r="CC31" t="n">
-        <v>27.89684498813715</v>
+        <v>27.89684497280067</v>
       </c>
       <c r="CD31" t="n">
-        <v>14.42712306578498</v>
+        <v>14.42712298052803</v>
       </c>
       <c r="CE31" t="inlineStr"/>
       <c r="CF31" t="n">
-        <v>21.25230524247631</v>
+        <v>21.25230519847145</v>
       </c>
       <c r="CG31" t="n">
-        <v>22.81343937727902</v>
+        <v>22.81343936380999</v>
       </c>
       <c r="CH31" t="n">
-        <v>20.53209543955112</v>
+        <v>20.53209542742899</v>
       </c>
       <c r="CI31" t="n">
         <v>4</v>
@@ -10582,10 +10558,10 @@
         <v>2.9</v>
       </c>
       <c r="CL31" t="n">
-        <v>20.84812075427025</v>
+        <v>20.84812068292166</v>
       </c>
       <c r="CM31" t="n">
-        <v>25.08714260610983</v>
+        <v>25.08714234710536</v>
       </c>
       <c r="CN31" t="inlineStr">
         <is>
@@ -10594,12 +10570,12 @@
       </c>
       <c r="CO31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="CP31" t="inlineStr">
         <is>
-          <t>última</t>
+          <t>próxima</t>
         </is>
       </c>
       <c r="CQ31" t="inlineStr"/>
@@ -10624,7 +10600,7 @@
         <v>-5.872573466739961</v>
       </c>
       <c r="CZ31" t="n">
-        <v>-20.0055653732595</v>
+        <v>-20.00555804362784</v>
       </c>
       <c r="DA31" t="b">
         <v>1</v>
@@ -10868,37 +10844,37 @@
         <v>44.54999923706055</v>
       </c>
       <c r="BX32" t="n">
-        <v>32.31239190591139</v>
+        <v>32.31239167628136</v>
       </c>
       <c r="BY32" t="n">
-        <v>44.51496102618957</v>
+        <v>44.51496147025176</v>
       </c>
       <c r="BZ32" t="n">
-        <v>51.2732020618559</v>
+        <v>51.27320293771162</v>
       </c>
       <c r="CA32" t="n">
         <v>48.07305068505902</v>
       </c>
       <c r="CB32" t="n">
-        <v>71.06107536662033</v>
+        <v>71.06107584029496</v>
       </c>
       <c r="CC32" t="n">
-        <v>59.89309458293646</v>
+        <v>59.89309467731584</v>
       </c>
       <c r="CD32" t="n">
-        <v>25.32931160603421</v>
+        <v>25.32931214011691</v>
       </c>
       <c r="CE32" t="n">
         <v>77.11023262183943</v>
       </c>
       <c r="CF32" t="n">
-        <v>51.19591498205578</v>
+        <v>51.19591525610886</v>
       </c>
       <c r="CG32" t="n">
-        <v>49.67312637345746</v>
+        <v>49.67312681138532</v>
       </c>
       <c r="CH32" t="n">
-        <v>44.70581373611172</v>
+        <v>44.70581413024679</v>
       </c>
       <c r="CI32" t="n">
         <v>8</v>
@@ -10910,10 +10886,10 @@
         <v>3</v>
       </c>
       <c r="CL32" t="n">
-        <v>0.3497519679451555</v>
+        <v>0.349752852647911</v>
       </c>
       <c r="CM32" t="n">
-        <v>14.91788071562208</v>
+        <v>14.91788133078051</v>
       </c>
       <c r="CN32" t="inlineStr">
         <is>
@@ -11178,10 +11154,10 @@
         <v>54.06999969482422</v>
       </c>
       <c r="BX33" t="n">
-        <v>10.57163146182461</v>
+        <v>10.57163144128664</v>
       </c>
       <c r="BY33" t="n">
-        <v>19.61037636168465</v>
+        <v>19.61037632358672</v>
       </c>
       <c r="BZ33" t="n">
         <v>61.97469688204333</v>
@@ -11190,7 +11166,7 @@
         <v>46.42658566900867</v>
       </c>
       <c r="CB33" t="n">
-        <v>82.96304808718925</v>
+        <v>82.9630480623163</v>
       </c>
       <c r="CC33" t="n">
         <v>11.76833333333333</v>
@@ -11200,7 +11176,7 @@
       </c>
       <c r="CE33" t="inlineStr"/>
       <c r="CF33" t="n">
-        <v>13.98344705228086</v>
+        <v>13.98344703273557</v>
       </c>
       <c r="CG33" t="n">
         <v>11.76833333333333</v>
@@ -11221,7 +11197,7 @@
         <v>-80.41150349587693</v>
       </c>
       <c r="CM33" t="n">
-        <v>-74.13825202292462</v>
+        <v>-74.13825205907276</v>
       </c>
       <c r="CN33" t="inlineStr">
         <is>
@@ -11486,10 +11462,10 @@
         <v>29.72999954223633</v>
       </c>
       <c r="BX34" t="n">
-        <v>15.54095035446847</v>
+        <v>15.54095033515084</v>
       </c>
       <c r="BY34" t="n">
-        <v>28.82846290753902</v>
+        <v>28.82846287170481</v>
       </c>
       <c r="BZ34" t="n">
         <v>54.78755131218794</v>
@@ -11498,23 +11474,23 @@
         <v>49.47462312565243</v>
       </c>
       <c r="CB34" t="n">
-        <v>61.00002213430175</v>
+        <v>61.00002213912055</v>
       </c>
       <c r="CC34" t="n">
-        <v>36.6350403106921</v>
+        <v>36.63504031419151</v>
       </c>
       <c r="CD34" t="n">
-        <v>30.36807371041787</v>
+        <v>30.36807373709011</v>
       </c>
       <c r="CE34" t="inlineStr"/>
       <c r="CF34" t="n">
-        <v>33.94800122122189</v>
+        <v>33.94800120830877</v>
       </c>
       <c r="CG34" t="n">
-        <v>32.73175160911556</v>
+        <v>32.73175159294816</v>
       </c>
       <c r="CH34" t="n">
-        <v>29.45857644820401</v>
+        <v>29.45857643365334</v>
       </c>
       <c r="CI34" t="n">
         <v>4</v>
@@ -11526,10 +11502,10 @@
         <v>3.5</v>
       </c>
       <c r="CL34" t="n">
-        <v>-0.9129603034359945</v>
+        <v>-0.9129603523787</v>
       </c>
       <c r="CM34" t="n">
-        <v>14.18769506872408</v>
+        <v>14.18769502528947</v>
       </c>
       <c r="CN34" t="inlineStr">
         <is>
@@ -11818,10 +11794,10 @@
         <v>10.5</v>
       </c>
       <c r="BX35" t="n">
-        <v>13.07484801560446</v>
+        <v>13.07484804592508</v>
       </c>
       <c r="BY35" t="n">
-        <v>19.0369787107201</v>
+        <v>19.03697875486692</v>
       </c>
       <c r="BZ35" t="n">
         <v>16.69724770642202</v>
@@ -11840,7 +11816,7 @@
         <v>14.75038161497534</v>
       </c>
       <c r="CF35" t="n">
-        <v>16.14617478847187</v>
+        <v>16.14617480088311</v>
       </c>
       <c r="CG35" t="n">
         <v>15.72381466069868</v>
@@ -11861,7 +11837,7 @@
         <v>34.77555423456013</v>
       </c>
       <c r="CM35" t="n">
-        <v>53.77309322354162</v>
+        <v>53.77309334174394</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -12144,37 +12120,37 @@
         <v>18.65999984741211</v>
       </c>
       <c r="BX36" t="n">
-        <v>8.753833598067141</v>
+        <v>8.753833593338662</v>
       </c>
       <c r="BY36" t="n">
-        <v>9.216135788133215</v>
+        <v>9.216135788373666</v>
       </c>
       <c r="BZ36" t="n">
-        <v>9.677566761480378</v>
+        <v>9.677566766960314</v>
       </c>
       <c r="CA36" t="n">
         <v>16.95274264519251</v>
       </c>
       <c r="CB36" t="n">
-        <v>9.24965515422797</v>
+        <v>9.249655158268371</v>
       </c>
       <c r="CC36" t="n">
-        <v>17.54241683712353</v>
+        <v>17.54241683828941</v>
       </c>
       <c r="CD36" t="n">
-        <v>3.939249717688818</v>
+        <v>3.939249723098197</v>
       </c>
       <c r="CE36" t="n">
         <v>16.17967221207829</v>
       </c>
       <c r="CF36" t="n">
-        <v>11.43890908924898</v>
+        <v>11.43890909069993</v>
       </c>
       <c r="CG36" t="n">
-        <v>9.463610957854174</v>
+        <v>9.463610962614343</v>
       </c>
       <c r="CH36" t="n">
-        <v>8.517249862068757</v>
+        <v>8.517249866352909</v>
       </c>
       <c r="CI36" t="n">
         <v>8</v>
@@ -12186,10 +12162,10 @@
         <v>4.5</v>
       </c>
       <c r="CL36" t="n">
-        <v>-54.35557378501272</v>
+        <v>-54.35557376205371</v>
       </c>
       <c r="CM36" t="n">
-        <v>-38.69823589073928</v>
+        <v>-38.69823588296358</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -13028,10 +13004,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="BX2" t="n">
-        <v>5.87427218800108</v>
+        <v>5.874272108025008</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.896774908742</v>
+        <v>10.89677476038639</v>
       </c>
       <c r="BZ2" t="n">
         <v>41.25748351662458</v>
@@ -13040,7 +13016,7 @@
         <v>27.69424604953494</v>
       </c>
       <c r="CB2" t="n">
-        <v>71.32928290717642</v>
+        <v>71.32928257194737</v>
       </c>
       <c r="CC2" t="n">
         <v>19.57807411896471</v>
@@ -13102,7 +13078,7 @@
         <v>-4.147472323669144</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-26.52097580569606</v>
+        <v>-26.52096568735769</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
@@ -13346,10 +13322,10 @@
         <v>13.36999988555908</v>
       </c>
       <c r="BX3" t="n">
-        <v>14.75007820110445</v>
+        <v>14.75007813219094</v>
       </c>
       <c r="BY3" t="n">
-        <v>27.36139506304876</v>
+        <v>27.3613949352142</v>
       </c>
       <c r="BZ3" t="n">
         <v>38.76422286294482</v>
@@ -13358,13 +13334,13 @@
         <v>23.45333307258707</v>
       </c>
       <c r="CB3" t="n">
-        <v>75.35854784329271</v>
+        <v>75.35854797043419</v>
       </c>
       <c r="CC3" t="n">
-        <v>48.54748521036084</v>
+        <v>48.54748526124334</v>
       </c>
       <c r="CD3" t="n">
-        <v>26.78098970630979</v>
+        <v>26.78098991892728</v>
       </c>
       <c r="CE3" t="n">
         <v>8.814883789850169</v>
@@ -13664,10 +13640,10 @@
         <v>24.60000038146973</v>
       </c>
       <c r="BX4" t="n">
-        <v>16.30060358702401</v>
+        <v>16.30060358833519</v>
       </c>
       <c r="BY4" t="n">
-        <v>30.23761965392954</v>
+        <v>30.23761965636179</v>
       </c>
       <c r="BZ4" t="n">
         <v>71.16812337433926</v>
@@ -13676,19 +13652,19 @@
         <v>51.52104017548554</v>
       </c>
       <c r="CB4" t="n">
-        <v>125.1392993823085</v>
+        <v>125.1392993818412</v>
       </c>
       <c r="CC4" t="n">
-        <v>25.69671526310594</v>
+        <v>25.69671526291816</v>
       </c>
       <c r="CD4" t="n">
-        <v>61.68777253041441</v>
+        <v>61.68777252760135</v>
       </c>
       <c r="CE4" t="n">
         <v>43.13507176990557</v>
       </c>
       <c r="CF4" t="n">
-        <v>47.24105712786337</v>
+        <v>47.24105712776861</v>
       </c>
       <c r="CG4" t="n">
         <v>47.32805597269555</v>
@@ -13709,7 +13685,7 @@
         <v>73.1514216053079</v>
       </c>
       <c r="CM4" t="n">
-        <v>92.03681461504496</v>
+        <v>92.03681461465976</v>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
@@ -13990,10 +13966,10 @@
         <v>4.110000133514404</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.73321908983248</v>
+        <v>3.733219077861432</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.925121411639251</v>
+        <v>6.925121389432955</v>
       </c>
       <c r="BZ5" t="n">
         <v>12.72371536660417</v>
@@ -14002,25 +13978,25 @@
         <v>8.566797975520885</v>
       </c>
       <c r="CB5" t="n">
-        <v>24.60513833552532</v>
+        <v>24.6051383438305</v>
       </c>
       <c r="CC5" t="n">
-        <v>11.20720451984052</v>
+        <v>11.2072045247466</v>
       </c>
       <c r="CD5" t="n">
-        <v>10.35562989645032</v>
+        <v>10.35562992628408</v>
       </c>
       <c r="CE5" t="n">
         <v>5.28099461109321</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.176577296858058</v>
+        <v>9.176577298946984</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.461213935985601</v>
+        <v>9.461213950902485</v>
       </c>
       <c r="CH5" t="n">
-        <v>8.515092542387041</v>
+        <v>8.515092555812236</v>
       </c>
       <c r="CI5" t="n">
         <v>6</v>
@@ -14032,10 +14008,10 @@
         <v>6.6</v>
       </c>
       <c r="CL5" t="n">
-        <v>107.1798604810726</v>
+        <v>107.1798608077197</v>
       </c>
       <c r="CM5" t="n">
-        <v>123.2743795317421</v>
+        <v>123.2743795825676</v>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
@@ -14300,10 +14276,10 @@
         <v>48.54000091552734</v>
       </c>
       <c r="BX6" t="n">
-        <v>18.49767256282114</v>
+        <v>18.49767258046552</v>
       </c>
       <c r="BY6" t="n">
-        <v>34.31318260403322</v>
+        <v>34.31318263676354</v>
       </c>
       <c r="BZ6" t="n">
         <v>75.48767748013348</v>
@@ -14312,23 +14288,23 @@
         <v>56.48770574587493</v>
       </c>
       <c r="CB6" t="n">
-        <v>101.3707432448298</v>
+        <v>101.3707432174032</v>
       </c>
       <c r="CC6" t="n">
-        <v>48.40360291175992</v>
+        <v>48.40360290749748</v>
       </c>
       <c r="CD6" t="n">
-        <v>59.83279359511664</v>
+        <v>59.83279355965287</v>
       </c>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="n">
-        <v>44.17553388968694</v>
+        <v>44.175533901215</v>
       </c>
       <c r="CG6" t="n">
-        <v>41.35839275789657</v>
+        <v>41.35839277213051</v>
       </c>
       <c r="CH6" t="n">
-        <v>37.22255348210691</v>
+        <v>37.22255349491746</v>
       </c>
       <c r="CI6" t="n">
         <v>4</v>
@@ -14340,10 +14316,10 @@
         <v>4.1</v>
       </c>
       <c r="CL6" t="n">
-        <v>-23.31571326732325</v>
+        <v>-23.31571324093151</v>
       </c>
       <c r="CM6" t="n">
-        <v>-8.991485256532549</v>
+        <v>-8.991485232782924</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
@@ -14626,10 +14602,10 @@
         <v>4.409999847412109</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.217002919301321</v>
+        <v>3.217002916849567</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.967540415303951</v>
+        <v>5.967540410755946</v>
       </c>
       <c r="BZ7" t="n">
         <v>12.73039171638572</v>
@@ -14638,7 +14614,7 @@
         <v>8.563510105820175</v>
       </c>
       <c r="CB7" t="n">
-        <v>24.223973547146</v>
+        <v>24.22397353966788</v>
       </c>
       <c r="CC7" t="n">
         <v>11.57513776217851</v>
@@ -14650,7 +14626,7 @@
         <v>5.278370495623927</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.42348769089854</v>
+        <v>11.42348768918052</v>
       </c>
       <c r="CG7" t="n">
         <v>11.57513776217851</v>
@@ -14671,7 +14647,7 @@
         <v>136.2273094425153</v>
       </c>
       <c r="CM7" t="n">
-        <v>159.0360110239484</v>
+        <v>159.036010984991</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
@@ -14710,7 +14686,7 @@
         <v>-2.556002609200203</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-42.88871827907796</v>
+        <v>-42.88872193099961</v>
       </c>
       <c r="DA7" t="b">
         <v>1</v>
@@ -15166,10 +15142,10 @@
         <v>41.45000076293945</v>
       </c>
       <c r="BX9" t="n">
-        <v>121.4412679716231</v>
+        <v>121.4412680126986</v>
       </c>
       <c r="BY9" t="n">
-        <v>225.2735520873608</v>
+        <v>225.273552163556</v>
       </c>
       <c r="BZ9" t="n">
         <v>136.9607257129545</v>
@@ -15190,13 +15166,13 @@
         <v>57.8068628710751</v>
       </c>
       <c r="CF9" t="n">
-        <v>116.5644819207811</v>
+        <v>116.5644819375341</v>
       </c>
       <c r="CG9" t="n">
-        <v>121.4412679716231</v>
+        <v>121.4412680126986</v>
       </c>
       <c r="CH9" t="n">
-        <v>109.2971411744608</v>
+        <v>109.2971412114288</v>
       </c>
       <c r="CI9" t="n">
         <v>7</v>
@@ -15208,10 +15184,10 @@
         <v>5.5</v>
       </c>
       <c r="CL9" t="n">
-        <v>163.684292310517</v>
+        <v>163.6842923997039</v>
       </c>
       <c r="CM9" t="n">
-        <v>181.2170802780822</v>
+        <v>181.2170803184995</v>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
@@ -15494,10 +15470,10 @@
         <v>15.67000007629395</v>
       </c>
       <c r="BX10" t="n">
-        <v>6.392639624814289</v>
+        <v>6.392639630005946</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.85834650403051</v>
+        <v>11.85834651366103</v>
       </c>
       <c r="BZ10" t="n">
         <v>25.41340281651098</v>
@@ -15506,19 +15482,19 @@
         <v>18.62224018162043</v>
       </c>
       <c r="CB10" t="n">
-        <v>35.3125200641127</v>
+        <v>35.31252005570318</v>
       </c>
       <c r="CC10" t="n">
-        <v>12.3015336058021</v>
+        <v>12.30153360481723</v>
       </c>
       <c r="CD10" t="n">
-        <v>20.43463668128798</v>
+        <v>20.43463667041001</v>
       </c>
       <c r="CE10" t="n">
         <v>18.38139646228262</v>
       </c>
       <c r="CF10" t="n">
-        <v>20.33201090223534</v>
+        <v>20.33201090071507</v>
       </c>
       <c r="CG10" t="n">
         <v>18.62224018162043</v>
@@ -15539,7 +15515,7 @@
         <v>6.956069443888868</v>
       </c>
       <c r="CM10" t="n">
-        <v>29.75118572586495</v>
+        <v>29.75118571616317</v>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
@@ -15822,37 +15798,37 @@
         <v>31.98999977111816</v>
       </c>
       <c r="BX11" t="n">
-        <v>23.76330226953226</v>
+        <v>23.76330220777687</v>
       </c>
       <c r="BY11" t="n">
-        <v>36.41661188629458</v>
+        <v>36.41661246186523</v>
       </c>
       <c r="BZ11" t="n">
-        <v>39.03790506670131</v>
+        <v>39.03790578515253</v>
       </c>
       <c r="CA11" t="n">
         <v>20.7706836705417</v>
       </c>
       <c r="CB11" t="n">
-        <v>52.98477640344</v>
+        <v>52.98477688095995</v>
       </c>
       <c r="CC11" t="n">
-        <v>51.52687081186153</v>
+        <v>51.52687089124198</v>
       </c>
       <c r="CD11" t="n">
-        <v>19.51897963063692</v>
+        <v>19.51897999137731</v>
       </c>
       <c r="CE11" t="n">
         <v>24.08135454201217</v>
       </c>
       <c r="CF11" t="n">
-        <v>33.51256053512756</v>
+        <v>33.51256080386597</v>
       </c>
       <c r="CG11" t="n">
-        <v>30.24898321415338</v>
+        <v>30.2489835019387</v>
       </c>
       <c r="CH11" t="n">
-        <v>27.22408489273804</v>
+        <v>27.22408515174483</v>
       </c>
       <c r="CI11" t="n">
         <v>8</v>
@@ -15864,10 +15840,10 @@
         <v>2.7</v>
       </c>
       <c r="CL11" t="n">
-        <v>-14.89813977017587</v>
+        <v>-14.89813896052664</v>
       </c>
       <c r="CM11" t="n">
-        <v>4.759489762122548</v>
+        <v>4.759490602192606</v>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
@@ -16150,10 +16126,10 @@
         <v>32.34999847412109</v>
       </c>
       <c r="BX12" t="n">
-        <v>45.1758884852444</v>
+        <v>45.17588854290364</v>
       </c>
       <c r="BY12" t="n">
-        <v>83.80127314012836</v>
+        <v>83.80127324708624</v>
       </c>
       <c r="BZ12" t="n">
         <v>68.14586324039816</v>
@@ -16174,7 +16150,7 @@
         <v>25.45102053342143</v>
       </c>
       <c r="CF12" t="n">
-        <v>77.26388350077593</v>
+        <v>77.26388352429265</v>
       </c>
       <c r="CG12" t="n">
         <v>68.14586324039816</v>
@@ -16195,7 +16171,7 @@
         <v>89.58664546899837</v>
       </c>
       <c r="CM12" t="n">
-        <v>138.8373636635082</v>
+        <v>138.8373637362028</v>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
@@ -16480,10 +16456,10 @@
         <v>45.93000030517578</v>
       </c>
       <c r="BX13" t="n">
-        <v>127.4901592234444</v>
+        <v>127.490158728825</v>
       </c>
       <c r="BY13" t="n">
-        <v>236.4942453594893</v>
+        <v>236.4942444419704</v>
       </c>
       <c r="BZ13" t="n">
         <v>137.0658792890943</v>
@@ -16504,13 +16480,13 @@
         <v>56.48463159734047</v>
       </c>
       <c r="CF13" t="n">
-        <v>142.809052208906</v>
+        <v>142.8090520323887</v>
       </c>
       <c r="CG13" t="n">
-        <v>126.3298773248559</v>
+        <v>126.3298770775462</v>
       </c>
       <c r="CH13" t="n">
-        <v>113.6968895923703</v>
+        <v>113.6968893697916</v>
       </c>
       <c r="CI13" t="n">
         <v>8</v>
@@ -16522,10 +16498,10 @@
         <v>5.5</v>
       </c>
       <c r="CL13" t="n">
-        <v>147.5438468036717</v>
+        <v>147.5438463190675</v>
       </c>
       <c r="CM13" t="n">
-        <v>210.9276099717618</v>
+        <v>210.9276095874438</v>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
@@ -16564,7 +16540,7 @@
         <v>-4.431848361876922</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-13.53632911913226</v>
+        <v>-13.53634187597278</v>
       </c>
       <c r="DA13" t="b">
         <v>1</v>
@@ -16808,10 +16784,10 @@
         <v>6.909999847412109</v>
       </c>
       <c r="BX14" t="n">
-        <v>6.487949229844635</v>
+        <v>6.48794922151543</v>
       </c>
       <c r="BY14" t="n">
-        <v>12.0351458213618</v>
+        <v>12.03514580591112</v>
       </c>
       <c r="BZ14" t="n">
         <v>40.33369954987244</v>
@@ -16820,7 +16796,7 @@
         <v>27.1935797236935</v>
       </c>
       <c r="CB14" t="n">
-        <v>85.67457573965046</v>
+        <v>85.67457568828091</v>
       </c>
       <c r="CC14" t="n">
         <v>51.88018214566937</v>
@@ -17120,10 +17096,10 @@
         <v>13.56999969482422</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.1998710114460401</v>
+        <v>0.1998710114230436</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.2910121926654344</v>
+        <v>0.2910121926319515</v>
       </c>
       <c r="BZ15" t="n">
         <v>75.87526711084509</v>
@@ -17414,10 +17390,10 @@
         <v>13.85000038146973</v>
       </c>
       <c r="BX16" t="n">
-        <v>10.05410344206793</v>
+        <v>10.05410336249058</v>
       </c>
       <c r="BY16" t="n">
-        <v>18.65036188503601</v>
+        <v>18.65036173742002</v>
       </c>
       <c r="BZ16" t="n">
         <v>49.59797433904698</v>
@@ -17426,23 +17402,23 @@
         <v>48.79127221912361</v>
       </c>
       <c r="CB16" t="n">
-        <v>69.01352270723687</v>
+        <v>69.01352255386078</v>
       </c>
       <c r="CC16" t="n">
-        <v>33.93511808352063</v>
+        <v>33.93511809588975</v>
       </c>
       <c r="CD16" t="n">
-        <v>29.46727354347165</v>
+        <v>29.46727363632887</v>
       </c>
       <c r="CE16" t="inlineStr"/>
       <c r="CF16" t="n">
-        <v>34.06115143586788</v>
+        <v>34.06115139078558</v>
       </c>
       <c r="CG16" t="n">
-        <v>33.93511808352063</v>
+        <v>33.93511809588975</v>
       </c>
       <c r="CH16" t="n">
-        <v>30.54160627516857</v>
+        <v>30.54160628630077</v>
       </c>
       <c r="CI16" t="n">
         <v>3</v>
@@ -17454,10 +17430,10 @@
         <v>4.9</v>
       </c>
       <c r="CL16" t="n">
-        <v>120.5170067434148</v>
+        <v>120.5170068237917</v>
       </c>
       <c r="CM16" t="n">
-        <v>145.9288844600985</v>
+        <v>145.9288841345945</v>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
@@ -17718,10 +17694,10 @@
         <v>19.20999908447266</v>
       </c>
       <c r="BX17" t="n">
-        <v>13.20480146414876</v>
+        <v>13.20480144991564</v>
       </c>
       <c r="BY17" t="n">
-        <v>24.49490671599595</v>
+        <v>24.49490668959352</v>
       </c>
       <c r="BZ17" t="n">
         <v>19.97900218754024</v>
@@ -17730,7 +17706,7 @@
         <v>12.48664452830808</v>
       </c>
       <c r="CB17" t="n">
-        <v>33.81124087749864</v>
+        <v>33.81124086185785</v>
       </c>
       <c r="CC17" t="n">
         <v>22.8984489302328</v>
@@ -17740,7 +17716,7 @@
       </c>
       <c r="CE17" t="inlineStr"/>
       <c r="CF17" t="n">
-        <v>20.14428982447944</v>
+        <v>20.14428981432055</v>
       </c>
       <c r="CG17" t="n">
         <v>21.43872555888652</v>
@@ -17761,7 +17737,7 @@
         <v>0.4417174522084899</v>
       </c>
       <c r="CM17" t="n">
-        <v>4.863564729484882</v>
+        <v>4.863564676601562</v>
       </c>
       <c r="CN17" t="inlineStr">
         <is>
@@ -18052,10 +18028,10 @@
         <v>7.119999885559082</v>
       </c>
       <c r="BX18" t="n">
-        <v>3.21473233594391</v>
+        <v>3.214732338826915</v>
       </c>
       <c r="BY18" t="n">
-        <v>5.963328483175953</v>
+        <v>5.963328488523926</v>
       </c>
       <c r="BZ18" t="n">
         <v>19.81932741253316</v>
@@ -18064,7 +18040,7 @@
         <v>13.57675850780915</v>
       </c>
       <c r="CB18" t="n">
-        <v>31.89206953500021</v>
+        <v>31.89206954347963</v>
       </c>
       <c r="CC18" t="n">
         <v>10.95072400487419</v>
@@ -18370,10 +18346,10 @@
         <v>17.47999954223633</v>
       </c>
       <c r="BX19" t="n">
-        <v>10.71384735269345</v>
+        <v>10.71384731370265</v>
       </c>
       <c r="BY19" t="n">
-        <v>19.87418683924636</v>
+        <v>19.87418676691842</v>
       </c>
       <c r="BZ19" t="n">
         <v>37.47734529686591</v>
@@ -18382,25 +18358,25 @@
         <v>37.0591905335928</v>
       </c>
       <c r="CB19" t="n">
-        <v>41.78101224739631</v>
+        <v>41.78101223101346</v>
       </c>
       <c r="CC19" t="n">
-        <v>34.50404065992525</v>
+        <v>34.50404066819012</v>
       </c>
       <c r="CD19" t="n">
-        <v>18.56246600890206</v>
+        <v>18.56246605412515</v>
       </c>
       <c r="CE19" t="n">
         <v>31.88800278970118</v>
       </c>
       <c r="CF19" t="n">
-        <v>31.59232062508998</v>
+        <v>31.59232062005814</v>
       </c>
       <c r="CG19" t="n">
-        <v>34.50404065992525</v>
+        <v>34.50404066819012</v>
       </c>
       <c r="CH19" t="n">
-        <v>31.05363659393273</v>
+        <v>31.05363660137111</v>
       </c>
       <c r="CI19" t="n">
         <v>7</v>
@@ -18412,10 +18388,10 @@
         <v>3.9</v>
       </c>
       <c r="CL19" t="n">
-        <v>77.65238791281934</v>
+        <v>77.65238795537302</v>
       </c>
       <c r="CM19" t="n">
-        <v>80.73410441890761</v>
+        <v>80.73410439012136</v>
       </c>
       <c r="CN19" t="inlineStr">
         <is>
@@ -18700,10 +18676,10 @@
         <v>3.480000019073486</v>
       </c>
       <c r="BX20" t="n">
-        <v>5.030148809289601</v>
+        <v>5.03014876148871</v>
       </c>
       <c r="BY20" t="n">
-        <v>9.330926041232209</v>
+        <v>9.330925952561557</v>
       </c>
       <c r="BZ20" t="n">
         <v>8.507380120428724</v>
@@ -18774,7 +18750,7 @@
         <v>-2.096134038389974</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-28.72157845771649</v>
+        <v>-28.72158548753347</v>
       </c>
       <c r="DA20" t="b">
         <v>1</v>
@@ -19018,37 +18994,37 @@
         <v>10.25</v>
       </c>
       <c r="BX21" t="n">
-        <v>10.27005386738239</v>
+        <v>10.27005390284119</v>
       </c>
       <c r="BY21" t="n">
-        <v>17.87947162401748</v>
+        <v>17.87947153337628</v>
       </c>
       <c r="BZ21" t="n">
-        <v>22.96597064665681</v>
+        <v>22.96597045093602</v>
       </c>
       <c r="CA21" t="n">
         <v>17.56827373614594</v>
       </c>
       <c r="CB21" t="n">
-        <v>36.09152089278309</v>
+        <v>36.09152085861933</v>
       </c>
       <c r="CC21" t="n">
-        <v>24.12174237813253</v>
+        <v>24.12174236283168</v>
       </c>
       <c r="CD21" t="n">
-        <v>11.33576890530264</v>
+        <v>11.33576882760532</v>
       </c>
       <c r="CE21" t="n">
         <v>10.25</v>
       </c>
       <c r="CF21" t="n">
-        <v>18.81035025630261</v>
+        <v>18.81035020904447</v>
       </c>
       <c r="CG21" t="n">
-        <v>17.72387268008171</v>
+        <v>17.72387263476111</v>
       </c>
       <c r="CH21" t="n">
-        <v>15.95148541207354</v>
+        <v>15.951485371285</v>
       </c>
       <c r="CI21" t="n">
         <v>8</v>
@@ -19060,10 +19036,10 @@
         <v>3.5</v>
       </c>
       <c r="CL21" t="n">
-        <v>55.62424792266869</v>
+        <v>55.62424752473167</v>
       </c>
       <c r="CM21" t="n">
-        <v>83.51561225661086</v>
+        <v>83.5156117955558</v>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
@@ -19346,10 +19322,10 @@
         <v>10.80000019073486</v>
       </c>
       <c r="BX22" t="n">
-        <v>3.367718440283852</v>
+        <v>3.367718439463935</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.247117706726545</v>
+        <v>6.2471177052056</v>
       </c>
       <c r="BZ22" t="n">
         <v>19.65659375374133</v>
@@ -19358,13 +19334,13 @@
         <v>18.52911526753888</v>
       </c>
       <c r="CB22" t="n">
-        <v>21.05981933951412</v>
+        <v>21.05981933959146</v>
       </c>
       <c r="CC22" t="n">
-        <v>15.92813033546488</v>
+        <v>15.92813033562657</v>
       </c>
       <c r="CD22" t="n">
-        <v>13.12984067363762</v>
+        <v>13.12984067467734</v>
       </c>
       <c r="CE22" t="n">
         <v>29.56959057813611</v>
@@ -19420,7 +19396,7 @@
         <v>-20.99487834338889</v>
       </c>
       <c r="CZ22" t="n">
-        <v>-34.59225116497123</v>
+        <v>-34.59224337860515</v>
       </c>
       <c r="DA22" t="b">
         <v>1</v>
@@ -19493,7 +19469,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -19664,37 +19640,37 @@
         <v>35.38999938964844</v>
       </c>
       <c r="BX23" t="n">
-        <v>25.4470063588914</v>
+        <v>25.44700657030386</v>
       </c>
       <c r="BY23" t="n">
-        <v>29.96724775302992</v>
+        <v>29.96724745780718</v>
       </c>
       <c r="BZ23" t="n">
-        <v>32.35749197739312</v>
+        <v>32.35749138979844</v>
       </c>
       <c r="CA23" t="n">
         <v>36.10305636518475</v>
       </c>
       <c r="CB23" t="n">
-        <v>45.98394667054951</v>
+        <v>45.98394623604176</v>
       </c>
       <c r="CC23" t="n">
-        <v>48.24425107554295</v>
+        <v>48.24425098245746</v>
       </c>
       <c r="CD23" t="n">
-        <v>14.83986891463602</v>
+        <v>14.83986843929625</v>
       </c>
       <c r="CE23" t="n">
         <v>30.48403103827181</v>
       </c>
       <c r="CF23" t="n">
-        <v>32.92836251918743</v>
+        <v>32.92836230989519</v>
       </c>
       <c r="CG23" t="n">
-        <v>31.42076150783247</v>
+        <v>31.42076121403512</v>
       </c>
       <c r="CH23" t="n">
-        <v>28.27868535704922</v>
+        <v>28.27868509263161</v>
       </c>
       <c r="CI23" t="n">
         <v>8</v>
@@ -19706,10 +19682,10 @@
         <v>3.3</v>
       </c>
       <c r="CL23" t="n">
-        <v>-20.09413437480667</v>
+        <v>-20.09413512196014</v>
       </c>
       <c r="CM23" t="n">
-        <v>-6.955741488882405</v>
+        <v>-6.955742080270488</v>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
@@ -19723,11 +19699,7 @@
       </c>
       <c r="CP23" t="inlineStr"/>
       <c r="CQ23" t="inlineStr"/>
-      <c r="CR23" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CR23" t="inlineStr"/>
       <c r="CS23" t="b">
         <v>0</v>
       </c>
@@ -19754,14 +19726,14 @@
         <v>0</v>
       </c>
       <c r="DB23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC23" t="b">
         <v>0</v>
       </c>
       <c r="DD23" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.1, +0.5% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -19896,13 +19868,13 @@
         <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AS24" t="b">
         <v>1</v>
       </c>
       <c r="AT24" t="n">
-        <v>5725241856</v>
+        <v>3602869248</v>
       </c>
       <c r="AU24" t="n">
         <v>6.7</v>
@@ -19992,10 +19964,10 @@
         <v>11.01000022888184</v>
       </c>
       <c r="BX24" t="n">
-        <v>9.531702557211867</v>
+        <v>9.531702563879664</v>
       </c>
       <c r="BY24" t="n">
-        <v>17.68130824362801</v>
+        <v>17.68130825599678</v>
       </c>
       <c r="BZ24" t="n">
         <v>21.77350791532602</v>
@@ -20004,25 +19976,25 @@
         <v>12.86392893329986</v>
       </c>
       <c r="CB24" t="n">
-        <v>31.27631901617183</v>
+        <v>31.27631899577072</v>
       </c>
       <c r="CC24" t="n">
-        <v>25.272397052258</v>
+        <v>25.27239704731914</v>
       </c>
       <c r="CD24" t="n">
-        <v>11.53006420794424</v>
+        <v>11.53006418636298</v>
       </c>
       <c r="CE24" t="n">
         <v>9.491669059101429</v>
       </c>
       <c r="CF24" t="n">
-        <v>17.42761212311766</v>
+        <v>17.42761211963207</v>
       </c>
       <c r="CG24" t="n">
-        <v>15.27261858846394</v>
+        <v>15.27261859464832</v>
       </c>
       <c r="CH24" t="n">
-        <v>13.74535672961754</v>
+        <v>13.74535673518349</v>
       </c>
       <c r="CI24" t="n">
         <v>8</v>
@@ -20034,10 +20006,10 @@
         <v>3.3</v>
       </c>
       <c r="CL24" t="n">
-        <v>24.84429104333914</v>
+        <v>24.84429109389268</v>
       </c>
       <c r="CM24" t="n">
-        <v>58.28893515733913</v>
+        <v>58.28893512568077</v>
       </c>
       <c r="CN24" t="inlineStr">
         <is>
@@ -20320,10 +20292,10 @@
         <v>14.43000030517578</v>
       </c>
       <c r="BX25" t="n">
-        <v>4.431663289484948</v>
+        <v>4.431663297379163</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.220735401994579</v>
+        <v>8.220735416638348</v>
       </c>
       <c r="BZ25" t="n">
         <v>24.1410989954014</v>
@@ -20332,25 +20304,25 @@
         <v>20.3388779315304</v>
       </c>
       <c r="CB25" t="n">
-        <v>29.54551956977053</v>
+        <v>29.54551956375417</v>
       </c>
       <c r="CC25" t="n">
-        <v>16.71779866014972</v>
+        <v>16.71779865851239</v>
       </c>
       <c r="CD25" t="n">
-        <v>18.514661129904</v>
+        <v>18.51466111735093</v>
       </c>
       <c r="CE25" t="n">
         <v>14.20112306536562</v>
       </c>
       <c r="CF25" t="n">
-        <v>18.81140210773089</v>
+        <v>18.81140210693618</v>
       </c>
       <c r="CG25" t="n">
-        <v>18.514661129904</v>
+        <v>18.51466111735093</v>
       </c>
       <c r="CH25" t="n">
-        <v>16.6631950169136</v>
+        <v>16.66319500561584</v>
       </c>
       <c r="CI25" t="n">
         <v>7</v>
@@ -20362,10 +20334,10 @@
         <v>6.7</v>
       </c>
       <c r="CL25" t="n">
-        <v>15.47605450109943</v>
+        <v>15.47605442280588</v>
       </c>
       <c r="CM25" t="n">
-        <v>30.36314421271067</v>
+        <v>30.3631442072033</v>
       </c>
       <c r="CN25" t="inlineStr">
         <is>
@@ -20787,7 +20759,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -20958,10 +20930,10 @@
         <v>13.60000038146973</v>
       </c>
       <c r="BX27" t="n">
-        <v>8.528550089815537</v>
+        <v>8.528550104935128</v>
       </c>
       <c r="BY27" t="n">
-        <v>15.82046041660782</v>
+        <v>15.82046044465466</v>
       </c>
       <c r="BZ27" t="n">
         <v>13.60000038146972</v>
@@ -20982,7 +20954,7 @@
         <v>6.216978540913663</v>
       </c>
       <c r="CF27" t="n">
-        <v>11.13864633142741</v>
+        <v>11.13864633759404</v>
       </c>
       <c r="CG27" t="n">
         <v>11.05492190131465</v>
@@ -21003,7 +20975,7 @@
         <v>-26.84243064625581</v>
       </c>
       <c r="CM27" t="n">
-        <v>-18.09819103678822</v>
+        <v>-18.09819099144534</v>
       </c>
       <c r="CN27" t="inlineStr">
         <is>
@@ -21017,11 +20989,7 @@
       </c>
       <c r="CP27" t="inlineStr"/>
       <c r="CQ27" t="inlineStr"/>
-      <c r="CR27" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CR27" t="inlineStr"/>
       <c r="CS27" t="b">
         <v>0</v>
       </c>
@@ -21048,14 +21016,14 @@
         <v>0</v>
       </c>
       <c r="DB27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC27" t="b">
         <v>0</v>
       </c>
       <c r="DD27" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.0, +0.5% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -21286,10 +21254,10 @@
         <v>27.42000007629395</v>
       </c>
       <c r="BX28" t="n">
-        <v>7.26488727784715</v>
+        <v>7.26488728278337</v>
       </c>
       <c r="BY28" t="n">
-        <v>13.47636590040646</v>
+        <v>13.47636590956315</v>
       </c>
       <c r="BZ28" t="n">
         <v>35.79458138038372</v>
@@ -21298,19 +21266,19 @@
         <v>28.30701155023988</v>
       </c>
       <c r="CB28" t="n">
-        <v>44.58429128193586</v>
+        <v>44.58429127456367</v>
       </c>
       <c r="CC28" t="n">
-        <v>26.46258109875249</v>
+        <v>26.46258109752097</v>
       </c>
       <c r="CD28" t="n">
-        <v>28.94259526759421</v>
+        <v>28.94259525868057</v>
       </c>
       <c r="CE28" t="n">
         <v>24.89125670295465</v>
       </c>
       <c r="CF28" t="n">
-        <v>28.92266902603818</v>
+        <v>28.9226690248438</v>
       </c>
       <c r="CG28" t="n">
         <v>28.30701155023988</v>
@@ -21331,7 +21299,7 @@
         <v>-7.088583791648051</v>
       </c>
       <c r="CM28" t="n">
-        <v>5.480193091040042</v>
+        <v>5.480193086684171</v>
       </c>
       <c r="CN28" t="inlineStr">
         <is>
@@ -21594,10 +21562,10 @@
         <v>39.40999984741211</v>
       </c>
       <c r="BX29" t="n">
-        <v>36.08952119338425</v>
+        <v>36.0895211397676</v>
       </c>
       <c r="BY29" t="n">
-        <v>52.54634285756747</v>
+        <v>52.54634277950162</v>
       </c>
       <c r="BZ29" t="n">
         <v>49.20336115403192</v>
@@ -21614,13 +21582,13 @@
       </c>
       <c r="CE29" t="inlineStr"/>
       <c r="CF29" t="n">
-        <v>49.33584754720034</v>
+        <v>49.33584751427971</v>
       </c>
       <c r="CG29" t="n">
-        <v>50.8748520057997</v>
+        <v>50.87485196676677</v>
       </c>
       <c r="CH29" t="n">
-        <v>45.78736680521973</v>
+        <v>45.7873667700901</v>
       </c>
       <c r="CI29" t="n">
         <v>4</v>
@@ -21632,10 +21600,10 @@
         <v>1.6</v>
       </c>
       <c r="CL29" t="n">
-        <v>16.18210348261748</v>
+        <v>16.18210339347861</v>
       </c>
       <c r="CM29" t="n">
-        <v>25.18611453493831</v>
+        <v>25.18611445140462</v>
       </c>
       <c r="CN29" t="inlineStr">
         <is>
@@ -21926,10 +21894,10 @@
         <v>24.09000015258789</v>
       </c>
       <c r="BX30" t="n">
-        <v>12.49848621915751</v>
+        <v>12.49848621547585</v>
       </c>
       <c r="BY30" t="n">
-        <v>23.18469193653717</v>
+        <v>23.1846919297077</v>
       </c>
       <c r="BZ30" t="n">
         <v>59.55083992943834</v>
@@ -21938,13 +21906,13 @@
         <v>49.85774466322926</v>
       </c>
       <c r="CB30" t="n">
-        <v>82.76196868278976</v>
+        <v>82.76196868258529</v>
       </c>
       <c r="CC30" t="n">
-        <v>33.64819480607403</v>
+        <v>33.57583309744623</v>
       </c>
       <c r="CD30" t="n">
-        <v>43.50838276034663</v>
+        <v>43.50838276626259</v>
       </c>
       <c r="CE30" t="n">
         <v>5.300682749020105</v>
@@ -22069,7 +22037,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -22240,10 +22208,10 @@
         <v>22.70000076293945</v>
       </c>
       <c r="BX31" t="n">
-        <v>3.19748135082587</v>
+        <v>3.197481352371524</v>
       </c>
       <c r="BY31" t="n">
-        <v>5.931327905781989</v>
+        <v>5.931327908649177</v>
       </c>
       <c r="BZ31" t="n">
         <v>32.87158580425658</v>
@@ -22252,7 +22220,7 @@
         <v>27.4632507976689</v>
       </c>
       <c r="CB31" t="n">
-        <v>42.10543719733923</v>
+        <v>42.10543719970417</v>
       </c>
       <c r="CC31" t="n">
         <v>10.85340539909456</v>
@@ -22292,16 +22260,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ31" t="inlineStr">
-        <is>
-          <t>A Vivara (VIVA3) apresenta-se como uma opção robusta no setor de consumo discricionário, destacando-se por uma eficiência operacional superior à de seus pares, evidenciada por um ROE de 18,4% e um ROIC de 17,3% que se posicionam confortavelmente acima das médias setoriais de 12,5% e 13,1%, respectivamente. Essa alta rentabilidade convive com múltiplos de valuation bastante atrativos, uma vez que o P/L de 9,15 e o P/VP de 1,68 sugerem que a qualidade da empresa não está precificada com ágio excessivo, configurando uma relação favorável entre qualidade e preço. No âmbito financeiro, a excelente rentabilidade é acompanhada por um endividamento muito saudável, com a relação dívida líquida por EBITDA em 1,1, patamar significativamente abaixo da média do setor de 2,67, o que, somado a uma liquidez corrente de 4,19, confere extrema segurança ao balanço. Por outro lado, o dividend yield de 3,07% mostra-se modesto, o que é coerente com a estratégia de retenção de lucros para expansão, embora a sustentabilidade desses proventos seja garantida pela baixa alavancagem e forte geração de caixa. O grande ponto de atenção reside no crescimento histórico, visto que o CAGR de receita de cinco anos de apenas 0,4% ficou muito abaixo da média setorial de 31,0%, indicando uma expansão recente mais lenta que a de seus concorrentes. No checklist de critérios fundamentalistas, a companhia demonstra solidez ao atender a 6 dos 8 requisitos avaliados, falhando apenas no crescimento frente ao setor e na ocorrência de venda de ações por insiders. Sob a ótica de valuation, as estimativas de preço-teto revelam uma enorme dispersão entre os métodos de fluxo de caixa descontado (R$ 32,87), Graham (R$ 27,46) e Lynch (R$ 42,11), que apontam para um potencial de valorização perante o preço atual de R$ 22,7, em contraste com os modelos focados em dividendos como Bazin (R$ 3,2) e Gordon (R$ 5,93), que penalizam o papel pelo seu baixo yield. Em balanço, os prós da VIVA3 concentram-se em sua alta rentabilidade, sólida estrutura de capital e múltiplos de preço convidativos, enquanto os contras ficam por conta do fraco crescimento histórico de receita comparado ao setor e do baixo retorno em dividendos no curto prazo.</t>
-        </is>
-      </c>
-      <c r="CR31" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CQ31" t="inlineStr"/>
+      <c r="CR31" t="inlineStr"/>
       <c r="CS31" t="b">
         <v>0</v>
       </c>
@@ -22328,14 +22288,14 @@
         <v>1</v>
       </c>
       <c r="DB31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD31" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.7, +1.8% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -22566,10 +22526,10 @@
         <v>11.8100004196167</v>
       </c>
       <c r="BX32" t="n">
-        <v>2.042839373979011</v>
+        <v>2.042839372878399</v>
       </c>
       <c r="BY32" t="n">
-        <v>3.789467038731066</v>
+        <v>3.789467036689429</v>
       </c>
       <c r="BZ32" t="n">
         <v>27.94330456427165</v>
@@ -22578,10 +22538,10 @@
         <v>23.67266534349759</v>
       </c>
       <c r="CB32" t="n">
-        <v>36.74102813034941</v>
+        <v>36.74102812759788</v>
       </c>
       <c r="CC32" t="n">
-        <v>5.481618986843681</v>
+        <v>9.158754146</v>
       </c>
       <c r="CD32" t="n">
         <v>25.51803662095752</v>
@@ -22880,10 +22840,10 @@
         <v>32.59999847412109</v>
       </c>
       <c r="BX33" t="n">
-        <v>3.234610403649413</v>
+        <v>3.234610402485425</v>
       </c>
       <c r="BY33" t="n">
-        <v>6.000202298769662</v>
+        <v>6.000202296610462</v>
       </c>
       <c r="BZ33" t="n">
         <v>32.59999847412109</v>
@@ -22892,7 +22852,7 @@
         <v>22.83825145099259</v>
       </c>
       <c r="CB33" t="n">
-        <v>40.32336020852137</v>
+        <v>40.32336020729149</v>
       </c>
       <c r="CC33" t="n">
         <v>10.59424454785779</v>
@@ -22962,7 +22922,7 @@
         <v>-0.458019926347808</v>
       </c>
       <c r="CZ33" t="n">
-        <v>-31.63291935983593</v>
+        <v>-31.63292499811159</v>
       </c>
       <c r="DA33" t="b">
         <v>1</v>
@@ -23206,10 +23166,10 @@
         <v>32.06000137329102</v>
       </c>
       <c r="BX34" t="n">
-        <v>7.605318787487681</v>
+        <v>7.605318819552148</v>
       </c>
       <c r="BY34" t="n">
-        <v>14.10786635078965</v>
+        <v>14.10786641026924</v>
       </c>
       <c r="BZ34" t="n">
         <v>62.56185834994196</v>
@@ -23218,7 +23178,7 @@
         <v>36.54683885613228</v>
       </c>
       <c r="CB34" t="n">
-        <v>86.50581496674414</v>
+        <v>86.50581503285645</v>
       </c>
       <c r="CC34" t="n">
         <v>22.51480113099953</v>
@@ -23502,35 +23462,35 @@
         <v>23.04000091552734</v>
       </c>
       <c r="BX35" t="n">
-        <v>16.53701901496614</v>
+        <v>16.53701906381534</v>
       </c>
       <c r="BY35" t="n">
-        <v>29.61599422105064</v>
+        <v>29.61599421364119</v>
       </c>
       <c r="BZ35" t="n">
-        <v>50.03895742072666</v>
+        <v>50.03895726039616</v>
       </c>
       <c r="CA35" t="n">
         <v>49.4284574677156</v>
       </c>
       <c r="CB35" t="n">
-        <v>61.73828445879847</v>
+        <v>61.73828447882226</v>
       </c>
       <c r="CC35" t="n">
-        <v>45.76200014831715</v>
+        <v>45.76200013768593</v>
       </c>
       <c r="CD35" t="n">
-        <v>24.54952766996527</v>
+        <v>24.54952760956814</v>
       </c>
       <c r="CE35" t="inlineStr"/>
       <c r="CF35" t="n">
-        <v>35.48849270126515</v>
+        <v>35.48849266888465</v>
       </c>
       <c r="CG35" t="n">
-        <v>37.6889971846839</v>
+        <v>37.68899717566356</v>
       </c>
       <c r="CH35" t="n">
-        <v>33.92009746621551</v>
+        <v>33.9200974580972</v>
       </c>
       <c r="CI35" t="n">
         <v>4</v>
@@ -23542,10 +23502,10 @@
         <v>3</v>
       </c>
       <c r="CL35" t="n">
-        <v>47.22263940256938</v>
+        <v>47.22263936733368</v>
       </c>
       <c r="CM35" t="n">
-        <v>54.02991011753129</v>
+        <v>54.02990997699093</v>
       </c>
       <c r="CN35" t="inlineStr">
         <is>
@@ -23824,10 +23784,10 @@
         <v>33.2599983215332</v>
       </c>
       <c r="BX36" t="n">
-        <v>15.07088091449172</v>
+        <v>15.07088089448291</v>
       </c>
       <c r="BY36" t="n">
-        <v>27.95648409638214</v>
+        <v>27.9564840592658</v>
       </c>
       <c r="BZ36" t="n">
         <v>19.95901167392731</v>
@@ -23836,7 +23796,7 @@
         <v>36.8531743095158</v>
       </c>
       <c r="CB36" t="n">
-        <v>26.87872796650888</v>
+        <v>26.87872795382213</v>
       </c>
       <c r="CC36" t="n">
         <v>15.03391666666667</v>
@@ -23848,7 +23808,7 @@
         <v>78.37239813230944</v>
       </c>
       <c r="CF36" t="n">
-        <v>22.38070951629279</v>
+        <v>22.38070950631966</v>
       </c>
       <c r="CG36" t="n">
         <v>19.95901167392731</v>
@@ -23869,7 +23829,7 @@
         <v>-45.99184782608695</v>
       </c>
       <c r="CM36" t="n">
-        <v>-32.70982968810595</v>
+        <v>-32.70982971809133</v>
       </c>
       <c r="CN36" t="inlineStr">
         <is>
@@ -24128,35 +24088,35 @@
         <v>12.89999961853027</v>
       </c>
       <c r="BX37" t="n">
-        <v>8.660681316715355</v>
+        <v>8.66068132458957</v>
       </c>
       <c r="BY37" t="n">
-        <v>13.90577872637139</v>
+        <v>13.90577871721078</v>
       </c>
       <c r="BZ37" t="n">
-        <v>18.56293297149125</v>
+        <v>18.56293294238543</v>
       </c>
       <c r="CA37" t="n">
         <v>17.46591874479647</v>
       </c>
       <c r="CB37" t="n">
-        <v>23.07483854973443</v>
+        <v>23.07483854222391</v>
       </c>
       <c r="CC37" t="n">
-        <v>17.33679306371927</v>
+        <v>17.33679306153915</v>
       </c>
       <c r="CD37" t="n">
-        <v>9.265468041206981</v>
+        <v>9.26546802779184</v>
       </c>
       <c r="CE37" t="inlineStr"/>
       <c r="CF37" t="n">
-        <v>14.61654651957432</v>
+        <v>14.61654651143123</v>
       </c>
       <c r="CG37" t="n">
-        <v>15.62128589504533</v>
+        <v>15.62128588937497</v>
       </c>
       <c r="CH37" t="n">
-        <v>14.0591573055408</v>
+        <v>14.05915730043747</v>
       </c>
       <c r="CI37" t="n">
         <v>4</v>
@@ -24168,10 +24128,10 @@
         <v>2.1</v>
       </c>
       <c r="CL37" t="n">
-        <v>8.985718769676909</v>
+        <v>8.985718730116222</v>
       </c>
       <c r="CM37" t="n">
-        <v>13.30656551786482</v>
+        <v>13.30656545474014</v>
       </c>
       <c r="CN37" t="inlineStr">
         <is>
@@ -24442,10 +24402,10 @@
         <v>14.92000007629395</v>
       </c>
       <c r="BX38" t="n">
-        <v>9.273887965142224</v>
+        <v>9.273888006358739</v>
       </c>
       <c r="BY38" t="n">
-        <v>17.20306217533882</v>
+        <v>17.20306225179546</v>
       </c>
       <c r="BZ38" t="n">
         <v>30.98589357537536</v>
@@ -24454,23 +24414,23 @@
         <v>29.53442297696593</v>
       </c>
       <c r="CB38" t="n">
-        <v>35.04844382265731</v>
+        <v>35.04844383156657</v>
       </c>
       <c r="CC38" t="n">
-        <v>25.51038176775274</v>
+        <v>25.51038175938443</v>
       </c>
       <c r="CD38" t="n">
-        <v>15.48617146806028</v>
+        <v>15.48617141681001</v>
       </c>
       <c r="CE38" t="inlineStr"/>
       <c r="CF38" t="n">
-        <v>20.74330637090229</v>
+        <v>20.74330639822849</v>
       </c>
       <c r="CG38" t="n">
-        <v>21.35672197154578</v>
+        <v>21.35672200558994</v>
       </c>
       <c r="CH38" t="n">
-        <v>19.2210497743912</v>
+        <v>19.22104980503095</v>
       </c>
       <c r="CI38" t="n">
         <v>4</v>
@@ -24482,10 +24442,10 @@
         <v>3.3</v>
       </c>
       <c r="CL38" t="n">
-        <v>28.8274106977459</v>
+        <v>28.82741090310614</v>
       </c>
       <c r="CM38" t="n">
-        <v>39.03020284739047</v>
+        <v>39.03020303054201</v>
       </c>
       <c r="CN38" t="inlineStr">
         <is>
@@ -24494,12 +24454,12 @@
       </c>
       <c r="CO38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="CP38" t="inlineStr">
         <is>
-          <t>última</t>
+          <t>próxima</t>
         </is>
       </c>
       <c r="CQ38" t="inlineStr"/>
@@ -24524,7 +24484,7 @@
         <v>-5.269840785435265</v>
       </c>
       <c r="CZ38" t="n">
-        <v>-17.97784039185961</v>
+        <v>-17.97783150576924</v>
       </c>
       <c r="DA38" t="b">
         <v>1</v>
@@ -24750,10 +24710,10 @@
         <v>39.45000076293945</v>
       </c>
       <c r="BX39" t="n">
-        <v>20.16682100364162</v>
+        <v>20.16682114779781</v>
       </c>
       <c r="BY39" t="n">
-        <v>37.40945296175521</v>
+        <v>37.40945322916494</v>
       </c>
       <c r="BZ39" t="n">
         <v>56.0249206976364</v>
@@ -24762,23 +24722,23 @@
         <v>42.37642446456151</v>
       </c>
       <c r="CB39" t="n">
-        <v>61.80196359830609</v>
+        <v>61.80196336153472</v>
       </c>
       <c r="CC39" t="n">
-        <v>45.16906420399834</v>
+        <v>45.16906415895728</v>
       </c>
       <c r="CD39" t="n">
-        <v>31.12131450130616</v>
+        <v>31.12131421651119</v>
       </c>
       <c r="CE39" t="inlineStr"/>
       <c r="CF39" t="n">
-        <v>39.69256471675789</v>
+        <v>39.69256480838911</v>
       </c>
       <c r="CG39" t="n">
-        <v>41.28925858287677</v>
+        <v>41.28925869406111</v>
       </c>
       <c r="CH39" t="n">
-        <v>37.1603327245891</v>
+        <v>37.160332824655</v>
       </c>
       <c r="CI39" t="n">
         <v>4</v>
@@ -24790,10 +24750,10 @@
         <v>2.8</v>
       </c>
       <c r="CL39" t="n">
-        <v>-5.803974636424702</v>
+        <v>-5.803974382772226</v>
       </c>
       <c r="CM39" t="n">
-        <v>0.6148642563432061</v>
+        <v>0.6148644886149857</v>
       </c>
       <c r="CN39" t="inlineStr">
         <is>
@@ -24905,7 +24865,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -25076,10 +25036,10 @@
         <v>5.989999771118164</v>
       </c>
       <c r="BX40" t="n">
-        <v>7.105835133233375</v>
+        <v>7.105835100490797</v>
       </c>
       <c r="BY40" t="n">
-        <v>13.18132417214791</v>
+        <v>13.18132411141043</v>
       </c>
       <c r="BZ40" t="n">
         <v>5.689426305900764</v>
@@ -25100,7 +25060,7 @@
         <v>5.473701748879975</v>
       </c>
       <c r="CF40" t="n">
-        <v>7.409413556726272</v>
+        <v>7.409413545041264</v>
       </c>
       <c r="CG40" t="n">
         <v>5.911379819617049</v>
@@ -25121,7 +25081,7 @@
         <v>-11.18126809774143</v>
       </c>
       <c r="CM40" t="n">
-        <v>23.69639131627452</v>
+        <v>23.69639112119926</v>
       </c>
       <c r="CN40" t="inlineStr">
         <is>
@@ -25138,16 +25098,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ40" t="inlineStr">
-        <is>
-          <t>A CSN Mineração (CMIN3) apresenta uma notável eficiência operacional, com seu ROE de 31,8% e ROIC de 20,3% situando-se muito acima dos pares do setor de materiais (5,6% e 9,2%, respectivamente), o que evidencia uma alta qualidade no emprego do capital. Essa forte rentabilidade, contudo, convive com múltiplos de preço que dividem opiniões: enquanto o P/L de 13,95 e o P/VP de 4,43 sugerem um prêmio em relação ao valor patrimonial, o indicador PEG de 0,15 sinaliza que o preço atual está bastante atrativo quando confrontado com o robusto crescimento da empresa. O espetacular avanço histórico é confirmado pelo CAGR de receita de 5 anos de 90,7%, que supera com folga a média setorial de 17,4%, validando o excelente desempenho operacional refletido no checklist de critérios, no qual a companhia atendeu a 7 de 8 requisitos possíveis. No âmbito financeiro, a excelente rentabilidade convive com um endividamento sob controle, visto que a relação Dívida Líquida/EBITDA de 0,2 está bem abaixo da média do setor de 1,76, embora a relação Dívida/Patrimônio de 1,24 e a liquidez corrente de 1,17 exijam monitoramento. Esse balanço saudável confere sustentabilidade ao expressivo dividend yield de 18,19%, uma vez que a geração de caixa e o baixo endividamento relativo dão suporte à distribuição de proventos sem comprometer a estrutura de capital. Sob a ótica do valuation, a análise dos preços-teto revela uma dispersão acentuada entre as metodologias, variando desde os conservadores R$ 3,61 pelo modelo de Graham até os otimistas R$ 13,18 pelo modelo de Gordon, resultando em uma média de R$ 7,41 e mediana de R$ 5,91. Frente ao preço atual de R$ 5,99, o preço-teto ajustado com margem de segurança fica em R$ 5,32, o que aponta para um upside negativo de 11,2% em relação a essa métrica mais rigorosa, apesar de o papel demonstrar tendência gráfica de alta e sinal de rompimento. Em suma, os principais pontos positivos da companhia residem em seu crescimento acelerado, rentabilidade muito acima dos pares e proventos altamente generosos, ao passo que os pontos negativos concentram-se na margem líquida de 13,41% (abaixo do patamar de 15% do checklist), na liquidez corrente apertada e na ausência de margem de segurança no preço atual perante o valuation ajustado.</t>
-        </is>
-      </c>
-      <c r="CR40" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CQ40" t="inlineStr"/>
+      <c r="CR40" t="inlineStr"/>
       <c r="CS40" t="b">
         <v>0</v>
       </c>
@@ -25174,14 +25126,14 @@
         <v>1</v>
       </c>
       <c r="DB40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD40" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.7, +0.3% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25193,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -25412,37 +25364,37 @@
         <v>26.75</v>
       </c>
       <c r="BX41" t="n">
-        <v>17.10458218354911</v>
+        <v>17.10458209521638</v>
       </c>
       <c r="BY41" t="n">
-        <v>28.31127777305716</v>
+        <v>28.31127776241475</v>
       </c>
       <c r="BZ41" t="n">
-        <v>47.34414620291996</v>
+        <v>47.34414642962103</v>
       </c>
       <c r="CA41" t="n">
         <v>53.24972279891534</v>
       </c>
       <c r="CB41" t="n">
-        <v>56.30911403290522</v>
+        <v>56.30911400495602</v>
       </c>
       <c r="CC41" t="n">
-        <v>43.03538679041579</v>
+        <v>43.03538680648636</v>
       </c>
       <c r="CD41" t="n">
-        <v>23.55902945142269</v>
+        <v>23.55902955022109</v>
       </c>
       <c r="CE41" t="n">
         <v>30.7680447869919</v>
       </c>
       <c r="CF41" t="n">
-        <v>37.46016300252215</v>
+        <v>37.46016302935286</v>
       </c>
       <c r="CG41" t="n">
-        <v>36.90171578870385</v>
+        <v>36.90171579673913</v>
       </c>
       <c r="CH41" t="n">
-        <v>33.21154420983346</v>
+        <v>33.21154421706522</v>
       </c>
       <c r="CI41" t="n">
         <v>8</v>
@@ -25454,10 +25406,10 @@
         <v>3.3</v>
       </c>
       <c r="CL41" t="n">
-        <v>24.15530545732136</v>
+        <v>24.15530548435596</v>
       </c>
       <c r="CM41" t="n">
-        <v>40.0379925327931</v>
+        <v>40.0379926330948</v>
       </c>
       <c r="CN41" t="inlineStr">
         <is>
@@ -25474,16 +25426,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="CQ41" t="inlineStr">
-        <is>
-          <t>A ISA CTEEP (ISAE4) apresenta-se como uma alternativa robusta no setor de serviços públicos, combinando uma rentabilidade sólida com múltiplos de valuation que sugerem um ponto de entrada descontado. O retorno sobre o patrimônio líquido (ROE) de 12,7% situa-se acima da média setorial de 12,1%, enquanto o retorno sobre o capital investido (ROIC) de 9,6% fica ligeiramente abaixo dos pares, configurando uma operação eficiente que convive com um preço atraente, evidenciado pelo P/L de 6,68 e pelo P/VP de 0,85. Essa rentabilidade saudável é acompanhada por um endividamento sob controle, onde a relação Dívida Líquida/EBITDA de 3,41 vezes está ligeiramente acima da média do setor de 3,4 vezes, mas é amplamente mitigada por uma robusta liquidez corrente de 5,28, garantindo folga financeira no curto prazo. O dividend yield de 6,48% mostra-se coerente com a geração de caixa e a estrutura de capital da companhia, oferecendo um retorno atrativo e sustentável frente ao perfil de endividamento moderado. No quesito expansão, a empresa destaca-se com um impressionante crescimento composto anual (CAGR) de receita nos últimos cinco anos de 220,0%, patamar vastamente superior à média setorial de 37,6%, o que corrobora o cumprimento de 5 dos 8 critérios do checklist fundamentalista, penalizado apenas pelas métricas de alavancagem e pelo ROE/ROIC abaixo da taxa Selic. Sob a ótica do valuation, as estimativas de preço-teto revelam uma dispersão acentuada entre os métodos, variando desde os conservadores R$ 17,10 pelo modelo de Bazin até os otimistas R$ 56,31 pelo critério de Lynch, estabelecendo uma média de R$ 37,46 e uma mediana de R$ 36,90. Tomando como referência o preço-teto ajustado com margem de segurança de R$ 33,21, o papel, cotado atualmente a R$ 26,75, oferece um upside potencial de 24,2%, mesmo diante de uma tendência gráfica lateralizada com sinal de rompimento. Em suma, os principais prós do ativo residem no seu crescimento exponencial de receita, margem líquida elevada de 26,39% e valuation descontado, enquanto os contras concentram-se em uma alavancagem ligeiramente superior à do setor e em retornos sobre o capital que ainda não superam o custo de oportunidade da taxa básica de juros.</t>
-        </is>
-      </c>
-      <c r="CR41" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CQ41" t="inlineStr"/>
+      <c r="CR41" t="inlineStr"/>
       <c r="CS41" t="b">
         <v>0</v>
       </c>
@@ -25510,14 +25454,14 @@
         <v>1</v>
       </c>
       <c r="DB41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD41" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.8, +0.1% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -25748,37 +25692,37 @@
         <v>15.23999977111816</v>
       </c>
       <c r="BX42" t="n">
-        <v>5.91237611142607</v>
+        <v>5.912376111442303</v>
       </c>
       <c r="BY42" t="n">
-        <v>8.495852362904266</v>
+        <v>8.495852362890863</v>
       </c>
       <c r="BZ42" t="n">
-        <v>10.76554978675262</v>
+        <v>10.76554978670608</v>
       </c>
       <c r="CA42" t="n">
         <v>11.60613937821477</v>
       </c>
       <c r="CB42" t="n">
-        <v>9.765538913190749</v>
+        <v>9.765538913164574</v>
       </c>
       <c r="CC42" t="n">
-        <v>14.90925468167973</v>
+        <v>14.90925468167401</v>
       </c>
       <c r="CD42" t="n">
-        <v>5.35951293928006</v>
+        <v>5.359512939253776</v>
       </c>
       <c r="CE42" t="n">
         <v>10.95502673090989</v>
       </c>
       <c r="CF42" t="n">
-        <v>9.721156363044768</v>
+        <v>9.721156363032032</v>
       </c>
       <c r="CG42" t="n">
-        <v>10.26554434997168</v>
+        <v>10.26554434993533</v>
       </c>
       <c r="CH42" t="n">
-        <v>9.238989914974516</v>
+        <v>9.238989914941794</v>
       </c>
       <c r="CI42" t="n">
         <v>8</v>
@@ -25790,10 +25734,10 @@
         <v>2.8</v>
       </c>
       <c r="CL42" t="n">
-        <v>-39.37670568418488</v>
+        <v>-39.3767056843996</v>
       </c>
       <c r="CM42" t="n">
-        <v>-36.21288379893772</v>
+        <v>-36.2128837990213</v>
       </c>
       <c r="CN42" t="inlineStr">
         <is>
@@ -26076,10 +26020,10 @@
         <v>9.069999694824219</v>
       </c>
       <c r="BX43" t="n">
-        <v>2.47271310469086</v>
+        <v>2.47271308823114</v>
       </c>
       <c r="BY43" t="n">
-        <v>4.586882809201544</v>
+        <v>4.586882778668765</v>
       </c>
       <c r="BZ43" t="n">
         <v>13.27928132115148</v>
@@ -26088,19 +26032,19 @@
         <v>14.99179191951746</v>
       </c>
       <c r="CB43" t="n">
-        <v>10.39861290843145</v>
+        <v>10.3986129060586</v>
       </c>
       <c r="CC43" t="n">
-        <v>7.310629035758283</v>
+        <v>7.310629037338892</v>
       </c>
       <c r="CD43" t="n">
-        <v>6.809197049060717</v>
+        <v>6.809197063574238</v>
       </c>
       <c r="CE43" t="n">
         <v>10.09419599164711</v>
       </c>
       <c r="CF43" t="n">
-        <v>9.63865586210972</v>
+        <v>9.638655859708079</v>
       </c>
       <c r="CG43" t="n">
         <v>10.09419599164711</v>
@@ -26121,7 +26065,7 @@
         <v>0.1629183920107025</v>
       </c>
       <c r="CM43" t="n">
-        <v>6.269638218510676</v>
+        <v>6.269638192031723</v>
       </c>
       <c r="CN43" t="inlineStr">
         <is>
@@ -26156,7 +26100,7 @@
         <v>-2.473123561220814</v>
       </c>
       <c r="CZ43" t="n">
-        <v>-36.49822149343045</v>
+        <v>-36.49822591325916</v>
       </c>
       <c r="DA43" t="b">
         <v>0</v>
@@ -26400,10 +26344,10 @@
         <v>11.55000019073486</v>
       </c>
       <c r="BX44" t="n">
-        <v>4.694665717083731</v>
+        <v>4.694665724427018</v>
       </c>
       <c r="BY44" t="n">
-        <v>8.708604905190318</v>
+        <v>8.708604918812117</v>
       </c>
       <c r="BZ44" t="n">
         <v>25.37935365294144</v>
@@ -26412,25 +26356,25 @@
         <v>28.56601611649146</v>
       </c>
       <c r="CB44" t="n">
-        <v>23.67014402516682</v>
+        <v>23.6701440317811</v>
       </c>
       <c r="CC44" t="n">
-        <v>14.17110276561749</v>
+        <v>14.17110276489373</v>
       </c>
       <c r="CD44" t="n">
-        <v>13.14403830064227</v>
+        <v>13.14403829408324</v>
       </c>
       <c r="CE44" t="n">
         <v>4.831418303116641</v>
       </c>
       <c r="CF44" t="n">
-        <v>18.93987662767497</v>
+        <v>18.93987662983385</v>
       </c>
       <c r="CG44" t="n">
-        <v>18.92062339539216</v>
+        <v>18.92062339833742</v>
       </c>
       <c r="CH44" t="n">
-        <v>17.02856105585294</v>
+        <v>17.02856105850367</v>
       </c>
       <c r="CI44" t="n">
         <v>6</v>
@@ -26442,10 +26386,10 @@
         <v>6.1</v>
       </c>
       <c r="CL44" t="n">
-        <v>47.43342662031165</v>
+        <v>47.43342664326171</v>
       </c>
       <c r="CM44" t="n">
-        <v>63.98161311605939</v>
+        <v>63.98161313475104</v>
       </c>
       <c r="CN44" t="inlineStr">
         <is>
@@ -26480,7 +26424,7 @@
         <v>-1.785714575338404</v>
       </c>
       <c r="CZ44" t="n">
-        <v>-29.75957896167223</v>
+        <v>-29.7595744927601</v>
       </c>
       <c r="DA44" t="b">
         <v>0</v>
@@ -26724,37 +26668,37 @@
         <v>38.93999862670898</v>
       </c>
       <c r="BX45" t="n">
-        <v>31.03837521548671</v>
+        <v>31.03837540531581</v>
       </c>
       <c r="BY45" t="n">
-        <v>35.59923868699851</v>
+        <v>35.59923853946942</v>
       </c>
       <c r="BZ45" t="n">
-        <v>38.66835340589296</v>
+        <v>38.66835300915131</v>
       </c>
       <c r="CA45" t="n">
         <v>49.91213791285566</v>
       </c>
       <c r="CB45" t="n">
-        <v>60.21617607377523</v>
+        <v>60.21617586066733</v>
       </c>
       <c r="CC45" t="n">
-        <v>16.76375509231805</v>
+        <v>16.76375507360725</v>
       </c>
       <c r="CD45" t="n">
-        <v>17.35171000040723</v>
+        <v>17.35170966396933</v>
       </c>
       <c r="CE45" t="n">
         <v>28.46736944905749</v>
       </c>
       <c r="CF45" t="n">
-        <v>34.75213947959898</v>
+        <v>34.7521393642617</v>
       </c>
       <c r="CG45" t="n">
-        <v>33.31880695124261</v>
+        <v>33.31880697239261</v>
       </c>
       <c r="CH45" t="n">
-        <v>29.98692625611835</v>
+        <v>29.98692627515335</v>
       </c>
       <c r="CI45" t="n">
         <v>8</v>
@@ -26766,10 +26710,10 @@
         <v>3.6</v>
       </c>
       <c r="CL45" t="n">
-        <v>-22.99196889146707</v>
+        <v>-22.99196884258416</v>
       </c>
       <c r="CM45" t="n">
-        <v>-10.75464636569747</v>
+        <v>-10.75464666188978</v>
       </c>
       <c r="CN45" t="inlineStr">
         <is>
@@ -27052,10 +26996,10 @@
         <v>33.61000061035156</v>
       </c>
       <c r="BX46" t="n">
-        <v>14.55544935139097</v>
+        <v>14.55544937649831</v>
       </c>
       <c r="BY46" t="n">
-        <v>27.00035854683025</v>
+        <v>27.00035859340436</v>
       </c>
       <c r="BZ46" t="n">
         <v>55.87609888170114</v>
@@ -27064,25 +27008,25 @@
         <v>43.18496416127684</v>
       </c>
       <c r="CB46" t="n">
-        <v>72.40109792154674</v>
+        <v>72.40109789011203</v>
       </c>
       <c r="CC46" t="n">
-        <v>38.4780588530453</v>
+        <v>38.47805884684188</v>
       </c>
       <c r="CD46" t="n">
-        <v>40.7035854683759</v>
+        <v>40.70358542089492</v>
       </c>
       <c r="CE46" t="n">
         <v>21.4898661708766</v>
       </c>
       <c r="CF46" t="n">
-        <v>42.73343285766468</v>
+        <v>42.73343285215825</v>
       </c>
       <c r="CG46" t="n">
-        <v>40.7035854683759</v>
+        <v>40.70358542089492</v>
       </c>
       <c r="CH46" t="n">
-        <v>36.63322692153831</v>
+        <v>36.63322687880542</v>
       </c>
       <c r="CI46" t="n">
         <v>7</v>
@@ -27094,10 +27038,10 @@
         <v>5</v>
       </c>
       <c r="CL46" t="n">
-        <v>8.995020102009832</v>
+        <v>8.995019974866448</v>
       </c>
       <c r="CM46" t="n">
-        <v>27.14499280462132</v>
+        <v>27.14499278823803</v>
       </c>
       <c r="CN46" t="inlineStr">
         <is>
@@ -27374,10 +27318,10 @@
         <v>6.519999980926514</v>
       </c>
       <c r="BX47" t="n">
-        <v>7.744252197708739</v>
+        <v>7.744252281669737</v>
       </c>
       <c r="BY47" t="n">
-        <v>11.27563119986392</v>
+        <v>11.27563132211114</v>
       </c>
       <c r="BZ47" t="n">
         <v>8.091646754371807</v>
@@ -27396,7 +27340,7 @@
         <v>5.352910135320273</v>
       </c>
       <c r="CF47" t="n">
-        <v>8.377257543391584</v>
+        <v>8.37725757775962</v>
       </c>
       <c r="CG47" t="n">
         <v>8.45165789549799</v>
@@ -27417,7 +27361,7 @@
         <v>16.66398969632026</v>
       </c>
       <c r="CM47" t="n">
-        <v>28.48554551991192</v>
+        <v>28.48554604702904</v>
       </c>
       <c r="CN47" t="inlineStr">
         <is>
@@ -27600,7 +27544,7 @@
         <v>1</v>
       </c>
       <c r="AT48" t="n">
-        <v>185049546752</v>
+        <v>184726978560</v>
       </c>
       <c r="AU48" t="n">
         <v>7.27</v>
@@ -27678,35 +27622,35 @@
         <v>16.98999977111816</v>
       </c>
       <c r="BX48" t="n">
-        <v>10.11113308174126</v>
+        <v>10.11113315030665</v>
       </c>
       <c r="BY48" t="n">
-        <v>17.73003376642088</v>
+        <v>17.73003375481931</v>
       </c>
       <c r="BZ48" t="n">
-        <v>29.27120913360595</v>
+        <v>29.27120891595919</v>
       </c>
       <c r="CA48" t="n">
         <v>29.45091649314749</v>
       </c>
       <c r="CB48" t="n">
-        <v>32.49121842356977</v>
+        <v>32.4912184199716</v>
       </c>
       <c r="CC48" t="n">
-        <v>27.89684498813715</v>
+        <v>27.89684497280067</v>
       </c>
       <c r="CD48" t="n">
-        <v>14.42712306578498</v>
+        <v>14.42712298052803</v>
       </c>
       <c r="CE48" t="inlineStr"/>
       <c r="CF48" t="n">
-        <v>21.25230524247631</v>
+        <v>21.25230519847145</v>
       </c>
       <c r="CG48" t="n">
-        <v>22.81343937727902</v>
+        <v>22.81343936380999</v>
       </c>
       <c r="CH48" t="n">
-        <v>20.53209543955112</v>
+        <v>20.53209542742899</v>
       </c>
       <c r="CI48" t="n">
         <v>4</v>
@@ -27718,10 +27662,10 @@
         <v>2.9</v>
       </c>
       <c r="CL48" t="n">
-        <v>20.84812075427025</v>
+        <v>20.84812068292166</v>
       </c>
       <c r="CM48" t="n">
-        <v>25.08714260610983</v>
+        <v>25.08714234710536</v>
       </c>
       <c r="CN48" t="inlineStr">
         <is>
@@ -27730,12 +27674,12 @@
       </c>
       <c r="CO48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="CP48" t="inlineStr">
         <is>
-          <t>última</t>
+          <t>próxima</t>
         </is>
       </c>
       <c r="CQ48" t="inlineStr"/>
@@ -27760,7 +27704,7 @@
         <v>-5.872573466739961</v>
       </c>
       <c r="CZ48" t="n">
-        <v>-20.0055653732595</v>
+        <v>-20.00555804362784</v>
       </c>
       <c r="DA48" t="b">
         <v>1</v>
@@ -27908,7 +27852,7 @@
         <v>1</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AS49" t="b">
         <v>1</v>
@@ -28004,10 +27948,10 @@
         <v>12.81999969482422</v>
       </c>
       <c r="BX49" t="n">
-        <v>1.578656294304152</v>
+        <v>1.57865629603639</v>
       </c>
       <c r="BY49" t="n">
-        <v>2.928407425934202</v>
+        <v>2.928407429147504</v>
       </c>
       <c r="BZ49" t="n">
         <v>12.71444580512132</v>
@@ -28016,7 +27960,7 @@
         <v>9.285889869344075</v>
       </c>
       <c r="CB49" t="n">
-        <v>16.04799278013633</v>
+        <v>16.04799278195155</v>
       </c>
       <c r="CC49" t="n">
         <v>6.104046666666666</v>
@@ -28147,7 +28091,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -28318,10 +28262,10 @@
         <v>32.79999923706055</v>
       </c>
       <c r="BX50" t="n">
-        <v>11.14562480779221</v>
+        <v>11.14562479332949</v>
       </c>
       <c r="BY50" t="n">
-        <v>20.67513401845454</v>
+        <v>20.6751339916262</v>
       </c>
       <c r="BZ50" t="n">
         <v>55.71794742192976</v>
@@ -28330,19 +28274,19 @@
         <v>52.6391393544375</v>
       </c>
       <c r="CB50" t="n">
-        <v>58.03633792387857</v>
+        <v>58.03633792703619</v>
       </c>
       <c r="CC50" t="n">
-        <v>28.35849379265688</v>
+        <v>28.35849375765919</v>
       </c>
       <c r="CD50" t="n">
-        <v>35.13913214506493</v>
+        <v>35.13913216336663</v>
       </c>
       <c r="CE50" t="n">
         <v>54.26380819457677</v>
       </c>
       <c r="CF50" t="n">
-        <v>43.54714183585698</v>
+        <v>43.54714183009032</v>
       </c>
       <c r="CG50" t="n">
         <v>52.6391393544375</v>
@@ -28363,7 +28307,7 @@
         <v>44.43666622243312</v>
       </c>
       <c r="CM50" t="n">
-        <v>32.76567941700832</v>
+        <v>32.76567939942703</v>
       </c>
       <c r="CN50" t="inlineStr">
         <is>
@@ -28377,11 +28321,7 @@
       </c>
       <c r="CP50" t="inlineStr"/>
       <c r="CQ50" t="inlineStr"/>
-      <c r="CR50" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CR50" t="inlineStr"/>
       <c r="CS50" t="b">
         <v>0</v>
       </c>
@@ -28402,20 +28342,20 @@
         <v>0.4286570431797809</v>
       </c>
       <c r="CZ50" t="n">
-        <v>-10.44671436519931</v>
+        <v>-10.44672380417929</v>
       </c>
       <c r="DA50" t="b">
         <v>0</v>
       </c>
       <c r="DB50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC50" t="b">
         <v>0</v>
       </c>
       <c r="DD50" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.2, +0.4% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -28646,37 +28586,37 @@
         <v>44.54999923706055</v>
       </c>
       <c r="BX51" t="n">
-        <v>32.31239190591139</v>
+        <v>32.31239167628136</v>
       </c>
       <c r="BY51" t="n">
-        <v>44.51496102618957</v>
+        <v>44.51496147025176</v>
       </c>
       <c r="BZ51" t="n">
-        <v>51.2732020618559</v>
+        <v>51.27320293771162</v>
       </c>
       <c r="CA51" t="n">
         <v>48.07305068505902</v>
       </c>
       <c r="CB51" t="n">
-        <v>71.06107536662033</v>
+        <v>71.06107584029496</v>
       </c>
       <c r="CC51" t="n">
-        <v>59.89309458293646</v>
+        <v>59.89309467731584</v>
       </c>
       <c r="CD51" t="n">
-        <v>25.32931160603421</v>
+        <v>25.32931214011691</v>
       </c>
       <c r="CE51" t="n">
         <v>77.11023262183943</v>
       </c>
       <c r="CF51" t="n">
-        <v>51.19591498205578</v>
+        <v>51.19591525610886</v>
       </c>
       <c r="CG51" t="n">
-        <v>49.67312637345746</v>
+        <v>49.67312681138532</v>
       </c>
       <c r="CH51" t="n">
-        <v>44.70581373611172</v>
+        <v>44.70581413024679</v>
       </c>
       <c r="CI51" t="n">
         <v>8</v>
@@ -28688,10 +28628,10 @@
         <v>3</v>
       </c>
       <c r="CL51" t="n">
-        <v>0.3497519679451555</v>
+        <v>0.349752852647911</v>
       </c>
       <c r="CM51" t="n">
-        <v>14.91788071562208</v>
+        <v>14.91788133078051</v>
       </c>
       <c r="CN51" t="inlineStr">
         <is>
@@ -28884,7 +28824,7 @@
         <v>1</v>
       </c>
       <c r="AT52" t="n">
-        <v>3043409408</v>
+        <v>3038503936</v>
       </c>
       <c r="AU52" t="n">
         <v>6.1</v>
@@ -28974,37 +28914,37 @@
         <v>10.36999988555908</v>
       </c>
       <c r="BX52" t="n">
-        <v>7.933673939371957</v>
+        <v>7.933673917337638</v>
       </c>
       <c r="BY52" t="n">
-        <v>11.42997362507514</v>
+        <v>11.42997361870822</v>
       </c>
       <c r="BZ52" t="n">
-        <v>17.49410631251846</v>
+        <v>17.49410635136024</v>
       </c>
       <c r="CA52" t="n">
         <v>23.9762107715994</v>
       </c>
       <c r="CB52" t="n">
-        <v>24.84378818272859</v>
+        <v>24.84378816689292</v>
       </c>
       <c r="CC52" t="n">
-        <v>21.06869220024945</v>
+        <v>21.06869220439255</v>
       </c>
       <c r="CD52" t="n">
-        <v>8.712223841196193</v>
+        <v>8.712223863029559</v>
       </c>
       <c r="CE52" t="n">
         <v>10.0158971835899</v>
       </c>
       <c r="CF52" t="n">
-        <v>15.68432075704114</v>
+        <v>15.6843207596138</v>
       </c>
       <c r="CG52" t="n">
-        <v>14.46203996879681</v>
+        <v>14.46203998503423</v>
       </c>
       <c r="CH52" t="n">
-        <v>13.01583597191713</v>
+        <v>13.01583598653081</v>
       </c>
       <c r="CI52" t="n">
         <v>8</v>
@@ -29016,10 +28956,10 @@
         <v>3.1</v>
       </c>
       <c r="CL52" t="n">
-        <v>25.51433091183104</v>
+        <v>25.51433105275371</v>
       </c>
       <c r="CM52" t="n">
-        <v>51.24706779295729</v>
+        <v>51.247067817766</v>
       </c>
       <c r="CN52" t="inlineStr">
         <is>
@@ -29280,10 +29220,10 @@
         <v>54.06999969482422</v>
       </c>
       <c r="BX53" t="n">
-        <v>10.57163146182461</v>
+        <v>10.57163144128664</v>
       </c>
       <c r="BY53" t="n">
-        <v>19.61037636168465</v>
+        <v>19.61037632358672</v>
       </c>
       <c r="BZ53" t="n">
         <v>61.97469688204333</v>
@@ -29292,7 +29232,7 @@
         <v>46.42658566900867</v>
       </c>
       <c r="CB53" t="n">
-        <v>82.96304808718925</v>
+        <v>82.9630480623163</v>
       </c>
       <c r="CC53" t="n">
         <v>11.76833333333333</v>
@@ -29302,7 +29242,7 @@
       </c>
       <c r="CE53" t="inlineStr"/>
       <c r="CF53" t="n">
-        <v>13.98344705228086</v>
+        <v>13.98344703273557</v>
       </c>
       <c r="CG53" t="n">
         <v>11.76833333333333</v>
@@ -29323,7 +29263,7 @@
         <v>-80.41150349587693</v>
       </c>
       <c r="CM53" t="n">
-        <v>-74.13825202292462</v>
+        <v>-74.13825205907276</v>
       </c>
       <c r="CN53" t="inlineStr">
         <is>
@@ -29588,10 +29528,10 @@
         <v>29.72999954223633</v>
       </c>
       <c r="BX54" t="n">
-        <v>15.54095035446847</v>
+        <v>15.54095033515084</v>
       </c>
       <c r="BY54" t="n">
-        <v>28.82846290753902</v>
+        <v>28.82846287170481</v>
       </c>
       <c r="BZ54" t="n">
         <v>54.78755131218794</v>
@@ -29600,23 +29540,23 @@
         <v>49.47462312565243</v>
       </c>
       <c r="CB54" t="n">
-        <v>61.00002213430175</v>
+        <v>61.00002213912055</v>
       </c>
       <c r="CC54" t="n">
-        <v>36.6350403106921</v>
+        <v>36.63504031419151</v>
       </c>
       <c r="CD54" t="n">
-        <v>30.36807371041787</v>
+        <v>30.36807373709011</v>
       </c>
       <c r="CE54" t="inlineStr"/>
       <c r="CF54" t="n">
-        <v>33.94800122122189</v>
+        <v>33.94800120830877</v>
       </c>
       <c r="CG54" t="n">
-        <v>32.73175160911556</v>
+        <v>32.73175159294816</v>
       </c>
       <c r="CH54" t="n">
-        <v>29.45857644820401</v>
+        <v>29.45857643365334</v>
       </c>
       <c r="CI54" t="n">
         <v>4</v>
@@ -29628,10 +29568,10 @@
         <v>3.5</v>
       </c>
       <c r="CL54" t="n">
-        <v>-0.9129603034359945</v>
+        <v>-0.9129603523787</v>
       </c>
       <c r="CM54" t="n">
-        <v>14.18769506872408</v>
+        <v>14.18769502528947</v>
       </c>
       <c r="CN54" t="inlineStr">
         <is>
@@ -29832,7 +29772,7 @@
         <v>1</v>
       </c>
       <c r="AT55" t="n">
-        <v>35655647232</v>
+        <v>35602051072</v>
       </c>
       <c r="AU55" t="n">
         <v>10.8</v>
@@ -29922,10 +29862,10 @@
         <v>33.45999908447266</v>
       </c>
       <c r="BX55" t="n">
-        <v>11.82529268830603</v>
+        <v>11.82529267884127</v>
       </c>
       <c r="BY55" t="n">
-        <v>21.93591793680769</v>
+        <v>21.93591791925056</v>
       </c>
       <c r="BZ55" t="n">
         <v>41.05046183974654</v>
@@ -29934,25 +29874,25 @@
         <v>33.4867992482282</v>
       </c>
       <c r="CB55" t="n">
-        <v>43.09926953949515</v>
+        <v>43.09926955273355</v>
       </c>
       <c r="CC55" t="n">
-        <v>23.86613729664683</v>
+        <v>23.86613729845012</v>
       </c>
       <c r="CD55" t="n">
-        <v>25.73202700789414</v>
+        <v>25.73202702392744</v>
       </c>
       <c r="CE55" t="n">
         <v>27.05001202269726</v>
       </c>
       <c r="CF55" t="n">
-        <v>28.50573969747773</v>
+        <v>28.50573969798437</v>
       </c>
       <c r="CG55" t="n">
-        <v>26.3910195152957</v>
+        <v>26.39101952331235</v>
       </c>
       <c r="CH55" t="n">
-        <v>23.75191756376613</v>
+        <v>23.75191757098112</v>
       </c>
       <c r="CI55" t="n">
         <v>8</v>
@@ -29964,10 +29904,10 @@
         <v>3.6</v>
       </c>
       <c r="CL55" t="n">
-        <v>-29.01399218869562</v>
+        <v>-29.01399216713261</v>
       </c>
       <c r="CM55" t="n">
-        <v>-14.80651381516022</v>
+        <v>-14.80651381364606</v>
       </c>
       <c r="CN55" t="inlineStr">
         <is>
@@ -30244,10 +30184,10 @@
         <v>10.5</v>
       </c>
       <c r="BX56" t="n">
-        <v>13.07484801560446</v>
+        <v>13.07484804592508</v>
       </c>
       <c r="BY56" t="n">
-        <v>19.0369787107201</v>
+        <v>19.03697875486692</v>
       </c>
       <c r="BZ56" t="n">
         <v>16.69724770642202</v>
@@ -30266,7 +30206,7 @@
         <v>14.75038161497534</v>
       </c>
       <c r="CF56" t="n">
-        <v>16.14617478847187</v>
+        <v>16.14617480088311</v>
       </c>
       <c r="CG56" t="n">
         <v>15.72381466069868</v>
@@ -30287,7 +30227,7 @@
         <v>34.77555423456013</v>
       </c>
       <c r="CM56" t="n">
-        <v>53.77309322354162</v>
+        <v>53.77309334174394</v>
       </c>
       <c r="CN56" t="inlineStr">
         <is>
@@ -30568,10 +30508,10 @@
         <v>4.599999904632568</v>
       </c>
       <c r="BX57" t="n">
-        <v>1.064239851735974</v>
+        <v>1.064239848680438</v>
       </c>
       <c r="BY57" t="n">
-        <v>1.974164924970232</v>
+        <v>1.974164919302213</v>
       </c>
       <c r="BZ57" t="n">
         <v>9.348159315395939</v>
@@ -30580,13 +30520,13 @@
         <v>8.767251826804014</v>
       </c>
       <c r="CB57" t="n">
-        <v>10.36596239190162</v>
+        <v>10.36596239155195</v>
       </c>
       <c r="CC57" t="n">
-        <v>4.222542560511426</v>
+        <v>4.22254256084497</v>
       </c>
       <c r="CD57" t="n">
-        <v>6.964100623325302</v>
+        <v>6.964100627229543</v>
       </c>
       <c r="CE57" t="n">
         <v>6.821405062665426</v>
@@ -30878,10 +30818,10 @@
         <v>24.5</v>
       </c>
       <c r="BX58" t="n">
-        <v>4.295923689298731</v>
+        <v>4.295923685323245</v>
       </c>
       <c r="BY58" t="n">
-        <v>7.968938443649145</v>
+        <v>7.968938436274618</v>
       </c>
       <c r="BZ58" t="n">
         <v>28.52592267135324</v>
@@ -30890,13 +30830,13 @@
         <v>28.41368392333003</v>
       </c>
       <c r="CB58" t="n">
-        <v>25.34548129704991</v>
+        <v>25.34548129935558</v>
       </c>
       <c r="CC58" t="n">
-        <v>2.969803055905918</v>
+        <v>2.969803055996728</v>
       </c>
       <c r="CD58" t="n">
-        <v>18.36078383435954</v>
+        <v>18.36078383888301</v>
       </c>
       <c r="CE58" t="n">
         <v>18.35697948459546</v>
@@ -31021,7 +30961,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Fundo duplo</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -31096,7 +31036,7 @@
         <v>1</v>
       </c>
       <c r="AR59" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="AS59" t="b">
         <v>1</v>
@@ -31192,10 +31132,10 @@
         <v>50.41999816894531</v>
       </c>
       <c r="BX59" t="n">
-        <v>8.391674390140382</v>
+        <v>8.391674400054772</v>
       </c>
       <c r="BY59" t="n">
-        <v>15.56655599371041</v>
+        <v>15.5665560121016</v>
       </c>
       <c r="BZ59" t="n">
         <v>19.74187280551197</v>
@@ -31204,25 +31144,25 @@
         <v>12.27389712793427</v>
       </c>
       <c r="CB59" t="n">
-        <v>13.92105407197445</v>
+        <v>13.92105403004959</v>
       </c>
       <c r="CC59" t="n">
-        <v>20.60989270840991</v>
+        <v>20.60989270246049</v>
       </c>
       <c r="CD59" t="n">
-        <v>10.54844685253013</v>
+        <v>10.54844682359915</v>
       </c>
       <c r="CE59" t="n">
         <v>13.14508072860394</v>
       </c>
       <c r="CF59" t="n">
-        <v>14.27480933485193</v>
+        <v>14.27480932878947</v>
       </c>
       <c r="CG59" t="n">
-        <v>13.5330674002892</v>
+        <v>13.53306737932677</v>
       </c>
       <c r="CH59" t="n">
-        <v>12.17976066026028</v>
+        <v>12.17976064139409</v>
       </c>
       <c r="CI59" t="n">
         <v>8</v>
@@ -31234,10 +31174,10 @@
         <v>2.5</v>
       </c>
       <c r="CL59" t="n">
-        <v>-75.84339329119207</v>
+        <v>-75.84339332861015</v>
       </c>
       <c r="CM59" t="n">
-        <v>-71.6881994183727</v>
+        <v>-71.68819943039662</v>
       </c>
       <c r="CN59" t="inlineStr">
         <is>
@@ -31261,7 +31201,7 @@
       </c>
       <c r="CR59" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Fundo duplo</t>
         </is>
       </c>
       <c r="CS59" t="b">
@@ -31288,7 +31228,7 @@
         <v>1.694224096144525</v>
       </c>
       <c r="CZ59" t="n">
-        <v>-7.120509036312395</v>
+        <v>-7.120502370201887</v>
       </c>
       <c r="DA59" t="b">
         <v>0</v>
@@ -31301,7 +31241,7 @@
       </c>
       <c r="DD59" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.0, +1.7% do topo, MM50&gt;MM200)</t>
+          <t>Fundo duplo — rompeu pescoço ~R$46.91 (candidato)</t>
         </is>
       </c>
     </row>
@@ -31361,7 +31301,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -31532,37 +31472,37 @@
         <v>24.17000007629395</v>
       </c>
       <c r="BX60" t="n">
-        <v>10.67724125962993</v>
+        <v>10.67724121358226</v>
       </c>
       <c r="BY60" t="n">
-        <v>14.53335823475097</v>
+        <v>14.53335826050759</v>
       </c>
       <c r="BZ60" t="n">
-        <v>18.1322015235521</v>
+        <v>18.13220163388538</v>
       </c>
       <c r="CA60" t="n">
         <v>21.47108887742095</v>
       </c>
       <c r="CB60" t="n">
-        <v>17.81559346610634</v>
+        <v>17.81559352576355</v>
       </c>
       <c r="CC60" t="n">
-        <v>23.23162604167893</v>
+        <v>23.23162605486268</v>
       </c>
       <c r="CD60" t="n">
-        <v>8.930526252697762</v>
+        <v>8.930526321463516</v>
       </c>
       <c r="CE60" t="n">
         <v>18.85377868281656</v>
       </c>
       <c r="CF60" t="n">
-        <v>16.70567679233169</v>
+        <v>16.70567682128781</v>
       </c>
       <c r="CG60" t="n">
-        <v>17.97389749482922</v>
+        <v>17.97389757982446</v>
       </c>
       <c r="CH60" t="n">
-        <v>16.1765077453463</v>
+        <v>16.17650782184202</v>
       </c>
       <c r="CI60" t="n">
         <v>8</v>
@@ -31574,10 +31514,10 @@
         <v>2.6</v>
       </c>
       <c r="CL60" t="n">
-        <v>-33.07195823630843</v>
+        <v>-33.07195791981808</v>
       </c>
       <c r="CM60" t="n">
-        <v>-30.88259520231982</v>
+        <v>-30.88259508251794</v>
       </c>
       <c r="CN60" t="inlineStr">
         <is>
@@ -31591,11 +31531,7 @@
       </c>
       <c r="CP60" t="inlineStr"/>
       <c r="CQ60" t="inlineStr"/>
-      <c r="CR60" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CR60" t="inlineStr"/>
       <c r="CS60" t="b">
         <v>0</v>
       </c>
@@ -31622,14 +31558,14 @@
         <v>0</v>
       </c>
       <c r="DB60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC60" t="b">
         <v>0</v>
       </c>
       <c r="DD60" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.0, +1.6% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -31860,10 +31796,10 @@
         <v>4.510000228881836</v>
       </c>
       <c r="BX61" t="n">
-        <v>2.928816044979391</v>
+        <v>2.928816049792685</v>
       </c>
       <c r="BY61" t="n">
-        <v>5.43295376343677</v>
+        <v>5.432953772365431</v>
       </c>
       <c r="BZ61" t="n">
         <v>13.13351715004051</v>
@@ -31872,13 +31808,13 @@
         <v>14.62895135179874</v>
       </c>
       <c r="CB61" t="n">
-        <v>14.98621651567374</v>
+        <v>14.98621652355658</v>
       </c>
       <c r="CC61" t="n">
-        <v>9.454733740128365</v>
+        <v>9.454733739505164</v>
       </c>
       <c r="CD61" t="n">
-        <v>6.403327803866501</v>
+        <v>6.403327799512203</v>
       </c>
       <c r="CE61" t="n">
         <v>1.460620462698704</v>
@@ -32174,37 +32110,37 @@
         <v>29.95047378540039</v>
       </c>
       <c r="BX62" t="n">
-        <v>13.84398575050471</v>
+        <v>13.84398566936791</v>
       </c>
       <c r="BY62" t="n">
-        <v>14.4161023441029</v>
+        <v>14.4161023274386</v>
       </c>
       <c r="BZ62" t="n">
-        <v>15.15461960558265</v>
+        <v>15.15461967688281</v>
       </c>
       <c r="CA62" t="n">
         <v>30.45828393213042</v>
       </c>
       <c r="CB62" t="n">
-        <v>14.18260470552558</v>
+        <v>14.18260474241191</v>
       </c>
       <c r="CC62" t="n">
-        <v>30.4537554605715</v>
+        <v>30.45375547755177</v>
       </c>
       <c r="CD62" t="n">
-        <v>6.070118658010612</v>
+        <v>6.070118729767992</v>
       </c>
       <c r="CE62" t="n">
         <v>37.49851027622562</v>
       </c>
       <c r="CF62" t="n">
-        <v>17.7970672080612</v>
+        <v>17.79706722222164</v>
       </c>
       <c r="CG62" t="n">
-        <v>14.4161023441029</v>
+        <v>14.4161023274386</v>
       </c>
       <c r="CH62" t="n">
-        <v>12.97449210969261</v>
+        <v>12.97449209469474</v>
       </c>
       <c r="CI62" t="n">
         <v>7</v>
@@ -32216,10 +32152,10 @@
         <v>6.2</v>
       </c>
       <c r="CL62" t="n">
-        <v>-56.68017740668551</v>
+        <v>-56.68017745676107</v>
       </c>
       <c r="CM62" t="n">
-        <v>-40.57834498519176</v>
+        <v>-40.57834493791225</v>
       </c>
       <c r="CN62" t="inlineStr">
         <is>
@@ -32498,35 +32434,35 @@
         <v>3.450000047683716</v>
       </c>
       <c r="BX63" t="n">
-        <v>2.648221204245976</v>
+        <v>2.648221199954213</v>
       </c>
       <c r="BY63" t="n">
-        <v>3.082676102941298</v>
+        <v>3.082676101534628</v>
       </c>
       <c r="BZ63" t="n">
-        <v>3.774427695418057</v>
+        <v>3.774427699812648</v>
       </c>
       <c r="CA63" t="n">
         <v>6.947717221214344</v>
       </c>
       <c r="CB63" t="n">
-        <v>5.677819680976434</v>
+        <v>5.677819678844693</v>
       </c>
       <c r="CC63" t="n">
-        <v>8.480104652946714</v>
+        <v>8.480104654006702</v>
       </c>
       <c r="CD63" t="n">
-        <v>1.71524182033807</v>
+        <v>1.715241823967528</v>
       </c>
       <c r="CE63" t="inlineStr"/>
       <c r="CF63" t="n">
-        <v>4.61802976829727</v>
+        <v>4.618029768476394</v>
       </c>
       <c r="CG63" t="n">
-        <v>3.774427695418057</v>
+        <v>3.774427699812648</v>
       </c>
       <c r="CH63" t="n">
-        <v>3.396984925876251</v>
+        <v>3.396984929831383</v>
       </c>
       <c r="CI63" t="n">
         <v>7</v>
@@ -32538,10 +32474,10 @@
         <v>4.9</v>
       </c>
       <c r="CL63" t="n">
-        <v>-1.536670176078925</v>
+        <v>-1.53667006143744</v>
       </c>
       <c r="CM63" t="n">
-        <v>33.85593346289237</v>
+        <v>33.8559334680844</v>
       </c>
       <c r="CN63" t="inlineStr">
         <is>
@@ -32820,37 +32756,37 @@
         <v>18.65999984741211</v>
       </c>
       <c r="BX64" t="n">
-        <v>8.753833598067141</v>
+        <v>8.753833593338662</v>
       </c>
       <c r="BY64" t="n">
-        <v>9.216135788133215</v>
+        <v>9.216135788373666</v>
       </c>
       <c r="BZ64" t="n">
-        <v>9.677566761480378</v>
+        <v>9.677566766960314</v>
       </c>
       <c r="CA64" t="n">
         <v>16.95274264519251</v>
       </c>
       <c r="CB64" t="n">
-        <v>9.24965515422797</v>
+        <v>9.249655158268371</v>
       </c>
       <c r="CC64" t="n">
-        <v>17.54241683712353</v>
+        <v>17.54241683828941</v>
       </c>
       <c r="CD64" t="n">
-        <v>3.939249717688818</v>
+        <v>3.939249723098197</v>
       </c>
       <c r="CE64" t="n">
         <v>16.17967221207829</v>
       </c>
       <c r="CF64" t="n">
-        <v>11.43890908924898</v>
+        <v>11.43890909069993</v>
       </c>
       <c r="CG64" t="n">
-        <v>9.463610957854174</v>
+        <v>9.463610962614343</v>
       </c>
       <c r="CH64" t="n">
-        <v>8.517249862068757</v>
+        <v>8.517249866352909</v>
       </c>
       <c r="CI64" t="n">
         <v>8</v>
@@ -32862,10 +32798,10 @@
         <v>4.5</v>
       </c>
       <c r="CL64" t="n">
-        <v>-54.35557378501272</v>
+        <v>-54.35557376205371</v>
       </c>
       <c r="CM64" t="n">
-        <v>-38.69823589073928</v>
+        <v>-38.69823588296358</v>
       </c>
       <c r="CN64" t="inlineStr">
         <is>
@@ -33126,10 +33062,10 @@
         <v>13.01000022888184</v>
       </c>
       <c r="BX65" t="n">
-        <v>11.00193368232698</v>
+        <v>11.00193371514201</v>
       </c>
       <c r="BY65" t="n">
-        <v>16.01881544146808</v>
+        <v>16.01881548924677</v>
       </c>
       <c r="BZ65" t="n">
         <v>15.8065423341555</v>
@@ -33146,13 +33082,13 @@
       </c>
       <c r="CE65" t="inlineStr"/>
       <c r="CF65" t="n">
-        <v>12.54015619782098</v>
+        <v>12.5401562179694</v>
       </c>
       <c r="CG65" t="n">
-        <v>13.40423800824124</v>
+        <v>13.40423802464876</v>
       </c>
       <c r="CH65" t="n">
-        <v>12.06381420741712</v>
+        <v>12.06381422218388</v>
       </c>
       <c r="CI65" t="n">
         <v>4</v>
@@ -33164,10 +33100,10 @@
         <v>2.2</v>
       </c>
       <c r="CL65" t="n">
-        <v>-7.272759452872357</v>
+        <v>-7.272759339369173</v>
       </c>
       <c r="CM65" t="n">
-        <v>-3.611406785511195</v>
+        <v>-3.611406630642433</v>
       </c>
       <c r="CN65" t="inlineStr">
         <is>
@@ -33275,7 +33211,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -33444,25 +33380,25 @@
         <v>2.230000019073486</v>
       </c>
       <c r="BX66" t="n">
-        <v>0.6400879170323638</v>
+        <v>0.640087919186489</v>
       </c>
       <c r="BY66" t="n">
-        <v>0.9083110511732729</v>
+        <v>0.9083110537881482</v>
       </c>
       <c r="BZ66" t="n">
-        <v>3.445624611015756</v>
+        <v>3.44562460933937</v>
       </c>
       <c r="CA66" t="n">
         <v>7.082796232577443</v>
       </c>
       <c r="CB66" t="n">
-        <v>2.645210819996298</v>
+        <v>2.645210823052456</v>
       </c>
       <c r="CC66" t="n">
-        <v>2.231318221924083</v>
+        <v>2.231318221826599</v>
       </c>
       <c r="CD66" t="n">
-        <v>1.712172251216327</v>
+        <v>1.71217225024766</v>
       </c>
       <c r="CE66" t="n">
         <v>4.877121459838516</v>
@@ -33493,11 +33429,7 @@
       </c>
       <c r="CP66" t="inlineStr"/>
       <c r="CQ66" t="inlineStr"/>
-      <c r="CR66" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CR66" t="inlineStr"/>
       <c r="CS66" t="b">
         <v>0</v>
       </c>
@@ -33524,14 +33456,14 @@
         <v>0</v>
       </c>
       <c r="DB66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC66" t="b">
         <v>0</v>
       </c>
       <c r="DD66" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.0, +0.5% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -33762,10 +33694,10 @@
         <v>35.29999923706055</v>
       </c>
       <c r="BX67" t="n">
-        <v>10.10703736352832</v>
+        <v>10.10703736611849</v>
       </c>
       <c r="BY67" t="n">
-        <v>18.74855430934504</v>
+        <v>18.7485543141498</v>
       </c>
       <c r="BZ67" t="n">
         <v>28.51981645677148</v>
@@ -33774,25 +33706,25 @@
         <v>21.18271110280847</v>
       </c>
       <c r="CB67" t="n">
-        <v>25.78113287961521</v>
+        <v>25.7811328733917</v>
       </c>
       <c r="CC67" t="n">
-        <v>22.8837908765584</v>
+        <v>22.88379087572786</v>
       </c>
       <c r="CD67" t="n">
-        <v>16.53208216666133</v>
+        <v>16.53208216135957</v>
       </c>
       <c r="CE67" t="n">
         <v>26.13806789836561</v>
       </c>
       <c r="CF67" t="n">
-        <v>21.23664913170673</v>
+        <v>21.23664913108662</v>
       </c>
       <c r="CG67" t="n">
-        <v>22.03325098968344</v>
+        <v>22.03325098926816</v>
       </c>
       <c r="CH67" t="n">
-        <v>19.8299258907151</v>
+        <v>19.82992589034135</v>
       </c>
       <c r="CI67" t="n">
         <v>8</v>
@@ -33804,10 +33736,10 @@
         <v>2.8</v>
       </c>
       <c r="CL67" t="n">
-        <v>-43.82457133342889</v>
+        <v>-43.82457133448765</v>
       </c>
       <c r="CM67" t="n">
-        <v>-39.83951957310262</v>
+        <v>-39.83951957485932</v>
       </c>
       <c r="CN67" t="inlineStr">
         <is>
@@ -34086,10 +34018,10 @@
         <v>8.369999885559082</v>
       </c>
       <c r="BX68" t="n">
-        <v>0.497878701237065</v>
+        <v>0.4978787011686301</v>
       </c>
       <c r="BY68" t="n">
-        <v>0.9235649907947556</v>
+        <v>0.9235649906678087</v>
       </c>
       <c r="BZ68" t="n">
         <v>9.438510509247473</v>
@@ -34098,13 +34030,13 @@
         <v>8.657076640576447</v>
       </c>
       <c r="CB68" t="n">
-        <v>10.36773199372814</v>
+        <v>10.36773199379232</v>
       </c>
       <c r="CC68" t="n">
-        <v>0.7358538297486488</v>
+        <v>0.7358538297499727</v>
       </c>
       <c r="CD68" t="n">
-        <v>8.046947281939167</v>
+        <v>8.046947282030764</v>
       </c>
       <c r="CE68" t="inlineStr"/>
       <c r="CF68" t="inlineStr"/>
@@ -34398,10 +34330,10 @@
         <v>8.310000419616699</v>
       </c>
       <c r="BX69" t="n">
-        <v>1.600348648229431</v>
+        <v>1.600348650238287</v>
       </c>
       <c r="BY69" t="n">
-        <v>2.968646742465594</v>
+        <v>2.968646746192022</v>
       </c>
       <c r="BZ69" t="n">
         <v>24.04094007858543</v>
@@ -34410,13 +34342,13 @@
         <v>23.7784718398941</v>
       </c>
       <c r="CB69" t="n">
-        <v>25.67792365036985</v>
+        <v>25.67792365283465</v>
       </c>
       <c r="CC69" t="n">
-        <v>6.70942594632635</v>
+        <v>6.709425946204396</v>
       </c>
       <c r="CD69" t="n">
-        <v>17.91257169426552</v>
+        <v>17.91257169195502</v>
       </c>
       <c r="CE69" t="n">
         <v>14.33275064778575</v>
@@ -34541,7 +34473,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -34712,10 +34644,10 @@
         <v>22.01000022888184</v>
       </c>
       <c r="BX70" t="n">
-        <v>6.086641393575827</v>
+        <v>6.086641387574164</v>
       </c>
       <c r="BY70" t="n">
-        <v>11.29071978508316</v>
+        <v>11.29071977395007</v>
       </c>
       <c r="BZ70" t="n">
         <v>32.8785234535157</v>
@@ -34724,25 +34656,25 @@
         <v>33.88891053961586</v>
       </c>
       <c r="CB70" t="n">
-        <v>29.32102004067283</v>
+        <v>29.3210200413669</v>
       </c>
       <c r="CC70" t="n">
-        <v>25.18528367372429</v>
+        <v>25.28068247647826</v>
       </c>
       <c r="CD70" t="n">
-        <v>19.02062593949426</v>
+        <v>19.02062594588483</v>
       </c>
       <c r="CE70" t="n">
         <v>13.2976614421224</v>
       </c>
       <c r="CF70" t="n">
-        <v>23.5546778391755</v>
+        <v>23.56830623899058</v>
       </c>
       <c r="CG70" t="n">
-        <v>25.18528367372429</v>
+        <v>25.28068247647826</v>
       </c>
       <c r="CH70" t="n">
-        <v>22.66675530635186</v>
+        <v>22.75261422883043</v>
       </c>
       <c r="CI70" t="n">
         <v>7</v>
@@ -34754,10 +34686,10 @@
         <v>5.6</v>
       </c>
       <c r="CL70" t="n">
-        <v>2.983894005635745</v>
+        <v>3.373984517156559</v>
       </c>
       <c r="CM70" t="n">
-        <v>7.018071759339262</v>
+        <v>7.079990885524423</v>
       </c>
       <c r="CN70" t="inlineStr">
         <is>
@@ -34771,11 +34703,7 @@
       </c>
       <c r="CP70" t="inlineStr"/>
       <c r="CQ70" t="inlineStr"/>
-      <c r="CR70" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CR70" t="inlineStr"/>
       <c r="CS70" t="b">
         <v>0</v>
       </c>
@@ -34802,14 +34730,14 @@
         <v>0</v>
       </c>
       <c r="DB70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC70" t="b">
         <v>0</v>
       </c>
       <c r="DD70" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.0, +0.8% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -35040,25 +34968,25 @@
         <v>17.35000038146973</v>
       </c>
       <c r="BX71" t="n">
-        <v>4.03806165495818</v>
+        <v>4.038061675581989</v>
       </c>
       <c r="BY71" t="n">
-        <v>6.921294107601996</v>
+        <v>6.921294132920286</v>
       </c>
       <c r="BZ71" t="n">
-        <v>23.44539823099441</v>
+        <v>23.44539819701441</v>
       </c>
       <c r="CA71" t="n">
         <v>32.9156248225843</v>
       </c>
       <c r="CB71" t="n">
-        <v>16.56490109862786</v>
+        <v>16.56490110840878</v>
       </c>
       <c r="CC71" t="n">
-        <v>20.29658945019877</v>
+        <v>20.29658944797749</v>
       </c>
       <c r="CD71" t="n">
-        <v>11.60585976953266</v>
+        <v>11.60585975564871</v>
       </c>
       <c r="CE71" t="n">
         <v>22.37681417341589</v>
@@ -35110,7 +35038,7 @@
         <v>-1.136865558091515</v>
       </c>
       <c r="CZ71" t="n">
-        <v>-39.9057468828705</v>
+        <v>-39.90574285278473</v>
       </c>
       <c r="DA71" t="b">
         <v>0</v>
@@ -35354,35 +35282,35 @@
         <v>23.92000007629395</v>
       </c>
       <c r="BX72" t="n">
-        <v>22.98145044574389</v>
+        <v>22.98145052883225</v>
       </c>
       <c r="BY72" t="n">
-        <v>28.94106194650103</v>
+        <v>28.9410619692223</v>
       </c>
       <c r="BZ72" t="n">
-        <v>38.28545855356551</v>
+        <v>38.28545844520369</v>
       </c>
       <c r="CA72" t="n">
         <v>61.7886423486284</v>
       </c>
       <c r="CB72" t="n">
-        <v>68.29187147002813</v>
+        <v>68.29187155335771</v>
       </c>
       <c r="CC72" t="n">
-        <v>41.71075101223551</v>
+        <v>41.71075100042413</v>
       </c>
       <c r="CD72" t="n">
-        <v>18.31133837518374</v>
+        <v>18.31133829745957</v>
       </c>
       <c r="CE72" t="inlineStr"/>
       <c r="CF72" t="n">
-        <v>40.04436773598376</v>
+        <v>40.04436773473258</v>
       </c>
       <c r="CG72" t="n">
-        <v>38.28545855356551</v>
+        <v>38.28545844520369</v>
       </c>
       <c r="CH72" t="n">
-        <v>34.45691269820896</v>
+        <v>34.45691260068332</v>
       </c>
       <c r="CI72" t="n">
         <v>7</v>
@@ -35394,10 +35322,10 @@
         <v>3.7</v>
       </c>
       <c r="CL72" t="n">
-        <v>44.05063791098263</v>
+        <v>44.05063750326674</v>
       </c>
       <c r="CM72" t="n">
-        <v>67.40956357968393</v>
+        <v>67.40956357445327</v>
       </c>
       <c r="CN72" t="inlineStr">
         <is>
@@ -35680,10 +35608,10 @@
         <v>25.05999946594238</v>
       </c>
       <c r="BX73" t="n">
-        <v>4.596834089057167</v>
+        <v>4.59683408541154</v>
       </c>
       <c r="BY73" t="n">
-        <v>8.527127235201045</v>
+        <v>8.527127228438408</v>
       </c>
       <c r="BZ73" t="n">
         <v>30.21337515229632</v>
@@ -35692,19 +35620,19 @@
         <v>25.61211449297552</v>
       </c>
       <c r="CB73" t="n">
-        <v>34.98906322082247</v>
+        <v>34.98906322526327</v>
       </c>
       <c r="CC73" t="n">
-        <v>11.7815487300817</v>
+        <v>11.78154873049792</v>
       </c>
       <c r="CD73" t="n">
-        <v>24.40384961956705</v>
+        <v>24.40384962527756</v>
       </c>
       <c r="CE73" t="n">
         <v>25.05999946594239</v>
       </c>
       <c r="CF73" t="n">
-        <v>25.34332511361424</v>
+        <v>25.34332511537549</v>
       </c>
       <c r="CG73" t="n">
         <v>25.33605697945895</v>
@@ -35725,7 +35653,7 @@
         <v>-9.008572356505551</v>
       </c>
       <c r="CM73" t="n">
-        <v>1.130589200757615</v>
+        <v>1.130589207785748</v>
       </c>
       <c r="CN73" t="inlineStr">
         <is>
@@ -36004,10 +35932,10 @@
         <v>4.099999904632568</v>
       </c>
       <c r="BX74" t="n">
-        <v>0.9952746088329852</v>
+        <v>0.9952746062621268</v>
       </c>
       <c r="BY74" t="n">
-        <v>1.846234399385188</v>
+        <v>1.846234394616245</v>
       </c>
       <c r="BZ74" t="n">
         <v>6.076621782593012</v>
@@ -36016,7 +35944,7 @@
         <v>4.033849326526731</v>
       </c>
       <c r="CB74" t="n">
-        <v>8.437790055162228</v>
+        <v>8.437790051136275</v>
       </c>
       <c r="CC74" t="n">
         <v>3.760485277130923</v>
@@ -36074,7 +36002,7 @@
         <v>1.2345607788387</v>
       </c>
       <c r="CZ74" t="n">
-        <v>-43.94937782560127</v>
+        <v>-43.94938155820927</v>
       </c>
       <c r="DA74" t="b">
         <v>0</v>
@@ -36318,10 +36246,10 @@
         <v>12.5</v>
       </c>
       <c r="BX75" t="n">
-        <v>2.06764356577</v>
+        <v>2.067643565120046</v>
       </c>
       <c r="BY75" t="n">
-        <v>3.835478814503349</v>
+        <v>3.835478813297684</v>
       </c>
       <c r="BZ75" t="n">
         <v>16.12706913339824</v>
@@ -36330,7 +36258,7 @@
         <v>12.79802361537235</v>
       </c>
       <c r="CB75" t="n">
-        <v>21.07565822013437</v>
+        <v>21.07565821924836</v>
       </c>
       <c r="CC75" t="n">
         <v>9.294207014285712</v>
@@ -36630,10 +36558,10 @@
         <v>55.09999847412109</v>
       </c>
       <c r="BX76" t="n">
-        <v>40.07181817750811</v>
+        <v>40.07181820827667</v>
       </c>
       <c r="BY76" t="n">
-        <v>58.34456726645181</v>
+        <v>58.34456731125084</v>
       </c>
       <c r="BZ76" t="n">
         <v>35.37283852659625</v>
@@ -36652,13 +36580,13 @@
         <v>47.96787202142232</v>
       </c>
       <c r="CF76" t="n">
-        <v>42.95650163633959</v>
+        <v>42.95650164893419</v>
       </c>
       <c r="CG76" t="n">
-        <v>41.12613199705611</v>
+        <v>41.12613201244039</v>
       </c>
       <c r="CH76" t="n">
-        <v>37.0135187973505</v>
+        <v>37.01351881119635</v>
       </c>
       <c r="CI76" t="n">
         <v>6</v>
@@ -36670,10 +36598,10 @@
         <v>6.4</v>
       </c>
       <c r="CL76" t="n">
-        <v>-32.82482790859839</v>
+        <v>-32.82482788346982</v>
       </c>
       <c r="CM76" t="n">
-        <v>-22.03901483497311</v>
+        <v>-22.0390148121154</v>
       </c>
       <c r="CN76" t="inlineStr">
         <is>
@@ -36952,10 +36880,10 @@
         <v>28.84000015258789</v>
       </c>
       <c r="BX77" t="n">
-        <v>13.47286417140859</v>
+        <v>13.47286416580892</v>
       </c>
       <c r="BY77" t="n">
-        <v>24.99216303796292</v>
+        <v>24.99216302757555</v>
       </c>
       <c r="BZ77" t="n">
         <v>37.02810097110363</v>
@@ -36964,19 +36892,19 @@
         <v>25.82035545899241</v>
       </c>
       <c r="CB77" t="n">
-        <v>42.23092873643785</v>
+        <v>42.23092874951424</v>
       </c>
       <c r="CC77" t="n">
-        <v>42.15771501991222</v>
+        <v>42.15771502278463</v>
       </c>
       <c r="CD77" t="n">
-        <v>22.52217029289583</v>
+        <v>22.52217030589018</v>
       </c>
       <c r="CE77" t="n">
         <v>25.11428706378544</v>
       </c>
       <c r="CF77" t="n">
-        <v>29.16732309406236</v>
+        <v>29.16732309568188</v>
       </c>
       <c r="CG77" t="n">
         <v>25.46732126138892</v>
@@ -36997,7 +36925,7 @@
         <v>-20.52500341892922</v>
       </c>
       <c r="CM77" t="n">
-        <v>1.134961649593125</v>
+        <v>1.134961655208633</v>
       </c>
       <c r="CN77" t="inlineStr">
         <is>
@@ -37040,7 +36968,7 @@
         <v>-1.653573943371112</v>
       </c>
       <c r="CZ77" t="n">
-        <v>-24.22121477099677</v>
+        <v>-24.22120680081555</v>
       </c>
       <c r="DA77" t="b">
         <v>0</v>
@@ -37284,10 +37212,10 @@
         <v>15.10000038146973</v>
       </c>
       <c r="BX78" t="n">
-        <v>2.436662808488616</v>
+        <v>2.436662819315114</v>
       </c>
       <c r="BY78" t="n">
-        <v>4.520009509746382</v>
+        <v>4.520009529829536</v>
       </c>
       <c r="BZ78" t="n">
         <v>25.42249111238549</v>
@@ -37296,7 +37224,7 @@
         <v>19.46778887244506</v>
       </c>
       <c r="CB78" t="n">
-        <v>33.11477573581785</v>
+        <v>33.11477575507719</v>
       </c>
       <c r="CC78" t="n">
         <v>10.38593205872702</v>
@@ -37598,10 +37526,10 @@
         <v>14.64999961853027</v>
       </c>
       <c r="BX79" t="n">
-        <v>9.577489860179213</v>
+        <v>9.577489891443905</v>
       </c>
       <c r="BY79" t="n">
-        <v>17.76624369063244</v>
+        <v>17.76624374862844</v>
       </c>
       <c r="BZ79" t="n">
         <v>13.92485616538925</v>
@@ -37622,7 +37550,7 @@
         <v>12.21188626720157</v>
       </c>
       <c r="CF79" t="n">
-        <v>15.01493740123908</v>
+        <v>15.01493741239666</v>
       </c>
       <c r="CG79" t="n">
         <v>13.27530794084946</v>
@@ -37643,7 +37571,7 @@
         <v>-18.44520506572443</v>
       </c>
       <c r="CM79" t="n">
-        <v>2.491042950248312</v>
+        <v>2.491043026409301</v>
       </c>
       <c r="CN79" t="inlineStr">
         <is>
@@ -37922,25 +37850,25 @@
         <v>26.43000030517578</v>
       </c>
       <c r="BX80" t="n">
-        <v>12.03762490870676</v>
+        <v>12.03762492331953</v>
       </c>
       <c r="BY80" t="n">
-        <v>12.71617177066824</v>
+        <v>12.71617177744198</v>
       </c>
       <c r="BZ80" t="n">
-        <v>13.985087439832</v>
+        <v>13.98508743030482</v>
       </c>
       <c r="CA80" t="n">
         <v>32.55457236063513</v>
       </c>
       <c r="CB80" t="n">
-        <v>13.04073166108254</v>
+        <v>13.04073166055599</v>
       </c>
       <c r="CC80" t="n">
-        <v>24.67111018853117</v>
+        <v>24.67111018656442</v>
       </c>
       <c r="CD80" t="n">
-        <v>5.719805436519869</v>
+        <v>5.719805427171202</v>
       </c>
       <c r="CE80" t="n">
         <v>64.37858937491418</v>
@@ -37992,7 +37920,7 @@
         <v>-2.767610712638247</v>
       </c>
       <c r="CZ80" t="n">
-        <v>-18.49373954324827</v>
+        <v>-18.49374923657961</v>
       </c>
       <c r="DA80" t="b">
         <v>0</v>
@@ -38236,10 +38164,10 @@
         <v>6.949999809265137</v>
       </c>
       <c r="BX81" t="n">
-        <v>1.252136524867497</v>
+        <v>1.252136524673465</v>
       </c>
       <c r="BY81" t="n">
-        <v>2.322713253629208</v>
+        <v>2.322713253269277</v>
       </c>
       <c r="BZ81" t="n">
         <v>10.39362273958951</v>
@@ -38248,13 +38176,13 @@
         <v>10.1957267373713</v>
       </c>
       <c r="CB81" t="n">
-        <v>10.0677285421747</v>
+        <v>10.06772854222885</v>
       </c>
       <c r="CC81" t="n">
-        <v>1.873451565621566</v>
+        <v>1.873451565629377</v>
       </c>
       <c r="CD81" t="n">
-        <v>7.180163108506266</v>
+        <v>7.18016310873302</v>
       </c>
       <c r="CE81" t="n">
         <v>11.09654186695129</v>
@@ -38550,10 +38478,10 @@
         <v>9.939999580383301</v>
       </c>
       <c r="BX82" t="n">
-        <v>6.09297728768885</v>
+        <v>6.092977391546688</v>
       </c>
       <c r="BY82" t="n">
-        <v>11.30247286866282</v>
+        <v>11.30247306131911</v>
       </c>
       <c r="BZ82" t="n">
         <v>7.958005706349167</v>
@@ -38574,7 +38502,7 @@
         <v>39.81362833472408</v>
       </c>
       <c r="CF82" t="n">
-        <v>10.11499326911501</v>
+        <v>10.11499331147417</v>
       </c>
       <c r="CG82" t="n">
         <v>7.958005706349167</v>
@@ -38595,7 +38523,7 @@
         <v>-27.94561933534745</v>
       </c>
       <c r="CM82" t="n">
-        <v>1.760499960956308</v>
+        <v>1.760500387104824</v>
       </c>
       <c r="CN82" t="inlineStr">
         <is>
@@ -39198,10 +39126,10 @@
         <v>5.199999809265137</v>
       </c>
       <c r="BX84" t="n">
-        <v>3.075082688450174</v>
+        <v>3.075082700852204</v>
       </c>
       <c r="BY84" t="n">
-        <v>4.477320394383454</v>
+        <v>4.47732041244081</v>
       </c>
       <c r="BZ84" t="n">
         <v>4.343774941072886</v>
@@ -39510,10 +39438,10 @@
         <v>18.6299991607666</v>
       </c>
       <c r="BX85" t="n">
-        <v>4.525590677347324</v>
+        <v>4.525590660514436</v>
       </c>
       <c r="BY85" t="n">
-        <v>8.394970706479285</v>
+        <v>8.394970675254278</v>
       </c>
       <c r="BZ85" t="n">
         <v>32.35222658979783</v>
@@ -39522,13 +39450,13 @@
         <v>34.90616862755231</v>
       </c>
       <c r="CB85" t="n">
-        <v>28.19287872533796</v>
+        <v>28.19287872037457</v>
       </c>
       <c r="CC85" t="n">
-        <v>11.13050349146053</v>
+        <v>11.13050349255322</v>
       </c>
       <c r="CD85" t="n">
-        <v>19.02445091085539</v>
+        <v>19.02445092714962</v>
       </c>
       <c r="CE85" t="n">
         <v>43.9950485000171</v>
@@ -40194,7 +40122,7 @@
         <v>-1.476013331733317</v>
       </c>
       <c r="CZ87" t="n">
-        <v>-17.49578257353508</v>
+        <v>-17.49577746727665</v>
       </c>
       <c r="DA87" t="b">
         <v>0</v>
@@ -40438,10 +40366,10 @@
         <v>22.8799991607666</v>
       </c>
       <c r="BX88" t="n">
-        <v>11.53052558531866</v>
+        <v>11.53052566157839</v>
       </c>
       <c r="BY88" t="n">
-        <v>21.38912496076611</v>
+        <v>21.38912510222791</v>
       </c>
       <c r="BZ88" t="n">
         <v>14.98566430450605</v>
@@ -40462,13 +40390,13 @@
         <v>22.8799991607666</v>
       </c>
       <c r="CF88" t="n">
-        <v>19.55745660985444</v>
+        <v>19.55745663706963</v>
       </c>
       <c r="CG88" t="n">
-        <v>18.18739463263608</v>
+        <v>18.18739470336698</v>
       </c>
       <c r="CH88" t="n">
-        <v>16.36865516937247</v>
+        <v>16.36865523303029</v>
       </c>
       <c r="CI88" t="n">
         <v>8</v>
@@ -40480,10 +40408,10 @@
         <v>2.9</v>
       </c>
       <c r="CL88" t="n">
-        <v>-28.45867233491614</v>
+        <v>-28.45867205669143</v>
       </c>
       <c r="CM88" t="n">
-        <v>-14.52160259083173</v>
+        <v>-14.5216024718842</v>
       </c>
       <c r="CN88" t="inlineStr">
         <is>
@@ -40762,25 +40690,25 @@
         <v>1.639999985694885</v>
       </c>
       <c r="BX89" t="n">
-        <v>0.1462397369520619</v>
+        <v>0.1462397372773545</v>
       </c>
       <c r="BY89" t="n">
-        <v>0.1665894434043839</v>
+        <v>0.1665894437603682</v>
       </c>
       <c r="BZ89" t="n">
-        <v>0.7471648524998562</v>
+        <v>0.7471648524344917</v>
       </c>
       <c r="CA89" t="n">
         <v>3.111432285836558</v>
       </c>
       <c r="CB89" t="n">
-        <v>0.2544830305863364</v>
+        <v>0.2544830307520647</v>
       </c>
       <c r="CC89" t="n">
-        <v>0.5414651045084542</v>
+        <v>0.5414651045032697</v>
       </c>
       <c r="CD89" t="n">
-        <v>0.3332100976791234</v>
+        <v>0.3332100976230169</v>
       </c>
       <c r="CE89" t="inlineStr"/>
       <c r="CF89" t="inlineStr"/>
@@ -41072,10 +41000,10 @@
         <v>14</v>
       </c>
       <c r="BX90" t="n">
-        <v>6.043656257806143</v>
+        <v>6.043656254783865</v>
       </c>
       <c r="BY90" t="n">
-        <v>8.799563511365745</v>
+        <v>8.799563506965308</v>
       </c>
       <c r="BZ90" t="n">
         <v>3.748712667353244</v>
@@ -41288,13 +41216,13 @@
         <v>0</v>
       </c>
       <c r="AR91" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="AS91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="n">
-        <v>2905931264</v>
+        <v>2883450880</v>
       </c>
       <c r="AU91" t="n">
         <v>6.69</v>
@@ -41384,10 +41312,10 @@
         <v>7.190000057220459</v>
       </c>
       <c r="BX91" t="n">
-        <v>2.991919275330102</v>
+        <v>2.991919275167895</v>
       </c>
       <c r="BY91" t="n">
-        <v>5.550010255737339</v>
+        <v>5.550010255436446</v>
       </c>
       <c r="BZ91" t="n">
         <v>14.24028411930808</v>
@@ -41396,23 +41324,23 @@
         <v>15.32820267413183</v>
       </c>
       <c r="CB91" t="n">
-        <v>13.52815312931932</v>
+        <v>13.52815312923149</v>
       </c>
       <c r="CC91" t="n">
-        <v>14.98505630948583</v>
+        <v>14.98505630951869</v>
       </c>
       <c r="CD91" t="n">
-        <v>7.438938484397434</v>
+        <v>7.438938484555592</v>
       </c>
       <c r="CE91" t="inlineStr"/>
       <c r="CF91" t="n">
-        <v>11.84510749539664</v>
+        <v>11.84510749536369</v>
       </c>
       <c r="CG91" t="n">
-        <v>13.8842186243137</v>
+        <v>13.88421862426978</v>
       </c>
       <c r="CH91" t="n">
-        <v>12.49579676188233</v>
+        <v>12.49579676184281</v>
       </c>
       <c r="CI91" t="n">
         <v>6</v>
@@ -41424,10 +41352,10 @@
         <v>5.1</v>
       </c>
       <c r="CL91" t="n">
-        <v>73.794112134027</v>
+        <v>73.79411213347728</v>
       </c>
       <c r="CM91" t="n">
-        <v>64.74419194894656</v>
+        <v>64.74419194848824</v>
       </c>
       <c r="CN91" t="inlineStr">
         <is>
@@ -41708,10 +41636,10 @@
         <v>3.599999904632568</v>
       </c>
       <c r="BX92" t="n">
-        <v>32.93904535431918</v>
+        <v>32.9390452860922</v>
       </c>
       <c r="BY92" t="n">
-        <v>61.10192913226209</v>
+        <v>61.10192900570102</v>
       </c>
       <c r="BZ92" t="n">
         <v>4.727452798452084</v>
@@ -42004,35 +41932,35 @@
         <v>19.52000045776367</v>
       </c>
       <c r="BX93" t="n">
-        <v>11.63736110639046</v>
+        <v>11.63736098559233</v>
       </c>
       <c r="BY93" t="n">
-        <v>15.01593043713283</v>
+        <v>15.01593036098333</v>
       </c>
       <c r="BZ93" t="n">
-        <v>23.30409406159995</v>
+        <v>23.30409418532029</v>
       </c>
       <c r="CA93" t="n">
         <v>42.3220394475809</v>
       </c>
       <c r="CB93" t="n">
-        <v>28.28916537247948</v>
+        <v>28.2891652885403</v>
       </c>
       <c r="CC93" t="n">
-        <v>15.78796529768099</v>
+        <v>15.78796530588506</v>
       </c>
       <c r="CD93" t="n">
-        <v>11.27107575460606</v>
+        <v>11.27107583954164</v>
       </c>
       <c r="CE93" t="inlineStr"/>
       <c r="CF93" t="n">
-        <v>16.43633772570106</v>
+        <v>16.43633770944525</v>
       </c>
       <c r="CG93" t="n">
-        <v>15.40194786740691</v>
+        <v>15.4019478334342</v>
       </c>
       <c r="CH93" t="n">
-        <v>13.86175308066622</v>
+        <v>13.86175305009078</v>
       </c>
       <c r="CI93" t="n">
         <v>4</v>
@@ -42044,10 +41972,10 @@
         <v>2</v>
       </c>
       <c r="CL93" t="n">
-        <v>-28.98692235863655</v>
+        <v>-28.986922515273</v>
       </c>
       <c r="CM93" t="n">
-        <v>-15.79745215034639</v>
+        <v>-15.79745223362408</v>
       </c>
       <c r="CN93" t="inlineStr">
         <is>
@@ -42336,10 +42264,10 @@
         <v>7.699999809265137</v>
       </c>
       <c r="BX94" t="n">
-        <v>4.956376408799809</v>
+        <v>4.956376447253745</v>
       </c>
       <c r="BY94" t="n">
-        <v>7.216484051212523</v>
+        <v>7.216484107201453</v>
       </c>
       <c r="BZ94" t="n">
         <v>5.840991831973553</v>
@@ -42358,13 +42286,13 @@
         <v>7.669958086796234</v>
       </c>
       <c r="CF94" t="n">
-        <v>6.576004390848374</v>
+        <v>6.576004406588852</v>
       </c>
       <c r="CG94" t="n">
-        <v>6.528737941593038</v>
+        <v>6.528737969587503</v>
       </c>
       <c r="CH94" t="n">
-        <v>5.875864147433735</v>
+        <v>5.875864172628753</v>
       </c>
       <c r="CI94" t="n">
         <v>6</v>
@@ -42376,10 +42304,10 @@
         <v>5.9</v>
       </c>
       <c r="CL94" t="n">
-        <v>-23.69007411709913</v>
+        <v>-23.69007378989109</v>
       </c>
       <c r="CM94" t="n">
-        <v>-14.59734345790891</v>
+        <v>-14.59734325348712</v>
       </c>
       <c r="CN94" t="inlineStr">
         <is>
@@ -42414,7 +42342,7 @@
         <v>-7.84022436025481</v>
       </c>
       <c r="CZ94" t="n">
-        <v>-20.64634560910679</v>
+        <v>-20.64635356542279</v>
       </c>
       <c r="DA94" t="b">
         <v>0</v>
@@ -42656,10 +42584,10 @@
         <v>78.44999694824219</v>
       </c>
       <c r="BX95" t="n">
-        <v>58.65254681466016</v>
+        <v>58.65254675917564</v>
       </c>
       <c r="BY95" t="n">
-        <v>85.39810816214521</v>
+        <v>85.39810808135972</v>
       </c>
       <c r="BZ95" t="n">
         <v>24.28937089198329</v>
@@ -42669,7 +42597,7 @@
       </c>
       <c r="CB95" t="inlineStr"/>
       <c r="CC95" t="n">
-        <v>43</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="CD95" t="n">
         <v>6.239165325275927</v>
@@ -42968,10 +42896,10 @@
         <v>35.40000152587891</v>
       </c>
       <c r="BX96" t="n">
-        <v>8.762922247219956</v>
+        <v>8.762922240458973</v>
       </c>
       <c r="BY96" t="n">
-        <v>16.25522076859302</v>
+        <v>16.2552207560514</v>
       </c>
       <c r="BZ96" t="n">
         <v>40.36575044904436</v>
@@ -42980,19 +42908,19 @@
         <v>40.62868896182997</v>
       </c>
       <c r="CB96" t="n">
-        <v>33.54007650492093</v>
+        <v>33.54007650872993</v>
       </c>
       <c r="CC96" t="n">
-        <v>50.02761776397175</v>
+        <v>50.0276177657972</v>
       </c>
       <c r="CD96" t="n">
-        <v>22.58447319460024</v>
+        <v>22.58447320211466</v>
       </c>
       <c r="CE96" t="n">
         <v>51.45658855125112</v>
       </c>
       <c r="CF96" t="n">
-        <v>36.40834517060163</v>
+        <v>36.40834517068838</v>
       </c>
       <c r="CG96" t="n">
         <v>40.36575044904436</v>
@@ -43013,7 +42941,7 @@
         <v>2.624784853700501</v>
       </c>
       <c r="CM96" t="n">
-        <v>2.848428252144508</v>
+        <v>2.848428252389557</v>
       </c>
       <c r="CN96" t="inlineStr">
         <is>
@@ -43204,7 +43132,7 @@
         <v>1</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AS97" t="b">
         <v>1</v>
@@ -43300,10 +43228,10 @@
         <v>19.30999946594238</v>
       </c>
       <c r="BX97" t="n">
-        <v>1.992800464187762</v>
+        <v>1.992800462965726</v>
       </c>
       <c r="BY97" t="n">
-        <v>3.696644861068299</v>
+        <v>3.696644858801421</v>
       </c>
       <c r="BZ97" t="n">
         <v>10.14904771613394</v>
@@ -43312,19 +43240,19 @@
         <v>8.468921507385986</v>
       </c>
       <c r="CB97" t="n">
-        <v>10.07185987839135</v>
+        <v>10.07185988086239</v>
       </c>
       <c r="CC97" t="n">
-        <v>7.543960938294576</v>
+        <v>7.543960938572281</v>
       </c>
       <c r="CD97" t="n">
-        <v>7.681483915508804</v>
+        <v>7.681483917488602</v>
       </c>
       <c r="CE97" t="n">
         <v>13.74780034812948</v>
       </c>
       <c r="CF97" t="n">
-        <v>8.765674166416062</v>
+        <v>8.765674166767727</v>
       </c>
       <c r="CG97" t="n">
         <v>8.468921507385986</v>
@@ -43345,7 +43273,7 @@
         <v>-60.5280705983934</v>
       </c>
       <c r="CM97" t="n">
-        <v>-54.60551833843217</v>
+        <v>-54.60551833661101</v>
       </c>
       <c r="CN97" t="inlineStr">
         <is>
@@ -43624,10 +43552,10 @@
         <v>7.130000114440918</v>
       </c>
       <c r="BX98" t="n">
-        <v>3.192404447627376</v>
+        <v>3.19240443515019</v>
       </c>
       <c r="BY98" t="n">
-        <v>5.921910250348782</v>
+        <v>5.921910227203602</v>
       </c>
       <c r="BZ98" t="inlineStr"/>
       <c r="CA98" t="inlineStr"/>
@@ -43638,13 +43566,13 @@
         <v>9.795329306466718</v>
       </c>
       <c r="CF98" t="n">
-        <v>6.303214668147625</v>
+        <v>6.303214656273504</v>
       </c>
       <c r="CG98" t="n">
-        <v>5.921910250348782</v>
+        <v>5.921910227203602</v>
       </c>
       <c r="CH98" t="n">
-        <v>5.329719225313904</v>
+        <v>5.329719204483242</v>
       </c>
       <c r="CI98" t="n">
         <v>3</v>
@@ -43656,10 +43584,10 @@
         <v>3.1</v>
       </c>
       <c r="CL98" t="n">
-        <v>-25.2493809289115</v>
+        <v>-25.24938122106666</v>
       </c>
       <c r="CM98" t="n">
-        <v>-11.59586862584677</v>
+        <v>-11.59586879238423</v>
       </c>
       <c r="CN98" t="inlineStr">
         <is>
@@ -43938,10 +43866,10 @@
         <v>16.29000091552734</v>
       </c>
       <c r="BX99" t="n">
-        <v>8.202603288440049</v>
+        <v>8.202603278645226</v>
       </c>
       <c r="BY99" t="n">
-        <v>15.21582910005629</v>
+        <v>15.21582908188689</v>
       </c>
       <c r="BZ99" t="n">
         <v>10.31751970032205</v>
@@ -43962,7 +43890,7 @@
         <v>9.919264240514863</v>
       </c>
       <c r="CF99" t="n">
-        <v>12.40800581567404</v>
+        <v>12.40800581217851</v>
       </c>
       <c r="CG99" t="n">
         <v>10.11839197041846</v>
@@ -43983,7 +43911,7 @@
         <v>-44.09728507322303</v>
       </c>
       <c r="CM99" t="n">
-        <v>-23.83053948237078</v>
+        <v>-23.83053950382889</v>
       </c>
       <c r="CN99" t="inlineStr">
         <is>
@@ -44262,37 +44190,37 @@
         <v>23.10000038146973</v>
       </c>
       <c r="BX100" t="n">
-        <v>5.059556813399968</v>
+        <v>5.059556840369771</v>
       </c>
       <c r="BY100" t="n">
-        <v>7.1635149654326</v>
+        <v>7.163514971392161</v>
       </c>
       <c r="BZ100" t="n">
-        <v>10.56595859294325</v>
+        <v>10.56595854541192</v>
       </c>
       <c r="CA100" t="n">
         <v>14.53591293928228</v>
       </c>
       <c r="CB100" t="n">
-        <v>7.113111158696245</v>
+        <v>7.113111131898985</v>
       </c>
       <c r="CC100" t="n">
-        <v>8.433635754024921</v>
+        <v>8.433635750611034</v>
       </c>
       <c r="CD100" t="n">
-        <v>5.248389309237264</v>
+        <v>5.248389281659023</v>
       </c>
       <c r="CE100" t="n">
         <v>10.59103290637341</v>
       </c>
       <c r="CF100" t="n">
-        <v>8.588889054923742</v>
+        <v>8.588889045874822</v>
       </c>
       <c r="CG100" t="n">
-        <v>7.79857535972876</v>
+        <v>7.798575361001597</v>
       </c>
       <c r="CH100" t="n">
-        <v>7.018717823755884</v>
+        <v>7.018717824901437</v>
       </c>
       <c r="CI100" t="n">
         <v>8</v>
@@ -44304,10 +44232,10 @@
         <v>2.9</v>
       </c>
       <c r="CL100" t="n">
-        <v>-69.61594065865846</v>
+        <v>-69.61594065369935</v>
       </c>
       <c r="CM100" t="n">
-        <v>-62.8186627139039</v>
+        <v>-62.81866275307672</v>
       </c>
       <c r="CN100" t="inlineStr">
         <is>
@@ -44586,10 +44514,10 @@
         <v>46.15000152587891</v>
       </c>
       <c r="BX101" t="n">
-        <v>10.09708139675373</v>
+        <v>10.0970814096681</v>
       </c>
       <c r="BY101" t="n">
-        <v>18.73008599097816</v>
+        <v>18.73008601493433</v>
       </c>
       <c r="BZ101" t="n">
         <v>85.64250983443914</v>
@@ -44598,13 +44526,13 @@
         <v>75.73923984409785</v>
       </c>
       <c r="CB101" t="n">
-        <v>102.8201043255792</v>
+        <v>102.8201043211778</v>
       </c>
       <c r="CC101" t="n">
-        <v>16.00028350710535</v>
+        <v>16.0002835064533</v>
       </c>
       <c r="CD101" t="n">
-        <v>69.45220512177474</v>
+        <v>69.45220510309126</v>
       </c>
       <c r="CE101" t="n">
         <v>22.17724767718654</v>
@@ -44904,25 +44832,25 @@
         <v>47.56999969482422</v>
       </c>
       <c r="BX102" t="n">
-        <v>18.28341043200535</v>
+        <v>18.28341039593941</v>
       </c>
       <c r="BY102" t="n">
-        <v>20.17639205926478</v>
+        <v>20.17639204257843</v>
       </c>
       <c r="BZ102" t="n">
-        <v>23.73199924155394</v>
+        <v>23.73199926874088</v>
       </c>
       <c r="CA102" t="n">
         <v>51.18507081724616</v>
       </c>
       <c r="CB102" t="n">
-        <v>19.70990832415644</v>
+        <v>19.7099083314823</v>
       </c>
       <c r="CC102" t="n">
-        <v>23.26809386884051</v>
+        <v>23.26809387184144</v>
       </c>
       <c r="CD102" t="n">
-        <v>10.24894880991898</v>
+        <v>10.24894883461116</v>
       </c>
       <c r="CE102" t="n">
         <v>118.416879883234</v>
@@ -45218,10 +45146,10 @@
         <v>12.09000015258789</v>
       </c>
       <c r="BX103" t="n">
-        <v>2.150806821310205</v>
+        <v>2.150806829613821</v>
       </c>
       <c r="BY103" t="n">
-        <v>3.989746653530429</v>
+        <v>3.989746668933637</v>
       </c>
       <c r="BZ103" t="n">
         <v>12.12660878287581</v>
@@ -45230,25 +45158,25 @@
         <v>13.43156485358001</v>
       </c>
       <c r="CB103" t="n">
-        <v>8.696806190664374</v>
+        <v>8.696806187316383</v>
       </c>
       <c r="CC103" t="n">
-        <v>5.735265293962883</v>
+        <v>5.73526529325149</v>
       </c>
       <c r="CD103" t="n">
-        <v>6.478711643634271</v>
+        <v>6.478711635998265</v>
       </c>
       <c r="CE103" t="n">
         <v>12.09000015258789</v>
       </c>
       <c r="CF103" t="n">
-        <v>8.935529081547953</v>
+        <v>8.935529082077641</v>
       </c>
       <c r="CG103" t="n">
-        <v>8.696806190664374</v>
+        <v>8.696806187316383</v>
       </c>
       <c r="CH103" t="n">
-        <v>7.827125571597937</v>
+        <v>7.827125568584745</v>
       </c>
       <c r="CI103" t="n">
         <v>7</v>
@@ -45260,10 +45188,10 @@
         <v>6.2</v>
       </c>
       <c r="CL103" t="n">
-        <v>-35.2595080826155</v>
+        <v>-35.25950810753851</v>
       </c>
       <c r="CM103" t="n">
-        <v>-26.09157180502364</v>
+        <v>-26.09157180064243</v>
       </c>
       <c r="CN103" t="inlineStr">
         <is>
@@ -45542,37 +45470,37 @@
         <v>53.40999984741211</v>
       </c>
       <c r="BX104" t="n">
-        <v>16.3150745459764</v>
+        <v>16.31507455044472</v>
       </c>
       <c r="BY104" t="n">
-        <v>24.73118743500826</v>
+        <v>24.73118743756069</v>
       </c>
       <c r="BZ104" t="n">
-        <v>44.34787922324436</v>
+        <v>44.34787921567552</v>
       </c>
       <c r="CA104" t="n">
         <v>61.77036746811122</v>
       </c>
       <c r="CB104" t="n">
-        <v>35.38002402151585</v>
+        <v>35.38002402014506</v>
       </c>
       <c r="CC104" t="n">
-        <v>26.75432547742663</v>
+        <v>26.75432547704056</v>
       </c>
       <c r="CD104" t="n">
-        <v>22.17049368287636</v>
+        <v>22.17049367899929</v>
       </c>
       <c r="CE104" t="n">
         <v>21.56859389198009</v>
       </c>
       <c r="CF104" t="n">
-        <v>31.62974321826739</v>
+        <v>31.62974321749464</v>
       </c>
       <c r="CG104" t="n">
-        <v>25.74275645621744</v>
+        <v>25.74275645730063</v>
       </c>
       <c r="CH104" t="n">
-        <v>23.1684808105957</v>
+        <v>23.16848081157056</v>
       </c>
       <c r="CI104" t="n">
         <v>8</v>
@@ -45584,10 +45512,10 @@
         <v>3.8</v>
       </c>
       <c r="CL104" t="n">
-        <v>-56.62145501444279</v>
+        <v>-56.62145501261755</v>
       </c>
       <c r="CM104" t="n">
-        <v>-40.77936096492994</v>
+        <v>-40.77936096637678</v>
       </c>
       <c r="CN104" t="inlineStr">
         <is>
@@ -45878,10 +45806,10 @@
         <v>3.049999952316284</v>
       </c>
       <c r="BX105" t="n">
-        <v>0.6383064645891081</v>
+        <v>0.6383064648494843</v>
       </c>
       <c r="BY105" t="n">
-        <v>1.184058491812795</v>
+        <v>1.184058492295793</v>
       </c>
       <c r="BZ105" t="n">
         <v>3.424788082050064</v>
@@ -45890,13 +45818,13 @@
         <v>3.961967112431116</v>
       </c>
       <c r="CB105" t="n">
-        <v>2.375711409583712</v>
+        <v>2.375711409543781</v>
       </c>
       <c r="CC105" t="n">
-        <v>2.634385252568863</v>
+        <v>2.634385252535403</v>
       </c>
       <c r="CD105" t="n">
-        <v>1.707775511806438</v>
+        <v>1.70777551158716</v>
       </c>
       <c r="CE105" t="n">
         <v>9.00430014677799</v>
@@ -46190,10 +46118,10 @@
         <v>56.20999908447266</v>
       </c>
       <c r="BX106" t="n">
-        <v>63.60341780251192</v>
+        <v>63.60341754095358</v>
       </c>
       <c r="BY106" t="n">
-        <v>92.60657632045736</v>
+        <v>92.60657593962841</v>
       </c>
       <c r="BZ106" t="n">
         <v>24.49032218175599</v>
@@ -46798,10 +46726,10 @@
         <v>6.380000114440918</v>
       </c>
       <c r="BX108" t="n">
-        <v>0.06112997611094304</v>
+        <v>0.06112997582794635</v>
       </c>
       <c r="BY108" t="n">
-        <v>0.1133961056857993</v>
+        <v>0.1133961051608405</v>
       </c>
       <c r="BZ108" t="inlineStr"/>
       <c r="CA108" t="inlineStr"/>
@@ -47100,10 +47028,10 @@
         <v>97.23000335693359</v>
       </c>
       <c r="BX109" t="n">
-        <v>4.964171920058876</v>
+        <v>4.96417192164953</v>
       </c>
       <c r="BY109" t="n">
-        <v>9.208538911709214</v>
+        <v>9.208538914659879</v>
       </c>
       <c r="BZ109" t="n">
         <v>41.67898882172015</v>
@@ -47112,13 +47040,13 @@
         <v>41.37414486486504</v>
       </c>
       <c r="CB109" t="n">
-        <v>34.1307176515576</v>
+        <v>34.13071764938083</v>
       </c>
       <c r="CC109" t="n">
-        <v>17.69250931426015</v>
+        <v>17.69250931411219</v>
       </c>
       <c r="CD109" t="n">
-        <v>28.44350971013298</v>
+        <v>28.44350970831187</v>
       </c>
       <c r="CE109" t="n">
         <v>42.92647655369059</v>
@@ -47724,10 +47652,10 @@
         <v>17.29999923706055</v>
       </c>
       <c r="BX111" t="n">
-        <v>3.248067571874746</v>
+        <v>3.248067544409685</v>
       </c>
       <c r="BY111" t="n">
-        <v>6.025165345827653</v>
+        <v>6.025165294879965</v>
       </c>
       <c r="BZ111" t="n">
         <v>14.7601410103704</v>
@@ -47736,23 +47664,23 @@
         <v>15.74100985524925</v>
       </c>
       <c r="CB111" t="n">
-        <v>10.37752216150218</v>
+        <v>10.37752218019267</v>
       </c>
       <c r="CC111" t="n">
-        <v>13.0156987712007</v>
+        <v>13.01569877595917</v>
       </c>
       <c r="CD111" t="n">
-        <v>7.658411072075382</v>
+        <v>7.658411099386638</v>
       </c>
       <c r="CE111" t="inlineStr"/>
       <c r="CF111" t="n">
-        <v>11.26299136937092</v>
+        <v>11.26299136933968</v>
       </c>
       <c r="CG111" t="n">
-        <v>11.69661046635144</v>
+        <v>11.69661047807592</v>
       </c>
       <c r="CH111" t="n">
-        <v>10.52694941971629</v>
+        <v>10.52694943026833</v>
       </c>
       <c r="CI111" t="n">
         <v>6</v>
@@ -47764,10 +47692,10 @@
         <v>4.8</v>
       </c>
       <c r="CL111" t="n">
-        <v>-39.15057870543043</v>
+        <v>-39.15057864443601</v>
       </c>
       <c r="CM111" t="n">
-        <v>-34.89600077413283</v>
+        <v>-34.89600077431343</v>
       </c>
       <c r="CN111" t="inlineStr">
         <is>
@@ -48046,25 +47974,25 @@
         <v>14.89000034332275</v>
       </c>
       <c r="BX112" t="n">
-        <v>3.758596869667647</v>
+        <v>3.758596877973428</v>
       </c>
       <c r="BY112" t="n">
-        <v>4.772963283113373</v>
+        <v>4.772963292264071</v>
       </c>
       <c r="BZ112" t="n">
-        <v>14.24690999060298</v>
+        <v>14.24690998643413</v>
       </c>
       <c r="CA112" t="n">
         <v>37.21259872540951</v>
       </c>
       <c r="CB112" t="n">
-        <v>9.75989094981893</v>
+        <v>9.75989095739873</v>
       </c>
       <c r="CC112" t="n">
-        <v>48.40176703845619</v>
+        <v>48.40176703704979</v>
       </c>
       <c r="CD112" t="n">
-        <v>6.841742172203974</v>
+        <v>6.841742169258412</v>
       </c>
       <c r="CE112" t="n">
         <v>26.30873549612496</v>
@@ -48189,7 +48117,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S113" t="n">
@@ -48270,7 +48198,7 @@
         <v>0</v>
       </c>
       <c r="AT113" t="n">
-        <v>27077031936</v>
+        <v>27074949120</v>
       </c>
       <c r="AU113" t="n">
         <v>22.1</v>
@@ -48360,10 +48288,10 @@
         <v>14.59000015258789</v>
       </c>
       <c r="BX113" t="n">
-        <v>1.365432036473731</v>
+        <v>1.365432032350586</v>
       </c>
       <c r="BY113" t="n">
-        <v>2.532876427658771</v>
+        <v>2.532876420010337</v>
       </c>
       <c r="BZ113" t="n">
         <v>8.747398281528938</v>
@@ -48372,13 +48300,13 @@
         <v>10.76538622376811</v>
       </c>
       <c r="CB113" t="n">
-        <v>4.84227355709375</v>
+        <v>4.8422735593768</v>
       </c>
       <c r="CC113" t="n">
-        <v>7.692407064565328</v>
+        <v>7.692407065103281</v>
       </c>
       <c r="CD113" t="n">
-        <v>4.263639754999405</v>
+        <v>4.263639758076261</v>
       </c>
       <c r="CE113" t="n">
         <v>11.59703453110523</v>
@@ -48409,11 +48337,7 @@
       </c>
       <c r="CP113" t="inlineStr"/>
       <c r="CQ113" t="inlineStr"/>
-      <c r="CR113" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CR113" t="inlineStr"/>
       <c r="CS113" t="b">
         <v>0</v>
       </c>
@@ -48440,14 +48364,14 @@
         <v>0</v>
       </c>
       <c r="DB113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC113" t="b">
         <v>0</v>
       </c>
       <c r="DD113" t="inlineStr">
         <is>
-          <t>Rompimento (vol x1.5, +0.4% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -48588,7 +48512,7 @@
         <v>1</v>
       </c>
       <c r="AT114" t="n">
-        <v>44512468992</v>
+        <v>44763660288</v>
       </c>
       <c r="AU114" t="n">
         <v>3282.69</v>
@@ -48678,10 +48602,10 @@
         <v>18.73999977111816</v>
       </c>
       <c r="BX114" t="n">
-        <v>11.98337145240504</v>
+        <v>11.9833713566135</v>
       </c>
       <c r="BY114" t="n">
-        <v>14.95316350800107</v>
+        <v>14.95316338846989</v>
       </c>
       <c r="BZ114" t="inlineStr"/>
       <c r="CA114" t="inlineStr"/>
@@ -48813,7 +48737,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S115" t="n">
@@ -48984,10 +48908,10 @@
         <v>11.19999980926514</v>
       </c>
       <c r="BX115" t="n">
-        <v>2.433903117341507</v>
+        <v>2.433903120478429</v>
       </c>
       <c r="BY115" t="n">
-        <v>4.514890282668495</v>
+        <v>4.514890288487486</v>
       </c>
       <c r="BZ115" t="n">
         <v>12.16393421907894</v>
@@ -48996,13 +48920,13 @@
         <v>12.67500423009855</v>
       </c>
       <c r="CB115" t="n">
-        <v>9.610755191541845</v>
+        <v>9.610755189955004</v>
       </c>
       <c r="CC115" t="n">
-        <v>0.7923060956068846</v>
+        <v>0.7923060955652164</v>
       </c>
       <c r="CD115" t="n">
-        <v>6.737902846451845</v>
+        <v>6.737902843191704</v>
       </c>
       <c r="CE115" t="n">
         <v>7.386557878337924</v>
@@ -49033,11 +48957,7 @@
       </c>
       <c r="CP115" t="inlineStr"/>
       <c r="CQ115" t="inlineStr"/>
-      <c r="CR115" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CR115" t="inlineStr"/>
       <c r="CS115" t="b">
         <v>0</v>
       </c>
@@ -49064,14 +48984,14 @@
         <v>0</v>
       </c>
       <c r="DB115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC115" t="b">
         <v>0</v>
       </c>
       <c r="DD115" t="inlineStr">
         <is>
-          <t>Rompimento (vol x2.5, +0.2% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -49302,25 +49222,25 @@
         <v>8.619999885559082</v>
       </c>
       <c r="BX116" t="n">
-        <v>2.216774735453219</v>
+        <v>2.216774740299081</v>
       </c>
       <c r="BY116" t="n">
-        <v>2.406049517385029</v>
+        <v>2.406049521315887</v>
       </c>
       <c r="BZ116" t="n">
-        <v>3.211368492204878</v>
+        <v>3.211368490431377</v>
       </c>
       <c r="CA116" t="n">
         <v>9.959097165558408</v>
       </c>
       <c r="CB116" t="n">
-        <v>1.895418474803551</v>
+        <v>1.895418475424566</v>
       </c>
       <c r="CC116" t="n">
-        <v>5.911010295992655</v>
+        <v>5.911010295619697</v>
       </c>
       <c r="CD116" t="n">
-        <v>1.360559973796588</v>
+        <v>1.360559972137752</v>
       </c>
       <c r="CE116" t="n">
         <v>14.26044816361022</v>
@@ -49616,10 +49536,10 @@
         <v>4.760000228881836</v>
       </c>
       <c r="BX117" t="n">
-        <v>1.4641303596948</v>
+        <v>1.464130357333658</v>
       </c>
       <c r="BY117" t="n">
-        <v>1.525949197104136</v>
+        <v>1.525949194643301</v>
       </c>
       <c r="BZ117" t="inlineStr"/>
       <c r="CA117" t="inlineStr"/>
@@ -49920,10 +49840,10 @@
         <v>3.390000104904175</v>
       </c>
       <c r="BX118" t="n">
-        <v>1.669870098396955</v>
+        <v>1.669870097561353</v>
       </c>
       <c r="BY118" t="n">
-        <v>3.097609032526351</v>
+        <v>3.097609030976309</v>
       </c>
       <c r="BZ118" t="n">
         <v>1.164872961358411</v>
@@ -49932,7 +49852,7 @@
         <v>4.650949362890212</v>
       </c>
       <c r="CB118" t="n">
-        <v>1.617302452903407</v>
+        <v>1.617302452600024</v>
       </c>
       <c r="CC118" t="n">
         <v>0.7445919647652398</v>
@@ -50234,10 +50154,10 @@
         <v>6.460000038146973</v>
       </c>
       <c r="BX119" t="n">
-        <v>1.037970428246864</v>
+        <v>1.037970427203467</v>
       </c>
       <c r="BY119" t="n">
-        <v>1.925435144397932</v>
+        <v>1.925435142462432</v>
       </c>
       <c r="BZ119" t="inlineStr"/>
       <c r="CA119" t="inlineStr"/>
@@ -50538,25 +50458,25 @@
         <v>3.700000047683716</v>
       </c>
       <c r="BX120" t="n">
-        <v>1.267390789010424</v>
+        <v>1.267390785428824</v>
       </c>
       <c r="BY120" t="n">
-        <v>1.271032376598156</v>
+        <v>1.271032374317904</v>
       </c>
       <c r="BZ120" t="n">
-        <v>1.28102991066594</v>
+        <v>1.281029911987895</v>
       </c>
       <c r="CA120" t="n">
         <v>4.001025037561948</v>
       </c>
       <c r="CB120" t="n">
-        <v>0.8638811649149755</v>
+        <v>0.8638811647528889</v>
       </c>
       <c r="CC120" t="n">
-        <v>2.294169854416263</v>
+        <v>2.294169854706273</v>
       </c>
       <c r="CD120" t="n">
-        <v>0.481688973402217</v>
+        <v>0.4816889748236822</v>
       </c>
       <c r="CE120" t="n">
         <v>5.12793832390089</v>
@@ -50856,10 +50776,10 @@
         <v>5.409999847412109</v>
       </c>
       <c r="BX121" t="n">
-        <v>5.361728605183001</v>
+        <v>5.36172860650333</v>
       </c>
       <c r="BY121" t="n">
-        <v>7.80667684914645</v>
+        <v>7.80667685106885</v>
       </c>
       <c r="BZ121" t="inlineStr"/>
       <c r="CA121" t="inlineStr"/>
@@ -50868,13 +50788,13 @@
       <c r="CD121" t="inlineStr"/>
       <c r="CE121" t="inlineStr"/>
       <c r="CF121" t="n">
-        <v>6.584202727164725</v>
+        <v>6.58420272878609</v>
       </c>
       <c r="CG121" t="n">
-        <v>6.584202727164725</v>
+        <v>6.58420272878609</v>
       </c>
       <c r="CH121" t="n">
-        <v>5.925782454448253</v>
+        <v>5.925782455907481</v>
       </c>
       <c r="CI121" t="n">
         <v>2</v>
@@ -50886,10 +50806,10 @@
         <v>1.5</v>
       </c>
       <c r="CL121" t="n">
-        <v>9.533874705798183</v>
+        <v>9.533874732770986</v>
       </c>
       <c r="CM121" t="n">
-        <v>21.70430522866464</v>
+        <v>21.70430525863443</v>
       </c>
       <c r="CN121" t="inlineStr">
         <is>
@@ -51168,10 +51088,10 @@
         <v>5.269999980926514</v>
       </c>
       <c r="BX122" t="n">
-        <v>5.801133153124746</v>
+        <v>5.801133196078029</v>
       </c>
       <c r="BY122" t="n">
-        <v>10.34279137348674</v>
+        <v>10.34279145006779</v>
       </c>
       <c r="BZ122" t="inlineStr"/>
       <c r="CA122" t="inlineStr"/>
@@ -51180,13 +51100,13 @@
       <c r="CD122" t="inlineStr"/>
       <c r="CE122" t="inlineStr"/>
       <c r="CF122" t="n">
-        <v>8.071962263305744</v>
+        <v>8.07196232307291</v>
       </c>
       <c r="CG122" t="n">
-        <v>8.071962263305744</v>
+        <v>8.07196232307291</v>
       </c>
       <c r="CH122" t="n">
-        <v>7.26476603697517</v>
+        <v>7.264766090765619</v>
       </c>
       <c r="CI122" t="n">
         <v>2</v>
@@ -51198,10 +51118,10 @@
         <v>1.8</v>
       </c>
       <c r="CL122" t="n">
-        <v>37.85134844911249</v>
+        <v>37.85134946980413</v>
       </c>
       <c r="CM122" t="n">
-        <v>53.16816494345833</v>
+        <v>53.16816607756014</v>
       </c>
       <c r="CN122" t="inlineStr">
         <is>
@@ -51466,10 +51386,10 @@
         <v>21.95000076293945</v>
       </c>
       <c r="BX123" t="n">
-        <v>38.06062411340983</v>
+        <v>38.06062406536317</v>
       </c>
       <c r="BY123" t="n">
-        <v>70.60245773037522</v>
+        <v>70.60245764124868</v>
       </c>
       <c r="BZ123" t="n">
         <v>19.70443835426475</v>
@@ -51488,7 +51408,7 @@
       </c>
       <c r="CE123" t="inlineStr"/>
       <c r="CF123" t="n">
-        <v>25.7799120320791</v>
+        <v>25.77991202407132</v>
       </c>
       <c r="CG123" t="n">
         <v>22.95190064526047</v>
@@ -51509,7 +51429,7 @@
         <v>-5.891982402062723</v>
       </c>
       <c r="CM123" t="n">
-        <v>17.44834230532737</v>
+        <v>17.44834226884549</v>
       </c>
       <c r="CN123" t="inlineStr">
         <is>
@@ -51788,25 +51708,25 @@
         <v>9.100000381469727</v>
       </c>
       <c r="BX124" t="n">
-        <v>3.518982036514904</v>
+        <v>3.518982038263483</v>
       </c>
       <c r="BY124" t="n">
-        <v>3.631773237478435</v>
+        <v>3.631773239005058</v>
       </c>
       <c r="BZ124" t="n">
-        <v>4.384535776531583</v>
+        <v>4.38453577619596</v>
       </c>
       <c r="CA124" t="n">
         <v>18.92550581922768</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.447697295905024</v>
+        <v>3.447697296959124</v>
       </c>
       <c r="CC124" t="n">
-        <v>7.7420737526935</v>
+        <v>7.742073752622711</v>
       </c>
       <c r="CD124" t="n">
-        <v>1.732023302002726</v>
+        <v>1.732023301659585</v>
       </c>
       <c r="CE124" t="n">
         <v>21.41757303071974</v>
@@ -52102,10 +52022,10 @@
         <v>11.15999984741211</v>
       </c>
       <c r="BX125" t="n">
-        <v>0.7591834706241289</v>
+        <v>0.7591834708138702</v>
       </c>
       <c r="BY125" t="n">
-        <v>1.408285338007759</v>
+        <v>1.408285338359729</v>
       </c>
       <c r="BZ125" t="n">
         <v>15.56526294507478</v>
@@ -52114,13 +52034,13 @@
         <v>16.22873369395297</v>
       </c>
       <c r="CB125" t="n">
-        <v>13.68378210178593</v>
+        <v>13.68378210175316</v>
       </c>
       <c r="CC125" t="n">
-        <v>1.678348606168765</v>
+        <v>1.678348606164733</v>
       </c>
       <c r="CD125" t="n">
-        <v>11.03621634903477</v>
+        <v>11.03621634883841</v>
       </c>
       <c r="CE125" t="inlineStr"/>
       <c r="CF125" t="inlineStr"/>
@@ -52708,25 +52628,25 @@
         <v>18.48999977111816</v>
       </c>
       <c r="BX127" t="n">
-        <v>0.5757657336425892</v>
+        <v>0.5757657337118239</v>
       </c>
       <c r="BY127" t="n">
-        <v>0.7745288704914169</v>
+        <v>0.7745288705782761</v>
       </c>
       <c r="BZ127" t="n">
-        <v>4.617060898582309</v>
+        <v>4.617060898544895</v>
       </c>
       <c r="CA127" t="n">
         <v>11.54423087308652</v>
       </c>
       <c r="CB127" t="n">
-        <v>1.773095571709356</v>
+        <v>1.773095571696646</v>
       </c>
       <c r="CC127" t="n">
-        <v>0.6742713011333784</v>
+        <v>0.6742713011328634</v>
       </c>
       <c r="CD127" t="n">
-        <v>2.266491624460873</v>
+        <v>2.26649162443705</v>
       </c>
       <c r="CE127" t="n">
         <v>18.48999977111816</v>
@@ -53022,10 +52942,10 @@
         <v>5.130000114440918</v>
       </c>
       <c r="BX128" t="n">
-        <v>1.264825958412034</v>
+        <v>1.264825957329981</v>
       </c>
       <c r="BY128" t="n">
-        <v>2.116858717669595</v>
+        <v>2.116858715858631</v>
       </c>
       <c r="BZ128" t="inlineStr"/>
       <c r="CA128" t="inlineStr"/>
@@ -53036,13 +52956,13 @@
         <v>5.943594333110627</v>
       </c>
       <c r="CF128" t="n">
-        <v>1.690842338040814</v>
+        <v>1.690842336594306</v>
       </c>
       <c r="CG128" t="n">
-        <v>1.690842338040814</v>
+        <v>1.690842336594306</v>
       </c>
       <c r="CH128" t="n">
-        <v>1.521758104236733</v>
+        <v>1.521758102934875</v>
       </c>
       <c r="CI128" t="n">
         <v>2</v>
@@ -53054,10 +52974,10 @@
         <v>4.7</v>
       </c>
       <c r="CL128" t="n">
-        <v>-70.33609999436466</v>
+        <v>-70.33610001974199</v>
       </c>
       <c r="CM128" t="n">
-        <v>-67.04011110484961</v>
+        <v>-67.04011113304665</v>
       </c>
       <c r="CN128" t="inlineStr">
         <is>
@@ -53332,10 +53252,10 @@
         <v>17.71999931335449</v>
       </c>
       <c r="BX129" t="n">
-        <v>1.364999319226129</v>
+        <v>1.364999319509205</v>
       </c>
       <c r="BY129" t="n">
-        <v>1.987439008793244</v>
+        <v>1.987439009205403</v>
       </c>
       <c r="BZ129" t="inlineStr"/>
       <c r="CA129" t="inlineStr"/>
@@ -53638,37 +53558,37 @@
         <v>17.54000091552734</v>
       </c>
       <c r="BX130" t="n">
-        <v>2.112517293345417</v>
+        <v>2.112517292600691</v>
       </c>
       <c r="BY130" t="n">
-        <v>3.738730506413547</v>
+        <v>3.738730505695782</v>
       </c>
       <c r="BZ130" t="n">
-        <v>9.72075907753095</v>
+        <v>9.720759079091609</v>
       </c>
       <c r="CA130" t="n">
         <v>12.04994556632769</v>
       </c>
       <c r="CB130" t="n">
-        <v>5.63591393327144</v>
+        <v>5.635913933770431</v>
       </c>
       <c r="CC130" t="n">
-        <v>5.536636594831648</v>
+        <v>5.53663659489681</v>
       </c>
       <c r="CD130" t="n">
-        <v>4.781798821626722</v>
+        <v>4.781798822227684</v>
       </c>
       <c r="CE130" t="n">
         <v>15.86963380230276</v>
       </c>
       <c r="CF130" t="n">
-        <v>6.910630750000332</v>
+        <v>6.910630750335002</v>
       </c>
       <c r="CG130" t="n">
-        <v>5.586275264051544</v>
+        <v>5.58627526433362</v>
       </c>
       <c r="CH130" t="n">
-        <v>5.027647737646389</v>
+        <v>5.027647737900258</v>
       </c>
       <c r="CI130" t="n">
         <v>6</v>
@@ -53680,10 +53600,10 @@
         <v>7.5</v>
       </c>
       <c r="CL130" t="n">
-        <v>-71.33610333397617</v>
+        <v>-71.33610333252881</v>
       </c>
       <c r="CM130" t="n">
-        <v>-60.60073894361845</v>
+        <v>-60.60073894171041</v>
       </c>
       <c r="CN130" t="inlineStr">
         <is>
@@ -53799,7 +53719,7 @@
         </is>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T131" t="n">
         <v>7</v>
@@ -53849,7 +53769,7 @@
         <v>0</v>
       </c>
       <c r="AK131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL131" t="inlineStr"/>
       <c r="AM131" t="b">
@@ -53912,7 +53832,7 @@
       <c r="BH131" t="inlineStr"/>
       <c r="BI131" t="inlineStr"/>
       <c r="BJ131" t="n">
-        <v>1.2</v>
+        <v>108.1</v>
       </c>
       <c r="BK131" t="n">
         <v>11.2</v>
@@ -53954,10 +53874,10 @@
         <v>4.170000076293945</v>
       </c>
       <c r="BX131" t="n">
-        <v>0.8773866917954516</v>
+        <v>0.8773866916069349</v>
       </c>
       <c r="BY131" t="n">
-        <v>0.9711573944810906</v>
+        <v>1.627552312930864</v>
       </c>
       <c r="BZ131" t="inlineStr"/>
       <c r="CA131" t="inlineStr"/>
@@ -53966,13 +53886,13 @@
       <c r="CD131" t="inlineStr"/>
       <c r="CE131" t="inlineStr"/>
       <c r="CF131" t="n">
-        <v>0.9242720431382712</v>
+        <v>1.2524695022689</v>
       </c>
       <c r="CG131" t="n">
-        <v>0.9242720431382712</v>
+        <v>1.2524695022689</v>
       </c>
       <c r="CH131" t="n">
-        <v>0.831844838824444</v>
+        <v>1.12722255204201</v>
       </c>
       <c r="CI131" t="n">
         <v>2</v>
@@ -53981,13 +53901,13 @@
         <v>1</v>
       </c>
       <c r="CK131" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="CL131" t="n">
-        <v>-80.05168288716821</v>
+        <v>-72.96828461826266</v>
       </c>
       <c r="CM131" t="n">
-        <v>-77.83520320796467</v>
+        <v>-69.9647606869585</v>
       </c>
       <c r="CN131" t="inlineStr">
         <is>
@@ -54268,10 +54188,10 @@
         <v>1.220000028610229</v>
       </c>
       <c r="BX132" t="n">
-        <v>0.3581979141752629</v>
+        <v>0.358197914138901</v>
       </c>
       <c r="BY132" t="n">
-        <v>0.6644571307951127</v>
+        <v>0.6644571307276613</v>
       </c>
       <c r="BZ132" t="inlineStr"/>
       <c r="CA132" t="inlineStr"/>
@@ -54280,13 +54200,13 @@
       <c r="CD132" t="inlineStr"/>
       <c r="CE132" t="inlineStr"/>
       <c r="CF132" t="n">
-        <v>0.5113275224851879</v>
+        <v>0.5113275224332812</v>
       </c>
       <c r="CG132" t="n">
-        <v>0.5113275224851879</v>
+        <v>0.5113275224332812</v>
       </c>
       <c r="CH132" t="n">
-        <v>0.4601947702366691</v>
+        <v>0.4601947701899531</v>
       </c>
       <c r="CI132" t="n">
         <v>2</v>
@@ -54298,10 +54218,10 @@
         <v>1.9</v>
       </c>
       <c r="CL132" t="n">
-        <v>-62.27911807830835</v>
+        <v>-62.27911808213753</v>
       </c>
       <c r="CM132" t="n">
-        <v>-58.08790897589816</v>
+        <v>-58.08790898015281</v>
       </c>
       <c r="CN132" t="inlineStr">
         <is>
@@ -54888,10 +54808,10 @@
         <v>36.83000183105469</v>
       </c>
       <c r="BX134" t="n">
-        <v>8.295373687028825</v>
+        <v>8.295373679871677</v>
       </c>
       <c r="BY134" t="n">
-        <v>12.07806408831397</v>
+        <v>12.07806407789316</v>
       </c>
       <c r="BZ134" t="n">
         <v>7.91388469097043</v>
@@ -55198,10 +55118,10 @@
         <v>5.510000228881836</v>
       </c>
       <c r="BX135" t="n">
-        <v>1.050454203757355</v>
+        <v>1.050454203741841</v>
       </c>
       <c r="BY135" t="n">
-        <v>1.948592547969894</v>
+        <v>1.948592547941116</v>
       </c>
       <c r="BZ135" t="inlineStr"/>
       <c r="CA135" t="inlineStr"/>
@@ -55212,13 +55132,13 @@
         <v>2.947784849753326</v>
       </c>
       <c r="CF135" t="n">
-        <v>1.982277200493525</v>
+        <v>1.982277200478761</v>
       </c>
       <c r="CG135" t="n">
-        <v>1.948592547969894</v>
+        <v>1.948592547941116</v>
       </c>
       <c r="CH135" t="n">
-        <v>1.753733293172904</v>
+        <v>1.753733293147004</v>
       </c>
       <c r="CI135" t="n">
         <v>3</v>
@@ -55230,10 +55150,10 @@
         <v>2.8</v>
       </c>
       <c r="CL135" t="n">
-        <v>-68.17181088341269</v>
+        <v>-68.17181088388276</v>
       </c>
       <c r="CM135" t="n">
-        <v>-64.02400874499064</v>
+        <v>-64.02400874525858</v>
       </c>
       <c r="CN135" t="inlineStr">
         <is>
@@ -55512,25 +55432,25 @@
         <v>4.909999847412109</v>
       </c>
       <c r="BX136" t="n">
-        <v>1.524384742263154</v>
+        <v>1.524384745951984</v>
       </c>
       <c r="BY136" t="n">
-        <v>1.685994553482747</v>
+        <v>1.685994556665972</v>
       </c>
       <c r="BZ136" t="n">
-        <v>2.489703120966195</v>
+        <v>2.489703119642068</v>
       </c>
       <c r="CA136" t="n">
         <v>7.747739573095417</v>
       </c>
       <c r="CB136" t="n">
-        <v>1.74519127787438</v>
+        <v>1.745191279283468</v>
       </c>
       <c r="CC136" t="n">
-        <v>1.782241841918749</v>
+        <v>1.782241841812248</v>
       </c>
       <c r="CD136" t="n">
-        <v>1.077858513699254</v>
+        <v>1.077858512501417</v>
       </c>
       <c r="CE136" t="n">
         <v>0.3949753537697956</v>
@@ -55824,10 +55744,10 @@
         <v>2.049999952316284</v>
       </c>
       <c r="BX137" t="n">
-        <v>0.5755235842397404</v>
+        <v>0.5755235840252012</v>
       </c>
       <c r="BY137" t="n">
-        <v>0.8379623386530621</v>
+        <v>0.8379623383406929</v>
       </c>
       <c r="BZ137" t="n">
         <v>0.3540939960818694</v>
@@ -55890,7 +55810,7 @@
         <v>2.499997615814209</v>
       </c>
       <c r="CZ137" t="n">
-        <v>-51.81496460226393</v>
+        <v>-51.81497002814127</v>
       </c>
       <c r="DA137" t="b">
         <v>0</v>
@@ -56132,10 +56052,10 @@
         <v>6.699999809265137</v>
       </c>
       <c r="BX138" t="n">
-        <v>1.838647097934396</v>
+        <v>1.838647083223697</v>
       </c>
       <c r="BY138" t="n">
-        <v>2.677070174592481</v>
+        <v>2.677070153173703</v>
       </c>
       <c r="BZ138" t="n">
         <v>1.700341581658307</v>
@@ -57624,10 +57544,10 @@
         <v>18.55999946594238</v>
       </c>
       <c r="BX143" t="n">
-        <v>28.21640533499345</v>
+        <v>28.2164053155272</v>
       </c>
       <c r="BY143" t="n">
-        <v>37.74728002592457</v>
+        <v>37.74727999988306</v>
       </c>
       <c r="BZ143" t="n">
         <v>2.525289847755857</v>
@@ -57636,7 +57556,7 @@
         <v>7.003524063352925</v>
       </c>
       <c r="CB143" t="n">
-        <v>6.4704780432995</v>
+        <v>6.470478039419</v>
       </c>
       <c r="CC143" t="n">
         <v>3.046690502845772</v>
@@ -57938,10 +57858,10 @@
         <v>3.710000038146973</v>
       </c>
       <c r="BX144" t="n">
-        <v>0.671083565987049</v>
+        <v>0.6710835678206811</v>
       </c>
       <c r="BY144" t="n">
-        <v>1.244860014905976</v>
+        <v>1.244860018307364</v>
       </c>
       <c r="BZ144" t="inlineStr"/>
       <c r="CA144" t="inlineStr"/>
@@ -57952,13 +57872,13 @@
         <v>3.377764827421347</v>
       </c>
       <c r="CF144" t="n">
-        <v>0.9579717904465124</v>
+        <v>0.9579717930640224</v>
       </c>
       <c r="CG144" t="n">
-        <v>0.9579717904465124</v>
+        <v>0.9579717930640224</v>
       </c>
       <c r="CH144" t="n">
-        <v>0.8621746114018611</v>
+        <v>0.8621746137576202</v>
       </c>
       <c r="CI144" t="n">
         <v>2</v>
@@ -57970,10 +57890,10 @@
         <v>5</v>
       </c>
       <c r="CL144" t="n">
-        <v>-76.76079238445264</v>
+        <v>-76.76079232095509</v>
       </c>
       <c r="CM144" t="n">
-        <v>-74.17865820494738</v>
+        <v>-74.17865813439455</v>
       </c>
       <c r="CN144" t="inlineStr">
         <is>
@@ -58250,10 +58170,10 @@
         <v>18.70999908447266</v>
       </c>
       <c r="BX145" t="n">
-        <v>9.483425386933316</v>
+        <v>9.48342545509354</v>
       </c>
       <c r="BY145" t="n">
-        <v>13.80786736337491</v>
+        <v>13.8078674626162</v>
       </c>
       <c r="BZ145" t="n">
         <v>4.677499771118164</v>
@@ -58703,7 +58623,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Rompimento</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="S147" t="n">
@@ -58913,11 +58833,7 @@
       </c>
       <c r="CP147" t="inlineStr"/>
       <c r="CQ147" t="inlineStr"/>
-      <c r="CR147" t="inlineStr">
-        <is>
-          <t>Rompimento</t>
-        </is>
-      </c>
+      <c r="CR147" t="inlineStr"/>
       <c r="CS147" t="b">
         <v>0</v>
       </c>
@@ -58944,14 +58860,14 @@
         <v>0</v>
       </c>
       <c r="DB147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC147" t="b">
         <v>0</v>
       </c>
       <c r="DD147" t="inlineStr">
         <is>
-          <t>Rompimento (vol x0.7, +1.1% do topo, MM50&gt;MM200)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -59182,10 +59098,10 @@
         <v>10.85000038146973</v>
       </c>
       <c r="BX148" t="n">
-        <v>5.797173326530743</v>
+        <v>5.79717331217266</v>
       </c>
       <c r="BY148" t="n">
-        <v>10.61097428878331</v>
+        <v>10.6109742625027</v>
       </c>
       <c r="BZ148" t="inlineStr"/>
       <c r="CA148" t="inlineStr"/>
@@ -59196,13 +59112,13 @@
         <v>3.235701042926842</v>
       </c>
       <c r="CF148" t="n">
-        <v>6.547949552746964</v>
+        <v>6.547949539200733</v>
       </c>
       <c r="CG148" t="n">
-        <v>5.797173326530743</v>
+        <v>5.79717331217266</v>
       </c>
       <c r="CH148" t="n">
-        <v>5.217455993877668</v>
+        <v>5.217455980955394</v>
       </c>
       <c r="CI148" t="n">
         <v>3</v>
@@ -59214,10 +59130,10 @@
         <v>3.3</v>
       </c>
       <c r="CL148" t="n">
-        <v>-51.91284967336638</v>
+        <v>-51.91284979246568</v>
       </c>
       <c r="CM148" t="n">
-        <v>-39.65023665870151</v>
+        <v>-39.65023678355155</v>
       </c>
       <c r="CN148" t="inlineStr">
         <is>
@@ -59398,13 +59314,13 @@
         <v>1</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AS149" t="b">
         <v>1</v>
       </c>
       <c r="AT149" t="n">
-        <v>50658746368</v>
+        <v>50465071104</v>
       </c>
       <c r="AU149" t="n">
         <v>53.28</v>
@@ -59810,10 +59726,10 @@
         <v>15.02999973297119</v>
       </c>
       <c r="BX150" t="n">
-        <v>3.845120466476121</v>
+        <v>3.845120467290324</v>
       </c>
       <c r="BY150" t="n">
-        <v>5.598495399189233</v>
+        <v>5.598495400374712</v>
       </c>
       <c r="BZ150" t="inlineStr"/>
       <c r="CA150" t="inlineStr"/>
@@ -59824,7 +59740,7 @@
         <v>5.387818010858983</v>
       </c>
       <c r="CF150" t="n">
-        <v>4.943811292174779</v>
+        <v>4.94381129284134</v>
       </c>
       <c r="CG150" t="n">
         <v>5.387818010858983</v>
@@ -59845,7 +59761,7 @@
         <v>-67.7376161282572</v>
       </c>
       <c r="CM150" t="n">
-        <v>-67.10704337985064</v>
+        <v>-67.10704337541577</v>
       </c>
       <c r="CN150" t="inlineStr">
         <is>
